--- a/data/research/lol.xlsx
+++ b/data/research/lol.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO19" headerRowCount="1">
-  <autoFilter ref="A1:CO19"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO22" headerRowCount="1">
+  <autoFilter ref="A1:CO22"/>
   <tableColumns count="93">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -752,19 +752,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$19)</f>
+        <f>COUNTA('Picks'!$A$2:$A$22)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$19,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$22,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$19,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$22,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$19,"settled",'Picks'!$V$2:$V$19,"win")+COUNTIFS('Picks'!$U$2:$U$19,"settled",'Picks'!$V$2:$V$19,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$22,"settled",'Picks'!$V$2:$V$22,"win")+COUNTIFS('Picks'!$U$2:$U$22,"settled",'Picks'!$V$2:$V$22,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -792,19 +792,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$19,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$22,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$19,"&gt;0",'Picks'!$V$2:$V$19,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$19,"&gt;0",'Picks'!$V$2:$V$19,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$22,"&gt;0",'Picks'!$V$2:$V$22,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$22,"&gt;0",'Picks'!$V$2:$V$22,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$19,"&gt;0",'Picks'!$V$2:$V$19,"win")/(COUNTIFS('Picks'!$BX$2:$BX$19,"&gt;0",'Picks'!$V$2:$V$19,"win")+COUNTIFS('Picks'!$BX$2:$BX$19,"&gt;0",'Picks'!$V$2:$V$19,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$22,"&gt;0",'Picks'!$V$2:$V$22,"win")/(COUNTIFS('Picks'!$BX$2:$BX$22,"&gt;0",'Picks'!$V$2:$V$22,"win")+COUNTIFS('Picks'!$BX$2:$BX$22,"&gt;0",'Picks'!$V$2:$V$22,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$19)/SUM('Picks'!$BX$2:$BX$19),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$22)/SUM('Picks'!$BX$2:$BX$22),0)</f>
         <v/>
       </c>
     </row>
@@ -832,19 +832,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$19)</f>
+        <f>SUM('Picks'!$BY$2:$BY$22)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$19,"&lt;&gt;",'Picks'!$AB$2:$AB$19),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$22,"&lt;&gt;",'Picks'!$AB$2:$AB$22),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$19,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$19,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$22,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$22,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$19,'Picks'!$AM$2:$AM$19,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$22,'Picks'!$AM$2:$AM$22,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -899,15 +899,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$19,$A14,'Picks'!$U$2:$U$19,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$22,$A14,'Picks'!$U$2:$U$22,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$19,$A14,'Picks'!$U$2:$U$19,"settled",'Picks'!$V$2:$V$19,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$22,$A14,'Picks'!$U$2:$U$22,"settled",'Picks'!$V$2:$V$22,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$19,$A14,'Picks'!$U$2:$U$19,"settled",'Picks'!$V$2:$V$19,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$22,$A14,'Picks'!$U$2:$U$22,"settled",'Picks'!$V$2:$V$22,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -915,11 +915,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$19,'Picks'!$H$2:$H$19,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$22,'Picks'!$H$2:$H$22,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$19,'Picks'!$H$2:$H$19,$A14,'Picks'!$U$2:$U$19,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$22,'Picks'!$H$2:$H$22,$A14,'Picks'!$U$2:$U$22,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -930,15 +930,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$19,$A15,'Picks'!$U$2:$U$19,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$22,$A15,'Picks'!$U$2:$U$22,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$19,$A15,'Picks'!$U$2:$U$19,"settled",'Picks'!$V$2:$V$19,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$22,$A15,'Picks'!$U$2:$U$22,"settled",'Picks'!$V$2:$V$22,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$19,$A15,'Picks'!$U$2:$U$19,"settled",'Picks'!$V$2:$V$19,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$22,$A15,'Picks'!$U$2:$U$22,"settled",'Picks'!$V$2:$V$22,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -946,11 +946,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$19,'Picks'!$H$2:$H$19,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$22,'Picks'!$H$2:$H$22,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$19,'Picks'!$H$2:$H$19,$A15,'Picks'!$U$2:$U$19,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$22,'Picks'!$H$2:$H$22,$A15,'Picks'!$U$2:$U$22,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -961,15 +961,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$19,$A16,'Picks'!$U$2:$U$19,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$22,$A16,'Picks'!$U$2:$U$22,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$19,$A16,'Picks'!$U$2:$U$19,"settled",'Picks'!$V$2:$V$19,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$22,$A16,'Picks'!$U$2:$U$22,"settled",'Picks'!$V$2:$V$22,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$19,$A16,'Picks'!$U$2:$U$19,"settled",'Picks'!$V$2:$V$19,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$22,$A16,'Picks'!$U$2:$U$22,"settled",'Picks'!$V$2:$V$22,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -977,11 +977,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$19,'Picks'!$H$2:$H$19,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$22,'Picks'!$H$2:$H$22,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$19,'Picks'!$H$2:$H$19,$A16,'Picks'!$U$2:$U$19,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$22,'Picks'!$H$2:$H$22,$A16,'Picks'!$U$2:$U$22,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO19"/>
+  <dimension ref="A1:CO22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3039,18 +3039,32 @@
       </c>
       <c r="U7" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V7" s="24" t="n"/>
-      <c r="W7" s="26" t="n"/>
-      <c r="X7" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V7" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W7" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y7" s="25" t="n"/>
       <c r="Z7" s="26" t="n"/>
       <c r="AA7" s="28" t="n"/>
       <c r="AB7" s="28" t="n"/>
-      <c r="AC7" s="30" t="n"/>
-      <c r="AD7" s="24" t="n"/>
+      <c r="AC7" s="30" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="AD7" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T01:51:59.451937Z</t>
+        </is>
+      </c>
       <c r="AE7" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.4000 (market_slug=aec-lol-g2-kc-2026-07-26).</t>
@@ -3300,18 +3314,32 @@
       </c>
       <c r="U8" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V8" s="24" t="n"/>
-      <c r="W8" s="26" t="n"/>
-      <c r="X8" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V8" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W8" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y8" s="25" t="n"/>
       <c r="Z8" s="26" t="n"/>
       <c r="AA8" s="28" t="n"/>
       <c r="AB8" s="28" t="n"/>
-      <c r="AC8" s="30" t="n"/>
-      <c r="AD8" s="24" t="n"/>
+      <c r="AC8" s="30" t="n">
+        <v>1.3889</v>
+      </c>
+      <c r="AD8" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T01:52:01.961047Z</t>
+        </is>
+      </c>
       <c r="AE8" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-lol-tl-c9-2026-07-26).</t>
@@ -3483,12 +3511,12 @@
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
         <is>
-          <t>5b1e9280f54a4e88</t>
+          <t>609696ae2e8245cf</t>
         </is>
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:32:06.087195Z</t>
+          <t>2026-07-26T20:10:52.122105Z</t>
         </is>
       </c>
       <c r="C9" s="24" t="inlineStr">
@@ -3561,18 +3589,32 @@
       </c>
       <c r="U9" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V9" s="24" t="n"/>
-      <c r="W9" s="26" t="n"/>
-      <c r="X9" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V9" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W9" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y9" s="25" t="n"/>
       <c r="Z9" s="26" t="n"/>
       <c r="AA9" s="28" t="n"/>
       <c r="AB9" s="28" t="n"/>
-      <c r="AC9" s="30" t="n"/>
-      <c r="AD9" s="24" t="n"/>
+      <c r="AC9" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T01:52:03.138650Z</t>
+        </is>
+      </c>
       <c r="AE9" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-lol-sr-dsg-2026-07-26).</t>
@@ -3694,7 +3736,7 @@
       </c>
       <c r="BH9" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:31:54.940088Z</t>
+          <t>2026-07-26T20:10:41.893354Z</t>
         </is>
       </c>
       <c r="BI9" s="24" t="inlineStr">
@@ -3744,22 +3786,22 @@
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
         <is>
-          <t>02d7b3eb10fb4e4e</t>
+          <t>fd1d1301189448ab</t>
         </is>
       </c>
       <c r="B10" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:32:06.087195Z</t>
+          <t>2026-07-27T05:24:25.946584Z</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T06:00:00Z</t>
+          <t>2026-07-27T06:45:00Z</t>
         </is>
       </c>
       <c r="D10" s="24" t="inlineStr">
         <is>
-          <t>60701</t>
+          <t>60706</t>
         </is>
       </c>
       <c r="E10" s="24" t="inlineStr">
@@ -3769,12 +3811,12 @@
       </c>
       <c r="F10" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>Hanwha Life Esports</t>
         </is>
       </c>
       <c r="G10" s="24" t="inlineStr">
         <is>
-          <t>BNK FEARX</t>
+          <t>Dplus KIA</t>
         </is>
       </c>
       <c r="H10" s="24" t="inlineStr">
@@ -3794,26 +3836,26 @@
         </is>
       </c>
       <c r="L10" s="26" t="n">
-        <v>-113</v>
+        <v>-194</v>
       </c>
       <c r="M10" s="27" t="n">
-        <v>1.884956</v>
+        <v>1.515464</v>
       </c>
       <c r="N10" s="28" t="n">
-        <v>0.530516</v>
+        <v>0.659864</v>
       </c>
       <c r="O10" s="28" t="n">
-        <v>0.811601</v>
+        <v>0.608349</v>
       </c>
       <c r="P10" s="28" t="n"/>
       <c r="Q10" s="28" t="n">
-        <v>0.281085</v>
+        <v>-0.051515</v>
       </c>
       <c r="R10" s="26" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S10" s="29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T10" s="24" t="inlineStr">
         <is>
@@ -3822,21 +3864,35 @@
       </c>
       <c r="U10" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V10" s="24" t="n"/>
-      <c r="W10" s="26" t="n"/>
-      <c r="X10" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V10" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W10" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y10" s="25" t="n"/>
       <c r="Z10" s="26" t="n"/>
       <c r="AA10" s="28" t="n"/>
       <c r="AB10" s="28" t="n"/>
-      <c r="AC10" s="30" t="n"/>
-      <c r="AD10" s="24" t="n"/>
+      <c r="AC10" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T10:24:44.763051Z</t>
+        </is>
+      </c>
       <c r="AE10" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5300 (market_slug=aec-lol-bfx-gen-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.6600 (market_slug=aec-lol-dk-hle-2026-07-27).</t>
         </is>
       </c>
       <c r="AF10" s="31" t="inlineStr">
@@ -3854,7 +3910,7 @@
       <c r="AJ10" s="31" t="n"/>
       <c r="AK10" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL10" s="26" t="n">
@@ -3862,47 +3918,47 @@
       </c>
       <c r="AM10" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN10" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO10" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP10" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>Hanwha Life Esports</t>
         </is>
       </c>
       <c r="AQ10" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>Hanwha Life Esports</t>
         </is>
       </c>
       <c r="AR10" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>Hanwha Life Esports</t>
         </is>
       </c>
       <c r="AS10" s="24" t="inlineStr">
         <is>
-          <t>BNK FEARX</t>
+          <t>Dplus KIA</t>
         </is>
       </c>
       <c r="AT10" s="24" t="inlineStr">
         <is>
-          <t>BNK FEARX</t>
+          <t>Dplus KIA</t>
         </is>
       </c>
       <c r="AU10" s="24" t="inlineStr">
         <is>
-          <t>BNK FEARX</t>
+          <t>Dplus KIA</t>
         </is>
       </c>
       <c r="AV10" s="24" t="n"/>
@@ -3955,7 +4011,7 @@
       </c>
       <c r="BH10" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:31:55.452705Z</t>
+          <t>2026-07-27T05:24:02.567595Z</t>
         </is>
       </c>
       <c r="BI10" s="24" t="inlineStr">
@@ -3965,13 +4021,13 @@
       </c>
       <c r="BJ10" s="25" t="n"/>
       <c r="BK10" s="26" t="n">
-        <v>-113</v>
+        <v>-194</v>
       </c>
       <c r="BL10" s="27" t="n">
-        <v>1.884956</v>
+        <v>1.515464</v>
       </c>
       <c r="BM10" s="28" t="n">
-        <v>0.530516</v>
+        <v>0.659864</v>
       </c>
       <c r="BN10" s="28" t="n"/>
       <c r="BO10" s="28" t="n"/>
@@ -4005,22 +4061,22 @@
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
         <is>
-          <t>c7da7f12c0aa45f4</t>
+          <t>75fe356302e240e0</t>
         </is>
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:32:06.087195Z</t>
+          <t>2026-07-27T17:37:52.168845Z</t>
         </is>
       </c>
       <c r="C11" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T06:45:00Z</t>
+          <t>2026-07-27T18:00:00Z</t>
         </is>
       </c>
       <c r="D11" s="24" t="inlineStr">
         <is>
-          <t>60706</t>
+          <t>60818</t>
         </is>
       </c>
       <c r="E11" s="24" t="inlineStr">
@@ -4030,12 +4086,12 @@
       </c>
       <c r="F11" s="24" t="inlineStr">
         <is>
-          <t>Hanwha Life Esports</t>
+          <t>Bulldog Esports</t>
         </is>
       </c>
       <c r="G11" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA</t>
+          <t>Arctic Pandas</t>
         </is>
       </c>
       <c r="H11" s="24" t="inlineStr">
@@ -4045,7 +4101,7 @@
       </c>
       <c r="I11" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J11" s="25" t="n"/>
@@ -4055,49 +4111,63 @@
         </is>
       </c>
       <c r="L11" s="26" t="n">
-        <v>-170</v>
+        <v>-104</v>
       </c>
       <c r="M11" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.961538</v>
       </c>
       <c r="N11" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.509804</v>
       </c>
       <c r="O11" s="28" t="n">
-        <v>0.608349</v>
+        <v>0.596094</v>
       </c>
       <c r="P11" s="28" t="n"/>
       <c r="Q11" s="28" t="n">
-        <v>-0.021281</v>
+        <v>0.08629000000000001</v>
       </c>
       <c r="R11" s="26" t="n">
-        <v>9</v>
+        <v>63</v>
       </c>
       <c r="S11" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T11" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U11" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V11" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W11" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="T11" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U11" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V11" s="24" t="n"/>
-      <c r="W11" s="26" t="n"/>
-      <c r="X11" s="26" t="n"/>
       <c r="Y11" s="25" t="n"/>
       <c r="Z11" s="26" t="n"/>
       <c r="AA11" s="28" t="n"/>
       <c r="AB11" s="28" t="n"/>
-      <c r="AC11" s="30" t="n"/>
-      <c r="AD11" s="24" t="n"/>
+      <c r="AC11" s="30" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD11" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T19:47:25.392207Z</t>
+        </is>
+      </c>
       <c r="AE11" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-lol-dk-hle-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-lol-ap-bld-2026-07-27).</t>
         </is>
       </c>
       <c r="AF11" s="31" t="inlineStr">
@@ -4107,7 +4177,7 @@
       </c>
       <c r="AG11" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH11" s="24" t="n"/>
@@ -4115,7 +4185,7 @@
       <c r="AJ11" s="31" t="n"/>
       <c r="AK11" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL11" s="26" t="n">
@@ -4123,47 +4193,47 @@
       </c>
       <c r="AM11" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN11" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO11" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP11" s="24" t="inlineStr">
         <is>
-          <t>Hanwha Life Esports</t>
+          <t>Bulldog Esports</t>
         </is>
       </c>
       <c r="AQ11" s="24" t="inlineStr">
         <is>
-          <t>Hanwha Life Esports</t>
+          <t>Bulldog Esports</t>
         </is>
       </c>
       <c r="AR11" s="24" t="inlineStr">
         <is>
-          <t>Hanwha Life Esports</t>
+          <t>Bulldog Esports</t>
         </is>
       </c>
       <c r="AS11" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA</t>
+          <t>Arctic Pandas</t>
         </is>
       </c>
       <c r="AT11" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA</t>
+          <t>Arctic Pandas</t>
         </is>
       </c>
       <c r="AU11" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA</t>
+          <t>Arctic Pandas</t>
         </is>
       </c>
       <c r="AV11" s="24" t="n"/>
@@ -4181,7 +4251,7 @@
       </c>
       <c r="BA11" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>181f161eadbc9c7936d57f0cb930b26b3363dbf664c19f1b39e954282aa7d3a8</t>
         </is>
       </c>
       <c r="BB11" s="24" t="inlineStr">
@@ -4196,7 +4266,7 @@
       </c>
       <c r="BD11" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>181f161eadbc9c7936d57f0cb930b26b3363dbf664c19f1b39e954282aa7d3a8</t>
         </is>
       </c>
       <c r="BE11" s="24" t="inlineStr">
@@ -4216,7 +4286,7 @@
       </c>
       <c r="BH11" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:31:56.010815Z</t>
+          <t>2026-07-27T17:37:32.913782Z</t>
         </is>
       </c>
       <c r="BI11" s="24" t="inlineStr">
@@ -4226,13 +4296,13 @@
       </c>
       <c r="BJ11" s="25" t="n"/>
       <c r="BK11" s="26" t="n">
-        <v>-170</v>
+        <v>-104</v>
       </c>
       <c r="BL11" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.961538</v>
       </c>
       <c r="BM11" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.509804</v>
       </c>
       <c r="BN11" s="28" t="n"/>
       <c r="BO11" s="28" t="n"/>
@@ -4266,22 +4336,22 @@
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
         <is>
-          <t>76183b9887974cfc</t>
+          <t>ca40c6c8e3314622</t>
         </is>
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:32:06.087195Z</t>
+          <t>2026-07-27T19:51:04.764967Z</t>
         </is>
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T07:30:00Z</t>
+          <t>2026-07-27T21:00:00Z</t>
         </is>
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>60707</t>
+          <t>61044</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
@@ -4291,12 +4361,12 @@
       </c>
       <c r="F12" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>Ei Nerd Esports</t>
         </is>
       </c>
       <c r="G12" s="24" t="inlineStr">
         <is>
-          <t>KT Rolster</t>
+          <t>paiN Gaming Academy</t>
         </is>
       </c>
       <c r="H12" s="24" t="inlineStr">
@@ -4306,7 +4376,7 @@
       </c>
       <c r="I12" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J12" s="25" t="n"/>
@@ -4316,23 +4386,23 @@
         </is>
       </c>
       <c r="L12" s="26" t="n">
-        <v>122</v>
+        <v>-178</v>
       </c>
       <c r="M12" s="27" t="n">
-        <v>2.22</v>
+        <v>1.561798</v>
       </c>
       <c r="N12" s="28" t="n">
-        <v>0.45045</v>
+        <v>0.640288</v>
       </c>
       <c r="O12" s="28" t="n">
-        <v>0.7097250000000001</v>
+        <v>0.654099</v>
       </c>
       <c r="P12" s="28" t="n"/>
       <c r="Q12" s="28" t="n">
-        <v>0.259275</v>
+        <v>0.013811</v>
       </c>
       <c r="R12" s="26" t="n">
-        <v>100</v>
+        <v>27</v>
       </c>
       <c r="S12" s="29" t="n">
         <v>2</v>
@@ -4344,21 +4414,35 @@
       </c>
       <c r="U12" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V12" s="24" t="n"/>
-      <c r="W12" s="26" t="n"/>
-      <c r="X12" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V12" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W12" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y12" s="25" t="n"/>
       <c r="Z12" s="26" t="n"/>
       <c r="AA12" s="28" t="n"/>
       <c r="AB12" s="28" t="n"/>
-      <c r="AC12" s="30" t="n"/>
-      <c r="AD12" s="24" t="n"/>
+      <c r="AC12" s="30" t="n">
+        <v>1.1236</v>
+      </c>
+      <c r="AD12" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T22:51:53.746120Z</t>
+        </is>
+      </c>
       <c r="AE12" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-lol-kt-gen-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-lol-pnga-nerd-2026-07-27).</t>
         </is>
       </c>
       <c r="AF12" s="31" t="inlineStr">
@@ -4399,32 +4483,32 @@
       </c>
       <c r="AP12" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>Ei Nerd Esports</t>
         </is>
       </c>
       <c r="AQ12" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>Ei Nerd Esports</t>
         </is>
       </c>
       <c r="AR12" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>Ei Nerd Esports</t>
         </is>
       </c>
       <c r="AS12" s="24" t="inlineStr">
         <is>
-          <t>KT Rolster</t>
+          <t>paiN Gaming Academy</t>
         </is>
       </c>
       <c r="AT12" s="24" t="inlineStr">
         <is>
-          <t>KT Rolster</t>
+          <t>paiN Gaming Academy</t>
         </is>
       </c>
       <c r="AU12" s="24" t="inlineStr">
         <is>
-          <t>KT Rolster</t>
+          <t>paiN Gaming Academy</t>
         </is>
       </c>
       <c r="AV12" s="24" t="n"/>
@@ -4442,7 +4526,7 @@
       </c>
       <c r="BA12" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>a1ec01e655fe8c74e1a10624d033e1ed3a28f75c65521824090c359f6c375c81</t>
         </is>
       </c>
       <c r="BB12" s="24" t="inlineStr">
@@ -4457,7 +4541,7 @@
       </c>
       <c r="BD12" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>a1ec01e655fe8c74e1a10624d033e1ed3a28f75c65521824090c359f6c375c81</t>
         </is>
       </c>
       <c r="BE12" s="24" t="inlineStr">
@@ -4477,7 +4561,7 @@
       </c>
       <c r="BH12" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:31:56.520012Z</t>
+          <t>2026-07-27T19:50:48.466474Z</t>
         </is>
       </c>
       <c r="BI12" s="24" t="inlineStr">
@@ -4487,13 +4571,13 @@
       </c>
       <c r="BJ12" s="25" t="n"/>
       <c r="BK12" s="26" t="n">
-        <v>122</v>
+        <v>-178</v>
       </c>
       <c r="BL12" s="27" t="n">
-        <v>2.22</v>
+        <v>1.561798</v>
       </c>
       <c r="BM12" s="28" t="n">
-        <v>0.45045</v>
+        <v>0.640288</v>
       </c>
       <c r="BN12" s="28" t="n"/>
       <c r="BO12" s="28" t="n"/>
@@ -4527,22 +4611,22 @@
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
         <is>
-          <t>291babafb06c4527</t>
+          <t>083f617e8c574600</t>
         </is>
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:32:06.087195Z</t>
+          <t>2026-07-28T01:59:34.734702Z</t>
         </is>
       </c>
       <c r="C13" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T08:00:00Z</t>
+          <t>2026-07-28T08:00:00Z</t>
         </is>
       </c>
       <c r="D13" s="24" t="inlineStr">
         <is>
-          <t>60708</t>
+          <t>61376</t>
         </is>
       </c>
       <c r="E13" s="24" t="inlineStr">
@@ -4552,12 +4636,12 @@
       </c>
       <c r="F13" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Esports Academy</t>
+          <t>HANJIN BRION Challengers</t>
         </is>
       </c>
       <c r="G13" s="24" t="inlineStr">
         <is>
-          <t>T1 Academy</t>
+          <t>Hanwha Life Esports Challengers</t>
         </is>
       </c>
       <c r="H13" s="24" t="inlineStr">
@@ -4586,14 +4670,14 @@
         <v>0.640288</v>
       </c>
       <c r="O13" s="28" t="n">
-        <v>0.6818</v>
+        <v>0.65045</v>
       </c>
       <c r="P13" s="28" t="n"/>
       <c r="Q13" s="28" t="n">
-        <v>0.041512</v>
+        <v>0.010162</v>
       </c>
       <c r="R13" s="26" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="S13" s="29" t="n">
         <v>2</v>
@@ -4619,7 +4703,7 @@
       <c r="AD13" s="24" t="n"/>
       <c r="AE13" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-lol-t1a-nsea-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-lol-hlec-hbc-2026-07-28).</t>
         </is>
       </c>
       <c r="AF13" s="31" t="inlineStr">
@@ -4660,32 +4744,32 @@
       </c>
       <c r="AP13" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Esports Academy</t>
+          <t>HANJIN BRION Challengers</t>
         </is>
       </c>
       <c r="AQ13" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Esports Academy</t>
+          <t>HANJIN BRION Challengers</t>
         </is>
       </c>
       <c r="AR13" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Esports Academy</t>
+          <t>HANJIN BRION Challengers</t>
         </is>
       </c>
       <c r="AS13" s="24" t="inlineStr">
         <is>
-          <t>T1 Academy</t>
+          <t>Hanwha Life Esports Challengers</t>
         </is>
       </c>
       <c r="AT13" s="24" t="inlineStr">
         <is>
-          <t>T1 Academy</t>
+          <t>Hanwha Life Esports Challengers</t>
         </is>
       </c>
       <c r="AU13" s="24" t="inlineStr">
         <is>
-          <t>T1 Academy</t>
+          <t>Hanwha Life Esports Challengers</t>
         </is>
       </c>
       <c r="AV13" s="24" t="n"/>
@@ -4703,7 +4787,7 @@
       </c>
       <c r="BA13" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
         </is>
       </c>
       <c r="BB13" s="24" t="inlineStr">
@@ -4718,7 +4802,7 @@
       </c>
       <c r="BD13" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
         </is>
       </c>
       <c r="BE13" s="24" t="inlineStr">
@@ -4738,7 +4822,7 @@
       </c>
       <c r="BH13" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:31:57.034856Z</t>
+          <t>2026-07-28T01:59:21.480440Z</t>
         </is>
       </c>
       <c r="BI13" s="24" t="inlineStr">
@@ -4788,22 +4872,22 @@
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="24" t="inlineStr">
         <is>
-          <t>431392cb36ee45ef</t>
+          <t>a1e66f405280442c</t>
         </is>
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:32:06.087195Z</t>
+          <t>2026-07-28T01:59:34.734702Z</t>
         </is>
       </c>
       <c r="C14" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T08:15:00Z</t>
+          <t>2026-07-28T10:00:00Z</t>
         </is>
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>60713</t>
+          <t>61400</t>
         </is>
       </c>
       <c r="E14" s="24" t="inlineStr">
@@ -4813,12 +4897,12 @@
       </c>
       <c r="F14" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Dplus KIA Challengers</t>
         </is>
       </c>
       <c r="G14" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA</t>
+          <t>KT Rolster Challengers</t>
         </is>
       </c>
       <c r="H14" s="24" t="inlineStr">
@@ -4838,26 +4922,26 @@
         </is>
       </c>
       <c r="L14" s="26" t="n">
-        <v>-203</v>
+        <v>117</v>
       </c>
       <c r="M14" s="27" t="n">
-        <v>1.492611</v>
+        <v>2.17</v>
       </c>
       <c r="N14" s="28" t="n">
-        <v>0.669967</v>
+        <v>0.460829</v>
       </c>
       <c r="O14" s="28" t="n">
-        <v>0.506725</v>
+        <v>0.659148</v>
       </c>
       <c r="P14" s="28" t="n"/>
       <c r="Q14" s="28" t="n">
-        <v>-0.163242</v>
+        <v>0.198319</v>
       </c>
       <c r="R14" s="26" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S14" s="29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T14" s="24" t="inlineStr">
         <is>
@@ -4880,7 +4964,7 @@
       <c r="AD14" s="24" t="n"/>
       <c r="AE14" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-lol-dk-t1-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-lol-ktc-dkc-2026-07-28).</t>
         </is>
       </c>
       <c r="AF14" s="31" t="inlineStr">
@@ -4898,7 +4982,7 @@
       <c r="AJ14" s="31" t="n"/>
       <c r="AK14" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL14" s="26" t="n">
@@ -4906,47 +4990,47 @@
       </c>
       <c r="AM14" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN14" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO14" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP14" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Dplus KIA Challengers</t>
         </is>
       </c>
       <c r="AQ14" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Dplus KIA Challengers</t>
         </is>
       </c>
       <c r="AR14" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Dplus KIA Challengers</t>
         </is>
       </c>
       <c r="AS14" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA</t>
+          <t>KT Rolster Challengers</t>
         </is>
       </c>
       <c r="AT14" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA</t>
+          <t>KT Rolster Challengers</t>
         </is>
       </c>
       <c r="AU14" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA</t>
+          <t>KT Rolster Challengers</t>
         </is>
       </c>
       <c r="AV14" s="24" t="n"/>
@@ -4964,7 +5048,7 @@
       </c>
       <c r="BA14" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
         </is>
       </c>
       <c r="BB14" s="24" t="inlineStr">
@@ -4979,7 +5063,7 @@
       </c>
       <c r="BD14" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
         </is>
       </c>
       <c r="BE14" s="24" t="inlineStr">
@@ -4999,7 +5083,7 @@
       </c>
       <c r="BH14" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:31:57.637015Z</t>
+          <t>2026-07-28T01:59:21.952203Z</t>
         </is>
       </c>
       <c r="BI14" s="24" t="inlineStr">
@@ -5009,13 +5093,13 @@
       </c>
       <c r="BJ14" s="25" t="n"/>
       <c r="BK14" s="26" t="n">
-        <v>-203</v>
+        <v>117</v>
       </c>
       <c r="BL14" s="27" t="n">
-        <v>1.492611</v>
+        <v>2.17</v>
       </c>
       <c r="BM14" s="28" t="n">
-        <v>0.669967</v>
+        <v>0.460829</v>
       </c>
       <c r="BN14" s="28" t="n"/>
       <c r="BO14" s="28" t="n"/>
@@ -5049,22 +5133,22 @@
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="24" t="inlineStr">
         <is>
-          <t>bcc827278e944024</t>
+          <t>3aa7acb2b30a4bd4</t>
         </is>
       </c>
       <c r="B15" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:32:06.087195Z</t>
+          <t>2026-07-28T01:59:34.734702Z</t>
         </is>
       </c>
       <c r="C15" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T09:00:00Z</t>
+          <t>2026-07-28T17:00:00Z</t>
         </is>
       </c>
       <c r="D15" s="24" t="inlineStr">
         <is>
-          <t>60716</t>
+          <t>61612</t>
         </is>
       </c>
       <c r="E15" s="24" t="inlineStr">
@@ -5074,12 +5158,12 @@
       </c>
       <c r="F15" s="24" t="inlineStr">
         <is>
-          <t>Kiwoom DRX</t>
+          <t>Dynasty</t>
         </is>
       </c>
       <c r="G15" s="24" t="inlineStr">
         <is>
-          <t>Hanwha Life Esports</t>
+          <t>ZennIT</t>
         </is>
       </c>
       <c r="H15" s="24" t="inlineStr">
@@ -5099,26 +5183,26 @@
         </is>
       </c>
       <c r="L15" s="26" t="n">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="M15" s="27" t="n">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="N15" s="28" t="n">
-        <v>0.480769</v>
+        <v>0.460829</v>
       </c>
       <c r="O15" s="28" t="n">
-        <v>0.912307</v>
+        <v>0.523131</v>
       </c>
       <c r="P15" s="28" t="n"/>
       <c r="Q15" s="28" t="n">
-        <v>0.431538</v>
+        <v>0.062302</v>
       </c>
       <c r="R15" s="26" t="n">
-        <v>100</v>
+        <v>51</v>
       </c>
       <c r="S15" s="29" t="n">
-        <v>2</v>
+        <v>0.75</v>
       </c>
       <c r="T15" s="24" t="inlineStr">
         <is>
@@ -5141,7 +5225,7 @@
       <c r="AD15" s="24" t="n"/>
       <c r="AE15" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4800 (market_slug=aec-lol-hle-krx-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-lol-znt-dyn-2026-07-28).</t>
         </is>
       </c>
       <c r="AF15" s="31" t="inlineStr">
@@ -5182,32 +5266,32 @@
       </c>
       <c r="AP15" s="24" t="inlineStr">
         <is>
-          <t>Kiwoom DRX</t>
+          <t>Dynasty</t>
         </is>
       </c>
       <c r="AQ15" s="24" t="inlineStr">
         <is>
-          <t>Kiwoom DRX</t>
+          <t>Dynasty</t>
         </is>
       </c>
       <c r="AR15" s="24" t="inlineStr">
         <is>
-          <t>Kiwoom DRX</t>
+          <t>Dynasty</t>
         </is>
       </c>
       <c r="AS15" s="24" t="inlineStr">
         <is>
-          <t>Hanwha Life Esports</t>
+          <t>ZennIT</t>
         </is>
       </c>
       <c r="AT15" s="24" t="inlineStr">
         <is>
-          <t>Hanwha Life Esports</t>
+          <t>ZennIT</t>
         </is>
       </c>
       <c r="AU15" s="24" t="inlineStr">
         <is>
-          <t>Hanwha Life Esports</t>
+          <t>ZennIT</t>
         </is>
       </c>
       <c r="AV15" s="24" t="n"/>
@@ -5225,7 +5309,7 @@
       </c>
       <c r="BA15" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
         </is>
       </c>
       <c r="BB15" s="24" t="inlineStr">
@@ -5240,7 +5324,7 @@
       </c>
       <c r="BD15" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
         </is>
       </c>
       <c r="BE15" s="24" t="inlineStr">
@@ -5260,7 +5344,7 @@
       </c>
       <c r="BH15" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:31:58.156214Z</t>
+          <t>2026-07-28T01:59:25.235547Z</t>
         </is>
       </c>
       <c r="BI15" s="24" t="inlineStr">
@@ -5270,13 +5354,13 @@
       </c>
       <c r="BJ15" s="25" t="n"/>
       <c r="BK15" s="26" t="n">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="BL15" s="27" t="n">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="BM15" s="28" t="n">
-        <v>0.480769</v>
+        <v>0.460829</v>
       </c>
       <c r="BN15" s="28" t="n"/>
       <c r="BO15" s="28" t="n"/>
@@ -5310,22 +5394,22 @@
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="24" t="inlineStr">
         <is>
-          <t>cbbef86c954249ca</t>
+          <t>e10f26c1e8834e53</t>
         </is>
       </c>
       <c r="B16" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:32:06.087195Z</t>
+          <t>2026-07-28T01:59:34.734702Z</t>
         </is>
       </c>
       <c r="C16" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T09:45:00Z</t>
+          <t>2026-07-28T17:00:00Z</t>
         </is>
       </c>
       <c r="D16" s="24" t="inlineStr">
         <is>
-          <t>60723</t>
+          <t>61611</t>
         </is>
       </c>
       <c r="E16" s="24" t="inlineStr">
@@ -5335,12 +5419,12 @@
       </c>
       <c r="F16" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Red Force</t>
+          <t>Esprit Shōnen</t>
         </is>
       </c>
       <c r="G16" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>ZYB Esport</t>
         </is>
       </c>
       <c r="H16" s="24" t="inlineStr">
@@ -5350,7 +5434,7 @@
       </c>
       <c r="I16" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J16" s="25" t="n"/>
@@ -5360,26 +5444,26 @@
         </is>
       </c>
       <c r="L16" s="26" t="n">
-        <v>-203</v>
+        <v>178</v>
       </c>
       <c r="M16" s="27" t="n">
-        <v>1.492611</v>
+        <v>2.78</v>
       </c>
       <c r="N16" s="28" t="n">
-        <v>0.669967</v>
+        <v>0.359712</v>
       </c>
       <c r="O16" s="28" t="n">
-        <v>0.865659</v>
+        <v>0.513552</v>
       </c>
       <c r="P16" s="28" t="n"/>
       <c r="Q16" s="28" t="n">
-        <v>0.195692</v>
+        <v>0.15384</v>
       </c>
       <c r="R16" s="26" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="S16" s="29" t="n">
-        <v>2</v>
+        <v>0.75</v>
       </c>
       <c r="T16" s="24" t="inlineStr">
         <is>
@@ -5402,7 +5486,7 @@
       <c r="AD16" s="24" t="n"/>
       <c r="AE16" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-lol-t1-ns-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.3600 (market_slug=aec-lol-zyb-ess-2026-07-28).</t>
         </is>
       </c>
       <c r="AF16" s="31" t="inlineStr">
@@ -5443,32 +5527,32 @@
       </c>
       <c r="AP16" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Red Force</t>
+          <t>Esprit Shōnen</t>
         </is>
       </c>
       <c r="AQ16" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Red Force</t>
+          <t>Esprit Shōnen</t>
         </is>
       </c>
       <c r="AR16" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Red Force</t>
+          <t>Esprit Shōnen</t>
         </is>
       </c>
       <c r="AS16" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>ZYB Esport</t>
         </is>
       </c>
       <c r="AT16" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>ZYB Esport</t>
         </is>
       </c>
       <c r="AU16" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>ZYB Esport</t>
         </is>
       </c>
       <c r="AV16" s="24" t="n"/>
@@ -5486,7 +5570,7 @@
       </c>
       <c r="BA16" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
         </is>
       </c>
       <c r="BB16" s="24" t="inlineStr">
@@ -5501,7 +5585,7 @@
       </c>
       <c r="BD16" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
         </is>
       </c>
       <c r="BE16" s="24" t="inlineStr">
@@ -5521,7 +5605,7 @@
       </c>
       <c r="BH16" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:31:58.672379Z</t>
+          <t>2026-07-28T01:59:25.710837Z</t>
         </is>
       </c>
       <c r="BI16" s="24" t="inlineStr">
@@ -5531,13 +5615,13 @@
       </c>
       <c r="BJ16" s="25" t="n"/>
       <c r="BK16" s="26" t="n">
-        <v>-203</v>
+        <v>178</v>
       </c>
       <c r="BL16" s="27" t="n">
-        <v>1.492611</v>
+        <v>2.78</v>
       </c>
       <c r="BM16" s="28" t="n">
-        <v>0.669967</v>
+        <v>0.359712</v>
       </c>
       <c r="BN16" s="28" t="n"/>
       <c r="BO16" s="28" t="n"/>
@@ -5571,22 +5655,22 @@
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="24" t="inlineStr">
         <is>
-          <t>cbdbbc7aaf994613</t>
+          <t>bd120340d8634830</t>
         </is>
       </c>
       <c r="B17" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:32:06.087195Z</t>
+          <t>2026-07-28T01:59:34.734702Z</t>
         </is>
       </c>
       <c r="C17" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T10:00:00Z</t>
+          <t>2026-07-28T18:00:00Z</t>
         </is>
       </c>
       <c r="D17" s="24" t="inlineStr">
         <is>
-          <t>60724</t>
+          <t>61724</t>
         </is>
       </c>
       <c r="E17" s="24" t="inlineStr">
@@ -5596,12 +5680,12 @@
       </c>
       <c r="F17" s="24" t="inlineStr">
         <is>
-          <t>BNK FearX Youth</t>
+          <t>Myth Esports</t>
         </is>
       </c>
       <c r="G17" s="24" t="inlineStr">
         <is>
-          <t>Gen.G Global Academy</t>
+          <t>The Bandits</t>
         </is>
       </c>
       <c r="H17" s="24" t="inlineStr">
@@ -5611,7 +5695,7 @@
       </c>
       <c r="I17" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J17" s="25" t="n"/>
@@ -5621,26 +5705,26 @@
         </is>
       </c>
       <c r="L17" s="26" t="n">
-        <v>-223</v>
+        <v>-122</v>
       </c>
       <c r="M17" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.819672</v>
       </c>
       <c r="N17" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.54955</v>
       </c>
       <c r="O17" s="28" t="n">
-        <v>0.654791</v>
+        <v>0.622675</v>
       </c>
       <c r="P17" s="28" t="n"/>
       <c r="Q17" s="28" t="n">
-        <v>-0.035611</v>
+        <v>0.073125</v>
       </c>
       <c r="R17" s="26" t="n">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="S17" s="29" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="T17" s="24" t="inlineStr">
         <is>
@@ -5663,7 +5747,7 @@
       <c r="AD17" s="24" t="n"/>
       <c r="AE17" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-lol-genga-foxy-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-lol-ban-myth-2026-07-28).</t>
         </is>
       </c>
       <c r="AF17" s="31" t="inlineStr">
@@ -5681,7 +5765,7 @@
       <c r="AJ17" s="31" t="n"/>
       <c r="AK17" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL17" s="26" t="n">
@@ -5689,47 +5773,47 @@
       </c>
       <c r="AM17" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN17" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO17" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP17" s="24" t="inlineStr">
         <is>
-          <t>BNK FearX Youth</t>
+          <t>Myth Esports</t>
         </is>
       </c>
       <c r="AQ17" s="24" t="inlineStr">
         <is>
-          <t>BNK FearX Youth</t>
+          <t>Myth Esports</t>
         </is>
       </c>
       <c r="AR17" s="24" t="inlineStr">
         <is>
-          <t>BNK FearX Youth</t>
+          <t>Myth Esports</t>
         </is>
       </c>
       <c r="AS17" s="24" t="inlineStr">
         <is>
-          <t>Gen.G Global Academy</t>
+          <t>The Bandits</t>
         </is>
       </c>
       <c r="AT17" s="24" t="inlineStr">
         <is>
-          <t>Gen.G Global Academy</t>
+          <t>The Bandits</t>
         </is>
       </c>
       <c r="AU17" s="24" t="inlineStr">
         <is>
-          <t>Gen.G Global Academy</t>
+          <t>The Bandits</t>
         </is>
       </c>
       <c r="AV17" s="24" t="n"/>
@@ -5747,7 +5831,7 @@
       </c>
       <c r="BA17" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
         </is>
       </c>
       <c r="BB17" s="24" t="inlineStr">
@@ -5762,7 +5846,7 @@
       </c>
       <c r="BD17" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
         </is>
       </c>
       <c r="BE17" s="24" t="inlineStr">
@@ -5782,7 +5866,7 @@
       </c>
       <c r="BH17" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:31:59.162720Z</t>
+          <t>2026-07-28T01:59:26.636317Z</t>
         </is>
       </c>
       <c r="BI17" s="24" t="inlineStr">
@@ -5792,13 +5876,13 @@
       </c>
       <c r="BJ17" s="25" t="n"/>
       <c r="BK17" s="26" t="n">
-        <v>-223</v>
+        <v>-122</v>
       </c>
       <c r="BL17" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.819672</v>
       </c>
       <c r="BM17" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.54955</v>
       </c>
       <c r="BN17" s="28" t="n"/>
       <c r="BO17" s="28" t="n"/>
@@ -5832,22 +5916,22 @@
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="24" t="inlineStr">
         <is>
-          <t>b652816244cd47fc</t>
+          <t>46688e47acf14a13</t>
         </is>
       </c>
       <c r="B18" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:32:06.087195Z</t>
+          <t>2026-07-28T01:59:34.734702Z</t>
         </is>
       </c>
       <c r="C18" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T10:30:00Z</t>
+          <t>2026-07-28T18:00:00Z</t>
         </is>
       </c>
       <c r="D18" s="24" t="inlineStr">
         <is>
-          <t>60725</t>
+          <t>61721</t>
         </is>
       </c>
       <c r="E18" s="24" t="inlineStr">
@@ -5857,12 +5941,12 @@
       </c>
       <c r="F18" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA</t>
+          <t>Galions</t>
         </is>
       </c>
       <c r="G18" s="24" t="inlineStr">
         <is>
-          <t>HANJIN BRION</t>
+          <t>Karmine Corp Blue</t>
         </is>
       </c>
       <c r="H18" s="24" t="inlineStr">
@@ -5882,26 +5966,26 @@
         </is>
       </c>
       <c r="L18" s="26" t="n">
-        <v>194</v>
+        <v>-203</v>
       </c>
       <c r="M18" s="27" t="n">
-        <v>2.94</v>
+        <v>1.492611</v>
       </c>
       <c r="N18" s="28" t="n">
-        <v>0.340136</v>
+        <v>0.669967</v>
       </c>
       <c r="O18" s="28" t="n">
-        <v>0.803091</v>
+        <v>0.636694</v>
       </c>
       <c r="P18" s="28" t="n"/>
       <c r="Q18" s="28" t="n">
-        <v>0.462955</v>
+        <v>-0.033273</v>
       </c>
       <c r="R18" s="26" t="n">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="S18" s="29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T18" s="24" t="inlineStr">
         <is>
@@ -5924,7 +6008,7 @@
       <c r="AD18" s="24" t="n"/>
       <c r="AE18" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3400 (market_slug=aec-lol-bro-dk-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-lol-kcb-gal-2026-07-28).</t>
         </is>
       </c>
       <c r="AF18" s="31" t="inlineStr">
@@ -5942,7 +6026,7 @@
       <c r="AJ18" s="31" t="n"/>
       <c r="AK18" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL18" s="26" t="n">
@@ -5950,47 +6034,47 @@
       </c>
       <c r="AM18" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN18" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO18" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP18" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA</t>
+          <t>Galions</t>
         </is>
       </c>
       <c r="AQ18" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA</t>
+          <t>Galions</t>
         </is>
       </c>
       <c r="AR18" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA</t>
+          <t>Galions</t>
         </is>
       </c>
       <c r="AS18" s="24" t="inlineStr">
         <is>
-          <t>HANJIN BRION</t>
+          <t>Karmine Corp Blue</t>
         </is>
       </c>
       <c r="AT18" s="24" t="inlineStr">
         <is>
-          <t>HANJIN BRION</t>
+          <t>Karmine Corp Blue</t>
         </is>
       </c>
       <c r="AU18" s="24" t="inlineStr">
         <is>
-          <t>HANJIN BRION</t>
+          <t>Karmine Corp Blue</t>
         </is>
       </c>
       <c r="AV18" s="24" t="n"/>
@@ -6008,7 +6092,7 @@
       </c>
       <c r="BA18" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
         </is>
       </c>
       <c r="BB18" s="24" t="inlineStr">
@@ -6023,7 +6107,7 @@
       </c>
       <c r="BD18" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
         </is>
       </c>
       <c r="BE18" s="24" t="inlineStr">
@@ -6043,7 +6127,7 @@
       </c>
       <c r="BH18" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:31:59.671342Z</t>
+          <t>2026-07-28T01:59:27.090438Z</t>
         </is>
       </c>
       <c r="BI18" s="24" t="inlineStr">
@@ -6053,13 +6137,13 @@
       </c>
       <c r="BJ18" s="25" t="n"/>
       <c r="BK18" s="26" t="n">
-        <v>194</v>
+        <v>-203</v>
       </c>
       <c r="BL18" s="27" t="n">
-        <v>2.94</v>
+        <v>1.492611</v>
       </c>
       <c r="BM18" s="28" t="n">
-        <v>0.340136</v>
+        <v>0.669967</v>
       </c>
       <c r="BN18" s="28" t="n"/>
       <c r="BO18" s="28" t="n"/>
@@ -6093,22 +6177,22 @@
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="24" t="inlineStr">
         <is>
-          <t>3f17180d8346415a</t>
+          <t>3b7ea83318fb45cd</t>
         </is>
       </c>
       <c r="B19" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:32:06.087195Z</t>
+          <t>2026-07-28T01:59:34.734702Z</t>
         </is>
       </c>
       <c r="C19" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T21:00:00Z</t>
+          <t>2026-07-28T19:00:00Z</t>
         </is>
       </c>
       <c r="D19" s="24" t="inlineStr">
         <is>
-          <t>61044</t>
+          <t>61851</t>
         </is>
       </c>
       <c r="E19" s="24" t="inlineStr">
@@ -6118,12 +6202,12 @@
       </c>
       <c r="F19" s="24" t="inlineStr">
         <is>
-          <t>Ei Nerd Esports</t>
+          <t>Vitality.Bee</t>
         </is>
       </c>
       <c r="G19" s="24" t="inlineStr">
         <is>
-          <t>paiN Gaming Academy</t>
+          <t>Joblife</t>
         </is>
       </c>
       <c r="H19" s="24" t="inlineStr">
@@ -6133,7 +6217,7 @@
       </c>
       <c r="I19" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J19" s="25" t="n"/>
@@ -6143,26 +6227,26 @@
         </is>
       </c>
       <c r="L19" s="26" t="n">
-        <v>-233</v>
+        <v>150</v>
       </c>
       <c r="M19" s="27" t="n">
-        <v>1.429185</v>
+        <v>2.5</v>
       </c>
       <c r="N19" s="28" t="n">
-        <v>0.6997</v>
+        <v>0.4</v>
       </c>
       <c r="O19" s="28" t="n">
-        <v>0.712884</v>
+        <v>0.547957</v>
       </c>
       <c r="P19" s="28" t="n"/>
       <c r="Q19" s="28" t="n">
-        <v>0.013184</v>
+        <v>0.147957</v>
       </c>
       <c r="R19" s="26" t="n">
-        <v>27</v>
+        <v>94</v>
       </c>
       <c r="S19" s="29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T19" s="24" t="inlineStr">
         <is>
@@ -6185,7 +6269,7 @@
       <c r="AD19" s="24" t="n"/>
       <c r="AE19" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-lol-pnga-nerd-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.4000 (market_slug=aec-lol-jl-vitb-2026-07-28).</t>
         </is>
       </c>
       <c r="AF19" s="31" t="inlineStr">
@@ -6226,32 +6310,32 @@
       </c>
       <c r="AP19" s="24" t="inlineStr">
         <is>
-          <t>Ei Nerd Esports</t>
+          <t>Vitality.Bee</t>
         </is>
       </c>
       <c r="AQ19" s="24" t="inlineStr">
         <is>
-          <t>Ei Nerd Esports</t>
+          <t>Vitality.Bee</t>
         </is>
       </c>
       <c r="AR19" s="24" t="inlineStr">
         <is>
-          <t>Ei Nerd Esports</t>
+          <t>Vitality.Bee</t>
         </is>
       </c>
       <c r="AS19" s="24" t="inlineStr">
         <is>
-          <t>paiN Gaming Academy</t>
+          <t>Joblife</t>
         </is>
       </c>
       <c r="AT19" s="24" t="inlineStr">
         <is>
-          <t>paiN Gaming Academy</t>
+          <t>Joblife</t>
         </is>
       </c>
       <c r="AU19" s="24" t="inlineStr">
         <is>
-          <t>paiN Gaming Academy</t>
+          <t>Joblife</t>
         </is>
       </c>
       <c r="AV19" s="24" t="n"/>
@@ -6269,7 +6353,7 @@
       </c>
       <c r="BA19" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
         </is>
       </c>
       <c r="BB19" s="24" t="inlineStr">
@@ -6284,7 +6368,7 @@
       </c>
       <c r="BD19" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
         </is>
       </c>
       <c r="BE19" s="24" t="inlineStr">
@@ -6304,7 +6388,7 @@
       </c>
       <c r="BH19" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:32:03.641211Z</t>
+          <t>2026-07-28T01:59:30.117610Z</t>
         </is>
       </c>
       <c r="BI19" s="24" t="inlineStr">
@@ -6314,13 +6398,13 @@
       </c>
       <c r="BJ19" s="25" t="n"/>
       <c r="BK19" s="26" t="n">
-        <v>-233</v>
+        <v>150</v>
       </c>
       <c r="BL19" s="27" t="n">
-        <v>1.429185</v>
+        <v>2.5</v>
       </c>
       <c r="BM19" s="28" t="n">
-        <v>0.6997</v>
+        <v>0.4</v>
       </c>
       <c r="BN19" s="28" t="n"/>
       <c r="BO19" s="28" t="n"/>
@@ -6351,6 +6435,789 @@
       <c r="CN19" s="24" t="n"/>
       <c r="CO19" s="24" t="n"/>
     </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>b4160e9e9fa44095</t>
+        </is>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:59:34.734702Z</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>62170</t>
+        </is>
+      </c>
+      <c r="E20" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F20" s="24" t="inlineStr">
+        <is>
+          <t>Maze Gaming</t>
+        </is>
+      </c>
+      <c r="G20" s="24" t="inlineStr">
+        <is>
+          <t>9z Globant</t>
+        </is>
+      </c>
+      <c r="H20" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I20" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J20" s="25" t="n"/>
+      <c r="K20" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L20" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="M20" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="N20" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="O20" s="28" t="n">
+        <v>0.61673</v>
+      </c>
+      <c r="P20" s="28" t="n"/>
+      <c r="Q20" s="28" t="n">
+        <v>-0.08297</v>
+      </c>
+      <c r="R20" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U20" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V20" s="24" t="n"/>
+      <c r="W20" s="26" t="n"/>
+      <c r="X20" s="26" t="n"/>
+      <c r="Y20" s="25" t="n"/>
+      <c r="Z20" s="26" t="n"/>
+      <c r="AA20" s="28" t="n"/>
+      <c r="AB20" s="28" t="n"/>
+      <c r="AC20" s="30" t="n"/>
+      <c r="AD20" s="24" t="n"/>
+      <c r="AE20" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-lol-9zg-maz-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF20" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG20" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH20" s="24" t="n"/>
+      <c r="AI20" s="31" t="n"/>
+      <c r="AJ20" s="31" t="n"/>
+      <c r="AK20" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL20" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM20" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN20" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO20" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP20" s="24" t="inlineStr">
+        <is>
+          <t>Maze Gaming</t>
+        </is>
+      </c>
+      <c r="AQ20" s="24" t="inlineStr">
+        <is>
+          <t>Maze Gaming</t>
+        </is>
+      </c>
+      <c r="AR20" s="24" t="inlineStr">
+        <is>
+          <t>Maze Gaming</t>
+        </is>
+      </c>
+      <c r="AS20" s="24" t="inlineStr">
+        <is>
+          <t>9z Globant</t>
+        </is>
+      </c>
+      <c r="AT20" s="24" t="inlineStr">
+        <is>
+          <t>9z Globant</t>
+        </is>
+      </c>
+      <c r="AU20" s="24" t="inlineStr">
+        <is>
+          <t>9z Globant</t>
+        </is>
+      </c>
+      <c r="AV20" s="24" t="n"/>
+      <c r="AW20" s="24" t="n"/>
+      <c r="AX20" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY20" s="24" t="n"/>
+      <c r="AZ20" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA20" s="24" t="inlineStr">
+        <is>
+          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
+        </is>
+      </c>
+      <c r="BB20" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC20" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD20" s="24" t="inlineStr">
+        <is>
+          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
+        </is>
+      </c>
+      <c r="BE20" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF20" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG20" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH20" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:59:30.596949Z</t>
+        </is>
+      </c>
+      <c r="BI20" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ20" s="25" t="n"/>
+      <c r="BK20" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="BL20" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="BM20" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="BN20" s="28" t="n"/>
+      <c r="BO20" s="28" t="n"/>
+      <c r="BP20" s="25" t="n"/>
+      <c r="BQ20" s="27" t="n"/>
+      <c r="BR20" s="28" t="n"/>
+      <c r="BS20" s="28" t="n"/>
+      <c r="BT20" s="28" t="n"/>
+      <c r="BU20" s="25" t="n"/>
+      <c r="BV20" s="29" t="n"/>
+      <c r="BW20" s="24" t="n"/>
+      <c r="BX20" s="30" t="n"/>
+      <c r="BY20" s="27" t="n"/>
+      <c r="BZ20" s="24" t="n"/>
+      <c r="CA20" s="31" t="n"/>
+      <c r="CB20" s="24" t="n"/>
+      <c r="CC20" s="24" t="n"/>
+      <c r="CD20" s="24" t="n"/>
+      <c r="CE20" s="24" t="n"/>
+      <c r="CF20" s="24" t="n"/>
+      <c r="CG20" s="24" t="n"/>
+      <c r="CH20" s="24" t="n"/>
+      <c r="CI20" s="24" t="n"/>
+      <c r="CJ20" s="24" t="n"/>
+      <c r="CK20" s="24" t="n"/>
+      <c r="CL20" s="24" t="n"/>
+      <c r="CM20" s="24" t="n"/>
+      <c r="CN20" s="24" t="n"/>
+      <c r="CO20" s="24" t="n"/>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="24" t="inlineStr">
+        <is>
+          <t>864c55aaf87b4f05</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:59:34.734702Z</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="D21" s="24" t="inlineStr">
+        <is>
+          <t>62171</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F21" s="24" t="inlineStr">
+        <is>
+          <t>Team Solid</t>
+        </is>
+      </c>
+      <c r="G21" s="24" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="H21" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I21" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J21" s="25" t="n"/>
+      <c r="K21" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L21" s="26" t="n">
+        <v>-186</v>
+      </c>
+      <c r="M21" s="27" t="n">
+        <v>1.537634</v>
+      </c>
+      <c r="N21" s="28" t="n">
+        <v>0.65035</v>
+      </c>
+      <c r="O21" s="28" t="n">
+        <v>0.773255</v>
+      </c>
+      <c r="P21" s="28" t="n"/>
+      <c r="Q21" s="28" t="n">
+        <v>0.122905</v>
+      </c>
+      <c r="R21" s="26" t="n">
+        <v>81</v>
+      </c>
+      <c r="S21" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U21" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V21" s="24" t="n"/>
+      <c r="W21" s="26" t="n"/>
+      <c r="X21" s="26" t="n"/>
+      <c r="Y21" s="25" t="n"/>
+      <c r="Z21" s="26" t="n"/>
+      <c r="AA21" s="28" t="n"/>
+      <c r="AB21" s="28" t="n"/>
+      <c r="AC21" s="30" t="n"/>
+      <c r="AD21" s="24" t="n"/>
+      <c r="AE21" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6500 (market_slug=aec-lol-pnga-tse-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF21" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG21" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH21" s="24" t="n"/>
+      <c r="AI21" s="31" t="n"/>
+      <c r="AJ21" s="31" t="n"/>
+      <c r="AK21" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL21" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM21" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN21" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO21" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP21" s="24" t="inlineStr">
+        <is>
+          <t>Team Solid</t>
+        </is>
+      </c>
+      <c r="AQ21" s="24" t="inlineStr">
+        <is>
+          <t>Team Solid</t>
+        </is>
+      </c>
+      <c r="AR21" s="24" t="inlineStr">
+        <is>
+          <t>Team Solid</t>
+        </is>
+      </c>
+      <c r="AS21" s="24" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="AT21" s="24" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="AU21" s="24" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="AV21" s="24" t="n"/>
+      <c r="AW21" s="24" t="n"/>
+      <c r="AX21" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY21" s="24" t="n"/>
+      <c r="AZ21" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA21" s="24" t="inlineStr">
+        <is>
+          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
+        </is>
+      </c>
+      <c r="BB21" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC21" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD21" s="24" t="inlineStr">
+        <is>
+          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
+        </is>
+      </c>
+      <c r="BE21" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF21" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG21" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH21" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:59:32.137972Z</t>
+        </is>
+      </c>
+      <c r="BI21" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ21" s="25" t="n"/>
+      <c r="BK21" s="26" t="n">
+        <v>-186</v>
+      </c>
+      <c r="BL21" s="27" t="n">
+        <v>1.537634</v>
+      </c>
+      <c r="BM21" s="28" t="n">
+        <v>0.65035</v>
+      </c>
+      <c r="BN21" s="28" t="n"/>
+      <c r="BO21" s="28" t="n"/>
+      <c r="BP21" s="25" t="n"/>
+      <c r="BQ21" s="27" t="n"/>
+      <c r="BR21" s="28" t="n"/>
+      <c r="BS21" s="28" t="n"/>
+      <c r="BT21" s="28" t="n"/>
+      <c r="BU21" s="25" t="n"/>
+      <c r="BV21" s="29" t="n"/>
+      <c r="BW21" s="24" t="n"/>
+      <c r="BX21" s="30" t="n"/>
+      <c r="BY21" s="27" t="n"/>
+      <c r="BZ21" s="24" t="n"/>
+      <c r="CA21" s="31" t="n"/>
+      <c r="CB21" s="24" t="n"/>
+      <c r="CC21" s="24" t="n"/>
+      <c r="CD21" s="24" t="n"/>
+      <c r="CE21" s="24" t="n"/>
+      <c r="CF21" s="24" t="n"/>
+      <c r="CG21" s="24" t="n"/>
+      <c r="CH21" s="24" t="n"/>
+      <c r="CI21" s="24" t="n"/>
+      <c r="CJ21" s="24" t="n"/>
+      <c r="CK21" s="24" t="n"/>
+      <c r="CL21" s="24" t="n"/>
+      <c r="CM21" s="24" t="n"/>
+      <c r="CN21" s="24" t="n"/>
+      <c r="CO21" s="24" t="n"/>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>437857d8a6ca4908</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:59:34.734702Z</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T23:00:00Z</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>62314</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F22" s="24" t="inlineStr">
+        <is>
+          <t>KaBuM! Ilha das Lendas</t>
+        </is>
+      </c>
+      <c r="G22" s="24" t="inlineStr">
+        <is>
+          <t>7REX</t>
+        </is>
+      </c>
+      <c r="H22" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I22" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J22" s="25" t="n"/>
+      <c r="K22" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L22" s="26" t="n">
+        <v>127</v>
+      </c>
+      <c r="M22" s="27" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="N22" s="28" t="n">
+        <v>0.440529</v>
+      </c>
+      <c r="O22" s="28" t="n">
+        <v>0.517575</v>
+      </c>
+      <c r="P22" s="28" t="n"/>
+      <c r="Q22" s="28" t="n">
+        <v>0.077046</v>
+      </c>
+      <c r="R22" s="26" t="n">
+        <v>59</v>
+      </c>
+      <c r="S22" s="29" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="T22" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U22" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V22" s="24" t="n"/>
+      <c r="W22" s="26" t="n"/>
+      <c r="X22" s="26" t="n"/>
+      <c r="Y22" s="25" t="n"/>
+      <c r="Z22" s="26" t="n"/>
+      <c r="AA22" s="28" t="n"/>
+      <c r="AB22" s="28" t="n"/>
+      <c r="AC22" s="30" t="n"/>
+      <c r="AD22" s="24" t="n"/>
+      <c r="AE22" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-lol-7rex-kbm-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF22" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG22" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH22" s="24" t="n"/>
+      <c r="AI22" s="31" t="n"/>
+      <c r="AJ22" s="31" t="n"/>
+      <c r="AK22" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL22" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM22" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN22" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO22" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP22" s="24" t="inlineStr">
+        <is>
+          <t>KaBuM! Ilha das Lendas</t>
+        </is>
+      </c>
+      <c r="AQ22" s="24" t="inlineStr">
+        <is>
+          <t>KaBuM! Ilha das Lendas</t>
+        </is>
+      </c>
+      <c r="AR22" s="24" t="inlineStr">
+        <is>
+          <t>KaBuM! Ilha das Lendas</t>
+        </is>
+      </c>
+      <c r="AS22" s="24" t="inlineStr">
+        <is>
+          <t>7REX</t>
+        </is>
+      </c>
+      <c r="AT22" s="24" t="inlineStr">
+        <is>
+          <t>7REX</t>
+        </is>
+      </c>
+      <c r="AU22" s="24" t="inlineStr">
+        <is>
+          <t>7REX</t>
+        </is>
+      </c>
+      <c r="AV22" s="24" t="n"/>
+      <c r="AW22" s="24" t="n"/>
+      <c r="AX22" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY22" s="24" t="n"/>
+      <c r="AZ22" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA22" s="24" t="inlineStr">
+        <is>
+          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
+        </is>
+      </c>
+      <c r="BB22" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC22" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD22" s="24" t="inlineStr">
+        <is>
+          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
+        </is>
+      </c>
+      <c r="BE22" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF22" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG22" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH22" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:59:34.228061Z</t>
+        </is>
+      </c>
+      <c r="BI22" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ22" s="25" t="n"/>
+      <c r="BK22" s="26" t="n">
+        <v>127</v>
+      </c>
+      <c r="BL22" s="27" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BM22" s="28" t="n">
+        <v>0.440529</v>
+      </c>
+      <c r="BN22" s="28" t="n"/>
+      <c r="BO22" s="28" t="n"/>
+      <c r="BP22" s="25" t="n"/>
+      <c r="BQ22" s="27" t="n"/>
+      <c r="BR22" s="28" t="n"/>
+      <c r="BS22" s="28" t="n"/>
+      <c r="BT22" s="28" t="n"/>
+      <c r="BU22" s="25" t="n"/>
+      <c r="BV22" s="29" t="n"/>
+      <c r="BW22" s="24" t="n"/>
+      <c r="BX22" s="30" t="n"/>
+      <c r="BY22" s="27" t="n"/>
+      <c r="BZ22" s="24" t="n"/>
+      <c r="CA22" s="31" t="n"/>
+      <c r="CB22" s="24" t="n"/>
+      <c r="CC22" s="24" t="n"/>
+      <c r="CD22" s="24" t="n"/>
+      <c r="CE22" s="24" t="n"/>
+      <c r="CF22" s="24" t="n"/>
+      <c r="CG22" s="24" t="n"/>
+      <c r="CH22" s="24" t="n"/>
+      <c r="CI22" s="24" t="n"/>
+      <c r="CJ22" s="24" t="n"/>
+      <c r="CK22" s="24" t="n"/>
+      <c r="CL22" s="24" t="n"/>
+      <c r="CM22" s="24" t="n"/>
+      <c r="CN22" s="24" t="n"/>
+      <c r="CO22" s="24" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research/lol.xlsx
+++ b/data/research/lol.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO22" headerRowCount="1">
-  <autoFilter ref="A1:CO22"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO14" headerRowCount="1">
+  <autoFilter ref="A1:CO14"/>
   <tableColumns count="93">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -752,19 +752,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$22)</f>
+        <f>COUNTA('Picks'!$A$2:$A$14)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$22,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$14,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$22,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$14,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$22,"settled",'Picks'!$V$2:$V$22,"win")+COUNTIFS('Picks'!$U$2:$U$22,"settled",'Picks'!$V$2:$V$22,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")+COUNTIFS('Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -792,19 +792,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$22,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$14,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$22,"&gt;0",'Picks'!$V$2:$V$22,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$22,"&gt;0",'Picks'!$V$2:$V$22,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$22,"&gt;0",'Picks'!$V$2:$V$22,"win")/(COUNTIFS('Picks'!$BX$2:$BX$22,"&gt;0",'Picks'!$V$2:$V$22,"win")+COUNTIFS('Picks'!$BX$2:$BX$22,"&gt;0",'Picks'!$V$2:$V$22,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"win")/(COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"win")+COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$22)/SUM('Picks'!$BX$2:$BX$22),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$14)/SUM('Picks'!$BX$2:$BX$14),0)</f>
         <v/>
       </c>
     </row>
@@ -832,19 +832,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$22)</f>
+        <f>SUM('Picks'!$BY$2:$BY$14)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$22,"&lt;&gt;",'Picks'!$AB$2:$AB$22),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$14,"&lt;&gt;",'Picks'!$AB$2:$AB$14),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$22,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$22,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$14,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$14,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$22,'Picks'!$AM$2:$AM$22,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$14,'Picks'!$AM$2:$AM$14,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -899,15 +899,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$22,$A14,'Picks'!$U$2:$U$22,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$22,$A14,'Picks'!$U$2:$U$22,"settled",'Picks'!$V$2:$V$22,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$22,$A14,'Picks'!$U$2:$U$22,"settled",'Picks'!$V$2:$V$22,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -915,11 +915,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$22,'Picks'!$H$2:$H$22,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$14,'Picks'!$H$2:$H$14,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$22,'Picks'!$H$2:$H$22,$A14,'Picks'!$U$2:$U$22,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$14,'Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -930,15 +930,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$22,$A15,'Picks'!$U$2:$U$22,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$22,$A15,'Picks'!$U$2:$U$22,"settled",'Picks'!$V$2:$V$22,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$22,$A15,'Picks'!$U$2:$U$22,"settled",'Picks'!$V$2:$V$22,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -946,11 +946,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$22,'Picks'!$H$2:$H$22,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$14,'Picks'!$H$2:$H$14,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$22,'Picks'!$H$2:$H$22,$A15,'Picks'!$U$2:$U$22,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$14,'Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -961,15 +961,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$22,$A16,'Picks'!$U$2:$U$22,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$22,$A16,'Picks'!$U$2:$U$22,"settled",'Picks'!$V$2:$V$22,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$22,$A16,'Picks'!$U$2:$U$22,"settled",'Picks'!$V$2:$V$22,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -977,11 +977,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$22,'Picks'!$H$2:$H$22,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$14,'Picks'!$H$2:$H$14,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$22,'Picks'!$H$2:$H$22,$A16,'Picks'!$U$2:$U$22,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$14,'Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO22"/>
+  <dimension ref="A1:CO14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4611,12 +4611,12 @@
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
         <is>
-          <t>083f617e8c574600</t>
+          <t>65f050e2f5d7407e</t>
         </is>
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T01:59:34.734702Z</t>
+          <t>2026-07-28T05:05:19.448075Z</t>
         </is>
       </c>
       <c r="C13" s="24" t="inlineStr">
@@ -4670,11 +4670,11 @@
         <v>0.640288</v>
       </c>
       <c r="O13" s="28" t="n">
-        <v>0.65045</v>
+        <v>0.6502599999999999</v>
       </c>
       <c r="P13" s="28" t="n"/>
       <c r="Q13" s="28" t="n">
-        <v>0.010162</v>
+        <v>0.009972</v>
       </c>
       <c r="R13" s="26" t="n">
         <v>25</v>
@@ -4689,18 +4689,32 @@
       </c>
       <c r="U13" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V13" s="24" t="n"/>
-      <c r="W13" s="26" t="n"/>
-      <c r="X13" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V13" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W13" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y13" s="25" t="n"/>
       <c r="Z13" s="26" t="n"/>
       <c r="AA13" s="28" t="n"/>
       <c r="AB13" s="28" t="n"/>
-      <c r="AC13" s="30" t="n"/>
-      <c r="AD13" s="24" t="n"/>
+      <c r="AC13" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD13" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T11:12:37.047119Z</t>
+        </is>
+      </c>
       <c r="AE13" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-lol-hlec-hbc-2026-07-28).</t>
@@ -4713,7 +4727,7 @@
       </c>
       <c r="AG13" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH13" s="24" t="n"/>
@@ -4787,7 +4801,7 @@
       </c>
       <c r="BA13" s="24" t="inlineStr">
         <is>
-          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
+          <t>9a599be054d1f2f2548e59017ab201f151d7f9e118fd5b364d64e4e515bcc72a</t>
         </is>
       </c>
       <c r="BB13" s="24" t="inlineStr">
@@ -4802,7 +4816,7 @@
       </c>
       <c r="BD13" s="24" t="inlineStr">
         <is>
-          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
+          <t>9a599be054d1f2f2548e59017ab201f151d7f9e118fd5b364d64e4e515bcc72a</t>
         </is>
       </c>
       <c r="BE13" s="24" t="inlineStr">
@@ -4822,7 +4836,7 @@
       </c>
       <c r="BH13" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T01:59:21.480440Z</t>
+          <t>2026-07-28T05:04:47.620446Z</t>
         </is>
       </c>
       <c r="BI13" s="24" t="inlineStr">
@@ -4872,12 +4886,12 @@
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="24" t="inlineStr">
         <is>
-          <t>a1e66f405280442c</t>
+          <t>91b03e93b6bb4b49</t>
         </is>
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T01:59:34.734702Z</t>
+          <t>2026-07-28T08:11:25.230149Z</t>
         </is>
       </c>
       <c r="C14" s="24" t="inlineStr">
@@ -4922,20 +4936,20 @@
         </is>
       </c>
       <c r="L14" s="26" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="M14" s="27" t="n">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="N14" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.469484</v>
       </c>
       <c r="O14" s="28" t="n">
-        <v>0.659148</v>
+        <v>0.659678</v>
       </c>
       <c r="P14" s="28" t="n"/>
       <c r="Q14" s="28" t="n">
-        <v>0.198319</v>
+        <v>0.190194</v>
       </c>
       <c r="R14" s="26" t="n">
         <v>100</v>
@@ -4950,21 +4964,35 @@
       </c>
       <c r="U14" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V14" s="24" t="n"/>
-      <c r="W14" s="26" t="n"/>
-      <c r="X14" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V14" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W14" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X14" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y14" s="25" t="n"/>
       <c r="Z14" s="26" t="n"/>
       <c r="AA14" s="28" t="n"/>
       <c r="AB14" s="28" t="n"/>
-      <c r="AC14" s="30" t="n"/>
-      <c r="AD14" s="24" t="n"/>
+      <c r="AC14" s="30" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AD14" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T14:18:42.681308Z</t>
+        </is>
+      </c>
       <c r="AE14" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-lol-ktc-dkc-2026-07-28).</t>
+          <t>Neutral Elo baseline; executable ask 0.4700 (market_slug=aec-lol-ktc-dkc-2026-07-28).</t>
         </is>
       </c>
       <c r="AF14" s="31" t="inlineStr">
@@ -5048,7 +5076,7 @@
       </c>
       <c r="BA14" s="24" t="inlineStr">
         <is>
-          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
+          <t>f70c60dff382bbc12c8f4c5f7776a2ae9cb7c56547818c66aa81fe255bb5bb7d</t>
         </is>
       </c>
       <c r="BB14" s="24" t="inlineStr">
@@ -5063,7 +5091,7 @@
       </c>
       <c r="BD14" s="24" t="inlineStr">
         <is>
-          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
+          <t>f70c60dff382bbc12c8f4c5f7776a2ae9cb7c56547818c66aa81fe255bb5bb7d</t>
         </is>
       </c>
       <c r="BE14" s="24" t="inlineStr">
@@ -5083,7 +5111,7 @@
       </c>
       <c r="BH14" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T01:59:21.952203Z</t>
+          <t>2026-07-28T08:10:53.411585Z</t>
         </is>
       </c>
       <c r="BI14" s="24" t="inlineStr">
@@ -5093,13 +5121,13 @@
       </c>
       <c r="BJ14" s="25" t="n"/>
       <c r="BK14" s="26" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="BL14" s="27" t="n">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="BM14" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.469484</v>
       </c>
       <c r="BN14" s="28" t="n"/>
       <c r="BO14" s="28" t="n"/>
@@ -5130,2094 +5158,6 @@
       <c r="CN14" s="24" t="n"/>
       <c r="CO14" s="24" t="n"/>
     </row>
-    <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="24" t="inlineStr">
-        <is>
-          <t>3aa7acb2b30a4bd4</t>
-        </is>
-      </c>
-      <c r="B15" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T01:59:34.734702Z</t>
-        </is>
-      </c>
-      <c r="C15" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T17:00:00Z</t>
-        </is>
-      </c>
-      <c r="D15" s="24" t="inlineStr">
-        <is>
-          <t>61612</t>
-        </is>
-      </c>
-      <c r="E15" s="24" t="inlineStr">
-        <is>
-          <t>LOL</t>
-        </is>
-      </c>
-      <c r="F15" s="24" t="inlineStr">
-        <is>
-          <t>Dynasty</t>
-        </is>
-      </c>
-      <c r="G15" s="24" t="inlineStr">
-        <is>
-          <t>ZennIT</t>
-        </is>
-      </c>
-      <c r="H15" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I15" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J15" s="25" t="n"/>
-      <c r="K15" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L15" s="26" t="n">
-        <v>117</v>
-      </c>
-      <c r="M15" s="27" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="N15" s="28" t="n">
-        <v>0.460829</v>
-      </c>
-      <c r="O15" s="28" t="n">
-        <v>0.523131</v>
-      </c>
-      <c r="P15" s="28" t="n"/>
-      <c r="Q15" s="28" t="n">
-        <v>0.062302</v>
-      </c>
-      <c r="R15" s="26" t="n">
-        <v>51</v>
-      </c>
-      <c r="S15" s="29" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="T15" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U15" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V15" s="24" t="n"/>
-      <c r="W15" s="26" t="n"/>
-      <c r="X15" s="26" t="n"/>
-      <c r="Y15" s="25" t="n"/>
-      <c r="Z15" s="26" t="n"/>
-      <c r="AA15" s="28" t="n"/>
-      <c r="AB15" s="28" t="n"/>
-      <c r="AC15" s="30" t="n"/>
-      <c r="AD15" s="24" t="n"/>
-      <c r="AE15" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-lol-znt-dyn-2026-07-28).</t>
-        </is>
-      </c>
-      <c r="AF15" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG15" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH15" s="24" t="n"/>
-      <c r="AI15" s="31" t="n"/>
-      <c r="AJ15" s="31" t="n"/>
-      <c r="AK15" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL15" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM15" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN15" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO15" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP15" s="24" t="inlineStr">
-        <is>
-          <t>Dynasty</t>
-        </is>
-      </c>
-      <c r="AQ15" s="24" t="inlineStr">
-        <is>
-          <t>Dynasty</t>
-        </is>
-      </c>
-      <c r="AR15" s="24" t="inlineStr">
-        <is>
-          <t>Dynasty</t>
-        </is>
-      </c>
-      <c r="AS15" s="24" t="inlineStr">
-        <is>
-          <t>ZennIT</t>
-        </is>
-      </c>
-      <c r="AT15" s="24" t="inlineStr">
-        <is>
-          <t>ZennIT</t>
-        </is>
-      </c>
-      <c r="AU15" s="24" t="inlineStr">
-        <is>
-          <t>ZennIT</t>
-        </is>
-      </c>
-      <c r="AV15" s="24" t="n"/>
-      <c r="AW15" s="24" t="n"/>
-      <c r="AX15" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY15" s="24" t="n"/>
-      <c r="AZ15" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA15" s="24" t="inlineStr">
-        <is>
-          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
-        </is>
-      </c>
-      <c r="BB15" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC15" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD15" s="24" t="inlineStr">
-        <is>
-          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
-        </is>
-      </c>
-      <c r="BE15" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF15" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG15" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH15" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T01:59:25.235547Z</t>
-        </is>
-      </c>
-      <c r="BI15" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ15" s="25" t="n"/>
-      <c r="BK15" s="26" t="n">
-        <v>117</v>
-      </c>
-      <c r="BL15" s="27" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="BM15" s="28" t="n">
-        <v>0.460829</v>
-      </c>
-      <c r="BN15" s="28" t="n"/>
-      <c r="BO15" s="28" t="n"/>
-      <c r="BP15" s="25" t="n"/>
-      <c r="BQ15" s="27" t="n"/>
-      <c r="BR15" s="28" t="n"/>
-      <c r="BS15" s="28" t="n"/>
-      <c r="BT15" s="28" t="n"/>
-      <c r="BU15" s="25" t="n"/>
-      <c r="BV15" s="29" t="n"/>
-      <c r="BW15" s="24" t="n"/>
-      <c r="BX15" s="30" t="n"/>
-      <c r="BY15" s="27" t="n"/>
-      <c r="BZ15" s="24" t="n"/>
-      <c r="CA15" s="31" t="n"/>
-      <c r="CB15" s="24" t="n"/>
-      <c r="CC15" s="24" t="n"/>
-      <c r="CD15" s="24" t="n"/>
-      <c r="CE15" s="24" t="n"/>
-      <c r="CF15" s="24" t="n"/>
-      <c r="CG15" s="24" t="n"/>
-      <c r="CH15" s="24" t="n"/>
-      <c r="CI15" s="24" t="n"/>
-      <c r="CJ15" s="24" t="n"/>
-      <c r="CK15" s="24" t="n"/>
-      <c r="CL15" s="24" t="n"/>
-      <c r="CM15" s="24" t="n"/>
-      <c r="CN15" s="24" t="n"/>
-      <c r="CO15" s="24" t="n"/>
-    </row>
-    <row r="16" ht="36" customHeight="1">
-      <c r="A16" s="24" t="inlineStr">
-        <is>
-          <t>e10f26c1e8834e53</t>
-        </is>
-      </c>
-      <c r="B16" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T01:59:34.734702Z</t>
-        </is>
-      </c>
-      <c r="C16" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T17:00:00Z</t>
-        </is>
-      </c>
-      <c r="D16" s="24" t="inlineStr">
-        <is>
-          <t>61611</t>
-        </is>
-      </c>
-      <c r="E16" s="24" t="inlineStr">
-        <is>
-          <t>LOL</t>
-        </is>
-      </c>
-      <c r="F16" s="24" t="inlineStr">
-        <is>
-          <t>Esprit Shōnen</t>
-        </is>
-      </c>
-      <c r="G16" s="24" t="inlineStr">
-        <is>
-          <t>ZYB Esport</t>
-        </is>
-      </c>
-      <c r="H16" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I16" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J16" s="25" t="n"/>
-      <c r="K16" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L16" s="26" t="n">
-        <v>178</v>
-      </c>
-      <c r="M16" s="27" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="N16" s="28" t="n">
-        <v>0.359712</v>
-      </c>
-      <c r="O16" s="28" t="n">
-        <v>0.513552</v>
-      </c>
-      <c r="P16" s="28" t="n"/>
-      <c r="Q16" s="28" t="n">
-        <v>0.15384</v>
-      </c>
-      <c r="R16" s="26" t="n">
-        <v>97</v>
-      </c>
-      <c r="S16" s="29" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="T16" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U16" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V16" s="24" t="n"/>
-      <c r="W16" s="26" t="n"/>
-      <c r="X16" s="26" t="n"/>
-      <c r="Y16" s="25" t="n"/>
-      <c r="Z16" s="26" t="n"/>
-      <c r="AA16" s="28" t="n"/>
-      <c r="AB16" s="28" t="n"/>
-      <c r="AC16" s="30" t="n"/>
-      <c r="AD16" s="24" t="n"/>
-      <c r="AE16" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.3600 (market_slug=aec-lol-zyb-ess-2026-07-28).</t>
-        </is>
-      </c>
-      <c r="AF16" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG16" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH16" s="24" t="n"/>
-      <c r="AI16" s="31" t="n"/>
-      <c r="AJ16" s="31" t="n"/>
-      <c r="AK16" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL16" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM16" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN16" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO16" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP16" s="24" t="inlineStr">
-        <is>
-          <t>Esprit Shōnen</t>
-        </is>
-      </c>
-      <c r="AQ16" s="24" t="inlineStr">
-        <is>
-          <t>Esprit Shōnen</t>
-        </is>
-      </c>
-      <c r="AR16" s="24" t="inlineStr">
-        <is>
-          <t>Esprit Shōnen</t>
-        </is>
-      </c>
-      <c r="AS16" s="24" t="inlineStr">
-        <is>
-          <t>ZYB Esport</t>
-        </is>
-      </c>
-      <c r="AT16" s="24" t="inlineStr">
-        <is>
-          <t>ZYB Esport</t>
-        </is>
-      </c>
-      <c r="AU16" s="24" t="inlineStr">
-        <is>
-          <t>ZYB Esport</t>
-        </is>
-      </c>
-      <c r="AV16" s="24" t="n"/>
-      <c r="AW16" s="24" t="n"/>
-      <c r="AX16" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY16" s="24" t="n"/>
-      <c r="AZ16" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA16" s="24" t="inlineStr">
-        <is>
-          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
-        </is>
-      </c>
-      <c r="BB16" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC16" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD16" s="24" t="inlineStr">
-        <is>
-          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
-        </is>
-      </c>
-      <c r="BE16" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF16" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG16" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH16" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T01:59:25.710837Z</t>
-        </is>
-      </c>
-      <c r="BI16" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ16" s="25" t="n"/>
-      <c r="BK16" s="26" t="n">
-        <v>178</v>
-      </c>
-      <c r="BL16" s="27" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BM16" s="28" t="n">
-        <v>0.359712</v>
-      </c>
-      <c r="BN16" s="28" t="n"/>
-      <c r="BO16" s="28" t="n"/>
-      <c r="BP16" s="25" t="n"/>
-      <c r="BQ16" s="27" t="n"/>
-      <c r="BR16" s="28" t="n"/>
-      <c r="BS16" s="28" t="n"/>
-      <c r="BT16" s="28" t="n"/>
-      <c r="BU16" s="25" t="n"/>
-      <c r="BV16" s="29" t="n"/>
-      <c r="BW16" s="24" t="n"/>
-      <c r="BX16" s="30" t="n"/>
-      <c r="BY16" s="27" t="n"/>
-      <c r="BZ16" s="24" t="n"/>
-      <c r="CA16" s="31" t="n"/>
-      <c r="CB16" s="24" t="n"/>
-      <c r="CC16" s="24" t="n"/>
-      <c r="CD16" s="24" t="n"/>
-      <c r="CE16" s="24" t="n"/>
-      <c r="CF16" s="24" t="n"/>
-      <c r="CG16" s="24" t="n"/>
-      <c r="CH16" s="24" t="n"/>
-      <c r="CI16" s="24" t="n"/>
-      <c r="CJ16" s="24" t="n"/>
-      <c r="CK16" s="24" t="n"/>
-      <c r="CL16" s="24" t="n"/>
-      <c r="CM16" s="24" t="n"/>
-      <c r="CN16" s="24" t="n"/>
-      <c r="CO16" s="24" t="n"/>
-    </row>
-    <row r="17" ht="36" customHeight="1">
-      <c r="A17" s="24" t="inlineStr">
-        <is>
-          <t>bd120340d8634830</t>
-        </is>
-      </c>
-      <c r="B17" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T01:59:34.734702Z</t>
-        </is>
-      </c>
-      <c r="C17" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T18:00:00Z</t>
-        </is>
-      </c>
-      <c r="D17" s="24" t="inlineStr">
-        <is>
-          <t>61724</t>
-        </is>
-      </c>
-      <c r="E17" s="24" t="inlineStr">
-        <is>
-          <t>LOL</t>
-        </is>
-      </c>
-      <c r="F17" s="24" t="inlineStr">
-        <is>
-          <t>Myth Esports</t>
-        </is>
-      </c>
-      <c r="G17" s="24" t="inlineStr">
-        <is>
-          <t>The Bandits</t>
-        </is>
-      </c>
-      <c r="H17" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I17" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J17" s="25" t="n"/>
-      <c r="K17" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L17" s="26" t="n">
-        <v>-122</v>
-      </c>
-      <c r="M17" s="27" t="n">
-        <v>1.819672</v>
-      </c>
-      <c r="N17" s="28" t="n">
-        <v>0.54955</v>
-      </c>
-      <c r="O17" s="28" t="n">
-        <v>0.622675</v>
-      </c>
-      <c r="P17" s="28" t="n"/>
-      <c r="Q17" s="28" t="n">
-        <v>0.073125</v>
-      </c>
-      <c r="R17" s="26" t="n">
-        <v>57</v>
-      </c>
-      <c r="S17" s="29" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="T17" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U17" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V17" s="24" t="n"/>
-      <c r="W17" s="26" t="n"/>
-      <c r="X17" s="26" t="n"/>
-      <c r="Y17" s="25" t="n"/>
-      <c r="Z17" s="26" t="n"/>
-      <c r="AA17" s="28" t="n"/>
-      <c r="AB17" s="28" t="n"/>
-      <c r="AC17" s="30" t="n"/>
-      <c r="AD17" s="24" t="n"/>
-      <c r="AE17" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-lol-ban-myth-2026-07-28).</t>
-        </is>
-      </c>
-      <c r="AF17" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG17" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH17" s="24" t="n"/>
-      <c r="AI17" s="31" t="n"/>
-      <c r="AJ17" s="31" t="n"/>
-      <c r="AK17" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL17" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM17" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN17" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO17" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP17" s="24" t="inlineStr">
-        <is>
-          <t>Myth Esports</t>
-        </is>
-      </c>
-      <c r="AQ17" s="24" t="inlineStr">
-        <is>
-          <t>Myth Esports</t>
-        </is>
-      </c>
-      <c r="AR17" s="24" t="inlineStr">
-        <is>
-          <t>Myth Esports</t>
-        </is>
-      </c>
-      <c r="AS17" s="24" t="inlineStr">
-        <is>
-          <t>The Bandits</t>
-        </is>
-      </c>
-      <c r="AT17" s="24" t="inlineStr">
-        <is>
-          <t>The Bandits</t>
-        </is>
-      </c>
-      <c r="AU17" s="24" t="inlineStr">
-        <is>
-          <t>The Bandits</t>
-        </is>
-      </c>
-      <c r="AV17" s="24" t="n"/>
-      <c r="AW17" s="24" t="n"/>
-      <c r="AX17" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY17" s="24" t="n"/>
-      <c r="AZ17" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA17" s="24" t="inlineStr">
-        <is>
-          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
-        </is>
-      </c>
-      <c r="BB17" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC17" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD17" s="24" t="inlineStr">
-        <is>
-          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
-        </is>
-      </c>
-      <c r="BE17" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF17" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG17" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH17" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T01:59:26.636317Z</t>
-        </is>
-      </c>
-      <c r="BI17" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ17" s="25" t="n"/>
-      <c r="BK17" s="26" t="n">
-        <v>-122</v>
-      </c>
-      <c r="BL17" s="27" t="n">
-        <v>1.819672</v>
-      </c>
-      <c r="BM17" s="28" t="n">
-        <v>0.54955</v>
-      </c>
-      <c r="BN17" s="28" t="n"/>
-      <c r="BO17" s="28" t="n"/>
-      <c r="BP17" s="25" t="n"/>
-      <c r="BQ17" s="27" t="n"/>
-      <c r="BR17" s="28" t="n"/>
-      <c r="BS17" s="28" t="n"/>
-      <c r="BT17" s="28" t="n"/>
-      <c r="BU17" s="25" t="n"/>
-      <c r="BV17" s="29" t="n"/>
-      <c r="BW17" s="24" t="n"/>
-      <c r="BX17" s="30" t="n"/>
-      <c r="BY17" s="27" t="n"/>
-      <c r="BZ17" s="24" t="n"/>
-      <c r="CA17" s="31" t="n"/>
-      <c r="CB17" s="24" t="n"/>
-      <c r="CC17" s="24" t="n"/>
-      <c r="CD17" s="24" t="n"/>
-      <c r="CE17" s="24" t="n"/>
-      <c r="CF17" s="24" t="n"/>
-      <c r="CG17" s="24" t="n"/>
-      <c r="CH17" s="24" t="n"/>
-      <c r="CI17" s="24" t="n"/>
-      <c r="CJ17" s="24" t="n"/>
-      <c r="CK17" s="24" t="n"/>
-      <c r="CL17" s="24" t="n"/>
-      <c r="CM17" s="24" t="n"/>
-      <c r="CN17" s="24" t="n"/>
-      <c r="CO17" s="24" t="n"/>
-    </row>
-    <row r="18" ht="36" customHeight="1">
-      <c r="A18" s="24" t="inlineStr">
-        <is>
-          <t>46688e47acf14a13</t>
-        </is>
-      </c>
-      <c r="B18" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T01:59:34.734702Z</t>
-        </is>
-      </c>
-      <c r="C18" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T18:00:00Z</t>
-        </is>
-      </c>
-      <c r="D18" s="24" t="inlineStr">
-        <is>
-          <t>61721</t>
-        </is>
-      </c>
-      <c r="E18" s="24" t="inlineStr">
-        <is>
-          <t>LOL</t>
-        </is>
-      </c>
-      <c r="F18" s="24" t="inlineStr">
-        <is>
-          <t>Galions</t>
-        </is>
-      </c>
-      <c r="G18" s="24" t="inlineStr">
-        <is>
-          <t>Karmine Corp Blue</t>
-        </is>
-      </c>
-      <c r="H18" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I18" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J18" s="25" t="n"/>
-      <c r="K18" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L18" s="26" t="n">
-        <v>-203</v>
-      </c>
-      <c r="M18" s="27" t="n">
-        <v>1.492611</v>
-      </c>
-      <c r="N18" s="28" t="n">
-        <v>0.669967</v>
-      </c>
-      <c r="O18" s="28" t="n">
-        <v>0.636694</v>
-      </c>
-      <c r="P18" s="28" t="n"/>
-      <c r="Q18" s="28" t="n">
-        <v>-0.033273</v>
-      </c>
-      <c r="R18" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="S18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U18" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V18" s="24" t="n"/>
-      <c r="W18" s="26" t="n"/>
-      <c r="X18" s="26" t="n"/>
-      <c r="Y18" s="25" t="n"/>
-      <c r="Z18" s="26" t="n"/>
-      <c r="AA18" s="28" t="n"/>
-      <c r="AB18" s="28" t="n"/>
-      <c r="AC18" s="30" t="n"/>
-      <c r="AD18" s="24" t="n"/>
-      <c r="AE18" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-lol-kcb-gal-2026-07-28).</t>
-        </is>
-      </c>
-      <c r="AF18" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG18" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH18" s="24" t="n"/>
-      <c r="AI18" s="31" t="n"/>
-      <c r="AJ18" s="31" t="n"/>
-      <c r="AK18" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL18" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM18" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN18" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO18" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP18" s="24" t="inlineStr">
-        <is>
-          <t>Galions</t>
-        </is>
-      </c>
-      <c r="AQ18" s="24" t="inlineStr">
-        <is>
-          <t>Galions</t>
-        </is>
-      </c>
-      <c r="AR18" s="24" t="inlineStr">
-        <is>
-          <t>Galions</t>
-        </is>
-      </c>
-      <c r="AS18" s="24" t="inlineStr">
-        <is>
-          <t>Karmine Corp Blue</t>
-        </is>
-      </c>
-      <c r="AT18" s="24" t="inlineStr">
-        <is>
-          <t>Karmine Corp Blue</t>
-        </is>
-      </c>
-      <c r="AU18" s="24" t="inlineStr">
-        <is>
-          <t>Karmine Corp Blue</t>
-        </is>
-      </c>
-      <c r="AV18" s="24" t="n"/>
-      <c r="AW18" s="24" t="n"/>
-      <c r="AX18" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY18" s="24" t="n"/>
-      <c r="AZ18" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA18" s="24" t="inlineStr">
-        <is>
-          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
-        </is>
-      </c>
-      <c r="BB18" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC18" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD18" s="24" t="inlineStr">
-        <is>
-          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
-        </is>
-      </c>
-      <c r="BE18" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF18" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG18" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH18" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T01:59:27.090438Z</t>
-        </is>
-      </c>
-      <c r="BI18" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ18" s="25" t="n"/>
-      <c r="BK18" s="26" t="n">
-        <v>-203</v>
-      </c>
-      <c r="BL18" s="27" t="n">
-        <v>1.492611</v>
-      </c>
-      <c r="BM18" s="28" t="n">
-        <v>0.669967</v>
-      </c>
-      <c r="BN18" s="28" t="n"/>
-      <c r="BO18" s="28" t="n"/>
-      <c r="BP18" s="25" t="n"/>
-      <c r="BQ18" s="27" t="n"/>
-      <c r="BR18" s="28" t="n"/>
-      <c r="BS18" s="28" t="n"/>
-      <c r="BT18" s="28" t="n"/>
-      <c r="BU18" s="25" t="n"/>
-      <c r="BV18" s="29" t="n"/>
-      <c r="BW18" s="24" t="n"/>
-      <c r="BX18" s="30" t="n"/>
-      <c r="BY18" s="27" t="n"/>
-      <c r="BZ18" s="24" t="n"/>
-      <c r="CA18" s="31" t="n"/>
-      <c r="CB18" s="24" t="n"/>
-      <c r="CC18" s="24" t="n"/>
-      <c r="CD18" s="24" t="n"/>
-      <c r="CE18" s="24" t="n"/>
-      <c r="CF18" s="24" t="n"/>
-      <c r="CG18" s="24" t="n"/>
-      <c r="CH18" s="24" t="n"/>
-      <c r="CI18" s="24" t="n"/>
-      <c r="CJ18" s="24" t="n"/>
-      <c r="CK18" s="24" t="n"/>
-      <c r="CL18" s="24" t="n"/>
-      <c r="CM18" s="24" t="n"/>
-      <c r="CN18" s="24" t="n"/>
-      <c r="CO18" s="24" t="n"/>
-    </row>
-    <row r="19" ht="36" customHeight="1">
-      <c r="A19" s="24" t="inlineStr">
-        <is>
-          <t>3b7ea83318fb45cd</t>
-        </is>
-      </c>
-      <c r="B19" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T01:59:34.734702Z</t>
-        </is>
-      </c>
-      <c r="C19" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T19:00:00Z</t>
-        </is>
-      </c>
-      <c r="D19" s="24" t="inlineStr">
-        <is>
-          <t>61851</t>
-        </is>
-      </c>
-      <c r="E19" s="24" t="inlineStr">
-        <is>
-          <t>LOL</t>
-        </is>
-      </c>
-      <c r="F19" s="24" t="inlineStr">
-        <is>
-          <t>Vitality.Bee</t>
-        </is>
-      </c>
-      <c r="G19" s="24" t="inlineStr">
-        <is>
-          <t>Joblife</t>
-        </is>
-      </c>
-      <c r="H19" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I19" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J19" s="25" t="n"/>
-      <c r="K19" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L19" s="26" t="n">
-        <v>150</v>
-      </c>
-      <c r="M19" s="27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N19" s="28" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O19" s="28" t="n">
-        <v>0.547957</v>
-      </c>
-      <c r="P19" s="28" t="n"/>
-      <c r="Q19" s="28" t="n">
-        <v>0.147957</v>
-      </c>
-      <c r="R19" s="26" t="n">
-        <v>94</v>
-      </c>
-      <c r="S19" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T19" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U19" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V19" s="24" t="n"/>
-      <c r="W19" s="26" t="n"/>
-      <c r="X19" s="26" t="n"/>
-      <c r="Y19" s="25" t="n"/>
-      <c r="Z19" s="26" t="n"/>
-      <c r="AA19" s="28" t="n"/>
-      <c r="AB19" s="28" t="n"/>
-      <c r="AC19" s="30" t="n"/>
-      <c r="AD19" s="24" t="n"/>
-      <c r="AE19" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.4000 (market_slug=aec-lol-jl-vitb-2026-07-28).</t>
-        </is>
-      </c>
-      <c r="AF19" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG19" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH19" s="24" t="n"/>
-      <c r="AI19" s="31" t="n"/>
-      <c r="AJ19" s="31" t="n"/>
-      <c r="AK19" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL19" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM19" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN19" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO19" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP19" s="24" t="inlineStr">
-        <is>
-          <t>Vitality.Bee</t>
-        </is>
-      </c>
-      <c r="AQ19" s="24" t="inlineStr">
-        <is>
-          <t>Vitality.Bee</t>
-        </is>
-      </c>
-      <c r="AR19" s="24" t="inlineStr">
-        <is>
-          <t>Vitality.Bee</t>
-        </is>
-      </c>
-      <c r="AS19" s="24" t="inlineStr">
-        <is>
-          <t>Joblife</t>
-        </is>
-      </c>
-      <c r="AT19" s="24" t="inlineStr">
-        <is>
-          <t>Joblife</t>
-        </is>
-      </c>
-      <c r="AU19" s="24" t="inlineStr">
-        <is>
-          <t>Joblife</t>
-        </is>
-      </c>
-      <c r="AV19" s="24" t="n"/>
-      <c r="AW19" s="24" t="n"/>
-      <c r="AX19" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY19" s="24" t="n"/>
-      <c r="AZ19" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA19" s="24" t="inlineStr">
-        <is>
-          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
-        </is>
-      </c>
-      <c r="BB19" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC19" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD19" s="24" t="inlineStr">
-        <is>
-          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
-        </is>
-      </c>
-      <c r="BE19" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF19" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG19" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH19" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T01:59:30.117610Z</t>
-        </is>
-      </c>
-      <c r="BI19" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ19" s="25" t="n"/>
-      <c r="BK19" s="26" t="n">
-        <v>150</v>
-      </c>
-      <c r="BL19" s="27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BM19" s="28" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BN19" s="28" t="n"/>
-      <c r="BO19" s="28" t="n"/>
-      <c r="BP19" s="25" t="n"/>
-      <c r="BQ19" s="27" t="n"/>
-      <c r="BR19" s="28" t="n"/>
-      <c r="BS19" s="28" t="n"/>
-      <c r="BT19" s="28" t="n"/>
-      <c r="BU19" s="25" t="n"/>
-      <c r="BV19" s="29" t="n"/>
-      <c r="BW19" s="24" t="n"/>
-      <c r="BX19" s="30" t="n"/>
-      <c r="BY19" s="27" t="n"/>
-      <c r="BZ19" s="24" t="n"/>
-      <c r="CA19" s="31" t="n"/>
-      <c r="CB19" s="24" t="n"/>
-      <c r="CC19" s="24" t="n"/>
-      <c r="CD19" s="24" t="n"/>
-      <c r="CE19" s="24" t="n"/>
-      <c r="CF19" s="24" t="n"/>
-      <c r="CG19" s="24" t="n"/>
-      <c r="CH19" s="24" t="n"/>
-      <c r="CI19" s="24" t="n"/>
-      <c r="CJ19" s="24" t="n"/>
-      <c r="CK19" s="24" t="n"/>
-      <c r="CL19" s="24" t="n"/>
-      <c r="CM19" s="24" t="n"/>
-      <c r="CN19" s="24" t="n"/>
-      <c r="CO19" s="24" t="n"/>
-    </row>
-    <row r="20" ht="36" customHeight="1">
-      <c r="A20" s="24" t="inlineStr">
-        <is>
-          <t>b4160e9e9fa44095</t>
-        </is>
-      </c>
-      <c r="B20" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T01:59:34.734702Z</t>
-        </is>
-      </c>
-      <c r="C20" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T20:00:00Z</t>
-        </is>
-      </c>
-      <c r="D20" s="24" t="inlineStr">
-        <is>
-          <t>62170</t>
-        </is>
-      </c>
-      <c r="E20" s="24" t="inlineStr">
-        <is>
-          <t>LOL</t>
-        </is>
-      </c>
-      <c r="F20" s="24" t="inlineStr">
-        <is>
-          <t>Maze Gaming</t>
-        </is>
-      </c>
-      <c r="G20" s="24" t="inlineStr">
-        <is>
-          <t>9z Globant</t>
-        </is>
-      </c>
-      <c r="H20" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I20" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J20" s="25" t="n"/>
-      <c r="K20" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L20" s="26" t="n">
-        <v>-233</v>
-      </c>
-      <c r="M20" s="27" t="n">
-        <v>1.429185</v>
-      </c>
-      <c r="N20" s="28" t="n">
-        <v>0.6997</v>
-      </c>
-      <c r="O20" s="28" t="n">
-        <v>0.61673</v>
-      </c>
-      <c r="P20" s="28" t="n"/>
-      <c r="Q20" s="28" t="n">
-        <v>-0.08297</v>
-      </c>
-      <c r="R20" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U20" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V20" s="24" t="n"/>
-      <c r="W20" s="26" t="n"/>
-      <c r="X20" s="26" t="n"/>
-      <c r="Y20" s="25" t="n"/>
-      <c r="Z20" s="26" t="n"/>
-      <c r="AA20" s="28" t="n"/>
-      <c r="AB20" s="28" t="n"/>
-      <c r="AC20" s="30" t="n"/>
-      <c r="AD20" s="24" t="n"/>
-      <c r="AE20" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-lol-9zg-maz-2026-07-28).</t>
-        </is>
-      </c>
-      <c r="AF20" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG20" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH20" s="24" t="n"/>
-      <c r="AI20" s="31" t="n"/>
-      <c r="AJ20" s="31" t="n"/>
-      <c r="AK20" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL20" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM20" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN20" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO20" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP20" s="24" t="inlineStr">
-        <is>
-          <t>Maze Gaming</t>
-        </is>
-      </c>
-      <c r="AQ20" s="24" t="inlineStr">
-        <is>
-          <t>Maze Gaming</t>
-        </is>
-      </c>
-      <c r="AR20" s="24" t="inlineStr">
-        <is>
-          <t>Maze Gaming</t>
-        </is>
-      </c>
-      <c r="AS20" s="24" t="inlineStr">
-        <is>
-          <t>9z Globant</t>
-        </is>
-      </c>
-      <c r="AT20" s="24" t="inlineStr">
-        <is>
-          <t>9z Globant</t>
-        </is>
-      </c>
-      <c r="AU20" s="24" t="inlineStr">
-        <is>
-          <t>9z Globant</t>
-        </is>
-      </c>
-      <c r="AV20" s="24" t="n"/>
-      <c r="AW20" s="24" t="n"/>
-      <c r="AX20" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY20" s="24" t="n"/>
-      <c r="AZ20" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA20" s="24" t="inlineStr">
-        <is>
-          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
-        </is>
-      </c>
-      <c r="BB20" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC20" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD20" s="24" t="inlineStr">
-        <is>
-          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
-        </is>
-      </c>
-      <c r="BE20" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF20" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG20" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH20" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T01:59:30.596949Z</t>
-        </is>
-      </c>
-      <c r="BI20" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ20" s="25" t="n"/>
-      <c r="BK20" s="26" t="n">
-        <v>-233</v>
-      </c>
-      <c r="BL20" s="27" t="n">
-        <v>1.429185</v>
-      </c>
-      <c r="BM20" s="28" t="n">
-        <v>0.6997</v>
-      </c>
-      <c r="BN20" s="28" t="n"/>
-      <c r="BO20" s="28" t="n"/>
-      <c r="BP20" s="25" t="n"/>
-      <c r="BQ20" s="27" t="n"/>
-      <c r="BR20" s="28" t="n"/>
-      <c r="BS20" s="28" t="n"/>
-      <c r="BT20" s="28" t="n"/>
-      <c r="BU20" s="25" t="n"/>
-      <c r="BV20" s="29" t="n"/>
-      <c r="BW20" s="24" t="n"/>
-      <c r="BX20" s="30" t="n"/>
-      <c r="BY20" s="27" t="n"/>
-      <c r="BZ20" s="24" t="n"/>
-      <c r="CA20" s="31" t="n"/>
-      <c r="CB20" s="24" t="n"/>
-      <c r="CC20" s="24" t="n"/>
-      <c r="CD20" s="24" t="n"/>
-      <c r="CE20" s="24" t="n"/>
-      <c r="CF20" s="24" t="n"/>
-      <c r="CG20" s="24" t="n"/>
-      <c r="CH20" s="24" t="n"/>
-      <c r="CI20" s="24" t="n"/>
-      <c r="CJ20" s="24" t="n"/>
-      <c r="CK20" s="24" t="n"/>
-      <c r="CL20" s="24" t="n"/>
-      <c r="CM20" s="24" t="n"/>
-      <c r="CN20" s="24" t="n"/>
-      <c r="CO20" s="24" t="n"/>
-    </row>
-    <row r="21" ht="36" customHeight="1">
-      <c r="A21" s="24" t="inlineStr">
-        <is>
-          <t>864c55aaf87b4f05</t>
-        </is>
-      </c>
-      <c r="B21" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T01:59:34.734702Z</t>
-        </is>
-      </c>
-      <c r="C21" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T20:00:00Z</t>
-        </is>
-      </c>
-      <c r="D21" s="24" t="inlineStr">
-        <is>
-          <t>62171</t>
-        </is>
-      </c>
-      <c r="E21" s="24" t="inlineStr">
-        <is>
-          <t>LOL</t>
-        </is>
-      </c>
-      <c r="F21" s="24" t="inlineStr">
-        <is>
-          <t>Team Solid</t>
-        </is>
-      </c>
-      <c r="G21" s="24" t="inlineStr">
-        <is>
-          <t>paiN Gaming Academy</t>
-        </is>
-      </c>
-      <c r="H21" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I21" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J21" s="25" t="n"/>
-      <c r="K21" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L21" s="26" t="n">
-        <v>-186</v>
-      </c>
-      <c r="M21" s="27" t="n">
-        <v>1.537634</v>
-      </c>
-      <c r="N21" s="28" t="n">
-        <v>0.65035</v>
-      </c>
-      <c r="O21" s="28" t="n">
-        <v>0.773255</v>
-      </c>
-      <c r="P21" s="28" t="n"/>
-      <c r="Q21" s="28" t="n">
-        <v>0.122905</v>
-      </c>
-      <c r="R21" s="26" t="n">
-        <v>81</v>
-      </c>
-      <c r="S21" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T21" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U21" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V21" s="24" t="n"/>
-      <c r="W21" s="26" t="n"/>
-      <c r="X21" s="26" t="n"/>
-      <c r="Y21" s="25" t="n"/>
-      <c r="Z21" s="26" t="n"/>
-      <c r="AA21" s="28" t="n"/>
-      <c r="AB21" s="28" t="n"/>
-      <c r="AC21" s="30" t="n"/>
-      <c r="AD21" s="24" t="n"/>
-      <c r="AE21" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6500 (market_slug=aec-lol-pnga-tse-2026-07-28).</t>
-        </is>
-      </c>
-      <c r="AF21" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG21" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH21" s="24" t="n"/>
-      <c r="AI21" s="31" t="n"/>
-      <c r="AJ21" s="31" t="n"/>
-      <c r="AK21" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL21" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM21" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN21" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO21" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP21" s="24" t="inlineStr">
-        <is>
-          <t>Team Solid</t>
-        </is>
-      </c>
-      <c r="AQ21" s="24" t="inlineStr">
-        <is>
-          <t>Team Solid</t>
-        </is>
-      </c>
-      <c r="AR21" s="24" t="inlineStr">
-        <is>
-          <t>Team Solid</t>
-        </is>
-      </c>
-      <c r="AS21" s="24" t="inlineStr">
-        <is>
-          <t>paiN Gaming Academy</t>
-        </is>
-      </c>
-      <c r="AT21" s="24" t="inlineStr">
-        <is>
-          <t>paiN Gaming Academy</t>
-        </is>
-      </c>
-      <c r="AU21" s="24" t="inlineStr">
-        <is>
-          <t>paiN Gaming Academy</t>
-        </is>
-      </c>
-      <c r="AV21" s="24" t="n"/>
-      <c r="AW21" s="24" t="n"/>
-      <c r="AX21" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY21" s="24" t="n"/>
-      <c r="AZ21" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA21" s="24" t="inlineStr">
-        <is>
-          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
-        </is>
-      </c>
-      <c r="BB21" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC21" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD21" s="24" t="inlineStr">
-        <is>
-          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
-        </is>
-      </c>
-      <c r="BE21" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF21" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG21" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH21" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T01:59:32.137972Z</t>
-        </is>
-      </c>
-      <c r="BI21" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ21" s="25" t="n"/>
-      <c r="BK21" s="26" t="n">
-        <v>-186</v>
-      </c>
-      <c r="BL21" s="27" t="n">
-        <v>1.537634</v>
-      </c>
-      <c r="BM21" s="28" t="n">
-        <v>0.65035</v>
-      </c>
-      <c r="BN21" s="28" t="n"/>
-      <c r="BO21" s="28" t="n"/>
-      <c r="BP21" s="25" t="n"/>
-      <c r="BQ21" s="27" t="n"/>
-      <c r="BR21" s="28" t="n"/>
-      <c r="BS21" s="28" t="n"/>
-      <c r="BT21" s="28" t="n"/>
-      <c r="BU21" s="25" t="n"/>
-      <c r="BV21" s="29" t="n"/>
-      <c r="BW21" s="24" t="n"/>
-      <c r="BX21" s="30" t="n"/>
-      <c r="BY21" s="27" t="n"/>
-      <c r="BZ21" s="24" t="n"/>
-      <c r="CA21" s="31" t="n"/>
-      <c r="CB21" s="24" t="n"/>
-      <c r="CC21" s="24" t="n"/>
-      <c r="CD21" s="24" t="n"/>
-      <c r="CE21" s="24" t="n"/>
-      <c r="CF21" s="24" t="n"/>
-      <c r="CG21" s="24" t="n"/>
-      <c r="CH21" s="24" t="n"/>
-      <c r="CI21" s="24" t="n"/>
-      <c r="CJ21" s="24" t="n"/>
-      <c r="CK21" s="24" t="n"/>
-      <c r="CL21" s="24" t="n"/>
-      <c r="CM21" s="24" t="n"/>
-      <c r="CN21" s="24" t="n"/>
-      <c r="CO21" s="24" t="n"/>
-    </row>
-    <row r="22" ht="36" customHeight="1">
-      <c r="A22" s="24" t="inlineStr">
-        <is>
-          <t>437857d8a6ca4908</t>
-        </is>
-      </c>
-      <c r="B22" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T01:59:34.734702Z</t>
-        </is>
-      </c>
-      <c r="C22" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T23:00:00Z</t>
-        </is>
-      </c>
-      <c r="D22" s="24" t="inlineStr">
-        <is>
-          <t>62314</t>
-        </is>
-      </c>
-      <c r="E22" s="24" t="inlineStr">
-        <is>
-          <t>LOL</t>
-        </is>
-      </c>
-      <c r="F22" s="24" t="inlineStr">
-        <is>
-          <t>KaBuM! Ilha das Lendas</t>
-        </is>
-      </c>
-      <c r="G22" s="24" t="inlineStr">
-        <is>
-          <t>7REX</t>
-        </is>
-      </c>
-      <c r="H22" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I22" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J22" s="25" t="n"/>
-      <c r="K22" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L22" s="26" t="n">
-        <v>127</v>
-      </c>
-      <c r="M22" s="27" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="N22" s="28" t="n">
-        <v>0.440529</v>
-      </c>
-      <c r="O22" s="28" t="n">
-        <v>0.517575</v>
-      </c>
-      <c r="P22" s="28" t="n"/>
-      <c r="Q22" s="28" t="n">
-        <v>0.077046</v>
-      </c>
-      <c r="R22" s="26" t="n">
-        <v>59</v>
-      </c>
-      <c r="S22" s="29" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="T22" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U22" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V22" s="24" t="n"/>
-      <c r="W22" s="26" t="n"/>
-      <c r="X22" s="26" t="n"/>
-      <c r="Y22" s="25" t="n"/>
-      <c r="Z22" s="26" t="n"/>
-      <c r="AA22" s="28" t="n"/>
-      <c r="AB22" s="28" t="n"/>
-      <c r="AC22" s="30" t="n"/>
-      <c r="AD22" s="24" t="n"/>
-      <c r="AE22" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-lol-7rex-kbm-2026-07-28).</t>
-        </is>
-      </c>
-      <c r="AF22" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG22" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH22" s="24" t="n"/>
-      <c r="AI22" s="31" t="n"/>
-      <c r="AJ22" s="31" t="n"/>
-      <c r="AK22" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL22" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM22" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN22" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO22" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP22" s="24" t="inlineStr">
-        <is>
-          <t>KaBuM! Ilha das Lendas</t>
-        </is>
-      </c>
-      <c r="AQ22" s="24" t="inlineStr">
-        <is>
-          <t>KaBuM! Ilha das Lendas</t>
-        </is>
-      </c>
-      <c r="AR22" s="24" t="inlineStr">
-        <is>
-          <t>KaBuM! Ilha das Lendas</t>
-        </is>
-      </c>
-      <c r="AS22" s="24" t="inlineStr">
-        <is>
-          <t>7REX</t>
-        </is>
-      </c>
-      <c r="AT22" s="24" t="inlineStr">
-        <is>
-          <t>7REX</t>
-        </is>
-      </c>
-      <c r="AU22" s="24" t="inlineStr">
-        <is>
-          <t>7REX</t>
-        </is>
-      </c>
-      <c r="AV22" s="24" t="n"/>
-      <c r="AW22" s="24" t="n"/>
-      <c r="AX22" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY22" s="24" t="n"/>
-      <c r="AZ22" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA22" s="24" t="inlineStr">
-        <is>
-          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
-        </is>
-      </c>
-      <c r="BB22" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC22" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD22" s="24" t="inlineStr">
-        <is>
-          <t>2f948fcee62eca618a11bc0cb9497f84d840dda34097b011ec969d83ce1b8586</t>
-        </is>
-      </c>
-      <c r="BE22" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF22" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG22" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH22" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T01:59:34.228061Z</t>
-        </is>
-      </c>
-      <c r="BI22" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ22" s="25" t="n"/>
-      <c r="BK22" s="26" t="n">
-        <v>127</v>
-      </c>
-      <c r="BL22" s="27" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="BM22" s="28" t="n">
-        <v>0.440529</v>
-      </c>
-      <c r="BN22" s="28" t="n"/>
-      <c r="BO22" s="28" t="n"/>
-      <c r="BP22" s="25" t="n"/>
-      <c r="BQ22" s="27" t="n"/>
-      <c r="BR22" s="28" t="n"/>
-      <c r="BS22" s="28" t="n"/>
-      <c r="BT22" s="28" t="n"/>
-      <c r="BU22" s="25" t="n"/>
-      <c r="BV22" s="29" t="n"/>
-      <c r="BW22" s="24" t="n"/>
-      <c r="BX22" s="30" t="n"/>
-      <c r="BY22" s="27" t="n"/>
-      <c r="BZ22" s="24" t="n"/>
-      <c r="CA22" s="31" t="n"/>
-      <c r="CB22" s="24" t="n"/>
-      <c r="CC22" s="24" t="n"/>
-      <c r="CD22" s="24" t="n"/>
-      <c r="CE22" s="24" t="n"/>
-      <c r="CF22" s="24" t="n"/>
-      <c r="CG22" s="24" t="n"/>
-      <c r="CH22" s="24" t="n"/>
-      <c r="CI22" s="24" t="n"/>
-      <c r="CJ22" s="24" t="n"/>
-      <c r="CK22" s="24" t="n"/>
-      <c r="CL22" s="24" t="n"/>
-      <c r="CM22" s="24" t="n"/>
-      <c r="CN22" s="24" t="n"/>
-      <c r="CO22" s="24" t="n"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research/lol.xlsx
+++ b/data/research/lol.xlsx
@@ -15689,18 +15689,32 @@
       </c>
       <c r="U53" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V53" s="24" t="n"/>
-      <c r="W53" s="26" t="n"/>
-      <c r="X53" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V53" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W53" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X53" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y53" s="25" t="n"/>
       <c r="Z53" s="26" t="n"/>
       <c r="AA53" s="28" t="n"/>
       <c r="AB53" s="28" t="n"/>
-      <c r="AC53" s="30" t="n"/>
-      <c r="AD53" s="24" t="n"/>
+      <c r="AC53" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD53" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T17:22:54.262034Z</t>
+        </is>
+      </c>
       <c r="AE53" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.6600 (market_slug=aec-lol-kcb-ijc-2026-07-30).</t>
@@ -15713,7 +15727,7 @@
       </c>
       <c r="AG53" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH53" s="24" t="n"/>
@@ -15872,12 +15886,12 @@
     <row r="54" ht="36" customHeight="1">
       <c r="A54" s="24" t="inlineStr">
         <is>
-          <t>6dc6f386fefe418f</t>
+          <t>d431652cfdba4fb8</t>
         </is>
       </c>
       <c r="B54" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:15.542075Z</t>
+          <t>2026-07-30T17:21:29.146399Z</t>
         </is>
       </c>
       <c r="C54" s="24" t="inlineStr">
@@ -15922,23 +15936,23 @@
         </is>
       </c>
       <c r="L54" s="26" t="n">
-        <v>-113</v>
+        <v>-163</v>
       </c>
       <c r="M54" s="27" t="n">
-        <v>1.884956</v>
+        <v>1.613497</v>
       </c>
       <c r="N54" s="28" t="n">
-        <v>0.530516</v>
+        <v>0.619772</v>
       </c>
       <c r="O54" s="28" t="n">
         <v>0.652006</v>
       </c>
       <c r="P54" s="28" t="n"/>
       <c r="Q54" s="28" t="n">
-        <v>0.12149</v>
+        <v>0.032234</v>
       </c>
       <c r="R54" s="26" t="n">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="S54" s="29" t="n">
         <v>2</v>
@@ -15964,7 +15978,7 @@
       <c r="AD54" s="24" t="n"/>
       <c r="AE54" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5300 (market_slug=aec-lol-su-bw-2026-07-30).</t>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-lol-su-bw-2026-07-30).</t>
         </is>
       </c>
       <c r="AF54" s="31" t="inlineStr">
@@ -16048,7 +16062,7 @@
       </c>
       <c r="BA54" s="24" t="inlineStr">
         <is>
-          <t>07b3050cc9bbacd4be4727de162f5af11b42125fe9fd5291f7a8fe3fbcb97dc5</t>
+          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
         </is>
       </c>
       <c r="BB54" s="24" t="inlineStr">
@@ -16063,7 +16077,7 @@
       </c>
       <c r="BD54" s="24" t="inlineStr">
         <is>
-          <t>07b3050cc9bbacd4be4727de162f5af11b42125fe9fd5291f7a8fe3fbcb97dc5</t>
+          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
         </is>
       </c>
       <c r="BE54" s="24" t="inlineStr">
@@ -16083,7 +16097,7 @@
       </c>
       <c r="BH54" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:02.795116Z</t>
+          <t>2026-07-30T17:21:16.453569Z</t>
         </is>
       </c>
       <c r="BI54" s="24" t="inlineStr">
@@ -16093,13 +16107,13 @@
       </c>
       <c r="BJ54" s="25" t="n"/>
       <c r="BK54" s="26" t="n">
-        <v>-113</v>
+        <v>-163</v>
       </c>
       <c r="BL54" s="27" t="n">
-        <v>1.884956</v>
+        <v>1.613497</v>
       </c>
       <c r="BM54" s="28" t="n">
-        <v>0.530516</v>
+        <v>0.619772</v>
       </c>
       <c r="BN54" s="28" t="n"/>
       <c r="BO54" s="28" t="n"/>
@@ -16133,12 +16147,12 @@
     <row r="55" ht="36" customHeight="1">
       <c r="A55" s="24" t="inlineStr">
         <is>
-          <t>8a323cb0474b40cb</t>
+          <t>169c37034e824947</t>
         </is>
       </c>
       <c r="B55" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:15.542075Z</t>
+          <t>2026-07-30T17:21:29.146399Z</t>
         </is>
       </c>
       <c r="C55" s="24" t="inlineStr">
@@ -16183,20 +16197,20 @@
         </is>
       </c>
       <c r="L55" s="26" t="n">
-        <v>-127</v>
+        <v>-133</v>
       </c>
       <c r="M55" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.75188</v>
       </c>
       <c r="N55" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.570815</v>
       </c>
       <c r="O55" s="28" t="n">
         <v>0.740872</v>
       </c>
       <c r="P55" s="28" t="n"/>
       <c r="Q55" s="28" t="n">
-        <v>0.181401</v>
+        <v>0.170057</v>
       </c>
       <c r="R55" s="26" t="n">
         <v>100</v>
@@ -16225,7 +16239,7 @@
       <c r="AD55" s="24" t="n"/>
       <c r="AE55" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-lol-mcn-sec-2026-07-30).</t>
+          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-lol-mcn-sec-2026-07-30).</t>
         </is>
       </c>
       <c r="AF55" s="31" t="inlineStr">
@@ -16309,7 +16323,7 @@
       </c>
       <c r="BA55" s="24" t="inlineStr">
         <is>
-          <t>07b3050cc9bbacd4be4727de162f5af11b42125fe9fd5291f7a8fe3fbcb97dc5</t>
+          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
         </is>
       </c>
       <c r="BB55" s="24" t="inlineStr">
@@ -16324,7 +16338,7 @@
       </c>
       <c r="BD55" s="24" t="inlineStr">
         <is>
-          <t>07b3050cc9bbacd4be4727de162f5af11b42125fe9fd5291f7a8fe3fbcb97dc5</t>
+          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
         </is>
       </c>
       <c r="BE55" s="24" t="inlineStr">
@@ -16344,7 +16358,7 @@
       </c>
       <c r="BH55" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:03.290679Z</t>
+          <t>2026-07-30T17:21:17.395840Z</t>
         </is>
       </c>
       <c r="BI55" s="24" t="inlineStr">
@@ -16354,13 +16368,13 @@
       </c>
       <c r="BJ55" s="25" t="n"/>
       <c r="BK55" s="26" t="n">
-        <v>-127</v>
+        <v>-133</v>
       </c>
       <c r="BL55" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.75188</v>
       </c>
       <c r="BM55" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.570815</v>
       </c>
       <c r="BN55" s="28" t="n"/>
       <c r="BO55" s="28" t="n"/>
@@ -16394,12 +16408,12 @@
     <row r="56" ht="36" customHeight="1">
       <c r="A56" s="24" t="inlineStr">
         <is>
-          <t>aacc774d843744cd</t>
+          <t>7e36301c26df456f</t>
         </is>
       </c>
       <c r="B56" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:15.542075Z</t>
+          <t>2026-07-30T17:21:29.146399Z</t>
         </is>
       </c>
       <c r="C56" s="24" t="inlineStr">
@@ -16570,7 +16584,7 @@
       </c>
       <c r="BA56" s="24" t="inlineStr">
         <is>
-          <t>07b3050cc9bbacd4be4727de162f5af11b42125fe9fd5291f7a8fe3fbcb97dc5</t>
+          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
         </is>
       </c>
       <c r="BB56" s="24" t="inlineStr">
@@ -16585,7 +16599,7 @@
       </c>
       <c r="BD56" s="24" t="inlineStr">
         <is>
-          <t>07b3050cc9bbacd4be4727de162f5af11b42125fe9fd5291f7a8fe3fbcb97dc5</t>
+          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
         </is>
       </c>
       <c r="BE56" s="24" t="inlineStr">
@@ -16605,7 +16619,7 @@
       </c>
       <c r="BH56" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:03.764482Z</t>
+          <t>2026-07-30T17:21:17.854408Z</t>
         </is>
       </c>
       <c r="BI56" s="24" t="inlineStr">
@@ -16655,12 +16669,12 @@
     <row r="57" ht="36" customHeight="1">
       <c r="A57" s="24" t="inlineStr">
         <is>
-          <t>7c4abb829f5f4d50</t>
+          <t>42c280920fa54570</t>
         </is>
       </c>
       <c r="B57" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:15.542075Z</t>
+          <t>2026-07-30T17:21:29.146399Z</t>
         </is>
       </c>
       <c r="C57" s="24" t="inlineStr">
@@ -16831,7 +16845,7 @@
       </c>
       <c r="BA57" s="24" t="inlineStr">
         <is>
-          <t>07b3050cc9bbacd4be4727de162f5af11b42125fe9fd5291f7a8fe3fbcb97dc5</t>
+          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
         </is>
       </c>
       <c r="BB57" s="24" t="inlineStr">
@@ -16846,7 +16860,7 @@
       </c>
       <c r="BD57" s="24" t="inlineStr">
         <is>
-          <t>07b3050cc9bbacd4be4727de162f5af11b42125fe9fd5291f7a8fe3fbcb97dc5</t>
+          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
         </is>
       </c>
       <c r="BE57" s="24" t="inlineStr">
@@ -16866,7 +16880,7 @@
       </c>
       <c r="BH57" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:04.718508Z</t>
+          <t>2026-07-30T17:21:18.840084Z</t>
         </is>
       </c>
       <c r="BI57" s="24" t="inlineStr">
@@ -16916,12 +16930,12 @@
     <row r="58" ht="36" customHeight="1">
       <c r="A58" s="24" t="inlineStr">
         <is>
-          <t>743db394bd0f4273</t>
+          <t>a580ef8f40ed40d0</t>
         </is>
       </c>
       <c r="B58" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:15.542075Z</t>
+          <t>2026-07-30T17:21:29.146399Z</t>
         </is>
       </c>
       <c r="C58" s="24" t="inlineStr">
@@ -17092,7 +17106,7 @@
       </c>
       <c r="BA58" s="24" t="inlineStr">
         <is>
-          <t>07b3050cc9bbacd4be4727de162f5af11b42125fe9fd5291f7a8fe3fbcb97dc5</t>
+          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
         </is>
       </c>
       <c r="BB58" s="24" t="inlineStr">
@@ -17107,7 +17121,7 @@
       </c>
       <c r="BD58" s="24" t="inlineStr">
         <is>
-          <t>07b3050cc9bbacd4be4727de162f5af11b42125fe9fd5291f7a8fe3fbcb97dc5</t>
+          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
         </is>
       </c>
       <c r="BE58" s="24" t="inlineStr">
@@ -17127,7 +17141,7 @@
       </c>
       <c r="BH58" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:05.222865Z</t>
+          <t>2026-07-30T17:21:19.790382Z</t>
         </is>
       </c>
       <c r="BI58" s="24" t="inlineStr">
@@ -17177,12 +17191,12 @@
     <row r="59" ht="36" customHeight="1">
       <c r="A59" s="24" t="inlineStr">
         <is>
-          <t>604b179904074fa5</t>
+          <t>fda8a24f6e284939</t>
         </is>
       </c>
       <c r="B59" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:15.542075Z</t>
+          <t>2026-07-30T17:21:29.146399Z</t>
         </is>
       </c>
       <c r="C59" s="24" t="inlineStr">
@@ -17353,7 +17367,7 @@
       </c>
       <c r="BA59" s="24" t="inlineStr">
         <is>
-          <t>07b3050cc9bbacd4be4727de162f5af11b42125fe9fd5291f7a8fe3fbcb97dc5</t>
+          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
         </is>
       </c>
       <c r="BB59" s="24" t="inlineStr">
@@ -17368,7 +17382,7 @@
       </c>
       <c r="BD59" s="24" t="inlineStr">
         <is>
-          <t>07b3050cc9bbacd4be4727de162f5af11b42125fe9fd5291f7a8fe3fbcb97dc5</t>
+          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
         </is>
       </c>
       <c r="BE59" s="24" t="inlineStr">
@@ -17388,7 +17402,7 @@
       </c>
       <c r="BH59" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:07.669000Z</t>
+          <t>2026-07-30T17:21:21.662513Z</t>
         </is>
       </c>
       <c r="BI59" s="24" t="inlineStr">
@@ -17438,12 +17452,12 @@
     <row r="60" ht="36" customHeight="1">
       <c r="A60" s="24" t="inlineStr">
         <is>
-          <t>5e045f57784e4313</t>
+          <t>d578f3249a734797</t>
         </is>
       </c>
       <c r="B60" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:15.542075Z</t>
+          <t>2026-07-30T17:21:29.146399Z</t>
         </is>
       </c>
       <c r="C60" s="24" t="inlineStr">
@@ -17614,7 +17628,7 @@
       </c>
       <c r="BA60" s="24" t="inlineStr">
         <is>
-          <t>07b3050cc9bbacd4be4727de162f5af11b42125fe9fd5291f7a8fe3fbcb97dc5</t>
+          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
         </is>
       </c>
       <c r="BB60" s="24" t="inlineStr">
@@ -17629,7 +17643,7 @@
       </c>
       <c r="BD60" s="24" t="inlineStr">
         <is>
-          <t>07b3050cc9bbacd4be4727de162f5af11b42125fe9fd5291f7a8fe3fbcb97dc5</t>
+          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
         </is>
       </c>
       <c r="BE60" s="24" t="inlineStr">
@@ -17649,7 +17663,7 @@
       </c>
       <c r="BH60" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:08.166583Z</t>
+          <t>2026-07-30T17:21:22.135548Z</t>
         </is>
       </c>
       <c r="BI60" s="24" t="inlineStr">
@@ -17699,12 +17713,12 @@
     <row r="61" ht="36" customHeight="1">
       <c r="A61" s="24" t="inlineStr">
         <is>
-          <t>ef215247954442d8</t>
+          <t>11d943896a5f4699</t>
         </is>
       </c>
       <c r="B61" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:15.542075Z</t>
+          <t>2026-07-30T17:21:29.146399Z</t>
         </is>
       </c>
       <c r="C61" s="24" t="inlineStr">
@@ -17875,7 +17889,7 @@
       </c>
       <c r="BA61" s="24" t="inlineStr">
         <is>
-          <t>07b3050cc9bbacd4be4727de162f5af11b42125fe9fd5291f7a8fe3fbcb97dc5</t>
+          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
         </is>
       </c>
       <c r="BB61" s="24" t="inlineStr">
@@ -17890,7 +17904,7 @@
       </c>
       <c r="BD61" s="24" t="inlineStr">
         <is>
-          <t>07b3050cc9bbacd4be4727de162f5af11b42125fe9fd5291f7a8fe3fbcb97dc5</t>
+          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
         </is>
       </c>
       <c r="BE61" s="24" t="inlineStr">
@@ -17910,7 +17924,7 @@
       </c>
       <c r="BH61" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:09.287881Z</t>
+          <t>2026-07-30T17:21:23.220632Z</t>
         </is>
       </c>
       <c r="BI61" s="24" t="inlineStr">
@@ -17960,12 +17974,12 @@
     <row r="62" ht="36" customHeight="1">
       <c r="A62" s="24" t="inlineStr">
         <is>
-          <t>a41bc5242a5548b3</t>
+          <t>5d39e5674a434284</t>
         </is>
       </c>
       <c r="B62" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:15.542075Z</t>
+          <t>2026-07-30T17:21:29.146399Z</t>
         </is>
       </c>
       <c r="C62" s="24" t="inlineStr">
@@ -18136,7 +18150,7 @@
       </c>
       <c r="BA62" s="24" t="inlineStr">
         <is>
-          <t>07b3050cc9bbacd4be4727de162f5af11b42125fe9fd5291f7a8fe3fbcb97dc5</t>
+          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
         </is>
       </c>
       <c r="BB62" s="24" t="inlineStr">
@@ -18151,7 +18165,7 @@
       </c>
       <c r="BD62" s="24" t="inlineStr">
         <is>
-          <t>07b3050cc9bbacd4be4727de162f5af11b42125fe9fd5291f7a8fe3fbcb97dc5</t>
+          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
         </is>
       </c>
       <c r="BE62" s="24" t="inlineStr">
@@ -18171,7 +18185,7 @@
       </c>
       <c r="BH62" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:10.894915Z</t>
+          <t>2026-07-30T17:21:24.630616Z</t>
         </is>
       </c>
       <c r="BI62" s="24" t="inlineStr">
@@ -18221,12 +18235,12 @@
     <row r="63" ht="36" customHeight="1">
       <c r="A63" s="24" t="inlineStr">
         <is>
-          <t>fd90c7fc782f4b31</t>
+          <t>19a36a40b4714919</t>
         </is>
       </c>
       <c r="B63" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:15.542075Z</t>
+          <t>2026-07-30T17:21:29.146399Z</t>
         </is>
       </c>
       <c r="C63" s="24" t="inlineStr">
@@ -18397,7 +18411,7 @@
       </c>
       <c r="BA63" s="24" t="inlineStr">
         <is>
-          <t>07b3050cc9bbacd4be4727de162f5af11b42125fe9fd5291f7a8fe3fbcb97dc5</t>
+          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
         </is>
       </c>
       <c r="BB63" s="24" t="inlineStr">
@@ -18412,7 +18426,7 @@
       </c>
       <c r="BD63" s="24" t="inlineStr">
         <is>
-          <t>07b3050cc9bbacd4be4727de162f5af11b42125fe9fd5291f7a8fe3fbcb97dc5</t>
+          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
         </is>
       </c>
       <c r="BE63" s="24" t="inlineStr">
@@ -18432,7 +18446,7 @@
       </c>
       <c r="BH63" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:11.471234Z</t>
+          <t>2026-07-30T17:21:25.109653Z</t>
         </is>
       </c>
       <c r="BI63" s="24" t="inlineStr">
@@ -18482,12 +18496,12 @@
     <row r="64" ht="36" customHeight="1">
       <c r="A64" s="24" t="inlineStr">
         <is>
-          <t>09b635c9c47c44aa</t>
+          <t>6dd123104c8b4bf1</t>
         </is>
       </c>
       <c r="B64" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:15.542075Z</t>
+          <t>2026-07-30T17:21:29.146399Z</t>
         </is>
       </c>
       <c r="C64" s="24" t="inlineStr">
@@ -18532,20 +18546,20 @@
         </is>
       </c>
       <c r="L64" s="26" t="n">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="M64" s="27" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="N64" s="28" t="n">
-        <v>0.420168</v>
+        <v>0.409836</v>
       </c>
       <c r="O64" s="28" t="n">
         <v>0.582579</v>
       </c>
       <c r="P64" s="28" t="n"/>
       <c r="Q64" s="28" t="n">
-        <v>0.162411</v>
+        <v>0.172743</v>
       </c>
       <c r="R64" s="26" t="n">
         <v>100</v>
@@ -18574,7 +18588,7 @@
       <c r="AD64" s="24" t="n"/>
       <c r="AE64" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-lol-eko-gmb-2026-07-31).</t>
+          <t>Neutral Elo baseline; executable ask 0.4100 (market_slug=aec-lol-eko-gmb-2026-07-31).</t>
         </is>
       </c>
       <c r="AF64" s="31" t="inlineStr">
@@ -18658,7 +18672,7 @@
       </c>
       <c r="BA64" s="24" t="inlineStr">
         <is>
-          <t>07b3050cc9bbacd4be4727de162f5af11b42125fe9fd5291f7a8fe3fbcb97dc5</t>
+          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
         </is>
       </c>
       <c r="BB64" s="24" t="inlineStr">
@@ -18673,7 +18687,7 @@
       </c>
       <c r="BD64" s="24" t="inlineStr">
         <is>
-          <t>07b3050cc9bbacd4be4727de162f5af11b42125fe9fd5291f7a8fe3fbcb97dc5</t>
+          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
         </is>
       </c>
       <c r="BE64" s="24" t="inlineStr">
@@ -18693,7 +18707,7 @@
       </c>
       <c r="BH64" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:12.493134Z</t>
+          <t>2026-07-30T17:21:26.089989Z</t>
         </is>
       </c>
       <c r="BI64" s="24" t="inlineStr">
@@ -18703,13 +18717,13 @@
       </c>
       <c r="BJ64" s="25" t="n"/>
       <c r="BK64" s="26" t="n">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="BL64" s="27" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="BM64" s="28" t="n">
-        <v>0.420168</v>
+        <v>0.409836</v>
       </c>
       <c r="BN64" s="28" t="n"/>
       <c r="BO64" s="28" t="n"/>
@@ -18743,12 +18757,12 @@
     <row r="65" ht="36" customHeight="1">
       <c r="A65" s="24" t="inlineStr">
         <is>
-          <t>da4e4908ec3e4c8e</t>
+          <t>f861803cd4a74db2</t>
         </is>
       </c>
       <c r="B65" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:15.542075Z</t>
+          <t>2026-07-30T17:21:29.146399Z</t>
         </is>
       </c>
       <c r="C65" s="24" t="inlineStr">
@@ -18919,7 +18933,7 @@
       </c>
       <c r="BA65" s="24" t="inlineStr">
         <is>
-          <t>07b3050cc9bbacd4be4727de162f5af11b42125fe9fd5291f7a8fe3fbcb97dc5</t>
+          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
         </is>
       </c>
       <c r="BB65" s="24" t="inlineStr">
@@ -18934,7 +18948,7 @@
       </c>
       <c r="BD65" s="24" t="inlineStr">
         <is>
-          <t>07b3050cc9bbacd4be4727de162f5af11b42125fe9fd5291f7a8fe3fbcb97dc5</t>
+          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
         </is>
       </c>
       <c r="BE65" s="24" t="inlineStr">
@@ -18954,7 +18968,7 @@
       </c>
       <c r="BH65" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:14.565701Z</t>
+          <t>2026-07-30T17:21:28.135625Z</t>
         </is>
       </c>
       <c r="BI65" s="24" t="inlineStr">
@@ -19004,12 +19018,12 @@
     <row r="66" ht="36" customHeight="1">
       <c r="A66" s="24" t="inlineStr">
         <is>
-          <t>588214e7bbc54517</t>
+          <t>2b7f14f09d044afd</t>
         </is>
       </c>
       <c r="B66" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:15.542075Z</t>
+          <t>2026-07-30T17:21:29.146399Z</t>
         </is>
       </c>
       <c r="C66" s="24" t="inlineStr">
@@ -19180,7 +19194,7 @@
       </c>
       <c r="BA66" s="24" t="inlineStr">
         <is>
-          <t>07b3050cc9bbacd4be4727de162f5af11b42125fe9fd5291f7a8fe3fbcb97dc5</t>
+          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
         </is>
       </c>
       <c r="BB66" s="24" t="inlineStr">
@@ -19195,7 +19209,7 @@
       </c>
       <c r="BD66" s="24" t="inlineStr">
         <is>
-          <t>07b3050cc9bbacd4be4727de162f5af11b42125fe9fd5291f7a8fe3fbcb97dc5</t>
+          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
         </is>
       </c>
       <c r="BE66" s="24" t="inlineStr">
@@ -19215,7 +19229,7 @@
       </c>
       <c r="BH66" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:15.040998Z</t>
+          <t>2026-07-30T17:21:28.657597Z</t>
         </is>
       </c>
       <c r="BI66" s="24" t="inlineStr">

--- a/data/research/lol.xlsx
+++ b/data/research/lol.xlsx
@@ -16147,12 +16147,12 @@
     <row r="55" ht="36" customHeight="1">
       <c r="A55" s="24" t="inlineStr">
         <is>
-          <t>169c37034e824947</t>
+          <t>5091eb8831764f31</t>
         </is>
       </c>
       <c r="B55" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:29.146399Z</t>
+          <t>2026-07-30T17:39:06.974381Z</t>
         </is>
       </c>
       <c r="C55" s="24" t="inlineStr">
@@ -16197,23 +16197,23 @@
         </is>
       </c>
       <c r="L55" s="26" t="n">
-        <v>-133</v>
+        <v>-144</v>
       </c>
       <c r="M55" s="27" t="n">
-        <v>1.75188</v>
+        <v>1.694444</v>
       </c>
       <c r="N55" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.590164</v>
       </c>
       <c r="O55" s="28" t="n">
-        <v>0.740872</v>
+        <v>0.7404230000000001</v>
       </c>
       <c r="P55" s="28" t="n"/>
       <c r="Q55" s="28" t="n">
-        <v>0.170057</v>
+        <v>0.150259</v>
       </c>
       <c r="R55" s="26" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="S55" s="29" t="n">
         <v>2</v>
@@ -16239,7 +16239,7 @@
       <c r="AD55" s="24" t="n"/>
       <c r="AE55" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-lol-mcn-sec-2026-07-30).</t>
+          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-lol-mcn-sec-2026-07-30).</t>
         </is>
       </c>
       <c r="AF55" s="31" t="inlineStr">
@@ -16323,7 +16323,7 @@
       </c>
       <c r="BA55" s="24" t="inlineStr">
         <is>
-          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
+          <t>c3ce12272f7ed38b30827d0b90f279d89c29fbee539b967177eebd40f854bfd6</t>
         </is>
       </c>
       <c r="BB55" s="24" t="inlineStr">
@@ -16338,7 +16338,7 @@
       </c>
       <c r="BD55" s="24" t="inlineStr">
         <is>
-          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
+          <t>c3ce12272f7ed38b30827d0b90f279d89c29fbee539b967177eebd40f854bfd6</t>
         </is>
       </c>
       <c r="BE55" s="24" t="inlineStr">
@@ -16358,7 +16358,7 @@
       </c>
       <c r="BH55" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:17.395840Z</t>
+          <t>2026-07-30T17:38:54.184184Z</t>
         </is>
       </c>
       <c r="BI55" s="24" t="inlineStr">
@@ -16368,13 +16368,13 @@
       </c>
       <c r="BJ55" s="25" t="n"/>
       <c r="BK55" s="26" t="n">
-        <v>-133</v>
+        <v>-144</v>
       </c>
       <c r="BL55" s="27" t="n">
-        <v>1.75188</v>
+        <v>1.694444</v>
       </c>
       <c r="BM55" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.590164</v>
       </c>
       <c r="BN55" s="28" t="n"/>
       <c r="BO55" s="28" t="n"/>
@@ -16408,12 +16408,12 @@
     <row r="56" ht="36" customHeight="1">
       <c r="A56" s="24" t="inlineStr">
         <is>
-          <t>7e36301c26df456f</t>
+          <t>70fd763fe6ef4cdf</t>
         </is>
       </c>
       <c r="B56" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:29.146399Z</t>
+          <t>2026-07-30T17:39:06.974381Z</t>
         </is>
       </c>
       <c r="C56" s="24" t="inlineStr">
@@ -16467,11 +16467,11 @@
         <v>0.680511</v>
       </c>
       <c r="O56" s="28" t="n">
-        <v>0.565313</v>
+        <v>0.565295</v>
       </c>
       <c r="P56" s="28" t="n"/>
       <c r="Q56" s="28" t="n">
-        <v>-0.115198</v>
+        <v>-0.115216</v>
       </c>
       <c r="R56" s="26" t="n">
         <v>0</v>
@@ -16584,7 +16584,7 @@
       </c>
       <c r="BA56" s="24" t="inlineStr">
         <is>
-          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
+          <t>c3ce12272f7ed38b30827d0b90f279d89c29fbee539b967177eebd40f854bfd6</t>
         </is>
       </c>
       <c r="BB56" s="24" t="inlineStr">
@@ -16599,7 +16599,7 @@
       </c>
       <c r="BD56" s="24" t="inlineStr">
         <is>
-          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
+          <t>c3ce12272f7ed38b30827d0b90f279d89c29fbee539b967177eebd40f854bfd6</t>
         </is>
       </c>
       <c r="BE56" s="24" t="inlineStr">
@@ -16619,7 +16619,7 @@
       </c>
       <c r="BH56" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:17.854408Z</t>
+          <t>2026-07-30T17:38:54.630662Z</t>
         </is>
       </c>
       <c r="BI56" s="24" t="inlineStr">
@@ -16669,12 +16669,12 @@
     <row r="57" ht="36" customHeight="1">
       <c r="A57" s="24" t="inlineStr">
         <is>
-          <t>42c280920fa54570</t>
+          <t>f7c1ce3402b642a5</t>
         </is>
       </c>
       <c r="B57" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:29.146399Z</t>
+          <t>2026-07-30T17:39:06.974381Z</t>
         </is>
       </c>
       <c r="C57" s="24" t="inlineStr">
@@ -16719,23 +16719,23 @@
         </is>
       </c>
       <c r="L57" s="26" t="n">
-        <v>-122</v>
+        <v>-133</v>
       </c>
       <c r="M57" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.75188</v>
       </c>
       <c r="N57" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.570815</v>
       </c>
       <c r="O57" s="28" t="n">
-        <v>0.651531</v>
+        <v>0.650967</v>
       </c>
       <c r="P57" s="28" t="n"/>
       <c r="Q57" s="28" t="n">
-        <v>0.101981</v>
+        <v>0.080152</v>
       </c>
       <c r="R57" s="26" t="n">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="S57" s="29" t="n">
         <v>2</v>
@@ -16761,7 +16761,7 @@
       <c r="AD57" s="24" t="n"/>
       <c r="AE57" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-lol-gng-jsk-2026-07-30).</t>
+          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-lol-gng-jsk-2026-07-30).</t>
         </is>
       </c>
       <c r="AF57" s="31" t="inlineStr">
@@ -16845,7 +16845,7 @@
       </c>
       <c r="BA57" s="24" t="inlineStr">
         <is>
-          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
+          <t>c3ce12272f7ed38b30827d0b90f279d89c29fbee539b967177eebd40f854bfd6</t>
         </is>
       </c>
       <c r="BB57" s="24" t="inlineStr">
@@ -16860,7 +16860,7 @@
       </c>
       <c r="BD57" s="24" t="inlineStr">
         <is>
-          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
+          <t>c3ce12272f7ed38b30827d0b90f279d89c29fbee539b967177eebd40f854bfd6</t>
         </is>
       </c>
       <c r="BE57" s="24" t="inlineStr">
@@ -16880,7 +16880,7 @@
       </c>
       <c r="BH57" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:18.840084Z</t>
+          <t>2026-07-30T17:38:55.192074Z</t>
         </is>
       </c>
       <c r="BI57" s="24" t="inlineStr">
@@ -16890,13 +16890,13 @@
       </c>
       <c r="BJ57" s="25" t="n"/>
       <c r="BK57" s="26" t="n">
-        <v>-122</v>
+        <v>-133</v>
       </c>
       <c r="BL57" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.75188</v>
       </c>
       <c r="BM57" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.570815</v>
       </c>
       <c r="BN57" s="28" t="n"/>
       <c r="BO57" s="28" t="n"/>
@@ -16930,12 +16930,12 @@
     <row r="58" ht="36" customHeight="1">
       <c r="A58" s="24" t="inlineStr">
         <is>
-          <t>a580ef8f40ed40d0</t>
+          <t>3fe75b5d16414847</t>
         </is>
       </c>
       <c r="B58" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:29.146399Z</t>
+          <t>2026-07-30T17:39:06.974381Z</t>
         </is>
       </c>
       <c r="C58" s="24" t="inlineStr">
@@ -16989,11 +16989,11 @@
         <v>0.640288</v>
       </c>
       <c r="O58" s="28" t="n">
-        <v>0.621173</v>
+        <v>0.620999</v>
       </c>
       <c r="P58" s="28" t="n"/>
       <c r="Q58" s="28" t="n">
-        <v>-0.019115</v>
+        <v>-0.019289</v>
       </c>
       <c r="R58" s="26" t="n">
         <v>10</v>
@@ -17106,7 +17106,7 @@
       </c>
       <c r="BA58" s="24" t="inlineStr">
         <is>
-          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
+          <t>c3ce12272f7ed38b30827d0b90f279d89c29fbee539b967177eebd40f854bfd6</t>
         </is>
       </c>
       <c r="BB58" s="24" t="inlineStr">
@@ -17121,7 +17121,7 @@
       </c>
       <c r="BD58" s="24" t="inlineStr">
         <is>
-          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
+          <t>c3ce12272f7ed38b30827d0b90f279d89c29fbee539b967177eebd40f854bfd6</t>
         </is>
       </c>
       <c r="BE58" s="24" t="inlineStr">
@@ -17141,7 +17141,7 @@
       </c>
       <c r="BH58" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:19.790382Z</t>
+          <t>2026-07-30T17:38:56.309159Z</t>
         </is>
       </c>
       <c r="BI58" s="24" t="inlineStr">
@@ -17191,12 +17191,12 @@
     <row r="59" ht="36" customHeight="1">
       <c r="A59" s="24" t="inlineStr">
         <is>
-          <t>fda8a24f6e284939</t>
+          <t>5c40f87d94b84fd8</t>
         </is>
       </c>
       <c r="B59" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:29.146399Z</t>
+          <t>2026-07-30T17:39:06.974381Z</t>
         </is>
       </c>
       <c r="C59" s="24" t="inlineStr">
@@ -17206,7 +17206,7 @@
       </c>
       <c r="D59" s="24" t="inlineStr">
         <is>
-          <t>64670</t>
+          <t>64669</t>
         </is>
       </c>
       <c r="E59" s="24" t="inlineStr">
@@ -17216,12 +17216,12 @@
       </c>
       <c r="F59" s="24" t="inlineStr">
         <is>
-          <t>DN SOOPers Challengers</t>
+          <t>HANJIN BRION Challengers</t>
         </is>
       </c>
       <c r="G59" s="24" t="inlineStr">
         <is>
-          <t>KT Rolster Challengers</t>
+          <t>Kiwoom DRX Challengers</t>
         </is>
       </c>
       <c r="H59" s="24" t="inlineStr">
@@ -17231,7 +17231,7 @@
       </c>
       <c r="I59" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J59" s="25" t="n"/>
@@ -17241,26 +17241,26 @@
         </is>
       </c>
       <c r="L59" s="26" t="n">
-        <v>-138</v>
+        <v>170</v>
       </c>
       <c r="M59" s="27" t="n">
-        <v>1.724638</v>
+        <v>2.7</v>
       </c>
       <c r="N59" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.37037</v>
       </c>
       <c r="O59" s="28" t="n">
-        <v>0.5802349999999999</v>
+        <v>0.505587</v>
       </c>
       <c r="P59" s="28" t="n"/>
       <c r="Q59" s="28" t="n">
-        <v>0.000403</v>
+        <v>0.135217</v>
       </c>
       <c r="R59" s="26" t="n">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="S59" s="29" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T59" s="24" t="inlineStr">
         <is>
@@ -17283,7 +17283,7 @@
       <c r="AD59" s="24" t="n"/>
       <c r="AE59" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-lol-ktc-dnsc-2026-07-31).</t>
+          <t>Neutral Elo baseline; executable ask 0.3700 (market_slug=aec-lol-krxc-hbc-2026-07-31).</t>
         </is>
       </c>
       <c r="AF59" s="31" t="inlineStr">
@@ -17301,7 +17301,7 @@
       <c r="AJ59" s="31" t="n"/>
       <c r="AK59" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL59" s="26" t="n">
@@ -17309,47 +17309,47 @@
       </c>
       <c r="AM59" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN59" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO59" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
         </is>
       </c>
       <c r="AP59" s="24" t="inlineStr">
         <is>
-          <t>DN SOOPers Challengers</t>
+          <t>HANJIN BRION Challengers</t>
         </is>
       </c>
       <c r="AQ59" s="24" t="inlineStr">
         <is>
-          <t>DN SOOPers Challengers</t>
+          <t>HANJIN BRION Challengers</t>
         </is>
       </c>
       <c r="AR59" s="24" t="inlineStr">
         <is>
-          <t>DN SOOPers Challengers</t>
+          <t>HANJIN BRION Challengers</t>
         </is>
       </c>
       <c r="AS59" s="24" t="inlineStr">
         <is>
-          <t>KT Rolster Challengers</t>
+          <t>Kiwoom DRX Challengers</t>
         </is>
       </c>
       <c r="AT59" s="24" t="inlineStr">
         <is>
-          <t>KT Rolster Challengers</t>
+          <t>Kiwoom DRX Challengers</t>
         </is>
       </c>
       <c r="AU59" s="24" t="inlineStr">
         <is>
-          <t>KT Rolster Challengers</t>
+          <t>Kiwoom DRX Challengers</t>
         </is>
       </c>
       <c r="AV59" s="24" t="n"/>
@@ -17367,7 +17367,7 @@
       </c>
       <c r="BA59" s="24" t="inlineStr">
         <is>
-          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
+          <t>c3ce12272f7ed38b30827d0b90f279d89c29fbee539b967177eebd40f854bfd6</t>
         </is>
       </c>
       <c r="BB59" s="24" t="inlineStr">
@@ -17382,7 +17382,7 @@
       </c>
       <c r="BD59" s="24" t="inlineStr">
         <is>
-          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
+          <t>c3ce12272f7ed38b30827d0b90f279d89c29fbee539b967177eebd40f854bfd6</t>
         </is>
       </c>
       <c r="BE59" s="24" t="inlineStr">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="BH59" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:21.662513Z</t>
+          <t>2026-07-30T17:38:58.396679Z</t>
         </is>
       </c>
       <c r="BI59" s="24" t="inlineStr">
@@ -17412,13 +17412,13 @@
       </c>
       <c r="BJ59" s="25" t="n"/>
       <c r="BK59" s="26" t="n">
-        <v>-138</v>
+        <v>170</v>
       </c>
       <c r="BL59" s="27" t="n">
-        <v>1.724638</v>
+        <v>2.7</v>
       </c>
       <c r="BM59" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.37037</v>
       </c>
       <c r="BN59" s="28" t="n"/>
       <c r="BO59" s="28" t="n"/>
@@ -17452,12 +17452,12 @@
     <row r="60" ht="36" customHeight="1">
       <c r="A60" s="24" t="inlineStr">
         <is>
-          <t>d578f3249a734797</t>
+          <t>a69529769d2c43b7</t>
         </is>
       </c>
       <c r="B60" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:29.146399Z</t>
+          <t>2026-07-30T17:39:06.974381Z</t>
         </is>
       </c>
       <c r="C60" s="24" t="inlineStr">
@@ -17467,7 +17467,7 @@
       </c>
       <c r="D60" s="24" t="inlineStr">
         <is>
-          <t>64669</t>
+          <t>64670</t>
         </is>
       </c>
       <c r="E60" s="24" t="inlineStr">
@@ -17477,12 +17477,12 @@
       </c>
       <c r="F60" s="24" t="inlineStr">
         <is>
-          <t>HANJIN BRION Challengers</t>
+          <t>DN SOOPers Challengers</t>
         </is>
       </c>
       <c r="G60" s="24" t="inlineStr">
         <is>
-          <t>Kiwoom DRX Challengers</t>
+          <t>KT Rolster Challengers</t>
         </is>
       </c>
       <c r="H60" s="24" t="inlineStr">
@@ -17492,7 +17492,7 @@
       </c>
       <c r="I60" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J60" s="25" t="n"/>
@@ -17502,26 +17502,26 @@
         </is>
       </c>
       <c r="L60" s="26" t="n">
-        <v>170</v>
+        <v>-138</v>
       </c>
       <c r="M60" s="27" t="n">
-        <v>2.7</v>
+        <v>1.724638</v>
       </c>
       <c r="N60" s="28" t="n">
-        <v>0.37037</v>
+        <v>0.579832</v>
       </c>
       <c r="O60" s="28" t="n">
-        <v>0.505773</v>
+        <v>0.580174</v>
       </c>
       <c r="P60" s="28" t="n"/>
       <c r="Q60" s="28" t="n">
-        <v>0.135403</v>
+        <v>0.000342</v>
       </c>
       <c r="R60" s="26" t="n">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="S60" s="29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T60" s="24" t="inlineStr">
         <is>
@@ -17544,7 +17544,7 @@
       <c r="AD60" s="24" t="n"/>
       <c r="AE60" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3700 (market_slug=aec-lol-krxc-hbc-2026-07-31).</t>
+          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-lol-ktc-dnsc-2026-07-31).</t>
         </is>
       </c>
       <c r="AF60" s="31" t="inlineStr">
@@ -17562,7 +17562,7 @@
       <c r="AJ60" s="31" t="n"/>
       <c r="AK60" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL60" s="26" t="n">
@@ -17570,47 +17570,47 @@
       </c>
       <c r="AM60" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN60" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO60" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP60" s="24" t="inlineStr">
         <is>
-          <t>HANJIN BRION Challengers</t>
+          <t>DN SOOPers Challengers</t>
         </is>
       </c>
       <c r="AQ60" s="24" t="inlineStr">
         <is>
-          <t>HANJIN BRION Challengers</t>
+          <t>DN SOOPers Challengers</t>
         </is>
       </c>
       <c r="AR60" s="24" t="inlineStr">
         <is>
-          <t>HANJIN BRION Challengers</t>
+          <t>DN SOOPers Challengers</t>
         </is>
       </c>
       <c r="AS60" s="24" t="inlineStr">
         <is>
-          <t>Kiwoom DRX Challengers</t>
+          <t>KT Rolster Challengers</t>
         </is>
       </c>
       <c r="AT60" s="24" t="inlineStr">
         <is>
-          <t>Kiwoom DRX Challengers</t>
+          <t>KT Rolster Challengers</t>
         </is>
       </c>
       <c r="AU60" s="24" t="inlineStr">
         <is>
-          <t>Kiwoom DRX Challengers</t>
+          <t>KT Rolster Challengers</t>
         </is>
       </c>
       <c r="AV60" s="24" t="n"/>
@@ -17628,7 +17628,7 @@
       </c>
       <c r="BA60" s="24" t="inlineStr">
         <is>
-          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
+          <t>c3ce12272f7ed38b30827d0b90f279d89c29fbee539b967177eebd40f854bfd6</t>
         </is>
       </c>
       <c r="BB60" s="24" t="inlineStr">
@@ -17643,7 +17643,7 @@
       </c>
       <c r="BD60" s="24" t="inlineStr">
         <is>
-          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
+          <t>c3ce12272f7ed38b30827d0b90f279d89c29fbee539b967177eebd40f854bfd6</t>
         </is>
       </c>
       <c r="BE60" s="24" t="inlineStr">
@@ -17663,7 +17663,7 @@
       </c>
       <c r="BH60" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:22.135548Z</t>
+          <t>2026-07-30T17:38:58.928794Z</t>
         </is>
       </c>
       <c r="BI60" s="24" t="inlineStr">
@@ -17673,13 +17673,13 @@
       </c>
       <c r="BJ60" s="25" t="n"/>
       <c r="BK60" s="26" t="n">
-        <v>170</v>
+        <v>-138</v>
       </c>
       <c r="BL60" s="27" t="n">
-        <v>2.7</v>
+        <v>1.724638</v>
       </c>
       <c r="BM60" s="28" t="n">
-        <v>0.37037</v>
+        <v>0.579832</v>
       </c>
       <c r="BN60" s="28" t="n"/>
       <c r="BO60" s="28" t="n"/>
@@ -17713,12 +17713,12 @@
     <row r="61" ht="36" customHeight="1">
       <c r="A61" s="24" t="inlineStr">
         <is>
-          <t>11d943896a5f4699</t>
+          <t>a90bb1f180a341f3</t>
         </is>
       </c>
       <c r="B61" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:29.146399Z</t>
+          <t>2026-07-30T17:39:06.974381Z</t>
         </is>
       </c>
       <c r="C61" s="24" t="inlineStr">
@@ -17763,20 +17763,20 @@
         </is>
       </c>
       <c r="L61" s="26" t="n">
-        <v>-170</v>
+        <v>-178</v>
       </c>
       <c r="M61" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.561798</v>
       </c>
       <c r="N61" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.640288</v>
       </c>
       <c r="O61" s="28" t="n">
-        <v>0.567988</v>
+        <v>0.567962</v>
       </c>
       <c r="P61" s="28" t="n"/>
       <c r="Q61" s="28" t="n">
-        <v>-0.061642</v>
+        <v>-0.072326</v>
       </c>
       <c r="R61" s="26" t="n">
         <v>0</v>
@@ -17805,7 +17805,7 @@
       <c r="AD61" s="24" t="n"/>
       <c r="AE61" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-lol-gen-t1-2026-07-31).</t>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-lol-gen-t1-2026-07-31).</t>
         </is>
       </c>
       <c r="AF61" s="31" t="inlineStr">
@@ -17889,7 +17889,7 @@
       </c>
       <c r="BA61" s="24" t="inlineStr">
         <is>
-          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
+          <t>c3ce12272f7ed38b30827d0b90f279d89c29fbee539b967177eebd40f854bfd6</t>
         </is>
       </c>
       <c r="BB61" s="24" t="inlineStr">
@@ -17904,7 +17904,7 @@
       </c>
       <c r="BD61" s="24" t="inlineStr">
         <is>
-          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
+          <t>c3ce12272f7ed38b30827d0b90f279d89c29fbee539b967177eebd40f854bfd6</t>
         </is>
       </c>
       <c r="BE61" s="24" t="inlineStr">
@@ -17924,7 +17924,7 @@
       </c>
       <c r="BH61" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:23.220632Z</t>
+          <t>2026-07-30T17:39:00.235027Z</t>
         </is>
       </c>
       <c r="BI61" s="24" t="inlineStr">
@@ -17934,13 +17934,13 @@
       </c>
       <c r="BJ61" s="25" t="n"/>
       <c r="BK61" s="26" t="n">
-        <v>-170</v>
+        <v>-178</v>
       </c>
       <c r="BL61" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.561798</v>
       </c>
       <c r="BM61" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.640288</v>
       </c>
       <c r="BN61" s="28" t="n"/>
       <c r="BO61" s="28" t="n"/>
@@ -17974,12 +17974,12 @@
     <row r="62" ht="36" customHeight="1">
       <c r="A62" s="24" t="inlineStr">
         <is>
-          <t>5d39e5674a434284</t>
+          <t>ed8f5a406a3d4ed9</t>
         </is>
       </c>
       <c r="B62" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:29.146399Z</t>
+          <t>2026-07-30T17:39:06.974381Z</t>
         </is>
       </c>
       <c r="C62" s="24" t="inlineStr">
@@ -18033,11 +18033,11 @@
         <v>0.4</v>
       </c>
       <c r="O62" s="28" t="n">
-        <v>0.502953</v>
+        <v>0.5027740000000001</v>
       </c>
       <c r="P62" s="28" t="n"/>
       <c r="Q62" s="28" t="n">
-        <v>0.102953</v>
+        <v>0.102774</v>
       </c>
       <c r="R62" s="26" t="n">
         <v>71</v>
@@ -18150,7 +18150,7 @@
       </c>
       <c r="BA62" s="24" t="inlineStr">
         <is>
-          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
+          <t>c3ce12272f7ed38b30827d0b90f279d89c29fbee539b967177eebd40f854bfd6</t>
         </is>
       </c>
       <c r="BB62" s="24" t="inlineStr">
@@ -18165,7 +18165,7 @@
       </c>
       <c r="BD62" s="24" t="inlineStr">
         <is>
-          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
+          <t>c3ce12272f7ed38b30827d0b90f279d89c29fbee539b967177eebd40f854bfd6</t>
         </is>
       </c>
       <c r="BE62" s="24" t="inlineStr">
@@ -18185,7 +18185,7 @@
       </c>
       <c r="BH62" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:24.630616Z</t>
+          <t>2026-07-30T17:39:01.920248Z</t>
         </is>
       </c>
       <c r="BI62" s="24" t="inlineStr">
@@ -18235,12 +18235,12 @@
     <row r="63" ht="36" customHeight="1">
       <c r="A63" s="24" t="inlineStr">
         <is>
-          <t>19a36a40b4714919</t>
+          <t>664ab7a4288d44ff</t>
         </is>
       </c>
       <c r="B63" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:29.146399Z</t>
+          <t>2026-07-30T17:39:06.974381Z</t>
         </is>
       </c>
       <c r="C63" s="24" t="inlineStr">
@@ -18294,11 +18294,11 @@
         <v>0.609375</v>
       </c>
       <c r="O63" s="28" t="n">
-        <v>0.649952</v>
+        <v>0.649392</v>
       </c>
       <c r="P63" s="28" t="n"/>
       <c r="Q63" s="28" t="n">
-        <v>0.040577</v>
+        <v>0.040017</v>
       </c>
       <c r="R63" s="26" t="n">
         <v>40</v>
@@ -18411,7 +18411,7 @@
       </c>
       <c r="BA63" s="24" t="inlineStr">
         <is>
-          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
+          <t>c3ce12272f7ed38b30827d0b90f279d89c29fbee539b967177eebd40f854bfd6</t>
         </is>
       </c>
       <c r="BB63" s="24" t="inlineStr">
@@ -18426,7 +18426,7 @@
       </c>
       <c r="BD63" s="24" t="inlineStr">
         <is>
-          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
+          <t>c3ce12272f7ed38b30827d0b90f279d89c29fbee539b967177eebd40f854bfd6</t>
         </is>
       </c>
       <c r="BE63" s="24" t="inlineStr">
@@ -18446,7 +18446,7 @@
       </c>
       <c r="BH63" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:25.109653Z</t>
+          <t>2026-07-30T17:39:02.536741Z</t>
         </is>
       </c>
       <c r="BI63" s="24" t="inlineStr">
@@ -18496,12 +18496,12 @@
     <row r="64" ht="36" customHeight="1">
       <c r="A64" s="24" t="inlineStr">
         <is>
-          <t>6dd123104c8b4bf1</t>
+          <t>1a5d465171574d72</t>
         </is>
       </c>
       <c r="B64" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:29.146399Z</t>
+          <t>2026-07-30T17:39:06.974381Z</t>
         </is>
       </c>
       <c r="C64" s="24" t="inlineStr">
@@ -18555,11 +18555,11 @@
         <v>0.409836</v>
       </c>
       <c r="O64" s="28" t="n">
-        <v>0.582579</v>
+        <v>0.58218</v>
       </c>
       <c r="P64" s="28" t="n"/>
       <c r="Q64" s="28" t="n">
-        <v>0.172743</v>
+        <v>0.172344</v>
       </c>
       <c r="R64" s="26" t="n">
         <v>100</v>
@@ -18672,7 +18672,7 @@
       </c>
       <c r="BA64" s="24" t="inlineStr">
         <is>
-          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
+          <t>c3ce12272f7ed38b30827d0b90f279d89c29fbee539b967177eebd40f854bfd6</t>
         </is>
       </c>
       <c r="BB64" s="24" t="inlineStr">
@@ -18687,7 +18687,7 @@
       </c>
       <c r="BD64" s="24" t="inlineStr">
         <is>
-          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
+          <t>c3ce12272f7ed38b30827d0b90f279d89c29fbee539b967177eebd40f854bfd6</t>
         </is>
       </c>
       <c r="BE64" s="24" t="inlineStr">
@@ -18707,7 +18707,7 @@
       </c>
       <c r="BH64" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:26.089989Z</t>
+          <t>2026-07-30T17:39:03.601758Z</t>
         </is>
       </c>
       <c r="BI64" s="24" t="inlineStr">
@@ -18757,12 +18757,12 @@
     <row r="65" ht="36" customHeight="1">
       <c r="A65" s="24" t="inlineStr">
         <is>
-          <t>f861803cd4a74db2</t>
+          <t>90658d0c150b43af</t>
         </is>
       </c>
       <c r="B65" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:29.146399Z</t>
+          <t>2026-07-30T17:39:06.974381Z</t>
         </is>
       </c>
       <c r="C65" s="24" t="inlineStr">
@@ -18807,20 +18807,20 @@
         </is>
       </c>
       <c r="L65" s="26" t="n">
-        <v>-133</v>
+        <v>-156</v>
       </c>
       <c r="M65" s="27" t="n">
-        <v>1.75188</v>
+        <v>1.641026</v>
       </c>
       <c r="N65" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.609375</v>
       </c>
       <c r="O65" s="28" t="n">
-        <v>0.527796</v>
+        <v>0.527886</v>
       </c>
       <c r="P65" s="28" t="n"/>
       <c r="Q65" s="28" t="n">
-        <v>-0.043019</v>
+        <v>-0.08148900000000001</v>
       </c>
       <c r="R65" s="26" t="n">
         <v>0</v>
@@ -18849,7 +18849,7 @@
       <c r="AD65" s="24" t="n"/>
       <c r="AE65" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-lol-zena-tts-2026-07-31).</t>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-lol-zena-tts-2026-07-31).</t>
         </is>
       </c>
       <c r="AF65" s="31" t="inlineStr">
@@ -18933,7 +18933,7 @@
       </c>
       <c r="BA65" s="24" t="inlineStr">
         <is>
-          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
+          <t>c3ce12272f7ed38b30827d0b90f279d89c29fbee539b967177eebd40f854bfd6</t>
         </is>
       </c>
       <c r="BB65" s="24" t="inlineStr">
@@ -18948,7 +18948,7 @@
       </c>
       <c r="BD65" s="24" t="inlineStr">
         <is>
-          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
+          <t>c3ce12272f7ed38b30827d0b90f279d89c29fbee539b967177eebd40f854bfd6</t>
         </is>
       </c>
       <c r="BE65" s="24" t="inlineStr">
@@ -18968,7 +18968,7 @@
       </c>
       <c r="BH65" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:28.135625Z</t>
+          <t>2026-07-30T17:39:05.771299Z</t>
         </is>
       </c>
       <c r="BI65" s="24" t="inlineStr">
@@ -18978,13 +18978,13 @@
       </c>
       <c r="BJ65" s="25" t="n"/>
       <c r="BK65" s="26" t="n">
-        <v>-133</v>
+        <v>-156</v>
       </c>
       <c r="BL65" s="27" t="n">
-        <v>1.75188</v>
+        <v>1.641026</v>
       </c>
       <c r="BM65" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.609375</v>
       </c>
       <c r="BN65" s="28" t="n"/>
       <c r="BO65" s="28" t="n"/>
@@ -19018,12 +19018,12 @@
     <row r="66" ht="36" customHeight="1">
       <c r="A66" s="24" t="inlineStr">
         <is>
-          <t>2b7f14f09d044afd</t>
+          <t>f1ae82d2346e4609</t>
         </is>
       </c>
       <c r="B66" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:29.146399Z</t>
+          <t>2026-07-30T17:39:06.974381Z</t>
         </is>
       </c>
       <c r="C66" s="24" t="inlineStr">
@@ -19077,11 +19077,11 @@
         <v>0.6</v>
       </c>
       <c r="O66" s="28" t="n">
-        <v>0.616673</v>
+        <v>0.616189</v>
       </c>
       <c r="P66" s="28" t="n"/>
       <c r="Q66" s="28" t="n">
-        <v>0.016673</v>
+        <v>0.016189</v>
       </c>
       <c r="R66" s="26" t="n">
         <v>28</v>
@@ -19194,7 +19194,7 @@
       </c>
       <c r="BA66" s="24" t="inlineStr">
         <is>
-          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
+          <t>c3ce12272f7ed38b30827d0b90f279d89c29fbee539b967177eebd40f854bfd6</t>
         </is>
       </c>
       <c r="BB66" s="24" t="inlineStr">
@@ -19209,7 +19209,7 @@
       </c>
       <c r="BD66" s="24" t="inlineStr">
         <is>
-          <t>be4f8256d05598c9d21c7a2ebe2351512630ea80ae3f06f1012082079379ce3a</t>
+          <t>c3ce12272f7ed38b30827d0b90f279d89c29fbee539b967177eebd40f854bfd6</t>
         </is>
       </c>
       <c r="BE66" s="24" t="inlineStr">
@@ -19229,7 +19229,7 @@
       </c>
       <c r="BH66" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:28.657597Z</t>
+          <t>2026-07-30T17:39:06.401584Z</t>
         </is>
       </c>
       <c r="BI66" s="24" t="inlineStr">

--- a/data/research/lol.xlsx
+++ b/data/research/lol.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO23" headerRowCount="1">
-  <autoFilter ref="A1:CO23"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO26" headerRowCount="1">
+  <autoFilter ref="A1:CO26"/>
   <tableColumns count="93">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -752,19 +752,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$23)</f>
+        <f>COUNTA('Picks'!$A$2:$A$26)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$23,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$26,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$23,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$26,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"win")+COUNTIFS('Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"win")+COUNTIFS('Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -792,19 +792,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$23,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$26,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$23,"&gt;0",'Picks'!$V$2:$V$23,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$23,"&gt;0",'Picks'!$V$2:$V$23,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$26,"&gt;0",'Picks'!$V$2:$V$26,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$26,"&gt;0",'Picks'!$V$2:$V$26,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$23,"&gt;0",'Picks'!$V$2:$V$23,"win")/(COUNTIFS('Picks'!$BX$2:$BX$23,"&gt;0",'Picks'!$V$2:$V$23,"win")+COUNTIFS('Picks'!$BX$2:$BX$23,"&gt;0",'Picks'!$V$2:$V$23,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$26,"&gt;0",'Picks'!$V$2:$V$26,"win")/(COUNTIFS('Picks'!$BX$2:$BX$26,"&gt;0",'Picks'!$V$2:$V$26,"win")+COUNTIFS('Picks'!$BX$2:$BX$26,"&gt;0",'Picks'!$V$2:$V$26,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$23)/SUM('Picks'!$BX$2:$BX$23),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$26)/SUM('Picks'!$BX$2:$BX$26),0)</f>
         <v/>
       </c>
     </row>
@@ -832,19 +832,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$23)</f>
+        <f>SUM('Picks'!$BY$2:$BY$26)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$23,"&lt;&gt;",'Picks'!$AB$2:$AB$23),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$26,"&lt;&gt;",'Picks'!$AB$2:$AB$26),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$23,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$23,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$26,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$26,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$23,'Picks'!$AM$2:$AM$23,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$26,'Picks'!$AM$2:$AM$26,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -899,15 +899,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$23,$A14,'Picks'!$U$2:$U$23,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$26,$A14,'Picks'!$U$2:$U$26,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$23,$A14,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$26,$A14,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$23,$A14,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$26,$A14,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -915,11 +915,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$23,'Picks'!$H$2:$H$23,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$26,'Picks'!$H$2:$H$26,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$23,'Picks'!$H$2:$H$23,$A14,'Picks'!$U$2:$U$23,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$26,'Picks'!$H$2:$H$26,$A14,'Picks'!$U$2:$U$26,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -930,15 +930,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$23,$A15,'Picks'!$U$2:$U$23,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$26,$A15,'Picks'!$U$2:$U$26,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$23,$A15,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$26,$A15,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$23,$A15,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$26,$A15,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -946,11 +946,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$23,'Picks'!$H$2:$H$23,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$26,'Picks'!$H$2:$H$26,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$23,'Picks'!$H$2:$H$23,$A15,'Picks'!$U$2:$U$23,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$26,'Picks'!$H$2:$H$26,$A15,'Picks'!$U$2:$U$26,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -961,15 +961,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$23,$A16,'Picks'!$U$2:$U$23,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$26,$A16,'Picks'!$U$2:$U$26,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$23,$A16,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$26,$A16,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$23,$A16,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$26,$A16,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -977,11 +977,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$23,'Picks'!$H$2:$H$23,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$26,'Picks'!$H$2:$H$26,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$23,'Picks'!$H$2:$H$23,$A16,'Picks'!$U$2:$U$23,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$26,'Picks'!$H$2:$H$26,$A16,'Picks'!$U$2:$U$26,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO23"/>
+  <dimension ref="A1:CO26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4713,22 +4713,22 @@
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
         <is>
-          <t>2ef79f8aa8e24ba5</t>
+          <t>73f8433cce1a461e</t>
         </is>
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T20:32:32.284273Z</t>
+          <t>2026-08-02T06:51:56.046278Z</t>
         </is>
       </c>
       <c r="C13" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T08:00:00Z</t>
+          <t>2026-08-02T07:00:00Z</t>
         </is>
       </c>
       <c r="D13" s="24" t="inlineStr">
         <is>
-          <t>67491</t>
+          <t>66779</t>
         </is>
       </c>
       <c r="E13" s="24" t="inlineStr">
@@ -4738,12 +4738,12 @@
       </c>
       <c r="F13" s="24" t="inlineStr">
         <is>
-          <t>Hanwha Life Esports</t>
+          <t>Team WE</t>
         </is>
       </c>
       <c r="G13" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>ThunderTalk Gaming</t>
         </is>
       </c>
       <c r="H13" s="24" t="inlineStr">
@@ -4763,26 +4763,26 @@
         </is>
       </c>
       <c r="L13" s="26" t="n">
-        <v>-117</v>
+        <v>-233</v>
       </c>
       <c r="M13" s="27" t="n">
-        <v>1.854701</v>
+        <v>1.429185</v>
       </c>
       <c r="N13" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.6997</v>
       </c>
       <c r="O13" s="28" t="n">
-        <v>0.581905</v>
+        <v>0.652554</v>
       </c>
       <c r="P13" s="28" t="n"/>
       <c r="Q13" s="28" t="n">
-        <v>0.042734</v>
+        <v>-0.047146</v>
       </c>
       <c r="R13" s="26" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="S13" s="29" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="T13" s="24" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
       <c r="AD13" s="24" t="n"/>
       <c r="AE13" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-lol-gen-hle-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-lol-tt-we-2026-08-02).</t>
         </is>
       </c>
       <c r="AF13" s="31" t="inlineStr">
@@ -4823,7 +4823,7 @@
       <c r="AJ13" s="31" t="n"/>
       <c r="AK13" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL13" s="26" t="n">
@@ -4831,47 +4831,47 @@
       </c>
       <c r="AM13" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN13" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO13" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP13" s="24" t="inlineStr">
         <is>
-          <t>Hanwha Life Esports</t>
+          <t>Team WE</t>
         </is>
       </c>
       <c r="AQ13" s="24" t="inlineStr">
         <is>
-          <t>Hanwha Life Esports</t>
+          <t>Team WE</t>
         </is>
       </c>
       <c r="AR13" s="24" t="inlineStr">
         <is>
-          <t>Hanwha Life Esports</t>
+          <t>Team WE</t>
         </is>
       </c>
       <c r="AS13" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>ThunderTalk Gaming</t>
         </is>
       </c>
       <c r="AT13" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>ThunderTalk Gaming</t>
         </is>
       </c>
       <c r="AU13" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>ThunderTalk Gaming</t>
         </is>
       </c>
       <c r="AV13" s="24" t="n"/>
@@ -4889,7 +4889,7 @@
       </c>
       <c r="BA13" s="24" t="inlineStr">
         <is>
-          <t>229baf64b9a74bdaa3fee70ecd0bde2986f6e2d651a8f5efad46c765670e1ff3</t>
+          <t>bdf823330923d145365ad4f6a02dd0ec337f4e55dcb78716824f971491f65d6e</t>
         </is>
       </c>
       <c r="BB13" s="24" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="BD13" s="24" t="inlineStr">
         <is>
-          <t>229baf64b9a74bdaa3fee70ecd0bde2986f6e2d651a8f5efad46c765670e1ff3</t>
+          <t>bdf823330923d145365ad4f6a02dd0ec337f4e55dcb78716824f971491f65d6e</t>
         </is>
       </c>
       <c r="BE13" s="24" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="BH13" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T20:32:24.237849Z</t>
+          <t>2026-08-02T06:51:40.260979Z</t>
         </is>
       </c>
       <c r="BI13" s="24" t="inlineStr">
@@ -4934,13 +4934,13 @@
       </c>
       <c r="BJ13" s="25" t="n"/>
       <c r="BK13" s="26" t="n">
-        <v>-117</v>
+        <v>-233</v>
       </c>
       <c r="BL13" s="27" t="n">
-        <v>1.854701</v>
+        <v>1.429185</v>
       </c>
       <c r="BM13" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.6997</v>
       </c>
       <c r="BN13" s="28" t="n"/>
       <c r="BO13" s="28" t="n"/>
@@ -4974,22 +4974,22 @@
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="24" t="inlineStr">
         <is>
-          <t>cdd3f968df384093</t>
+          <t>ea2d86c22c2d4903</t>
         </is>
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T20:32:32.284273Z</t>
+          <t>2026-08-02T07:15:56.246313Z</t>
         </is>
       </c>
       <c r="C14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T08:00:00Z</t>
+          <t>2026-08-02T10:00:00Z</t>
         </is>
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>67492</t>
+          <t>66811</t>
         </is>
       </c>
       <c r="E14" s="24" t="inlineStr">
@@ -4999,12 +4999,12 @@
       </c>
       <c r="F14" s="24" t="inlineStr">
         <is>
-          <t>BNK FearX Youth</t>
+          <t>Ancient Ones</t>
         </is>
       </c>
       <c r="G14" s="24" t="inlineStr">
         <is>
-          <t>HANJIN BRION Challengers</t>
+          <t>Crystal Rose</t>
         </is>
       </c>
       <c r="H14" s="24" t="inlineStr">
@@ -5024,23 +5024,23 @@
         </is>
       </c>
       <c r="L14" s="26" t="n">
-        <v>-203</v>
+        <v>170</v>
       </c>
       <c r="M14" s="27" t="n">
-        <v>1.492611</v>
+        <v>2.7</v>
       </c>
       <c r="N14" s="28" t="n">
-        <v>0.669967</v>
+        <v>0.37037</v>
       </c>
       <c r="O14" s="28" t="n">
-        <v>0.635857</v>
+        <v>0.615811</v>
       </c>
       <c r="P14" s="28" t="n"/>
       <c r="Q14" s="28" t="n">
-        <v>-0.03411</v>
+        <v>0.245441</v>
       </c>
       <c r="R14" s="26" t="n">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="S14" s="29" t="n">
         <v>1.5</v>
@@ -5066,7 +5066,7 @@
       <c r="AD14" s="24" t="n"/>
       <c r="AE14" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-lol-hbc-foxy-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.3700 (market_slug=aec-lol-cr-ao-2026-08-02).</t>
         </is>
       </c>
       <c r="AF14" s="31" t="inlineStr">
@@ -5084,7 +5084,7 @@
       <c r="AJ14" s="31" t="n"/>
       <c r="AK14" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL14" s="26" t="n">
@@ -5092,47 +5092,47 @@
       </c>
       <c r="AM14" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN14" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO14" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP14" s="24" t="inlineStr">
         <is>
-          <t>BNK FearX Youth</t>
+          <t>Ancient Ones</t>
         </is>
       </c>
       <c r="AQ14" s="24" t="inlineStr">
         <is>
-          <t>BNK FearX Youth</t>
+          <t>Ancient Ones</t>
         </is>
       </c>
       <c r="AR14" s="24" t="inlineStr">
         <is>
-          <t>BNK FearX Youth</t>
+          <t>Ancient Ones</t>
         </is>
       </c>
       <c r="AS14" s="24" t="inlineStr">
         <is>
-          <t>HANJIN BRION Challengers</t>
+          <t>Crystal Rose</t>
         </is>
       </c>
       <c r="AT14" s="24" t="inlineStr">
         <is>
-          <t>HANJIN BRION Challengers</t>
+          <t>Crystal Rose</t>
         </is>
       </c>
       <c r="AU14" s="24" t="inlineStr">
         <is>
-          <t>HANJIN BRION Challengers</t>
+          <t>Crystal Rose</t>
         </is>
       </c>
       <c r="AV14" s="24" t="n"/>
@@ -5150,7 +5150,7 @@
       </c>
       <c r="BA14" s="24" t="inlineStr">
         <is>
-          <t>229baf64b9a74bdaa3fee70ecd0bde2986f6e2d651a8f5efad46c765670e1ff3</t>
+          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
         </is>
       </c>
       <c r="BB14" s="24" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="BD14" s="24" t="inlineStr">
         <is>
-          <t>229baf64b9a74bdaa3fee70ecd0bde2986f6e2d651a8f5efad46c765670e1ff3</t>
+          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
         </is>
       </c>
       <c r="BE14" s="24" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="BH14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T20:32:24.725130Z</t>
+          <t>2026-08-02T07:15:42.166882Z</t>
         </is>
       </c>
       <c r="BI14" s="24" t="inlineStr">
@@ -5195,13 +5195,13 @@
       </c>
       <c r="BJ14" s="25" t="n"/>
       <c r="BK14" s="26" t="n">
-        <v>-203</v>
+        <v>170</v>
       </c>
       <c r="BL14" s="27" t="n">
-        <v>1.492611</v>
+        <v>2.7</v>
       </c>
       <c r="BM14" s="28" t="n">
-        <v>0.669967</v>
+        <v>0.37037</v>
       </c>
       <c r="BN14" s="28" t="n"/>
       <c r="BO14" s="28" t="n"/>
@@ -5235,22 +5235,22 @@
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="24" t="inlineStr">
         <is>
-          <t>a37b0ad25559475f</t>
+          <t>d448911e6ca34774</t>
         </is>
       </c>
       <c r="B15" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T20:32:32.284273Z</t>
+          <t>2026-08-02T07:15:56.246313Z</t>
         </is>
       </c>
       <c r="C15" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T10:00:00Z</t>
+          <t>2026-08-02T11:00:00Z</t>
         </is>
       </c>
       <c r="D15" s="24" t="inlineStr">
         <is>
-          <t>67511</t>
+          <t>66837</t>
         </is>
       </c>
       <c r="E15" s="24" t="inlineStr">
@@ -5260,12 +5260,12 @@
       </c>
       <c r="F15" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA Challengers</t>
+          <t>Lille Esport</t>
         </is>
       </c>
       <c r="G15" s="24" t="inlineStr">
         <is>
-          <t>DN SOOPers Challengers</t>
+          <t>Lausanne-Sport Esports</t>
         </is>
       </c>
       <c r="H15" s="24" t="inlineStr">
@@ -5275,7 +5275,7 @@
       </c>
       <c r="I15" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J15" s="25" t="n"/>
@@ -5285,26 +5285,26 @@
         </is>
       </c>
       <c r="L15" s="26" t="n">
-        <v>-223</v>
+        <v>108</v>
       </c>
       <c r="M15" s="27" t="n">
-        <v>1.44843</v>
+        <v>2.08</v>
       </c>
       <c r="N15" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.480769</v>
       </c>
       <c r="O15" s="28" t="n">
-        <v>0.705384</v>
+        <v>0.58589</v>
       </c>
       <c r="P15" s="28" t="n"/>
       <c r="Q15" s="28" t="n">
-        <v>0.014982</v>
+        <v>0.105121</v>
       </c>
       <c r="R15" s="26" t="n">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="S15" s="29" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="T15" s="24" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
       <c r="AD15" s="24" t="n"/>
       <c r="AE15" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-lol-dnsc-dkc-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.4800 (market_slug=aec-lol-els-lil-2026-08-02).</t>
         </is>
       </c>
       <c r="AF15" s="31" t="inlineStr">
@@ -5368,32 +5368,32 @@
       </c>
       <c r="AP15" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA Challengers</t>
+          <t>Lille Esport</t>
         </is>
       </c>
       <c r="AQ15" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA Challengers</t>
+          <t>Lille Esport</t>
         </is>
       </c>
       <c r="AR15" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA Challengers</t>
+          <t>Lille Esport</t>
         </is>
       </c>
       <c r="AS15" s="24" t="inlineStr">
         <is>
-          <t>DN SOOPers Challengers</t>
+          <t>Lausanne-Sport Esports</t>
         </is>
       </c>
       <c r="AT15" s="24" t="inlineStr">
         <is>
-          <t>DN SOOPers Challengers</t>
+          <t>Lausanne-Sport Esports</t>
         </is>
       </c>
       <c r="AU15" s="24" t="inlineStr">
         <is>
-          <t>DN SOOPers Challengers</t>
+          <t>Lausanne-Sport Esports</t>
         </is>
       </c>
       <c r="AV15" s="24" t="n"/>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="BA15" s="24" t="inlineStr">
         <is>
-          <t>229baf64b9a74bdaa3fee70ecd0bde2986f6e2d651a8f5efad46c765670e1ff3</t>
+          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
         </is>
       </c>
       <c r="BB15" s="24" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="BD15" s="24" t="inlineStr">
         <is>
-          <t>229baf64b9a74bdaa3fee70ecd0bde2986f6e2d651a8f5efad46c765670e1ff3</t>
+          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
         </is>
       </c>
       <c r="BE15" s="24" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="BH15" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T20:32:25.226163Z</t>
+          <t>2026-08-02T07:15:42.626245Z</t>
         </is>
       </c>
       <c r="BI15" s="24" t="inlineStr">
@@ -5456,13 +5456,13 @@
       </c>
       <c r="BJ15" s="25" t="n"/>
       <c r="BK15" s="26" t="n">
-        <v>-223</v>
+        <v>108</v>
       </c>
       <c r="BL15" s="27" t="n">
-        <v>1.44843</v>
+        <v>2.08</v>
       </c>
       <c r="BM15" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.480769</v>
       </c>
       <c r="BN15" s="28" t="n"/>
       <c r="BO15" s="28" t="n"/>
@@ -5496,22 +5496,22 @@
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="24" t="inlineStr">
         <is>
-          <t>a366f6a535204619</t>
+          <t>30d50d5f99ff41cc</t>
         </is>
       </c>
       <c r="B16" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T20:32:32.284273Z</t>
+          <t>2026-08-02T07:15:56.246313Z</t>
         </is>
       </c>
       <c r="C16" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T10:30:00Z</t>
+          <t>2026-08-02T11:00:00Z</t>
         </is>
       </c>
       <c r="D16" s="24" t="inlineStr">
         <is>
-          <t>67515</t>
+          <t>66838</t>
         </is>
       </c>
       <c r="E16" s="24" t="inlineStr">
@@ -5521,12 +5521,12 @@
       </c>
       <c r="F16" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>JD Gaming</t>
         </is>
       </c>
       <c r="G16" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Red Force</t>
+          <t>Top Esports</t>
         </is>
       </c>
       <c r="H16" s="24" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="I16" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J16" s="25" t="n"/>
@@ -5546,26 +5546,26 @@
         </is>
       </c>
       <c r="L16" s="26" t="n">
-        <v>-170</v>
+        <v>-117</v>
       </c>
       <c r="M16" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.854701</v>
       </c>
       <c r="N16" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.539171</v>
       </c>
       <c r="O16" s="28" t="n">
-        <v>0.748331</v>
+        <v>0.549306</v>
       </c>
       <c r="P16" s="28" t="n"/>
       <c r="Q16" s="28" t="n">
-        <v>0.118701</v>
+        <v>0.010135</v>
       </c>
       <c r="R16" s="26" t="n">
-        <v>79</v>
+        <v>25</v>
       </c>
       <c r="S16" s="29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T16" s="24" t="inlineStr">
         <is>
@@ -5588,7 +5588,7 @@
       <c r="AD16" s="24" t="n"/>
       <c r="AE16" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-lol-ns-t1-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-lol-tes-jdg-2026-08-02).</t>
         </is>
       </c>
       <c r="AF16" s="31" t="inlineStr">
@@ -5606,7 +5606,7 @@
       <c r="AJ16" s="31" t="n"/>
       <c r="AK16" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL16" s="26" t="n">
@@ -5614,47 +5614,47 @@
       </c>
       <c r="AM16" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN16" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO16" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP16" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>JD Gaming</t>
         </is>
       </c>
       <c r="AQ16" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>JD Gaming</t>
         </is>
       </c>
       <c r="AR16" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>JD Gaming</t>
         </is>
       </c>
       <c r="AS16" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Red Force</t>
+          <t>Top Esports</t>
         </is>
       </c>
       <c r="AT16" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Red Force</t>
+          <t>Top Esports</t>
         </is>
       </c>
       <c r="AU16" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Red Force</t>
+          <t>Top Esports</t>
         </is>
       </c>
       <c r="AV16" s="24" t="n"/>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="BA16" s="24" t="inlineStr">
         <is>
-          <t>229baf64b9a74bdaa3fee70ecd0bde2986f6e2d651a8f5efad46c765670e1ff3</t>
+          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
         </is>
       </c>
       <c r="BB16" s="24" t="inlineStr">
@@ -5687,7 +5687,7 @@
       </c>
       <c r="BD16" s="24" t="inlineStr">
         <is>
-          <t>229baf64b9a74bdaa3fee70ecd0bde2986f6e2d651a8f5efad46c765670e1ff3</t>
+          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
         </is>
       </c>
       <c r="BE16" s="24" t="inlineStr">
@@ -5707,7 +5707,7 @@
       </c>
       <c r="BH16" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T20:32:25.741380Z</t>
+          <t>2026-08-02T07:15:43.093607Z</t>
         </is>
       </c>
       <c r="BI16" s="24" t="inlineStr">
@@ -5717,13 +5717,13 @@
       </c>
       <c r="BJ16" s="25" t="n"/>
       <c r="BK16" s="26" t="n">
-        <v>-170</v>
+        <v>-117</v>
       </c>
       <c r="BL16" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.854701</v>
       </c>
       <c r="BM16" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.539171</v>
       </c>
       <c r="BN16" s="28" t="n"/>
       <c r="BO16" s="28" t="n"/>
@@ -5757,22 +5757,22 @@
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="24" t="inlineStr">
         <is>
-          <t>25064c2e48c74794</t>
+          <t>cf551c273736402d</t>
         </is>
       </c>
       <c r="B17" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T20:32:32.284273Z</t>
+          <t>2026-08-02T07:15:56.246313Z</t>
         </is>
       </c>
       <c r="C17" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T20:00:00Z</t>
+          <t>2026-08-02T12:00:00Z</t>
         </is>
       </c>
       <c r="D17" s="24" t="inlineStr">
         <is>
-          <t>67937</t>
+          <t>66847</t>
         </is>
       </c>
       <c r="E17" s="24" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="F17" s="24" t="inlineStr">
         <is>
-          <t>Docta Esports</t>
+          <t>Galions Sharks</t>
         </is>
       </c>
       <c r="G17" s="24" t="inlineStr">
         <is>
-          <t>Volticons</t>
+          <t>Karmine Corp Blue Stars</t>
         </is>
       </c>
       <c r="H17" s="24" t="inlineStr">
@@ -5807,26 +5807,26 @@
         </is>
       </c>
       <c r="L17" s="26" t="n">
-        <v>-144</v>
+        <v>-213</v>
       </c>
       <c r="M17" s="27" t="n">
-        <v>1.694444</v>
+        <v>1.469484</v>
       </c>
       <c r="N17" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.680511</v>
       </c>
       <c r="O17" s="28" t="n">
-        <v>0.651311</v>
+        <v>0.553715</v>
       </c>
       <c r="P17" s="28" t="n"/>
       <c r="Q17" s="28" t="n">
-        <v>0.061147</v>
+        <v>-0.126796</v>
       </c>
       <c r="R17" s="26" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="S17" s="29" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="T17" s="24" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
       <c r="AD17" s="24" t="n"/>
       <c r="AE17" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-lol-vtc-doh-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-lol-kcbs-gls-2026-08-02).</t>
         </is>
       </c>
       <c r="AF17" s="31" t="inlineStr">
@@ -5867,7 +5867,7 @@
       <c r="AJ17" s="31" t="n"/>
       <c r="AK17" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL17" s="26" t="n">
@@ -5875,47 +5875,47 @@
       </c>
       <c r="AM17" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN17" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO17" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP17" s="24" t="inlineStr">
         <is>
-          <t>Docta Esports</t>
+          <t>Galions Sharks</t>
         </is>
       </c>
       <c r="AQ17" s="24" t="inlineStr">
         <is>
-          <t>Docta Esports</t>
+          <t>Galions Sharks</t>
         </is>
       </c>
       <c r="AR17" s="24" t="inlineStr">
         <is>
-          <t>Docta Esports</t>
+          <t>Galions Sharks</t>
         </is>
       </c>
       <c r="AS17" s="24" t="inlineStr">
         <is>
-          <t>Volticons</t>
+          <t>Karmine Corp Blue Stars</t>
         </is>
       </c>
       <c r="AT17" s="24" t="inlineStr">
         <is>
-          <t>Volticons</t>
+          <t>Karmine Corp Blue Stars</t>
         </is>
       </c>
       <c r="AU17" s="24" t="inlineStr">
         <is>
-          <t>Volticons</t>
+          <t>Karmine Corp Blue Stars</t>
         </is>
       </c>
       <c r="AV17" s="24" t="n"/>
@@ -5933,7 +5933,7 @@
       </c>
       <c r="BA17" s="24" t="inlineStr">
         <is>
-          <t>229baf64b9a74bdaa3fee70ecd0bde2986f6e2d651a8f5efad46c765670e1ff3</t>
+          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
         </is>
       </c>
       <c r="BB17" s="24" t="inlineStr">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="BD17" s="24" t="inlineStr">
         <is>
-          <t>229baf64b9a74bdaa3fee70ecd0bde2986f6e2d651a8f5efad46c765670e1ff3</t>
+          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
         </is>
       </c>
       <c r="BE17" s="24" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="BH17" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T20:32:29.680102Z</t>
+          <t>2026-08-02T07:15:43.668159Z</t>
         </is>
       </c>
       <c r="BI17" s="24" t="inlineStr">
@@ -5978,13 +5978,13 @@
       </c>
       <c r="BJ17" s="25" t="n"/>
       <c r="BK17" s="26" t="n">
-        <v>-144</v>
+        <v>-213</v>
       </c>
       <c r="BL17" s="27" t="n">
-        <v>1.694444</v>
+        <v>1.469484</v>
       </c>
       <c r="BM17" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.680511</v>
       </c>
       <c r="BN17" s="28" t="n"/>
       <c r="BO17" s="28" t="n"/>
@@ -6018,22 +6018,22 @@
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="24" t="inlineStr">
         <is>
-          <t>8243536f208b4cc2</t>
+          <t>e7034161fa2349ed</t>
         </is>
       </c>
       <c r="B18" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T20:32:32.284273Z</t>
+          <t>2026-08-02T07:15:56.246313Z</t>
         </is>
       </c>
       <c r="C18" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T22:00:00Z</t>
+          <t>2026-08-02T14:00:00Z</t>
         </is>
       </c>
       <c r="D18" s="24" t="inlineStr">
         <is>
-          <t>68011</t>
+          <t>66876</t>
         </is>
       </c>
       <c r="E18" s="24" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="F18" s="24" t="inlineStr">
         <is>
-          <t>Vivo Keyd Stars Academy</t>
+          <t>Caldya Esport</t>
         </is>
       </c>
       <c r="G18" s="24" t="inlineStr">
         <is>
-          <t>paiN Gaming Academy</t>
+          <t>Zephyr Esport</t>
         </is>
       </c>
       <c r="H18" s="24" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="I18" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J18" s="25" t="n"/>
@@ -6068,23 +6068,23 @@
         </is>
       </c>
       <c r="L18" s="26" t="n">
-        <v>-108</v>
+        <v>186</v>
       </c>
       <c r="M18" s="27" t="n">
-        <v>1.925926</v>
+        <v>2.86</v>
       </c>
       <c r="N18" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.34965</v>
       </c>
       <c r="O18" s="28" t="n">
-        <v>0.501978</v>
+        <v>0.525701</v>
       </c>
       <c r="P18" s="28" t="n"/>
       <c r="Q18" s="28" t="n">
-        <v>-0.017253</v>
+        <v>0.176051</v>
       </c>
       <c r="R18" s="26" t="n">
-        <v>11</v>
+        <v>100</v>
       </c>
       <c r="S18" s="29" t="n">
         <v>1</v>
@@ -6110,7 +6110,7 @@
       <c r="AD18" s="24" t="n"/>
       <c r="AE18" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5200 (market_slug=aec-lol-pnga-vksa-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.3500 (market_slug=aec-lol-zpr-cla-2026-08-02).</t>
         </is>
       </c>
       <c r="AF18" s="31" t="inlineStr">
@@ -6151,32 +6151,32 @@
       </c>
       <c r="AP18" s="24" t="inlineStr">
         <is>
-          <t>Vivo Keyd Stars Academy</t>
+          <t>Caldya Esport</t>
         </is>
       </c>
       <c r="AQ18" s="24" t="inlineStr">
         <is>
-          <t>Vivo Keyd Stars Academy</t>
+          <t>Caldya Esport</t>
         </is>
       </c>
       <c r="AR18" s="24" t="inlineStr">
         <is>
-          <t>Vivo Keyd Stars Academy</t>
+          <t>Caldya Esport</t>
         </is>
       </c>
       <c r="AS18" s="24" t="inlineStr">
         <is>
-          <t>paiN Gaming Academy</t>
+          <t>Zephyr Esport</t>
         </is>
       </c>
       <c r="AT18" s="24" t="inlineStr">
         <is>
-          <t>paiN Gaming Academy</t>
+          <t>Zephyr Esport</t>
         </is>
       </c>
       <c r="AU18" s="24" t="inlineStr">
         <is>
-          <t>paiN Gaming Academy</t>
+          <t>Zephyr Esport</t>
         </is>
       </c>
       <c r="AV18" s="24" t="n"/>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="BA18" s="24" t="inlineStr">
         <is>
-          <t>229baf64b9a74bdaa3fee70ecd0bde2986f6e2d651a8f5efad46c765670e1ff3</t>
+          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
         </is>
       </c>
       <c r="BB18" s="24" t="inlineStr">
@@ -6209,7 +6209,7 @@
       </c>
       <c r="BD18" s="24" t="inlineStr">
         <is>
-          <t>229baf64b9a74bdaa3fee70ecd0bde2986f6e2d651a8f5efad46c765670e1ff3</t>
+          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
         </is>
       </c>
       <c r="BE18" s="24" t="inlineStr">
@@ -6229,7 +6229,7 @@
       </c>
       <c r="BH18" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T20:32:31.277314Z</t>
+          <t>2026-08-02T07:15:44.600133Z</t>
         </is>
       </c>
       <c r="BI18" s="24" t="inlineStr">
@@ -6239,13 +6239,13 @@
       </c>
       <c r="BJ18" s="25" t="n"/>
       <c r="BK18" s="26" t="n">
-        <v>-108</v>
+        <v>186</v>
       </c>
       <c r="BL18" s="27" t="n">
-        <v>1.925926</v>
+        <v>2.86</v>
       </c>
       <c r="BM18" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.34965</v>
       </c>
       <c r="BN18" s="28" t="n"/>
       <c r="BO18" s="28" t="n"/>
@@ -6279,22 +6279,22 @@
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="24" t="inlineStr">
         <is>
-          <t>800684a78c4b422a</t>
+          <t>e14dbaebac5846fe</t>
         </is>
       </c>
       <c r="B19" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:24:03.087958Z</t>
+          <t>2026-08-02T07:15:56.246313Z</t>
         </is>
       </c>
       <c r="C19" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:00:00Z</t>
+          <t>2026-08-02T16:00:00Z</t>
         </is>
       </c>
       <c r="D19" s="24" t="inlineStr">
         <is>
-          <t>66779</t>
+          <t>66902</t>
         </is>
       </c>
       <c r="E19" s="24" t="inlineStr">
@@ -6304,12 +6304,12 @@
       </c>
       <c r="F19" s="24" t="inlineStr">
         <is>
-          <t>Team WE</t>
+          <t>LOUD</t>
         </is>
       </c>
       <c r="G19" s="24" t="inlineStr">
         <is>
-          <t>ThunderTalk Gaming</t>
+          <t>Fluxo W7M</t>
         </is>
       </c>
       <c r="H19" s="24" t="inlineStr">
@@ -6329,26 +6329,26 @@
         </is>
       </c>
       <c r="L19" s="26" t="n">
-        <v>-203</v>
+        <v>-138</v>
       </c>
       <c r="M19" s="27" t="n">
-        <v>1.492611</v>
+        <v>1.724638</v>
       </c>
       <c r="N19" s="28" t="n">
-        <v>0.669967</v>
+        <v>0.579832</v>
       </c>
       <c r="O19" s="28" t="n">
-        <v>0.65184</v>
+        <v>0.5601159999999999</v>
       </c>
       <c r="P19" s="28" t="n"/>
       <c r="Q19" s="28" t="n">
-        <v>-0.018127</v>
+        <v>-0.019716</v>
       </c>
       <c r="R19" s="26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="S19" s="29" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="T19" s="24" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
       <c r="AD19" s="24" t="n"/>
       <c r="AE19" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-lol-tt-we-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-lol-fxw7-lll-2026-08-02).</t>
         </is>
       </c>
       <c r="AF19" s="31" t="inlineStr">
@@ -6412,32 +6412,32 @@
       </c>
       <c r="AP19" s="24" t="inlineStr">
         <is>
-          <t>Team WE</t>
+          <t>LOUD</t>
         </is>
       </c>
       <c r="AQ19" s="24" t="inlineStr">
         <is>
-          <t>Team WE</t>
+          <t>LOUD</t>
         </is>
       </c>
       <c r="AR19" s="24" t="inlineStr">
         <is>
-          <t>Team WE</t>
+          <t>LOUD</t>
         </is>
       </c>
       <c r="AS19" s="24" t="inlineStr">
         <is>
-          <t>ThunderTalk Gaming</t>
+          <t>Fluxo W7M</t>
         </is>
       </c>
       <c r="AT19" s="24" t="inlineStr">
         <is>
-          <t>ThunderTalk Gaming</t>
+          <t>Fluxo W7M</t>
         </is>
       </c>
       <c r="AU19" s="24" t="inlineStr">
         <is>
-          <t>ThunderTalk Gaming</t>
+          <t>Fluxo W7M</t>
         </is>
       </c>
       <c r="AV19" s="24" t="n"/>
@@ -6455,7 +6455,7 @@
       </c>
       <c r="BA19" s="24" t="inlineStr">
         <is>
-          <t>dc39c5116885ddd336fb0cde92b52b07c9279e66e6d5cc726919628dc99e77ef</t>
+          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
         </is>
       </c>
       <c r="BB19" s="24" t="inlineStr">
@@ -6470,7 +6470,7 @@
       </c>
       <c r="BD19" s="24" t="inlineStr">
         <is>
-          <t>dc39c5116885ddd336fb0cde92b52b07c9279e66e6d5cc726919628dc99e77ef</t>
+          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
         </is>
       </c>
       <c r="BE19" s="24" t="inlineStr">
@@ -6490,7 +6490,7 @@
       </c>
       <c r="BH19" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:45.910262Z</t>
+          <t>2026-08-02T07:15:45.555467Z</t>
         </is>
       </c>
       <c r="BI19" s="24" t="inlineStr">
@@ -6500,13 +6500,13 @@
       </c>
       <c r="BJ19" s="25" t="n"/>
       <c r="BK19" s="26" t="n">
-        <v>-203</v>
+        <v>-138</v>
       </c>
       <c r="BL19" s="27" t="n">
-        <v>1.492611</v>
+        <v>1.724638</v>
       </c>
       <c r="BM19" s="28" t="n">
-        <v>0.669967</v>
+        <v>0.579832</v>
       </c>
       <c r="BN19" s="28" t="n"/>
       <c r="BO19" s="28" t="n"/>
@@ -6540,22 +6540,22 @@
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="24" t="inlineStr">
         <is>
-          <t>200ffb9d63d5400b</t>
+          <t>3f7353916d03449d</t>
         </is>
       </c>
       <c r="B20" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:24:03.087958Z</t>
+          <t>2026-08-02T07:15:56.246313Z</t>
         </is>
       </c>
       <c r="C20" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T11:00:00Z</t>
+          <t>2026-08-02T17:15:00Z</t>
         </is>
       </c>
       <c r="D20" s="24" t="inlineStr">
         <is>
-          <t>66838</t>
+          <t>66955</t>
         </is>
       </c>
       <c r="E20" s="24" t="inlineStr">
@@ -6565,12 +6565,12 @@
       </c>
       <c r="F20" s="24" t="inlineStr">
         <is>
-          <t>JD Gaming</t>
+          <t>Movistar KOI</t>
         </is>
       </c>
       <c r="G20" s="24" t="inlineStr">
         <is>
-          <t>Top Esports</t>
+          <t>Fnatic</t>
         </is>
       </c>
       <c r="H20" s="24" t="inlineStr">
@@ -6580,7 +6580,7 @@
       </c>
       <c r="I20" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J20" s="25" t="n"/>
@@ -6590,26 +6590,26 @@
         </is>
       </c>
       <c r="L20" s="26" t="n">
-        <v>-122</v>
+        <v>-186</v>
       </c>
       <c r="M20" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.537634</v>
       </c>
       <c r="N20" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.65035</v>
       </c>
       <c r="O20" s="28" t="n">
-        <v>0.549951</v>
+        <v>0.594427</v>
       </c>
       <c r="P20" s="28" t="n"/>
       <c r="Q20" s="28" t="n">
-        <v>0.000401</v>
+        <v>-0.055923</v>
       </c>
       <c r="R20" s="26" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="S20" s="29" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="T20" s="24" t="inlineStr">
         <is>
@@ -6632,7 +6632,7 @@
       <c r="AD20" s="24" t="n"/>
       <c r="AE20" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-lol-tes-jdg-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.6500 (market_slug=aec-lol-fnc-mkoi-2026-08-02).</t>
         </is>
       </c>
       <c r="AF20" s="31" t="inlineStr">
@@ -6673,32 +6673,32 @@
       </c>
       <c r="AP20" s="24" t="inlineStr">
         <is>
-          <t>JD Gaming</t>
+          <t>Movistar KOI</t>
         </is>
       </c>
       <c r="AQ20" s="24" t="inlineStr">
         <is>
-          <t>JD Gaming</t>
+          <t>Movistar KOI</t>
         </is>
       </c>
       <c r="AR20" s="24" t="inlineStr">
         <is>
-          <t>JD Gaming</t>
+          <t>Movistar KOI</t>
         </is>
       </c>
       <c r="AS20" s="24" t="inlineStr">
         <is>
-          <t>Top Esports</t>
+          <t>Fnatic</t>
         </is>
       </c>
       <c r="AT20" s="24" t="inlineStr">
         <is>
-          <t>Top Esports</t>
+          <t>Fnatic</t>
         </is>
       </c>
       <c r="AU20" s="24" t="inlineStr">
         <is>
-          <t>Top Esports</t>
+          <t>Fnatic</t>
         </is>
       </c>
       <c r="AV20" s="24" t="n"/>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="BA20" s="24" t="inlineStr">
         <is>
-          <t>dc39c5116885ddd336fb0cde92b52b07c9279e66e6d5cc726919628dc99e77ef</t>
+          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
         </is>
       </c>
       <c r="BB20" s="24" t="inlineStr">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="BD20" s="24" t="inlineStr">
         <is>
-          <t>dc39c5116885ddd336fb0cde92b52b07c9279e66e6d5cc726919628dc99e77ef</t>
+          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
         </is>
       </c>
       <c r="BE20" s="24" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="BH20" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:49.593238Z</t>
+          <t>2026-08-02T07:15:46.035443Z</t>
         </is>
       </c>
       <c r="BI20" s="24" t="inlineStr">
@@ -6761,13 +6761,13 @@
       </c>
       <c r="BJ20" s="25" t="n"/>
       <c r="BK20" s="26" t="n">
-        <v>-122</v>
+        <v>-186</v>
       </c>
       <c r="BL20" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.537634</v>
       </c>
       <c r="BM20" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.65035</v>
       </c>
       <c r="BN20" s="28" t="n"/>
       <c r="BO20" s="28" t="n"/>
@@ -6801,22 +6801,22 @@
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="24" t="inlineStr">
         <is>
-          <t>e0a07f02df774029</t>
+          <t>a977f54662824001</t>
         </is>
       </c>
       <c r="B21" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:24:03.087958Z</t>
+          <t>2026-08-02T07:15:56.246313Z</t>
         </is>
       </c>
       <c r="C21" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:00:00Z</t>
+          <t>2026-08-03T08:00:00Z</t>
         </is>
       </c>
       <c r="D21" s="24" t="inlineStr">
         <is>
-          <t>66902</t>
+          <t>67491</t>
         </is>
       </c>
       <c r="E21" s="24" t="inlineStr">
@@ -6826,12 +6826,12 @@
       </c>
       <c r="F21" s="24" t="inlineStr">
         <is>
-          <t>LOUD</t>
+          <t>Hanwha Life Esports</t>
         </is>
       </c>
       <c r="G21" s="24" t="inlineStr">
         <is>
-          <t>Fluxo W7M</t>
+          <t>Gen.G</t>
         </is>
       </c>
       <c r="H21" s="24" t="inlineStr">
@@ -6851,26 +6851,26 @@
         </is>
       </c>
       <c r="L21" s="26" t="n">
-        <v>-156</v>
+        <v>-133</v>
       </c>
       <c r="M21" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.75188</v>
       </c>
       <c r="N21" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.570815</v>
       </c>
       <c r="O21" s="28" t="n">
-        <v>0.559377</v>
+        <v>0.5826210000000001</v>
       </c>
       <c r="P21" s="28" t="n"/>
       <c r="Q21" s="28" t="n">
-        <v>-0.049998</v>
+        <v>0.011806</v>
       </c>
       <c r="R21" s="26" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="S21" s="29" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="T21" s="24" t="inlineStr">
         <is>
@@ -6893,7 +6893,7 @@
       <c r="AD21" s="24" t="n"/>
       <c r="AE21" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-lol-fxw7-lll-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-lol-gen-hle-2026-08-03).</t>
         </is>
       </c>
       <c r="AF21" s="31" t="inlineStr">
@@ -6911,7 +6911,7 @@
       <c r="AJ21" s="31" t="n"/>
       <c r="AK21" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL21" s="26" t="n">
@@ -6919,47 +6919,47 @@
       </c>
       <c r="AM21" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN21" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO21" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP21" s="24" t="inlineStr">
         <is>
-          <t>LOUD</t>
+          <t>Hanwha Life Esports</t>
         </is>
       </c>
       <c r="AQ21" s="24" t="inlineStr">
         <is>
-          <t>LOUD</t>
+          <t>Hanwha Life Esports</t>
         </is>
       </c>
       <c r="AR21" s="24" t="inlineStr">
         <is>
-          <t>LOUD</t>
+          <t>Hanwha Life Esports</t>
         </is>
       </c>
       <c r="AS21" s="24" t="inlineStr">
         <is>
-          <t>Fluxo W7M</t>
+          <t>Gen.G</t>
         </is>
       </c>
       <c r="AT21" s="24" t="inlineStr">
         <is>
-          <t>Fluxo W7M</t>
+          <t>Gen.G</t>
         </is>
       </c>
       <c r="AU21" s="24" t="inlineStr">
         <is>
-          <t>Fluxo W7M</t>
+          <t>Gen.G</t>
         </is>
       </c>
       <c r="AV21" s="24" t="n"/>
@@ -6977,7 +6977,7 @@
       </c>
       <c r="BA21" s="24" t="inlineStr">
         <is>
-          <t>dc39c5116885ddd336fb0cde92b52b07c9279e66e6d5cc726919628dc99e77ef</t>
+          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
         </is>
       </c>
       <c r="BB21" s="24" t="inlineStr">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="BD21" s="24" t="inlineStr">
         <is>
-          <t>dc39c5116885ddd336fb0cde92b52b07c9279e66e6d5cc726919628dc99e77ef</t>
+          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
         </is>
       </c>
       <c r="BE21" s="24" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="BH21" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:52.060055Z</t>
+          <t>2026-08-02T07:15:48.091630Z</t>
         </is>
       </c>
       <c r="BI21" s="24" t="inlineStr">
@@ -7022,13 +7022,13 @@
       </c>
       <c r="BJ21" s="25" t="n"/>
       <c r="BK21" s="26" t="n">
-        <v>-156</v>
+        <v>-133</v>
       </c>
       <c r="BL21" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.75188</v>
       </c>
       <c r="BM21" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.570815</v>
       </c>
       <c r="BN21" s="28" t="n"/>
       <c r="BO21" s="28" t="n"/>
@@ -7062,22 +7062,22 @@
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="24" t="inlineStr">
         <is>
-          <t>0e5bd6a464e849ce</t>
+          <t>1555011929a640aa</t>
         </is>
       </c>
       <c r="B22" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:24:03.087958Z</t>
+          <t>2026-08-02T07:15:56.246313Z</t>
         </is>
       </c>
       <c r="C22" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:15:00Z</t>
+          <t>2026-08-03T08:00:00Z</t>
         </is>
       </c>
       <c r="D22" s="24" t="inlineStr">
         <is>
-          <t>66955</t>
+          <t>67492</t>
         </is>
       </c>
       <c r="E22" s="24" t="inlineStr">
@@ -7087,12 +7087,12 @@
       </c>
       <c r="F22" s="24" t="inlineStr">
         <is>
-          <t>Movistar KOI</t>
+          <t>BNK FearX Youth</t>
         </is>
       </c>
       <c r="G22" s="24" t="inlineStr">
         <is>
-          <t>Fnatic</t>
+          <t>HANJIN BRION Challengers</t>
         </is>
       </c>
       <c r="H22" s="24" t="inlineStr">
@@ -7112,26 +7112,26 @@
         </is>
       </c>
       <c r="L22" s="26" t="n">
-        <v>-186</v>
+        <v>-223</v>
       </c>
       <c r="M22" s="27" t="n">
-        <v>1.537634</v>
+        <v>1.44843</v>
       </c>
       <c r="N22" s="28" t="n">
-        <v>0.65035</v>
+        <v>0.690402</v>
       </c>
       <c r="O22" s="28" t="n">
-        <v>0.5937249999999999</v>
+        <v>0.636575</v>
       </c>
       <c r="P22" s="28" t="n"/>
       <c r="Q22" s="28" t="n">
-        <v>-0.056625</v>
+        <v>-0.053827</v>
       </c>
       <c r="R22" s="26" t="n">
         <v>0</v>
       </c>
       <c r="S22" s="29" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="T22" s="24" t="inlineStr">
         <is>
@@ -7154,7 +7154,7 @@
       <c r="AD22" s="24" t="n"/>
       <c r="AE22" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6500 (market_slug=aec-lol-fnc-mkoi-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-lol-hbc-foxy-2026-08-03).</t>
         </is>
       </c>
       <c r="AF22" s="31" t="inlineStr">
@@ -7195,32 +7195,32 @@
       </c>
       <c r="AP22" s="24" t="inlineStr">
         <is>
-          <t>Movistar KOI</t>
+          <t>BNK FearX Youth</t>
         </is>
       </c>
       <c r="AQ22" s="24" t="inlineStr">
         <is>
-          <t>Movistar KOI</t>
+          <t>BNK FearX Youth</t>
         </is>
       </c>
       <c r="AR22" s="24" t="inlineStr">
         <is>
-          <t>Movistar KOI</t>
+          <t>BNK FearX Youth</t>
         </is>
       </c>
       <c r="AS22" s="24" t="inlineStr">
         <is>
-          <t>Fnatic</t>
+          <t>HANJIN BRION Challengers</t>
         </is>
       </c>
       <c r="AT22" s="24" t="inlineStr">
         <is>
-          <t>Fnatic</t>
+          <t>HANJIN BRION Challengers</t>
         </is>
       </c>
       <c r="AU22" s="24" t="inlineStr">
         <is>
-          <t>Fnatic</t>
+          <t>HANJIN BRION Challengers</t>
         </is>
       </c>
       <c r="AV22" s="24" t="n"/>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="BA22" s="24" t="inlineStr">
         <is>
-          <t>dc39c5116885ddd336fb0cde92b52b07c9279e66e6d5cc726919628dc99e77ef</t>
+          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
         </is>
       </c>
       <c r="BB22" s="24" t="inlineStr">
@@ -7253,7 +7253,7 @@
       </c>
       <c r="BD22" s="24" t="inlineStr">
         <is>
-          <t>dc39c5116885ddd336fb0cde92b52b07c9279e66e6d5cc726919628dc99e77ef</t>
+          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
         </is>
       </c>
       <c r="BE22" s="24" t="inlineStr">
@@ -7273,7 +7273,7 @@
       </c>
       <c r="BH22" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:52.612840Z</t>
+          <t>2026-08-02T07:15:48.572339Z</t>
         </is>
       </c>
       <c r="BI22" s="24" t="inlineStr">
@@ -7283,13 +7283,13 @@
       </c>
       <c r="BJ22" s="25" t="n"/>
       <c r="BK22" s="26" t="n">
-        <v>-186</v>
+        <v>-223</v>
       </c>
       <c r="BL22" s="27" t="n">
-        <v>1.537634</v>
+        <v>1.44843</v>
       </c>
       <c r="BM22" s="28" t="n">
-        <v>0.65035</v>
+        <v>0.690402</v>
       </c>
       <c r="BN22" s="28" t="n"/>
       <c r="BO22" s="28" t="n"/>
@@ -7323,22 +7323,22 @@
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="24" t="inlineStr">
         <is>
-          <t>e6798caa596e40dc</t>
+          <t>8ed69f703f774054</t>
         </is>
       </c>
       <c r="B23" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:24:03.087958Z</t>
+          <t>2026-08-02T07:15:56.246313Z</t>
         </is>
       </c>
       <c r="C23" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:00:00Z</t>
+          <t>2026-08-03T10:00:00Z</t>
         </is>
       </c>
       <c r="D23" s="24" t="inlineStr">
         <is>
-          <t>66956</t>
+          <t>67511</t>
         </is>
       </c>
       <c r="E23" s="24" t="inlineStr">
@@ -7348,12 +7348,12 @@
       </c>
       <c r="F23" s="24" t="inlineStr">
         <is>
-          <t>RED Canids</t>
+          <t>Dplus KIA Challengers</t>
         </is>
       </c>
       <c r="G23" s="24" t="inlineStr">
         <is>
-          <t>LOS</t>
+          <t>DN SOOPers Challengers</t>
         </is>
       </c>
       <c r="H23" s="24" t="inlineStr">
@@ -7363,7 +7363,7 @@
       </c>
       <c r="I23" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J23" s="25" t="n"/>
@@ -7373,26 +7373,26 @@
         </is>
       </c>
       <c r="L23" s="26" t="n">
-        <v>-186</v>
+        <v>-223</v>
       </c>
       <c r="M23" s="27" t="n">
-        <v>1.537634</v>
+        <v>1.44843</v>
       </c>
       <c r="N23" s="28" t="n">
-        <v>0.65035</v>
+        <v>0.690402</v>
       </c>
       <c r="O23" s="28" t="n">
-        <v>0.5755670000000001</v>
+        <v>0.70607</v>
       </c>
       <c r="P23" s="28" t="n"/>
       <c r="Q23" s="28" t="n">
-        <v>-0.074783</v>
+        <v>0.015668</v>
       </c>
       <c r="R23" s="26" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="S23" s="29" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="T23" s="24" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
       <c r="AD23" s="24" t="n"/>
       <c r="AE23" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6500 (market_slug=aec-lol-los-red-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-lol-dnsc-dkc-2026-08-03).</t>
         </is>
       </c>
       <c r="AF23" s="31" t="inlineStr">
@@ -7433,7 +7433,7 @@
       <c r="AJ23" s="31" t="n"/>
       <c r="AK23" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL23" s="26" t="n">
@@ -7441,47 +7441,47 @@
       </c>
       <c r="AM23" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN23" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO23" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP23" s="24" t="inlineStr">
         <is>
-          <t>RED Canids</t>
+          <t>Dplus KIA Challengers</t>
         </is>
       </c>
       <c r="AQ23" s="24" t="inlineStr">
         <is>
-          <t>RED Canids</t>
+          <t>Dplus KIA Challengers</t>
         </is>
       </c>
       <c r="AR23" s="24" t="inlineStr">
         <is>
-          <t>RED Canids</t>
+          <t>Dplus KIA Challengers</t>
         </is>
       </c>
       <c r="AS23" s="24" t="inlineStr">
         <is>
-          <t>LOS</t>
+          <t>DN SOOPers Challengers</t>
         </is>
       </c>
       <c r="AT23" s="24" t="inlineStr">
         <is>
-          <t>LOS</t>
+          <t>DN SOOPers Challengers</t>
         </is>
       </c>
       <c r="AU23" s="24" t="inlineStr">
         <is>
-          <t>LOS</t>
+          <t>DN SOOPers Challengers</t>
         </is>
       </c>
       <c r="AV23" s="24" t="n"/>
@@ -7499,7 +7499,7 @@
       </c>
       <c r="BA23" s="24" t="inlineStr">
         <is>
-          <t>dc39c5116885ddd336fb0cde92b52b07c9279e66e6d5cc726919628dc99e77ef</t>
+          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
         </is>
       </c>
       <c r="BB23" s="24" t="inlineStr">
@@ -7514,7 +7514,7 @@
       </c>
       <c r="BD23" s="24" t="inlineStr">
         <is>
-          <t>dc39c5116885ddd336fb0cde92b52b07c9279e66e6d5cc726919628dc99e77ef</t>
+          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
         </is>
       </c>
       <c r="BE23" s="24" t="inlineStr">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="BH23" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:53.105912Z</t>
+          <t>2026-08-02T07:15:49.062474Z</t>
         </is>
       </c>
       <c r="BI23" s="24" t="inlineStr">
@@ -7544,13 +7544,13 @@
       </c>
       <c r="BJ23" s="25" t="n"/>
       <c r="BK23" s="26" t="n">
-        <v>-186</v>
+        <v>-223</v>
       </c>
       <c r="BL23" s="27" t="n">
-        <v>1.537634</v>
+        <v>1.44843</v>
       </c>
       <c r="BM23" s="28" t="n">
-        <v>0.65035</v>
+        <v>0.690402</v>
       </c>
       <c r="BN23" s="28" t="n"/>
       <c r="BO23" s="28" t="n"/>
@@ -7581,6 +7581,789 @@
       <c r="CN23" s="24" t="n"/>
       <c r="CO23" s="24" t="n"/>
     </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>13c04f6fa3534a6f</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:15:56.246313Z</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="D24" s="24" t="inlineStr">
+        <is>
+          <t>67515</t>
+        </is>
+      </c>
+      <c r="E24" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F24" s="24" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="G24" s="24" t="inlineStr">
+        <is>
+          <t>Nongshim Red Force</t>
+        </is>
+      </c>
+      <c r="H24" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I24" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J24" s="25" t="n"/>
+      <c r="K24" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L24" s="26" t="n">
+        <v>-186</v>
+      </c>
+      <c r="M24" s="27" t="n">
+        <v>1.537634</v>
+      </c>
+      <c r="N24" s="28" t="n">
+        <v>0.65035</v>
+      </c>
+      <c r="O24" s="28" t="n">
+        <v>0.748974</v>
+      </c>
+      <c r="P24" s="28" t="n"/>
+      <c r="Q24" s="28" t="n">
+        <v>0.098624</v>
+      </c>
+      <c r="R24" s="26" t="n">
+        <v>69</v>
+      </c>
+      <c r="S24" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T24" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U24" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V24" s="24" t="n"/>
+      <c r="W24" s="26" t="n"/>
+      <c r="X24" s="26" t="n"/>
+      <c r="Y24" s="25" t="n"/>
+      <c r="Z24" s="26" t="n"/>
+      <c r="AA24" s="28" t="n"/>
+      <c r="AB24" s="28" t="n"/>
+      <c r="AC24" s="30" t="n"/>
+      <c r="AD24" s="24" t="n"/>
+      <c r="AE24" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6500 (market_slug=aec-lol-ns-t1-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF24" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG24" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH24" s="24" t="n"/>
+      <c r="AI24" s="31" t="n"/>
+      <c r="AJ24" s="31" t="n"/>
+      <c r="AK24" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL24" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM24" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN24" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO24" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP24" s="24" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="AQ24" s="24" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="AR24" s="24" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="AS24" s="24" t="inlineStr">
+        <is>
+          <t>Nongshim Red Force</t>
+        </is>
+      </c>
+      <c r="AT24" s="24" t="inlineStr">
+        <is>
+          <t>Nongshim Red Force</t>
+        </is>
+      </c>
+      <c r="AU24" s="24" t="inlineStr">
+        <is>
+          <t>Nongshim Red Force</t>
+        </is>
+      </c>
+      <c r="AV24" s="24" t="n"/>
+      <c r="AW24" s="24" t="n"/>
+      <c r="AX24" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY24" s="24" t="n"/>
+      <c r="AZ24" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA24" s="24" t="inlineStr">
+        <is>
+          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
+        </is>
+      </c>
+      <c r="BB24" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC24" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD24" s="24" t="inlineStr">
+        <is>
+          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
+        </is>
+      </c>
+      <c r="BE24" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF24" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG24" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:15:49.527302Z</t>
+        </is>
+      </c>
+      <c r="BI24" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ24" s="25" t="n"/>
+      <c r="BK24" s="26" t="n">
+        <v>-186</v>
+      </c>
+      <c r="BL24" s="27" t="n">
+        <v>1.537634</v>
+      </c>
+      <c r="BM24" s="28" t="n">
+        <v>0.65035</v>
+      </c>
+      <c r="BN24" s="28" t="n"/>
+      <c r="BO24" s="28" t="n"/>
+      <c r="BP24" s="25" t="n"/>
+      <c r="BQ24" s="27" t="n"/>
+      <c r="BR24" s="28" t="n"/>
+      <c r="BS24" s="28" t="n"/>
+      <c r="BT24" s="28" t="n"/>
+      <c r="BU24" s="25" t="n"/>
+      <c r="BV24" s="29" t="n"/>
+      <c r="BW24" s="24" t="n"/>
+      <c r="BX24" s="30" t="n"/>
+      <c r="BY24" s="27" t="n"/>
+      <c r="BZ24" s="24" t="n"/>
+      <c r="CA24" s="31" t="n"/>
+      <c r="CB24" s="24" t="n"/>
+      <c r="CC24" s="24" t="n"/>
+      <c r="CD24" s="24" t="n"/>
+      <c r="CE24" s="24" t="n"/>
+      <c r="CF24" s="24" t="n"/>
+      <c r="CG24" s="24" t="n"/>
+      <c r="CH24" s="24" t="n"/>
+      <c r="CI24" s="24" t="n"/>
+      <c r="CJ24" s="24" t="n"/>
+      <c r="CK24" s="24" t="n"/>
+      <c r="CL24" s="24" t="n"/>
+      <c r="CM24" s="24" t="n"/>
+      <c r="CN24" s="24" t="n"/>
+      <c r="CO24" s="24" t="n"/>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>01563e5bbe284ba8</t>
+        </is>
+      </c>
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:15:56.246313Z</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="D25" s="24" t="inlineStr">
+        <is>
+          <t>67937</t>
+        </is>
+      </c>
+      <c r="E25" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F25" s="24" t="inlineStr">
+        <is>
+          <t>Docta Esports</t>
+        </is>
+      </c>
+      <c r="G25" s="24" t="inlineStr">
+        <is>
+          <t>Volticons</t>
+        </is>
+      </c>
+      <c r="H25" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I25" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J25" s="25" t="n"/>
+      <c r="K25" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L25" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="M25" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="N25" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="O25" s="28" t="n">
+        <v>0.650712</v>
+      </c>
+      <c r="P25" s="28" t="n"/>
+      <c r="Q25" s="28" t="n">
+        <v>0.060548</v>
+      </c>
+      <c r="R25" s="26" t="n">
+        <v>50</v>
+      </c>
+      <c r="S25" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T25" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U25" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V25" s="24" t="n"/>
+      <c r="W25" s="26" t="n"/>
+      <c r="X25" s="26" t="n"/>
+      <c r="Y25" s="25" t="n"/>
+      <c r="Z25" s="26" t="n"/>
+      <c r="AA25" s="28" t="n"/>
+      <c r="AB25" s="28" t="n"/>
+      <c r="AC25" s="30" t="n"/>
+      <c r="AD25" s="24" t="n"/>
+      <c r="AE25" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-lol-vtc-doh-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF25" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG25" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH25" s="24" t="n"/>
+      <c r="AI25" s="31" t="n"/>
+      <c r="AJ25" s="31" t="n"/>
+      <c r="AK25" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL25" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM25" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN25" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO25" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP25" s="24" t="inlineStr">
+        <is>
+          <t>Docta Esports</t>
+        </is>
+      </c>
+      <c r="AQ25" s="24" t="inlineStr">
+        <is>
+          <t>Docta Esports</t>
+        </is>
+      </c>
+      <c r="AR25" s="24" t="inlineStr">
+        <is>
+          <t>Docta Esports</t>
+        </is>
+      </c>
+      <c r="AS25" s="24" t="inlineStr">
+        <is>
+          <t>Volticons</t>
+        </is>
+      </c>
+      <c r="AT25" s="24" t="inlineStr">
+        <is>
+          <t>Volticons</t>
+        </is>
+      </c>
+      <c r="AU25" s="24" t="inlineStr">
+        <is>
+          <t>Volticons</t>
+        </is>
+      </c>
+      <c r="AV25" s="24" t="n"/>
+      <c r="AW25" s="24" t="n"/>
+      <c r="AX25" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY25" s="24" t="n"/>
+      <c r="AZ25" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA25" s="24" t="inlineStr">
+        <is>
+          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
+        </is>
+      </c>
+      <c r="BB25" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC25" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD25" s="24" t="inlineStr">
+        <is>
+          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
+        </is>
+      </c>
+      <c r="BE25" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF25" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG25" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:15:53.573864Z</t>
+        </is>
+      </c>
+      <c r="BI25" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ25" s="25" t="n"/>
+      <c r="BK25" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="BL25" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="BM25" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="BN25" s="28" t="n"/>
+      <c r="BO25" s="28" t="n"/>
+      <c r="BP25" s="25" t="n"/>
+      <c r="BQ25" s="27" t="n"/>
+      <c r="BR25" s="28" t="n"/>
+      <c r="BS25" s="28" t="n"/>
+      <c r="BT25" s="28" t="n"/>
+      <c r="BU25" s="25" t="n"/>
+      <c r="BV25" s="29" t="n"/>
+      <c r="BW25" s="24" t="n"/>
+      <c r="BX25" s="30" t="n"/>
+      <c r="BY25" s="27" t="n"/>
+      <c r="BZ25" s="24" t="n"/>
+      <c r="CA25" s="31" t="n"/>
+      <c r="CB25" s="24" t="n"/>
+      <c r="CC25" s="24" t="n"/>
+      <c r="CD25" s="24" t="n"/>
+      <c r="CE25" s="24" t="n"/>
+      <c r="CF25" s="24" t="n"/>
+      <c r="CG25" s="24" t="n"/>
+      <c r="CH25" s="24" t="n"/>
+      <c r="CI25" s="24" t="n"/>
+      <c r="CJ25" s="24" t="n"/>
+      <c r="CK25" s="24" t="n"/>
+      <c r="CL25" s="24" t="n"/>
+      <c r="CM25" s="24" t="n"/>
+      <c r="CN25" s="24" t="n"/>
+      <c r="CO25" s="24" t="n"/>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>a3d1b8d8dd864270</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:15:56.246313Z</t>
+        </is>
+      </c>
+      <c r="C26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="D26" s="24" t="inlineStr">
+        <is>
+          <t>68011</t>
+        </is>
+      </c>
+      <c r="E26" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F26" s="24" t="inlineStr">
+        <is>
+          <t>Vivo Keyd Stars Academy</t>
+        </is>
+      </c>
+      <c r="G26" s="24" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="H26" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I26" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J26" s="25" t="n"/>
+      <c r="K26" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L26" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="M26" s="27" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="N26" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="O26" s="28" t="n">
+        <v>0.502645</v>
+      </c>
+      <c r="P26" s="28" t="n"/>
+      <c r="Q26" s="28" t="n">
+        <v>-0.016586</v>
+      </c>
+      <c r="R26" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="S26" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T26" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U26" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V26" s="24" t="n"/>
+      <c r="W26" s="26" t="n"/>
+      <c r="X26" s="26" t="n"/>
+      <c r="Y26" s="25" t="n"/>
+      <c r="Z26" s="26" t="n"/>
+      <c r="AA26" s="28" t="n"/>
+      <c r="AB26" s="28" t="n"/>
+      <c r="AC26" s="30" t="n"/>
+      <c r="AD26" s="24" t="n"/>
+      <c r="AE26" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5200 (market_slug=aec-lol-pnga-vksa-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF26" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG26" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH26" s="24" t="n"/>
+      <c r="AI26" s="31" t="n"/>
+      <c r="AJ26" s="31" t="n"/>
+      <c r="AK26" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL26" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM26" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN26" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO26" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP26" s="24" t="inlineStr">
+        <is>
+          <t>Vivo Keyd Stars Academy</t>
+        </is>
+      </c>
+      <c r="AQ26" s="24" t="inlineStr">
+        <is>
+          <t>Vivo Keyd Stars Academy</t>
+        </is>
+      </c>
+      <c r="AR26" s="24" t="inlineStr">
+        <is>
+          <t>Vivo Keyd Stars Academy</t>
+        </is>
+      </c>
+      <c r="AS26" s="24" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="AT26" s="24" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="AU26" s="24" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="AV26" s="24" t="n"/>
+      <c r="AW26" s="24" t="n"/>
+      <c r="AX26" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY26" s="24" t="n"/>
+      <c r="AZ26" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA26" s="24" t="inlineStr">
+        <is>
+          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
+        </is>
+      </c>
+      <c r="BB26" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC26" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD26" s="24" t="inlineStr">
+        <is>
+          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
+        </is>
+      </c>
+      <c r="BE26" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF26" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG26" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:15:55.156743Z</t>
+        </is>
+      </c>
+      <c r="BI26" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ26" s="25" t="n"/>
+      <c r="BK26" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="BL26" s="27" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="BM26" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="BN26" s="28" t="n"/>
+      <c r="BO26" s="28" t="n"/>
+      <c r="BP26" s="25" t="n"/>
+      <c r="BQ26" s="27" t="n"/>
+      <c r="BR26" s="28" t="n"/>
+      <c r="BS26" s="28" t="n"/>
+      <c r="BT26" s="28" t="n"/>
+      <c r="BU26" s="25" t="n"/>
+      <c r="BV26" s="29" t="n"/>
+      <c r="BW26" s="24" t="n"/>
+      <c r="BX26" s="30" t="n"/>
+      <c r="BY26" s="27" t="n"/>
+      <c r="BZ26" s="24" t="n"/>
+      <c r="CA26" s="31" t="n"/>
+      <c r="CB26" s="24" t="n"/>
+      <c r="CC26" s="24" t="n"/>
+      <c r="CD26" s="24" t="n"/>
+      <c r="CE26" s="24" t="n"/>
+      <c r="CF26" s="24" t="n"/>
+      <c r="CG26" s="24" t="n"/>
+      <c r="CH26" s="24" t="n"/>
+      <c r="CI26" s="24" t="n"/>
+      <c r="CJ26" s="24" t="n"/>
+      <c r="CK26" s="24" t="n"/>
+      <c r="CL26" s="24" t="n"/>
+      <c r="CM26" s="24" t="n"/>
+      <c r="CN26" s="24" t="n"/>
+      <c r="CO26" s="24" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research/lol.xlsx
+++ b/data/research/lol.xlsx
@@ -4974,12 +4974,12 @@
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="24" t="inlineStr">
         <is>
-          <t>ea2d86c22c2d4903</t>
+          <t>10b3e168b1dc4745</t>
         </is>
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:15:56.246313Z</t>
+          <t>2026-08-02T08:19:01.327445Z</t>
         </is>
       </c>
       <c r="C14" s="24" t="inlineStr">
@@ -5150,7 +5150,7 @@
       </c>
       <c r="BA14" s="24" t="inlineStr">
         <is>
-          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
+          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
         </is>
       </c>
       <c r="BB14" s="24" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="BD14" s="24" t="inlineStr">
         <is>
-          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
+          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
         </is>
       </c>
       <c r="BE14" s="24" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="BH14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:15:42.166882Z</t>
+          <t>2026-08-02T08:18:46.585713Z</t>
         </is>
       </c>
       <c r="BI14" s="24" t="inlineStr">
@@ -5235,12 +5235,12 @@
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="24" t="inlineStr">
         <is>
-          <t>d448911e6ca34774</t>
+          <t>2f3059b54cbf4f50</t>
         </is>
       </c>
       <c r="B15" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:15:56.246313Z</t>
+          <t>2026-08-02T08:19:01.327445Z</t>
         </is>
       </c>
       <c r="C15" s="24" t="inlineStr">
@@ -5285,23 +5285,23 @@
         </is>
       </c>
       <c r="L15" s="26" t="n">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="M15" s="27" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="N15" s="28" t="n">
-        <v>0.480769</v>
+        <v>0.5</v>
       </c>
       <c r="O15" s="28" t="n">
         <v>0.58589</v>
       </c>
       <c r="P15" s="28" t="n"/>
       <c r="Q15" s="28" t="n">
-        <v>0.105121</v>
+        <v>0.08588999999999999</v>
       </c>
       <c r="R15" s="26" t="n">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="S15" s="29" t="n">
         <v>1.25</v>
@@ -5327,7 +5327,7 @@
       <c r="AD15" s="24" t="n"/>
       <c r="AE15" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4800 (market_slug=aec-lol-els-lil-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.5000 (market_slug=aec-lol-els-lil-2026-08-02).</t>
         </is>
       </c>
       <c r="AF15" s="31" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="BA15" s="24" t="inlineStr">
         <is>
-          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
+          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
         </is>
       </c>
       <c r="BB15" s="24" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="BD15" s="24" t="inlineStr">
         <is>
-          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
+          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
         </is>
       </c>
       <c r="BE15" s="24" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="BH15" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:15:42.626245Z</t>
+          <t>2026-08-02T08:18:47.154301Z</t>
         </is>
       </c>
       <c r="BI15" s="24" t="inlineStr">
@@ -5456,13 +5456,13 @@
       </c>
       <c r="BJ15" s="25" t="n"/>
       <c r="BK15" s="26" t="n">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="BL15" s="27" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="BM15" s="28" t="n">
-        <v>0.480769</v>
+        <v>0.5</v>
       </c>
       <c r="BN15" s="28" t="n"/>
       <c r="BO15" s="28" t="n"/>
@@ -5496,12 +5496,12 @@
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="24" t="inlineStr">
         <is>
-          <t>30d50d5f99ff41cc</t>
+          <t>5187c15e8da743cc</t>
         </is>
       </c>
       <c r="B16" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:15:56.246313Z</t>
+          <t>2026-08-02T08:19:01.327445Z</t>
         </is>
       </c>
       <c r="C16" s="24" t="inlineStr">
@@ -5672,7 +5672,7 @@
       </c>
       <c r="BA16" s="24" t="inlineStr">
         <is>
-          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
+          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
         </is>
       </c>
       <c r="BB16" s="24" t="inlineStr">
@@ -5687,7 +5687,7 @@
       </c>
       <c r="BD16" s="24" t="inlineStr">
         <is>
-          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
+          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
         </is>
       </c>
       <c r="BE16" s="24" t="inlineStr">
@@ -5707,7 +5707,7 @@
       </c>
       <c r="BH16" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:15:43.093607Z</t>
+          <t>2026-08-02T08:18:47.619287Z</t>
         </is>
       </c>
       <c r="BI16" s="24" t="inlineStr">
@@ -5757,12 +5757,12 @@
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="24" t="inlineStr">
         <is>
-          <t>cf551c273736402d</t>
+          <t>7a99912c12b14fcc</t>
         </is>
       </c>
       <c r="B17" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:15:56.246313Z</t>
+          <t>2026-08-02T08:19:01.327445Z</t>
         </is>
       </c>
       <c r="C17" s="24" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="BA17" s="24" t="inlineStr">
         <is>
-          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
+          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
         </is>
       </c>
       <c r="BB17" s="24" t="inlineStr">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="BD17" s="24" t="inlineStr">
         <is>
-          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
+          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
         </is>
       </c>
       <c r="BE17" s="24" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="BH17" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:15:43.668159Z</t>
+          <t>2026-08-02T08:18:48.081954Z</t>
         </is>
       </c>
       <c r="BI17" s="24" t="inlineStr">
@@ -6018,12 +6018,12 @@
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="24" t="inlineStr">
         <is>
-          <t>e7034161fa2349ed</t>
+          <t>8b6c584759414cc1</t>
         </is>
       </c>
       <c r="B18" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:15:56.246313Z</t>
+          <t>2026-08-02T08:19:01.327445Z</t>
         </is>
       </c>
       <c r="C18" s="24" t="inlineStr">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="BA18" s="24" t="inlineStr">
         <is>
-          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
+          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
         </is>
       </c>
       <c r="BB18" s="24" t="inlineStr">
@@ -6209,7 +6209,7 @@
       </c>
       <c r="BD18" s="24" t="inlineStr">
         <is>
-          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
+          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
         </is>
       </c>
       <c r="BE18" s="24" t="inlineStr">
@@ -6229,7 +6229,7 @@
       </c>
       <c r="BH18" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:15:44.600133Z</t>
+          <t>2026-08-02T08:18:49.035396Z</t>
         </is>
       </c>
       <c r="BI18" s="24" t="inlineStr">
@@ -6279,12 +6279,12 @@
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="24" t="inlineStr">
         <is>
-          <t>e14dbaebac5846fe</t>
+          <t>6a7ed9700d124b3d</t>
         </is>
       </c>
       <c r="B19" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:15:56.246313Z</t>
+          <t>2026-08-02T08:19:01.327445Z</t>
         </is>
       </c>
       <c r="C19" s="24" t="inlineStr">
@@ -6455,7 +6455,7 @@
       </c>
       <c r="BA19" s="24" t="inlineStr">
         <is>
-          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
+          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
         </is>
       </c>
       <c r="BB19" s="24" t="inlineStr">
@@ -6470,7 +6470,7 @@
       </c>
       <c r="BD19" s="24" t="inlineStr">
         <is>
-          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
+          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
         </is>
       </c>
       <c r="BE19" s="24" t="inlineStr">
@@ -6490,7 +6490,7 @@
       </c>
       <c r="BH19" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:15:45.555467Z</t>
+          <t>2026-08-02T08:18:49.959371Z</t>
         </is>
       </c>
       <c r="BI19" s="24" t="inlineStr">
@@ -6540,12 +6540,12 @@
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="24" t="inlineStr">
         <is>
-          <t>3f7353916d03449d</t>
+          <t>a67cfd0aaf844da3</t>
         </is>
       </c>
       <c r="B20" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:15:56.246313Z</t>
+          <t>2026-08-02T08:19:01.327445Z</t>
         </is>
       </c>
       <c r="C20" s="24" t="inlineStr">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="BA20" s="24" t="inlineStr">
         <is>
-          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
+          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
         </is>
       </c>
       <c r="BB20" s="24" t="inlineStr">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="BD20" s="24" t="inlineStr">
         <is>
-          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
+          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
         </is>
       </c>
       <c r="BE20" s="24" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="BH20" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:15:46.035443Z</t>
+          <t>2026-08-02T08:18:50.513547Z</t>
         </is>
       </c>
       <c r="BI20" s="24" t="inlineStr">
@@ -6801,12 +6801,12 @@
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="24" t="inlineStr">
         <is>
-          <t>a977f54662824001</t>
+          <t>02b2318b3dad4b98</t>
         </is>
       </c>
       <c r="B21" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:15:56.246313Z</t>
+          <t>2026-08-02T08:19:01.327445Z</t>
         </is>
       </c>
       <c r="C21" s="24" t="inlineStr">
@@ -6977,7 +6977,7 @@
       </c>
       <c r="BA21" s="24" t="inlineStr">
         <is>
-          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
+          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
         </is>
       </c>
       <c r="BB21" s="24" t="inlineStr">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="BD21" s="24" t="inlineStr">
         <is>
-          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
+          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
         </is>
       </c>
       <c r="BE21" s="24" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="BH21" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:15:48.091630Z</t>
+          <t>2026-08-02T08:18:52.523888Z</t>
         </is>
       </c>
       <c r="BI21" s="24" t="inlineStr">
@@ -7062,12 +7062,12 @@
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="24" t="inlineStr">
         <is>
-          <t>1555011929a640aa</t>
+          <t>e32be00abe7c4f54</t>
         </is>
       </c>
       <c r="B22" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:15:56.246313Z</t>
+          <t>2026-08-02T08:19:01.327445Z</t>
         </is>
       </c>
       <c r="C22" s="24" t="inlineStr">
@@ -7238,7 +7238,7 @@
       </c>
       <c r="BA22" s="24" t="inlineStr">
         <is>
-          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
+          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
         </is>
       </c>
       <c r="BB22" s="24" t="inlineStr">
@@ -7253,7 +7253,7 @@
       </c>
       <c r="BD22" s="24" t="inlineStr">
         <is>
-          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
+          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
         </is>
       </c>
       <c r="BE22" s="24" t="inlineStr">
@@ -7273,7 +7273,7 @@
       </c>
       <c r="BH22" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:15:48.572339Z</t>
+          <t>2026-08-02T08:18:53.072135Z</t>
         </is>
       </c>
       <c r="BI22" s="24" t="inlineStr">
@@ -7323,12 +7323,12 @@
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="24" t="inlineStr">
         <is>
-          <t>8ed69f703f774054</t>
+          <t>dd07955ffed94f69</t>
         </is>
       </c>
       <c r="B23" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:15:56.246313Z</t>
+          <t>2026-08-02T08:19:01.327445Z</t>
         </is>
       </c>
       <c r="C23" s="24" t="inlineStr">
@@ -7499,7 +7499,7 @@
       </c>
       <c r="BA23" s="24" t="inlineStr">
         <is>
-          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
+          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
         </is>
       </c>
       <c r="BB23" s="24" t="inlineStr">
@@ -7514,7 +7514,7 @@
       </c>
       <c r="BD23" s="24" t="inlineStr">
         <is>
-          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
+          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
         </is>
       </c>
       <c r="BE23" s="24" t="inlineStr">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="BH23" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:15:49.062474Z</t>
+          <t>2026-08-02T08:18:53.565307Z</t>
         </is>
       </c>
       <c r="BI23" s="24" t="inlineStr">
@@ -7584,12 +7584,12 @@
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="24" t="inlineStr">
         <is>
-          <t>13c04f6fa3534a6f</t>
+          <t>2b7562e5296f4388</t>
         </is>
       </c>
       <c r="B24" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:15:56.246313Z</t>
+          <t>2026-08-02T08:19:01.327445Z</t>
         </is>
       </c>
       <c r="C24" s="24" t="inlineStr">
@@ -7760,7 +7760,7 @@
       </c>
       <c r="BA24" s="24" t="inlineStr">
         <is>
-          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
+          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
         </is>
       </c>
       <c r="BB24" s="24" t="inlineStr">
@@ -7775,7 +7775,7 @@
       </c>
       <c r="BD24" s="24" t="inlineStr">
         <is>
-          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
+          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
         </is>
       </c>
       <c r="BE24" s="24" t="inlineStr">
@@ -7795,7 +7795,7 @@
       </c>
       <c r="BH24" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:15:49.527302Z</t>
+          <t>2026-08-02T08:18:54.139986Z</t>
         </is>
       </c>
       <c r="BI24" s="24" t="inlineStr">
@@ -7845,12 +7845,12 @@
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="24" t="inlineStr">
         <is>
-          <t>01563e5bbe284ba8</t>
+          <t>12831962246047a9</t>
         </is>
       </c>
       <c r="B25" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:15:56.246313Z</t>
+          <t>2026-08-02T08:19:01.327445Z</t>
         </is>
       </c>
       <c r="C25" s="24" t="inlineStr">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="BA25" s="24" t="inlineStr">
         <is>
-          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
+          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
         </is>
       </c>
       <c r="BB25" s="24" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BD25" s="24" t="inlineStr">
         <is>
-          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
+          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
         </is>
       </c>
       <c r="BE25" s="24" t="inlineStr">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="BH25" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:15:53.573864Z</t>
+          <t>2026-08-02T08:18:58.476467Z</t>
         </is>
       </c>
       <c r="BI25" s="24" t="inlineStr">
@@ -8106,12 +8106,12 @@
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="24" t="inlineStr">
         <is>
-          <t>a3d1b8d8dd864270</t>
+          <t>b864f5557c944960</t>
         </is>
       </c>
       <c r="B26" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:15:56.246313Z</t>
+          <t>2026-08-02T08:19:01.327445Z</t>
         </is>
       </c>
       <c r="C26" s="24" t="inlineStr">
@@ -8156,23 +8156,23 @@
         </is>
       </c>
       <c r="L26" s="26" t="n">
-        <v>-108</v>
+        <v>-122</v>
       </c>
       <c r="M26" s="27" t="n">
-        <v>1.925926</v>
+        <v>1.819672</v>
       </c>
       <c r="N26" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.54955</v>
       </c>
       <c r="O26" s="28" t="n">
         <v>0.502645</v>
       </c>
       <c r="P26" s="28" t="n"/>
       <c r="Q26" s="28" t="n">
-        <v>-0.016586</v>
+        <v>-0.046905</v>
       </c>
       <c r="R26" s="26" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="S26" s="29" t="n">
         <v>1</v>
@@ -8198,7 +8198,7 @@
       <c r="AD26" s="24" t="n"/>
       <c r="AE26" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5200 (market_slug=aec-lol-pnga-vksa-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-lol-pnga-vksa-2026-08-03).</t>
         </is>
       </c>
       <c r="AF26" s="31" t="inlineStr">
@@ -8282,7 +8282,7 @@
       </c>
       <c r="BA26" s="24" t="inlineStr">
         <is>
-          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
+          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
         </is>
       </c>
       <c r="BB26" s="24" t="inlineStr">
@@ -8297,7 +8297,7 @@
       </c>
       <c r="BD26" s="24" t="inlineStr">
         <is>
-          <t>1be0e48907712ac09a6b1f5865795bcbf7b504588c657f88df3298ce2f194843</t>
+          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
         </is>
       </c>
       <c r="BE26" s="24" t="inlineStr">
@@ -8317,7 +8317,7 @@
       </c>
       <c r="BH26" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:15:55.156743Z</t>
+          <t>2026-08-02T08:19:00.252145Z</t>
         </is>
       </c>
       <c r="BI26" s="24" t="inlineStr">
@@ -8327,13 +8327,13 @@
       </c>
       <c r="BJ26" s="25" t="n"/>
       <c r="BK26" s="26" t="n">
-        <v>-108</v>
+        <v>-122</v>
       </c>
       <c r="BL26" s="27" t="n">
-        <v>1.925926</v>
+        <v>1.819672</v>
       </c>
       <c r="BM26" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.54955</v>
       </c>
       <c r="BN26" s="28" t="n"/>
       <c r="BO26" s="28" t="n"/>

--- a/data/research/lol.xlsx
+++ b/data/research/lol.xlsx
@@ -4791,18 +4791,38 @@
       </c>
       <c r="U13" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V13" s="24" t="n"/>
-      <c r="W13" s="26" t="n"/>
-      <c r="X13" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V13" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W13" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y13" s="25" t="n"/>
-      <c r="Z13" s="26" t="n"/>
-      <c r="AA13" s="28" t="n"/>
-      <c r="AB13" s="28" t="n"/>
-      <c r="AC13" s="30" t="n"/>
-      <c r="AD13" s="24" t="n"/>
+      <c r="Z13" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="AA13" s="28" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AB13" s="28" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="AC13" s="30" t="n">
+        <v>0.7511</v>
+      </c>
+      <c r="AD13" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T09:53:38.533320Z</t>
+        </is>
+      </c>
       <c r="AE13" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-lol-tt-we-2026-08-02).</t>
@@ -4945,8 +4965,12 @@
       <c r="BN13" s="28" t="n"/>
       <c r="BO13" s="28" t="n"/>
       <c r="BP13" s="25" t="n"/>
-      <c r="BQ13" s="27" t="n"/>
-      <c r="BR13" s="28" t="n"/>
+      <c r="BQ13" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="BR13" s="28" t="n">
+        <v>0.7</v>
+      </c>
       <c r="BS13" s="28" t="n"/>
       <c r="BT13" s="28" t="n"/>
       <c r="BU13" s="25" t="n"/>
@@ -4974,12 +4998,12 @@
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="24" t="inlineStr">
         <is>
-          <t>10b3e168b1dc4745</t>
+          <t>33757bba99024f37</t>
         </is>
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:01.327445Z</t>
+          <t>2026-08-02T09:59:37.296167Z</t>
         </is>
       </c>
       <c r="C14" s="24" t="inlineStr">
@@ -5024,23 +5048,23 @@
         </is>
       </c>
       <c r="L14" s="26" t="n">
-        <v>170</v>
+        <v>113</v>
       </c>
       <c r="M14" s="27" t="n">
-        <v>2.7</v>
+        <v>2.13</v>
       </c>
       <c r="N14" s="28" t="n">
-        <v>0.37037</v>
+        <v>0.469484</v>
       </c>
       <c r="O14" s="28" t="n">
-        <v>0.615811</v>
+        <v>0.614494</v>
       </c>
       <c r="P14" s="28" t="n"/>
       <c r="Q14" s="28" t="n">
-        <v>0.245441</v>
+        <v>0.14501</v>
       </c>
       <c r="R14" s="26" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="S14" s="29" t="n">
         <v>1.5</v>
@@ -5066,7 +5090,7 @@
       <c r="AD14" s="24" t="n"/>
       <c r="AE14" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3700 (market_slug=aec-lol-cr-ao-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.4700 (market_slug=aec-lol-cr-ao-2026-08-02).</t>
         </is>
       </c>
       <c r="AF14" s="31" t="inlineStr">
@@ -5150,7 +5174,7 @@
       </c>
       <c r="BA14" s="24" t="inlineStr">
         <is>
-          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
+          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
         </is>
       </c>
       <c r="BB14" s="24" t="inlineStr">
@@ -5165,7 +5189,7 @@
       </c>
       <c r="BD14" s="24" t="inlineStr">
         <is>
-          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
+          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
         </is>
       </c>
       <c r="BE14" s="24" t="inlineStr">
@@ -5185,7 +5209,7 @@
       </c>
       <c r="BH14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:18:46.585713Z</t>
+          <t>2026-08-02T09:59:22.583724Z</t>
         </is>
       </c>
       <c r="BI14" s="24" t="inlineStr">
@@ -5195,13 +5219,13 @@
       </c>
       <c r="BJ14" s="25" t="n"/>
       <c r="BK14" s="26" t="n">
-        <v>170</v>
+        <v>113</v>
       </c>
       <c r="BL14" s="27" t="n">
-        <v>2.7</v>
+        <v>2.13</v>
       </c>
       <c r="BM14" s="28" t="n">
-        <v>0.37037</v>
+        <v>0.469484</v>
       </c>
       <c r="BN14" s="28" t="n"/>
       <c r="BO14" s="28" t="n"/>
@@ -5235,12 +5259,12 @@
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="24" t="inlineStr">
         <is>
-          <t>2f3059b54cbf4f50</t>
+          <t>74461a45898a4a7d</t>
         </is>
       </c>
       <c r="B15" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:01.327445Z</t>
+          <t>2026-08-02T09:59:37.296167Z</t>
         </is>
       </c>
       <c r="C15" s="24" t="inlineStr">
@@ -5294,11 +5318,11 @@
         <v>0.5</v>
       </c>
       <c r="O15" s="28" t="n">
-        <v>0.58589</v>
+        <v>0.586093</v>
       </c>
       <c r="P15" s="28" t="n"/>
       <c r="Q15" s="28" t="n">
-        <v>0.08588999999999999</v>
+        <v>0.086093</v>
       </c>
       <c r="R15" s="26" t="n">
         <v>63</v>
@@ -5411,7 +5435,7 @@
       </c>
       <c r="BA15" s="24" t="inlineStr">
         <is>
-          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
+          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
         </is>
       </c>
       <c r="BB15" s="24" t="inlineStr">
@@ -5426,7 +5450,7 @@
       </c>
       <c r="BD15" s="24" t="inlineStr">
         <is>
-          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
+          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
         </is>
       </c>
       <c r="BE15" s="24" t="inlineStr">
@@ -5446,7 +5470,7 @@
       </c>
       <c r="BH15" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:18:47.154301Z</t>
+          <t>2026-08-02T09:59:23.587864Z</t>
         </is>
       </c>
       <c r="BI15" s="24" t="inlineStr">
@@ -5496,12 +5520,12 @@
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="24" t="inlineStr">
         <is>
-          <t>5187c15e8da743cc</t>
+          <t>7b4139d22f3f4b67</t>
         </is>
       </c>
       <c r="B16" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:01.327445Z</t>
+          <t>2026-08-02T09:59:37.296167Z</t>
         </is>
       </c>
       <c r="C16" s="24" t="inlineStr">
@@ -5555,11 +5579,11 @@
         <v>0.539171</v>
       </c>
       <c r="O16" s="28" t="n">
-        <v>0.549306</v>
+        <v>0.5497840000000001</v>
       </c>
       <c r="P16" s="28" t="n"/>
       <c r="Q16" s="28" t="n">
-        <v>0.010135</v>
+        <v>0.010613</v>
       </c>
       <c r="R16" s="26" t="n">
         <v>25</v>
@@ -5672,7 +5696,7 @@
       </c>
       <c r="BA16" s="24" t="inlineStr">
         <is>
-          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
+          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
         </is>
       </c>
       <c r="BB16" s="24" t="inlineStr">
@@ -5687,7 +5711,7 @@
       </c>
       <c r="BD16" s="24" t="inlineStr">
         <is>
-          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
+          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
         </is>
       </c>
       <c r="BE16" s="24" t="inlineStr">
@@ -5707,7 +5731,7 @@
       </c>
       <c r="BH16" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:18:47.619287Z</t>
+          <t>2026-08-02T09:59:24.043094Z</t>
         </is>
       </c>
       <c r="BI16" s="24" t="inlineStr">
@@ -5757,12 +5781,12 @@
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="24" t="inlineStr">
         <is>
-          <t>7a99912c12b14fcc</t>
+          <t>4f302100dfd64584</t>
         </is>
       </c>
       <c r="B17" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:01.327445Z</t>
+          <t>2026-08-02T09:59:37.296167Z</t>
         </is>
       </c>
       <c r="C17" s="24" t="inlineStr">
@@ -5816,11 +5840,11 @@
         <v>0.680511</v>
       </c>
       <c r="O17" s="28" t="n">
-        <v>0.553715</v>
+        <v>0.55411</v>
       </c>
       <c r="P17" s="28" t="n"/>
       <c r="Q17" s="28" t="n">
-        <v>-0.126796</v>
+        <v>-0.126401</v>
       </c>
       <c r="R17" s="26" t="n">
         <v>0</v>
@@ -5933,7 +5957,7 @@
       </c>
       <c r="BA17" s="24" t="inlineStr">
         <is>
-          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
+          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
         </is>
       </c>
       <c r="BB17" s="24" t="inlineStr">
@@ -5948,7 +5972,7 @@
       </c>
       <c r="BD17" s="24" t="inlineStr">
         <is>
-          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
+          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
         </is>
       </c>
       <c r="BE17" s="24" t="inlineStr">
@@ -5968,7 +5992,7 @@
       </c>
       <c r="BH17" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:18:48.081954Z</t>
+          <t>2026-08-02T09:59:24.695366Z</t>
         </is>
       </c>
       <c r="BI17" s="24" t="inlineStr">
@@ -6018,12 +6042,12 @@
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="24" t="inlineStr">
         <is>
-          <t>8b6c584759414cc1</t>
+          <t>af581e92b3bb4d90</t>
         </is>
       </c>
       <c r="B18" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:01.327445Z</t>
+          <t>2026-08-02T09:59:37.296167Z</t>
         </is>
       </c>
       <c r="C18" s="24" t="inlineStr">
@@ -6077,11 +6101,11 @@
         <v>0.34965</v>
       </c>
       <c r="O18" s="28" t="n">
-        <v>0.525701</v>
+        <v>0.526261</v>
       </c>
       <c r="P18" s="28" t="n"/>
       <c r="Q18" s="28" t="n">
-        <v>0.176051</v>
+        <v>0.176611</v>
       </c>
       <c r="R18" s="26" t="n">
         <v>100</v>
@@ -6194,7 +6218,7 @@
       </c>
       <c r="BA18" s="24" t="inlineStr">
         <is>
-          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
+          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
         </is>
       </c>
       <c r="BB18" s="24" t="inlineStr">
@@ -6209,7 +6233,7 @@
       </c>
       <c r="BD18" s="24" t="inlineStr">
         <is>
-          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
+          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
         </is>
       </c>
       <c r="BE18" s="24" t="inlineStr">
@@ -6229,7 +6253,7 @@
       </c>
       <c r="BH18" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:18:49.035396Z</t>
+          <t>2026-08-02T09:59:25.615269Z</t>
         </is>
       </c>
       <c r="BI18" s="24" t="inlineStr">
@@ -6279,12 +6303,12 @@
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="24" t="inlineStr">
         <is>
-          <t>6a7ed9700d124b3d</t>
+          <t>b8d9e8fb666e4bbc</t>
         </is>
       </c>
       <c r="B19" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:01.327445Z</t>
+          <t>2026-08-02T09:59:37.296167Z</t>
         </is>
       </c>
       <c r="C19" s="24" t="inlineStr">
@@ -6338,11 +6362,11 @@
         <v>0.579832</v>
       </c>
       <c r="O19" s="28" t="n">
-        <v>0.5601159999999999</v>
+        <v>0.559106</v>
       </c>
       <c r="P19" s="28" t="n"/>
       <c r="Q19" s="28" t="n">
-        <v>-0.019716</v>
+        <v>-0.020726</v>
       </c>
       <c r="R19" s="26" t="n">
         <v>10</v>
@@ -6455,7 +6479,7 @@
       </c>
       <c r="BA19" s="24" t="inlineStr">
         <is>
-          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
+          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
         </is>
       </c>
       <c r="BB19" s="24" t="inlineStr">
@@ -6470,7 +6494,7 @@
       </c>
       <c r="BD19" s="24" t="inlineStr">
         <is>
-          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
+          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
         </is>
       </c>
       <c r="BE19" s="24" t="inlineStr">
@@ -6490,7 +6514,7 @@
       </c>
       <c r="BH19" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:18:49.959371Z</t>
+          <t>2026-08-02T09:59:26.548060Z</t>
         </is>
       </c>
       <c r="BI19" s="24" t="inlineStr">
@@ -6540,12 +6564,12 @@
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="24" t="inlineStr">
         <is>
-          <t>a67cfd0aaf844da3</t>
+          <t>9503651634e249ed</t>
         </is>
       </c>
       <c r="B20" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:01.327445Z</t>
+          <t>2026-08-02T09:59:37.296167Z</t>
         </is>
       </c>
       <c r="C20" s="24" t="inlineStr">
@@ -6599,11 +6623,11 @@
         <v>0.65035</v>
       </c>
       <c r="O20" s="28" t="n">
-        <v>0.594427</v>
+        <v>0.593207</v>
       </c>
       <c r="P20" s="28" t="n"/>
       <c r="Q20" s="28" t="n">
-        <v>-0.055923</v>
+        <v>-0.057143</v>
       </c>
       <c r="R20" s="26" t="n">
         <v>0</v>
@@ -6716,7 +6740,7 @@
       </c>
       <c r="BA20" s="24" t="inlineStr">
         <is>
-          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
+          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
         </is>
       </c>
       <c r="BB20" s="24" t="inlineStr">
@@ -6731,7 +6755,7 @@
       </c>
       <c r="BD20" s="24" t="inlineStr">
         <is>
-          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
+          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
         </is>
       </c>
       <c r="BE20" s="24" t="inlineStr">
@@ -6751,7 +6775,7 @@
       </c>
       <c r="BH20" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:18:50.513547Z</t>
+          <t>2026-08-02T09:59:27.003766Z</t>
         </is>
       </c>
       <c r="BI20" s="24" t="inlineStr">
@@ -6801,12 +6825,12 @@
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="24" t="inlineStr">
         <is>
-          <t>02b2318b3dad4b98</t>
+          <t>318d4eefbc8146b4</t>
         </is>
       </c>
       <c r="B21" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:01.327445Z</t>
+          <t>2026-08-02T09:59:37.296167Z</t>
         </is>
       </c>
       <c r="C21" s="24" t="inlineStr">
@@ -6860,14 +6884,14 @@
         <v>0.570815</v>
       </c>
       <c r="O21" s="28" t="n">
-        <v>0.5826210000000001</v>
+        <v>0.581317</v>
       </c>
       <c r="P21" s="28" t="n"/>
       <c r="Q21" s="28" t="n">
-        <v>0.011806</v>
+        <v>0.010502</v>
       </c>
       <c r="R21" s="26" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="S21" s="29" t="n">
         <v>1.25</v>
@@ -6977,7 +7001,7 @@
       </c>
       <c r="BA21" s="24" t="inlineStr">
         <is>
-          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
+          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
         </is>
       </c>
       <c r="BB21" s="24" t="inlineStr">
@@ -6992,7 +7016,7 @@
       </c>
       <c r="BD21" s="24" t="inlineStr">
         <is>
-          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
+          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
         </is>
       </c>
       <c r="BE21" s="24" t="inlineStr">
@@ -7012,7 +7036,7 @@
       </c>
       <c r="BH21" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:18:52.523888Z</t>
+          <t>2026-08-02T09:59:28.910019Z</t>
         </is>
       </c>
       <c r="BI21" s="24" t="inlineStr">
@@ -7062,12 +7086,12 @@
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="24" t="inlineStr">
         <is>
-          <t>e32be00abe7c4f54</t>
+          <t>80b922686c084928</t>
         </is>
       </c>
       <c r="B22" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:01.327445Z</t>
+          <t>2026-08-02T09:59:37.296167Z</t>
         </is>
       </c>
       <c r="C22" s="24" t="inlineStr">
@@ -7121,11 +7145,11 @@
         <v>0.690402</v>
       </c>
       <c r="O22" s="28" t="n">
-        <v>0.636575</v>
+        <v>0.635143</v>
       </c>
       <c r="P22" s="28" t="n"/>
       <c r="Q22" s="28" t="n">
-        <v>-0.053827</v>
+        <v>-0.055259</v>
       </c>
       <c r="R22" s="26" t="n">
         <v>0</v>
@@ -7238,7 +7262,7 @@
       </c>
       <c r="BA22" s="24" t="inlineStr">
         <is>
-          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
+          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
         </is>
       </c>
       <c r="BB22" s="24" t="inlineStr">
@@ -7253,7 +7277,7 @@
       </c>
       <c r="BD22" s="24" t="inlineStr">
         <is>
-          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
+          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
         </is>
       </c>
       <c r="BE22" s="24" t="inlineStr">
@@ -7273,7 +7297,7 @@
       </c>
       <c r="BH22" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:18:53.072135Z</t>
+          <t>2026-08-02T09:59:29.389516Z</t>
         </is>
       </c>
       <c r="BI22" s="24" t="inlineStr">
@@ -7323,12 +7347,12 @@
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="24" t="inlineStr">
         <is>
-          <t>dd07955ffed94f69</t>
+          <t>53d526ff50734853</t>
         </is>
       </c>
       <c r="B23" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:01.327445Z</t>
+          <t>2026-08-02T09:59:37.296167Z</t>
         </is>
       </c>
       <c r="C23" s="24" t="inlineStr">
@@ -7382,14 +7406,14 @@
         <v>0.690402</v>
       </c>
       <c r="O23" s="28" t="n">
-        <v>0.70607</v>
+        <v>0.704215</v>
       </c>
       <c r="P23" s="28" t="n"/>
       <c r="Q23" s="28" t="n">
-        <v>0.015668</v>
+        <v>0.013813</v>
       </c>
       <c r="R23" s="26" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="S23" s="29" t="n">
         <v>2</v>
@@ -7499,7 +7523,7 @@
       </c>
       <c r="BA23" s="24" t="inlineStr">
         <is>
-          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
+          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
         </is>
       </c>
       <c r="BB23" s="24" t="inlineStr">
@@ -7514,7 +7538,7 @@
       </c>
       <c r="BD23" s="24" t="inlineStr">
         <is>
-          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
+          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
         </is>
       </c>
       <c r="BE23" s="24" t="inlineStr">
@@ -7534,7 +7558,7 @@
       </c>
       <c r="BH23" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:18:53.565307Z</t>
+          <t>2026-08-02T09:59:29.886639Z</t>
         </is>
       </c>
       <c r="BI23" s="24" t="inlineStr">
@@ -7584,12 +7608,12 @@
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="24" t="inlineStr">
         <is>
-          <t>2b7562e5296f4388</t>
+          <t>34c1afbf4268408a</t>
         </is>
       </c>
       <c r="B24" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:01.327445Z</t>
+          <t>2026-08-02T09:59:37.296167Z</t>
         </is>
       </c>
       <c r="C24" s="24" t="inlineStr">
@@ -7634,23 +7658,23 @@
         </is>
       </c>
       <c r="L24" s="26" t="n">
-        <v>-186</v>
+        <v>-170</v>
       </c>
       <c r="M24" s="27" t="n">
-        <v>1.537634</v>
+        <v>1.588235</v>
       </c>
       <c r="N24" s="28" t="n">
-        <v>0.65035</v>
+        <v>0.62963</v>
       </c>
       <c r="O24" s="28" t="n">
-        <v>0.748974</v>
+        <v>0.7472800000000001</v>
       </c>
       <c r="P24" s="28" t="n"/>
       <c r="Q24" s="28" t="n">
-        <v>0.098624</v>
+        <v>0.11765</v>
       </c>
       <c r="R24" s="26" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="S24" s="29" t="n">
         <v>2</v>
@@ -7676,7 +7700,7 @@
       <c r="AD24" s="24" t="n"/>
       <c r="AE24" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6500 (market_slug=aec-lol-ns-t1-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-lol-ns-t1-2026-08-03).</t>
         </is>
       </c>
       <c r="AF24" s="31" t="inlineStr">
@@ -7760,7 +7784,7 @@
       </c>
       <c r="BA24" s="24" t="inlineStr">
         <is>
-          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
+          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
         </is>
       </c>
       <c r="BB24" s="24" t="inlineStr">
@@ -7775,7 +7799,7 @@
       </c>
       <c r="BD24" s="24" t="inlineStr">
         <is>
-          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
+          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
         </is>
       </c>
       <c r="BE24" s="24" t="inlineStr">
@@ -7795,7 +7819,7 @@
       </c>
       <c r="BH24" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:18:54.139986Z</t>
+          <t>2026-08-02T09:59:30.347963Z</t>
         </is>
       </c>
       <c r="BI24" s="24" t="inlineStr">
@@ -7805,13 +7829,13 @@
       </c>
       <c r="BJ24" s="25" t="n"/>
       <c r="BK24" s="26" t="n">
-        <v>-186</v>
+        <v>-170</v>
       </c>
       <c r="BL24" s="27" t="n">
-        <v>1.537634</v>
+        <v>1.588235</v>
       </c>
       <c r="BM24" s="28" t="n">
-        <v>0.65035</v>
+        <v>0.62963</v>
       </c>
       <c r="BN24" s="28" t="n"/>
       <c r="BO24" s="28" t="n"/>
@@ -7845,12 +7869,12 @@
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="24" t="inlineStr">
         <is>
-          <t>12831962246047a9</t>
+          <t>43e40a955abb4a1a</t>
         </is>
       </c>
       <c r="B25" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:01.327445Z</t>
+          <t>2026-08-02T09:59:37.296167Z</t>
         </is>
       </c>
       <c r="C25" s="24" t="inlineStr">
@@ -7904,11 +7928,11 @@
         <v>0.590164</v>
       </c>
       <c r="O25" s="28" t="n">
-        <v>0.650712</v>
+        <v>0.650541</v>
       </c>
       <c r="P25" s="28" t="n"/>
       <c r="Q25" s="28" t="n">
-        <v>0.060548</v>
+        <v>0.060377</v>
       </c>
       <c r="R25" s="26" t="n">
         <v>50</v>
@@ -8021,7 +8045,7 @@
       </c>
       <c r="BA25" s="24" t="inlineStr">
         <is>
-          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
+          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
         </is>
       </c>
       <c r="BB25" s="24" t="inlineStr">
@@ -8036,7 +8060,7 @@
       </c>
       <c r="BD25" s="24" t="inlineStr">
         <is>
-          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
+          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
         </is>
       </c>
       <c r="BE25" s="24" t="inlineStr">
@@ -8056,7 +8080,7 @@
       </c>
       <c r="BH25" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:18:58.476467Z</t>
+          <t>2026-08-02T09:59:34.514458Z</t>
         </is>
       </c>
       <c r="BI25" s="24" t="inlineStr">
@@ -8106,12 +8130,12 @@
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="24" t="inlineStr">
         <is>
-          <t>b864f5557c944960</t>
+          <t>8493ae69b0ec40f5</t>
         </is>
       </c>
       <c r="B26" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:01.327445Z</t>
+          <t>2026-08-02T09:59:37.296167Z</t>
         </is>
       </c>
       <c r="C26" s="24" t="inlineStr">
@@ -8156,20 +8180,20 @@
         </is>
       </c>
       <c r="L26" s="26" t="n">
-        <v>-122</v>
+        <v>-127</v>
       </c>
       <c r="M26" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.787402</v>
       </c>
       <c r="N26" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="O26" s="28" t="n">
-        <v>0.502645</v>
+        <v>0.501894</v>
       </c>
       <c r="P26" s="28" t="n"/>
       <c r="Q26" s="28" t="n">
-        <v>-0.046905</v>
+        <v>-0.057577</v>
       </c>
       <c r="R26" s="26" t="n">
         <v>0</v>
@@ -8198,7 +8222,7 @@
       <c r="AD26" s="24" t="n"/>
       <c r="AE26" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-lol-pnga-vksa-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-lol-pnga-vksa-2026-08-03).</t>
         </is>
       </c>
       <c r="AF26" s="31" t="inlineStr">
@@ -8282,7 +8306,7 @@
       </c>
       <c r="BA26" s="24" t="inlineStr">
         <is>
-          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
+          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
         </is>
       </c>
       <c r="BB26" s="24" t="inlineStr">
@@ -8297,7 +8321,7 @@
       </c>
       <c r="BD26" s="24" t="inlineStr">
         <is>
-          <t>1ed8905623cbc8c98babb2ad99db0cfcbc25ed6f42aaba07936af0afd46ae104</t>
+          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
         </is>
       </c>
       <c r="BE26" s="24" t="inlineStr">
@@ -8317,7 +8341,7 @@
       </c>
       <c r="BH26" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:00.252145Z</t>
+          <t>2026-08-02T09:59:36.264347Z</t>
         </is>
       </c>
       <c r="BI26" s="24" t="inlineStr">
@@ -8327,13 +8351,13 @@
       </c>
       <c r="BJ26" s="25" t="n"/>
       <c r="BK26" s="26" t="n">
-        <v>-122</v>
+        <v>-127</v>
       </c>
       <c r="BL26" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.787402</v>
       </c>
       <c r="BM26" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="BN26" s="28" t="n"/>
       <c r="BO26" s="28" t="n"/>

--- a/data/research/lol.xlsx
+++ b/data/research/lol.xlsx
@@ -300,9 +300,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO26" headerRowCount="1">
-  <autoFilter ref="A1:CO26"/>
-  <tableColumns count="93">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CP27" headerRowCount="1">
+  <autoFilter ref="A1:CP27"/>
+  <tableColumns count="94">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
     <tableColumn id="3" name="event_start_utc"/>
@@ -396,6 +396,7 @@
     <tableColumn id="91" name="back_to_back_gap"/>
     <tableColumn id="92" name="games_last_7_gap"/>
     <tableColumn id="93" name="schedule_missingness"/>
+    <tableColumn id="94" name="trade_candidate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -752,19 +753,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$26)</f>
+        <f>COUNTA('Picks'!$A$2:$A$27)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$26,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$27,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$26,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$27,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"win")+COUNTIFS('Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"win")+COUNTIFS('Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -792,19 +793,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$26,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$27,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$26,"&gt;0",'Picks'!$V$2:$V$26,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$26,"&gt;0",'Picks'!$V$2:$V$26,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$27,"&gt;0",'Picks'!$V$2:$V$27,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$27,"&gt;0",'Picks'!$V$2:$V$27,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$26,"&gt;0",'Picks'!$V$2:$V$26,"win")/(COUNTIFS('Picks'!$BX$2:$BX$26,"&gt;0",'Picks'!$V$2:$V$26,"win")+COUNTIFS('Picks'!$BX$2:$BX$26,"&gt;0",'Picks'!$V$2:$V$26,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$27,"&gt;0",'Picks'!$V$2:$V$27,"win")/(COUNTIFS('Picks'!$BX$2:$BX$27,"&gt;0",'Picks'!$V$2:$V$27,"win")+COUNTIFS('Picks'!$BX$2:$BX$27,"&gt;0",'Picks'!$V$2:$V$27,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$26)/SUM('Picks'!$BX$2:$BX$26),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$27)/SUM('Picks'!$BX$2:$BX$27),0)</f>
         <v/>
       </c>
     </row>
@@ -832,19 +833,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$26)</f>
+        <f>SUM('Picks'!$BY$2:$BY$27)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$26,"&lt;&gt;",'Picks'!$AB$2:$AB$26),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$27,"&lt;&gt;",'Picks'!$AB$2:$AB$27),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$26,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$26,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$27,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$27,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$26,'Picks'!$AM$2:$AM$26,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$27,'Picks'!$AM$2:$AM$27,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -899,15 +900,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$26,$A14,'Picks'!$U$2:$U$26,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$27,$A14,'Picks'!$U$2:$U$27,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$26,$A14,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$27,$A14,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$26,$A14,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$27,$A14,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -915,11 +916,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$26,'Picks'!$H$2:$H$26,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$27,'Picks'!$H$2:$H$27,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$26,'Picks'!$H$2:$H$26,$A14,'Picks'!$U$2:$U$26,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$27,'Picks'!$H$2:$H$27,$A14,'Picks'!$U$2:$U$27,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -930,15 +931,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$26,$A15,'Picks'!$U$2:$U$26,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$27,$A15,'Picks'!$U$2:$U$27,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$26,$A15,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$27,$A15,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$26,$A15,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$27,$A15,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -946,11 +947,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$26,'Picks'!$H$2:$H$26,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$27,'Picks'!$H$2:$H$27,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$26,'Picks'!$H$2:$H$26,$A15,'Picks'!$U$2:$U$26,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$27,'Picks'!$H$2:$H$27,$A15,'Picks'!$U$2:$U$27,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -961,15 +962,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$26,$A16,'Picks'!$U$2:$U$26,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$27,$A16,'Picks'!$U$2:$U$27,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$26,$A16,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$27,$A16,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$26,$A16,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$27,$A16,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -977,11 +978,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$26,'Picks'!$H$2:$H$26,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$27,'Picks'!$H$2:$H$27,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$26,'Picks'!$H$2:$H$26,$A16,'Picks'!$U$2:$U$26,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$27,'Picks'!$H$2:$H$27,$A16,'Picks'!$U$2:$U$27,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1010,7 +1011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO26"/>
+  <dimension ref="A1:CP27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1106,6 +1107,7 @@
     <col width="18" customWidth="1" min="91" max="91"/>
     <col width="18" customWidth="1" min="92" max="92"/>
     <col width="22" customWidth="1" min="93" max="93"/>
+    <col width="17" customWidth="1" min="94" max="94"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1572,6 +1574,11 @@
       <c r="CO1" s="23" t="inlineStr">
         <is>
           <t>schedule_missingness</t>
+        </is>
+      </c>
+      <c r="CP1" s="23" t="inlineStr">
+        <is>
+          <t>trade_candidate</t>
         </is>
       </c>
     </row>
@@ -1859,6 +1866,7 @@
       <c r="CM2" s="24" t="n"/>
       <c r="CN2" s="24" t="n"/>
       <c r="CO2" s="24" t="n"/>
+      <c r="CP2" s="24" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
@@ -2144,6 +2152,7 @@
       <c r="CM3" s="24" t="n"/>
       <c r="CN3" s="24" t="n"/>
       <c r="CO3" s="24" t="n"/>
+      <c r="CP3" s="24" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
@@ -2429,6 +2438,7 @@
       <c r="CM4" s="24" t="n"/>
       <c r="CN4" s="24" t="n"/>
       <c r="CO4" s="24" t="n"/>
+      <c r="CP4" s="24" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
@@ -2714,6 +2724,7 @@
       <c r="CM5" s="24" t="n"/>
       <c r="CN5" s="24" t="n"/>
       <c r="CO5" s="24" t="n"/>
+      <c r="CP5" s="24" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
@@ -2999,6 +3010,7 @@
       <c r="CM6" s="24" t="n"/>
       <c r="CN6" s="24" t="n"/>
       <c r="CO6" s="24" t="n"/>
+      <c r="CP6" s="24" t="n"/>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
@@ -3284,6 +3296,7 @@
       <c r="CM7" s="24" t="n"/>
       <c r="CN7" s="24" t="n"/>
       <c r="CO7" s="24" t="n"/>
+      <c r="CP7" s="24" t="n"/>
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
@@ -3569,6 +3582,7 @@
       <c r="CM8" s="24" t="n"/>
       <c r="CN8" s="24" t="n"/>
       <c r="CO8" s="24" t="n"/>
+      <c r="CP8" s="24" t="n"/>
     </row>
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
@@ -3854,6 +3868,7 @@
       <c r="CM9" s="24" t="n"/>
       <c r="CN9" s="24" t="n"/>
       <c r="CO9" s="24" t="n"/>
+      <c r="CP9" s="24" t="n"/>
     </row>
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
@@ -4139,6 +4154,7 @@
       <c r="CM10" s="24" t="n"/>
       <c r="CN10" s="24" t="n"/>
       <c r="CO10" s="24" t="n"/>
+      <c r="CP10" s="24" t="n"/>
     </row>
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
@@ -4424,6 +4440,7 @@
       <c r="CM11" s="24" t="n"/>
       <c r="CN11" s="24" t="n"/>
       <c r="CO11" s="24" t="n"/>
+      <c r="CP11" s="24" t="n"/>
     </row>
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
@@ -4709,6 +4726,7 @@
       <c r="CM12" s="24" t="n"/>
       <c r="CN12" s="24" t="n"/>
       <c r="CO12" s="24" t="n"/>
+      <c r="CP12" s="24" t="n"/>
     </row>
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
@@ -4994,6 +5012,7 @@
       <c r="CM13" s="24" t="n"/>
       <c r="CN13" s="24" t="n"/>
       <c r="CO13" s="24" t="n"/>
+      <c r="CP13" s="24" t="n"/>
     </row>
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="24" t="inlineStr">
@@ -5076,18 +5095,38 @@
       </c>
       <c r="U14" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V14" s="24" t="n"/>
-      <c r="W14" s="26" t="n"/>
-      <c r="X14" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V14" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W14" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X14" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y14" s="25" t="n"/>
-      <c r="Z14" s="26" t="n"/>
-      <c r="AA14" s="28" t="n"/>
-      <c r="AB14" s="28" t="n"/>
-      <c r="AC14" s="30" t="n"/>
-      <c r="AD14" s="24" t="n"/>
+      <c r="Z14" s="26" t="n">
+        <v>113</v>
+      </c>
+      <c r="AA14" s="28" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="AB14" s="28" t="n">
+        <v>0.000516</v>
+      </c>
+      <c r="AC14" s="30" t="n">
+        <v>1.695</v>
+      </c>
+      <c r="AD14" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T11:45:14.956616Z</t>
+        </is>
+      </c>
       <c r="AE14" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.4700 (market_slug=aec-lol-cr-ao-2026-08-02).</t>
@@ -5230,8 +5269,12 @@
       <c r="BN14" s="28" t="n"/>
       <c r="BO14" s="28" t="n"/>
       <c r="BP14" s="25" t="n"/>
-      <c r="BQ14" s="27" t="n"/>
-      <c r="BR14" s="28" t="n"/>
+      <c r="BQ14" s="27" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BR14" s="28" t="n">
+        <v>0.47</v>
+      </c>
       <c r="BS14" s="28" t="n"/>
       <c r="BT14" s="28" t="n"/>
       <c r="BU14" s="25" t="n"/>
@@ -5255,6 +5298,7 @@
       <c r="CM14" s="24" t="n"/>
       <c r="CN14" s="24" t="n"/>
       <c r="CO14" s="24" t="n"/>
+      <c r="CP14" s="24" t="n"/>
     </row>
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="24" t="inlineStr">
@@ -5337,18 +5381,38 @@
       </c>
       <c r="U15" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V15" s="24" t="n"/>
-      <c r="W15" s="26" t="n"/>
-      <c r="X15" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V15" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W15" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y15" s="25" t="n"/>
-      <c r="Z15" s="26" t="n"/>
-      <c r="AA15" s="28" t="n"/>
-      <c r="AB15" s="28" t="n"/>
-      <c r="AC15" s="30" t="n"/>
-      <c r="AD15" s="24" t="n"/>
+      <c r="Z15" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA15" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB15" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="30" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AD15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T11:45:16.142000Z</t>
+        </is>
+      </c>
       <c r="AE15" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5000 (market_slug=aec-lol-els-lil-2026-08-02).</t>
@@ -5361,7 +5425,7 @@
       </c>
       <c r="AG15" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH15" s="24" t="n"/>
@@ -5491,8 +5555,12 @@
       <c r="BN15" s="28" t="n"/>
       <c r="BO15" s="28" t="n"/>
       <c r="BP15" s="25" t="n"/>
-      <c r="BQ15" s="27" t="n"/>
-      <c r="BR15" s="28" t="n"/>
+      <c r="BQ15" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR15" s="28" t="n">
+        <v>0.5</v>
+      </c>
       <c r="BS15" s="28" t="n"/>
       <c r="BT15" s="28" t="n"/>
       <c r="BU15" s="25" t="n"/>
@@ -5516,6 +5584,7 @@
       <c r="CM15" s="24" t="n"/>
       <c r="CN15" s="24" t="n"/>
       <c r="CO15" s="24" t="n"/>
+      <c r="CP15" s="24" t="n"/>
     </row>
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="24" t="inlineStr">
@@ -5777,16 +5846,17 @@
       <c r="CM16" s="24" t="n"/>
       <c r="CN16" s="24" t="n"/>
       <c r="CO16" s="24" t="n"/>
+      <c r="CP16" s="24" t="n"/>
     </row>
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="24" t="inlineStr">
         <is>
-          <t>4f302100dfd64584</t>
+          <t>d68cc80d286f41da</t>
         </is>
       </c>
       <c r="B17" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:59:37.296167Z</t>
+          <t>2026-08-02T11:51:23.384049Z</t>
         </is>
       </c>
       <c r="C17" s="24" t="inlineStr">
@@ -5840,11 +5910,11 @@
         <v>0.680511</v>
       </c>
       <c r="O17" s="28" t="n">
-        <v>0.55411</v>
+        <v>0.55445</v>
       </c>
       <c r="P17" s="28" t="n"/>
       <c r="Q17" s="28" t="n">
-        <v>-0.126401</v>
+        <v>-0.126061</v>
       </c>
       <c r="R17" s="26" t="n">
         <v>0</v>
@@ -5859,18 +5929,38 @@
       </c>
       <c r="U17" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V17" s="24" t="n"/>
-      <c r="W17" s="26" t="n"/>
-      <c r="X17" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V17" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W17" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y17" s="25" t="n"/>
-      <c r="Z17" s="26" t="n"/>
-      <c r="AA17" s="28" t="n"/>
-      <c r="AB17" s="28" t="n"/>
-      <c r="AC17" s="30" t="n"/>
-      <c r="AD17" s="24" t="n"/>
+      <c r="Z17" s="26" t="n">
+        <v>-213</v>
+      </c>
+      <c r="AA17" s="28" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AB17" s="28" t="n">
+        <v>-0.000511</v>
+      </c>
+      <c r="AC17" s="30" t="n">
+        <v>0.4695</v>
+      </c>
+      <c r="AD17" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T13:01:29.241433Z</t>
+        </is>
+      </c>
       <c r="AE17" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-lol-kcbs-gls-2026-08-02).</t>
@@ -5957,7 +6047,7 @@
       </c>
       <c r="BA17" s="24" t="inlineStr">
         <is>
-          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
+          <t>0b6e6d5c93b93c005802ef0c5f9541d5ee8d587023a9a0b60009a394291af476</t>
         </is>
       </c>
       <c r="BB17" s="24" t="inlineStr">
@@ -5972,7 +6062,7 @@
       </c>
       <c r="BD17" s="24" t="inlineStr">
         <is>
-          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
+          <t>0b6e6d5c93b93c005802ef0c5f9541d5ee8d587023a9a0b60009a394291af476</t>
         </is>
       </c>
       <c r="BE17" s="24" t="inlineStr">
@@ -5992,7 +6082,7 @@
       </c>
       <c r="BH17" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:59:24.695366Z</t>
+          <t>2026-08-02T11:51:10.693295Z</t>
         </is>
       </c>
       <c r="BI17" s="24" t="inlineStr">
@@ -6013,8 +6103,12 @@
       <c r="BN17" s="28" t="n"/>
       <c r="BO17" s="28" t="n"/>
       <c r="BP17" s="25" t="n"/>
-      <c r="BQ17" s="27" t="n"/>
-      <c r="BR17" s="28" t="n"/>
+      <c r="BQ17" s="27" t="n">
+        <v>1.469484</v>
+      </c>
+      <c r="BR17" s="28" t="n">
+        <v>0.68</v>
+      </c>
       <c r="BS17" s="28" t="n"/>
       <c r="BT17" s="28" t="n"/>
       <c r="BU17" s="25" t="n"/>
@@ -6038,16 +6132,17 @@
       <c r="CM17" s="24" t="n"/>
       <c r="CN17" s="24" t="n"/>
       <c r="CO17" s="24" t="n"/>
+      <c r="CP17" s="24" t="n"/>
     </row>
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="24" t="inlineStr">
         <is>
-          <t>af581e92b3bb4d90</t>
+          <t>2b83893e5c494a36</t>
         </is>
       </c>
       <c r="B18" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:59:37.296167Z</t>
+          <t>2026-08-02T13:07:30.652675Z</t>
         </is>
       </c>
       <c r="C18" s="24" t="inlineStr">
@@ -6101,11 +6196,11 @@
         <v>0.34965</v>
       </c>
       <c r="O18" s="28" t="n">
-        <v>0.526261</v>
+        <v>0.526683</v>
       </c>
       <c r="P18" s="28" t="n"/>
       <c r="Q18" s="28" t="n">
-        <v>0.176611</v>
+        <v>0.177033</v>
       </c>
       <c r="R18" s="26" t="n">
         <v>100</v>
@@ -6218,7 +6313,7 @@
       </c>
       <c r="BA18" s="24" t="inlineStr">
         <is>
-          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
+          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
         </is>
       </c>
       <c r="BB18" s="24" t="inlineStr">
@@ -6233,7 +6328,7 @@
       </c>
       <c r="BD18" s="24" t="inlineStr">
         <is>
-          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
+          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
         </is>
       </c>
       <c r="BE18" s="24" t="inlineStr">
@@ -6253,7 +6348,7 @@
       </c>
       <c r="BH18" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:59:25.615269Z</t>
+          <t>2026-08-02T13:07:18.920620Z</t>
         </is>
       </c>
       <c r="BI18" s="24" t="inlineStr">
@@ -6299,16 +6394,17 @@
       <c r="CM18" s="24" t="n"/>
       <c r="CN18" s="24" t="n"/>
       <c r="CO18" s="24" t="n"/>
+      <c r="CP18" s="24" t="n"/>
     </row>
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="24" t="inlineStr">
         <is>
-          <t>b8d9e8fb666e4bbc</t>
+          <t>b1cb64fc389043e7</t>
         </is>
       </c>
       <c r="B19" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:59:37.296167Z</t>
+          <t>2026-08-02T13:07:30.652675Z</t>
         </is>
       </c>
       <c r="C19" s="24" t="inlineStr">
@@ -6353,23 +6449,23 @@
         </is>
       </c>
       <c r="L19" s="26" t="n">
-        <v>-138</v>
+        <v>-122</v>
       </c>
       <c r="M19" s="27" t="n">
-        <v>1.724638</v>
+        <v>1.819672</v>
       </c>
       <c r="N19" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.54955</v>
       </c>
       <c r="O19" s="28" t="n">
-        <v>0.559106</v>
+        <v>0.5584440000000001</v>
       </c>
       <c r="P19" s="28" t="n"/>
       <c r="Q19" s="28" t="n">
-        <v>-0.020726</v>
+        <v>0.008894000000000001</v>
       </c>
       <c r="R19" s="26" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="S19" s="29" t="n">
         <v>1</v>
@@ -6395,7 +6491,7 @@
       <c r="AD19" s="24" t="n"/>
       <c r="AE19" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-lol-fxw7-lll-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-lol-fxw7-lll-2026-08-02).</t>
         </is>
       </c>
       <c r="AF19" s="31" t="inlineStr">
@@ -6413,7 +6509,7 @@
       <c r="AJ19" s="31" t="n"/>
       <c r="AK19" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL19" s="26" t="n">
@@ -6421,17 +6517,17 @@
       </c>
       <c r="AM19" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN19" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO19" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP19" s="24" t="inlineStr">
@@ -6479,7 +6575,7 @@
       </c>
       <c r="BA19" s="24" t="inlineStr">
         <is>
-          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
+          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
         </is>
       </c>
       <c r="BB19" s="24" t="inlineStr">
@@ -6494,7 +6590,7 @@
       </c>
       <c r="BD19" s="24" t="inlineStr">
         <is>
-          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
+          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
         </is>
       </c>
       <c r="BE19" s="24" t="inlineStr">
@@ -6514,7 +6610,7 @@
       </c>
       <c r="BH19" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:59:26.548060Z</t>
+          <t>2026-08-02T13:07:19.930355Z</t>
         </is>
       </c>
       <c r="BI19" s="24" t="inlineStr">
@@ -6524,13 +6620,13 @@
       </c>
       <c r="BJ19" s="25" t="n"/>
       <c r="BK19" s="26" t="n">
-        <v>-138</v>
+        <v>-122</v>
       </c>
       <c r="BL19" s="27" t="n">
-        <v>1.724638</v>
+        <v>1.819672</v>
       </c>
       <c r="BM19" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.54955</v>
       </c>
       <c r="BN19" s="28" t="n"/>
       <c r="BO19" s="28" t="n"/>
@@ -6560,16 +6656,17 @@
       <c r="CM19" s="24" t="n"/>
       <c r="CN19" s="24" t="n"/>
       <c r="CO19" s="24" t="n"/>
+      <c r="CP19" s="24" t="n"/>
     </row>
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="24" t="inlineStr">
         <is>
-          <t>9503651634e249ed</t>
+          <t>0c6b04aa59674149</t>
         </is>
       </c>
       <c r="B20" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:59:37.296167Z</t>
+          <t>2026-08-02T13:07:30.652675Z</t>
         </is>
       </c>
       <c r="C20" s="24" t="inlineStr">
@@ -6614,20 +6711,20 @@
         </is>
       </c>
       <c r="L20" s="26" t="n">
-        <v>-186</v>
+        <v>-194</v>
       </c>
       <c r="M20" s="27" t="n">
-        <v>1.537634</v>
+        <v>1.515464</v>
       </c>
       <c r="N20" s="28" t="n">
-        <v>0.65035</v>
+        <v>0.659864</v>
       </c>
       <c r="O20" s="28" t="n">
-        <v>0.593207</v>
+        <v>0.592477</v>
       </c>
       <c r="P20" s="28" t="n"/>
       <c r="Q20" s="28" t="n">
-        <v>-0.057143</v>
+        <v>-0.067387</v>
       </c>
       <c r="R20" s="26" t="n">
         <v>0</v>
@@ -6656,7 +6753,7 @@
       <c r="AD20" s="24" t="n"/>
       <c r="AE20" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6500 (market_slug=aec-lol-fnc-mkoi-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.6600 (market_slug=aec-lol-fnc-mkoi-2026-08-02).</t>
         </is>
       </c>
       <c r="AF20" s="31" t="inlineStr">
@@ -6740,7 +6837,7 @@
       </c>
       <c r="BA20" s="24" t="inlineStr">
         <is>
-          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
+          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
         </is>
       </c>
       <c r="BB20" s="24" t="inlineStr">
@@ -6755,7 +6852,7 @@
       </c>
       <c r="BD20" s="24" t="inlineStr">
         <is>
-          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
+          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
         </is>
       </c>
       <c r="BE20" s="24" t="inlineStr">
@@ -6775,7 +6872,7 @@
       </c>
       <c r="BH20" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:59:27.003766Z</t>
+          <t>2026-08-02T13:07:20.483371Z</t>
         </is>
       </c>
       <c r="BI20" s="24" t="inlineStr">
@@ -6785,13 +6882,13 @@
       </c>
       <c r="BJ20" s="25" t="n"/>
       <c r="BK20" s="26" t="n">
-        <v>-186</v>
+        <v>-194</v>
       </c>
       <c r="BL20" s="27" t="n">
-        <v>1.537634</v>
+        <v>1.515464</v>
       </c>
       <c r="BM20" s="28" t="n">
-        <v>0.65035</v>
+        <v>0.659864</v>
       </c>
       <c r="BN20" s="28" t="n"/>
       <c r="BO20" s="28" t="n"/>
@@ -6821,16 +6918,17 @@
       <c r="CM20" s="24" t="n"/>
       <c r="CN20" s="24" t="n"/>
       <c r="CO20" s="24" t="n"/>
+      <c r="CP20" s="24" t="n"/>
     </row>
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="24" t="inlineStr">
         <is>
-          <t>318d4eefbc8146b4</t>
+          <t>42ce1bbba99e4389</t>
         </is>
       </c>
       <c r="B21" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:59:37.296167Z</t>
+          <t>2026-08-02T13:07:30.652675Z</t>
         </is>
       </c>
       <c r="C21" s="24" t="inlineStr">
@@ -6884,11 +6982,11 @@
         <v>0.570815</v>
       </c>
       <c r="O21" s="28" t="n">
-        <v>0.581317</v>
+        <v>0.58052</v>
       </c>
       <c r="P21" s="28" t="n"/>
       <c r="Q21" s="28" t="n">
-        <v>0.010502</v>
+        <v>0.009705</v>
       </c>
       <c r="R21" s="26" t="n">
         <v>25</v>
@@ -7001,7 +7099,7 @@
       </c>
       <c r="BA21" s="24" t="inlineStr">
         <is>
-          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
+          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
         </is>
       </c>
       <c r="BB21" s="24" t="inlineStr">
@@ -7016,7 +7114,7 @@
       </c>
       <c r="BD21" s="24" t="inlineStr">
         <is>
-          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
+          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
         </is>
       </c>
       <c r="BE21" s="24" t="inlineStr">
@@ -7036,7 +7134,7 @@
       </c>
       <c r="BH21" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:59:28.910019Z</t>
+          <t>2026-08-02T13:07:22.606056Z</t>
         </is>
       </c>
       <c r="BI21" s="24" t="inlineStr">
@@ -7082,16 +7180,17 @@
       <c r="CM21" s="24" t="n"/>
       <c r="CN21" s="24" t="n"/>
       <c r="CO21" s="24" t="n"/>
+      <c r="CP21" s="24" t="n"/>
     </row>
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="24" t="inlineStr">
         <is>
-          <t>80b922686c084928</t>
+          <t>02458941fd3f4362</t>
         </is>
       </c>
       <c r="B22" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:59:37.296167Z</t>
+          <t>2026-08-02T13:07:30.652675Z</t>
         </is>
       </c>
       <c r="C22" s="24" t="inlineStr">
@@ -7136,20 +7235,20 @@
         </is>
       </c>
       <c r="L22" s="26" t="n">
-        <v>-223</v>
+        <v>-213</v>
       </c>
       <c r="M22" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.469484</v>
       </c>
       <c r="N22" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.680511</v>
       </c>
       <c r="O22" s="28" t="n">
-        <v>0.635143</v>
+        <v>0.63434</v>
       </c>
       <c r="P22" s="28" t="n"/>
       <c r="Q22" s="28" t="n">
-        <v>-0.055259</v>
+        <v>-0.046171</v>
       </c>
       <c r="R22" s="26" t="n">
         <v>0</v>
@@ -7178,7 +7277,7 @@
       <c r="AD22" s="24" t="n"/>
       <c r="AE22" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-lol-hbc-foxy-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-lol-hbc-foxy-2026-08-03).</t>
         </is>
       </c>
       <c r="AF22" s="31" t="inlineStr">
@@ -7262,7 +7361,7 @@
       </c>
       <c r="BA22" s="24" t="inlineStr">
         <is>
-          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
+          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
         </is>
       </c>
       <c r="BB22" s="24" t="inlineStr">
@@ -7277,7 +7376,7 @@
       </c>
       <c r="BD22" s="24" t="inlineStr">
         <is>
-          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
+          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
         </is>
       </c>
       <c r="BE22" s="24" t="inlineStr">
@@ -7297,7 +7396,7 @@
       </c>
       <c r="BH22" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:59:29.389516Z</t>
+          <t>2026-08-02T13:07:23.091424Z</t>
         </is>
       </c>
       <c r="BI22" s="24" t="inlineStr">
@@ -7307,13 +7406,13 @@
       </c>
       <c r="BJ22" s="25" t="n"/>
       <c r="BK22" s="26" t="n">
-        <v>-223</v>
+        <v>-213</v>
       </c>
       <c r="BL22" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.469484</v>
       </c>
       <c r="BM22" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.680511</v>
       </c>
       <c r="BN22" s="28" t="n"/>
       <c r="BO22" s="28" t="n"/>
@@ -7343,16 +7442,17 @@
       <c r="CM22" s="24" t="n"/>
       <c r="CN22" s="24" t="n"/>
       <c r="CO22" s="24" t="n"/>
+      <c r="CP22" s="24" t="n"/>
     </row>
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="24" t="inlineStr">
         <is>
-          <t>53d526ff50734853</t>
+          <t>5c5778fbf88d4bad</t>
         </is>
       </c>
       <c r="B23" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:59:37.296167Z</t>
+          <t>2026-08-02T13:07:30.652675Z</t>
         </is>
       </c>
       <c r="C23" s="24" t="inlineStr">
@@ -7406,14 +7506,14 @@
         <v>0.690402</v>
       </c>
       <c r="O23" s="28" t="n">
-        <v>0.704215</v>
+        <v>0.703234</v>
       </c>
       <c r="P23" s="28" t="n"/>
       <c r="Q23" s="28" t="n">
-        <v>0.013813</v>
+        <v>0.012832</v>
       </c>
       <c r="R23" s="26" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S23" s="29" t="n">
         <v>2</v>
@@ -7523,7 +7623,7 @@
       </c>
       <c r="BA23" s="24" t="inlineStr">
         <is>
-          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
+          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
         </is>
       </c>
       <c r="BB23" s="24" t="inlineStr">
@@ -7538,7 +7638,7 @@
       </c>
       <c r="BD23" s="24" t="inlineStr">
         <is>
-          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
+          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
         </is>
       </c>
       <c r="BE23" s="24" t="inlineStr">
@@ -7558,7 +7658,7 @@
       </c>
       <c r="BH23" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:59:29.886639Z</t>
+          <t>2026-08-02T13:07:23.605808Z</t>
         </is>
       </c>
       <c r="BI23" s="24" t="inlineStr">
@@ -7604,16 +7704,17 @@
       <c r="CM23" s="24" t="n"/>
       <c r="CN23" s="24" t="n"/>
       <c r="CO23" s="24" t="n"/>
+      <c r="CP23" s="24" t="n"/>
     </row>
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="24" t="inlineStr">
         <is>
-          <t>34c1afbf4268408a</t>
+          <t>1531b3ab80db4f56</t>
         </is>
       </c>
       <c r="B24" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:59:37.296167Z</t>
+          <t>2026-08-02T13:07:30.652675Z</t>
         </is>
       </c>
       <c r="C24" s="24" t="inlineStr">
@@ -7667,14 +7768,14 @@
         <v>0.62963</v>
       </c>
       <c r="O24" s="28" t="n">
-        <v>0.7472800000000001</v>
+        <v>0.746484</v>
       </c>
       <c r="P24" s="28" t="n"/>
       <c r="Q24" s="28" t="n">
-        <v>0.11765</v>
+        <v>0.116854</v>
       </c>
       <c r="R24" s="26" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S24" s="29" t="n">
         <v>2</v>
@@ -7784,7 +7885,7 @@
       </c>
       <c r="BA24" s="24" t="inlineStr">
         <is>
-          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
+          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
         </is>
       </c>
       <c r="BB24" s="24" t="inlineStr">
@@ -7799,7 +7900,7 @@
       </c>
       <c r="BD24" s="24" t="inlineStr">
         <is>
-          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
+          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
         </is>
       </c>
       <c r="BE24" s="24" t="inlineStr">
@@ -7819,7 +7920,7 @@
       </c>
       <c r="BH24" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:59:30.347963Z</t>
+          <t>2026-08-02T13:07:24.188851Z</t>
         </is>
       </c>
       <c r="BI24" s="24" t="inlineStr">
@@ -7865,26 +7966,27 @@
       <c r="CM24" s="24" t="n"/>
       <c r="CN24" s="24" t="n"/>
       <c r="CO24" s="24" t="n"/>
+      <c r="CP24" s="24" t="n"/>
     </row>
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="24" t="inlineStr">
         <is>
-          <t>43e40a955abb4a1a</t>
+          <t>dc68b9a8665d44ee</t>
         </is>
       </c>
       <c r="B25" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:59:37.296167Z</t>
+          <t>2026-08-02T13:07:30.652675Z</t>
         </is>
       </c>
       <c r="C25" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T20:00:00Z</t>
+          <t>2026-08-03T15:00:00Z</t>
         </is>
       </c>
       <c r="D25" s="24" t="inlineStr">
         <is>
-          <t>67937</t>
+          <t>67566</t>
         </is>
       </c>
       <c r="E25" s="24" t="inlineStr">
@@ -7894,12 +7996,12 @@
       </c>
       <c r="F25" s="24" t="inlineStr">
         <is>
-          <t>Docta Esports</t>
+          <t>Shifters</t>
         </is>
       </c>
       <c r="G25" s="24" t="inlineStr">
         <is>
-          <t>Volticons</t>
+          <t>Natus Vincere</t>
         </is>
       </c>
       <c r="H25" s="24" t="inlineStr">
@@ -7919,26 +8021,26 @@
         </is>
       </c>
       <c r="L25" s="26" t="n">
-        <v>-144</v>
+        <v>-233</v>
       </c>
       <c r="M25" s="27" t="n">
-        <v>1.694444</v>
+        <v>1.429185</v>
       </c>
       <c r="N25" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.6997</v>
       </c>
       <c r="O25" s="28" t="n">
-        <v>0.650541</v>
+        <v>0.74769</v>
       </c>
       <c r="P25" s="28" t="n"/>
       <c r="Q25" s="28" t="n">
-        <v>0.060377</v>
+        <v>0.04799</v>
       </c>
       <c r="R25" s="26" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="S25" s="29" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="T25" s="24" t="inlineStr">
         <is>
@@ -7961,7 +8063,7 @@
       <c r="AD25" s="24" t="n"/>
       <c r="AE25" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-lol-vtc-doh-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-lol-navi-shft-2026-08-03).</t>
         </is>
       </c>
       <c r="AF25" s="31" t="inlineStr">
@@ -8002,32 +8104,32 @@
       </c>
       <c r="AP25" s="24" t="inlineStr">
         <is>
-          <t>Docta Esports</t>
+          <t>Shifters</t>
         </is>
       </c>
       <c r="AQ25" s="24" t="inlineStr">
         <is>
-          <t>Docta Esports</t>
+          <t>Shifters</t>
         </is>
       </c>
       <c r="AR25" s="24" t="inlineStr">
         <is>
-          <t>Docta Esports</t>
+          <t>Shifters</t>
         </is>
       </c>
       <c r="AS25" s="24" t="inlineStr">
         <is>
-          <t>Volticons</t>
+          <t>Natus Vincere</t>
         </is>
       </c>
       <c r="AT25" s="24" t="inlineStr">
         <is>
-          <t>Volticons</t>
+          <t>Natus Vincere</t>
         </is>
       </c>
       <c r="AU25" s="24" t="inlineStr">
         <is>
-          <t>Volticons</t>
+          <t>Natus Vincere</t>
         </is>
       </c>
       <c r="AV25" s="24" t="n"/>
@@ -8045,7 +8147,7 @@
       </c>
       <c r="BA25" s="24" t="inlineStr">
         <is>
-          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
+          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
         </is>
       </c>
       <c r="BB25" s="24" t="inlineStr">
@@ -8060,7 +8162,7 @@
       </c>
       <c r="BD25" s="24" t="inlineStr">
         <is>
-          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
+          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
         </is>
       </c>
       <c r="BE25" s="24" t="inlineStr">
@@ -8080,7 +8182,7 @@
       </c>
       <c r="BH25" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:59:34.514458Z</t>
+          <t>2026-08-02T13:07:24.702936Z</t>
         </is>
       </c>
       <c r="BI25" s="24" t="inlineStr">
@@ -8090,13 +8192,13 @@
       </c>
       <c r="BJ25" s="25" t="n"/>
       <c r="BK25" s="26" t="n">
-        <v>-144</v>
+        <v>-233</v>
       </c>
       <c r="BL25" s="27" t="n">
-        <v>1.694444</v>
+        <v>1.429185</v>
       </c>
       <c r="BM25" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.6997</v>
       </c>
       <c r="BN25" s="28" t="n"/>
       <c r="BO25" s="28" t="n"/>
@@ -8126,26 +8228,27 @@
       <c r="CM25" s="24" t="n"/>
       <c r="CN25" s="24" t="n"/>
       <c r="CO25" s="24" t="n"/>
+      <c r="CP25" s="24" t="n"/>
     </row>
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="24" t="inlineStr">
         <is>
-          <t>8493ae69b0ec40f5</t>
+          <t>99c874f0d80d4a9c</t>
         </is>
       </c>
       <c r="B26" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:59:37.296167Z</t>
+          <t>2026-08-02T13:07:30.652675Z</t>
         </is>
       </c>
       <c r="C26" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T22:00:00Z</t>
+          <t>2026-08-03T20:00:00Z</t>
         </is>
       </c>
       <c r="D26" s="24" t="inlineStr">
         <is>
-          <t>68011</t>
+          <t>67937</t>
         </is>
       </c>
       <c r="E26" s="24" t="inlineStr">
@@ -8155,12 +8258,12 @@
       </c>
       <c r="F26" s="24" t="inlineStr">
         <is>
-          <t>Vivo Keyd Stars Academy</t>
+          <t>Docta Esports</t>
         </is>
       </c>
       <c r="G26" s="24" t="inlineStr">
         <is>
-          <t>paiN Gaming Academy</t>
+          <t>Volticons</t>
         </is>
       </c>
       <c r="H26" s="24" t="inlineStr">
@@ -8170,7 +8273,7 @@
       </c>
       <c r="I26" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J26" s="25" t="n"/>
@@ -8180,26 +8283,26 @@
         </is>
       </c>
       <c r="L26" s="26" t="n">
-        <v>-127</v>
+        <v>-144</v>
       </c>
       <c r="M26" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.694444</v>
       </c>
       <c r="N26" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.590164</v>
       </c>
       <c r="O26" s="28" t="n">
-        <v>0.501894</v>
+        <v>0.650601</v>
       </c>
       <c r="P26" s="28" t="n"/>
       <c r="Q26" s="28" t="n">
-        <v>-0.057577</v>
+        <v>0.060437</v>
       </c>
       <c r="R26" s="26" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="S26" s="29" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="T26" s="24" t="inlineStr">
         <is>
@@ -8222,7 +8325,7 @@
       <c r="AD26" s="24" t="n"/>
       <c r="AE26" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-lol-pnga-vksa-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-lol-vtc-doh-2026-08-03).</t>
         </is>
       </c>
       <c r="AF26" s="31" t="inlineStr">
@@ -8240,7 +8343,7 @@
       <c r="AJ26" s="31" t="n"/>
       <c r="AK26" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL26" s="26" t="n">
@@ -8248,47 +8351,47 @@
       </c>
       <c r="AM26" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN26" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO26" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP26" s="24" t="inlineStr">
         <is>
-          <t>Vivo Keyd Stars Academy</t>
+          <t>Docta Esports</t>
         </is>
       </c>
       <c r="AQ26" s="24" t="inlineStr">
         <is>
-          <t>Vivo Keyd Stars Academy</t>
+          <t>Docta Esports</t>
         </is>
       </c>
       <c r="AR26" s="24" t="inlineStr">
         <is>
-          <t>Vivo Keyd Stars Academy</t>
+          <t>Docta Esports</t>
         </is>
       </c>
       <c r="AS26" s="24" t="inlineStr">
         <is>
-          <t>paiN Gaming Academy</t>
+          <t>Volticons</t>
         </is>
       </c>
       <c r="AT26" s="24" t="inlineStr">
         <is>
-          <t>paiN Gaming Academy</t>
+          <t>Volticons</t>
         </is>
       </c>
       <c r="AU26" s="24" t="inlineStr">
         <is>
-          <t>paiN Gaming Academy</t>
+          <t>Volticons</t>
         </is>
       </c>
       <c r="AV26" s="24" t="n"/>
@@ -8306,7 +8409,7 @@
       </c>
       <c r="BA26" s="24" t="inlineStr">
         <is>
-          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
+          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
         </is>
       </c>
       <c r="BB26" s="24" t="inlineStr">
@@ -8321,7 +8424,7 @@
       </c>
       <c r="BD26" s="24" t="inlineStr">
         <is>
-          <t>872990f5864d469e34c183f4364739fd3897540762b962f4ec2e55405665b2e8</t>
+          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
         </is>
       </c>
       <c r="BE26" s="24" t="inlineStr">
@@ -8341,7 +8444,7 @@
       </c>
       <c r="BH26" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:59:36.264347Z</t>
+          <t>2026-08-02T13:07:28.257607Z</t>
         </is>
       </c>
       <c r="BI26" s="24" t="inlineStr">
@@ -8351,13 +8454,13 @@
       </c>
       <c r="BJ26" s="25" t="n"/>
       <c r="BK26" s="26" t="n">
-        <v>-127</v>
+        <v>-144</v>
       </c>
       <c r="BL26" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.694444</v>
       </c>
       <c r="BM26" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.590164</v>
       </c>
       <c r="BN26" s="28" t="n"/>
       <c r="BO26" s="28" t="n"/>
@@ -8387,6 +8490,269 @@
       <c r="CM26" s="24" t="n"/>
       <c r="CN26" s="24" t="n"/>
       <c r="CO26" s="24" t="n"/>
+      <c r="CP26" s="24" t="n"/>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>b766e9fe9f404c40</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T13:07:30.652675Z</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="D27" s="24" t="inlineStr">
+        <is>
+          <t>68011</t>
+        </is>
+      </c>
+      <c r="E27" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F27" s="24" t="inlineStr">
+        <is>
+          <t>Vivo Keyd Stars Academy</t>
+        </is>
+      </c>
+      <c r="G27" s="24" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="H27" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I27" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J27" s="25" t="n"/>
+      <c r="K27" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L27" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="M27" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="N27" s="28" t="n">
+        <v>0.539171</v>
+      </c>
+      <c r="O27" s="28" t="n">
+        <v>0.501386</v>
+      </c>
+      <c r="P27" s="28" t="n"/>
+      <c r="Q27" s="28" t="n">
+        <v>-0.037785</v>
+      </c>
+      <c r="R27" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="S27" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U27" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V27" s="24" t="n"/>
+      <c r="W27" s="26" t="n"/>
+      <c r="X27" s="26" t="n"/>
+      <c r="Y27" s="25" t="n"/>
+      <c r="Z27" s="26" t="n"/>
+      <c r="AA27" s="28" t="n"/>
+      <c r="AB27" s="28" t="n"/>
+      <c r="AC27" s="30" t="n"/>
+      <c r="AD27" s="24" t="n"/>
+      <c r="AE27" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-lol-pnga-vksa-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF27" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG27" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH27" s="24" t="n"/>
+      <c r="AI27" s="31" t="n"/>
+      <c r="AJ27" s="31" t="n"/>
+      <c r="AK27" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL27" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM27" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN27" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO27" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP27" s="24" t="inlineStr">
+        <is>
+          <t>Vivo Keyd Stars Academy</t>
+        </is>
+      </c>
+      <c r="AQ27" s="24" t="inlineStr">
+        <is>
+          <t>Vivo Keyd Stars Academy</t>
+        </is>
+      </c>
+      <c r="AR27" s="24" t="inlineStr">
+        <is>
+          <t>Vivo Keyd Stars Academy</t>
+        </is>
+      </c>
+      <c r="AS27" s="24" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="AT27" s="24" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="AU27" s="24" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="AV27" s="24" t="n"/>
+      <c r="AW27" s="24" t="n"/>
+      <c r="AX27" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY27" s="24" t="n"/>
+      <c r="AZ27" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA27" s="24" t="inlineStr">
+        <is>
+          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
+        </is>
+      </c>
+      <c r="BB27" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC27" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD27" s="24" t="inlineStr">
+        <is>
+          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
+        </is>
+      </c>
+      <c r="BE27" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF27" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG27" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T13:07:29.695648Z</t>
+        </is>
+      </c>
+      <c r="BI27" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ27" s="25" t="n"/>
+      <c r="BK27" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="BL27" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="BM27" s="28" t="n">
+        <v>0.539171</v>
+      </c>
+      <c r="BN27" s="28" t="n"/>
+      <c r="BO27" s="28" t="n"/>
+      <c r="BP27" s="25" t="n"/>
+      <c r="BQ27" s="27" t="n"/>
+      <c r="BR27" s="28" t="n"/>
+      <c r="BS27" s="28" t="n"/>
+      <c r="BT27" s="28" t="n"/>
+      <c r="BU27" s="25" t="n"/>
+      <c r="BV27" s="29" t="n"/>
+      <c r="BW27" s="24" t="n"/>
+      <c r="BX27" s="30" t="n"/>
+      <c r="BY27" s="27" t="n"/>
+      <c r="BZ27" s="24" t="n"/>
+      <c r="CA27" s="31" t="n"/>
+      <c r="CB27" s="24" t="n"/>
+      <c r="CC27" s="24" t="n"/>
+      <c r="CD27" s="24" t="n"/>
+      <c r="CE27" s="24" t="n"/>
+      <c r="CF27" s="24" t="n"/>
+      <c r="CG27" s="24" t="n"/>
+      <c r="CH27" s="24" t="n"/>
+      <c r="CI27" s="24" t="n"/>
+      <c r="CJ27" s="24" t="n"/>
+      <c r="CK27" s="24" t="n"/>
+      <c r="CL27" s="24" t="n"/>
+      <c r="CM27" s="24" t="n"/>
+      <c r="CN27" s="24" t="n"/>
+      <c r="CO27" s="24" t="n"/>
+      <c r="CP27" s="24" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/research/lol.xlsx
+++ b/data/research/lol.xlsx
@@ -5667,18 +5667,38 @@
       </c>
       <c r="U16" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V16" s="24" t="n"/>
-      <c r="W16" s="26" t="n"/>
-      <c r="X16" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V16" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W16" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y16" s="25" t="n"/>
-      <c r="Z16" s="26" t="n"/>
-      <c r="AA16" s="28" t="n"/>
-      <c r="AB16" s="28" t="n"/>
-      <c r="AC16" s="30" t="n"/>
-      <c r="AD16" s="24" t="n"/>
+      <c r="Z16" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="AA16" s="28" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AB16" s="28" t="n">
+        <v>0.000829</v>
+      </c>
+      <c r="AC16" s="30" t="n">
+        <v>0.8547</v>
+      </c>
+      <c r="AD16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:53:03.900779Z</t>
+        </is>
+      </c>
       <c r="AE16" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-lol-tes-jdg-2026-08-02).</t>
@@ -5821,8 +5841,12 @@
       <c r="BN16" s="28" t="n"/>
       <c r="BO16" s="28" t="n"/>
       <c r="BP16" s="25" t="n"/>
-      <c r="BQ16" s="27" t="n"/>
-      <c r="BR16" s="28" t="n"/>
+      <c r="BQ16" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="BR16" s="28" t="n">
+        <v>0.54</v>
+      </c>
       <c r="BS16" s="28" t="n"/>
       <c r="BT16" s="28" t="n"/>
       <c r="BU16" s="25" t="n"/>
@@ -6215,18 +6239,38 @@
       </c>
       <c r="U18" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V18" s="24" t="n"/>
-      <c r="W18" s="26" t="n"/>
-      <c r="X18" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V18" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W18" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X18" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y18" s="25" t="n"/>
-      <c r="Z18" s="26" t="n"/>
-      <c r="AA18" s="28" t="n"/>
-      <c r="AB18" s="28" t="n"/>
-      <c r="AC18" s="30" t="n"/>
-      <c r="AD18" s="24" t="n"/>
+      <c r="Z18" s="26" t="n">
+        <v>186</v>
+      </c>
+      <c r="AA18" s="28" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AB18" s="28" t="n">
+        <v>0.00035</v>
+      </c>
+      <c r="AC18" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD18" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:53:05.143124Z</t>
+        </is>
+      </c>
       <c r="AE18" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.3500 (market_slug=aec-lol-zpr-cla-2026-08-02).</t>
@@ -6239,7 +6283,7 @@
       </c>
       <c r="AG18" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH18" s="24" t="n"/>
@@ -6369,8 +6413,12 @@
       <c r="BN18" s="28" t="n"/>
       <c r="BO18" s="28" t="n"/>
       <c r="BP18" s="25" t="n"/>
-      <c r="BQ18" s="27" t="n"/>
-      <c r="BR18" s="28" t="n"/>
+      <c r="BQ18" s="27" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BR18" s="28" t="n">
+        <v>0.35</v>
+      </c>
       <c r="BS18" s="28" t="n"/>
       <c r="BT18" s="28" t="n"/>
       <c r="BU18" s="25" t="n"/>
@@ -6399,12 +6447,12 @@
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="24" t="inlineStr">
         <is>
-          <t>b1cb64fc389043e7</t>
+          <t>3afbf086a69f4a1f</t>
         </is>
       </c>
       <c r="B19" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:30.652675Z</t>
+          <t>2026-08-02T15:51:19.985321Z</t>
         </is>
       </c>
       <c r="C19" s="24" t="inlineStr">
@@ -6449,23 +6497,23 @@
         </is>
       </c>
       <c r="L19" s="26" t="n">
-        <v>-122</v>
+        <v>-117</v>
       </c>
       <c r="M19" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.854701</v>
       </c>
       <c r="N19" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.539171</v>
       </c>
       <c r="O19" s="28" t="n">
-        <v>0.5584440000000001</v>
+        <v>0.558818</v>
       </c>
       <c r="P19" s="28" t="n"/>
       <c r="Q19" s="28" t="n">
-        <v>0.008894000000000001</v>
+        <v>0.019647</v>
       </c>
       <c r="R19" s="26" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="S19" s="29" t="n">
         <v>1</v>
@@ -6491,7 +6539,7 @@
       <c r="AD19" s="24" t="n"/>
       <c r="AE19" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-lol-fxw7-lll-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-lol-fxw7-lll-2026-08-02).</t>
         </is>
       </c>
       <c r="AF19" s="31" t="inlineStr">
@@ -6575,7 +6623,7 @@
       </c>
       <c r="BA19" s="24" t="inlineStr">
         <is>
-          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
+          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
         </is>
       </c>
       <c r="BB19" s="24" t="inlineStr">
@@ -6590,7 +6638,7 @@
       </c>
       <c r="BD19" s="24" t="inlineStr">
         <is>
-          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
+          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
         </is>
       </c>
       <c r="BE19" s="24" t="inlineStr">
@@ -6610,7 +6658,7 @@
       </c>
       <c r="BH19" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:19.930355Z</t>
+          <t>2026-08-02T15:51:09.199778Z</t>
         </is>
       </c>
       <c r="BI19" s="24" t="inlineStr">
@@ -6620,13 +6668,13 @@
       </c>
       <c r="BJ19" s="25" t="n"/>
       <c r="BK19" s="26" t="n">
-        <v>-122</v>
+        <v>-117</v>
       </c>
       <c r="BL19" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.854701</v>
       </c>
       <c r="BM19" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.539171</v>
       </c>
       <c r="BN19" s="28" t="n"/>
       <c r="BO19" s="28" t="n"/>
@@ -6656,17 +6704,21 @@
       <c r="CM19" s="24" t="n"/>
       <c r="CN19" s="24" t="n"/>
       <c r="CO19" s="24" t="n"/>
-      <c r="CP19" s="24" t="n"/>
+      <c r="CP19" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="24" t="inlineStr">
         <is>
-          <t>0c6b04aa59674149</t>
+          <t>bc54b79b21264c05</t>
         </is>
       </c>
       <c r="B20" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:30.652675Z</t>
+          <t>2026-08-02T15:51:19.985321Z</t>
         </is>
       </c>
       <c r="C20" s="24" t="inlineStr">
@@ -6720,11 +6772,11 @@
         <v>0.659864</v>
       </c>
       <c r="O20" s="28" t="n">
-        <v>0.592477</v>
+        <v>0.592731</v>
       </c>
       <c r="P20" s="28" t="n"/>
       <c r="Q20" s="28" t="n">
-        <v>-0.067387</v>
+        <v>-0.067133</v>
       </c>
       <c r="R20" s="26" t="n">
         <v>0</v>
@@ -6837,7 +6889,7 @@
       </c>
       <c r="BA20" s="24" t="inlineStr">
         <is>
-          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
+          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
         </is>
       </c>
       <c r="BB20" s="24" t="inlineStr">
@@ -6852,7 +6904,7 @@
       </c>
       <c r="BD20" s="24" t="inlineStr">
         <is>
-          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
+          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
         </is>
       </c>
       <c r="BE20" s="24" t="inlineStr">
@@ -6872,7 +6924,7 @@
       </c>
       <c r="BH20" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:20.483371Z</t>
+          <t>2026-08-02T15:51:09.700659Z</t>
         </is>
       </c>
       <c r="BI20" s="24" t="inlineStr">
@@ -6918,17 +6970,21 @@
       <c r="CM20" s="24" t="n"/>
       <c r="CN20" s="24" t="n"/>
       <c r="CO20" s="24" t="n"/>
-      <c r="CP20" s="24" t="n"/>
+      <c r="CP20" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="24" t="inlineStr">
         <is>
-          <t>42ce1bbba99e4389</t>
+          <t>dae0495990e943f3</t>
         </is>
       </c>
       <c r="B21" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:30.652675Z</t>
+          <t>2026-08-02T15:51:19.985321Z</t>
         </is>
       </c>
       <c r="C21" s="24" t="inlineStr">
@@ -6938,7 +6994,7 @@
       </c>
       <c r="D21" s="24" t="inlineStr">
         <is>
-          <t>67491</t>
+          <t>67492</t>
         </is>
       </c>
       <c r="E21" s="24" t="inlineStr">
@@ -6948,12 +7004,12 @@
       </c>
       <c r="F21" s="24" t="inlineStr">
         <is>
-          <t>Hanwha Life Esports</t>
+          <t>BNK FearX Youth</t>
         </is>
       </c>
       <c r="G21" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>HANJIN BRION Challengers</t>
         </is>
       </c>
       <c r="H21" s="24" t="inlineStr">
@@ -6973,26 +7029,26 @@
         </is>
       </c>
       <c r="L21" s="26" t="n">
-        <v>-133</v>
+        <v>-223</v>
       </c>
       <c r="M21" s="27" t="n">
-        <v>1.75188</v>
+        <v>1.44843</v>
       </c>
       <c r="N21" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.690402</v>
       </c>
       <c r="O21" s="28" t="n">
-        <v>0.58052</v>
+        <v>0.634473</v>
       </c>
       <c r="P21" s="28" t="n"/>
       <c r="Q21" s="28" t="n">
-        <v>0.009705</v>
+        <v>-0.055929</v>
       </c>
       <c r="R21" s="26" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="S21" s="29" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="T21" s="24" t="inlineStr">
         <is>
@@ -7015,7 +7071,7 @@
       <c r="AD21" s="24" t="n"/>
       <c r="AE21" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-lol-gen-hle-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-lol-hbc-foxy-2026-08-03).</t>
         </is>
       </c>
       <c r="AF21" s="31" t="inlineStr">
@@ -7033,7 +7089,7 @@
       <c r="AJ21" s="31" t="n"/>
       <c r="AK21" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL21" s="26" t="n">
@@ -7041,47 +7097,47 @@
       </c>
       <c r="AM21" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN21" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO21" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP21" s="24" t="inlineStr">
         <is>
-          <t>Hanwha Life Esports</t>
+          <t>BNK FearX Youth</t>
         </is>
       </c>
       <c r="AQ21" s="24" t="inlineStr">
         <is>
-          <t>Hanwha Life Esports</t>
+          <t>BNK FearX Youth</t>
         </is>
       </c>
       <c r="AR21" s="24" t="inlineStr">
         <is>
-          <t>Hanwha Life Esports</t>
+          <t>BNK FearX Youth</t>
         </is>
       </c>
       <c r="AS21" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>HANJIN BRION Challengers</t>
         </is>
       </c>
       <c r="AT21" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>HANJIN BRION Challengers</t>
         </is>
       </c>
       <c r="AU21" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>HANJIN BRION Challengers</t>
         </is>
       </c>
       <c r="AV21" s="24" t="n"/>
@@ -7099,7 +7155,7 @@
       </c>
       <c r="BA21" s="24" t="inlineStr">
         <is>
-          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
+          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
         </is>
       </c>
       <c r="BB21" s="24" t="inlineStr">
@@ -7114,7 +7170,7 @@
       </c>
       <c r="BD21" s="24" t="inlineStr">
         <is>
-          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
+          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
         </is>
       </c>
       <c r="BE21" s="24" t="inlineStr">
@@ -7134,7 +7190,7 @@
       </c>
       <c r="BH21" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:22.606056Z</t>
+          <t>2026-08-02T15:51:11.750256Z</t>
         </is>
       </c>
       <c r="BI21" s="24" t="inlineStr">
@@ -7144,13 +7200,13 @@
       </c>
       <c r="BJ21" s="25" t="n"/>
       <c r="BK21" s="26" t="n">
-        <v>-133</v>
+        <v>-223</v>
       </c>
       <c r="BL21" s="27" t="n">
-        <v>1.75188</v>
+        <v>1.44843</v>
       </c>
       <c r="BM21" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.690402</v>
       </c>
       <c r="BN21" s="28" t="n"/>
       <c r="BO21" s="28" t="n"/>
@@ -7180,17 +7236,21 @@
       <c r="CM21" s="24" t="n"/>
       <c r="CN21" s="24" t="n"/>
       <c r="CO21" s="24" t="n"/>
-      <c r="CP21" s="24" t="n"/>
+      <c r="CP21" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="24" t="inlineStr">
         <is>
-          <t>02458941fd3f4362</t>
+          <t>c3c74c8064844b1e</t>
         </is>
       </c>
       <c r="B22" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:30.652675Z</t>
+          <t>2026-08-02T15:51:19.985321Z</t>
         </is>
       </c>
       <c r="C22" s="24" t="inlineStr">
@@ -7200,7 +7260,7 @@
       </c>
       <c r="D22" s="24" t="inlineStr">
         <is>
-          <t>67492</t>
+          <t>67491</t>
         </is>
       </c>
       <c r="E22" s="24" t="inlineStr">
@@ -7210,12 +7270,12 @@
       </c>
       <c r="F22" s="24" t="inlineStr">
         <is>
-          <t>BNK FearX Youth</t>
+          <t>Hanwha Life Esports</t>
         </is>
       </c>
       <c r="G22" s="24" t="inlineStr">
         <is>
-          <t>HANJIN BRION Challengers</t>
+          <t>Gen.G</t>
         </is>
       </c>
       <c r="H22" s="24" t="inlineStr">
@@ -7235,26 +7295,26 @@
         </is>
       </c>
       <c r="L22" s="26" t="n">
-        <v>-213</v>
+        <v>-144</v>
       </c>
       <c r="M22" s="27" t="n">
-        <v>1.469484</v>
+        <v>1.694444</v>
       </c>
       <c r="N22" s="28" t="n">
-        <v>0.680511</v>
+        <v>0.590164</v>
       </c>
       <c r="O22" s="28" t="n">
-        <v>0.63434</v>
+        <v>0.53577</v>
       </c>
       <c r="P22" s="28" t="n"/>
       <c r="Q22" s="28" t="n">
-        <v>-0.046171</v>
+        <v>-0.054394</v>
       </c>
       <c r="R22" s="26" t="n">
         <v>0</v>
       </c>
       <c r="S22" s="29" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="T22" s="24" t="inlineStr">
         <is>
@@ -7277,7 +7337,7 @@
       <c r="AD22" s="24" t="n"/>
       <c r="AE22" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-lol-hbc-foxy-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-lol-gen-hle-2026-08-03).</t>
         </is>
       </c>
       <c r="AF22" s="31" t="inlineStr">
@@ -7318,32 +7378,32 @@
       </c>
       <c r="AP22" s="24" t="inlineStr">
         <is>
-          <t>BNK FearX Youth</t>
+          <t>Hanwha Life Esports</t>
         </is>
       </c>
       <c r="AQ22" s="24" t="inlineStr">
         <is>
-          <t>BNK FearX Youth</t>
+          <t>Hanwha Life Esports</t>
         </is>
       </c>
       <c r="AR22" s="24" t="inlineStr">
         <is>
-          <t>BNK FearX Youth</t>
+          <t>Hanwha Life Esports</t>
         </is>
       </c>
       <c r="AS22" s="24" t="inlineStr">
         <is>
-          <t>HANJIN BRION Challengers</t>
+          <t>Gen.G</t>
         </is>
       </c>
       <c r="AT22" s="24" t="inlineStr">
         <is>
-          <t>HANJIN BRION Challengers</t>
+          <t>Gen.G</t>
         </is>
       </c>
       <c r="AU22" s="24" t="inlineStr">
         <is>
-          <t>HANJIN BRION Challengers</t>
+          <t>Gen.G</t>
         </is>
       </c>
       <c r="AV22" s="24" t="n"/>
@@ -7361,7 +7421,7 @@
       </c>
       <c r="BA22" s="24" t="inlineStr">
         <is>
-          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
+          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
         </is>
       </c>
       <c r="BB22" s="24" t="inlineStr">
@@ -7376,7 +7436,7 @@
       </c>
       <c r="BD22" s="24" t="inlineStr">
         <is>
-          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
+          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
         </is>
       </c>
       <c r="BE22" s="24" t="inlineStr">
@@ -7396,7 +7456,7 @@
       </c>
       <c r="BH22" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:23.091424Z</t>
+          <t>2026-08-02T15:51:12.301759Z</t>
         </is>
       </c>
       <c r="BI22" s="24" t="inlineStr">
@@ -7406,13 +7466,13 @@
       </c>
       <c r="BJ22" s="25" t="n"/>
       <c r="BK22" s="26" t="n">
-        <v>-213</v>
+        <v>-144</v>
       </c>
       <c r="BL22" s="27" t="n">
-        <v>1.469484</v>
+        <v>1.694444</v>
       </c>
       <c r="BM22" s="28" t="n">
-        <v>0.680511</v>
+        <v>0.590164</v>
       </c>
       <c r="BN22" s="28" t="n"/>
       <c r="BO22" s="28" t="n"/>
@@ -7442,17 +7502,21 @@
       <c r="CM22" s="24" t="n"/>
       <c r="CN22" s="24" t="n"/>
       <c r="CO22" s="24" t="n"/>
-      <c r="CP22" s="24" t="n"/>
+      <c r="CP22" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="24" t="inlineStr">
         <is>
-          <t>5c5778fbf88d4bad</t>
+          <t>1f67cd97fc1f4d6c</t>
         </is>
       </c>
       <c r="B23" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:30.652675Z</t>
+          <t>2026-08-02T15:51:19.985321Z</t>
         </is>
       </c>
       <c r="C23" s="24" t="inlineStr">
@@ -7506,11 +7570,11 @@
         <v>0.690402</v>
       </c>
       <c r="O23" s="28" t="n">
-        <v>0.703234</v>
+        <v>0.703159</v>
       </c>
       <c r="P23" s="28" t="n"/>
       <c r="Q23" s="28" t="n">
-        <v>0.012832</v>
+        <v>0.012757</v>
       </c>
       <c r="R23" s="26" t="n">
         <v>26</v>
@@ -7623,7 +7687,7 @@
       </c>
       <c r="BA23" s="24" t="inlineStr">
         <is>
-          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
+          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
         </is>
       </c>
       <c r="BB23" s="24" t="inlineStr">
@@ -7638,7 +7702,7 @@
       </c>
       <c r="BD23" s="24" t="inlineStr">
         <is>
-          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
+          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
         </is>
       </c>
       <c r="BE23" s="24" t="inlineStr">
@@ -7658,7 +7722,7 @@
       </c>
       <c r="BH23" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:23.605808Z</t>
+          <t>2026-08-02T15:51:12.813283Z</t>
         </is>
       </c>
       <c r="BI23" s="24" t="inlineStr">
@@ -7704,17 +7768,21 @@
       <c r="CM23" s="24" t="n"/>
       <c r="CN23" s="24" t="n"/>
       <c r="CO23" s="24" t="n"/>
-      <c r="CP23" s="24" t="n"/>
+      <c r="CP23" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="24" t="inlineStr">
         <is>
-          <t>1531b3ab80db4f56</t>
+          <t>48c53315f7064d79</t>
         </is>
       </c>
       <c r="B24" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:30.652675Z</t>
+          <t>2026-08-02T15:51:19.985321Z</t>
         </is>
       </c>
       <c r="C24" s="24" t="inlineStr">
@@ -7759,23 +7827,23 @@
         </is>
       </c>
       <c r="L24" s="26" t="n">
-        <v>-170</v>
+        <v>-163</v>
       </c>
       <c r="M24" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.613497</v>
       </c>
       <c r="N24" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.619772</v>
       </c>
       <c r="O24" s="28" t="n">
-        <v>0.746484</v>
+        <v>0.746312</v>
       </c>
       <c r="P24" s="28" t="n"/>
       <c r="Q24" s="28" t="n">
-        <v>0.116854</v>
+        <v>0.12654</v>
       </c>
       <c r="R24" s="26" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="S24" s="29" t="n">
         <v>2</v>
@@ -7801,7 +7869,7 @@
       <c r="AD24" s="24" t="n"/>
       <c r="AE24" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-lol-ns-t1-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-lol-ns-t1-2026-08-03).</t>
         </is>
       </c>
       <c r="AF24" s="31" t="inlineStr">
@@ -7885,7 +7953,7 @@
       </c>
       <c r="BA24" s="24" t="inlineStr">
         <is>
-          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
+          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
         </is>
       </c>
       <c r="BB24" s="24" t="inlineStr">
@@ -7900,7 +7968,7 @@
       </c>
       <c r="BD24" s="24" t="inlineStr">
         <is>
-          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
+          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
         </is>
       </c>
       <c r="BE24" s="24" t="inlineStr">
@@ -7920,7 +7988,7 @@
       </c>
       <c r="BH24" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:24.188851Z</t>
+          <t>2026-08-02T15:51:13.406755Z</t>
         </is>
       </c>
       <c r="BI24" s="24" t="inlineStr">
@@ -7930,13 +7998,13 @@
       </c>
       <c r="BJ24" s="25" t="n"/>
       <c r="BK24" s="26" t="n">
-        <v>-170</v>
+        <v>-163</v>
       </c>
       <c r="BL24" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.613497</v>
       </c>
       <c r="BM24" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.619772</v>
       </c>
       <c r="BN24" s="28" t="n"/>
       <c r="BO24" s="28" t="n"/>
@@ -7966,17 +8034,21 @@
       <c r="CM24" s="24" t="n"/>
       <c r="CN24" s="24" t="n"/>
       <c r="CO24" s="24" t="n"/>
-      <c r="CP24" s="24" t="n"/>
+      <c r="CP24" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="24" t="inlineStr">
         <is>
-          <t>dc68b9a8665d44ee</t>
+          <t>8dccf8d14155413d</t>
         </is>
       </c>
       <c r="B25" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:30.652675Z</t>
+          <t>2026-08-02T15:51:19.985321Z</t>
         </is>
       </c>
       <c r="C25" s="24" t="inlineStr">
@@ -8030,14 +8102,14 @@
         <v>0.6997</v>
       </c>
       <c r="O25" s="28" t="n">
-        <v>0.74769</v>
+        <v>0.74664</v>
       </c>
       <c r="P25" s="28" t="n"/>
       <c r="Q25" s="28" t="n">
-        <v>0.04799</v>
+        <v>0.04694</v>
       </c>
       <c r="R25" s="26" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="S25" s="29" t="n">
         <v>2</v>
@@ -8147,7 +8219,7 @@
       </c>
       <c r="BA25" s="24" t="inlineStr">
         <is>
-          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
+          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
         </is>
       </c>
       <c r="BB25" s="24" t="inlineStr">
@@ -8162,7 +8234,7 @@
       </c>
       <c r="BD25" s="24" t="inlineStr">
         <is>
-          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
+          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
         </is>
       </c>
       <c r="BE25" s="24" t="inlineStr">
@@ -8182,7 +8254,7 @@
       </c>
       <c r="BH25" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:24.702936Z</t>
+          <t>2026-08-02T15:51:13.923521Z</t>
         </is>
       </c>
       <c r="BI25" s="24" t="inlineStr">
@@ -8228,17 +8300,21 @@
       <c r="CM25" s="24" t="n"/>
       <c r="CN25" s="24" t="n"/>
       <c r="CO25" s="24" t="n"/>
-      <c r="CP25" s="24" t="n"/>
+      <c r="CP25" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="24" t="inlineStr">
         <is>
-          <t>99c874f0d80d4a9c</t>
+          <t>754060c98b474189</t>
         </is>
       </c>
       <c r="B26" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:30.652675Z</t>
+          <t>2026-08-02T15:51:19.985321Z</t>
         </is>
       </c>
       <c r="C26" s="24" t="inlineStr">
@@ -8292,11 +8368,11 @@
         <v>0.590164</v>
       </c>
       <c r="O26" s="28" t="n">
-        <v>0.650601</v>
+        <v>0.649674</v>
       </c>
       <c r="P26" s="28" t="n"/>
       <c r="Q26" s="28" t="n">
-        <v>0.060437</v>
+        <v>0.05951</v>
       </c>
       <c r="R26" s="26" t="n">
         <v>50</v>
@@ -8409,7 +8485,7 @@
       </c>
       <c r="BA26" s="24" t="inlineStr">
         <is>
-          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
+          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
         </is>
       </c>
       <c r="BB26" s="24" t="inlineStr">
@@ -8424,7 +8500,7 @@
       </c>
       <c r="BD26" s="24" t="inlineStr">
         <is>
-          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
+          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
         </is>
       </c>
       <c r="BE26" s="24" t="inlineStr">
@@ -8444,7 +8520,7 @@
       </c>
       <c r="BH26" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:28.257607Z</t>
+          <t>2026-08-02T15:51:17.539022Z</t>
         </is>
       </c>
       <c r="BI26" s="24" t="inlineStr">
@@ -8490,17 +8566,21 @@
       <c r="CM26" s="24" t="n"/>
       <c r="CN26" s="24" t="n"/>
       <c r="CO26" s="24" t="n"/>
-      <c r="CP26" s="24" t="n"/>
+      <c r="CP26" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="24" t="inlineStr">
         <is>
-          <t>b766e9fe9f404c40</t>
+          <t>b6d34c8bb890474f</t>
         </is>
       </c>
       <c r="B27" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:30.652675Z</t>
+          <t>2026-08-02T15:51:19.985321Z</t>
         </is>
       </c>
       <c r="C27" s="24" t="inlineStr">
@@ -8545,23 +8625,23 @@
         </is>
       </c>
       <c r="L27" s="26" t="n">
-        <v>-117</v>
+        <v>-127</v>
       </c>
       <c r="M27" s="27" t="n">
-        <v>1.854701</v>
+        <v>1.787402</v>
       </c>
       <c r="N27" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="O27" s="28" t="n">
-        <v>0.501386</v>
+        <v>0.501936</v>
       </c>
       <c r="P27" s="28" t="n"/>
       <c r="Q27" s="28" t="n">
-        <v>-0.037785</v>
+        <v>-0.057535</v>
       </c>
       <c r="R27" s="26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" s="29" t="n">
         <v>1</v>
@@ -8587,7 +8667,7 @@
       <c r="AD27" s="24" t="n"/>
       <c r="AE27" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-lol-pnga-vksa-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-lol-pnga-vksa-2026-08-03).</t>
         </is>
       </c>
       <c r="AF27" s="31" t="inlineStr">
@@ -8671,7 +8751,7 @@
       </c>
       <c r="BA27" s="24" t="inlineStr">
         <is>
-          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
+          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
         </is>
       </c>
       <c r="BB27" s="24" t="inlineStr">
@@ -8686,7 +8766,7 @@
       </c>
       <c r="BD27" s="24" t="inlineStr">
         <is>
-          <t>20de1d712cda0a66426c95ed103aa2e610c5fbde0bd61721abf492218cad1cd2</t>
+          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
         </is>
       </c>
       <c r="BE27" s="24" t="inlineStr">
@@ -8706,7 +8786,7 @@
       </c>
       <c r="BH27" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:29.695648Z</t>
+          <t>2026-08-02T15:51:19.046288Z</t>
         </is>
       </c>
       <c r="BI27" s="24" t="inlineStr">
@@ -8716,13 +8796,13 @@
       </c>
       <c r="BJ27" s="25" t="n"/>
       <c r="BK27" s="26" t="n">
-        <v>-117</v>
+        <v>-127</v>
       </c>
       <c r="BL27" s="27" t="n">
-        <v>1.854701</v>
+        <v>1.787402</v>
       </c>
       <c r="BM27" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="BN27" s="28" t="n"/>
       <c r="BO27" s="28" t="n"/>
@@ -8752,7 +8832,11 @@
       <c r="CM27" s="24" t="n"/>
       <c r="CN27" s="24" t="n"/>
       <c r="CO27" s="24" t="n"/>
-      <c r="CP27" s="24" t="n"/>
+      <c r="CP27" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/research/lol.xlsx
+++ b/data/research/lol.xlsx
@@ -300,9 +300,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CP27" headerRowCount="1">
-  <autoFilter ref="A1:CP27"/>
-  <tableColumns count="94">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ27" headerRowCount="1">
+  <autoFilter ref="A1:CQ27"/>
+  <tableColumns count="95">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
     <tableColumn id="3" name="event_start_utc"/>
@@ -396,7 +396,8 @@
     <tableColumn id="91" name="back_to_back_gap"/>
     <tableColumn id="92" name="games_last_7_gap"/>
     <tableColumn id="93" name="schedule_missingness"/>
-    <tableColumn id="94" name="trade_candidate"/>
+    <tableColumn id="94" name="market_residual_probability"/>
+    <tableColumn id="95" name="trade_candidate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1011,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CP27"/>
+  <dimension ref="A1:CQ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1107,7 +1108,8 @@
     <col width="18" customWidth="1" min="91" max="91"/>
     <col width="18" customWidth="1" min="92" max="92"/>
     <col width="22" customWidth="1" min="93" max="93"/>
-    <col width="17" customWidth="1" min="94" max="94"/>
+    <col width="22" customWidth="1" min="94" max="94"/>
+    <col width="17" customWidth="1" min="95" max="95"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1577,6 +1579,11 @@
         </is>
       </c>
       <c r="CP1" s="23" t="inlineStr">
+        <is>
+          <t>market_residual_probability</t>
+        </is>
+      </c>
+      <c r="CQ1" s="23" t="inlineStr">
         <is>
           <t>trade_candidate</t>
         </is>
@@ -1867,6 +1874,7 @@
       <c r="CN2" s="24" t="n"/>
       <c r="CO2" s="24" t="n"/>
       <c r="CP2" s="24" t="n"/>
+      <c r="CQ2" s="24" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
@@ -2153,6 +2161,7 @@
       <c r="CN3" s="24" t="n"/>
       <c r="CO3" s="24" t="n"/>
       <c r="CP3" s="24" t="n"/>
+      <c r="CQ3" s="24" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
@@ -2439,6 +2448,7 @@
       <c r="CN4" s="24" t="n"/>
       <c r="CO4" s="24" t="n"/>
       <c r="CP4" s="24" t="n"/>
+      <c r="CQ4" s="24" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
@@ -2725,6 +2735,7 @@
       <c r="CN5" s="24" t="n"/>
       <c r="CO5" s="24" t="n"/>
       <c r="CP5" s="24" t="n"/>
+      <c r="CQ5" s="24" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
@@ -3011,6 +3022,7 @@
       <c r="CN6" s="24" t="n"/>
       <c r="CO6" s="24" t="n"/>
       <c r="CP6" s="24" t="n"/>
+      <c r="CQ6" s="24" t="n"/>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
@@ -3297,6 +3309,7 @@
       <c r="CN7" s="24" t="n"/>
       <c r="CO7" s="24" t="n"/>
       <c r="CP7" s="24" t="n"/>
+      <c r="CQ7" s="24" t="n"/>
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
@@ -3583,6 +3596,7 @@
       <c r="CN8" s="24" t="n"/>
       <c r="CO8" s="24" t="n"/>
       <c r="CP8" s="24" t="n"/>
+      <c r="CQ8" s="24" t="n"/>
     </row>
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
@@ -3869,6 +3883,7 @@
       <c r="CN9" s="24" t="n"/>
       <c r="CO9" s="24" t="n"/>
       <c r="CP9" s="24" t="n"/>
+      <c r="CQ9" s="24" t="n"/>
     </row>
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
@@ -4155,6 +4170,7 @@
       <c r="CN10" s="24" t="n"/>
       <c r="CO10" s="24" t="n"/>
       <c r="CP10" s="24" t="n"/>
+      <c r="CQ10" s="24" t="n"/>
     </row>
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
@@ -4441,6 +4457,7 @@
       <c r="CN11" s="24" t="n"/>
       <c r="CO11" s="24" t="n"/>
       <c r="CP11" s="24" t="n"/>
+      <c r="CQ11" s="24" t="n"/>
     </row>
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
@@ -4727,6 +4744,7 @@
       <c r="CN12" s="24" t="n"/>
       <c r="CO12" s="24" t="n"/>
       <c r="CP12" s="24" t="n"/>
+      <c r="CQ12" s="24" t="n"/>
     </row>
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
@@ -5013,6 +5031,7 @@
       <c r="CN13" s="24" t="n"/>
       <c r="CO13" s="24" t="n"/>
       <c r="CP13" s="24" t="n"/>
+      <c r="CQ13" s="24" t="n"/>
     </row>
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="24" t="inlineStr">
@@ -5299,6 +5318,7 @@
       <c r="CN14" s="24" t="n"/>
       <c r="CO14" s="24" t="n"/>
       <c r="CP14" s="24" t="n"/>
+      <c r="CQ14" s="24" t="n"/>
     </row>
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="24" t="inlineStr">
@@ -5585,6 +5605,7 @@
       <c r="CN15" s="24" t="n"/>
       <c r="CO15" s="24" t="n"/>
       <c r="CP15" s="24" t="n"/>
+      <c r="CQ15" s="24" t="n"/>
     </row>
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="24" t="inlineStr">
@@ -5871,6 +5892,7 @@
       <c r="CN16" s="24" t="n"/>
       <c r="CO16" s="24" t="n"/>
       <c r="CP16" s="24" t="n"/>
+      <c r="CQ16" s="24" t="n"/>
     </row>
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="24" t="inlineStr">
@@ -6157,6 +6179,7 @@
       <c r="CN17" s="24" t="n"/>
       <c r="CO17" s="24" t="n"/>
       <c r="CP17" s="24" t="n"/>
+      <c r="CQ17" s="24" t="n"/>
     </row>
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="24" t="inlineStr">
@@ -6443,6 +6466,7 @@
       <c r="CN18" s="24" t="n"/>
       <c r="CO18" s="24" t="n"/>
       <c r="CP18" s="24" t="n"/>
+      <c r="CQ18" s="24" t="n"/>
     </row>
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="24" t="inlineStr">
@@ -6704,7 +6728,8 @@
       <c r="CM19" s="24" t="n"/>
       <c r="CN19" s="24" t="n"/>
       <c r="CO19" s="24" t="n"/>
-      <c r="CP19" s="24" t="inlineStr">
+      <c r="CP19" s="24" t="n"/>
+      <c r="CQ19" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -6713,12 +6738,12 @@
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="24" t="inlineStr">
         <is>
-          <t>bc54b79b21264c05</t>
+          <t>a744d539d2b64aa6</t>
         </is>
       </c>
       <c r="B20" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:19.985321Z</t>
+          <t>2026-08-02T16:14:52.169624Z</t>
         </is>
       </c>
       <c r="C20" s="24" t="inlineStr">
@@ -6763,20 +6788,20 @@
         </is>
       </c>
       <c r="L20" s="26" t="n">
-        <v>-194</v>
+        <v>-186</v>
       </c>
       <c r="M20" s="27" t="n">
-        <v>1.515464</v>
+        <v>1.537634</v>
       </c>
       <c r="N20" s="28" t="n">
-        <v>0.659864</v>
+        <v>0.65035</v>
       </c>
       <c r="O20" s="28" t="n">
         <v>0.592731</v>
       </c>
       <c r="P20" s="28" t="n"/>
       <c r="Q20" s="28" t="n">
-        <v>-0.067133</v>
+        <v>-0.057619</v>
       </c>
       <c r="R20" s="26" t="n">
         <v>0</v>
@@ -6805,7 +6830,7 @@
       <c r="AD20" s="24" t="n"/>
       <c r="AE20" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6600 (market_slug=aec-lol-fnc-mkoi-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.6500 (market_slug=aec-lol-fnc-mkoi-2026-08-02).</t>
         </is>
       </c>
       <c r="AF20" s="31" t="inlineStr">
@@ -6889,7 +6914,7 @@
       </c>
       <c r="BA20" s="24" t="inlineStr">
         <is>
-          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
+          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
         </is>
       </c>
       <c r="BB20" s="24" t="inlineStr">
@@ -6904,7 +6929,7 @@
       </c>
       <c r="BD20" s="24" t="inlineStr">
         <is>
-          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
+          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
         </is>
       </c>
       <c r="BE20" s="24" t="inlineStr">
@@ -6924,7 +6949,7 @@
       </c>
       <c r="BH20" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:09.700659Z</t>
+          <t>2026-08-02T16:14:42.310322Z</t>
         </is>
       </c>
       <c r="BI20" s="24" t="inlineStr">
@@ -6934,13 +6959,13 @@
       </c>
       <c r="BJ20" s="25" t="n"/>
       <c r="BK20" s="26" t="n">
-        <v>-194</v>
+        <v>-186</v>
       </c>
       <c r="BL20" s="27" t="n">
-        <v>1.515464</v>
+        <v>1.537634</v>
       </c>
       <c r="BM20" s="28" t="n">
-        <v>0.659864</v>
+        <v>0.65035</v>
       </c>
       <c r="BN20" s="28" t="n"/>
       <c r="BO20" s="28" t="n"/>
@@ -6970,7 +6995,8 @@
       <c r="CM20" s="24" t="n"/>
       <c r="CN20" s="24" t="n"/>
       <c r="CO20" s="24" t="n"/>
-      <c r="CP20" s="24" t="inlineStr">
+      <c r="CP20" s="24" t="n"/>
+      <c r="CQ20" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -6979,12 +7005,12 @@
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="24" t="inlineStr">
         <is>
-          <t>dae0495990e943f3</t>
+          <t>07e88610202f4442</t>
         </is>
       </c>
       <c r="B21" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:19.985321Z</t>
+          <t>2026-08-02T16:14:52.169624Z</t>
         </is>
       </c>
       <c r="C21" s="24" t="inlineStr">
@@ -7155,7 +7181,7 @@
       </c>
       <c r="BA21" s="24" t="inlineStr">
         <is>
-          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
+          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
         </is>
       </c>
       <c r="BB21" s="24" t="inlineStr">
@@ -7170,7 +7196,7 @@
       </c>
       <c r="BD21" s="24" t="inlineStr">
         <is>
-          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
+          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
         </is>
       </c>
       <c r="BE21" s="24" t="inlineStr">
@@ -7190,7 +7216,7 @@
       </c>
       <c r="BH21" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:11.750256Z</t>
+          <t>2026-08-02T16:14:44.213769Z</t>
         </is>
       </c>
       <c r="BI21" s="24" t="inlineStr">
@@ -7236,7 +7262,8 @@
       <c r="CM21" s="24" t="n"/>
       <c r="CN21" s="24" t="n"/>
       <c r="CO21" s="24" t="n"/>
-      <c r="CP21" s="24" t="inlineStr">
+      <c r="CP21" s="24" t="n"/>
+      <c r="CQ21" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -7245,12 +7272,12 @@
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="24" t="inlineStr">
         <is>
-          <t>c3c74c8064844b1e</t>
+          <t>fc755a70629b4542</t>
         </is>
       </c>
       <c r="B22" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:19.985321Z</t>
+          <t>2026-08-02T16:14:52.169624Z</t>
         </is>
       </c>
       <c r="C22" s="24" t="inlineStr">
@@ -7421,7 +7448,7 @@
       </c>
       <c r="BA22" s="24" t="inlineStr">
         <is>
-          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
+          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
         </is>
       </c>
       <c r="BB22" s="24" t="inlineStr">
@@ -7436,7 +7463,7 @@
       </c>
       <c r="BD22" s="24" t="inlineStr">
         <is>
-          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
+          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
         </is>
       </c>
       <c r="BE22" s="24" t="inlineStr">
@@ -7456,7 +7483,7 @@
       </c>
       <c r="BH22" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:12.301759Z</t>
+          <t>2026-08-02T16:14:44.719266Z</t>
         </is>
       </c>
       <c r="BI22" s="24" t="inlineStr">
@@ -7502,7 +7529,8 @@
       <c r="CM22" s="24" t="n"/>
       <c r="CN22" s="24" t="n"/>
       <c r="CO22" s="24" t="n"/>
-      <c r="CP22" s="24" t="inlineStr">
+      <c r="CP22" s="24" t="n"/>
+      <c r="CQ22" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -7511,12 +7539,12 @@
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="24" t="inlineStr">
         <is>
-          <t>1f67cd97fc1f4d6c</t>
+          <t>2b170e75a3c345a5</t>
         </is>
       </c>
       <c r="B23" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:19.985321Z</t>
+          <t>2026-08-02T16:14:52.169624Z</t>
         </is>
       </c>
       <c r="C23" s="24" t="inlineStr">
@@ -7687,7 +7715,7 @@
       </c>
       <c r="BA23" s="24" t="inlineStr">
         <is>
-          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
+          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
         </is>
       </c>
       <c r="BB23" s="24" t="inlineStr">
@@ -7702,7 +7730,7 @@
       </c>
       <c r="BD23" s="24" t="inlineStr">
         <is>
-          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
+          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
         </is>
       </c>
       <c r="BE23" s="24" t="inlineStr">
@@ -7722,7 +7750,7 @@
       </c>
       <c r="BH23" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:12.813283Z</t>
+          <t>2026-08-02T16:14:45.283320Z</t>
         </is>
       </c>
       <c r="BI23" s="24" t="inlineStr">
@@ -7768,7 +7796,8 @@
       <c r="CM23" s="24" t="n"/>
       <c r="CN23" s="24" t="n"/>
       <c r="CO23" s="24" t="n"/>
-      <c r="CP23" s="24" t="inlineStr">
+      <c r="CP23" s="24" t="n"/>
+      <c r="CQ23" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -7777,12 +7806,12 @@
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="24" t="inlineStr">
         <is>
-          <t>48c53315f7064d79</t>
+          <t>2ca3b812440f45c0</t>
         </is>
       </c>
       <c r="B24" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:19.985321Z</t>
+          <t>2026-08-02T16:14:52.169624Z</t>
         </is>
       </c>
       <c r="C24" s="24" t="inlineStr">
@@ -7953,7 +7982,7 @@
       </c>
       <c r="BA24" s="24" t="inlineStr">
         <is>
-          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
+          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
         </is>
       </c>
       <c r="BB24" s="24" t="inlineStr">
@@ -7968,7 +7997,7 @@
       </c>
       <c r="BD24" s="24" t="inlineStr">
         <is>
-          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
+          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
         </is>
       </c>
       <c r="BE24" s="24" t="inlineStr">
@@ -7988,7 +8017,7 @@
       </c>
       <c r="BH24" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:13.406755Z</t>
+          <t>2026-08-02T16:14:45.864824Z</t>
         </is>
       </c>
       <c r="BI24" s="24" t="inlineStr">
@@ -8034,7 +8063,8 @@
       <c r="CM24" s="24" t="n"/>
       <c r="CN24" s="24" t="n"/>
       <c r="CO24" s="24" t="n"/>
-      <c r="CP24" s="24" t="inlineStr">
+      <c r="CP24" s="24" t="n"/>
+      <c r="CQ24" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -8043,12 +8073,12 @@
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="24" t="inlineStr">
         <is>
-          <t>8dccf8d14155413d</t>
+          <t>1d66cb95ad0a40ab</t>
         </is>
       </c>
       <c r="B25" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:19.985321Z</t>
+          <t>2026-08-02T16:14:52.169624Z</t>
         </is>
       </c>
       <c r="C25" s="24" t="inlineStr">
@@ -8219,7 +8249,7 @@
       </c>
       <c r="BA25" s="24" t="inlineStr">
         <is>
-          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
+          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
         </is>
       </c>
       <c r="BB25" s="24" t="inlineStr">
@@ -8234,7 +8264,7 @@
       </c>
       <c r="BD25" s="24" t="inlineStr">
         <is>
-          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
+          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
         </is>
       </c>
       <c r="BE25" s="24" t="inlineStr">
@@ -8254,7 +8284,7 @@
       </c>
       <c r="BH25" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:13.923521Z</t>
+          <t>2026-08-02T16:14:46.366525Z</t>
         </is>
       </c>
       <c r="BI25" s="24" t="inlineStr">
@@ -8300,7 +8330,8 @@
       <c r="CM25" s="24" t="n"/>
       <c r="CN25" s="24" t="n"/>
       <c r="CO25" s="24" t="n"/>
-      <c r="CP25" s="24" t="inlineStr">
+      <c r="CP25" s="24" t="n"/>
+      <c r="CQ25" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -8309,12 +8340,12 @@
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="24" t="inlineStr">
         <is>
-          <t>754060c98b474189</t>
+          <t>7ca7eef3557448d0</t>
         </is>
       </c>
       <c r="B26" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:19.985321Z</t>
+          <t>2026-08-02T16:14:52.169624Z</t>
         </is>
       </c>
       <c r="C26" s="24" t="inlineStr">
@@ -8485,7 +8516,7 @@
       </c>
       <c r="BA26" s="24" t="inlineStr">
         <is>
-          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
+          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
         </is>
       </c>
       <c r="BB26" s="24" t="inlineStr">
@@ -8500,7 +8531,7 @@
       </c>
       <c r="BD26" s="24" t="inlineStr">
         <is>
-          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
+          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
         </is>
       </c>
       <c r="BE26" s="24" t="inlineStr">
@@ -8520,7 +8551,7 @@
       </c>
       <c r="BH26" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:17.539022Z</t>
+          <t>2026-08-02T16:14:49.714123Z</t>
         </is>
       </c>
       <c r="BI26" s="24" t="inlineStr">
@@ -8566,7 +8597,8 @@
       <c r="CM26" s="24" t="n"/>
       <c r="CN26" s="24" t="n"/>
       <c r="CO26" s="24" t="n"/>
-      <c r="CP26" s="24" t="inlineStr">
+      <c r="CP26" s="24" t="n"/>
+      <c r="CQ26" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -8575,12 +8607,12 @@
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="24" t="inlineStr">
         <is>
-          <t>b6d34c8bb890474f</t>
+          <t>ca4a461da428429f</t>
         </is>
       </c>
       <c r="B27" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:19.985321Z</t>
+          <t>2026-08-02T16:14:52.169624Z</t>
         </is>
       </c>
       <c r="C27" s="24" t="inlineStr">
@@ -8625,20 +8657,20 @@
         </is>
       </c>
       <c r="L27" s="26" t="n">
-        <v>-127</v>
+        <v>-122</v>
       </c>
       <c r="M27" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.819672</v>
       </c>
       <c r="N27" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.54955</v>
       </c>
       <c r="O27" s="28" t="n">
         <v>0.501936</v>
       </c>
       <c r="P27" s="28" t="n"/>
       <c r="Q27" s="28" t="n">
-        <v>-0.057535</v>
+        <v>-0.047614</v>
       </c>
       <c r="R27" s="26" t="n">
         <v>0</v>
@@ -8667,7 +8699,7 @@
       <c r="AD27" s="24" t="n"/>
       <c r="AE27" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-lol-pnga-vksa-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-lol-pnga-vksa-2026-08-03).</t>
         </is>
       </c>
       <c r="AF27" s="31" t="inlineStr">
@@ -8751,7 +8783,7 @@
       </c>
       <c r="BA27" s="24" t="inlineStr">
         <is>
-          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
+          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
         </is>
       </c>
       <c r="BB27" s="24" t="inlineStr">
@@ -8766,7 +8798,7 @@
       </c>
       <c r="BD27" s="24" t="inlineStr">
         <is>
-          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
+          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
         </is>
       </c>
       <c r="BE27" s="24" t="inlineStr">
@@ -8786,7 +8818,7 @@
       </c>
       <c r="BH27" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:19.046288Z</t>
+          <t>2026-08-02T16:14:51.167478Z</t>
         </is>
       </c>
       <c r="BI27" s="24" t="inlineStr">
@@ -8796,13 +8828,13 @@
       </c>
       <c r="BJ27" s="25" t="n"/>
       <c r="BK27" s="26" t="n">
-        <v>-127</v>
+        <v>-122</v>
       </c>
       <c r="BL27" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.819672</v>
       </c>
       <c r="BM27" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.54955</v>
       </c>
       <c r="BN27" s="28" t="n"/>
       <c r="BO27" s="28" t="n"/>
@@ -8832,7 +8864,8 @@
       <c r="CM27" s="24" t="n"/>
       <c r="CN27" s="24" t="n"/>
       <c r="CO27" s="24" t="n"/>
-      <c r="CP27" s="24" t="inlineStr">
+      <c r="CP27" s="24" t="n"/>
+      <c r="CQ27" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/data/research/lol.xlsx
+++ b/data/research/lol.xlsx
@@ -6738,12 +6738,12 @@
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="24" t="inlineStr">
         <is>
-          <t>a744d539d2b64aa6</t>
+          <t>12fc8231d03748b7</t>
         </is>
       </c>
       <c r="B20" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:14:52.169624Z</t>
+          <t>2026-08-02T16:53:11.967172Z</t>
         </is>
       </c>
       <c r="C20" s="24" t="inlineStr">
@@ -6914,7 +6914,7 @@
       </c>
       <c r="BA20" s="24" t="inlineStr">
         <is>
-          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
+          <t>7a524d830547b62f7f9c941aadbdf0fc52dbd67b16b701b974612cc0a7507dd8</t>
         </is>
       </c>
       <c r="BB20" s="24" t="inlineStr">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="BD20" s="24" t="inlineStr">
         <is>
-          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
+          <t>7a524d830547b62f7f9c941aadbdf0fc52dbd67b16b701b974612cc0a7507dd8</t>
         </is>
       </c>
       <c r="BE20" s="24" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="BH20" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:14:42.310322Z</t>
+          <t>2026-08-02T16:53:02.304568Z</t>
         </is>
       </c>
       <c r="BI20" s="24" t="inlineStr">
@@ -7005,12 +7005,12 @@
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="24" t="inlineStr">
         <is>
-          <t>07e88610202f4442</t>
+          <t>b63efeb632214e6e</t>
         </is>
       </c>
       <c r="B21" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:14:52.169624Z</t>
+          <t>2026-08-02T16:53:11.967172Z</t>
         </is>
       </c>
       <c r="C21" s="24" t="inlineStr">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="BA21" s="24" t="inlineStr">
         <is>
-          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
+          <t>7a524d830547b62f7f9c941aadbdf0fc52dbd67b16b701b974612cc0a7507dd8</t>
         </is>
       </c>
       <c r="BB21" s="24" t="inlineStr">
@@ -7196,7 +7196,7 @@
       </c>
       <c r="BD21" s="24" t="inlineStr">
         <is>
-          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
+          <t>7a524d830547b62f7f9c941aadbdf0fc52dbd67b16b701b974612cc0a7507dd8</t>
         </is>
       </c>
       <c r="BE21" s="24" t="inlineStr">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="BH21" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:14:44.213769Z</t>
+          <t>2026-08-02T16:53:04.258724Z</t>
         </is>
       </c>
       <c r="BI21" s="24" t="inlineStr">
@@ -7272,12 +7272,12 @@
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="24" t="inlineStr">
         <is>
-          <t>fc755a70629b4542</t>
+          <t>36b1d914397a4a71</t>
         </is>
       </c>
       <c r="B22" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:14:52.169624Z</t>
+          <t>2026-08-02T16:53:11.967172Z</t>
         </is>
       </c>
       <c r="C22" s="24" t="inlineStr">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="BA22" s="24" t="inlineStr">
         <is>
-          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
+          <t>7a524d830547b62f7f9c941aadbdf0fc52dbd67b16b701b974612cc0a7507dd8</t>
         </is>
       </c>
       <c r="BB22" s="24" t="inlineStr">
@@ -7463,7 +7463,7 @@
       </c>
       <c r="BD22" s="24" t="inlineStr">
         <is>
-          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
+          <t>7a524d830547b62f7f9c941aadbdf0fc52dbd67b16b701b974612cc0a7507dd8</t>
         </is>
       </c>
       <c r="BE22" s="24" t="inlineStr">
@@ -7483,7 +7483,7 @@
       </c>
       <c r="BH22" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:14:44.719266Z</t>
+          <t>2026-08-02T16:53:04.775409Z</t>
         </is>
       </c>
       <c r="BI22" s="24" t="inlineStr">
@@ -7539,12 +7539,12 @@
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="24" t="inlineStr">
         <is>
-          <t>2b170e75a3c345a5</t>
+          <t>16a7fb73a44a4394</t>
         </is>
       </c>
       <c r="B23" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:14:52.169624Z</t>
+          <t>2026-08-02T16:53:11.967172Z</t>
         </is>
       </c>
       <c r="C23" s="24" t="inlineStr">
@@ -7715,7 +7715,7 @@
       </c>
       <c r="BA23" s="24" t="inlineStr">
         <is>
-          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
+          <t>7a524d830547b62f7f9c941aadbdf0fc52dbd67b16b701b974612cc0a7507dd8</t>
         </is>
       </c>
       <c r="BB23" s="24" t="inlineStr">
@@ -7730,7 +7730,7 @@
       </c>
       <c r="BD23" s="24" t="inlineStr">
         <is>
-          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
+          <t>7a524d830547b62f7f9c941aadbdf0fc52dbd67b16b701b974612cc0a7507dd8</t>
         </is>
       </c>
       <c r="BE23" s="24" t="inlineStr">
@@ -7750,7 +7750,7 @@
       </c>
       <c r="BH23" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:14:45.283320Z</t>
+          <t>2026-08-02T16:53:05.228074Z</t>
         </is>
       </c>
       <c r="BI23" s="24" t="inlineStr">
@@ -7806,12 +7806,12 @@
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="24" t="inlineStr">
         <is>
-          <t>2ca3b812440f45c0</t>
+          <t>804dd62b0492486d</t>
         </is>
       </c>
       <c r="B24" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:14:52.169624Z</t>
+          <t>2026-08-02T16:53:11.967172Z</t>
         </is>
       </c>
       <c r="C24" s="24" t="inlineStr">
@@ -7982,7 +7982,7 @@
       </c>
       <c r="BA24" s="24" t="inlineStr">
         <is>
-          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
+          <t>7a524d830547b62f7f9c941aadbdf0fc52dbd67b16b701b974612cc0a7507dd8</t>
         </is>
       </c>
       <c r="BB24" s="24" t="inlineStr">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="BD24" s="24" t="inlineStr">
         <is>
-          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
+          <t>7a524d830547b62f7f9c941aadbdf0fc52dbd67b16b701b974612cc0a7507dd8</t>
         </is>
       </c>
       <c r="BE24" s="24" t="inlineStr">
@@ -8017,7 +8017,7 @@
       </c>
       <c r="BH24" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:14:45.864824Z</t>
+          <t>2026-08-02T16:53:05.711202Z</t>
         </is>
       </c>
       <c r="BI24" s="24" t="inlineStr">
@@ -8073,12 +8073,12 @@
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="24" t="inlineStr">
         <is>
-          <t>1d66cb95ad0a40ab</t>
+          <t>1cbe38c60c6c4a71</t>
         </is>
       </c>
       <c r="B25" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:14:52.169624Z</t>
+          <t>2026-08-02T16:53:11.967172Z</t>
         </is>
       </c>
       <c r="C25" s="24" t="inlineStr">
@@ -8249,7 +8249,7 @@
       </c>
       <c r="BA25" s="24" t="inlineStr">
         <is>
-          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
+          <t>7a524d830547b62f7f9c941aadbdf0fc52dbd67b16b701b974612cc0a7507dd8</t>
         </is>
       </c>
       <c r="BB25" s="24" t="inlineStr">
@@ -8264,7 +8264,7 @@
       </c>
       <c r="BD25" s="24" t="inlineStr">
         <is>
-          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
+          <t>7a524d830547b62f7f9c941aadbdf0fc52dbd67b16b701b974612cc0a7507dd8</t>
         </is>
       </c>
       <c r="BE25" s="24" t="inlineStr">
@@ -8284,7 +8284,7 @@
       </c>
       <c r="BH25" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:14:46.366525Z</t>
+          <t>2026-08-02T16:53:06.165699Z</t>
         </is>
       </c>
       <c r="BI25" s="24" t="inlineStr">
@@ -8340,12 +8340,12 @@
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="24" t="inlineStr">
         <is>
-          <t>7ca7eef3557448d0</t>
+          <t>aa70becef10142af</t>
         </is>
       </c>
       <c r="B26" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:14:52.169624Z</t>
+          <t>2026-08-02T16:53:11.967172Z</t>
         </is>
       </c>
       <c r="C26" s="24" t="inlineStr">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="BA26" s="24" t="inlineStr">
         <is>
-          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
+          <t>7a524d830547b62f7f9c941aadbdf0fc52dbd67b16b701b974612cc0a7507dd8</t>
         </is>
       </c>
       <c r="BB26" s="24" t="inlineStr">
@@ -8531,7 +8531,7 @@
       </c>
       <c r="BD26" s="24" t="inlineStr">
         <is>
-          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
+          <t>7a524d830547b62f7f9c941aadbdf0fc52dbd67b16b701b974612cc0a7507dd8</t>
         </is>
       </c>
       <c r="BE26" s="24" t="inlineStr">
@@ -8551,7 +8551,7 @@
       </c>
       <c r="BH26" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:14:49.714123Z</t>
+          <t>2026-08-02T16:53:09.518110Z</t>
         </is>
       </c>
       <c r="BI26" s="24" t="inlineStr">
@@ -8607,12 +8607,12 @@
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="24" t="inlineStr">
         <is>
-          <t>ca4a461da428429f</t>
+          <t>138c9f70d80b4105</t>
         </is>
       </c>
       <c r="B27" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:14:52.169624Z</t>
+          <t>2026-08-02T16:53:11.967172Z</t>
         </is>
       </c>
       <c r="C27" s="24" t="inlineStr">
@@ -8657,23 +8657,23 @@
         </is>
       </c>
       <c r="L27" s="26" t="n">
-        <v>-122</v>
+        <v>-113</v>
       </c>
       <c r="M27" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.884956</v>
       </c>
       <c r="N27" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.530516</v>
       </c>
       <c r="O27" s="28" t="n">
         <v>0.501936</v>
       </c>
       <c r="P27" s="28" t="n"/>
       <c r="Q27" s="28" t="n">
-        <v>-0.047614</v>
+        <v>-0.02858</v>
       </c>
       <c r="R27" s="26" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S27" s="29" t="n">
         <v>1</v>
@@ -8699,7 +8699,7 @@
       <c r="AD27" s="24" t="n"/>
       <c r="AE27" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-lol-pnga-vksa-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.5300 (market_slug=aec-lol-pnga-vksa-2026-08-03).</t>
         </is>
       </c>
       <c r="AF27" s="31" t="inlineStr">
@@ -8783,7 +8783,7 @@
       </c>
       <c r="BA27" s="24" t="inlineStr">
         <is>
-          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
+          <t>7a524d830547b62f7f9c941aadbdf0fc52dbd67b16b701b974612cc0a7507dd8</t>
         </is>
       </c>
       <c r="BB27" s="24" t="inlineStr">
@@ -8798,7 +8798,7 @@
       </c>
       <c r="BD27" s="24" t="inlineStr">
         <is>
-          <t>9542afb825eb6d09e3691d14391f247ee8669cf2eca817dd7cafaf375e184157</t>
+          <t>7a524d830547b62f7f9c941aadbdf0fc52dbd67b16b701b974612cc0a7507dd8</t>
         </is>
       </c>
       <c r="BE27" s="24" t="inlineStr">
@@ -8818,7 +8818,7 @@
       </c>
       <c r="BH27" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:14:51.167478Z</t>
+          <t>2026-08-02T16:53:10.958524Z</t>
         </is>
       </c>
       <c r="BI27" s="24" t="inlineStr">
@@ -8828,13 +8828,13 @@
       </c>
       <c r="BJ27" s="25" t="n"/>
       <c r="BK27" s="26" t="n">
-        <v>-122</v>
+        <v>-113</v>
       </c>
       <c r="BL27" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.884956</v>
       </c>
       <c r="BM27" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.530516</v>
       </c>
       <c r="BN27" s="28" t="n"/>
       <c r="BO27" s="28" t="n"/>

--- a/data/research/lol.xlsx
+++ b/data/research/lol.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ27" headerRowCount="1">
-  <autoFilter ref="A1:CQ27"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ20" headerRowCount="1">
+  <autoFilter ref="A1:CQ20"/>
   <tableColumns count="95">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -754,19 +754,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$27)</f>
+        <f>COUNTA('Picks'!$A$2:$A$20)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$27,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$20,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$27,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$20,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"win")+COUNTIFS('Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"win")+COUNTIFS('Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +794,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$27,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$20,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$27,"&gt;0",'Picks'!$V$2:$V$27,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$27,"&gt;0",'Picks'!$V$2:$V$27,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$20,"&gt;0",'Picks'!$V$2:$V$20,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$20,"&gt;0",'Picks'!$V$2:$V$20,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$27,"&gt;0",'Picks'!$V$2:$V$27,"win")/(COUNTIFS('Picks'!$BX$2:$BX$27,"&gt;0",'Picks'!$V$2:$V$27,"win")+COUNTIFS('Picks'!$BX$2:$BX$27,"&gt;0",'Picks'!$V$2:$V$27,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$20,"&gt;0",'Picks'!$V$2:$V$20,"win")/(COUNTIFS('Picks'!$BX$2:$BX$20,"&gt;0",'Picks'!$V$2:$V$20,"win")+COUNTIFS('Picks'!$BX$2:$BX$20,"&gt;0",'Picks'!$V$2:$V$20,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$27)/SUM('Picks'!$BX$2:$BX$27),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$20)/SUM('Picks'!$BX$2:$BX$20),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +834,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$27)</f>
+        <f>SUM('Picks'!$BY$2:$BY$20)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$27,"&lt;&gt;",'Picks'!$AB$2:$AB$27),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$20,"&lt;&gt;",'Picks'!$AB$2:$AB$20),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$27,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$27,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$20,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$20,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$27,'Picks'!$AM$2:$AM$27,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$20,'Picks'!$AM$2:$AM$20,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +901,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$27,$A14,'Picks'!$U$2:$U$27,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$20,$A14,'Picks'!$U$2:$U$20,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$27,$A14,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$20,$A14,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$27,$A14,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$20,$A14,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +917,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$27,'Picks'!$H$2:$H$27,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$20,'Picks'!$H$2:$H$20,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$27,'Picks'!$H$2:$H$27,$A14,'Picks'!$U$2:$U$27,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$20,'Picks'!$H$2:$H$20,$A14,'Picks'!$U$2:$U$20,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +932,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$27,$A15,'Picks'!$U$2:$U$27,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$20,$A15,'Picks'!$U$2:$U$20,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$27,$A15,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$20,$A15,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$27,$A15,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$20,$A15,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +948,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$27,'Picks'!$H$2:$H$27,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$20,'Picks'!$H$2:$H$20,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$27,'Picks'!$H$2:$H$27,$A15,'Picks'!$U$2:$U$27,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$20,'Picks'!$H$2:$H$20,$A15,'Picks'!$U$2:$U$20,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +963,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$27,$A16,'Picks'!$U$2:$U$27,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$20,$A16,'Picks'!$U$2:$U$20,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$27,$A16,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$20,$A16,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$27,$A16,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$20,$A16,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +979,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$27,'Picks'!$H$2:$H$27,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$20,'Picks'!$H$2:$H$20,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$27,'Picks'!$H$2:$H$27,$A16,'Picks'!$U$2:$U$27,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$20,'Picks'!$H$2:$H$20,$A16,'Picks'!$U$2:$U$20,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ27"/>
+  <dimension ref="A1:CQ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7002,1875 +7002,6 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="36" customHeight="1">
-      <c r="A21" s="24" t="inlineStr">
-        <is>
-          <t>b63efeb632214e6e</t>
-        </is>
-      </c>
-      <c r="B21" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:11.967172Z</t>
-        </is>
-      </c>
-      <c r="C21" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T08:00:00Z</t>
-        </is>
-      </c>
-      <c r="D21" s="24" t="inlineStr">
-        <is>
-          <t>67492</t>
-        </is>
-      </c>
-      <c r="E21" s="24" t="inlineStr">
-        <is>
-          <t>LOL</t>
-        </is>
-      </c>
-      <c r="F21" s="24" t="inlineStr">
-        <is>
-          <t>BNK FearX Youth</t>
-        </is>
-      </c>
-      <c r="G21" s="24" t="inlineStr">
-        <is>
-          <t>HANJIN BRION Challengers</t>
-        </is>
-      </c>
-      <c r="H21" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I21" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J21" s="25" t="n"/>
-      <c r="K21" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L21" s="26" t="n">
-        <v>-223</v>
-      </c>
-      <c r="M21" s="27" t="n">
-        <v>1.44843</v>
-      </c>
-      <c r="N21" s="28" t="n">
-        <v>0.690402</v>
-      </c>
-      <c r="O21" s="28" t="n">
-        <v>0.634473</v>
-      </c>
-      <c r="P21" s="28" t="n"/>
-      <c r="Q21" s="28" t="n">
-        <v>-0.055929</v>
-      </c>
-      <c r="R21" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" s="29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T21" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U21" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V21" s="24" t="n"/>
-      <c r="W21" s="26" t="n"/>
-      <c r="X21" s="26" t="n"/>
-      <c r="Y21" s="25" t="n"/>
-      <c r="Z21" s="26" t="n"/>
-      <c r="AA21" s="28" t="n"/>
-      <c r="AB21" s="28" t="n"/>
-      <c r="AC21" s="30" t="n"/>
-      <c r="AD21" s="24" t="n"/>
-      <c r="AE21" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-lol-hbc-foxy-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF21" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG21" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH21" s="24" t="n"/>
-      <c r="AI21" s="31" t="n"/>
-      <c r="AJ21" s="31" t="n"/>
-      <c r="AK21" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL21" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM21" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN21" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO21" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP21" s="24" t="inlineStr">
-        <is>
-          <t>BNK FearX Youth</t>
-        </is>
-      </c>
-      <c r="AQ21" s="24" t="inlineStr">
-        <is>
-          <t>BNK FearX Youth</t>
-        </is>
-      </c>
-      <c r="AR21" s="24" t="inlineStr">
-        <is>
-          <t>BNK FearX Youth</t>
-        </is>
-      </c>
-      <c r="AS21" s="24" t="inlineStr">
-        <is>
-          <t>HANJIN BRION Challengers</t>
-        </is>
-      </c>
-      <c r="AT21" s="24" t="inlineStr">
-        <is>
-          <t>HANJIN BRION Challengers</t>
-        </is>
-      </c>
-      <c r="AU21" s="24" t="inlineStr">
-        <is>
-          <t>HANJIN BRION Challengers</t>
-        </is>
-      </c>
-      <c r="AV21" s="24" t="n"/>
-      <c r="AW21" s="24" t="n"/>
-      <c r="AX21" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY21" s="24" t="n"/>
-      <c r="AZ21" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA21" s="24" t="inlineStr">
-        <is>
-          <t>7a524d830547b62f7f9c941aadbdf0fc52dbd67b16b701b974612cc0a7507dd8</t>
-        </is>
-      </c>
-      <c r="BB21" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC21" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD21" s="24" t="inlineStr">
-        <is>
-          <t>7a524d830547b62f7f9c941aadbdf0fc52dbd67b16b701b974612cc0a7507dd8</t>
-        </is>
-      </c>
-      <c r="BE21" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF21" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG21" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH21" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:04.258724Z</t>
-        </is>
-      </c>
-      <c r="BI21" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ21" s="25" t="n"/>
-      <c r="BK21" s="26" t="n">
-        <v>-223</v>
-      </c>
-      <c r="BL21" s="27" t="n">
-        <v>1.44843</v>
-      </c>
-      <c r="BM21" s="28" t="n">
-        <v>0.690402</v>
-      </c>
-      <c r="BN21" s="28" t="n"/>
-      <c r="BO21" s="28" t="n"/>
-      <c r="BP21" s="25" t="n"/>
-      <c r="BQ21" s="27" t="n"/>
-      <c r="BR21" s="28" t="n"/>
-      <c r="BS21" s="28" t="n"/>
-      <c r="BT21" s="28" t="n"/>
-      <c r="BU21" s="25" t="n"/>
-      <c r="BV21" s="29" t="n"/>
-      <c r="BW21" s="24" t="n"/>
-      <c r="BX21" s="30" t="n"/>
-      <c r="BY21" s="27" t="n"/>
-      <c r="BZ21" s="24" t="n"/>
-      <c r="CA21" s="31" t="n"/>
-      <c r="CB21" s="24" t="n"/>
-      <c r="CC21" s="24" t="n"/>
-      <c r="CD21" s="24" t="n"/>
-      <c r="CE21" s="24" t="n"/>
-      <c r="CF21" s="24" t="n"/>
-      <c r="CG21" s="24" t="n"/>
-      <c r="CH21" s="24" t="n"/>
-      <c r="CI21" s="24" t="n"/>
-      <c r="CJ21" s="24" t="n"/>
-      <c r="CK21" s="24" t="n"/>
-      <c r="CL21" s="24" t="n"/>
-      <c r="CM21" s="24" t="n"/>
-      <c r="CN21" s="24" t="n"/>
-      <c r="CO21" s="24" t="n"/>
-      <c r="CP21" s="24" t="n"/>
-      <c r="CQ21" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="36" customHeight="1">
-      <c r="A22" s="24" t="inlineStr">
-        <is>
-          <t>36b1d914397a4a71</t>
-        </is>
-      </c>
-      <c r="B22" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:11.967172Z</t>
-        </is>
-      </c>
-      <c r="C22" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T08:00:00Z</t>
-        </is>
-      </c>
-      <c r="D22" s="24" t="inlineStr">
-        <is>
-          <t>67491</t>
-        </is>
-      </c>
-      <c r="E22" s="24" t="inlineStr">
-        <is>
-          <t>LOL</t>
-        </is>
-      </c>
-      <c r="F22" s="24" t="inlineStr">
-        <is>
-          <t>Hanwha Life Esports</t>
-        </is>
-      </c>
-      <c r="G22" s="24" t="inlineStr">
-        <is>
-          <t>Gen.G</t>
-        </is>
-      </c>
-      <c r="H22" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I22" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J22" s="25" t="n"/>
-      <c r="K22" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L22" s="26" t="n">
-        <v>-144</v>
-      </c>
-      <c r="M22" s="27" t="n">
-        <v>1.694444</v>
-      </c>
-      <c r="N22" s="28" t="n">
-        <v>0.590164</v>
-      </c>
-      <c r="O22" s="28" t="n">
-        <v>0.53577</v>
-      </c>
-      <c r="P22" s="28" t="n"/>
-      <c r="Q22" s="28" t="n">
-        <v>-0.054394</v>
-      </c>
-      <c r="R22" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T22" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U22" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V22" s="24" t="n"/>
-      <c r="W22" s="26" t="n"/>
-      <c r="X22" s="26" t="n"/>
-      <c r="Y22" s="25" t="n"/>
-      <c r="Z22" s="26" t="n"/>
-      <c r="AA22" s="28" t="n"/>
-      <c r="AB22" s="28" t="n"/>
-      <c r="AC22" s="30" t="n"/>
-      <c r="AD22" s="24" t="n"/>
-      <c r="AE22" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-lol-gen-hle-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF22" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG22" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH22" s="24" t="n"/>
-      <c r="AI22" s="31" t="n"/>
-      <c r="AJ22" s="31" t="n"/>
-      <c r="AK22" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL22" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM22" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN22" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO22" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP22" s="24" t="inlineStr">
-        <is>
-          <t>Hanwha Life Esports</t>
-        </is>
-      </c>
-      <c r="AQ22" s="24" t="inlineStr">
-        <is>
-          <t>Hanwha Life Esports</t>
-        </is>
-      </c>
-      <c r="AR22" s="24" t="inlineStr">
-        <is>
-          <t>Hanwha Life Esports</t>
-        </is>
-      </c>
-      <c r="AS22" s="24" t="inlineStr">
-        <is>
-          <t>Gen.G</t>
-        </is>
-      </c>
-      <c r="AT22" s="24" t="inlineStr">
-        <is>
-          <t>Gen.G</t>
-        </is>
-      </c>
-      <c r="AU22" s="24" t="inlineStr">
-        <is>
-          <t>Gen.G</t>
-        </is>
-      </c>
-      <c r="AV22" s="24" t="n"/>
-      <c r="AW22" s="24" t="n"/>
-      <c r="AX22" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY22" s="24" t="n"/>
-      <c r="AZ22" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA22" s="24" t="inlineStr">
-        <is>
-          <t>7a524d830547b62f7f9c941aadbdf0fc52dbd67b16b701b974612cc0a7507dd8</t>
-        </is>
-      </c>
-      <c r="BB22" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC22" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD22" s="24" t="inlineStr">
-        <is>
-          <t>7a524d830547b62f7f9c941aadbdf0fc52dbd67b16b701b974612cc0a7507dd8</t>
-        </is>
-      </c>
-      <c r="BE22" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF22" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG22" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH22" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:04.775409Z</t>
-        </is>
-      </c>
-      <c r="BI22" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ22" s="25" t="n"/>
-      <c r="BK22" s="26" t="n">
-        <v>-144</v>
-      </c>
-      <c r="BL22" s="27" t="n">
-        <v>1.694444</v>
-      </c>
-      <c r="BM22" s="28" t="n">
-        <v>0.590164</v>
-      </c>
-      <c r="BN22" s="28" t="n"/>
-      <c r="BO22" s="28" t="n"/>
-      <c r="BP22" s="25" t="n"/>
-      <c r="BQ22" s="27" t="n"/>
-      <c r="BR22" s="28" t="n"/>
-      <c r="BS22" s="28" t="n"/>
-      <c r="BT22" s="28" t="n"/>
-      <c r="BU22" s="25" t="n"/>
-      <c r="BV22" s="29" t="n"/>
-      <c r="BW22" s="24" t="n"/>
-      <c r="BX22" s="30" t="n"/>
-      <c r="BY22" s="27" t="n"/>
-      <c r="BZ22" s="24" t="n"/>
-      <c r="CA22" s="31" t="n"/>
-      <c r="CB22" s="24" t="n"/>
-      <c r="CC22" s="24" t="n"/>
-      <c r="CD22" s="24" t="n"/>
-      <c r="CE22" s="24" t="n"/>
-      <c r="CF22" s="24" t="n"/>
-      <c r="CG22" s="24" t="n"/>
-      <c r="CH22" s="24" t="n"/>
-      <c r="CI22" s="24" t="n"/>
-      <c r="CJ22" s="24" t="n"/>
-      <c r="CK22" s="24" t="n"/>
-      <c r="CL22" s="24" t="n"/>
-      <c r="CM22" s="24" t="n"/>
-      <c r="CN22" s="24" t="n"/>
-      <c r="CO22" s="24" t="n"/>
-      <c r="CP22" s="24" t="n"/>
-      <c r="CQ22" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="36" customHeight="1">
-      <c r="A23" s="24" t="inlineStr">
-        <is>
-          <t>16a7fb73a44a4394</t>
-        </is>
-      </c>
-      <c r="B23" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:11.967172Z</t>
-        </is>
-      </c>
-      <c r="C23" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T10:00:00Z</t>
-        </is>
-      </c>
-      <c r="D23" s="24" t="inlineStr">
-        <is>
-          <t>67511</t>
-        </is>
-      </c>
-      <c r="E23" s="24" t="inlineStr">
-        <is>
-          <t>LOL</t>
-        </is>
-      </c>
-      <c r="F23" s="24" t="inlineStr">
-        <is>
-          <t>Dplus KIA Challengers</t>
-        </is>
-      </c>
-      <c r="G23" s="24" t="inlineStr">
-        <is>
-          <t>DN SOOPers Challengers</t>
-        </is>
-      </c>
-      <c r="H23" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I23" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J23" s="25" t="n"/>
-      <c r="K23" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L23" s="26" t="n">
-        <v>-223</v>
-      </c>
-      <c r="M23" s="27" t="n">
-        <v>1.44843</v>
-      </c>
-      <c r="N23" s="28" t="n">
-        <v>0.690402</v>
-      </c>
-      <c r="O23" s="28" t="n">
-        <v>0.703159</v>
-      </c>
-      <c r="P23" s="28" t="n"/>
-      <c r="Q23" s="28" t="n">
-        <v>0.012757</v>
-      </c>
-      <c r="R23" s="26" t="n">
-        <v>26</v>
-      </c>
-      <c r="S23" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T23" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U23" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V23" s="24" t="n"/>
-      <c r="W23" s="26" t="n"/>
-      <c r="X23" s="26" t="n"/>
-      <c r="Y23" s="25" t="n"/>
-      <c r="Z23" s="26" t="n"/>
-      <c r="AA23" s="28" t="n"/>
-      <c r="AB23" s="28" t="n"/>
-      <c r="AC23" s="30" t="n"/>
-      <c r="AD23" s="24" t="n"/>
-      <c r="AE23" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-lol-dnsc-dkc-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF23" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG23" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH23" s="24" t="n"/>
-      <c r="AI23" s="31" t="n"/>
-      <c r="AJ23" s="31" t="n"/>
-      <c r="AK23" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL23" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM23" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN23" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO23" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP23" s="24" t="inlineStr">
-        <is>
-          <t>Dplus KIA Challengers</t>
-        </is>
-      </c>
-      <c r="AQ23" s="24" t="inlineStr">
-        <is>
-          <t>Dplus KIA Challengers</t>
-        </is>
-      </c>
-      <c r="AR23" s="24" t="inlineStr">
-        <is>
-          <t>Dplus KIA Challengers</t>
-        </is>
-      </c>
-      <c r="AS23" s="24" t="inlineStr">
-        <is>
-          <t>DN SOOPers Challengers</t>
-        </is>
-      </c>
-      <c r="AT23" s="24" t="inlineStr">
-        <is>
-          <t>DN SOOPers Challengers</t>
-        </is>
-      </c>
-      <c r="AU23" s="24" t="inlineStr">
-        <is>
-          <t>DN SOOPers Challengers</t>
-        </is>
-      </c>
-      <c r="AV23" s="24" t="n"/>
-      <c r="AW23" s="24" t="n"/>
-      <c r="AX23" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY23" s="24" t="n"/>
-      <c r="AZ23" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA23" s="24" t="inlineStr">
-        <is>
-          <t>7a524d830547b62f7f9c941aadbdf0fc52dbd67b16b701b974612cc0a7507dd8</t>
-        </is>
-      </c>
-      <c r="BB23" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC23" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD23" s="24" t="inlineStr">
-        <is>
-          <t>7a524d830547b62f7f9c941aadbdf0fc52dbd67b16b701b974612cc0a7507dd8</t>
-        </is>
-      </c>
-      <c r="BE23" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF23" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG23" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH23" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:05.228074Z</t>
-        </is>
-      </c>
-      <c r="BI23" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ23" s="25" t="n"/>
-      <c r="BK23" s="26" t="n">
-        <v>-223</v>
-      </c>
-      <c r="BL23" s="27" t="n">
-        <v>1.44843</v>
-      </c>
-      <c r="BM23" s="28" t="n">
-        <v>0.690402</v>
-      </c>
-      <c r="BN23" s="28" t="n"/>
-      <c r="BO23" s="28" t="n"/>
-      <c r="BP23" s="25" t="n"/>
-      <c r="BQ23" s="27" t="n"/>
-      <c r="BR23" s="28" t="n"/>
-      <c r="BS23" s="28" t="n"/>
-      <c r="BT23" s="28" t="n"/>
-      <c r="BU23" s="25" t="n"/>
-      <c r="BV23" s="29" t="n"/>
-      <c r="BW23" s="24" t="n"/>
-      <c r="BX23" s="30" t="n"/>
-      <c r="BY23" s="27" t="n"/>
-      <c r="BZ23" s="24" t="n"/>
-      <c r="CA23" s="31" t="n"/>
-      <c r="CB23" s="24" t="n"/>
-      <c r="CC23" s="24" t="n"/>
-      <c r="CD23" s="24" t="n"/>
-      <c r="CE23" s="24" t="n"/>
-      <c r="CF23" s="24" t="n"/>
-      <c r="CG23" s="24" t="n"/>
-      <c r="CH23" s="24" t="n"/>
-      <c r="CI23" s="24" t="n"/>
-      <c r="CJ23" s="24" t="n"/>
-      <c r="CK23" s="24" t="n"/>
-      <c r="CL23" s="24" t="n"/>
-      <c r="CM23" s="24" t="n"/>
-      <c r="CN23" s="24" t="n"/>
-      <c r="CO23" s="24" t="n"/>
-      <c r="CP23" s="24" t="n"/>
-      <c r="CQ23" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="36" customHeight="1">
-      <c r="A24" s="24" t="inlineStr">
-        <is>
-          <t>804dd62b0492486d</t>
-        </is>
-      </c>
-      <c r="B24" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:11.967172Z</t>
-        </is>
-      </c>
-      <c r="C24" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T10:30:00Z</t>
-        </is>
-      </c>
-      <c r="D24" s="24" t="inlineStr">
-        <is>
-          <t>67515</t>
-        </is>
-      </c>
-      <c r="E24" s="24" t="inlineStr">
-        <is>
-          <t>LOL</t>
-        </is>
-      </c>
-      <c r="F24" s="24" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="G24" s="24" t="inlineStr">
-        <is>
-          <t>Nongshim Red Force</t>
-        </is>
-      </c>
-      <c r="H24" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I24" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J24" s="25" t="n"/>
-      <c r="K24" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L24" s="26" t="n">
-        <v>-163</v>
-      </c>
-      <c r="M24" s="27" t="n">
-        <v>1.613497</v>
-      </c>
-      <c r="N24" s="28" t="n">
-        <v>0.619772</v>
-      </c>
-      <c r="O24" s="28" t="n">
-        <v>0.746312</v>
-      </c>
-      <c r="P24" s="28" t="n"/>
-      <c r="Q24" s="28" t="n">
-        <v>0.12654</v>
-      </c>
-      <c r="R24" s="26" t="n">
-        <v>83</v>
-      </c>
-      <c r="S24" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T24" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U24" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V24" s="24" t="n"/>
-      <c r="W24" s="26" t="n"/>
-      <c r="X24" s="26" t="n"/>
-      <c r="Y24" s="25" t="n"/>
-      <c r="Z24" s="26" t="n"/>
-      <c r="AA24" s="28" t="n"/>
-      <c r="AB24" s="28" t="n"/>
-      <c r="AC24" s="30" t="n"/>
-      <c r="AD24" s="24" t="n"/>
-      <c r="AE24" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-lol-ns-t1-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF24" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG24" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH24" s="24" t="n"/>
-      <c r="AI24" s="31" t="n"/>
-      <c r="AJ24" s="31" t="n"/>
-      <c r="AK24" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL24" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM24" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN24" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO24" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP24" s="24" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="AQ24" s="24" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="AR24" s="24" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="AS24" s="24" t="inlineStr">
-        <is>
-          <t>Nongshim Red Force</t>
-        </is>
-      </c>
-      <c r="AT24" s="24" t="inlineStr">
-        <is>
-          <t>Nongshim Red Force</t>
-        </is>
-      </c>
-      <c r="AU24" s="24" t="inlineStr">
-        <is>
-          <t>Nongshim Red Force</t>
-        </is>
-      </c>
-      <c r="AV24" s="24" t="n"/>
-      <c r="AW24" s="24" t="n"/>
-      <c r="AX24" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY24" s="24" t="n"/>
-      <c r="AZ24" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA24" s="24" t="inlineStr">
-        <is>
-          <t>7a524d830547b62f7f9c941aadbdf0fc52dbd67b16b701b974612cc0a7507dd8</t>
-        </is>
-      </c>
-      <c r="BB24" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC24" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD24" s="24" t="inlineStr">
-        <is>
-          <t>7a524d830547b62f7f9c941aadbdf0fc52dbd67b16b701b974612cc0a7507dd8</t>
-        </is>
-      </c>
-      <c r="BE24" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF24" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG24" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH24" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:05.711202Z</t>
-        </is>
-      </c>
-      <c r="BI24" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ24" s="25" t="n"/>
-      <c r="BK24" s="26" t="n">
-        <v>-163</v>
-      </c>
-      <c r="BL24" s="27" t="n">
-        <v>1.613497</v>
-      </c>
-      <c r="BM24" s="28" t="n">
-        <v>0.619772</v>
-      </c>
-      <c r="BN24" s="28" t="n"/>
-      <c r="BO24" s="28" t="n"/>
-      <c r="BP24" s="25" t="n"/>
-      <c r="BQ24" s="27" t="n"/>
-      <c r="BR24" s="28" t="n"/>
-      <c r="BS24" s="28" t="n"/>
-      <c r="BT24" s="28" t="n"/>
-      <c r="BU24" s="25" t="n"/>
-      <c r="BV24" s="29" t="n"/>
-      <c r="BW24" s="24" t="n"/>
-      <c r="BX24" s="30" t="n"/>
-      <c r="BY24" s="27" t="n"/>
-      <c r="BZ24" s="24" t="n"/>
-      <c r="CA24" s="31" t="n"/>
-      <c r="CB24" s="24" t="n"/>
-      <c r="CC24" s="24" t="n"/>
-      <c r="CD24" s="24" t="n"/>
-      <c r="CE24" s="24" t="n"/>
-      <c r="CF24" s="24" t="n"/>
-      <c r="CG24" s="24" t="n"/>
-      <c r="CH24" s="24" t="n"/>
-      <c r="CI24" s="24" t="n"/>
-      <c r="CJ24" s="24" t="n"/>
-      <c r="CK24" s="24" t="n"/>
-      <c r="CL24" s="24" t="n"/>
-      <c r="CM24" s="24" t="n"/>
-      <c r="CN24" s="24" t="n"/>
-      <c r="CO24" s="24" t="n"/>
-      <c r="CP24" s="24" t="n"/>
-      <c r="CQ24" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="36" customHeight="1">
-      <c r="A25" s="24" t="inlineStr">
-        <is>
-          <t>1cbe38c60c6c4a71</t>
-        </is>
-      </c>
-      <c r="B25" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:11.967172Z</t>
-        </is>
-      </c>
-      <c r="C25" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T15:00:00Z</t>
-        </is>
-      </c>
-      <c r="D25" s="24" t="inlineStr">
-        <is>
-          <t>67566</t>
-        </is>
-      </c>
-      <c r="E25" s="24" t="inlineStr">
-        <is>
-          <t>LOL</t>
-        </is>
-      </c>
-      <c r="F25" s="24" t="inlineStr">
-        <is>
-          <t>Shifters</t>
-        </is>
-      </c>
-      <c r="G25" s="24" t="inlineStr">
-        <is>
-          <t>Natus Vincere</t>
-        </is>
-      </c>
-      <c r="H25" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I25" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J25" s="25" t="n"/>
-      <c r="K25" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L25" s="26" t="n">
-        <v>-233</v>
-      </c>
-      <c r="M25" s="27" t="n">
-        <v>1.429185</v>
-      </c>
-      <c r="N25" s="28" t="n">
-        <v>0.6997</v>
-      </c>
-      <c r="O25" s="28" t="n">
-        <v>0.74664</v>
-      </c>
-      <c r="P25" s="28" t="n"/>
-      <c r="Q25" s="28" t="n">
-        <v>0.04694</v>
-      </c>
-      <c r="R25" s="26" t="n">
-        <v>43</v>
-      </c>
-      <c r="S25" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T25" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U25" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V25" s="24" t="n"/>
-      <c r="W25" s="26" t="n"/>
-      <c r="X25" s="26" t="n"/>
-      <c r="Y25" s="25" t="n"/>
-      <c r="Z25" s="26" t="n"/>
-      <c r="AA25" s="28" t="n"/>
-      <c r="AB25" s="28" t="n"/>
-      <c r="AC25" s="30" t="n"/>
-      <c r="AD25" s="24" t="n"/>
-      <c r="AE25" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-lol-navi-shft-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF25" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG25" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH25" s="24" t="n"/>
-      <c r="AI25" s="31" t="n"/>
-      <c r="AJ25" s="31" t="n"/>
-      <c r="AK25" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL25" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM25" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN25" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO25" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP25" s="24" t="inlineStr">
-        <is>
-          <t>Shifters</t>
-        </is>
-      </c>
-      <c r="AQ25" s="24" t="inlineStr">
-        <is>
-          <t>Shifters</t>
-        </is>
-      </c>
-      <c r="AR25" s="24" t="inlineStr">
-        <is>
-          <t>Shifters</t>
-        </is>
-      </c>
-      <c r="AS25" s="24" t="inlineStr">
-        <is>
-          <t>Natus Vincere</t>
-        </is>
-      </c>
-      <c r="AT25" s="24" t="inlineStr">
-        <is>
-          <t>Natus Vincere</t>
-        </is>
-      </c>
-      <c r="AU25" s="24" t="inlineStr">
-        <is>
-          <t>Natus Vincere</t>
-        </is>
-      </c>
-      <c r="AV25" s="24" t="n"/>
-      <c r="AW25" s="24" t="n"/>
-      <c r="AX25" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY25" s="24" t="n"/>
-      <c r="AZ25" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA25" s="24" t="inlineStr">
-        <is>
-          <t>7a524d830547b62f7f9c941aadbdf0fc52dbd67b16b701b974612cc0a7507dd8</t>
-        </is>
-      </c>
-      <c r="BB25" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC25" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD25" s="24" t="inlineStr">
-        <is>
-          <t>7a524d830547b62f7f9c941aadbdf0fc52dbd67b16b701b974612cc0a7507dd8</t>
-        </is>
-      </c>
-      <c r="BE25" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF25" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG25" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH25" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:06.165699Z</t>
-        </is>
-      </c>
-      <c r="BI25" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ25" s="25" t="n"/>
-      <c r="BK25" s="26" t="n">
-        <v>-233</v>
-      </c>
-      <c r="BL25" s="27" t="n">
-        <v>1.429185</v>
-      </c>
-      <c r="BM25" s="28" t="n">
-        <v>0.6997</v>
-      </c>
-      <c r="BN25" s="28" t="n"/>
-      <c r="BO25" s="28" t="n"/>
-      <c r="BP25" s="25" t="n"/>
-      <c r="BQ25" s="27" t="n"/>
-      <c r="BR25" s="28" t="n"/>
-      <c r="BS25" s="28" t="n"/>
-      <c r="BT25" s="28" t="n"/>
-      <c r="BU25" s="25" t="n"/>
-      <c r="BV25" s="29" t="n"/>
-      <c r="BW25" s="24" t="n"/>
-      <c r="BX25" s="30" t="n"/>
-      <c r="BY25" s="27" t="n"/>
-      <c r="BZ25" s="24" t="n"/>
-      <c r="CA25" s="31" t="n"/>
-      <c r="CB25" s="24" t="n"/>
-      <c r="CC25" s="24" t="n"/>
-      <c r="CD25" s="24" t="n"/>
-      <c r="CE25" s="24" t="n"/>
-      <c r="CF25" s="24" t="n"/>
-      <c r="CG25" s="24" t="n"/>
-      <c r="CH25" s="24" t="n"/>
-      <c r="CI25" s="24" t="n"/>
-      <c r="CJ25" s="24" t="n"/>
-      <c r="CK25" s="24" t="n"/>
-      <c r="CL25" s="24" t="n"/>
-      <c r="CM25" s="24" t="n"/>
-      <c r="CN25" s="24" t="n"/>
-      <c r="CO25" s="24" t="n"/>
-      <c r="CP25" s="24" t="n"/>
-      <c r="CQ25" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="36" customHeight="1">
-      <c r="A26" s="24" t="inlineStr">
-        <is>
-          <t>aa70becef10142af</t>
-        </is>
-      </c>
-      <c r="B26" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:11.967172Z</t>
-        </is>
-      </c>
-      <c r="C26" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T20:00:00Z</t>
-        </is>
-      </c>
-      <c r="D26" s="24" t="inlineStr">
-        <is>
-          <t>67937</t>
-        </is>
-      </c>
-      <c r="E26" s="24" t="inlineStr">
-        <is>
-          <t>LOL</t>
-        </is>
-      </c>
-      <c r="F26" s="24" t="inlineStr">
-        <is>
-          <t>Docta Esports</t>
-        </is>
-      </c>
-      <c r="G26" s="24" t="inlineStr">
-        <is>
-          <t>Volticons</t>
-        </is>
-      </c>
-      <c r="H26" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I26" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J26" s="25" t="n"/>
-      <c r="K26" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L26" s="26" t="n">
-        <v>-144</v>
-      </c>
-      <c r="M26" s="27" t="n">
-        <v>1.694444</v>
-      </c>
-      <c r="N26" s="28" t="n">
-        <v>0.590164</v>
-      </c>
-      <c r="O26" s="28" t="n">
-        <v>0.649674</v>
-      </c>
-      <c r="P26" s="28" t="n"/>
-      <c r="Q26" s="28" t="n">
-        <v>0.05951</v>
-      </c>
-      <c r="R26" s="26" t="n">
-        <v>50</v>
-      </c>
-      <c r="S26" s="29" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="T26" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U26" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V26" s="24" t="n"/>
-      <c r="W26" s="26" t="n"/>
-      <c r="X26" s="26" t="n"/>
-      <c r="Y26" s="25" t="n"/>
-      <c r="Z26" s="26" t="n"/>
-      <c r="AA26" s="28" t="n"/>
-      <c r="AB26" s="28" t="n"/>
-      <c r="AC26" s="30" t="n"/>
-      <c r="AD26" s="24" t="n"/>
-      <c r="AE26" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-lol-vtc-doh-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF26" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG26" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH26" s="24" t="n"/>
-      <c r="AI26" s="31" t="n"/>
-      <c r="AJ26" s="31" t="n"/>
-      <c r="AK26" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL26" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM26" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN26" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO26" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP26" s="24" t="inlineStr">
-        <is>
-          <t>Docta Esports</t>
-        </is>
-      </c>
-      <c r="AQ26" s="24" t="inlineStr">
-        <is>
-          <t>Docta Esports</t>
-        </is>
-      </c>
-      <c r="AR26" s="24" t="inlineStr">
-        <is>
-          <t>Docta Esports</t>
-        </is>
-      </c>
-      <c r="AS26" s="24" t="inlineStr">
-        <is>
-          <t>Volticons</t>
-        </is>
-      </c>
-      <c r="AT26" s="24" t="inlineStr">
-        <is>
-          <t>Volticons</t>
-        </is>
-      </c>
-      <c r="AU26" s="24" t="inlineStr">
-        <is>
-          <t>Volticons</t>
-        </is>
-      </c>
-      <c r="AV26" s="24" t="n"/>
-      <c r="AW26" s="24" t="n"/>
-      <c r="AX26" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY26" s="24" t="n"/>
-      <c r="AZ26" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA26" s="24" t="inlineStr">
-        <is>
-          <t>7a524d830547b62f7f9c941aadbdf0fc52dbd67b16b701b974612cc0a7507dd8</t>
-        </is>
-      </c>
-      <c r="BB26" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC26" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD26" s="24" t="inlineStr">
-        <is>
-          <t>7a524d830547b62f7f9c941aadbdf0fc52dbd67b16b701b974612cc0a7507dd8</t>
-        </is>
-      </c>
-      <c r="BE26" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF26" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG26" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH26" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:09.518110Z</t>
-        </is>
-      </c>
-      <c r="BI26" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ26" s="25" t="n"/>
-      <c r="BK26" s="26" t="n">
-        <v>-144</v>
-      </c>
-      <c r="BL26" s="27" t="n">
-        <v>1.694444</v>
-      </c>
-      <c r="BM26" s="28" t="n">
-        <v>0.590164</v>
-      </c>
-      <c r="BN26" s="28" t="n"/>
-      <c r="BO26" s="28" t="n"/>
-      <c r="BP26" s="25" t="n"/>
-      <c r="BQ26" s="27" t="n"/>
-      <c r="BR26" s="28" t="n"/>
-      <c r="BS26" s="28" t="n"/>
-      <c r="BT26" s="28" t="n"/>
-      <c r="BU26" s="25" t="n"/>
-      <c r="BV26" s="29" t="n"/>
-      <c r="BW26" s="24" t="n"/>
-      <c r="BX26" s="30" t="n"/>
-      <c r="BY26" s="27" t="n"/>
-      <c r="BZ26" s="24" t="n"/>
-      <c r="CA26" s="31" t="n"/>
-      <c r="CB26" s="24" t="n"/>
-      <c r="CC26" s="24" t="n"/>
-      <c r="CD26" s="24" t="n"/>
-      <c r="CE26" s="24" t="n"/>
-      <c r="CF26" s="24" t="n"/>
-      <c r="CG26" s="24" t="n"/>
-      <c r="CH26" s="24" t="n"/>
-      <c r="CI26" s="24" t="n"/>
-      <c r="CJ26" s="24" t="n"/>
-      <c r="CK26" s="24" t="n"/>
-      <c r="CL26" s="24" t="n"/>
-      <c r="CM26" s="24" t="n"/>
-      <c r="CN26" s="24" t="n"/>
-      <c r="CO26" s="24" t="n"/>
-      <c r="CP26" s="24" t="n"/>
-      <c r="CQ26" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="36" customHeight="1">
-      <c r="A27" s="24" t="inlineStr">
-        <is>
-          <t>138c9f70d80b4105</t>
-        </is>
-      </c>
-      <c r="B27" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:11.967172Z</t>
-        </is>
-      </c>
-      <c r="C27" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T22:00:00Z</t>
-        </is>
-      </c>
-      <c r="D27" s="24" t="inlineStr">
-        <is>
-          <t>68011</t>
-        </is>
-      </c>
-      <c r="E27" s="24" t="inlineStr">
-        <is>
-          <t>LOL</t>
-        </is>
-      </c>
-      <c r="F27" s="24" t="inlineStr">
-        <is>
-          <t>Vivo Keyd Stars Academy</t>
-        </is>
-      </c>
-      <c r="G27" s="24" t="inlineStr">
-        <is>
-          <t>paiN Gaming Academy</t>
-        </is>
-      </c>
-      <c r="H27" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I27" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J27" s="25" t="n"/>
-      <c r="K27" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L27" s="26" t="n">
-        <v>-113</v>
-      </c>
-      <c r="M27" s="27" t="n">
-        <v>1.884956</v>
-      </c>
-      <c r="N27" s="28" t="n">
-        <v>0.530516</v>
-      </c>
-      <c r="O27" s="28" t="n">
-        <v>0.501936</v>
-      </c>
-      <c r="P27" s="28" t="n"/>
-      <c r="Q27" s="28" t="n">
-        <v>-0.02858</v>
-      </c>
-      <c r="R27" s="26" t="n">
-        <v>6</v>
-      </c>
-      <c r="S27" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T27" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U27" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V27" s="24" t="n"/>
-      <c r="W27" s="26" t="n"/>
-      <c r="X27" s="26" t="n"/>
-      <c r="Y27" s="25" t="n"/>
-      <c r="Z27" s="26" t="n"/>
-      <c r="AA27" s="28" t="n"/>
-      <c r="AB27" s="28" t="n"/>
-      <c r="AC27" s="30" t="n"/>
-      <c r="AD27" s="24" t="n"/>
-      <c r="AE27" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5300 (market_slug=aec-lol-pnga-vksa-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF27" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG27" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH27" s="24" t="n"/>
-      <c r="AI27" s="31" t="n"/>
-      <c r="AJ27" s="31" t="n"/>
-      <c r="AK27" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL27" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM27" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN27" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO27" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP27" s="24" t="inlineStr">
-        <is>
-          <t>Vivo Keyd Stars Academy</t>
-        </is>
-      </c>
-      <c r="AQ27" s="24" t="inlineStr">
-        <is>
-          <t>Vivo Keyd Stars Academy</t>
-        </is>
-      </c>
-      <c r="AR27" s="24" t="inlineStr">
-        <is>
-          <t>Vivo Keyd Stars Academy</t>
-        </is>
-      </c>
-      <c r="AS27" s="24" t="inlineStr">
-        <is>
-          <t>paiN Gaming Academy</t>
-        </is>
-      </c>
-      <c r="AT27" s="24" t="inlineStr">
-        <is>
-          <t>paiN Gaming Academy</t>
-        </is>
-      </c>
-      <c r="AU27" s="24" t="inlineStr">
-        <is>
-          <t>paiN Gaming Academy</t>
-        </is>
-      </c>
-      <c r="AV27" s="24" t="n"/>
-      <c r="AW27" s="24" t="n"/>
-      <c r="AX27" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY27" s="24" t="n"/>
-      <c r="AZ27" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA27" s="24" t="inlineStr">
-        <is>
-          <t>7a524d830547b62f7f9c941aadbdf0fc52dbd67b16b701b974612cc0a7507dd8</t>
-        </is>
-      </c>
-      <c r="BB27" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC27" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD27" s="24" t="inlineStr">
-        <is>
-          <t>7a524d830547b62f7f9c941aadbdf0fc52dbd67b16b701b974612cc0a7507dd8</t>
-        </is>
-      </c>
-      <c r="BE27" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF27" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG27" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH27" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:10.958524Z</t>
-        </is>
-      </c>
-      <c r="BI27" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ27" s="25" t="n"/>
-      <c r="BK27" s="26" t="n">
-        <v>-113</v>
-      </c>
-      <c r="BL27" s="27" t="n">
-        <v>1.884956</v>
-      </c>
-      <c r="BM27" s="28" t="n">
-        <v>0.530516</v>
-      </c>
-      <c r="BN27" s="28" t="n"/>
-      <c r="BO27" s="28" t="n"/>
-      <c r="BP27" s="25" t="n"/>
-      <c r="BQ27" s="27" t="n"/>
-      <c r="BR27" s="28" t="n"/>
-      <c r="BS27" s="28" t="n"/>
-      <c r="BT27" s="28" t="n"/>
-      <c r="BU27" s="25" t="n"/>
-      <c r="BV27" s="29" t="n"/>
-      <c r="BW27" s="24" t="n"/>
-      <c r="BX27" s="30" t="n"/>
-      <c r="BY27" s="27" t="n"/>
-      <c r="BZ27" s="24" t="n"/>
-      <c r="CA27" s="31" t="n"/>
-      <c r="CB27" s="24" t="n"/>
-      <c r="CC27" s="24" t="n"/>
-      <c r="CD27" s="24" t="n"/>
-      <c r="CE27" s="24" t="n"/>
-      <c r="CF27" s="24" t="n"/>
-      <c r="CG27" s="24" t="n"/>
-      <c r="CH27" s="24" t="n"/>
-      <c r="CI27" s="24" t="n"/>
-      <c r="CJ27" s="24" t="n"/>
-      <c r="CK27" s="24" t="n"/>
-      <c r="CL27" s="24" t="n"/>
-      <c r="CM27" s="24" t="n"/>
-      <c r="CN27" s="24" t="n"/>
-      <c r="CO27" s="24" t="n"/>
-      <c r="CP27" s="24" t="n"/>
-      <c r="CQ27" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research/lol.xlsx
+++ b/data/research/lol.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ20" headerRowCount="1">
-  <autoFilter ref="A1:CQ20"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ27" headerRowCount="1">
+  <autoFilter ref="A1:CQ27"/>
   <tableColumns count="95">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -754,19 +754,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$20)</f>
+        <f>COUNTA('Picks'!$A$2:$A$27)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$20,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$27,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$20,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$27,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"win")+COUNTIFS('Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"win")+COUNTIFS('Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +794,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$20,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$27,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$20,"&gt;0",'Picks'!$V$2:$V$20,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$20,"&gt;0",'Picks'!$V$2:$V$20,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$27,"&gt;0",'Picks'!$V$2:$V$27,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$27,"&gt;0",'Picks'!$V$2:$V$27,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$20,"&gt;0",'Picks'!$V$2:$V$20,"win")/(COUNTIFS('Picks'!$BX$2:$BX$20,"&gt;0",'Picks'!$V$2:$V$20,"win")+COUNTIFS('Picks'!$BX$2:$BX$20,"&gt;0",'Picks'!$V$2:$V$20,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$27,"&gt;0",'Picks'!$V$2:$V$27,"win")/(COUNTIFS('Picks'!$BX$2:$BX$27,"&gt;0",'Picks'!$V$2:$V$27,"win")+COUNTIFS('Picks'!$BX$2:$BX$27,"&gt;0",'Picks'!$V$2:$V$27,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$20)/SUM('Picks'!$BX$2:$BX$20),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$27)/SUM('Picks'!$BX$2:$BX$27),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +834,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$20)</f>
+        <f>SUM('Picks'!$BY$2:$BY$27)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$20,"&lt;&gt;",'Picks'!$AB$2:$AB$20),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$27,"&lt;&gt;",'Picks'!$AB$2:$AB$27),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$20,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$20,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$27,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$27,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$20,'Picks'!$AM$2:$AM$20,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$27,'Picks'!$AM$2:$AM$27,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +901,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$20,$A14,'Picks'!$U$2:$U$20,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$27,$A14,'Picks'!$U$2:$U$27,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$20,$A14,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$27,$A14,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$20,$A14,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$27,$A14,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +917,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$20,'Picks'!$H$2:$H$20,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$27,'Picks'!$H$2:$H$27,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$20,'Picks'!$H$2:$H$20,$A14,'Picks'!$U$2:$U$20,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$27,'Picks'!$H$2:$H$27,$A14,'Picks'!$U$2:$U$27,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +932,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$20,$A15,'Picks'!$U$2:$U$20,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$27,$A15,'Picks'!$U$2:$U$27,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$20,$A15,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$27,$A15,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$20,$A15,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$27,$A15,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +948,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$20,'Picks'!$H$2:$H$20,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$27,'Picks'!$H$2:$H$27,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$20,'Picks'!$H$2:$H$20,$A15,'Picks'!$U$2:$U$20,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$27,'Picks'!$H$2:$H$27,$A15,'Picks'!$U$2:$U$27,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +963,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$20,$A16,'Picks'!$U$2:$U$20,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$27,$A16,'Picks'!$U$2:$U$27,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$20,$A16,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$27,$A16,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$20,$A16,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$27,$A16,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +979,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$20,'Picks'!$H$2:$H$20,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$27,'Picks'!$H$2:$H$27,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$20,'Picks'!$H$2:$H$20,$A16,'Picks'!$U$2:$U$20,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$27,'Picks'!$H$2:$H$27,$A16,'Picks'!$U$2:$U$27,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ20"/>
+  <dimension ref="A1:CQ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6549,18 +6549,38 @@
       </c>
       <c r="U19" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V19" s="24" t="n"/>
-      <c r="W19" s="26" t="n"/>
-      <c r="X19" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V19" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W19" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X19" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y19" s="25" t="n"/>
-      <c r="Z19" s="26" t="n"/>
-      <c r="AA19" s="28" t="n"/>
-      <c r="AB19" s="28" t="n"/>
-      <c r="AC19" s="30" t="n"/>
-      <c r="AD19" s="24" t="n"/>
+      <c r="Z19" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="AA19" s="28" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AB19" s="28" t="n">
+        <v>0.000829</v>
+      </c>
+      <c r="AC19" s="30" t="n">
+        <v>0.8547</v>
+      </c>
+      <c r="AD19" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:34:43.910160Z</t>
+        </is>
+      </c>
       <c r="AE19" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-lol-fxw7-lll-2026-08-02).</t>
@@ -6703,8 +6723,12 @@
       <c r="BN19" s="28" t="n"/>
       <c r="BO19" s="28" t="n"/>
       <c r="BP19" s="25" t="n"/>
-      <c r="BQ19" s="27" t="n"/>
-      <c r="BR19" s="28" t="n"/>
+      <c r="BQ19" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="BR19" s="28" t="n">
+        <v>0.54</v>
+      </c>
       <c r="BS19" s="28" t="n"/>
       <c r="BT19" s="28" t="n"/>
       <c r="BU19" s="25" t="n"/>
@@ -7002,6 +7026,1875 @@
         </is>
       </c>
     </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="24" t="inlineStr">
+        <is>
+          <t>d32ace632e1a4343</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:24.510796Z</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="D21" s="24" t="inlineStr">
+        <is>
+          <t>67491</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F21" s="24" t="inlineStr">
+        <is>
+          <t>Hanwha Life Esports</t>
+        </is>
+      </c>
+      <c r="G21" s="24" t="inlineStr">
+        <is>
+          <t>Gen.G</t>
+        </is>
+      </c>
+      <c r="H21" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I21" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J21" s="25" t="n"/>
+      <c r="K21" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L21" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="M21" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="N21" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="O21" s="28" t="n">
+        <v>0.5360740000000001</v>
+      </c>
+      <c r="P21" s="28" t="n"/>
+      <c r="Q21" s="28" t="n">
+        <v>-0.05409</v>
+      </c>
+      <c r="R21" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U21" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V21" s="24" t="n"/>
+      <c r="W21" s="26" t="n"/>
+      <c r="X21" s="26" t="n"/>
+      <c r="Y21" s="25" t="n"/>
+      <c r="Z21" s="26" t="n"/>
+      <c r="AA21" s="28" t="n"/>
+      <c r="AB21" s="28" t="n"/>
+      <c r="AC21" s="30" t="n"/>
+      <c r="AD21" s="24" t="n"/>
+      <c r="AE21" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-lol-gen-hle-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF21" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG21" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH21" s="24" t="n"/>
+      <c r="AI21" s="31" t="n"/>
+      <c r="AJ21" s="31" t="n"/>
+      <c r="AK21" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL21" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM21" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN21" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO21" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP21" s="24" t="inlineStr">
+        <is>
+          <t>Hanwha Life Esports</t>
+        </is>
+      </c>
+      <c r="AQ21" s="24" t="inlineStr">
+        <is>
+          <t>Hanwha Life Esports</t>
+        </is>
+      </c>
+      <c r="AR21" s="24" t="inlineStr">
+        <is>
+          <t>Hanwha Life Esports</t>
+        </is>
+      </c>
+      <c r="AS21" s="24" t="inlineStr">
+        <is>
+          <t>Gen.G</t>
+        </is>
+      </c>
+      <c r="AT21" s="24" t="inlineStr">
+        <is>
+          <t>Gen.G</t>
+        </is>
+      </c>
+      <c r="AU21" s="24" t="inlineStr">
+        <is>
+          <t>Gen.G</t>
+        </is>
+      </c>
+      <c r="AV21" s="24" t="n"/>
+      <c r="AW21" s="24" t="n"/>
+      <c r="AX21" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY21" s="24" t="n"/>
+      <c r="AZ21" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA21" s="24" t="inlineStr">
+        <is>
+          <t>94c9ecefe7862fcd0f8932ee0f8a5cf2fb1ce42b7196a6254eed26b3593462b8</t>
+        </is>
+      </c>
+      <c r="BB21" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC21" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD21" s="24" t="inlineStr">
+        <is>
+          <t>94c9ecefe7862fcd0f8932ee0f8a5cf2fb1ce42b7196a6254eed26b3593462b8</t>
+        </is>
+      </c>
+      <c r="BE21" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF21" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG21" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:16.193695Z</t>
+        </is>
+      </c>
+      <c r="BI21" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ21" s="25" t="n"/>
+      <c r="BK21" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="BL21" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="BM21" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="BN21" s="28" t="n"/>
+      <c r="BO21" s="28" t="n"/>
+      <c r="BP21" s="25" t="n"/>
+      <c r="BQ21" s="27" t="n"/>
+      <c r="BR21" s="28" t="n"/>
+      <c r="BS21" s="28" t="n"/>
+      <c r="BT21" s="28" t="n"/>
+      <c r="BU21" s="25" t="n"/>
+      <c r="BV21" s="29" t="n"/>
+      <c r="BW21" s="24" t="n"/>
+      <c r="BX21" s="30" t="n"/>
+      <c r="BY21" s="27" t="n"/>
+      <c r="BZ21" s="24" t="n"/>
+      <c r="CA21" s="31" t="n"/>
+      <c r="CB21" s="24" t="n"/>
+      <c r="CC21" s="24" t="n"/>
+      <c r="CD21" s="24" t="n"/>
+      <c r="CE21" s="24" t="n"/>
+      <c r="CF21" s="24" t="n"/>
+      <c r="CG21" s="24" t="n"/>
+      <c r="CH21" s="24" t="n"/>
+      <c r="CI21" s="24" t="n"/>
+      <c r="CJ21" s="24" t="n"/>
+      <c r="CK21" s="24" t="n"/>
+      <c r="CL21" s="24" t="n"/>
+      <c r="CM21" s="24" t="n"/>
+      <c r="CN21" s="24" t="n"/>
+      <c r="CO21" s="24" t="n"/>
+      <c r="CP21" s="24" t="n"/>
+      <c r="CQ21" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>1a4e59d2677c4b4f</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:24.510796Z</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>67492</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F22" s="24" t="inlineStr">
+        <is>
+          <t>BNK FearX Youth</t>
+        </is>
+      </c>
+      <c r="G22" s="24" t="inlineStr">
+        <is>
+          <t>HANJIN BRION Challengers</t>
+        </is>
+      </c>
+      <c r="H22" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I22" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J22" s="25" t="n"/>
+      <c r="K22" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L22" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="M22" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="N22" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="O22" s="28" t="n">
+        <v>0.634708</v>
+      </c>
+      <c r="P22" s="28" t="n"/>
+      <c r="Q22" s="28" t="n">
+        <v>-0.055694</v>
+      </c>
+      <c r="R22" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T22" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U22" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V22" s="24" t="n"/>
+      <c r="W22" s="26" t="n"/>
+      <c r="X22" s="26" t="n"/>
+      <c r="Y22" s="25" t="n"/>
+      <c r="Z22" s="26" t="n"/>
+      <c r="AA22" s="28" t="n"/>
+      <c r="AB22" s="28" t="n"/>
+      <c r="AC22" s="30" t="n"/>
+      <c r="AD22" s="24" t="n"/>
+      <c r="AE22" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-lol-hbc-foxy-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF22" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG22" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH22" s="24" t="n"/>
+      <c r="AI22" s="31" t="n"/>
+      <c r="AJ22" s="31" t="n"/>
+      <c r="AK22" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL22" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM22" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN22" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO22" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP22" s="24" t="inlineStr">
+        <is>
+          <t>BNK FearX Youth</t>
+        </is>
+      </c>
+      <c r="AQ22" s="24" t="inlineStr">
+        <is>
+          <t>BNK FearX Youth</t>
+        </is>
+      </c>
+      <c r="AR22" s="24" t="inlineStr">
+        <is>
+          <t>BNK FearX Youth</t>
+        </is>
+      </c>
+      <c r="AS22" s="24" t="inlineStr">
+        <is>
+          <t>HANJIN BRION Challengers</t>
+        </is>
+      </c>
+      <c r="AT22" s="24" t="inlineStr">
+        <is>
+          <t>HANJIN BRION Challengers</t>
+        </is>
+      </c>
+      <c r="AU22" s="24" t="inlineStr">
+        <is>
+          <t>HANJIN BRION Challengers</t>
+        </is>
+      </c>
+      <c r="AV22" s="24" t="n"/>
+      <c r="AW22" s="24" t="n"/>
+      <c r="AX22" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY22" s="24" t="n"/>
+      <c r="AZ22" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA22" s="24" t="inlineStr">
+        <is>
+          <t>94c9ecefe7862fcd0f8932ee0f8a5cf2fb1ce42b7196a6254eed26b3593462b8</t>
+        </is>
+      </c>
+      <c r="BB22" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC22" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD22" s="24" t="inlineStr">
+        <is>
+          <t>94c9ecefe7862fcd0f8932ee0f8a5cf2fb1ce42b7196a6254eed26b3593462b8</t>
+        </is>
+      </c>
+      <c r="BE22" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF22" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG22" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:16.786728Z</t>
+        </is>
+      </c>
+      <c r="BI22" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ22" s="25" t="n"/>
+      <c r="BK22" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="BL22" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="BM22" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="BN22" s="28" t="n"/>
+      <c r="BO22" s="28" t="n"/>
+      <c r="BP22" s="25" t="n"/>
+      <c r="BQ22" s="27" t="n"/>
+      <c r="BR22" s="28" t="n"/>
+      <c r="BS22" s="28" t="n"/>
+      <c r="BT22" s="28" t="n"/>
+      <c r="BU22" s="25" t="n"/>
+      <c r="BV22" s="29" t="n"/>
+      <c r="BW22" s="24" t="n"/>
+      <c r="BX22" s="30" t="n"/>
+      <c r="BY22" s="27" t="n"/>
+      <c r="BZ22" s="24" t="n"/>
+      <c r="CA22" s="31" t="n"/>
+      <c r="CB22" s="24" t="n"/>
+      <c r="CC22" s="24" t="n"/>
+      <c r="CD22" s="24" t="n"/>
+      <c r="CE22" s="24" t="n"/>
+      <c r="CF22" s="24" t="n"/>
+      <c r="CG22" s="24" t="n"/>
+      <c r="CH22" s="24" t="n"/>
+      <c r="CI22" s="24" t="n"/>
+      <c r="CJ22" s="24" t="n"/>
+      <c r="CK22" s="24" t="n"/>
+      <c r="CL22" s="24" t="n"/>
+      <c r="CM22" s="24" t="n"/>
+      <c r="CN22" s="24" t="n"/>
+      <c r="CO22" s="24" t="n"/>
+      <c r="CP22" s="24" t="n"/>
+      <c r="CQ22" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="24" t="inlineStr">
+        <is>
+          <t>9de7c0b55556414c</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:24.510796Z</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="D23" s="24" t="inlineStr">
+        <is>
+          <t>67511</t>
+        </is>
+      </c>
+      <c r="E23" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F23" s="24" t="inlineStr">
+        <is>
+          <t>Dplus KIA Challengers</t>
+        </is>
+      </c>
+      <c r="G23" s="24" t="inlineStr">
+        <is>
+          <t>DN SOOPers Challengers</t>
+        </is>
+      </c>
+      <c r="H23" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I23" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J23" s="25" t="n"/>
+      <c r="K23" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L23" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="M23" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="N23" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="O23" s="28" t="n">
+        <v>0.70331</v>
+      </c>
+      <c r="P23" s="28" t="n"/>
+      <c r="Q23" s="28" t="n">
+        <v>0.012908</v>
+      </c>
+      <c r="R23" s="26" t="n">
+        <v>26</v>
+      </c>
+      <c r="S23" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T23" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U23" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V23" s="24" t="n"/>
+      <c r="W23" s="26" t="n"/>
+      <c r="X23" s="26" t="n"/>
+      <c r="Y23" s="25" t="n"/>
+      <c r="Z23" s="26" t="n"/>
+      <c r="AA23" s="28" t="n"/>
+      <c r="AB23" s="28" t="n"/>
+      <c r="AC23" s="30" t="n"/>
+      <c r="AD23" s="24" t="n"/>
+      <c r="AE23" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-lol-dnsc-dkc-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF23" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG23" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH23" s="24" t="n"/>
+      <c r="AI23" s="31" t="n"/>
+      <c r="AJ23" s="31" t="n"/>
+      <c r="AK23" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL23" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM23" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN23" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO23" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP23" s="24" t="inlineStr">
+        <is>
+          <t>Dplus KIA Challengers</t>
+        </is>
+      </c>
+      <c r="AQ23" s="24" t="inlineStr">
+        <is>
+          <t>Dplus KIA Challengers</t>
+        </is>
+      </c>
+      <c r="AR23" s="24" t="inlineStr">
+        <is>
+          <t>Dplus KIA Challengers</t>
+        </is>
+      </c>
+      <c r="AS23" s="24" t="inlineStr">
+        <is>
+          <t>DN SOOPers Challengers</t>
+        </is>
+      </c>
+      <c r="AT23" s="24" t="inlineStr">
+        <is>
+          <t>DN SOOPers Challengers</t>
+        </is>
+      </c>
+      <c r="AU23" s="24" t="inlineStr">
+        <is>
+          <t>DN SOOPers Challengers</t>
+        </is>
+      </c>
+      <c r="AV23" s="24" t="n"/>
+      <c r="AW23" s="24" t="n"/>
+      <c r="AX23" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY23" s="24" t="n"/>
+      <c r="AZ23" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA23" s="24" t="inlineStr">
+        <is>
+          <t>94c9ecefe7862fcd0f8932ee0f8a5cf2fb1ce42b7196a6254eed26b3593462b8</t>
+        </is>
+      </c>
+      <c r="BB23" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC23" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD23" s="24" t="inlineStr">
+        <is>
+          <t>94c9ecefe7862fcd0f8932ee0f8a5cf2fb1ce42b7196a6254eed26b3593462b8</t>
+        </is>
+      </c>
+      <c r="BE23" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF23" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG23" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:17.281478Z</t>
+        </is>
+      </c>
+      <c r="BI23" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ23" s="25" t="n"/>
+      <c r="BK23" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="BL23" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="BM23" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="BN23" s="28" t="n"/>
+      <c r="BO23" s="28" t="n"/>
+      <c r="BP23" s="25" t="n"/>
+      <c r="BQ23" s="27" t="n"/>
+      <c r="BR23" s="28" t="n"/>
+      <c r="BS23" s="28" t="n"/>
+      <c r="BT23" s="28" t="n"/>
+      <c r="BU23" s="25" t="n"/>
+      <c r="BV23" s="29" t="n"/>
+      <c r="BW23" s="24" t="n"/>
+      <c r="BX23" s="30" t="n"/>
+      <c r="BY23" s="27" t="n"/>
+      <c r="BZ23" s="24" t="n"/>
+      <c r="CA23" s="31" t="n"/>
+      <c r="CB23" s="24" t="n"/>
+      <c r="CC23" s="24" t="n"/>
+      <c r="CD23" s="24" t="n"/>
+      <c r="CE23" s="24" t="n"/>
+      <c r="CF23" s="24" t="n"/>
+      <c r="CG23" s="24" t="n"/>
+      <c r="CH23" s="24" t="n"/>
+      <c r="CI23" s="24" t="n"/>
+      <c r="CJ23" s="24" t="n"/>
+      <c r="CK23" s="24" t="n"/>
+      <c r="CL23" s="24" t="n"/>
+      <c r="CM23" s="24" t="n"/>
+      <c r="CN23" s="24" t="n"/>
+      <c r="CO23" s="24" t="n"/>
+      <c r="CP23" s="24" t="n"/>
+      <c r="CQ23" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>82603ddeb58f4a47</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:24.510796Z</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="D24" s="24" t="inlineStr">
+        <is>
+          <t>67515</t>
+        </is>
+      </c>
+      <c r="E24" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F24" s="24" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="G24" s="24" t="inlineStr">
+        <is>
+          <t>Nongshim Red Force</t>
+        </is>
+      </c>
+      <c r="H24" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I24" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J24" s="25" t="n"/>
+      <c r="K24" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L24" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="M24" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="N24" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="O24" s="28" t="n">
+        <v>0.746406</v>
+      </c>
+      <c r="P24" s="28" t="n"/>
+      <c r="Q24" s="28" t="n">
+        <v>0.137031</v>
+      </c>
+      <c r="R24" s="26" t="n">
+        <v>89</v>
+      </c>
+      <c r="S24" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T24" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U24" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V24" s="24" t="n"/>
+      <c r="W24" s="26" t="n"/>
+      <c r="X24" s="26" t="n"/>
+      <c r="Y24" s="25" t="n"/>
+      <c r="Z24" s="26" t="n"/>
+      <c r="AA24" s="28" t="n"/>
+      <c r="AB24" s="28" t="n"/>
+      <c r="AC24" s="30" t="n"/>
+      <c r="AD24" s="24" t="n"/>
+      <c r="AE24" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-lol-ns-t1-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF24" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG24" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH24" s="24" t="n"/>
+      <c r="AI24" s="31" t="n"/>
+      <c r="AJ24" s="31" t="n"/>
+      <c r="AK24" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL24" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM24" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN24" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO24" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP24" s="24" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="AQ24" s="24" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="AR24" s="24" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="AS24" s="24" t="inlineStr">
+        <is>
+          <t>Nongshim Red Force</t>
+        </is>
+      </c>
+      <c r="AT24" s="24" t="inlineStr">
+        <is>
+          <t>Nongshim Red Force</t>
+        </is>
+      </c>
+      <c r="AU24" s="24" t="inlineStr">
+        <is>
+          <t>Nongshim Red Force</t>
+        </is>
+      </c>
+      <c r="AV24" s="24" t="n"/>
+      <c r="AW24" s="24" t="n"/>
+      <c r="AX24" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY24" s="24" t="n"/>
+      <c r="AZ24" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA24" s="24" t="inlineStr">
+        <is>
+          <t>94c9ecefe7862fcd0f8932ee0f8a5cf2fb1ce42b7196a6254eed26b3593462b8</t>
+        </is>
+      </c>
+      <c r="BB24" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC24" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD24" s="24" t="inlineStr">
+        <is>
+          <t>94c9ecefe7862fcd0f8932ee0f8a5cf2fb1ce42b7196a6254eed26b3593462b8</t>
+        </is>
+      </c>
+      <c r="BE24" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF24" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG24" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:17.851259Z</t>
+        </is>
+      </c>
+      <c r="BI24" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ24" s="25" t="n"/>
+      <c r="BK24" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="BL24" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="BM24" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="BN24" s="28" t="n"/>
+      <c r="BO24" s="28" t="n"/>
+      <c r="BP24" s="25" t="n"/>
+      <c r="BQ24" s="27" t="n"/>
+      <c r="BR24" s="28" t="n"/>
+      <c r="BS24" s="28" t="n"/>
+      <c r="BT24" s="28" t="n"/>
+      <c r="BU24" s="25" t="n"/>
+      <c r="BV24" s="29" t="n"/>
+      <c r="BW24" s="24" t="n"/>
+      <c r="BX24" s="30" t="n"/>
+      <c r="BY24" s="27" t="n"/>
+      <c r="BZ24" s="24" t="n"/>
+      <c r="CA24" s="31" t="n"/>
+      <c r="CB24" s="24" t="n"/>
+      <c r="CC24" s="24" t="n"/>
+      <c r="CD24" s="24" t="n"/>
+      <c r="CE24" s="24" t="n"/>
+      <c r="CF24" s="24" t="n"/>
+      <c r="CG24" s="24" t="n"/>
+      <c r="CH24" s="24" t="n"/>
+      <c r="CI24" s="24" t="n"/>
+      <c r="CJ24" s="24" t="n"/>
+      <c r="CK24" s="24" t="n"/>
+      <c r="CL24" s="24" t="n"/>
+      <c r="CM24" s="24" t="n"/>
+      <c r="CN24" s="24" t="n"/>
+      <c r="CO24" s="24" t="n"/>
+      <c r="CP24" s="24" t="n"/>
+      <c r="CQ24" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>f17d1384a79e4e47</t>
+        </is>
+      </c>
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:24.510796Z</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D25" s="24" t="inlineStr">
+        <is>
+          <t>67566</t>
+        </is>
+      </c>
+      <c r="E25" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F25" s="24" t="inlineStr">
+        <is>
+          <t>Shifters</t>
+        </is>
+      </c>
+      <c r="G25" s="24" t="inlineStr">
+        <is>
+          <t>Natus Vincere</t>
+        </is>
+      </c>
+      <c r="H25" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I25" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J25" s="25" t="n"/>
+      <c r="K25" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L25" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="M25" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="N25" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="O25" s="28" t="n">
+        <v>0.746125</v>
+      </c>
+      <c r="P25" s="28" t="n"/>
+      <c r="Q25" s="28" t="n">
+        <v>0.046425</v>
+      </c>
+      <c r="R25" s="26" t="n">
+        <v>43</v>
+      </c>
+      <c r="S25" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T25" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U25" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V25" s="24" t="n"/>
+      <c r="W25" s="26" t="n"/>
+      <c r="X25" s="26" t="n"/>
+      <c r="Y25" s="25" t="n"/>
+      <c r="Z25" s="26" t="n"/>
+      <c r="AA25" s="28" t="n"/>
+      <c r="AB25" s="28" t="n"/>
+      <c r="AC25" s="30" t="n"/>
+      <c r="AD25" s="24" t="n"/>
+      <c r="AE25" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-lol-navi-shft-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF25" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG25" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH25" s="24" t="n"/>
+      <c r="AI25" s="31" t="n"/>
+      <c r="AJ25" s="31" t="n"/>
+      <c r="AK25" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL25" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM25" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN25" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO25" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP25" s="24" t="inlineStr">
+        <is>
+          <t>Shifters</t>
+        </is>
+      </c>
+      <c r="AQ25" s="24" t="inlineStr">
+        <is>
+          <t>Shifters</t>
+        </is>
+      </c>
+      <c r="AR25" s="24" t="inlineStr">
+        <is>
+          <t>Shifters</t>
+        </is>
+      </c>
+      <c r="AS25" s="24" t="inlineStr">
+        <is>
+          <t>Natus Vincere</t>
+        </is>
+      </c>
+      <c r="AT25" s="24" t="inlineStr">
+        <is>
+          <t>Natus Vincere</t>
+        </is>
+      </c>
+      <c r="AU25" s="24" t="inlineStr">
+        <is>
+          <t>Natus Vincere</t>
+        </is>
+      </c>
+      <c r="AV25" s="24" t="n"/>
+      <c r="AW25" s="24" t="n"/>
+      <c r="AX25" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY25" s="24" t="n"/>
+      <c r="AZ25" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA25" s="24" t="inlineStr">
+        <is>
+          <t>94c9ecefe7862fcd0f8932ee0f8a5cf2fb1ce42b7196a6254eed26b3593462b8</t>
+        </is>
+      </c>
+      <c r="BB25" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC25" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD25" s="24" t="inlineStr">
+        <is>
+          <t>94c9ecefe7862fcd0f8932ee0f8a5cf2fb1ce42b7196a6254eed26b3593462b8</t>
+        </is>
+      </c>
+      <c r="BE25" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF25" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG25" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:18.386531Z</t>
+        </is>
+      </c>
+      <c r="BI25" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ25" s="25" t="n"/>
+      <c r="BK25" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="BL25" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="BM25" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="BN25" s="28" t="n"/>
+      <c r="BO25" s="28" t="n"/>
+      <c r="BP25" s="25" t="n"/>
+      <c r="BQ25" s="27" t="n"/>
+      <c r="BR25" s="28" t="n"/>
+      <c r="BS25" s="28" t="n"/>
+      <c r="BT25" s="28" t="n"/>
+      <c r="BU25" s="25" t="n"/>
+      <c r="BV25" s="29" t="n"/>
+      <c r="BW25" s="24" t="n"/>
+      <c r="BX25" s="30" t="n"/>
+      <c r="BY25" s="27" t="n"/>
+      <c r="BZ25" s="24" t="n"/>
+      <c r="CA25" s="31" t="n"/>
+      <c r="CB25" s="24" t="n"/>
+      <c r="CC25" s="24" t="n"/>
+      <c r="CD25" s="24" t="n"/>
+      <c r="CE25" s="24" t="n"/>
+      <c r="CF25" s="24" t="n"/>
+      <c r="CG25" s="24" t="n"/>
+      <c r="CH25" s="24" t="n"/>
+      <c r="CI25" s="24" t="n"/>
+      <c r="CJ25" s="24" t="n"/>
+      <c r="CK25" s="24" t="n"/>
+      <c r="CL25" s="24" t="n"/>
+      <c r="CM25" s="24" t="n"/>
+      <c r="CN25" s="24" t="n"/>
+      <c r="CO25" s="24" t="n"/>
+      <c r="CP25" s="24" t="n"/>
+      <c r="CQ25" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>83da637bf20f41b9</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:24.510796Z</t>
+        </is>
+      </c>
+      <c r="C26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="D26" s="24" t="inlineStr">
+        <is>
+          <t>67937</t>
+        </is>
+      </c>
+      <c r="E26" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F26" s="24" t="inlineStr">
+        <is>
+          <t>Docta Esports</t>
+        </is>
+      </c>
+      <c r="G26" s="24" t="inlineStr">
+        <is>
+          <t>Volticons</t>
+        </is>
+      </c>
+      <c r="H26" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I26" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J26" s="25" t="n"/>
+      <c r="K26" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L26" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="M26" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="N26" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="O26" s="28" t="n">
+        <v>0.649195</v>
+      </c>
+      <c r="P26" s="28" t="n"/>
+      <c r="Q26" s="28" t="n">
+        <v>0.059031</v>
+      </c>
+      <c r="R26" s="26" t="n">
+        <v>50</v>
+      </c>
+      <c r="S26" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T26" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U26" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V26" s="24" t="n"/>
+      <c r="W26" s="26" t="n"/>
+      <c r="X26" s="26" t="n"/>
+      <c r="Y26" s="25" t="n"/>
+      <c r="Z26" s="26" t="n"/>
+      <c r="AA26" s="28" t="n"/>
+      <c r="AB26" s="28" t="n"/>
+      <c r="AC26" s="30" t="n"/>
+      <c r="AD26" s="24" t="n"/>
+      <c r="AE26" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-lol-vtc-doh-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF26" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG26" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH26" s="24" t="n"/>
+      <c r="AI26" s="31" t="n"/>
+      <c r="AJ26" s="31" t="n"/>
+      <c r="AK26" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL26" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM26" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN26" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO26" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP26" s="24" t="inlineStr">
+        <is>
+          <t>Docta Esports</t>
+        </is>
+      </c>
+      <c r="AQ26" s="24" t="inlineStr">
+        <is>
+          <t>Docta Esports</t>
+        </is>
+      </c>
+      <c r="AR26" s="24" t="inlineStr">
+        <is>
+          <t>Docta Esports</t>
+        </is>
+      </c>
+      <c r="AS26" s="24" t="inlineStr">
+        <is>
+          <t>Volticons</t>
+        </is>
+      </c>
+      <c r="AT26" s="24" t="inlineStr">
+        <is>
+          <t>Volticons</t>
+        </is>
+      </c>
+      <c r="AU26" s="24" t="inlineStr">
+        <is>
+          <t>Volticons</t>
+        </is>
+      </c>
+      <c r="AV26" s="24" t="n"/>
+      <c r="AW26" s="24" t="n"/>
+      <c r="AX26" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY26" s="24" t="n"/>
+      <c r="AZ26" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA26" s="24" t="inlineStr">
+        <is>
+          <t>94c9ecefe7862fcd0f8932ee0f8a5cf2fb1ce42b7196a6254eed26b3593462b8</t>
+        </is>
+      </c>
+      <c r="BB26" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC26" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD26" s="24" t="inlineStr">
+        <is>
+          <t>94c9ecefe7862fcd0f8932ee0f8a5cf2fb1ce42b7196a6254eed26b3593462b8</t>
+        </is>
+      </c>
+      <c r="BE26" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF26" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG26" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:21.959634Z</t>
+        </is>
+      </c>
+      <c r="BI26" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ26" s="25" t="n"/>
+      <c r="BK26" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="BL26" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="BM26" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="BN26" s="28" t="n"/>
+      <c r="BO26" s="28" t="n"/>
+      <c r="BP26" s="25" t="n"/>
+      <c r="BQ26" s="27" t="n"/>
+      <c r="BR26" s="28" t="n"/>
+      <c r="BS26" s="28" t="n"/>
+      <c r="BT26" s="28" t="n"/>
+      <c r="BU26" s="25" t="n"/>
+      <c r="BV26" s="29" t="n"/>
+      <c r="BW26" s="24" t="n"/>
+      <c r="BX26" s="30" t="n"/>
+      <c r="BY26" s="27" t="n"/>
+      <c r="BZ26" s="24" t="n"/>
+      <c r="CA26" s="31" t="n"/>
+      <c r="CB26" s="24" t="n"/>
+      <c r="CC26" s="24" t="n"/>
+      <c r="CD26" s="24" t="n"/>
+      <c r="CE26" s="24" t="n"/>
+      <c r="CF26" s="24" t="n"/>
+      <c r="CG26" s="24" t="n"/>
+      <c r="CH26" s="24" t="n"/>
+      <c r="CI26" s="24" t="n"/>
+      <c r="CJ26" s="24" t="n"/>
+      <c r="CK26" s="24" t="n"/>
+      <c r="CL26" s="24" t="n"/>
+      <c r="CM26" s="24" t="n"/>
+      <c r="CN26" s="24" t="n"/>
+      <c r="CO26" s="24" t="n"/>
+      <c r="CP26" s="24" t="n"/>
+      <c r="CQ26" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>727ef0630f6b4470</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:24.510796Z</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="D27" s="24" t="inlineStr">
+        <is>
+          <t>68011</t>
+        </is>
+      </c>
+      <c r="E27" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F27" s="24" t="inlineStr">
+        <is>
+          <t>Vivo Keyd Stars Academy</t>
+        </is>
+      </c>
+      <c r="G27" s="24" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="H27" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I27" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J27" s="25" t="n"/>
+      <c r="K27" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L27" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="M27" s="27" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="N27" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="O27" s="28" t="n">
+        <v>0.502316</v>
+      </c>
+      <c r="P27" s="28" t="n"/>
+      <c r="Q27" s="28" t="n">
+        <v>-0.016915</v>
+      </c>
+      <c r="R27" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="S27" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U27" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V27" s="24" t="n"/>
+      <c r="W27" s="26" t="n"/>
+      <c r="X27" s="26" t="n"/>
+      <c r="Y27" s="25" t="n"/>
+      <c r="Z27" s="26" t="n"/>
+      <c r="AA27" s="28" t="n"/>
+      <c r="AB27" s="28" t="n"/>
+      <c r="AC27" s="30" t="n"/>
+      <c r="AD27" s="24" t="n"/>
+      <c r="AE27" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5200 (market_slug=aec-lol-pnga-vksa-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF27" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG27" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH27" s="24" t="n"/>
+      <c r="AI27" s="31" t="n"/>
+      <c r="AJ27" s="31" t="n"/>
+      <c r="AK27" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL27" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM27" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN27" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO27" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP27" s="24" t="inlineStr">
+        <is>
+          <t>Vivo Keyd Stars Academy</t>
+        </is>
+      </c>
+      <c r="AQ27" s="24" t="inlineStr">
+        <is>
+          <t>Vivo Keyd Stars Academy</t>
+        </is>
+      </c>
+      <c r="AR27" s="24" t="inlineStr">
+        <is>
+          <t>Vivo Keyd Stars Academy</t>
+        </is>
+      </c>
+      <c r="AS27" s="24" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="AT27" s="24" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="AU27" s="24" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="AV27" s="24" t="n"/>
+      <c r="AW27" s="24" t="n"/>
+      <c r="AX27" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY27" s="24" t="n"/>
+      <c r="AZ27" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA27" s="24" t="inlineStr">
+        <is>
+          <t>94c9ecefe7862fcd0f8932ee0f8a5cf2fb1ce42b7196a6254eed26b3593462b8</t>
+        </is>
+      </c>
+      <c r="BB27" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC27" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD27" s="24" t="inlineStr">
+        <is>
+          <t>94c9ecefe7862fcd0f8932ee0f8a5cf2fb1ce42b7196a6254eed26b3593462b8</t>
+        </is>
+      </c>
+      <c r="BE27" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF27" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG27" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:23.429810Z</t>
+        </is>
+      </c>
+      <c r="BI27" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ27" s="25" t="n"/>
+      <c r="BK27" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="BL27" s="27" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="BM27" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="BN27" s="28" t="n"/>
+      <c r="BO27" s="28" t="n"/>
+      <c r="BP27" s="25" t="n"/>
+      <c r="BQ27" s="27" t="n"/>
+      <c r="BR27" s="28" t="n"/>
+      <c r="BS27" s="28" t="n"/>
+      <c r="BT27" s="28" t="n"/>
+      <c r="BU27" s="25" t="n"/>
+      <c r="BV27" s="29" t="n"/>
+      <c r="BW27" s="24" t="n"/>
+      <c r="BX27" s="30" t="n"/>
+      <c r="BY27" s="27" t="n"/>
+      <c r="BZ27" s="24" t="n"/>
+      <c r="CA27" s="31" t="n"/>
+      <c r="CB27" s="24" t="n"/>
+      <c r="CC27" s="24" t="n"/>
+      <c r="CD27" s="24" t="n"/>
+      <c r="CE27" s="24" t="n"/>
+      <c r="CF27" s="24" t="n"/>
+      <c r="CG27" s="24" t="n"/>
+      <c r="CH27" s="24" t="n"/>
+      <c r="CI27" s="24" t="n"/>
+      <c r="CJ27" s="24" t="n"/>
+      <c r="CK27" s="24" t="n"/>
+      <c r="CL27" s="24" t="n"/>
+      <c r="CM27" s="24" t="n"/>
+      <c r="CN27" s="24" t="n"/>
+      <c r="CO27" s="24" t="n"/>
+      <c r="CP27" s="24" t="n"/>
+      <c r="CQ27" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research/lol.xlsx
+++ b/data/research/lol.xlsx
@@ -7029,12 +7029,12 @@
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="24" t="inlineStr">
         <is>
-          <t>d32ace632e1a4343</t>
+          <t>22b68a8702f04658</t>
         </is>
       </c>
       <c r="B21" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:24.510796Z</t>
+          <t>2026-08-02T18:12:25.393675Z</t>
         </is>
       </c>
       <c r="C21" s="24" t="inlineStr">
@@ -7205,7 +7205,7 @@
       </c>
       <c r="BA21" s="24" t="inlineStr">
         <is>
-          <t>94c9ecefe7862fcd0f8932ee0f8a5cf2fb1ce42b7196a6254eed26b3593462b8</t>
+          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
         </is>
       </c>
       <c r="BB21" s="24" t="inlineStr">
@@ -7220,7 +7220,7 @@
       </c>
       <c r="BD21" s="24" t="inlineStr">
         <is>
-          <t>94c9ecefe7862fcd0f8932ee0f8a5cf2fb1ce42b7196a6254eed26b3593462b8</t>
+          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
         </is>
       </c>
       <c r="BE21" s="24" t="inlineStr">
@@ -7240,7 +7240,7 @@
       </c>
       <c r="BH21" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:16.193695Z</t>
+          <t>2026-08-02T18:12:16.992475Z</t>
         </is>
       </c>
       <c r="BI21" s="24" t="inlineStr">
@@ -7296,12 +7296,12 @@
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="24" t="inlineStr">
         <is>
-          <t>1a4e59d2677c4b4f</t>
+          <t>faf62962167c465b</t>
         </is>
       </c>
       <c r="B22" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:24.510796Z</t>
+          <t>2026-08-02T18:12:25.393675Z</t>
         </is>
       </c>
       <c r="C22" s="24" t="inlineStr">
@@ -7472,7 +7472,7 @@
       </c>
       <c r="BA22" s="24" t="inlineStr">
         <is>
-          <t>94c9ecefe7862fcd0f8932ee0f8a5cf2fb1ce42b7196a6254eed26b3593462b8</t>
+          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
         </is>
       </c>
       <c r="BB22" s="24" t="inlineStr">
@@ -7487,7 +7487,7 @@
       </c>
       <c r="BD22" s="24" t="inlineStr">
         <is>
-          <t>94c9ecefe7862fcd0f8932ee0f8a5cf2fb1ce42b7196a6254eed26b3593462b8</t>
+          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
         </is>
       </c>
       <c r="BE22" s="24" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="BH22" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:16.786728Z</t>
+          <t>2026-08-02T18:12:17.534127Z</t>
         </is>
       </c>
       <c r="BI22" s="24" t="inlineStr">
@@ -7563,12 +7563,12 @@
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="24" t="inlineStr">
         <is>
-          <t>9de7c0b55556414c</t>
+          <t>a4670ac2154d4957</t>
         </is>
       </c>
       <c r="B23" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:24.510796Z</t>
+          <t>2026-08-02T18:12:25.393675Z</t>
         </is>
       </c>
       <c r="C23" s="24" t="inlineStr">
@@ -7739,7 +7739,7 @@
       </c>
       <c r="BA23" s="24" t="inlineStr">
         <is>
-          <t>94c9ecefe7862fcd0f8932ee0f8a5cf2fb1ce42b7196a6254eed26b3593462b8</t>
+          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
         </is>
       </c>
       <c r="BB23" s="24" t="inlineStr">
@@ -7754,7 +7754,7 @@
       </c>
       <c r="BD23" s="24" t="inlineStr">
         <is>
-          <t>94c9ecefe7862fcd0f8932ee0f8a5cf2fb1ce42b7196a6254eed26b3593462b8</t>
+          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
         </is>
       </c>
       <c r="BE23" s="24" t="inlineStr">
@@ -7774,7 +7774,7 @@
       </c>
       <c r="BH23" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:17.281478Z</t>
+          <t>2026-08-02T18:12:18.085863Z</t>
         </is>
       </c>
       <c r="BI23" s="24" t="inlineStr">
@@ -7830,12 +7830,12 @@
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="24" t="inlineStr">
         <is>
-          <t>82603ddeb58f4a47</t>
+          <t>0d113f85cca94270</t>
         </is>
       </c>
       <c r="B24" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:24.510796Z</t>
+          <t>2026-08-02T18:12:25.393675Z</t>
         </is>
       </c>
       <c r="C24" s="24" t="inlineStr">
@@ -8006,7 +8006,7 @@
       </c>
       <c r="BA24" s="24" t="inlineStr">
         <is>
-          <t>94c9ecefe7862fcd0f8932ee0f8a5cf2fb1ce42b7196a6254eed26b3593462b8</t>
+          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
         </is>
       </c>
       <c r="BB24" s="24" t="inlineStr">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="BD24" s="24" t="inlineStr">
         <is>
-          <t>94c9ecefe7862fcd0f8932ee0f8a5cf2fb1ce42b7196a6254eed26b3593462b8</t>
+          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
         </is>
       </c>
       <c r="BE24" s="24" t="inlineStr">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="BH24" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:17.851259Z</t>
+          <t>2026-08-02T18:12:18.584911Z</t>
         </is>
       </c>
       <c r="BI24" s="24" t="inlineStr">
@@ -8097,12 +8097,12 @@
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="24" t="inlineStr">
         <is>
-          <t>f17d1384a79e4e47</t>
+          <t>e91560b32ac84323</t>
         </is>
       </c>
       <c r="B25" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:24.510796Z</t>
+          <t>2026-08-02T18:12:25.393675Z</t>
         </is>
       </c>
       <c r="C25" s="24" t="inlineStr">
@@ -8273,7 +8273,7 @@
       </c>
       <c r="BA25" s="24" t="inlineStr">
         <is>
-          <t>94c9ecefe7862fcd0f8932ee0f8a5cf2fb1ce42b7196a6254eed26b3593462b8</t>
+          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
         </is>
       </c>
       <c r="BB25" s="24" t="inlineStr">
@@ -8288,7 +8288,7 @@
       </c>
       <c r="BD25" s="24" t="inlineStr">
         <is>
-          <t>94c9ecefe7862fcd0f8932ee0f8a5cf2fb1ce42b7196a6254eed26b3593462b8</t>
+          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
         </is>
       </c>
       <c r="BE25" s="24" t="inlineStr">
@@ -8308,7 +8308,7 @@
       </c>
       <c r="BH25" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:18.386531Z</t>
+          <t>2026-08-02T18:12:19.163906Z</t>
         </is>
       </c>
       <c r="BI25" s="24" t="inlineStr">
@@ -8364,12 +8364,12 @@
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="24" t="inlineStr">
         <is>
-          <t>83da637bf20f41b9</t>
+          <t>657186cb61214e6c</t>
         </is>
       </c>
       <c r="B26" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:24.510796Z</t>
+          <t>2026-08-02T18:12:25.393675Z</t>
         </is>
       </c>
       <c r="C26" s="24" t="inlineStr">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="BA26" s="24" t="inlineStr">
         <is>
-          <t>94c9ecefe7862fcd0f8932ee0f8a5cf2fb1ce42b7196a6254eed26b3593462b8</t>
+          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
         </is>
       </c>
       <c r="BB26" s="24" t="inlineStr">
@@ -8555,7 +8555,7 @@
       </c>
       <c r="BD26" s="24" t="inlineStr">
         <is>
-          <t>94c9ecefe7862fcd0f8932ee0f8a5cf2fb1ce42b7196a6254eed26b3593462b8</t>
+          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
         </is>
       </c>
       <c r="BE26" s="24" t="inlineStr">
@@ -8575,7 +8575,7 @@
       </c>
       <c r="BH26" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:21.959634Z</t>
+          <t>2026-08-02T18:12:22.895388Z</t>
         </is>
       </c>
       <c r="BI26" s="24" t="inlineStr">
@@ -8631,12 +8631,12 @@
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="24" t="inlineStr">
         <is>
-          <t>727ef0630f6b4470</t>
+          <t>35d450cb7d394ddc</t>
         </is>
       </c>
       <c r="B27" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:24.510796Z</t>
+          <t>2026-08-02T18:12:25.393675Z</t>
         </is>
       </c>
       <c r="C27" s="24" t="inlineStr">
@@ -8681,23 +8681,23 @@
         </is>
       </c>
       <c r="L27" s="26" t="n">
-        <v>-108</v>
+        <v>-104</v>
       </c>
       <c r="M27" s="27" t="n">
-        <v>1.925926</v>
+        <v>1.961538</v>
       </c>
       <c r="N27" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.509804</v>
       </c>
       <c r="O27" s="28" t="n">
         <v>0.502316</v>
       </c>
       <c r="P27" s="28" t="n"/>
       <c r="Q27" s="28" t="n">
-        <v>-0.016915</v>
+        <v>-0.007488</v>
       </c>
       <c r="R27" s="26" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="S27" s="29" t="n">
         <v>1</v>
@@ -8723,7 +8723,7 @@
       <c r="AD27" s="24" t="n"/>
       <c r="AE27" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5200 (market_slug=aec-lol-pnga-vksa-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-lol-pnga-vksa-2026-08-03).</t>
         </is>
       </c>
       <c r="AF27" s="31" t="inlineStr">
@@ -8807,7 +8807,7 @@
       </c>
       <c r="BA27" s="24" t="inlineStr">
         <is>
-          <t>94c9ecefe7862fcd0f8932ee0f8a5cf2fb1ce42b7196a6254eed26b3593462b8</t>
+          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
         </is>
       </c>
       <c r="BB27" s="24" t="inlineStr">
@@ -8822,7 +8822,7 @@
       </c>
       <c r="BD27" s="24" t="inlineStr">
         <is>
-          <t>94c9ecefe7862fcd0f8932ee0f8a5cf2fb1ce42b7196a6254eed26b3593462b8</t>
+          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
         </is>
       </c>
       <c r="BE27" s="24" t="inlineStr">
@@ -8842,7 +8842,7 @@
       </c>
       <c r="BH27" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:23.429810Z</t>
+          <t>2026-08-02T18:12:24.464493Z</t>
         </is>
       </c>
       <c r="BI27" s="24" t="inlineStr">
@@ -8852,13 +8852,13 @@
       </c>
       <c r="BJ27" s="25" t="n"/>
       <c r="BK27" s="26" t="n">
-        <v>-108</v>
+        <v>-104</v>
       </c>
       <c r="BL27" s="27" t="n">
-        <v>1.925926</v>
+        <v>1.961538</v>
       </c>
       <c r="BM27" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.509804</v>
       </c>
       <c r="BN27" s="28" t="n"/>
       <c r="BO27" s="28" t="n"/>

--- a/data/research/lol.xlsx
+++ b/data/research/lol.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ27" headerRowCount="1">
-  <autoFilter ref="A1:CQ27"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ20" headerRowCount="1">
+  <autoFilter ref="A1:CQ20"/>
   <tableColumns count="95">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -754,19 +754,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$27)</f>
+        <f>COUNTA('Picks'!$A$2:$A$20)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$27,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$20,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$27,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$20,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"win")+COUNTIFS('Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"win")+COUNTIFS('Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +794,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$27,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$20,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$27,"&gt;0",'Picks'!$V$2:$V$27,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$27,"&gt;0",'Picks'!$V$2:$V$27,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$20,"&gt;0",'Picks'!$V$2:$V$20,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$20,"&gt;0",'Picks'!$V$2:$V$20,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$27,"&gt;0",'Picks'!$V$2:$V$27,"win")/(COUNTIFS('Picks'!$BX$2:$BX$27,"&gt;0",'Picks'!$V$2:$V$27,"win")+COUNTIFS('Picks'!$BX$2:$BX$27,"&gt;0",'Picks'!$V$2:$V$27,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$20,"&gt;0",'Picks'!$V$2:$V$20,"win")/(COUNTIFS('Picks'!$BX$2:$BX$20,"&gt;0",'Picks'!$V$2:$V$20,"win")+COUNTIFS('Picks'!$BX$2:$BX$20,"&gt;0",'Picks'!$V$2:$V$20,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$27)/SUM('Picks'!$BX$2:$BX$27),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$20)/SUM('Picks'!$BX$2:$BX$20),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +834,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$27)</f>
+        <f>SUM('Picks'!$BY$2:$BY$20)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$27,"&lt;&gt;",'Picks'!$AB$2:$AB$27),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$20,"&lt;&gt;",'Picks'!$AB$2:$AB$20),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$27,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$27,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$20,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$20,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$27,'Picks'!$AM$2:$AM$27,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$20,'Picks'!$AM$2:$AM$20,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +901,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$27,$A14,'Picks'!$U$2:$U$27,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$20,$A14,'Picks'!$U$2:$U$20,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$27,$A14,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$20,$A14,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$27,$A14,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$20,$A14,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +917,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$27,'Picks'!$H$2:$H$27,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$20,'Picks'!$H$2:$H$20,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$27,'Picks'!$H$2:$H$27,$A14,'Picks'!$U$2:$U$27,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$20,'Picks'!$H$2:$H$20,$A14,'Picks'!$U$2:$U$20,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +932,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$27,$A15,'Picks'!$U$2:$U$27,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$20,$A15,'Picks'!$U$2:$U$20,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$27,$A15,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$20,$A15,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$27,$A15,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$20,$A15,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +948,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$27,'Picks'!$H$2:$H$27,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$20,'Picks'!$H$2:$H$20,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$27,'Picks'!$H$2:$H$27,$A15,'Picks'!$U$2:$U$27,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$20,'Picks'!$H$2:$H$20,$A15,'Picks'!$U$2:$U$20,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +963,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$27,$A16,'Picks'!$U$2:$U$27,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$20,$A16,'Picks'!$U$2:$U$20,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$27,$A16,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$20,$A16,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$27,$A16,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$20,$A16,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +979,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$27,'Picks'!$H$2:$H$27,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$20,'Picks'!$H$2:$H$20,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$27,'Picks'!$H$2:$H$27,$A16,'Picks'!$U$2:$U$27,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$20,'Picks'!$H$2:$H$20,$A16,'Picks'!$U$2:$U$20,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ27"/>
+  <dimension ref="A1:CQ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7026,1875 +7026,6 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="36" customHeight="1">
-      <c r="A21" s="24" t="inlineStr">
-        <is>
-          <t>22b68a8702f04658</t>
-        </is>
-      </c>
-      <c r="B21" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:12:25.393675Z</t>
-        </is>
-      </c>
-      <c r="C21" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T08:00:00Z</t>
-        </is>
-      </c>
-      <c r="D21" s="24" t="inlineStr">
-        <is>
-          <t>67491</t>
-        </is>
-      </c>
-      <c r="E21" s="24" t="inlineStr">
-        <is>
-          <t>LOL</t>
-        </is>
-      </c>
-      <c r="F21" s="24" t="inlineStr">
-        <is>
-          <t>Hanwha Life Esports</t>
-        </is>
-      </c>
-      <c r="G21" s="24" t="inlineStr">
-        <is>
-          <t>Gen.G</t>
-        </is>
-      </c>
-      <c r="H21" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I21" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J21" s="25" t="n"/>
-      <c r="K21" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L21" s="26" t="n">
-        <v>-144</v>
-      </c>
-      <c r="M21" s="27" t="n">
-        <v>1.694444</v>
-      </c>
-      <c r="N21" s="28" t="n">
-        <v>0.590164</v>
-      </c>
-      <c r="O21" s="28" t="n">
-        <v>0.5360740000000001</v>
-      </c>
-      <c r="P21" s="28" t="n"/>
-      <c r="Q21" s="28" t="n">
-        <v>-0.05409</v>
-      </c>
-      <c r="R21" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T21" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U21" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V21" s="24" t="n"/>
-      <c r="W21" s="26" t="n"/>
-      <c r="X21" s="26" t="n"/>
-      <c r="Y21" s="25" t="n"/>
-      <c r="Z21" s="26" t="n"/>
-      <c r="AA21" s="28" t="n"/>
-      <c r="AB21" s="28" t="n"/>
-      <c r="AC21" s="30" t="n"/>
-      <c r="AD21" s="24" t="n"/>
-      <c r="AE21" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-lol-gen-hle-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF21" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG21" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH21" s="24" t="n"/>
-      <c r="AI21" s="31" t="n"/>
-      <c r="AJ21" s="31" t="n"/>
-      <c r="AK21" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL21" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM21" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN21" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO21" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP21" s="24" t="inlineStr">
-        <is>
-          <t>Hanwha Life Esports</t>
-        </is>
-      </c>
-      <c r="AQ21" s="24" t="inlineStr">
-        <is>
-          <t>Hanwha Life Esports</t>
-        </is>
-      </c>
-      <c r="AR21" s="24" t="inlineStr">
-        <is>
-          <t>Hanwha Life Esports</t>
-        </is>
-      </c>
-      <c r="AS21" s="24" t="inlineStr">
-        <is>
-          <t>Gen.G</t>
-        </is>
-      </c>
-      <c r="AT21" s="24" t="inlineStr">
-        <is>
-          <t>Gen.G</t>
-        </is>
-      </c>
-      <c r="AU21" s="24" t="inlineStr">
-        <is>
-          <t>Gen.G</t>
-        </is>
-      </c>
-      <c r="AV21" s="24" t="n"/>
-      <c r="AW21" s="24" t="n"/>
-      <c r="AX21" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY21" s="24" t="n"/>
-      <c r="AZ21" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA21" s="24" t="inlineStr">
-        <is>
-          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
-        </is>
-      </c>
-      <c r="BB21" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC21" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD21" s="24" t="inlineStr">
-        <is>
-          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
-        </is>
-      </c>
-      <c r="BE21" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF21" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG21" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH21" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:12:16.992475Z</t>
-        </is>
-      </c>
-      <c r="BI21" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ21" s="25" t="n"/>
-      <c r="BK21" s="26" t="n">
-        <v>-144</v>
-      </c>
-      <c r="BL21" s="27" t="n">
-        <v>1.694444</v>
-      </c>
-      <c r="BM21" s="28" t="n">
-        <v>0.590164</v>
-      </c>
-      <c r="BN21" s="28" t="n"/>
-      <c r="BO21" s="28" t="n"/>
-      <c r="BP21" s="25" t="n"/>
-      <c r="BQ21" s="27" t="n"/>
-      <c r="BR21" s="28" t="n"/>
-      <c r="BS21" s="28" t="n"/>
-      <c r="BT21" s="28" t="n"/>
-      <c r="BU21" s="25" t="n"/>
-      <c r="BV21" s="29" t="n"/>
-      <c r="BW21" s="24" t="n"/>
-      <c r="BX21" s="30" t="n"/>
-      <c r="BY21" s="27" t="n"/>
-      <c r="BZ21" s="24" t="n"/>
-      <c r="CA21" s="31" t="n"/>
-      <c r="CB21" s="24" t="n"/>
-      <c r="CC21" s="24" t="n"/>
-      <c r="CD21" s="24" t="n"/>
-      <c r="CE21" s="24" t="n"/>
-      <c r="CF21" s="24" t="n"/>
-      <c r="CG21" s="24" t="n"/>
-      <c r="CH21" s="24" t="n"/>
-      <c r="CI21" s="24" t="n"/>
-      <c r="CJ21" s="24" t="n"/>
-      <c r="CK21" s="24" t="n"/>
-      <c r="CL21" s="24" t="n"/>
-      <c r="CM21" s="24" t="n"/>
-      <c r="CN21" s="24" t="n"/>
-      <c r="CO21" s="24" t="n"/>
-      <c r="CP21" s="24" t="n"/>
-      <c r="CQ21" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="36" customHeight="1">
-      <c r="A22" s="24" t="inlineStr">
-        <is>
-          <t>faf62962167c465b</t>
-        </is>
-      </c>
-      <c r="B22" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:12:25.393675Z</t>
-        </is>
-      </c>
-      <c r="C22" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T08:00:00Z</t>
-        </is>
-      </c>
-      <c r="D22" s="24" t="inlineStr">
-        <is>
-          <t>67492</t>
-        </is>
-      </c>
-      <c r="E22" s="24" t="inlineStr">
-        <is>
-          <t>LOL</t>
-        </is>
-      </c>
-      <c r="F22" s="24" t="inlineStr">
-        <is>
-          <t>BNK FearX Youth</t>
-        </is>
-      </c>
-      <c r="G22" s="24" t="inlineStr">
-        <is>
-          <t>HANJIN BRION Challengers</t>
-        </is>
-      </c>
-      <c r="H22" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I22" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J22" s="25" t="n"/>
-      <c r="K22" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L22" s="26" t="n">
-        <v>-223</v>
-      </c>
-      <c r="M22" s="27" t="n">
-        <v>1.44843</v>
-      </c>
-      <c r="N22" s="28" t="n">
-        <v>0.690402</v>
-      </c>
-      <c r="O22" s="28" t="n">
-        <v>0.634708</v>
-      </c>
-      <c r="P22" s="28" t="n"/>
-      <c r="Q22" s="28" t="n">
-        <v>-0.055694</v>
-      </c>
-      <c r="R22" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" s="29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T22" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U22" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V22" s="24" t="n"/>
-      <c r="W22" s="26" t="n"/>
-      <c r="X22" s="26" t="n"/>
-      <c r="Y22" s="25" t="n"/>
-      <c r="Z22" s="26" t="n"/>
-      <c r="AA22" s="28" t="n"/>
-      <c r="AB22" s="28" t="n"/>
-      <c r="AC22" s="30" t="n"/>
-      <c r="AD22" s="24" t="n"/>
-      <c r="AE22" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-lol-hbc-foxy-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF22" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG22" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH22" s="24" t="n"/>
-      <c r="AI22" s="31" t="n"/>
-      <c r="AJ22" s="31" t="n"/>
-      <c r="AK22" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL22" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM22" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN22" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO22" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP22" s="24" t="inlineStr">
-        <is>
-          <t>BNK FearX Youth</t>
-        </is>
-      </c>
-      <c r="AQ22" s="24" t="inlineStr">
-        <is>
-          <t>BNK FearX Youth</t>
-        </is>
-      </c>
-      <c r="AR22" s="24" t="inlineStr">
-        <is>
-          <t>BNK FearX Youth</t>
-        </is>
-      </c>
-      <c r="AS22" s="24" t="inlineStr">
-        <is>
-          <t>HANJIN BRION Challengers</t>
-        </is>
-      </c>
-      <c r="AT22" s="24" t="inlineStr">
-        <is>
-          <t>HANJIN BRION Challengers</t>
-        </is>
-      </c>
-      <c r="AU22" s="24" t="inlineStr">
-        <is>
-          <t>HANJIN BRION Challengers</t>
-        </is>
-      </c>
-      <c r="AV22" s="24" t="n"/>
-      <c r="AW22" s="24" t="n"/>
-      <c r="AX22" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY22" s="24" t="n"/>
-      <c r="AZ22" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA22" s="24" t="inlineStr">
-        <is>
-          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
-        </is>
-      </c>
-      <c r="BB22" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC22" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD22" s="24" t="inlineStr">
-        <is>
-          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
-        </is>
-      </c>
-      <c r="BE22" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF22" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG22" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH22" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:12:17.534127Z</t>
-        </is>
-      </c>
-      <c r="BI22" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ22" s="25" t="n"/>
-      <c r="BK22" s="26" t="n">
-        <v>-223</v>
-      </c>
-      <c r="BL22" s="27" t="n">
-        <v>1.44843</v>
-      </c>
-      <c r="BM22" s="28" t="n">
-        <v>0.690402</v>
-      </c>
-      <c r="BN22" s="28" t="n"/>
-      <c r="BO22" s="28" t="n"/>
-      <c r="BP22" s="25" t="n"/>
-      <c r="BQ22" s="27" t="n"/>
-      <c r="BR22" s="28" t="n"/>
-      <c r="BS22" s="28" t="n"/>
-      <c r="BT22" s="28" t="n"/>
-      <c r="BU22" s="25" t="n"/>
-      <c r="BV22" s="29" t="n"/>
-      <c r="BW22" s="24" t="n"/>
-      <c r="BX22" s="30" t="n"/>
-      <c r="BY22" s="27" t="n"/>
-      <c r="BZ22" s="24" t="n"/>
-      <c r="CA22" s="31" t="n"/>
-      <c r="CB22" s="24" t="n"/>
-      <c r="CC22" s="24" t="n"/>
-      <c r="CD22" s="24" t="n"/>
-      <c r="CE22" s="24" t="n"/>
-      <c r="CF22" s="24" t="n"/>
-      <c r="CG22" s="24" t="n"/>
-      <c r="CH22" s="24" t="n"/>
-      <c r="CI22" s="24" t="n"/>
-      <c r="CJ22" s="24" t="n"/>
-      <c r="CK22" s="24" t="n"/>
-      <c r="CL22" s="24" t="n"/>
-      <c r="CM22" s="24" t="n"/>
-      <c r="CN22" s="24" t="n"/>
-      <c r="CO22" s="24" t="n"/>
-      <c r="CP22" s="24" t="n"/>
-      <c r="CQ22" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="36" customHeight="1">
-      <c r="A23" s="24" t="inlineStr">
-        <is>
-          <t>a4670ac2154d4957</t>
-        </is>
-      </c>
-      <c r="B23" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:12:25.393675Z</t>
-        </is>
-      </c>
-      <c r="C23" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T10:00:00Z</t>
-        </is>
-      </c>
-      <c r="D23" s="24" t="inlineStr">
-        <is>
-          <t>67511</t>
-        </is>
-      </c>
-      <c r="E23" s="24" t="inlineStr">
-        <is>
-          <t>LOL</t>
-        </is>
-      </c>
-      <c r="F23" s="24" t="inlineStr">
-        <is>
-          <t>Dplus KIA Challengers</t>
-        </is>
-      </c>
-      <c r="G23" s="24" t="inlineStr">
-        <is>
-          <t>DN SOOPers Challengers</t>
-        </is>
-      </c>
-      <c r="H23" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I23" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J23" s="25" t="n"/>
-      <c r="K23" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L23" s="26" t="n">
-        <v>-223</v>
-      </c>
-      <c r="M23" s="27" t="n">
-        <v>1.44843</v>
-      </c>
-      <c r="N23" s="28" t="n">
-        <v>0.690402</v>
-      </c>
-      <c r="O23" s="28" t="n">
-        <v>0.70331</v>
-      </c>
-      <c r="P23" s="28" t="n"/>
-      <c r="Q23" s="28" t="n">
-        <v>0.012908</v>
-      </c>
-      <c r="R23" s="26" t="n">
-        <v>26</v>
-      </c>
-      <c r="S23" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T23" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U23" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V23" s="24" t="n"/>
-      <c r="W23" s="26" t="n"/>
-      <c r="X23" s="26" t="n"/>
-      <c r="Y23" s="25" t="n"/>
-      <c r="Z23" s="26" t="n"/>
-      <c r="AA23" s="28" t="n"/>
-      <c r="AB23" s="28" t="n"/>
-      <c r="AC23" s="30" t="n"/>
-      <c r="AD23" s="24" t="n"/>
-      <c r="AE23" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-lol-dnsc-dkc-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF23" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG23" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH23" s="24" t="n"/>
-      <c r="AI23" s="31" t="n"/>
-      <c r="AJ23" s="31" t="n"/>
-      <c r="AK23" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL23" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM23" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN23" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO23" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP23" s="24" t="inlineStr">
-        <is>
-          <t>Dplus KIA Challengers</t>
-        </is>
-      </c>
-      <c r="AQ23" s="24" t="inlineStr">
-        <is>
-          <t>Dplus KIA Challengers</t>
-        </is>
-      </c>
-      <c r="AR23" s="24" t="inlineStr">
-        <is>
-          <t>Dplus KIA Challengers</t>
-        </is>
-      </c>
-      <c r="AS23" s="24" t="inlineStr">
-        <is>
-          <t>DN SOOPers Challengers</t>
-        </is>
-      </c>
-      <c r="AT23" s="24" t="inlineStr">
-        <is>
-          <t>DN SOOPers Challengers</t>
-        </is>
-      </c>
-      <c r="AU23" s="24" t="inlineStr">
-        <is>
-          <t>DN SOOPers Challengers</t>
-        </is>
-      </c>
-      <c r="AV23" s="24" t="n"/>
-      <c r="AW23" s="24" t="n"/>
-      <c r="AX23" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY23" s="24" t="n"/>
-      <c r="AZ23" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA23" s="24" t="inlineStr">
-        <is>
-          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
-        </is>
-      </c>
-      <c r="BB23" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC23" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD23" s="24" t="inlineStr">
-        <is>
-          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
-        </is>
-      </c>
-      <c r="BE23" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF23" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG23" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH23" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:12:18.085863Z</t>
-        </is>
-      </c>
-      <c r="BI23" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ23" s="25" t="n"/>
-      <c r="BK23" s="26" t="n">
-        <v>-223</v>
-      </c>
-      <c r="BL23" s="27" t="n">
-        <v>1.44843</v>
-      </c>
-      <c r="BM23" s="28" t="n">
-        <v>0.690402</v>
-      </c>
-      <c r="BN23" s="28" t="n"/>
-      <c r="BO23" s="28" t="n"/>
-      <c r="BP23" s="25" t="n"/>
-      <c r="BQ23" s="27" t="n"/>
-      <c r="BR23" s="28" t="n"/>
-      <c r="BS23" s="28" t="n"/>
-      <c r="BT23" s="28" t="n"/>
-      <c r="BU23" s="25" t="n"/>
-      <c r="BV23" s="29" t="n"/>
-      <c r="BW23" s="24" t="n"/>
-      <c r="BX23" s="30" t="n"/>
-      <c r="BY23" s="27" t="n"/>
-      <c r="BZ23" s="24" t="n"/>
-      <c r="CA23" s="31" t="n"/>
-      <c r="CB23" s="24" t="n"/>
-      <c r="CC23" s="24" t="n"/>
-      <c r="CD23" s="24" t="n"/>
-      <c r="CE23" s="24" t="n"/>
-      <c r="CF23" s="24" t="n"/>
-      <c r="CG23" s="24" t="n"/>
-      <c r="CH23" s="24" t="n"/>
-      <c r="CI23" s="24" t="n"/>
-      <c r="CJ23" s="24" t="n"/>
-      <c r="CK23" s="24" t="n"/>
-      <c r="CL23" s="24" t="n"/>
-      <c r="CM23" s="24" t="n"/>
-      <c r="CN23" s="24" t="n"/>
-      <c r="CO23" s="24" t="n"/>
-      <c r="CP23" s="24" t="n"/>
-      <c r="CQ23" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="36" customHeight="1">
-      <c r="A24" s="24" t="inlineStr">
-        <is>
-          <t>0d113f85cca94270</t>
-        </is>
-      </c>
-      <c r="B24" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:12:25.393675Z</t>
-        </is>
-      </c>
-      <c r="C24" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T10:30:00Z</t>
-        </is>
-      </c>
-      <c r="D24" s="24" t="inlineStr">
-        <is>
-          <t>67515</t>
-        </is>
-      </c>
-      <c r="E24" s="24" t="inlineStr">
-        <is>
-          <t>LOL</t>
-        </is>
-      </c>
-      <c r="F24" s="24" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="G24" s="24" t="inlineStr">
-        <is>
-          <t>Nongshim Red Force</t>
-        </is>
-      </c>
-      <c r="H24" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I24" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J24" s="25" t="n"/>
-      <c r="K24" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L24" s="26" t="n">
-        <v>-156</v>
-      </c>
-      <c r="M24" s="27" t="n">
-        <v>1.641026</v>
-      </c>
-      <c r="N24" s="28" t="n">
-        <v>0.609375</v>
-      </c>
-      <c r="O24" s="28" t="n">
-        <v>0.746406</v>
-      </c>
-      <c r="P24" s="28" t="n"/>
-      <c r="Q24" s="28" t="n">
-        <v>0.137031</v>
-      </c>
-      <c r="R24" s="26" t="n">
-        <v>89</v>
-      </c>
-      <c r="S24" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T24" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U24" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V24" s="24" t="n"/>
-      <c r="W24" s="26" t="n"/>
-      <c r="X24" s="26" t="n"/>
-      <c r="Y24" s="25" t="n"/>
-      <c r="Z24" s="26" t="n"/>
-      <c r="AA24" s="28" t="n"/>
-      <c r="AB24" s="28" t="n"/>
-      <c r="AC24" s="30" t="n"/>
-      <c r="AD24" s="24" t="n"/>
-      <c r="AE24" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-lol-ns-t1-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF24" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG24" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH24" s="24" t="n"/>
-      <c r="AI24" s="31" t="n"/>
-      <c r="AJ24" s="31" t="n"/>
-      <c r="AK24" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL24" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM24" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN24" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO24" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP24" s="24" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="AQ24" s="24" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="AR24" s="24" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="AS24" s="24" t="inlineStr">
-        <is>
-          <t>Nongshim Red Force</t>
-        </is>
-      </c>
-      <c r="AT24" s="24" t="inlineStr">
-        <is>
-          <t>Nongshim Red Force</t>
-        </is>
-      </c>
-      <c r="AU24" s="24" t="inlineStr">
-        <is>
-          <t>Nongshim Red Force</t>
-        </is>
-      </c>
-      <c r="AV24" s="24" t="n"/>
-      <c r="AW24" s="24" t="n"/>
-      <c r="AX24" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY24" s="24" t="n"/>
-      <c r="AZ24" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA24" s="24" t="inlineStr">
-        <is>
-          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
-        </is>
-      </c>
-      <c r="BB24" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC24" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD24" s="24" t="inlineStr">
-        <is>
-          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
-        </is>
-      </c>
-      <c r="BE24" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF24" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG24" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH24" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:12:18.584911Z</t>
-        </is>
-      </c>
-      <c r="BI24" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ24" s="25" t="n"/>
-      <c r="BK24" s="26" t="n">
-        <v>-156</v>
-      </c>
-      <c r="BL24" s="27" t="n">
-        <v>1.641026</v>
-      </c>
-      <c r="BM24" s="28" t="n">
-        <v>0.609375</v>
-      </c>
-      <c r="BN24" s="28" t="n"/>
-      <c r="BO24" s="28" t="n"/>
-      <c r="BP24" s="25" t="n"/>
-      <c r="BQ24" s="27" t="n"/>
-      <c r="BR24" s="28" t="n"/>
-      <c r="BS24" s="28" t="n"/>
-      <c r="BT24" s="28" t="n"/>
-      <c r="BU24" s="25" t="n"/>
-      <c r="BV24" s="29" t="n"/>
-      <c r="BW24" s="24" t="n"/>
-      <c r="BX24" s="30" t="n"/>
-      <c r="BY24" s="27" t="n"/>
-      <c r="BZ24" s="24" t="n"/>
-      <c r="CA24" s="31" t="n"/>
-      <c r="CB24" s="24" t="n"/>
-      <c r="CC24" s="24" t="n"/>
-      <c r="CD24" s="24" t="n"/>
-      <c r="CE24" s="24" t="n"/>
-      <c r="CF24" s="24" t="n"/>
-      <c r="CG24" s="24" t="n"/>
-      <c r="CH24" s="24" t="n"/>
-      <c r="CI24" s="24" t="n"/>
-      <c r="CJ24" s="24" t="n"/>
-      <c r="CK24" s="24" t="n"/>
-      <c r="CL24" s="24" t="n"/>
-      <c r="CM24" s="24" t="n"/>
-      <c r="CN24" s="24" t="n"/>
-      <c r="CO24" s="24" t="n"/>
-      <c r="CP24" s="24" t="n"/>
-      <c r="CQ24" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="36" customHeight="1">
-      <c r="A25" s="24" t="inlineStr">
-        <is>
-          <t>e91560b32ac84323</t>
-        </is>
-      </c>
-      <c r="B25" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:12:25.393675Z</t>
-        </is>
-      </c>
-      <c r="C25" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T15:00:00Z</t>
-        </is>
-      </c>
-      <c r="D25" s="24" t="inlineStr">
-        <is>
-          <t>67566</t>
-        </is>
-      </c>
-      <c r="E25" s="24" t="inlineStr">
-        <is>
-          <t>LOL</t>
-        </is>
-      </c>
-      <c r="F25" s="24" t="inlineStr">
-        <is>
-          <t>Shifters</t>
-        </is>
-      </c>
-      <c r="G25" s="24" t="inlineStr">
-        <is>
-          <t>Natus Vincere</t>
-        </is>
-      </c>
-      <c r="H25" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I25" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J25" s="25" t="n"/>
-      <c r="K25" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L25" s="26" t="n">
-        <v>-233</v>
-      </c>
-      <c r="M25" s="27" t="n">
-        <v>1.429185</v>
-      </c>
-      <c r="N25" s="28" t="n">
-        <v>0.6997</v>
-      </c>
-      <c r="O25" s="28" t="n">
-        <v>0.746125</v>
-      </c>
-      <c r="P25" s="28" t="n"/>
-      <c r="Q25" s="28" t="n">
-        <v>0.046425</v>
-      </c>
-      <c r="R25" s="26" t="n">
-        <v>43</v>
-      </c>
-      <c r="S25" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T25" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U25" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V25" s="24" t="n"/>
-      <c r="W25" s="26" t="n"/>
-      <c r="X25" s="26" t="n"/>
-      <c r="Y25" s="25" t="n"/>
-      <c r="Z25" s="26" t="n"/>
-      <c r="AA25" s="28" t="n"/>
-      <c r="AB25" s="28" t="n"/>
-      <c r="AC25" s="30" t="n"/>
-      <c r="AD25" s="24" t="n"/>
-      <c r="AE25" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-lol-navi-shft-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF25" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG25" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH25" s="24" t="n"/>
-      <c r="AI25" s="31" t="n"/>
-      <c r="AJ25" s="31" t="n"/>
-      <c r="AK25" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL25" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM25" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN25" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO25" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP25" s="24" t="inlineStr">
-        <is>
-          <t>Shifters</t>
-        </is>
-      </c>
-      <c r="AQ25" s="24" t="inlineStr">
-        <is>
-          <t>Shifters</t>
-        </is>
-      </c>
-      <c r="AR25" s="24" t="inlineStr">
-        <is>
-          <t>Shifters</t>
-        </is>
-      </c>
-      <c r="AS25" s="24" t="inlineStr">
-        <is>
-          <t>Natus Vincere</t>
-        </is>
-      </c>
-      <c r="AT25" s="24" t="inlineStr">
-        <is>
-          <t>Natus Vincere</t>
-        </is>
-      </c>
-      <c r="AU25" s="24" t="inlineStr">
-        <is>
-          <t>Natus Vincere</t>
-        </is>
-      </c>
-      <c r="AV25" s="24" t="n"/>
-      <c r="AW25" s="24" t="n"/>
-      <c r="AX25" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY25" s="24" t="n"/>
-      <c r="AZ25" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA25" s="24" t="inlineStr">
-        <is>
-          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
-        </is>
-      </c>
-      <c r="BB25" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC25" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD25" s="24" t="inlineStr">
-        <is>
-          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
-        </is>
-      </c>
-      <c r="BE25" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF25" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG25" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH25" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:12:19.163906Z</t>
-        </is>
-      </c>
-      <c r="BI25" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ25" s="25" t="n"/>
-      <c r="BK25" s="26" t="n">
-        <v>-233</v>
-      </c>
-      <c r="BL25" s="27" t="n">
-        <v>1.429185</v>
-      </c>
-      <c r="BM25" s="28" t="n">
-        <v>0.6997</v>
-      </c>
-      <c r="BN25" s="28" t="n"/>
-      <c r="BO25" s="28" t="n"/>
-      <c r="BP25" s="25" t="n"/>
-      <c r="BQ25" s="27" t="n"/>
-      <c r="BR25" s="28" t="n"/>
-      <c r="BS25" s="28" t="n"/>
-      <c r="BT25" s="28" t="n"/>
-      <c r="BU25" s="25" t="n"/>
-      <c r="BV25" s="29" t="n"/>
-      <c r="BW25" s="24" t="n"/>
-      <c r="BX25" s="30" t="n"/>
-      <c r="BY25" s="27" t="n"/>
-      <c r="BZ25" s="24" t="n"/>
-      <c r="CA25" s="31" t="n"/>
-      <c r="CB25" s="24" t="n"/>
-      <c r="CC25" s="24" t="n"/>
-      <c r="CD25" s="24" t="n"/>
-      <c r="CE25" s="24" t="n"/>
-      <c r="CF25" s="24" t="n"/>
-      <c r="CG25" s="24" t="n"/>
-      <c r="CH25" s="24" t="n"/>
-      <c r="CI25" s="24" t="n"/>
-      <c r="CJ25" s="24" t="n"/>
-      <c r="CK25" s="24" t="n"/>
-      <c r="CL25" s="24" t="n"/>
-      <c r="CM25" s="24" t="n"/>
-      <c r="CN25" s="24" t="n"/>
-      <c r="CO25" s="24" t="n"/>
-      <c r="CP25" s="24" t="n"/>
-      <c r="CQ25" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="36" customHeight="1">
-      <c r="A26" s="24" t="inlineStr">
-        <is>
-          <t>657186cb61214e6c</t>
-        </is>
-      </c>
-      <c r="B26" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:12:25.393675Z</t>
-        </is>
-      </c>
-      <c r="C26" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T20:00:00Z</t>
-        </is>
-      </c>
-      <c r="D26" s="24" t="inlineStr">
-        <is>
-          <t>67937</t>
-        </is>
-      </c>
-      <c r="E26" s="24" t="inlineStr">
-        <is>
-          <t>LOL</t>
-        </is>
-      </c>
-      <c r="F26" s="24" t="inlineStr">
-        <is>
-          <t>Docta Esports</t>
-        </is>
-      </c>
-      <c r="G26" s="24" t="inlineStr">
-        <is>
-          <t>Volticons</t>
-        </is>
-      </c>
-      <c r="H26" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I26" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J26" s="25" t="n"/>
-      <c r="K26" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L26" s="26" t="n">
-        <v>-144</v>
-      </c>
-      <c r="M26" s="27" t="n">
-        <v>1.694444</v>
-      </c>
-      <c r="N26" s="28" t="n">
-        <v>0.590164</v>
-      </c>
-      <c r="O26" s="28" t="n">
-        <v>0.649195</v>
-      </c>
-      <c r="P26" s="28" t="n"/>
-      <c r="Q26" s="28" t="n">
-        <v>0.059031</v>
-      </c>
-      <c r="R26" s="26" t="n">
-        <v>50</v>
-      </c>
-      <c r="S26" s="29" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="T26" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U26" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V26" s="24" t="n"/>
-      <c r="W26" s="26" t="n"/>
-      <c r="X26" s="26" t="n"/>
-      <c r="Y26" s="25" t="n"/>
-      <c r="Z26" s="26" t="n"/>
-      <c r="AA26" s="28" t="n"/>
-      <c r="AB26" s="28" t="n"/>
-      <c r="AC26" s="30" t="n"/>
-      <c r="AD26" s="24" t="n"/>
-      <c r="AE26" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-lol-vtc-doh-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF26" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG26" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH26" s="24" t="n"/>
-      <c r="AI26" s="31" t="n"/>
-      <c r="AJ26" s="31" t="n"/>
-      <c r="AK26" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL26" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM26" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN26" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO26" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP26" s="24" t="inlineStr">
-        <is>
-          <t>Docta Esports</t>
-        </is>
-      </c>
-      <c r="AQ26" s="24" t="inlineStr">
-        <is>
-          <t>Docta Esports</t>
-        </is>
-      </c>
-      <c r="AR26" s="24" t="inlineStr">
-        <is>
-          <t>Docta Esports</t>
-        </is>
-      </c>
-      <c r="AS26" s="24" t="inlineStr">
-        <is>
-          <t>Volticons</t>
-        </is>
-      </c>
-      <c r="AT26" s="24" t="inlineStr">
-        <is>
-          <t>Volticons</t>
-        </is>
-      </c>
-      <c r="AU26" s="24" t="inlineStr">
-        <is>
-          <t>Volticons</t>
-        </is>
-      </c>
-      <c r="AV26" s="24" t="n"/>
-      <c r="AW26" s="24" t="n"/>
-      <c r="AX26" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY26" s="24" t="n"/>
-      <c r="AZ26" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA26" s="24" t="inlineStr">
-        <is>
-          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
-        </is>
-      </c>
-      <c r="BB26" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC26" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD26" s="24" t="inlineStr">
-        <is>
-          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
-        </is>
-      </c>
-      <c r="BE26" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF26" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG26" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH26" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:12:22.895388Z</t>
-        </is>
-      </c>
-      <c r="BI26" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ26" s="25" t="n"/>
-      <c r="BK26" s="26" t="n">
-        <v>-144</v>
-      </c>
-      <c r="BL26" s="27" t="n">
-        <v>1.694444</v>
-      </c>
-      <c r="BM26" s="28" t="n">
-        <v>0.590164</v>
-      </c>
-      <c r="BN26" s="28" t="n"/>
-      <c r="BO26" s="28" t="n"/>
-      <c r="BP26" s="25" t="n"/>
-      <c r="BQ26" s="27" t="n"/>
-      <c r="BR26" s="28" t="n"/>
-      <c r="BS26" s="28" t="n"/>
-      <c r="BT26" s="28" t="n"/>
-      <c r="BU26" s="25" t="n"/>
-      <c r="BV26" s="29" t="n"/>
-      <c r="BW26" s="24" t="n"/>
-      <c r="BX26" s="30" t="n"/>
-      <c r="BY26" s="27" t="n"/>
-      <c r="BZ26" s="24" t="n"/>
-      <c r="CA26" s="31" t="n"/>
-      <c r="CB26" s="24" t="n"/>
-      <c r="CC26" s="24" t="n"/>
-      <c r="CD26" s="24" t="n"/>
-      <c r="CE26" s="24" t="n"/>
-      <c r="CF26" s="24" t="n"/>
-      <c r="CG26" s="24" t="n"/>
-      <c r="CH26" s="24" t="n"/>
-      <c r="CI26" s="24" t="n"/>
-      <c r="CJ26" s="24" t="n"/>
-      <c r="CK26" s="24" t="n"/>
-      <c r="CL26" s="24" t="n"/>
-      <c r="CM26" s="24" t="n"/>
-      <c r="CN26" s="24" t="n"/>
-      <c r="CO26" s="24" t="n"/>
-      <c r="CP26" s="24" t="n"/>
-      <c r="CQ26" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="36" customHeight="1">
-      <c r="A27" s="24" t="inlineStr">
-        <is>
-          <t>35d450cb7d394ddc</t>
-        </is>
-      </c>
-      <c r="B27" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:12:25.393675Z</t>
-        </is>
-      </c>
-      <c r="C27" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T22:00:00Z</t>
-        </is>
-      </c>
-      <c r="D27" s="24" t="inlineStr">
-        <is>
-          <t>68011</t>
-        </is>
-      </c>
-      <c r="E27" s="24" t="inlineStr">
-        <is>
-          <t>LOL</t>
-        </is>
-      </c>
-      <c r="F27" s="24" t="inlineStr">
-        <is>
-          <t>Vivo Keyd Stars Academy</t>
-        </is>
-      </c>
-      <c r="G27" s="24" t="inlineStr">
-        <is>
-          <t>paiN Gaming Academy</t>
-        </is>
-      </c>
-      <c r="H27" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I27" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J27" s="25" t="n"/>
-      <c r="K27" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L27" s="26" t="n">
-        <v>-104</v>
-      </c>
-      <c r="M27" s="27" t="n">
-        <v>1.961538</v>
-      </c>
-      <c r="N27" s="28" t="n">
-        <v>0.509804</v>
-      </c>
-      <c r="O27" s="28" t="n">
-        <v>0.502316</v>
-      </c>
-      <c r="P27" s="28" t="n"/>
-      <c r="Q27" s="28" t="n">
-        <v>-0.007488</v>
-      </c>
-      <c r="R27" s="26" t="n">
-        <v>16</v>
-      </c>
-      <c r="S27" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T27" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U27" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V27" s="24" t="n"/>
-      <c r="W27" s="26" t="n"/>
-      <c r="X27" s="26" t="n"/>
-      <c r="Y27" s="25" t="n"/>
-      <c r="Z27" s="26" t="n"/>
-      <c r="AA27" s="28" t="n"/>
-      <c r="AB27" s="28" t="n"/>
-      <c r="AC27" s="30" t="n"/>
-      <c r="AD27" s="24" t="n"/>
-      <c r="AE27" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-lol-pnga-vksa-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF27" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG27" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH27" s="24" t="n"/>
-      <c r="AI27" s="31" t="n"/>
-      <c r="AJ27" s="31" t="n"/>
-      <c r="AK27" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL27" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM27" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN27" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO27" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP27" s="24" t="inlineStr">
-        <is>
-          <t>Vivo Keyd Stars Academy</t>
-        </is>
-      </c>
-      <c r="AQ27" s="24" t="inlineStr">
-        <is>
-          <t>Vivo Keyd Stars Academy</t>
-        </is>
-      </c>
-      <c r="AR27" s="24" t="inlineStr">
-        <is>
-          <t>Vivo Keyd Stars Academy</t>
-        </is>
-      </c>
-      <c r="AS27" s="24" t="inlineStr">
-        <is>
-          <t>paiN Gaming Academy</t>
-        </is>
-      </c>
-      <c r="AT27" s="24" t="inlineStr">
-        <is>
-          <t>paiN Gaming Academy</t>
-        </is>
-      </c>
-      <c r="AU27" s="24" t="inlineStr">
-        <is>
-          <t>paiN Gaming Academy</t>
-        </is>
-      </c>
-      <c r="AV27" s="24" t="n"/>
-      <c r="AW27" s="24" t="n"/>
-      <c r="AX27" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY27" s="24" t="n"/>
-      <c r="AZ27" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA27" s="24" t="inlineStr">
-        <is>
-          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
-        </is>
-      </c>
-      <c r="BB27" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC27" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD27" s="24" t="inlineStr">
-        <is>
-          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
-        </is>
-      </c>
-      <c r="BE27" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF27" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG27" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH27" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:12:24.464493Z</t>
-        </is>
-      </c>
-      <c r="BI27" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ27" s="25" t="n"/>
-      <c r="BK27" s="26" t="n">
-        <v>-104</v>
-      </c>
-      <c r="BL27" s="27" t="n">
-        <v>1.961538</v>
-      </c>
-      <c r="BM27" s="28" t="n">
-        <v>0.509804</v>
-      </c>
-      <c r="BN27" s="28" t="n"/>
-      <c r="BO27" s="28" t="n"/>
-      <c r="BP27" s="25" t="n"/>
-      <c r="BQ27" s="27" t="n"/>
-      <c r="BR27" s="28" t="n"/>
-      <c r="BS27" s="28" t="n"/>
-      <c r="BT27" s="28" t="n"/>
-      <c r="BU27" s="25" t="n"/>
-      <c r="BV27" s="29" t="n"/>
-      <c r="BW27" s="24" t="n"/>
-      <c r="BX27" s="30" t="n"/>
-      <c r="BY27" s="27" t="n"/>
-      <c r="BZ27" s="24" t="n"/>
-      <c r="CA27" s="31" t="n"/>
-      <c r="CB27" s="24" t="n"/>
-      <c r="CC27" s="24" t="n"/>
-      <c r="CD27" s="24" t="n"/>
-      <c r="CE27" s="24" t="n"/>
-      <c r="CF27" s="24" t="n"/>
-      <c r="CG27" s="24" t="n"/>
-      <c r="CH27" s="24" t="n"/>
-      <c r="CI27" s="24" t="n"/>
-      <c r="CJ27" s="24" t="n"/>
-      <c r="CK27" s="24" t="n"/>
-      <c r="CL27" s="24" t="n"/>
-      <c r="CM27" s="24" t="n"/>
-      <c r="CN27" s="24" t="n"/>
-      <c r="CO27" s="24" t="n"/>
-      <c r="CP27" s="24" t="n"/>
-      <c r="CQ27" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research/lol.xlsx
+++ b/data/research/lol.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ20" headerRowCount="1">
-  <autoFilter ref="A1:CQ20"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ28" headerRowCount="1">
+  <autoFilter ref="A1:CQ28"/>
   <tableColumns count="95">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -754,19 +754,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$20)</f>
+        <f>COUNTA('Picks'!$A$2:$A$28)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$20,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$28,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$20,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$28,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"win")+COUNTIFS('Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$28,"settled",'Picks'!$V$2:$V$28,"win")+COUNTIFS('Picks'!$U$2:$U$28,"settled",'Picks'!$V$2:$V$28,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +794,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$20,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$28,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$20,"&gt;0",'Picks'!$V$2:$V$20,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$20,"&gt;0",'Picks'!$V$2:$V$20,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$28,"&gt;0",'Picks'!$V$2:$V$28,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$28,"&gt;0",'Picks'!$V$2:$V$28,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$20,"&gt;0",'Picks'!$V$2:$V$20,"win")/(COUNTIFS('Picks'!$BX$2:$BX$20,"&gt;0",'Picks'!$V$2:$V$20,"win")+COUNTIFS('Picks'!$BX$2:$BX$20,"&gt;0",'Picks'!$V$2:$V$20,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$28,"&gt;0",'Picks'!$V$2:$V$28,"win")/(COUNTIFS('Picks'!$BX$2:$BX$28,"&gt;0",'Picks'!$V$2:$V$28,"win")+COUNTIFS('Picks'!$BX$2:$BX$28,"&gt;0",'Picks'!$V$2:$V$28,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$20)/SUM('Picks'!$BX$2:$BX$20),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$28)/SUM('Picks'!$BX$2:$BX$28),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +834,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$20)</f>
+        <f>SUM('Picks'!$BY$2:$BY$28)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$20,"&lt;&gt;",'Picks'!$AB$2:$AB$20),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$28,"&lt;&gt;",'Picks'!$AB$2:$AB$28),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$20,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$20,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$28,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$28,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$20,'Picks'!$AM$2:$AM$20,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$28,'Picks'!$AM$2:$AM$28,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +901,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$20,$A14,'Picks'!$U$2:$U$20,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$28,$A14,'Picks'!$U$2:$U$28,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$20,$A14,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$28,$A14,'Picks'!$U$2:$U$28,"settled",'Picks'!$V$2:$V$28,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$20,$A14,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$28,$A14,'Picks'!$U$2:$U$28,"settled",'Picks'!$V$2:$V$28,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +917,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$20,'Picks'!$H$2:$H$20,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$28,'Picks'!$H$2:$H$28,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$20,'Picks'!$H$2:$H$20,$A14,'Picks'!$U$2:$U$20,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$28,'Picks'!$H$2:$H$28,$A14,'Picks'!$U$2:$U$28,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +932,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$20,$A15,'Picks'!$U$2:$U$20,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$28,$A15,'Picks'!$U$2:$U$28,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$20,$A15,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$28,$A15,'Picks'!$U$2:$U$28,"settled",'Picks'!$V$2:$V$28,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$20,$A15,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$28,$A15,'Picks'!$U$2:$U$28,"settled",'Picks'!$V$2:$V$28,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +948,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$20,'Picks'!$H$2:$H$20,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$28,'Picks'!$H$2:$H$28,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$20,'Picks'!$H$2:$H$20,$A15,'Picks'!$U$2:$U$20,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$28,'Picks'!$H$2:$H$28,$A15,'Picks'!$U$2:$U$28,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +963,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$20,$A16,'Picks'!$U$2:$U$20,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$28,$A16,'Picks'!$U$2:$U$28,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$20,$A16,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$28,$A16,'Picks'!$U$2:$U$28,"settled",'Picks'!$V$2:$V$28,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$20,$A16,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$28,$A16,'Picks'!$U$2:$U$28,"settled",'Picks'!$V$2:$V$28,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +979,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$20,'Picks'!$H$2:$H$20,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$28,'Picks'!$H$2:$H$28,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$20,'Picks'!$H$2:$H$20,$A16,'Picks'!$U$2:$U$20,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$28,'Picks'!$H$2:$H$28,$A16,'Picks'!$U$2:$U$28,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ20"/>
+  <dimension ref="A1:CQ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7026,6 +7026,2142 @@
         </is>
       </c>
     </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="24" t="inlineStr">
+        <is>
+          <t>0fe6aecb14c149f9</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:16.736104Z</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="D21" s="24" t="inlineStr">
+        <is>
+          <t>67491</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F21" s="24" t="inlineStr">
+        <is>
+          <t>Hanwha Life Esports</t>
+        </is>
+      </c>
+      <c r="G21" s="24" t="inlineStr">
+        <is>
+          <t>Gen.G</t>
+        </is>
+      </c>
+      <c r="H21" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I21" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J21" s="25" t="n"/>
+      <c r="K21" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L21" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="M21" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="N21" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="O21" s="28" t="n">
+        <v>0.5360740000000001</v>
+      </c>
+      <c r="P21" s="28" t="n"/>
+      <c r="Q21" s="28" t="n">
+        <v>-0.05409</v>
+      </c>
+      <c r="R21" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U21" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V21" s="24" t="n"/>
+      <c r="W21" s="26" t="n"/>
+      <c r="X21" s="26" t="n"/>
+      <c r="Y21" s="25" t="n"/>
+      <c r="Z21" s="26" t="n"/>
+      <c r="AA21" s="28" t="n"/>
+      <c r="AB21" s="28" t="n"/>
+      <c r="AC21" s="30" t="n"/>
+      <c r="AD21" s="24" t="n"/>
+      <c r="AE21" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-lol-gen-hle-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF21" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG21" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH21" s="24" t="n"/>
+      <c r="AI21" s="31" t="n"/>
+      <c r="AJ21" s="31" t="n"/>
+      <c r="AK21" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL21" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM21" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN21" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO21" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP21" s="24" t="inlineStr">
+        <is>
+          <t>Hanwha Life Esports</t>
+        </is>
+      </c>
+      <c r="AQ21" s="24" t="inlineStr">
+        <is>
+          <t>Hanwha Life Esports</t>
+        </is>
+      </c>
+      <c r="AR21" s="24" t="inlineStr">
+        <is>
+          <t>Hanwha Life Esports</t>
+        </is>
+      </c>
+      <c r="AS21" s="24" t="inlineStr">
+        <is>
+          <t>Gen.G</t>
+        </is>
+      </c>
+      <c r="AT21" s="24" t="inlineStr">
+        <is>
+          <t>Gen.G</t>
+        </is>
+      </c>
+      <c r="AU21" s="24" t="inlineStr">
+        <is>
+          <t>Gen.G</t>
+        </is>
+      </c>
+      <c r="AV21" s="24" t="n"/>
+      <c r="AW21" s="24" t="n"/>
+      <c r="AX21" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY21" s="24" t="n"/>
+      <c r="AZ21" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA21" s="24" t="inlineStr">
+        <is>
+          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+        </is>
+      </c>
+      <c r="BB21" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC21" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD21" s="24" t="inlineStr">
+        <is>
+          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+        </is>
+      </c>
+      <c r="BE21" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF21" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG21" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:08.792428Z</t>
+        </is>
+      </c>
+      <c r="BI21" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ21" s="25" t="n"/>
+      <c r="BK21" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="BL21" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="BM21" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="BN21" s="28" t="n"/>
+      <c r="BO21" s="28" t="n"/>
+      <c r="BP21" s="25" t="n"/>
+      <c r="BQ21" s="27" t="n"/>
+      <c r="BR21" s="28" t="n"/>
+      <c r="BS21" s="28" t="n"/>
+      <c r="BT21" s="28" t="n"/>
+      <c r="BU21" s="25" t="n"/>
+      <c r="BV21" s="29" t="n"/>
+      <c r="BW21" s="24" t="n"/>
+      <c r="BX21" s="30" t="n"/>
+      <c r="BY21" s="27" t="n"/>
+      <c r="BZ21" s="24" t="n"/>
+      <c r="CA21" s="31" t="n"/>
+      <c r="CB21" s="24" t="n"/>
+      <c r="CC21" s="24" t="n"/>
+      <c r="CD21" s="24" t="n"/>
+      <c r="CE21" s="24" t="n"/>
+      <c r="CF21" s="24" t="n"/>
+      <c r="CG21" s="24" t="n"/>
+      <c r="CH21" s="24" t="n"/>
+      <c r="CI21" s="24" t="n"/>
+      <c r="CJ21" s="24" t="n"/>
+      <c r="CK21" s="24" t="n"/>
+      <c r="CL21" s="24" t="n"/>
+      <c r="CM21" s="24" t="n"/>
+      <c r="CN21" s="24" t="n"/>
+      <c r="CO21" s="24" t="n"/>
+      <c r="CP21" s="24" t="n"/>
+      <c r="CQ21" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>148846ecebb94256</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:16.736104Z</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>67492</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F22" s="24" t="inlineStr">
+        <is>
+          <t>BNK FearX Youth</t>
+        </is>
+      </c>
+      <c r="G22" s="24" t="inlineStr">
+        <is>
+          <t>HANJIN BRION Challengers</t>
+        </is>
+      </c>
+      <c r="H22" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I22" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J22" s="25" t="n"/>
+      <c r="K22" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L22" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="M22" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="N22" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="O22" s="28" t="n">
+        <v>0.634708</v>
+      </c>
+      <c r="P22" s="28" t="n"/>
+      <c r="Q22" s="28" t="n">
+        <v>-0.055694</v>
+      </c>
+      <c r="R22" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T22" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U22" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V22" s="24" t="n"/>
+      <c r="W22" s="26" t="n"/>
+      <c r="X22" s="26" t="n"/>
+      <c r="Y22" s="25" t="n"/>
+      <c r="Z22" s="26" t="n"/>
+      <c r="AA22" s="28" t="n"/>
+      <c r="AB22" s="28" t="n"/>
+      <c r="AC22" s="30" t="n"/>
+      <c r="AD22" s="24" t="n"/>
+      <c r="AE22" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-lol-hbc-foxy-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF22" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG22" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH22" s="24" t="n"/>
+      <c r="AI22" s="31" t="n"/>
+      <c r="AJ22" s="31" t="n"/>
+      <c r="AK22" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL22" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM22" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN22" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO22" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP22" s="24" t="inlineStr">
+        <is>
+          <t>BNK FearX Youth</t>
+        </is>
+      </c>
+      <c r="AQ22" s="24" t="inlineStr">
+        <is>
+          <t>BNK FearX Youth</t>
+        </is>
+      </c>
+      <c r="AR22" s="24" t="inlineStr">
+        <is>
+          <t>BNK FearX Youth</t>
+        </is>
+      </c>
+      <c r="AS22" s="24" t="inlineStr">
+        <is>
+          <t>HANJIN BRION Challengers</t>
+        </is>
+      </c>
+      <c r="AT22" s="24" t="inlineStr">
+        <is>
+          <t>HANJIN BRION Challengers</t>
+        </is>
+      </c>
+      <c r="AU22" s="24" t="inlineStr">
+        <is>
+          <t>HANJIN BRION Challengers</t>
+        </is>
+      </c>
+      <c r="AV22" s="24" t="n"/>
+      <c r="AW22" s="24" t="n"/>
+      <c r="AX22" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY22" s="24" t="n"/>
+      <c r="AZ22" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA22" s="24" t="inlineStr">
+        <is>
+          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+        </is>
+      </c>
+      <c r="BB22" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC22" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD22" s="24" t="inlineStr">
+        <is>
+          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+        </is>
+      </c>
+      <c r="BE22" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF22" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG22" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:09.253322Z</t>
+        </is>
+      </c>
+      <c r="BI22" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ22" s="25" t="n"/>
+      <c r="BK22" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="BL22" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="BM22" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="BN22" s="28" t="n"/>
+      <c r="BO22" s="28" t="n"/>
+      <c r="BP22" s="25" t="n"/>
+      <c r="BQ22" s="27" t="n"/>
+      <c r="BR22" s="28" t="n"/>
+      <c r="BS22" s="28" t="n"/>
+      <c r="BT22" s="28" t="n"/>
+      <c r="BU22" s="25" t="n"/>
+      <c r="BV22" s="29" t="n"/>
+      <c r="BW22" s="24" t="n"/>
+      <c r="BX22" s="30" t="n"/>
+      <c r="BY22" s="27" t="n"/>
+      <c r="BZ22" s="24" t="n"/>
+      <c r="CA22" s="31" t="n"/>
+      <c r="CB22" s="24" t="n"/>
+      <c r="CC22" s="24" t="n"/>
+      <c r="CD22" s="24" t="n"/>
+      <c r="CE22" s="24" t="n"/>
+      <c r="CF22" s="24" t="n"/>
+      <c r="CG22" s="24" t="n"/>
+      <c r="CH22" s="24" t="n"/>
+      <c r="CI22" s="24" t="n"/>
+      <c r="CJ22" s="24" t="n"/>
+      <c r="CK22" s="24" t="n"/>
+      <c r="CL22" s="24" t="n"/>
+      <c r="CM22" s="24" t="n"/>
+      <c r="CN22" s="24" t="n"/>
+      <c r="CO22" s="24" t="n"/>
+      <c r="CP22" s="24" t="n"/>
+      <c r="CQ22" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="24" t="inlineStr">
+        <is>
+          <t>65b82d9b551747a1</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:16.736104Z</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="D23" s="24" t="inlineStr">
+        <is>
+          <t>67511</t>
+        </is>
+      </c>
+      <c r="E23" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F23" s="24" t="inlineStr">
+        <is>
+          <t>Dplus KIA Challengers</t>
+        </is>
+      </c>
+      <c r="G23" s="24" t="inlineStr">
+        <is>
+          <t>DN SOOPers Challengers</t>
+        </is>
+      </c>
+      <c r="H23" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I23" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J23" s="25" t="n"/>
+      <c r="K23" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L23" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="M23" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="N23" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="O23" s="28" t="n">
+        <v>0.70331</v>
+      </c>
+      <c r="P23" s="28" t="n"/>
+      <c r="Q23" s="28" t="n">
+        <v>0.012908</v>
+      </c>
+      <c r="R23" s="26" t="n">
+        <v>26</v>
+      </c>
+      <c r="S23" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T23" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U23" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V23" s="24" t="n"/>
+      <c r="W23" s="26" t="n"/>
+      <c r="X23" s="26" t="n"/>
+      <c r="Y23" s="25" t="n"/>
+      <c r="Z23" s="26" t="n"/>
+      <c r="AA23" s="28" t="n"/>
+      <c r="AB23" s="28" t="n"/>
+      <c r="AC23" s="30" t="n"/>
+      <c r="AD23" s="24" t="n"/>
+      <c r="AE23" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-lol-dnsc-dkc-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF23" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG23" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH23" s="24" t="n"/>
+      <c r="AI23" s="31" t="n"/>
+      <c r="AJ23" s="31" t="n"/>
+      <c r="AK23" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL23" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM23" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN23" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO23" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP23" s="24" t="inlineStr">
+        <is>
+          <t>Dplus KIA Challengers</t>
+        </is>
+      </c>
+      <c r="AQ23" s="24" t="inlineStr">
+        <is>
+          <t>Dplus KIA Challengers</t>
+        </is>
+      </c>
+      <c r="AR23" s="24" t="inlineStr">
+        <is>
+          <t>Dplus KIA Challengers</t>
+        </is>
+      </c>
+      <c r="AS23" s="24" t="inlineStr">
+        <is>
+          <t>DN SOOPers Challengers</t>
+        </is>
+      </c>
+      <c r="AT23" s="24" t="inlineStr">
+        <is>
+          <t>DN SOOPers Challengers</t>
+        </is>
+      </c>
+      <c r="AU23" s="24" t="inlineStr">
+        <is>
+          <t>DN SOOPers Challengers</t>
+        </is>
+      </c>
+      <c r="AV23" s="24" t="n"/>
+      <c r="AW23" s="24" t="n"/>
+      <c r="AX23" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY23" s="24" t="n"/>
+      <c r="AZ23" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA23" s="24" t="inlineStr">
+        <is>
+          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+        </is>
+      </c>
+      <c r="BB23" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC23" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD23" s="24" t="inlineStr">
+        <is>
+          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+        </is>
+      </c>
+      <c r="BE23" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF23" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG23" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:09.781954Z</t>
+        </is>
+      </c>
+      <c r="BI23" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ23" s="25" t="n"/>
+      <c r="BK23" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="BL23" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="BM23" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="BN23" s="28" t="n"/>
+      <c r="BO23" s="28" t="n"/>
+      <c r="BP23" s="25" t="n"/>
+      <c r="BQ23" s="27" t="n"/>
+      <c r="BR23" s="28" t="n"/>
+      <c r="BS23" s="28" t="n"/>
+      <c r="BT23" s="28" t="n"/>
+      <c r="BU23" s="25" t="n"/>
+      <c r="BV23" s="29" t="n"/>
+      <c r="BW23" s="24" t="n"/>
+      <c r="BX23" s="30" t="n"/>
+      <c r="BY23" s="27" t="n"/>
+      <c r="BZ23" s="24" t="n"/>
+      <c r="CA23" s="31" t="n"/>
+      <c r="CB23" s="24" t="n"/>
+      <c r="CC23" s="24" t="n"/>
+      <c r="CD23" s="24" t="n"/>
+      <c r="CE23" s="24" t="n"/>
+      <c r="CF23" s="24" t="n"/>
+      <c r="CG23" s="24" t="n"/>
+      <c r="CH23" s="24" t="n"/>
+      <c r="CI23" s="24" t="n"/>
+      <c r="CJ23" s="24" t="n"/>
+      <c r="CK23" s="24" t="n"/>
+      <c r="CL23" s="24" t="n"/>
+      <c r="CM23" s="24" t="n"/>
+      <c r="CN23" s="24" t="n"/>
+      <c r="CO23" s="24" t="n"/>
+      <c r="CP23" s="24" t="n"/>
+      <c r="CQ23" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>a1231e3cef1a450e</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:16.736104Z</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="D24" s="24" t="inlineStr">
+        <is>
+          <t>67515</t>
+        </is>
+      </c>
+      <c r="E24" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F24" s="24" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="G24" s="24" t="inlineStr">
+        <is>
+          <t>Nongshim Red Force</t>
+        </is>
+      </c>
+      <c r="H24" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I24" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J24" s="25" t="n"/>
+      <c r="K24" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L24" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="M24" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="N24" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="O24" s="28" t="n">
+        <v>0.746406</v>
+      </c>
+      <c r="P24" s="28" t="n"/>
+      <c r="Q24" s="28" t="n">
+        <v>0.137031</v>
+      </c>
+      <c r="R24" s="26" t="n">
+        <v>89</v>
+      </c>
+      <c r="S24" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T24" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U24" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V24" s="24" t="n"/>
+      <c r="W24" s="26" t="n"/>
+      <c r="X24" s="26" t="n"/>
+      <c r="Y24" s="25" t="n"/>
+      <c r="Z24" s="26" t="n"/>
+      <c r="AA24" s="28" t="n"/>
+      <c r="AB24" s="28" t="n"/>
+      <c r="AC24" s="30" t="n"/>
+      <c r="AD24" s="24" t="n"/>
+      <c r="AE24" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-lol-ns-t1-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF24" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG24" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH24" s="24" t="n"/>
+      <c r="AI24" s="31" t="n"/>
+      <c r="AJ24" s="31" t="n"/>
+      <c r="AK24" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL24" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM24" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN24" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO24" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP24" s="24" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="AQ24" s="24" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="AR24" s="24" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="AS24" s="24" t="inlineStr">
+        <is>
+          <t>Nongshim Red Force</t>
+        </is>
+      </c>
+      <c r="AT24" s="24" t="inlineStr">
+        <is>
+          <t>Nongshim Red Force</t>
+        </is>
+      </c>
+      <c r="AU24" s="24" t="inlineStr">
+        <is>
+          <t>Nongshim Red Force</t>
+        </is>
+      </c>
+      <c r="AV24" s="24" t="n"/>
+      <c r="AW24" s="24" t="n"/>
+      <c r="AX24" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY24" s="24" t="n"/>
+      <c r="AZ24" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA24" s="24" t="inlineStr">
+        <is>
+          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+        </is>
+      </c>
+      <c r="BB24" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC24" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD24" s="24" t="inlineStr">
+        <is>
+          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+        </is>
+      </c>
+      <c r="BE24" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF24" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG24" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:10.279453Z</t>
+        </is>
+      </c>
+      <c r="BI24" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ24" s="25" t="n"/>
+      <c r="BK24" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="BL24" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="BM24" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="BN24" s="28" t="n"/>
+      <c r="BO24" s="28" t="n"/>
+      <c r="BP24" s="25" t="n"/>
+      <c r="BQ24" s="27" t="n"/>
+      <c r="BR24" s="28" t="n"/>
+      <c r="BS24" s="28" t="n"/>
+      <c r="BT24" s="28" t="n"/>
+      <c r="BU24" s="25" t="n"/>
+      <c r="BV24" s="29" t="n"/>
+      <c r="BW24" s="24" t="n"/>
+      <c r="BX24" s="30" t="n"/>
+      <c r="BY24" s="27" t="n"/>
+      <c r="BZ24" s="24" t="n"/>
+      <c r="CA24" s="31" t="n"/>
+      <c r="CB24" s="24" t="n"/>
+      <c r="CC24" s="24" t="n"/>
+      <c r="CD24" s="24" t="n"/>
+      <c r="CE24" s="24" t="n"/>
+      <c r="CF24" s="24" t="n"/>
+      <c r="CG24" s="24" t="n"/>
+      <c r="CH24" s="24" t="n"/>
+      <c r="CI24" s="24" t="n"/>
+      <c r="CJ24" s="24" t="n"/>
+      <c r="CK24" s="24" t="n"/>
+      <c r="CL24" s="24" t="n"/>
+      <c r="CM24" s="24" t="n"/>
+      <c r="CN24" s="24" t="n"/>
+      <c r="CO24" s="24" t="n"/>
+      <c r="CP24" s="24" t="n"/>
+      <c r="CQ24" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>800f259dfb7c4c27</t>
+        </is>
+      </c>
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:16.736104Z</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D25" s="24" t="inlineStr">
+        <is>
+          <t>67566</t>
+        </is>
+      </c>
+      <c r="E25" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F25" s="24" t="inlineStr">
+        <is>
+          <t>Shifters</t>
+        </is>
+      </c>
+      <c r="G25" s="24" t="inlineStr">
+        <is>
+          <t>Natus Vincere</t>
+        </is>
+      </c>
+      <c r="H25" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I25" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J25" s="25" t="n"/>
+      <c r="K25" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L25" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="M25" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="N25" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="O25" s="28" t="n">
+        <v>0.746125</v>
+      </c>
+      <c r="P25" s="28" t="n"/>
+      <c r="Q25" s="28" t="n">
+        <v>0.046425</v>
+      </c>
+      <c r="R25" s="26" t="n">
+        <v>43</v>
+      </c>
+      <c r="S25" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T25" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U25" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V25" s="24" t="n"/>
+      <c r="W25" s="26" t="n"/>
+      <c r="X25" s="26" t="n"/>
+      <c r="Y25" s="25" t="n"/>
+      <c r="Z25" s="26" t="n"/>
+      <c r="AA25" s="28" t="n"/>
+      <c r="AB25" s="28" t="n"/>
+      <c r="AC25" s="30" t="n"/>
+      <c r="AD25" s="24" t="n"/>
+      <c r="AE25" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-lol-navi-shft-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF25" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG25" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH25" s="24" t="n"/>
+      <c r="AI25" s="31" t="n"/>
+      <c r="AJ25" s="31" t="n"/>
+      <c r="AK25" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL25" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM25" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN25" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO25" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP25" s="24" t="inlineStr">
+        <is>
+          <t>Shifters</t>
+        </is>
+      </c>
+      <c r="AQ25" s="24" t="inlineStr">
+        <is>
+          <t>Shifters</t>
+        </is>
+      </c>
+      <c r="AR25" s="24" t="inlineStr">
+        <is>
+          <t>Shifters</t>
+        </is>
+      </c>
+      <c r="AS25" s="24" t="inlineStr">
+        <is>
+          <t>Natus Vincere</t>
+        </is>
+      </c>
+      <c r="AT25" s="24" t="inlineStr">
+        <is>
+          <t>Natus Vincere</t>
+        </is>
+      </c>
+      <c r="AU25" s="24" t="inlineStr">
+        <is>
+          <t>Natus Vincere</t>
+        </is>
+      </c>
+      <c r="AV25" s="24" t="n"/>
+      <c r="AW25" s="24" t="n"/>
+      <c r="AX25" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY25" s="24" t="n"/>
+      <c r="AZ25" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA25" s="24" t="inlineStr">
+        <is>
+          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+        </is>
+      </c>
+      <c r="BB25" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC25" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD25" s="24" t="inlineStr">
+        <is>
+          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+        </is>
+      </c>
+      <c r="BE25" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF25" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG25" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:10.786284Z</t>
+        </is>
+      </c>
+      <c r="BI25" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ25" s="25" t="n"/>
+      <c r="BK25" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="BL25" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="BM25" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="BN25" s="28" t="n"/>
+      <c r="BO25" s="28" t="n"/>
+      <c r="BP25" s="25" t="n"/>
+      <c r="BQ25" s="27" t="n"/>
+      <c r="BR25" s="28" t="n"/>
+      <c r="BS25" s="28" t="n"/>
+      <c r="BT25" s="28" t="n"/>
+      <c r="BU25" s="25" t="n"/>
+      <c r="BV25" s="29" t="n"/>
+      <c r="BW25" s="24" t="n"/>
+      <c r="BX25" s="30" t="n"/>
+      <c r="BY25" s="27" t="n"/>
+      <c r="BZ25" s="24" t="n"/>
+      <c r="CA25" s="31" t="n"/>
+      <c r="CB25" s="24" t="n"/>
+      <c r="CC25" s="24" t="n"/>
+      <c r="CD25" s="24" t="n"/>
+      <c r="CE25" s="24" t="n"/>
+      <c r="CF25" s="24" t="n"/>
+      <c r="CG25" s="24" t="n"/>
+      <c r="CH25" s="24" t="n"/>
+      <c r="CI25" s="24" t="n"/>
+      <c r="CJ25" s="24" t="n"/>
+      <c r="CK25" s="24" t="n"/>
+      <c r="CL25" s="24" t="n"/>
+      <c r="CM25" s="24" t="n"/>
+      <c r="CN25" s="24" t="n"/>
+      <c r="CO25" s="24" t="n"/>
+      <c r="CP25" s="24" t="n"/>
+      <c r="CQ25" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>c403f3e6973e46e2</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:16.736104Z</t>
+        </is>
+      </c>
+      <c r="C26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="D26" s="24" t="inlineStr">
+        <is>
+          <t>67937</t>
+        </is>
+      </c>
+      <c r="E26" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F26" s="24" t="inlineStr">
+        <is>
+          <t>Docta Esports</t>
+        </is>
+      </c>
+      <c r="G26" s="24" t="inlineStr">
+        <is>
+          <t>Volticons</t>
+        </is>
+      </c>
+      <c r="H26" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I26" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J26" s="25" t="n"/>
+      <c r="K26" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L26" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="M26" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="N26" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="O26" s="28" t="n">
+        <v>0.649195</v>
+      </c>
+      <c r="P26" s="28" t="n"/>
+      <c r="Q26" s="28" t="n">
+        <v>0.059031</v>
+      </c>
+      <c r="R26" s="26" t="n">
+        <v>50</v>
+      </c>
+      <c r="S26" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T26" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U26" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V26" s="24" t="n"/>
+      <c r="W26" s="26" t="n"/>
+      <c r="X26" s="26" t="n"/>
+      <c r="Y26" s="25" t="n"/>
+      <c r="Z26" s="26" t="n"/>
+      <c r="AA26" s="28" t="n"/>
+      <c r="AB26" s="28" t="n"/>
+      <c r="AC26" s="30" t="n"/>
+      <c r="AD26" s="24" t="n"/>
+      <c r="AE26" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-lol-vtc-doh-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF26" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG26" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH26" s="24" t="n"/>
+      <c r="AI26" s="31" t="n"/>
+      <c r="AJ26" s="31" t="n"/>
+      <c r="AK26" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL26" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM26" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN26" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO26" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP26" s="24" t="inlineStr">
+        <is>
+          <t>Docta Esports</t>
+        </is>
+      </c>
+      <c r="AQ26" s="24" t="inlineStr">
+        <is>
+          <t>Docta Esports</t>
+        </is>
+      </c>
+      <c r="AR26" s="24" t="inlineStr">
+        <is>
+          <t>Docta Esports</t>
+        </is>
+      </c>
+      <c r="AS26" s="24" t="inlineStr">
+        <is>
+          <t>Volticons</t>
+        </is>
+      </c>
+      <c r="AT26" s="24" t="inlineStr">
+        <is>
+          <t>Volticons</t>
+        </is>
+      </c>
+      <c r="AU26" s="24" t="inlineStr">
+        <is>
+          <t>Volticons</t>
+        </is>
+      </c>
+      <c r="AV26" s="24" t="n"/>
+      <c r="AW26" s="24" t="n"/>
+      <c r="AX26" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY26" s="24" t="n"/>
+      <c r="AZ26" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA26" s="24" t="inlineStr">
+        <is>
+          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+        </is>
+      </c>
+      <c r="BB26" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC26" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD26" s="24" t="inlineStr">
+        <is>
+          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+        </is>
+      </c>
+      <c r="BE26" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF26" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG26" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:14.243617Z</t>
+        </is>
+      </c>
+      <c r="BI26" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ26" s="25" t="n"/>
+      <c r="BK26" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="BL26" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="BM26" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="BN26" s="28" t="n"/>
+      <c r="BO26" s="28" t="n"/>
+      <c r="BP26" s="25" t="n"/>
+      <c r="BQ26" s="27" t="n"/>
+      <c r="BR26" s="28" t="n"/>
+      <c r="BS26" s="28" t="n"/>
+      <c r="BT26" s="28" t="n"/>
+      <c r="BU26" s="25" t="n"/>
+      <c r="BV26" s="29" t="n"/>
+      <c r="BW26" s="24" t="n"/>
+      <c r="BX26" s="30" t="n"/>
+      <c r="BY26" s="27" t="n"/>
+      <c r="BZ26" s="24" t="n"/>
+      <c r="CA26" s="31" t="n"/>
+      <c r="CB26" s="24" t="n"/>
+      <c r="CC26" s="24" t="n"/>
+      <c r="CD26" s="24" t="n"/>
+      <c r="CE26" s="24" t="n"/>
+      <c r="CF26" s="24" t="n"/>
+      <c r="CG26" s="24" t="n"/>
+      <c r="CH26" s="24" t="n"/>
+      <c r="CI26" s="24" t="n"/>
+      <c r="CJ26" s="24" t="n"/>
+      <c r="CK26" s="24" t="n"/>
+      <c r="CL26" s="24" t="n"/>
+      <c r="CM26" s="24" t="n"/>
+      <c r="CN26" s="24" t="n"/>
+      <c r="CO26" s="24" t="n"/>
+      <c r="CP26" s="24" t="n"/>
+      <c r="CQ26" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>e1b999e0b2d44565</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:16.736104Z</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="D27" s="24" t="inlineStr">
+        <is>
+          <t>67938</t>
+        </is>
+      </c>
+      <c r="E27" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F27" s="24" t="inlineStr">
+        <is>
+          <t>Ei Nerd Esports</t>
+        </is>
+      </c>
+      <c r="G27" s="24" t="inlineStr">
+        <is>
+          <t>RMD Gaming</t>
+        </is>
+      </c>
+      <c r="H27" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I27" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J27" s="25" t="n"/>
+      <c r="K27" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L27" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="M27" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="N27" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="O27" s="28" t="n">
+        <v>0.62116</v>
+      </c>
+      <c r="P27" s="28" t="n"/>
+      <c r="Q27" s="28" t="n">
+        <v>-0.07854</v>
+      </c>
+      <c r="R27" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T27" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U27" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V27" s="24" t="n"/>
+      <c r="W27" s="26" t="n"/>
+      <c r="X27" s="26" t="n"/>
+      <c r="Y27" s="25" t="n"/>
+      <c r="Z27" s="26" t="n"/>
+      <c r="AA27" s="28" t="n"/>
+      <c r="AB27" s="28" t="n"/>
+      <c r="AC27" s="30" t="n"/>
+      <c r="AD27" s="24" t="n"/>
+      <c r="AE27" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-lol-rmd-nerd-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF27" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG27" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH27" s="24" t="n"/>
+      <c r="AI27" s="31" t="n"/>
+      <c r="AJ27" s="31" t="n"/>
+      <c r="AK27" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL27" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM27" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN27" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO27" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP27" s="24" t="inlineStr">
+        <is>
+          <t>Ei Nerd Esports</t>
+        </is>
+      </c>
+      <c r="AQ27" s="24" t="inlineStr">
+        <is>
+          <t>Ei Nerd Esports</t>
+        </is>
+      </c>
+      <c r="AR27" s="24" t="inlineStr">
+        <is>
+          <t>Ei Nerd Esports</t>
+        </is>
+      </c>
+      <c r="AS27" s="24" t="inlineStr">
+        <is>
+          <t>RMD Gaming</t>
+        </is>
+      </c>
+      <c r="AT27" s="24" t="inlineStr">
+        <is>
+          <t>RMD Gaming</t>
+        </is>
+      </c>
+      <c r="AU27" s="24" t="inlineStr">
+        <is>
+          <t>RMD Gaming</t>
+        </is>
+      </c>
+      <c r="AV27" s="24" t="n"/>
+      <c r="AW27" s="24" t="n"/>
+      <c r="AX27" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY27" s="24" t="n"/>
+      <c r="AZ27" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA27" s="24" t="inlineStr">
+        <is>
+          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+        </is>
+      </c>
+      <c r="BB27" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC27" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD27" s="24" t="inlineStr">
+        <is>
+          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+        </is>
+      </c>
+      <c r="BE27" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF27" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG27" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:14.766196Z</t>
+        </is>
+      </c>
+      <c r="BI27" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ27" s="25" t="n"/>
+      <c r="BK27" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="BL27" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="BM27" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="BN27" s="28" t="n"/>
+      <c r="BO27" s="28" t="n"/>
+      <c r="BP27" s="25" t="n"/>
+      <c r="BQ27" s="27" t="n"/>
+      <c r="BR27" s="28" t="n"/>
+      <c r="BS27" s="28" t="n"/>
+      <c r="BT27" s="28" t="n"/>
+      <c r="BU27" s="25" t="n"/>
+      <c r="BV27" s="29" t="n"/>
+      <c r="BW27" s="24" t="n"/>
+      <c r="BX27" s="30" t="n"/>
+      <c r="BY27" s="27" t="n"/>
+      <c r="BZ27" s="24" t="n"/>
+      <c r="CA27" s="31" t="n"/>
+      <c r="CB27" s="24" t="n"/>
+      <c r="CC27" s="24" t="n"/>
+      <c r="CD27" s="24" t="n"/>
+      <c r="CE27" s="24" t="n"/>
+      <c r="CF27" s="24" t="n"/>
+      <c r="CG27" s="24" t="n"/>
+      <c r="CH27" s="24" t="n"/>
+      <c r="CI27" s="24" t="n"/>
+      <c r="CJ27" s="24" t="n"/>
+      <c r="CK27" s="24" t="n"/>
+      <c r="CL27" s="24" t="n"/>
+      <c r="CM27" s="24" t="n"/>
+      <c r="CN27" s="24" t="n"/>
+      <c r="CO27" s="24" t="n"/>
+      <c r="CP27" s="24" t="n"/>
+      <c r="CQ27" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>b051e3167888422a</t>
+        </is>
+      </c>
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:16.736104Z</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="D28" s="24" t="inlineStr">
+        <is>
+          <t>68011</t>
+        </is>
+      </c>
+      <c r="E28" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F28" s="24" t="inlineStr">
+        <is>
+          <t>Vivo Keyd Stars Academy</t>
+        </is>
+      </c>
+      <c r="G28" s="24" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="H28" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I28" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J28" s="25" t="n"/>
+      <c r="K28" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L28" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="M28" s="27" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="N28" s="28" t="n">
+        <v>0.509804</v>
+      </c>
+      <c r="O28" s="28" t="n">
+        <v>0.502316</v>
+      </c>
+      <c r="P28" s="28" t="n"/>
+      <c r="Q28" s="28" t="n">
+        <v>-0.007488</v>
+      </c>
+      <c r="R28" s="26" t="n">
+        <v>16</v>
+      </c>
+      <c r="S28" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T28" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U28" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V28" s="24" t="n"/>
+      <c r="W28" s="26" t="n"/>
+      <c r="X28" s="26" t="n"/>
+      <c r="Y28" s="25" t="n"/>
+      <c r="Z28" s="26" t="n"/>
+      <c r="AA28" s="28" t="n"/>
+      <c r="AB28" s="28" t="n"/>
+      <c r="AC28" s="30" t="n"/>
+      <c r="AD28" s="24" t="n"/>
+      <c r="AE28" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-lol-pnga-vksa-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF28" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG28" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH28" s="24" t="n"/>
+      <c r="AI28" s="31" t="n"/>
+      <c r="AJ28" s="31" t="n"/>
+      <c r="AK28" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL28" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM28" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN28" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO28" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP28" s="24" t="inlineStr">
+        <is>
+          <t>Vivo Keyd Stars Academy</t>
+        </is>
+      </c>
+      <c r="AQ28" s="24" t="inlineStr">
+        <is>
+          <t>Vivo Keyd Stars Academy</t>
+        </is>
+      </c>
+      <c r="AR28" s="24" t="inlineStr">
+        <is>
+          <t>Vivo Keyd Stars Academy</t>
+        </is>
+      </c>
+      <c r="AS28" s="24" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="AT28" s="24" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="AU28" s="24" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="AV28" s="24" t="n"/>
+      <c r="AW28" s="24" t="n"/>
+      <c r="AX28" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY28" s="24" t="n"/>
+      <c r="AZ28" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA28" s="24" t="inlineStr">
+        <is>
+          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+        </is>
+      </c>
+      <c r="BB28" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC28" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD28" s="24" t="inlineStr">
+        <is>
+          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+        </is>
+      </c>
+      <c r="BE28" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF28" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG28" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH28" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:15.724362Z</t>
+        </is>
+      </c>
+      <c r="BI28" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ28" s="25" t="n"/>
+      <c r="BK28" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="BL28" s="27" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="BM28" s="28" t="n">
+        <v>0.509804</v>
+      </c>
+      <c r="BN28" s="28" t="n"/>
+      <c r="BO28" s="28" t="n"/>
+      <c r="BP28" s="25" t="n"/>
+      <c r="BQ28" s="27" t="n"/>
+      <c r="BR28" s="28" t="n"/>
+      <c r="BS28" s="28" t="n"/>
+      <c r="BT28" s="28" t="n"/>
+      <c r="BU28" s="25" t="n"/>
+      <c r="BV28" s="29" t="n"/>
+      <c r="BW28" s="24" t="n"/>
+      <c r="BX28" s="30" t="n"/>
+      <c r="BY28" s="27" t="n"/>
+      <c r="BZ28" s="24" t="n"/>
+      <c r="CA28" s="31" t="n"/>
+      <c r="CB28" s="24" t="n"/>
+      <c r="CC28" s="24" t="n"/>
+      <c r="CD28" s="24" t="n"/>
+      <c r="CE28" s="24" t="n"/>
+      <c r="CF28" s="24" t="n"/>
+      <c r="CG28" s="24" t="n"/>
+      <c r="CH28" s="24" t="n"/>
+      <c r="CI28" s="24" t="n"/>
+      <c r="CJ28" s="24" t="n"/>
+      <c r="CK28" s="24" t="n"/>
+      <c r="CL28" s="24" t="n"/>
+      <c r="CM28" s="24" t="n"/>
+      <c r="CN28" s="24" t="n"/>
+      <c r="CO28" s="24" t="n"/>
+      <c r="CP28" s="24" t="n"/>
+      <c r="CQ28" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research/lol.xlsx
+++ b/data/research/lol.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ28" headerRowCount="1">
-  <autoFilter ref="A1:CQ28"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ46" headerRowCount="1">
+  <autoFilter ref="A1:CQ46"/>
   <tableColumns count="95">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -754,19 +754,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$28)</f>
+        <f>COUNTA('Picks'!$A$2:$A$46)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$28,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$46,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$28,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$46,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$28,"settled",'Picks'!$V$2:$V$28,"win")+COUNTIFS('Picks'!$U$2:$U$28,"settled",'Picks'!$V$2:$V$28,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$46,"settled",'Picks'!$V$2:$V$46,"win")+COUNTIFS('Picks'!$U$2:$U$46,"settled",'Picks'!$V$2:$V$46,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +794,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$28,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$46,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$28,"&gt;0",'Picks'!$V$2:$V$28,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$28,"&gt;0",'Picks'!$V$2:$V$28,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$46,"&gt;0",'Picks'!$V$2:$V$46,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$46,"&gt;0",'Picks'!$V$2:$V$46,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$28,"&gt;0",'Picks'!$V$2:$V$28,"win")/(COUNTIFS('Picks'!$BX$2:$BX$28,"&gt;0",'Picks'!$V$2:$V$28,"win")+COUNTIFS('Picks'!$BX$2:$BX$28,"&gt;0",'Picks'!$V$2:$V$28,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$46,"&gt;0",'Picks'!$V$2:$V$46,"win")/(COUNTIFS('Picks'!$BX$2:$BX$46,"&gt;0",'Picks'!$V$2:$V$46,"win")+COUNTIFS('Picks'!$BX$2:$BX$46,"&gt;0",'Picks'!$V$2:$V$46,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$28)/SUM('Picks'!$BX$2:$BX$28),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$46)/SUM('Picks'!$BX$2:$BX$46),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +834,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$28)</f>
+        <f>SUM('Picks'!$BY$2:$BY$46)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$28,"&lt;&gt;",'Picks'!$AB$2:$AB$28),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$46,"&lt;&gt;",'Picks'!$AB$2:$AB$46),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$28,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$28,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$46,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$46,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$28,'Picks'!$AM$2:$AM$28,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$46,'Picks'!$AM$2:$AM$46,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +901,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$28,$A14,'Picks'!$U$2:$U$28,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$46,$A14,'Picks'!$U$2:$U$46,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$28,$A14,'Picks'!$U$2:$U$28,"settled",'Picks'!$V$2:$V$28,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$46,$A14,'Picks'!$U$2:$U$46,"settled",'Picks'!$V$2:$V$46,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$28,$A14,'Picks'!$U$2:$U$28,"settled",'Picks'!$V$2:$V$28,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$46,$A14,'Picks'!$U$2:$U$46,"settled",'Picks'!$V$2:$V$46,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +917,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$28,'Picks'!$H$2:$H$28,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$46,'Picks'!$H$2:$H$46,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$28,'Picks'!$H$2:$H$28,$A14,'Picks'!$U$2:$U$28,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$46,'Picks'!$H$2:$H$46,$A14,'Picks'!$U$2:$U$46,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +932,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$28,$A15,'Picks'!$U$2:$U$28,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$46,$A15,'Picks'!$U$2:$U$46,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$28,$A15,'Picks'!$U$2:$U$28,"settled",'Picks'!$V$2:$V$28,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$46,$A15,'Picks'!$U$2:$U$46,"settled",'Picks'!$V$2:$V$46,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$28,$A15,'Picks'!$U$2:$U$28,"settled",'Picks'!$V$2:$V$28,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$46,$A15,'Picks'!$U$2:$U$46,"settled",'Picks'!$V$2:$V$46,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +948,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$28,'Picks'!$H$2:$H$28,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$46,'Picks'!$H$2:$H$46,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$28,'Picks'!$H$2:$H$28,$A15,'Picks'!$U$2:$U$28,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$46,'Picks'!$H$2:$H$46,$A15,'Picks'!$U$2:$U$46,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +963,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$28,$A16,'Picks'!$U$2:$U$28,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$46,$A16,'Picks'!$U$2:$U$46,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$28,$A16,'Picks'!$U$2:$U$28,"settled",'Picks'!$V$2:$V$28,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$46,$A16,'Picks'!$U$2:$U$46,"settled",'Picks'!$V$2:$V$46,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$28,$A16,'Picks'!$U$2:$U$28,"settled",'Picks'!$V$2:$V$28,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$46,$A16,'Picks'!$U$2:$U$46,"settled",'Picks'!$V$2:$V$46,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +979,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$28,'Picks'!$H$2:$H$28,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$46,'Picks'!$H$2:$H$46,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$28,'Picks'!$H$2:$H$28,$A16,'Picks'!$U$2:$U$28,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$46,'Picks'!$H$2:$H$46,$A16,'Picks'!$U$2:$U$46,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ28"/>
+  <dimension ref="A1:CQ46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6840,18 +6840,38 @@
       </c>
       <c r="U20" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V20" s="24" t="n"/>
-      <c r="W20" s="26" t="n"/>
-      <c r="X20" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V20" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W20" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X20" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y20" s="25" t="n"/>
-      <c r="Z20" s="26" t="n"/>
-      <c r="AA20" s="28" t="n"/>
-      <c r="AB20" s="28" t="n"/>
-      <c r="AC20" s="30" t="n"/>
-      <c r="AD20" s="24" t="n"/>
+      <c r="Z20" s="26" t="n">
+        <v>-186</v>
+      </c>
+      <c r="AA20" s="28" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AB20" s="28" t="n">
+        <v>-0.00035</v>
+      </c>
+      <c r="AC20" s="30" t="n">
+        <v>0.672</v>
+      </c>
+      <c r="AD20" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:13:21.369953Z</t>
+        </is>
+      </c>
       <c r="AE20" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.6500 (market_slug=aec-lol-fnc-mkoi-2026-08-02).</t>
@@ -6994,8 +7014,12 @@
       <c r="BN20" s="28" t="n"/>
       <c r="BO20" s="28" t="n"/>
       <c r="BP20" s="25" t="n"/>
-      <c r="BQ20" s="27" t="n"/>
-      <c r="BR20" s="28" t="n"/>
+      <c r="BQ20" s="27" t="n">
+        <v>1.537634</v>
+      </c>
+      <c r="BR20" s="28" t="n">
+        <v>0.65</v>
+      </c>
       <c r="BS20" s="28" t="n"/>
       <c r="BT20" s="28" t="n"/>
       <c r="BU20" s="25" t="n"/>
@@ -7029,12 +7053,12 @@
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="24" t="inlineStr">
         <is>
-          <t>0fe6aecb14c149f9</t>
+          <t>ec894d2a1ca74d47</t>
         </is>
       </c>
       <c r="B21" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:24:16.736104Z</t>
+          <t>2026-08-03T06:30:34.654651Z</t>
         </is>
       </c>
       <c r="C21" s="24" t="inlineStr">
@@ -7079,23 +7103,23 @@
         </is>
       </c>
       <c r="L21" s="26" t="n">
-        <v>-144</v>
+        <v>-113</v>
       </c>
       <c r="M21" s="27" t="n">
-        <v>1.694444</v>
+        <v>1.884956</v>
       </c>
       <c r="N21" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.530516</v>
       </c>
       <c r="O21" s="28" t="n">
-        <v>0.5360740000000001</v>
+        <v>0.536423</v>
       </c>
       <c r="P21" s="28" t="n"/>
       <c r="Q21" s="28" t="n">
-        <v>-0.05409</v>
+        <v>0.005907</v>
       </c>
       <c r="R21" s="26" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="S21" s="29" t="n">
         <v>1</v>
@@ -7107,21 +7131,41 @@
       </c>
       <c r="U21" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V21" s="24" t="n"/>
-      <c r="W21" s="26" t="n"/>
-      <c r="X21" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V21" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W21" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X21" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y21" s="25" t="n"/>
-      <c r="Z21" s="26" t="n"/>
-      <c r="AA21" s="28" t="n"/>
-      <c r="AB21" s="28" t="n"/>
-      <c r="AC21" s="30" t="n"/>
-      <c r="AD21" s="24" t="n"/>
+      <c r="Z21" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="AA21" s="28" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AB21" s="28" t="n">
+        <v>-0.000516</v>
+      </c>
+      <c r="AC21" s="30" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="AD21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:06:50.751709Z</t>
+        </is>
+      </c>
       <c r="AE21" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-lol-gen-hle-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.5300 (market_slug=aec-lol-gen-hle-2026-08-03).</t>
         </is>
       </c>
       <c r="AF21" s="31" t="inlineStr">
@@ -7205,7 +7249,7 @@
       </c>
       <c r="BA21" s="24" t="inlineStr">
         <is>
-          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+          <t>ff2b770f59073a39e60976cbc1ae4f05ce9c0ac0477f1609e756119cbdd7431b</t>
         </is>
       </c>
       <c r="BB21" s="24" t="inlineStr">
@@ -7220,7 +7264,7 @@
       </c>
       <c r="BD21" s="24" t="inlineStr">
         <is>
-          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+          <t>ff2b770f59073a39e60976cbc1ae4f05ce9c0ac0477f1609e756119cbdd7431b</t>
         </is>
       </c>
       <c r="BE21" s="24" t="inlineStr">
@@ -7240,7 +7284,7 @@
       </c>
       <c r="BH21" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:24:08.792428Z</t>
+          <t>2026-08-03T06:30:12.139868Z</t>
         </is>
       </c>
       <c r="BI21" s="24" t="inlineStr">
@@ -7250,19 +7294,23 @@
       </c>
       <c r="BJ21" s="25" t="n"/>
       <c r="BK21" s="26" t="n">
-        <v>-144</v>
+        <v>-113</v>
       </c>
       <c r="BL21" s="27" t="n">
-        <v>1.694444</v>
+        <v>1.884956</v>
       </c>
       <c r="BM21" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.530516</v>
       </c>
       <c r="BN21" s="28" t="n"/>
       <c r="BO21" s="28" t="n"/>
       <c r="BP21" s="25" t="n"/>
-      <c r="BQ21" s="27" t="n"/>
-      <c r="BR21" s="28" t="n"/>
+      <c r="BQ21" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="BR21" s="28" t="n">
+        <v>0.53</v>
+      </c>
       <c r="BS21" s="28" t="n"/>
       <c r="BT21" s="28" t="n"/>
       <c r="BU21" s="25" t="n"/>
@@ -7289,29 +7337,29 @@
       <c r="CP21" s="24" t="n"/>
       <c r="CQ21" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="24" t="inlineStr">
         <is>
-          <t>148846ecebb94256</t>
+          <t>189c180a73404fa7</t>
         </is>
       </c>
       <c r="B22" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:24:16.736104Z</t>
+          <t>2026-08-03T06:30:34.654651Z</t>
         </is>
       </c>
       <c r="C22" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T08:00:00Z</t>
+          <t>2026-08-03T10:00:00Z</t>
         </is>
       </c>
       <c r="D22" s="24" t="inlineStr">
         <is>
-          <t>67492</t>
+          <t>67511</t>
         </is>
       </c>
       <c r="E22" s="24" t="inlineStr">
@@ -7321,12 +7369,12 @@
       </c>
       <c r="F22" s="24" t="inlineStr">
         <is>
-          <t>BNK FearX Youth</t>
+          <t>Dplus KIA Challengers</t>
         </is>
       </c>
       <c r="G22" s="24" t="inlineStr">
         <is>
-          <t>HANJIN BRION Challengers</t>
+          <t>DN SOOPers Challengers</t>
         </is>
       </c>
       <c r="H22" s="24" t="inlineStr">
@@ -7346,49 +7394,69 @@
         </is>
       </c>
       <c r="L22" s="26" t="n">
-        <v>-223</v>
+        <v>-170</v>
       </c>
       <c r="M22" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.588235</v>
       </c>
       <c r="N22" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.62963</v>
       </c>
       <c r="O22" s="28" t="n">
-        <v>0.634708</v>
+        <v>0.703892</v>
       </c>
       <c r="P22" s="28" t="n"/>
       <c r="Q22" s="28" t="n">
-        <v>-0.055694</v>
+        <v>0.07426199999999999</v>
       </c>
       <c r="R22" s="26" t="n">
+        <v>57</v>
+      </c>
+      <c r="S22" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U22" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V22" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W22" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="S22" s="29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T22" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U22" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V22" s="24" t="n"/>
-      <c r="W22" s="26" t="n"/>
-      <c r="X22" s="26" t="n"/>
+      <c r="X22" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y22" s="25" t="n"/>
-      <c r="Z22" s="26" t="n"/>
-      <c r="AA22" s="28" t="n"/>
-      <c r="AB22" s="28" t="n"/>
-      <c r="AC22" s="30" t="n"/>
-      <c r="AD22" s="24" t="n"/>
+      <c r="Z22" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="AA22" s="28" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AB22" s="28" t="n">
+        <v>0.00037</v>
+      </c>
+      <c r="AC22" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T13:27:30.699600Z</t>
+        </is>
+      </c>
       <c r="AE22" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-lol-hbc-foxy-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-lol-dnsc-dkc-2026-08-03).</t>
         </is>
       </c>
       <c r="AF22" s="31" t="inlineStr">
@@ -7398,7 +7466,7 @@
       </c>
       <c r="AG22" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH22" s="24" t="n"/>
@@ -7406,7 +7474,7 @@
       <c r="AJ22" s="31" t="n"/>
       <c r="AK22" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL22" s="26" t="n">
@@ -7414,47 +7482,47 @@
       </c>
       <c r="AM22" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN22" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO22" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP22" s="24" t="inlineStr">
         <is>
-          <t>BNK FearX Youth</t>
+          <t>Dplus KIA Challengers</t>
         </is>
       </c>
       <c r="AQ22" s="24" t="inlineStr">
         <is>
-          <t>BNK FearX Youth</t>
+          <t>Dplus KIA Challengers</t>
         </is>
       </c>
       <c r="AR22" s="24" t="inlineStr">
         <is>
-          <t>BNK FearX Youth</t>
+          <t>Dplus KIA Challengers</t>
         </is>
       </c>
       <c r="AS22" s="24" t="inlineStr">
         <is>
-          <t>HANJIN BRION Challengers</t>
+          <t>DN SOOPers Challengers</t>
         </is>
       </c>
       <c r="AT22" s="24" t="inlineStr">
         <is>
-          <t>HANJIN BRION Challengers</t>
+          <t>DN SOOPers Challengers</t>
         </is>
       </c>
       <c r="AU22" s="24" t="inlineStr">
         <is>
-          <t>HANJIN BRION Challengers</t>
+          <t>DN SOOPers Challengers</t>
         </is>
       </c>
       <c r="AV22" s="24" t="n"/>
@@ -7472,7 +7540,7 @@
       </c>
       <c r="BA22" s="24" t="inlineStr">
         <is>
-          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+          <t>ff2b770f59073a39e60976cbc1ae4f05ce9c0ac0477f1609e756119cbdd7431b</t>
         </is>
       </c>
       <c r="BB22" s="24" t="inlineStr">
@@ -7487,7 +7555,7 @@
       </c>
       <c r="BD22" s="24" t="inlineStr">
         <is>
-          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+          <t>ff2b770f59073a39e60976cbc1ae4f05ce9c0ac0477f1609e756119cbdd7431b</t>
         </is>
       </c>
       <c r="BE22" s="24" t="inlineStr">
@@ -7507,7 +7575,7 @@
       </c>
       <c r="BH22" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:24:09.253322Z</t>
+          <t>2026-08-03T06:30:13.245481Z</t>
         </is>
       </c>
       <c r="BI22" s="24" t="inlineStr">
@@ -7517,19 +7585,23 @@
       </c>
       <c r="BJ22" s="25" t="n"/>
       <c r="BK22" s="26" t="n">
-        <v>-223</v>
+        <v>-170</v>
       </c>
       <c r="BL22" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.588235</v>
       </c>
       <c r="BM22" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.62963</v>
       </c>
       <c r="BN22" s="28" t="n"/>
       <c r="BO22" s="28" t="n"/>
       <c r="BP22" s="25" t="n"/>
-      <c r="BQ22" s="27" t="n"/>
-      <c r="BR22" s="28" t="n"/>
+      <c r="BQ22" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="BR22" s="28" t="n">
+        <v>0.63</v>
+      </c>
       <c r="BS22" s="28" t="n"/>
       <c r="BT22" s="28" t="n"/>
       <c r="BU22" s="25" t="n"/>
@@ -7556,29 +7628,29 @@
       <c r="CP22" s="24" t="n"/>
       <c r="CQ22" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="24" t="inlineStr">
         <is>
-          <t>65b82d9b551747a1</t>
+          <t>48604a24f80c46ae</t>
         </is>
       </c>
       <c r="B23" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:24:16.736104Z</t>
+          <t>2026-08-03T13:30:58.881408Z</t>
         </is>
       </c>
       <c r="C23" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T10:00:00Z</t>
+          <t>2026-08-03T15:00:00Z</t>
         </is>
       </c>
       <c r="D23" s="24" t="inlineStr">
         <is>
-          <t>67511</t>
+          <t>67566</t>
         </is>
       </c>
       <c r="E23" s="24" t="inlineStr">
@@ -7588,12 +7660,12 @@
       </c>
       <c r="F23" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA Challengers</t>
+          <t>Shifters</t>
         </is>
       </c>
       <c r="G23" s="24" t="inlineStr">
         <is>
-          <t>DN SOOPers Challengers</t>
+          <t>Natus Vincere</t>
         </is>
       </c>
       <c r="H23" s="24" t="inlineStr">
@@ -7603,7 +7675,7 @@
       </c>
       <c r="I23" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J23" s="25" t="n"/>
@@ -7622,14 +7694,14 @@
         <v>0.690402</v>
       </c>
       <c r="O23" s="28" t="n">
-        <v>0.70331</v>
+        <v>0.745478</v>
       </c>
       <c r="P23" s="28" t="n"/>
       <c r="Q23" s="28" t="n">
-        <v>0.012908</v>
+        <v>0.055076</v>
       </c>
       <c r="R23" s="26" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="S23" s="29" t="n">
         <v>2</v>
@@ -7641,21 +7713,41 @@
       </c>
       <c r="U23" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V23" s="24" t="n"/>
-      <c r="W23" s="26" t="n"/>
-      <c r="X23" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V23" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W23" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y23" s="25" t="n"/>
-      <c r="Z23" s="26" t="n"/>
-      <c r="AA23" s="28" t="n"/>
-      <c r="AB23" s="28" t="n"/>
-      <c r="AC23" s="30" t="n"/>
-      <c r="AD23" s="24" t="n"/>
+      <c r="Z23" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="AA23" s="28" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AB23" s="28" t="n">
+        <v>-0.000402</v>
+      </c>
+      <c r="AC23" s="30" t="n">
+        <v>0.8969</v>
+      </c>
+      <c r="AD23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T17:05:58.041180Z</t>
+        </is>
+      </c>
       <c r="AE23" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-lol-dnsc-dkc-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-lol-navi-shft-2026-08-03).</t>
         </is>
       </c>
       <c r="AF23" s="31" t="inlineStr">
@@ -7696,32 +7788,32 @@
       </c>
       <c r="AP23" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA Challengers</t>
+          <t>Shifters</t>
         </is>
       </c>
       <c r="AQ23" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA Challengers</t>
+          <t>Shifters</t>
         </is>
       </c>
       <c r="AR23" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA Challengers</t>
+          <t>Shifters</t>
         </is>
       </c>
       <c r="AS23" s="24" t="inlineStr">
         <is>
-          <t>DN SOOPers Challengers</t>
+          <t>Natus Vincere</t>
         </is>
       </c>
       <c r="AT23" s="24" t="inlineStr">
         <is>
-          <t>DN SOOPers Challengers</t>
+          <t>Natus Vincere</t>
         </is>
       </c>
       <c r="AU23" s="24" t="inlineStr">
         <is>
-          <t>DN SOOPers Challengers</t>
+          <t>Natus Vincere</t>
         </is>
       </c>
       <c r="AV23" s="24" t="n"/>
@@ -7739,7 +7831,7 @@
       </c>
       <c r="BA23" s="24" t="inlineStr">
         <is>
-          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+          <t>8e100718c38982e9b6a67d6c835251aad775fa6c0f7d64cbcae66021f2cd7f9c</t>
         </is>
       </c>
       <c r="BB23" s="24" t="inlineStr">
@@ -7754,7 +7846,7 @@
       </c>
       <c r="BD23" s="24" t="inlineStr">
         <is>
-          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+          <t>8e100718c38982e9b6a67d6c835251aad775fa6c0f7d64cbcae66021f2cd7f9c</t>
         </is>
       </c>
       <c r="BE23" s="24" t="inlineStr">
@@ -7774,7 +7866,7 @@
       </c>
       <c r="BH23" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:24:09.781954Z</t>
+          <t>2026-08-03T13:30:33.645010Z</t>
         </is>
       </c>
       <c r="BI23" s="24" t="inlineStr">
@@ -7795,8 +7887,12 @@
       <c r="BN23" s="28" t="n"/>
       <c r="BO23" s="28" t="n"/>
       <c r="BP23" s="25" t="n"/>
-      <c r="BQ23" s="27" t="n"/>
-      <c r="BR23" s="28" t="n"/>
+      <c r="BQ23" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="BR23" s="28" t="n">
+        <v>0.6899999999999999</v>
+      </c>
       <c r="BS23" s="28" t="n"/>
       <c r="BT23" s="28" t="n"/>
       <c r="BU23" s="25" t="n"/>
@@ -7830,22 +7926,22 @@
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="24" t="inlineStr">
         <is>
-          <t>a1231e3cef1a450e</t>
+          <t>041c950aba214cca</t>
         </is>
       </c>
       <c r="B24" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:24:16.736104Z</t>
+          <t>2026-08-03T17:09:03.086605Z</t>
         </is>
       </c>
       <c r="C24" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T10:30:00Z</t>
+          <t>2026-08-03T18:00:00Z</t>
         </is>
       </c>
       <c r="D24" s="24" t="inlineStr">
         <is>
-          <t>67515</t>
+          <t>67655</t>
         </is>
       </c>
       <c r="E24" s="24" t="inlineStr">
@@ -7855,12 +7951,12 @@
       </c>
       <c r="F24" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Lundqvist Lightside</t>
         </is>
       </c>
       <c r="G24" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Red Force</t>
+          <t>LEO</t>
         </is>
       </c>
       <c r="H24" s="24" t="inlineStr">
@@ -7870,7 +7966,7 @@
       </c>
       <c r="I24" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J24" s="25" t="n"/>
@@ -7880,26 +7976,26 @@
         </is>
       </c>
       <c r="L24" s="26" t="n">
-        <v>-156</v>
+        <v>-203</v>
       </c>
       <c r="M24" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.492611</v>
       </c>
       <c r="N24" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.669967</v>
       </c>
       <c r="O24" s="28" t="n">
-        <v>0.746406</v>
+        <v>0.617946</v>
       </c>
       <c r="P24" s="28" t="n"/>
       <c r="Q24" s="28" t="n">
-        <v>0.137031</v>
+        <v>-0.052021</v>
       </c>
       <c r="R24" s="26" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="S24" s="29" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="T24" s="24" t="inlineStr">
         <is>
@@ -7908,21 +8004,41 @@
       </c>
       <c r="U24" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V24" s="24" t="n"/>
-      <c r="W24" s="26" t="n"/>
-      <c r="X24" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V24" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W24" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X24" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y24" s="25" t="n"/>
-      <c r="Z24" s="26" t="n"/>
-      <c r="AA24" s="28" t="n"/>
-      <c r="AB24" s="28" t="n"/>
-      <c r="AC24" s="30" t="n"/>
-      <c r="AD24" s="24" t="n"/>
+      <c r="Z24" s="26" t="n">
+        <v>-203</v>
+      </c>
+      <c r="AA24" s="28" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AB24" s="28" t="n">
+        <v>3.3e-05</v>
+      </c>
+      <c r="AC24" s="30" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T22:55:40.163072Z</t>
+        </is>
+      </c>
       <c r="AE24" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-lol-ns-t1-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-lol-leo-ll-2026-08-03).</t>
         </is>
       </c>
       <c r="AF24" s="31" t="inlineStr">
@@ -7932,7 +8048,7 @@
       </c>
       <c r="AG24" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH24" s="24" t="n"/>
@@ -7940,7 +8056,7 @@
       <c r="AJ24" s="31" t="n"/>
       <c r="AK24" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL24" s="26" t="n">
@@ -7948,47 +8064,47 @@
       </c>
       <c r="AM24" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN24" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO24" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP24" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Lundqvist Lightside</t>
         </is>
       </c>
       <c r="AQ24" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Lundqvist Lightside</t>
         </is>
       </c>
       <c r="AR24" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Lundqvist Lightside</t>
         </is>
       </c>
       <c r="AS24" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Red Force</t>
+          <t>LEO</t>
         </is>
       </c>
       <c r="AT24" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Red Force</t>
+          <t>LEO</t>
         </is>
       </c>
       <c r="AU24" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Red Force</t>
+          <t>LEO</t>
         </is>
       </c>
       <c r="AV24" s="24" t="n"/>
@@ -8006,7 +8122,7 @@
       </c>
       <c r="BA24" s="24" t="inlineStr">
         <is>
-          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+          <t>efcbb93ea7594fbafcf9325219d1c95ecb0ddde1698943dd2007a07a55350fa4</t>
         </is>
       </c>
       <c r="BB24" s="24" t="inlineStr">
@@ -8021,7 +8137,7 @@
       </c>
       <c r="BD24" s="24" t="inlineStr">
         <is>
-          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+          <t>efcbb93ea7594fbafcf9325219d1c95ecb0ddde1698943dd2007a07a55350fa4</t>
         </is>
       </c>
       <c r="BE24" s="24" t="inlineStr">
@@ -8041,7 +8157,7 @@
       </c>
       <c r="BH24" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:24:10.279453Z</t>
+          <t>2026-08-03T17:08:42.741673Z</t>
         </is>
       </c>
       <c r="BI24" s="24" t="inlineStr">
@@ -8051,19 +8167,23 @@
       </c>
       <c r="BJ24" s="25" t="n"/>
       <c r="BK24" s="26" t="n">
-        <v>-156</v>
+        <v>-203</v>
       </c>
       <c r="BL24" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.492611</v>
       </c>
       <c r="BM24" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.669967</v>
       </c>
       <c r="BN24" s="28" t="n"/>
       <c r="BO24" s="28" t="n"/>
       <c r="BP24" s="25" t="n"/>
-      <c r="BQ24" s="27" t="n"/>
-      <c r="BR24" s="28" t="n"/>
+      <c r="BQ24" s="27" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="BR24" s="28" t="n">
+        <v>0.67</v>
+      </c>
       <c r="BS24" s="28" t="n"/>
       <c r="BT24" s="28" t="n"/>
       <c r="BU24" s="25" t="n"/>
@@ -8090,29 +8210,29 @@
       <c r="CP24" s="24" t="n"/>
       <c r="CQ24" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="24" t="inlineStr">
         <is>
-          <t>800f259dfb7c4c27</t>
+          <t>809bba47d823450b</t>
         </is>
       </c>
       <c r="B25" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:24:16.736104Z</t>
+          <t>2026-08-03T17:09:03.086605Z</t>
         </is>
       </c>
       <c r="C25" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00Z</t>
+          <t>2026-08-03T19:00:00Z</t>
         </is>
       </c>
       <c r="D25" s="24" t="inlineStr">
         <is>
-          <t>67566</t>
+          <t>63451</t>
         </is>
       </c>
       <c r="E25" s="24" t="inlineStr">
@@ -8122,12 +8242,12 @@
       </c>
       <c r="F25" s="24" t="inlineStr">
         <is>
-          <t>Shifters</t>
+          <t>Vivo Keyd Stars Academy</t>
         </is>
       </c>
       <c r="G25" s="24" t="inlineStr">
         <is>
-          <t>Natus Vincere</t>
+          <t>Team Solid</t>
         </is>
       </c>
       <c r="H25" s="24" t="inlineStr">
@@ -8137,7 +8257,7 @@
       </c>
       <c r="I25" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J25" s="25" t="n"/>
@@ -8147,23 +8267,23 @@
         </is>
       </c>
       <c r="L25" s="26" t="n">
-        <v>-233</v>
+        <v>-223</v>
       </c>
       <c r="M25" s="27" t="n">
-        <v>1.429185</v>
+        <v>1.44843</v>
       </c>
       <c r="N25" s="28" t="n">
-        <v>0.6997</v>
+        <v>0.690402</v>
       </c>
       <c r="O25" s="28" t="n">
-        <v>0.746125</v>
+        <v>0.727674</v>
       </c>
       <c r="P25" s="28" t="n"/>
       <c r="Q25" s="28" t="n">
-        <v>0.046425</v>
+        <v>0.037272</v>
       </c>
       <c r="R25" s="26" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="S25" s="29" t="n">
         <v>2</v>
@@ -8175,21 +8295,41 @@
       </c>
       <c r="U25" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V25" s="24" t="n"/>
-      <c r="W25" s="26" t="n"/>
-      <c r="X25" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V25" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W25" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y25" s="25" t="n"/>
-      <c r="Z25" s="26" t="n"/>
-      <c r="AA25" s="28" t="n"/>
-      <c r="AB25" s="28" t="n"/>
-      <c r="AC25" s="30" t="n"/>
-      <c r="AD25" s="24" t="n"/>
+      <c r="Z25" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="AA25" s="28" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AB25" s="28" t="n">
+        <v>-0.000402</v>
+      </c>
+      <c r="AC25" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T19:52:08.258946Z</t>
+        </is>
+      </c>
       <c r="AE25" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-lol-navi-shft-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-lol-tse-vksa-2026-07-30).</t>
         </is>
       </c>
       <c r="AF25" s="31" t="inlineStr">
@@ -8199,7 +8339,7 @@
       </c>
       <c r="AG25" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH25" s="24" t="n"/>
@@ -8230,32 +8370,32 @@
       </c>
       <c r="AP25" s="24" t="inlineStr">
         <is>
-          <t>Shifters</t>
+          <t>Vivo Keyd Stars Academy</t>
         </is>
       </c>
       <c r="AQ25" s="24" t="inlineStr">
         <is>
-          <t>Shifters</t>
+          <t>Vivo Keyd Stars Academy</t>
         </is>
       </c>
       <c r="AR25" s="24" t="inlineStr">
         <is>
-          <t>Shifters</t>
+          <t>Vivo Keyd Stars Academy</t>
         </is>
       </c>
       <c r="AS25" s="24" t="inlineStr">
         <is>
-          <t>Natus Vincere</t>
+          <t>Team Solid</t>
         </is>
       </c>
       <c r="AT25" s="24" t="inlineStr">
         <is>
-          <t>Natus Vincere</t>
+          <t>Team Solid</t>
         </is>
       </c>
       <c r="AU25" s="24" t="inlineStr">
         <is>
-          <t>Natus Vincere</t>
+          <t>Team Solid</t>
         </is>
       </c>
       <c r="AV25" s="24" t="n"/>
@@ -8273,7 +8413,7 @@
       </c>
       <c r="BA25" s="24" t="inlineStr">
         <is>
-          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+          <t>efcbb93ea7594fbafcf9325219d1c95ecb0ddde1698943dd2007a07a55350fa4</t>
         </is>
       </c>
       <c r="BB25" s="24" t="inlineStr">
@@ -8288,7 +8428,7 @@
       </c>
       <c r="BD25" s="24" t="inlineStr">
         <is>
-          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+          <t>efcbb93ea7594fbafcf9325219d1c95ecb0ddde1698943dd2007a07a55350fa4</t>
         </is>
       </c>
       <c r="BE25" s="24" t="inlineStr">
@@ -8308,7 +8448,7 @@
       </c>
       <c r="BH25" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:24:10.786284Z</t>
+          <t>2026-08-03T17:08:43.723243Z</t>
         </is>
       </c>
       <c r="BI25" s="24" t="inlineStr">
@@ -8318,19 +8458,23 @@
       </c>
       <c r="BJ25" s="25" t="n"/>
       <c r="BK25" s="26" t="n">
-        <v>-233</v>
+        <v>-223</v>
       </c>
       <c r="BL25" s="27" t="n">
-        <v>1.429185</v>
+        <v>1.44843</v>
       </c>
       <c r="BM25" s="28" t="n">
-        <v>0.6997</v>
+        <v>0.690402</v>
       </c>
       <c r="BN25" s="28" t="n"/>
       <c r="BO25" s="28" t="n"/>
       <c r="BP25" s="25" t="n"/>
-      <c r="BQ25" s="27" t="n"/>
-      <c r="BR25" s="28" t="n"/>
+      <c r="BQ25" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="BR25" s="28" t="n">
+        <v>0.6899999999999999</v>
+      </c>
       <c r="BS25" s="28" t="n"/>
       <c r="BT25" s="28" t="n"/>
       <c r="BU25" s="25" t="n"/>
@@ -8364,12 +8508,12 @@
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="24" t="inlineStr">
         <is>
-          <t>c403f3e6973e46e2</t>
+          <t>f63ed8330d2b456d</t>
         </is>
       </c>
       <c r="B26" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:24:16.736104Z</t>
+          <t>2026-08-03T19:55:05.099553Z</t>
         </is>
       </c>
       <c r="C26" s="24" t="inlineStr">
@@ -8414,23 +8558,23 @@
         </is>
       </c>
       <c r="L26" s="26" t="n">
-        <v>-144</v>
+        <v>-233</v>
       </c>
       <c r="M26" s="27" t="n">
-        <v>1.694444</v>
+        <v>1.429185</v>
       </c>
       <c r="N26" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.6997</v>
       </c>
       <c r="O26" s="28" t="n">
-        <v>0.649195</v>
+        <v>0.648218</v>
       </c>
       <c r="P26" s="28" t="n"/>
       <c r="Q26" s="28" t="n">
-        <v>0.059031</v>
+        <v>-0.051482</v>
       </c>
       <c r="R26" s="26" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="S26" s="29" t="n">
         <v>1.75</v>
@@ -8442,21 +8586,41 @@
       </c>
       <c r="U26" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V26" s="24" t="n"/>
-      <c r="W26" s="26" t="n"/>
-      <c r="X26" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V26" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W26" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X26" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y26" s="25" t="n"/>
-      <c r="Z26" s="26" t="n"/>
-      <c r="AA26" s="28" t="n"/>
-      <c r="AB26" s="28" t="n"/>
-      <c r="AC26" s="30" t="n"/>
-      <c r="AD26" s="24" t="n"/>
+      <c r="Z26" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="AA26" s="28" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AB26" s="28" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="AC26" s="30" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="AD26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T01:58:52.039236Z</t>
+        </is>
+      </c>
       <c r="AE26" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-lol-vtc-doh-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-lol-vtc-doh-2026-08-03).</t>
         </is>
       </c>
       <c r="AF26" s="31" t="inlineStr">
@@ -8466,7 +8630,7 @@
       </c>
       <c r="AG26" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH26" s="24" t="n"/>
@@ -8474,7 +8638,7 @@
       <c r="AJ26" s="31" t="n"/>
       <c r="AK26" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL26" s="26" t="n">
@@ -8482,17 +8646,17 @@
       </c>
       <c r="AM26" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN26" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO26" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP26" s="24" t="inlineStr">
@@ -8540,7 +8704,7 @@
       </c>
       <c r="BA26" s="24" t="inlineStr">
         <is>
-          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+          <t>9ed3b7c0f543c614a78fccecbb0979eec8778e51fbb9fd911e0de01bc829c3f7</t>
         </is>
       </c>
       <c r="BB26" s="24" t="inlineStr">
@@ -8555,7 +8719,7 @@
       </c>
       <c r="BD26" s="24" t="inlineStr">
         <is>
-          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+          <t>9ed3b7c0f543c614a78fccecbb0979eec8778e51fbb9fd911e0de01bc829c3f7</t>
         </is>
       </c>
       <c r="BE26" s="24" t="inlineStr">
@@ -8575,7 +8739,7 @@
       </c>
       <c r="BH26" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:24:14.243617Z</t>
+          <t>2026-08-03T19:54:45.717086Z</t>
         </is>
       </c>
       <c r="BI26" s="24" t="inlineStr">
@@ -8585,19 +8749,23 @@
       </c>
       <c r="BJ26" s="25" t="n"/>
       <c r="BK26" s="26" t="n">
-        <v>-144</v>
+        <v>-233</v>
       </c>
       <c r="BL26" s="27" t="n">
-        <v>1.694444</v>
+        <v>1.429185</v>
       </c>
       <c r="BM26" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.6997</v>
       </c>
       <c r="BN26" s="28" t="n"/>
       <c r="BO26" s="28" t="n"/>
       <c r="BP26" s="25" t="n"/>
-      <c r="BQ26" s="27" t="n"/>
-      <c r="BR26" s="28" t="n"/>
+      <c r="BQ26" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="BR26" s="28" t="n">
+        <v>0.7</v>
+      </c>
       <c r="BS26" s="28" t="n"/>
       <c r="BT26" s="28" t="n"/>
       <c r="BU26" s="25" t="n"/>
@@ -8624,19 +8792,19 @@
       <c r="CP26" s="24" t="n"/>
       <c r="CQ26" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="24" t="inlineStr">
         <is>
-          <t>e1b999e0b2d44565</t>
+          <t>4f3d9aa6fc9b4d2c</t>
         </is>
       </c>
       <c r="B27" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:24:16.736104Z</t>
+          <t>2026-08-03T19:55:05.099553Z</t>
         </is>
       </c>
       <c r="C27" s="24" t="inlineStr">
@@ -8690,11 +8858,11 @@
         <v>0.6997</v>
       </c>
       <c r="O27" s="28" t="n">
-        <v>0.62116</v>
+        <v>0.623328</v>
       </c>
       <c r="P27" s="28" t="n"/>
       <c r="Q27" s="28" t="n">
-        <v>-0.07854</v>
+        <v>-0.076372</v>
       </c>
       <c r="R27" s="26" t="n">
         <v>0</v>
@@ -8709,18 +8877,38 @@
       </c>
       <c r="U27" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V27" s="24" t="n"/>
-      <c r="W27" s="26" t="n"/>
-      <c r="X27" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V27" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W27" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y27" s="25" t="n"/>
-      <c r="Z27" s="26" t="n"/>
-      <c r="AA27" s="28" t="n"/>
-      <c r="AB27" s="28" t="n"/>
-      <c r="AC27" s="30" t="n"/>
-      <c r="AD27" s="24" t="n"/>
+      <c r="Z27" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="AA27" s="28" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AB27" s="28" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="AC27" s="30" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T22:55:42.656458Z</t>
+        </is>
+      </c>
       <c r="AE27" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-lol-rmd-nerd-2026-08-03).</t>
@@ -8733,7 +8921,7 @@
       </c>
       <c r="AG27" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH27" s="24" t="n"/>
@@ -8807,7 +8995,7 @@
       </c>
       <c r="BA27" s="24" t="inlineStr">
         <is>
-          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+          <t>9ed3b7c0f543c614a78fccecbb0979eec8778e51fbb9fd911e0de01bc829c3f7</t>
         </is>
       </c>
       <c r="BB27" s="24" t="inlineStr">
@@ -8822,7 +9010,7 @@
       </c>
       <c r="BD27" s="24" t="inlineStr">
         <is>
-          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+          <t>9ed3b7c0f543c614a78fccecbb0979eec8778e51fbb9fd911e0de01bc829c3f7</t>
         </is>
       </c>
       <c r="BE27" s="24" t="inlineStr">
@@ -8842,7 +9030,7 @@
       </c>
       <c r="BH27" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:24:14.766196Z</t>
+          <t>2026-08-03T19:54:46.201689Z</t>
         </is>
       </c>
       <c r="BI27" s="24" t="inlineStr">
@@ -8863,8 +9051,12 @@
       <c r="BN27" s="28" t="n"/>
       <c r="BO27" s="28" t="n"/>
       <c r="BP27" s="25" t="n"/>
-      <c r="BQ27" s="27" t="n"/>
-      <c r="BR27" s="28" t="n"/>
+      <c r="BQ27" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="BR27" s="28" t="n">
+        <v>0.7</v>
+      </c>
       <c r="BS27" s="28" t="n"/>
       <c r="BT27" s="28" t="n"/>
       <c r="BU27" s="25" t="n"/>
@@ -8898,12 +9090,12 @@
     <row r="28" ht="36" customHeight="1">
       <c r="A28" s="24" t="inlineStr">
         <is>
-          <t>b051e3167888422a</t>
+          <t>a7f139b165184216</t>
         </is>
       </c>
       <c r="B28" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:24:16.736104Z</t>
+          <t>2026-08-03T19:55:05.099553Z</t>
         </is>
       </c>
       <c r="C28" s="24" t="inlineStr">
@@ -8938,7 +9130,7 @@
       </c>
       <c r="I28" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J28" s="25" t="n"/>
@@ -8948,23 +9140,23 @@
         </is>
       </c>
       <c r="L28" s="26" t="n">
-        <v>-104</v>
+        <v>113</v>
       </c>
       <c r="M28" s="27" t="n">
-        <v>1.961538</v>
+        <v>2.13</v>
       </c>
       <c r="N28" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.469484</v>
       </c>
       <c r="O28" s="28" t="n">
-        <v>0.502316</v>
+        <v>0.53706</v>
       </c>
       <c r="P28" s="28" t="n"/>
       <c r="Q28" s="28" t="n">
-        <v>-0.007488</v>
+        <v>0.067576</v>
       </c>
       <c r="R28" s="26" t="n">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="S28" s="29" t="n">
         <v>1</v>
@@ -8976,21 +9168,41 @@
       </c>
       <c r="U28" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V28" s="24" t="n"/>
-      <c r="W28" s="26" t="n"/>
-      <c r="X28" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V28" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W28" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y28" s="25" t="n"/>
-      <c r="Z28" s="26" t="n"/>
-      <c r="AA28" s="28" t="n"/>
-      <c r="AB28" s="28" t="n"/>
-      <c r="AC28" s="30" t="n"/>
-      <c r="AD28" s="24" t="n"/>
+      <c r="Z28" s="26" t="n">
+        <v>113</v>
+      </c>
+      <c r="AA28" s="28" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="AB28" s="28" t="n">
+        <v>0.000516</v>
+      </c>
+      <c r="AC28" s="30" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AD28" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T22:55:44.139370Z</t>
+        </is>
+      </c>
       <c r="AE28" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-lol-pnga-vksa-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.4700 (market_slug=aec-lol-pnga-vksa-2026-08-03).</t>
         </is>
       </c>
       <c r="AF28" s="31" t="inlineStr">
@@ -9074,7 +9286,7 @@
       </c>
       <c r="BA28" s="24" t="inlineStr">
         <is>
-          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+          <t>9ed3b7c0f543c614a78fccecbb0979eec8778e51fbb9fd911e0de01bc829c3f7</t>
         </is>
       </c>
       <c r="BB28" s="24" t="inlineStr">
@@ -9089,7 +9301,7 @@
       </c>
       <c r="BD28" s="24" t="inlineStr">
         <is>
-          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+          <t>9ed3b7c0f543c614a78fccecbb0979eec8778e51fbb9fd911e0de01bc829c3f7</t>
         </is>
       </c>
       <c r="BE28" s="24" t="inlineStr">
@@ -9109,7 +9321,7 @@
       </c>
       <c r="BH28" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:24:15.724362Z</t>
+          <t>2026-08-03T19:54:47.216198Z</t>
         </is>
       </c>
       <c r="BI28" s="24" t="inlineStr">
@@ -9119,19 +9331,23 @@
       </c>
       <c r="BJ28" s="25" t="n"/>
       <c r="BK28" s="26" t="n">
-        <v>-104</v>
+        <v>113</v>
       </c>
       <c r="BL28" s="27" t="n">
-        <v>1.961538</v>
+        <v>2.13</v>
       </c>
       <c r="BM28" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.469484</v>
       </c>
       <c r="BN28" s="28" t="n"/>
       <c r="BO28" s="28" t="n"/>
       <c r="BP28" s="25" t="n"/>
-      <c r="BQ28" s="27" t="n"/>
-      <c r="BR28" s="28" t="n"/>
+      <c r="BQ28" s="27" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BR28" s="28" t="n">
+        <v>0.47</v>
+      </c>
       <c r="BS28" s="28" t="n"/>
       <c r="BT28" s="28" t="n"/>
       <c r="BU28" s="25" t="n"/>
@@ -9158,7 +9374,4813 @@
       <c r="CP28" s="24" t="n"/>
       <c r="CQ28" s="24" t="inlineStr">
         <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>b2c01b5fde4a412c</t>
+        </is>
+      </c>
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:56.302645Z</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="D29" s="24" t="inlineStr">
+        <is>
+          <t>70669</t>
+        </is>
+      </c>
+      <c r="E29" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F29" s="24" t="inlineStr">
+        <is>
+          <t>Hanwha Life Esports</t>
+        </is>
+      </c>
+      <c r="G29" s="24" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="H29" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I29" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J29" s="25" t="n"/>
+      <c r="K29" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L29" s="26" t="n">
+        <v>-194</v>
+      </c>
+      <c r="M29" s="27" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="N29" s="28" t="n">
+        <v>0.659864</v>
+      </c>
+      <c r="O29" s="28" t="n">
+        <v>0.530268</v>
+      </c>
+      <c r="P29" s="28" t="n"/>
+      <c r="Q29" s="28" t="n">
+        <v>-0.129596</v>
+      </c>
+      <c r="R29" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T29" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U29" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V29" s="24" t="n"/>
+      <c r="W29" s="26" t="n"/>
+      <c r="X29" s="26" t="n"/>
+      <c r="Y29" s="25" t="n"/>
+      <c r="Z29" s="26" t="n"/>
+      <c r="AA29" s="28" t="n"/>
+      <c r="AB29" s="28" t="n"/>
+      <c r="AC29" s="30" t="n"/>
+      <c r="AD29" s="24" t="n"/>
+      <c r="AE29" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6600 (market_slug=aec-lol-t1-hle-2026-08-04).</t>
+        </is>
+      </c>
+      <c r="AF29" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG29" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH29" s="24" t="n"/>
+      <c r="AI29" s="31" t="n"/>
+      <c r="AJ29" s="31" t="n"/>
+      <c r="AK29" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL29" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM29" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN29" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO29" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP29" s="24" t="inlineStr">
+        <is>
+          <t>Hanwha Life Esports</t>
+        </is>
+      </c>
+      <c r="AQ29" s="24" t="inlineStr">
+        <is>
+          <t>Hanwha Life Esports</t>
+        </is>
+      </c>
+      <c r="AR29" s="24" t="inlineStr">
+        <is>
+          <t>Hanwha Life Esports</t>
+        </is>
+      </c>
+      <c r="AS29" s="24" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="AT29" s="24" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="AU29" s="24" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="AV29" s="24" t="n"/>
+      <c r="AW29" s="24" t="n"/>
+      <c r="AX29" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY29" s="24" t="n"/>
+      <c r="AZ29" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA29" s="24" t="inlineStr">
+        <is>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+        </is>
+      </c>
+      <c r="BB29" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC29" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD29" s="24" t="inlineStr">
+        <is>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+        </is>
+      </c>
+      <c r="BE29" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF29" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG29" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH29" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:40.152554Z</t>
+        </is>
+      </c>
+      <c r="BI29" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ29" s="25" t="n"/>
+      <c r="BK29" s="26" t="n">
+        <v>-194</v>
+      </c>
+      <c r="BL29" s="27" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="BM29" s="28" t="n">
+        <v>0.659864</v>
+      </c>
+      <c r="BN29" s="28" t="n"/>
+      <c r="BO29" s="28" t="n"/>
+      <c r="BP29" s="25" t="n"/>
+      <c r="BQ29" s="27" t="n"/>
+      <c r="BR29" s="28" t="n"/>
+      <c r="BS29" s="28" t="n"/>
+      <c r="BT29" s="28" t="n"/>
+      <c r="BU29" s="25" t="n"/>
+      <c r="BV29" s="29" t="n"/>
+      <c r="BW29" s="24" t="n"/>
+      <c r="BX29" s="30" t="n"/>
+      <c r="BY29" s="27" t="n"/>
+      <c r="BZ29" s="24" t="n"/>
+      <c r="CA29" s="31" t="n"/>
+      <c r="CB29" s="24" t="n"/>
+      <c r="CC29" s="24" t="n"/>
+      <c r="CD29" s="24" t="n"/>
+      <c r="CE29" s="24" t="n"/>
+      <c r="CF29" s="24" t="n"/>
+      <c r="CG29" s="24" t="n"/>
+      <c r="CH29" s="24" t="n"/>
+      <c r="CI29" s="24" t="n"/>
+      <c r="CJ29" s="24" t="n"/>
+      <c r="CK29" s="24" t="n"/>
+      <c r="CL29" s="24" t="n"/>
+      <c r="CM29" s="24" t="n"/>
+      <c r="CN29" s="24" t="n"/>
+      <c r="CO29" s="24" t="n"/>
+      <c r="CP29" s="24" t="n"/>
+      <c r="CQ29" s="24" t="inlineStr">
+        <is>
           <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>3519cc599f834356</t>
+        </is>
+      </c>
+      <c r="B30" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:56.302645Z</t>
+        </is>
+      </c>
+      <c r="C30" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="D30" s="24" t="inlineStr">
+        <is>
+          <t>68284</t>
+        </is>
+      </c>
+      <c r="E30" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F30" s="24" t="inlineStr">
+        <is>
+          <t>KT Rolster Challengers</t>
+        </is>
+      </c>
+      <c r="G30" s="24" t="inlineStr">
+        <is>
+          <t>T1 Academy</t>
+        </is>
+      </c>
+      <c r="H30" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I30" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J30" s="25" t="n"/>
+      <c r="K30" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L30" s="26" t="n">
+        <v>-213</v>
+      </c>
+      <c r="M30" s="27" t="n">
+        <v>1.469484</v>
+      </c>
+      <c r="N30" s="28" t="n">
+        <v>0.680511</v>
+      </c>
+      <c r="O30" s="28" t="n">
+        <v>0.613874</v>
+      </c>
+      <c r="P30" s="28" t="n"/>
+      <c r="Q30" s="28" t="n">
+        <v>-0.066637</v>
+      </c>
+      <c r="R30" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T30" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U30" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V30" s="24" t="n"/>
+      <c r="W30" s="26" t="n"/>
+      <c r="X30" s="26" t="n"/>
+      <c r="Y30" s="25" t="n"/>
+      <c r="Z30" s="26" t="n"/>
+      <c r="AA30" s="28" t="n"/>
+      <c r="AB30" s="28" t="n"/>
+      <c r="AC30" s="30" t="n"/>
+      <c r="AD30" s="24" t="n"/>
+      <c r="AE30" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-lol-t1a-ktc-2026-08-04).</t>
+        </is>
+      </c>
+      <c r="AF30" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG30" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH30" s="24" t="n"/>
+      <c r="AI30" s="31" t="n"/>
+      <c r="AJ30" s="31" t="n"/>
+      <c r="AK30" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL30" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM30" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN30" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO30" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP30" s="24" t="inlineStr">
+        <is>
+          <t>KT Rolster Challengers</t>
+        </is>
+      </c>
+      <c r="AQ30" s="24" t="inlineStr">
+        <is>
+          <t>KT Rolster Challengers</t>
+        </is>
+      </c>
+      <c r="AR30" s="24" t="inlineStr">
+        <is>
+          <t>KT Rolster Challengers</t>
+        </is>
+      </c>
+      <c r="AS30" s="24" t="inlineStr">
+        <is>
+          <t>T1 Academy</t>
+        </is>
+      </c>
+      <c r="AT30" s="24" t="inlineStr">
+        <is>
+          <t>T1 Academy</t>
+        </is>
+      </c>
+      <c r="AU30" s="24" t="inlineStr">
+        <is>
+          <t>T1 Academy</t>
+        </is>
+      </c>
+      <c r="AV30" s="24" t="n"/>
+      <c r="AW30" s="24" t="n"/>
+      <c r="AX30" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY30" s="24" t="n"/>
+      <c r="AZ30" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA30" s="24" t="inlineStr">
+        <is>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+        </is>
+      </c>
+      <c r="BB30" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC30" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD30" s="24" t="inlineStr">
+        <is>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+        </is>
+      </c>
+      <c r="BE30" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF30" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG30" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH30" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:41.711967Z</t>
+        </is>
+      </c>
+      <c r="BI30" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ30" s="25" t="n"/>
+      <c r="BK30" s="26" t="n">
+        <v>-213</v>
+      </c>
+      <c r="BL30" s="27" t="n">
+        <v>1.469484</v>
+      </c>
+      <c r="BM30" s="28" t="n">
+        <v>0.680511</v>
+      </c>
+      <c r="BN30" s="28" t="n"/>
+      <c r="BO30" s="28" t="n"/>
+      <c r="BP30" s="25" t="n"/>
+      <c r="BQ30" s="27" t="n"/>
+      <c r="BR30" s="28" t="n"/>
+      <c r="BS30" s="28" t="n"/>
+      <c r="BT30" s="28" t="n"/>
+      <c r="BU30" s="25" t="n"/>
+      <c r="BV30" s="29" t="n"/>
+      <c r="BW30" s="24" t="n"/>
+      <c r="BX30" s="30" t="n"/>
+      <c r="BY30" s="27" t="n"/>
+      <c r="BZ30" s="24" t="n"/>
+      <c r="CA30" s="31" t="n"/>
+      <c r="CB30" s="24" t="n"/>
+      <c r="CC30" s="24" t="n"/>
+      <c r="CD30" s="24" t="n"/>
+      <c r="CE30" s="24" t="n"/>
+      <c r="CF30" s="24" t="n"/>
+      <c r="CG30" s="24" t="n"/>
+      <c r="CH30" s="24" t="n"/>
+      <c r="CI30" s="24" t="n"/>
+      <c r="CJ30" s="24" t="n"/>
+      <c r="CK30" s="24" t="n"/>
+      <c r="CL30" s="24" t="n"/>
+      <c r="CM30" s="24" t="n"/>
+      <c r="CN30" s="24" t="n"/>
+      <c r="CO30" s="24" t="n"/>
+      <c r="CP30" s="24" t="n"/>
+      <c r="CQ30" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>3fb0de25f8e046fa</t>
+        </is>
+      </c>
+      <c r="B31" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:56.302645Z</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="D31" s="24" t="inlineStr">
+        <is>
+          <t>68295</t>
+        </is>
+      </c>
+      <c r="E31" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F31" s="24" t="inlineStr">
+        <is>
+          <t>Kiwoom DRX</t>
+        </is>
+      </c>
+      <c r="G31" s="24" t="inlineStr">
+        <is>
+          <t>HANJIN BRION</t>
+        </is>
+      </c>
+      <c r="H31" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I31" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J31" s="25" t="n"/>
+      <c r="K31" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L31" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="M31" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="N31" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O31" s="28" t="n">
+        <v>0.578292</v>
+      </c>
+      <c r="P31" s="28" t="n"/>
+      <c r="Q31" s="28" t="n">
+        <v>-0.021708</v>
+      </c>
+      <c r="R31" s="26" t="n">
+        <v>9</v>
+      </c>
+      <c r="S31" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T31" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U31" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V31" s="24" t="n"/>
+      <c r="W31" s="26" t="n"/>
+      <c r="X31" s="26" t="n"/>
+      <c r="Y31" s="25" t="n"/>
+      <c r="Z31" s="26" t="n"/>
+      <c r="AA31" s="28" t="n"/>
+      <c r="AB31" s="28" t="n"/>
+      <c r="AC31" s="30" t="n"/>
+      <c r="AD31" s="24" t="n"/>
+      <c r="AE31" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-lol-bro-krx-2026-08-04).</t>
+        </is>
+      </c>
+      <c r="AF31" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG31" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH31" s="24" t="n"/>
+      <c r="AI31" s="31" t="n"/>
+      <c r="AJ31" s="31" t="n"/>
+      <c r="AK31" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL31" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM31" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN31" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO31" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP31" s="24" t="inlineStr">
+        <is>
+          <t>Kiwoom DRX</t>
+        </is>
+      </c>
+      <c r="AQ31" s="24" t="inlineStr">
+        <is>
+          <t>Kiwoom DRX</t>
+        </is>
+      </c>
+      <c r="AR31" s="24" t="inlineStr">
+        <is>
+          <t>Kiwoom DRX</t>
+        </is>
+      </c>
+      <c r="AS31" s="24" t="inlineStr">
+        <is>
+          <t>HANJIN BRION</t>
+        </is>
+      </c>
+      <c r="AT31" s="24" t="inlineStr">
+        <is>
+          <t>HANJIN BRION</t>
+        </is>
+      </c>
+      <c r="AU31" s="24" t="inlineStr">
+        <is>
+          <t>HANJIN BRION</t>
+        </is>
+      </c>
+      <c r="AV31" s="24" t="n"/>
+      <c r="AW31" s="24" t="n"/>
+      <c r="AX31" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY31" s="24" t="n"/>
+      <c r="AZ31" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA31" s="24" t="inlineStr">
+        <is>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+        </is>
+      </c>
+      <c r="BB31" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC31" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD31" s="24" t="inlineStr">
+        <is>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+        </is>
+      </c>
+      <c r="BE31" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF31" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG31" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH31" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:42.207831Z</t>
+        </is>
+      </c>
+      <c r="BI31" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ31" s="25" t="n"/>
+      <c r="BK31" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="BL31" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="BM31" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BN31" s="28" t="n"/>
+      <c r="BO31" s="28" t="n"/>
+      <c r="BP31" s="25" t="n"/>
+      <c r="BQ31" s="27" t="n"/>
+      <c r="BR31" s="28" t="n"/>
+      <c r="BS31" s="28" t="n"/>
+      <c r="BT31" s="28" t="n"/>
+      <c r="BU31" s="25" t="n"/>
+      <c r="BV31" s="29" t="n"/>
+      <c r="BW31" s="24" t="n"/>
+      <c r="BX31" s="30" t="n"/>
+      <c r="BY31" s="27" t="n"/>
+      <c r="BZ31" s="24" t="n"/>
+      <c r="CA31" s="31" t="n"/>
+      <c r="CB31" s="24" t="n"/>
+      <c r="CC31" s="24" t="n"/>
+      <c r="CD31" s="24" t="n"/>
+      <c r="CE31" s="24" t="n"/>
+      <c r="CF31" s="24" t="n"/>
+      <c r="CG31" s="24" t="n"/>
+      <c r="CH31" s="24" t="n"/>
+      <c r="CI31" s="24" t="n"/>
+      <c r="CJ31" s="24" t="n"/>
+      <c r="CK31" s="24" t="n"/>
+      <c r="CL31" s="24" t="n"/>
+      <c r="CM31" s="24" t="n"/>
+      <c r="CN31" s="24" t="n"/>
+      <c r="CO31" s="24" t="n"/>
+      <c r="CP31" s="24" t="n"/>
+      <c r="CQ31" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>966d0ee860cf46b4</t>
+        </is>
+      </c>
+      <c r="B32" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:56.302645Z</t>
+        </is>
+      </c>
+      <c r="C32" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D32" s="24" t="inlineStr">
+        <is>
+          <t>70566</t>
+        </is>
+      </c>
+      <c r="E32" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F32" s="24" t="inlineStr">
+        <is>
+          <t>Barcząca Esports</t>
+        </is>
+      </c>
+      <c r="G32" s="24" t="inlineStr">
+        <is>
+          <t>Lodis</t>
+        </is>
+      </c>
+      <c r="H32" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I32" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J32" s="25" t="n"/>
+      <c r="K32" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L32" s="26" t="n">
+        <v>223</v>
+      </c>
+      <c r="M32" s="27" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="N32" s="28" t="n">
+        <v>0.309598</v>
+      </c>
+      <c r="O32" s="28" t="n">
+        <v>0.69409</v>
+      </c>
+      <c r="P32" s="28" t="n"/>
+      <c r="Q32" s="28" t="n">
+        <v>0.384492</v>
+      </c>
+      <c r="R32" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S32" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T32" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U32" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V32" s="24" t="n"/>
+      <c r="W32" s="26" t="n"/>
+      <c r="X32" s="26" t="n"/>
+      <c r="Y32" s="25" t="n"/>
+      <c r="Z32" s="26" t="n"/>
+      <c r="AA32" s="28" t="n"/>
+      <c r="AB32" s="28" t="n"/>
+      <c r="AC32" s="30" t="n"/>
+      <c r="AD32" s="24" t="n"/>
+      <c r="AE32" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3100 (market_slug=aec-lol-lds-bce-2026-08-04).</t>
+        </is>
+      </c>
+      <c r="AF32" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG32" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH32" s="24" t="n"/>
+      <c r="AI32" s="31" t="n"/>
+      <c r="AJ32" s="31" t="n"/>
+      <c r="AK32" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL32" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM32" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN32" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO32" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP32" s="24" t="inlineStr">
+        <is>
+          <t>Barcząca Esports</t>
+        </is>
+      </c>
+      <c r="AQ32" s="24" t="inlineStr">
+        <is>
+          <t>Barcząca Esports</t>
+        </is>
+      </c>
+      <c r="AR32" s="24" t="inlineStr">
+        <is>
+          <t>Barcząca Esports</t>
+        </is>
+      </c>
+      <c r="AS32" s="24" t="inlineStr">
+        <is>
+          <t>Lodis</t>
+        </is>
+      </c>
+      <c r="AT32" s="24" t="inlineStr">
+        <is>
+          <t>Lodis</t>
+        </is>
+      </c>
+      <c r="AU32" s="24" t="inlineStr">
+        <is>
+          <t>Lodis</t>
+        </is>
+      </c>
+      <c r="AV32" s="24" t="n"/>
+      <c r="AW32" s="24" t="n"/>
+      <c r="AX32" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY32" s="24" t="n"/>
+      <c r="AZ32" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA32" s="24" t="inlineStr">
+        <is>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+        </is>
+      </c>
+      <c r="BB32" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC32" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD32" s="24" t="inlineStr">
+        <is>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+        </is>
+      </c>
+      <c r="BE32" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF32" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG32" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH32" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:43.286617Z</t>
+        </is>
+      </c>
+      <c r="BI32" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ32" s="25" t="n"/>
+      <c r="BK32" s="26" t="n">
+        <v>223</v>
+      </c>
+      <c r="BL32" s="27" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="BM32" s="28" t="n">
+        <v>0.309598</v>
+      </c>
+      <c r="BN32" s="28" t="n"/>
+      <c r="BO32" s="28" t="n"/>
+      <c r="BP32" s="25" t="n"/>
+      <c r="BQ32" s="27" t="n"/>
+      <c r="BR32" s="28" t="n"/>
+      <c r="BS32" s="28" t="n"/>
+      <c r="BT32" s="28" t="n"/>
+      <c r="BU32" s="25" t="n"/>
+      <c r="BV32" s="29" t="n"/>
+      <c r="BW32" s="24" t="n"/>
+      <c r="BX32" s="30" t="n"/>
+      <c r="BY32" s="27" t="n"/>
+      <c r="BZ32" s="24" t="n"/>
+      <c r="CA32" s="31" t="n"/>
+      <c r="CB32" s="24" t="n"/>
+      <c r="CC32" s="24" t="n"/>
+      <c r="CD32" s="24" t="n"/>
+      <c r="CE32" s="24" t="n"/>
+      <c r="CF32" s="24" t="n"/>
+      <c r="CG32" s="24" t="n"/>
+      <c r="CH32" s="24" t="n"/>
+      <c r="CI32" s="24" t="n"/>
+      <c r="CJ32" s="24" t="n"/>
+      <c r="CK32" s="24" t="n"/>
+      <c r="CL32" s="24" t="n"/>
+      <c r="CM32" s="24" t="n"/>
+      <c r="CN32" s="24" t="n"/>
+      <c r="CO32" s="24" t="n"/>
+      <c r="CP32" s="24" t="n"/>
+      <c r="CQ32" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>87e0f926f2124592</t>
+        </is>
+      </c>
+      <c r="B33" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:56.302645Z</t>
+        </is>
+      </c>
+      <c r="C33" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="D33" s="24" t="inlineStr">
+        <is>
+          <t>68509</t>
+        </is>
+      </c>
+      <c r="E33" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F33" s="24" t="inlineStr">
+        <is>
+          <t>Skillcamp Esport</t>
+        </is>
+      </c>
+      <c r="G33" s="24" t="inlineStr">
+        <is>
+          <t>Ici Japon Corp. Esport</t>
+        </is>
+      </c>
+      <c r="H33" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I33" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J33" s="25" t="n"/>
+      <c r="K33" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L33" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="M33" s="27" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="N33" s="28" t="n">
+        <v>0.509804</v>
+      </c>
+      <c r="O33" s="28" t="n">
+        <v>0.631317</v>
+      </c>
+      <c r="P33" s="28" t="n"/>
+      <c r="Q33" s="28" t="n">
+        <v>0.121513</v>
+      </c>
+      <c r="R33" s="26" t="n">
+        <v>81</v>
+      </c>
+      <c r="S33" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T33" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U33" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V33" s="24" t="n"/>
+      <c r="W33" s="26" t="n"/>
+      <c r="X33" s="26" t="n"/>
+      <c r="Y33" s="25" t="n"/>
+      <c r="Z33" s="26" t="n"/>
+      <c r="AA33" s="28" t="n"/>
+      <c r="AB33" s="28" t="n"/>
+      <c r="AC33" s="30" t="n"/>
+      <c r="AD33" s="24" t="n"/>
+      <c r="AE33" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-lol-ijc-sc-2026-08-04).</t>
+        </is>
+      </c>
+      <c r="AF33" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG33" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH33" s="24" t="n"/>
+      <c r="AI33" s="31" t="n"/>
+      <c r="AJ33" s="31" t="n"/>
+      <c r="AK33" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL33" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM33" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN33" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO33" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP33" s="24" t="inlineStr">
+        <is>
+          <t>Skillcamp Esport</t>
+        </is>
+      </c>
+      <c r="AQ33" s="24" t="inlineStr">
+        <is>
+          <t>Skillcamp Esport</t>
+        </is>
+      </c>
+      <c r="AR33" s="24" t="inlineStr">
+        <is>
+          <t>Skillcamp Esport</t>
+        </is>
+      </c>
+      <c r="AS33" s="24" t="inlineStr">
+        <is>
+          <t>Ici Japon Corp. Esport</t>
+        </is>
+      </c>
+      <c r="AT33" s="24" t="inlineStr">
+        <is>
+          <t>Ici Japon Corp. Esport</t>
+        </is>
+      </c>
+      <c r="AU33" s="24" t="inlineStr">
+        <is>
+          <t>Ici Japon Corp. Esport</t>
+        </is>
+      </c>
+      <c r="AV33" s="24" t="n"/>
+      <c r="AW33" s="24" t="n"/>
+      <c r="AX33" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY33" s="24" t="n"/>
+      <c r="AZ33" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA33" s="24" t="inlineStr">
+        <is>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+        </is>
+      </c>
+      <c r="BB33" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC33" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD33" s="24" t="inlineStr">
+        <is>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+        </is>
+      </c>
+      <c r="BE33" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF33" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG33" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH33" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:44.932625Z</t>
+        </is>
+      </c>
+      <c r="BI33" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ33" s="25" t="n"/>
+      <c r="BK33" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="BL33" s="27" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="BM33" s="28" t="n">
+        <v>0.509804</v>
+      </c>
+      <c r="BN33" s="28" t="n"/>
+      <c r="BO33" s="28" t="n"/>
+      <c r="BP33" s="25" t="n"/>
+      <c r="BQ33" s="27" t="n"/>
+      <c r="BR33" s="28" t="n"/>
+      <c r="BS33" s="28" t="n"/>
+      <c r="BT33" s="28" t="n"/>
+      <c r="BU33" s="25" t="n"/>
+      <c r="BV33" s="29" t="n"/>
+      <c r="BW33" s="24" t="n"/>
+      <c r="BX33" s="30" t="n"/>
+      <c r="BY33" s="27" t="n"/>
+      <c r="BZ33" s="24" t="n"/>
+      <c r="CA33" s="31" t="n"/>
+      <c r="CB33" s="24" t="n"/>
+      <c r="CC33" s="24" t="n"/>
+      <c r="CD33" s="24" t="n"/>
+      <c r="CE33" s="24" t="n"/>
+      <c r="CF33" s="24" t="n"/>
+      <c r="CG33" s="24" t="n"/>
+      <c r="CH33" s="24" t="n"/>
+      <c r="CI33" s="24" t="n"/>
+      <c r="CJ33" s="24" t="n"/>
+      <c r="CK33" s="24" t="n"/>
+      <c r="CL33" s="24" t="n"/>
+      <c r="CM33" s="24" t="n"/>
+      <c r="CN33" s="24" t="n"/>
+      <c r="CO33" s="24" t="n"/>
+      <c r="CP33" s="24" t="n"/>
+      <c r="CQ33" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>6bdcf6660f9a4dde</t>
+        </is>
+      </c>
+      <c r="B34" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:56.302645Z</t>
+        </is>
+      </c>
+      <c r="C34" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="D34" s="24" t="inlineStr">
+        <is>
+          <t>68585</t>
+        </is>
+      </c>
+      <c r="E34" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F34" s="24" t="inlineStr">
+        <is>
+          <t>The Bandits</t>
+        </is>
+      </c>
+      <c r="G34" s="24" t="inlineStr">
+        <is>
+          <t>mCon esports</t>
+        </is>
+      </c>
+      <c r="H34" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I34" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J34" s="25" t="n"/>
+      <c r="K34" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L34" s="26" t="n">
+        <v>212</v>
+      </c>
+      <c r="M34" s="27" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="N34" s="28" t="n">
+        <v>0.320513</v>
+      </c>
+      <c r="O34" s="28" t="n">
+        <v>0.509157</v>
+      </c>
+      <c r="P34" s="28" t="n"/>
+      <c r="Q34" s="28" t="n">
+        <v>0.188644</v>
+      </c>
+      <c r="R34" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S34" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T34" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U34" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V34" s="24" t="n"/>
+      <c r="W34" s="26" t="n"/>
+      <c r="X34" s="26" t="n"/>
+      <c r="Y34" s="25" t="n"/>
+      <c r="Z34" s="26" t="n"/>
+      <c r="AA34" s="28" t="n"/>
+      <c r="AB34" s="28" t="n"/>
+      <c r="AC34" s="30" t="n"/>
+      <c r="AD34" s="24" t="n"/>
+      <c r="AE34" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3200 (market_slug=aec-lol-mcn-ban-2026-08-04).</t>
+        </is>
+      </c>
+      <c r="AF34" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG34" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH34" s="24" t="n"/>
+      <c r="AI34" s="31" t="n"/>
+      <c r="AJ34" s="31" t="n"/>
+      <c r="AK34" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL34" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM34" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN34" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO34" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP34" s="24" t="inlineStr">
+        <is>
+          <t>The Bandits</t>
+        </is>
+      </c>
+      <c r="AQ34" s="24" t="inlineStr">
+        <is>
+          <t>The Bandits</t>
+        </is>
+      </c>
+      <c r="AR34" s="24" t="inlineStr">
+        <is>
+          <t>The Bandits</t>
+        </is>
+      </c>
+      <c r="AS34" s="24" t="inlineStr">
+        <is>
+          <t>mCon esports</t>
+        </is>
+      </c>
+      <c r="AT34" s="24" t="inlineStr">
+        <is>
+          <t>mCon esports</t>
+        </is>
+      </c>
+      <c r="AU34" s="24" t="inlineStr">
+        <is>
+          <t>mCon esports</t>
+        </is>
+      </c>
+      <c r="AV34" s="24" t="n"/>
+      <c r="AW34" s="24" t="n"/>
+      <c r="AX34" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY34" s="24" t="n"/>
+      <c r="AZ34" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA34" s="24" t="inlineStr">
+        <is>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+        </is>
+      </c>
+      <c r="BB34" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC34" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD34" s="24" t="inlineStr">
+        <is>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+        </is>
+      </c>
+      <c r="BE34" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF34" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG34" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH34" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:46.530291Z</t>
+        </is>
+      </c>
+      <c r="BI34" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ34" s="25" t="n"/>
+      <c r="BK34" s="26" t="n">
+        <v>212</v>
+      </c>
+      <c r="BL34" s="27" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="BM34" s="28" t="n">
+        <v>0.320513</v>
+      </c>
+      <c r="BN34" s="28" t="n"/>
+      <c r="BO34" s="28" t="n"/>
+      <c r="BP34" s="25" t="n"/>
+      <c r="BQ34" s="27" t="n"/>
+      <c r="BR34" s="28" t="n"/>
+      <c r="BS34" s="28" t="n"/>
+      <c r="BT34" s="28" t="n"/>
+      <c r="BU34" s="25" t="n"/>
+      <c r="BV34" s="29" t="n"/>
+      <c r="BW34" s="24" t="n"/>
+      <c r="BX34" s="30" t="n"/>
+      <c r="BY34" s="27" t="n"/>
+      <c r="BZ34" s="24" t="n"/>
+      <c r="CA34" s="31" t="n"/>
+      <c r="CB34" s="24" t="n"/>
+      <c r="CC34" s="24" t="n"/>
+      <c r="CD34" s="24" t="n"/>
+      <c r="CE34" s="24" t="n"/>
+      <c r="CF34" s="24" t="n"/>
+      <c r="CG34" s="24" t="n"/>
+      <c r="CH34" s="24" t="n"/>
+      <c r="CI34" s="24" t="n"/>
+      <c r="CJ34" s="24" t="n"/>
+      <c r="CK34" s="24" t="n"/>
+      <c r="CL34" s="24" t="n"/>
+      <c r="CM34" s="24" t="n"/>
+      <c r="CN34" s="24" t="n"/>
+      <c r="CO34" s="24" t="n"/>
+      <c r="CP34" s="24" t="n"/>
+      <c r="CQ34" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="36" customHeight="1">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>c9c778eee56441ba</t>
+        </is>
+      </c>
+      <c r="B35" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:56.302645Z</t>
+        </is>
+      </c>
+      <c r="C35" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="D35" s="24" t="inlineStr">
+        <is>
+          <t>70567</t>
+        </is>
+      </c>
+      <c r="E35" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F35" s="24" t="inlineStr">
+        <is>
+          <t>Anonymo Esports</t>
+        </is>
+      </c>
+      <c r="G35" s="24" t="inlineStr">
+        <is>
+          <t>DOCISK</t>
+        </is>
+      </c>
+      <c r="H35" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I35" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J35" s="25" t="n"/>
+      <c r="K35" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L35" s="26" t="n">
+        <v>163</v>
+      </c>
+      <c r="M35" s="27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="N35" s="28" t="n">
+        <v>0.380228</v>
+      </c>
+      <c r="O35" s="28" t="n">
+        <v>0.518338</v>
+      </c>
+      <c r="P35" s="28" t="n"/>
+      <c r="Q35" s="28" t="n">
+        <v>0.13811</v>
+      </c>
+      <c r="R35" s="26" t="n">
+        <v>89</v>
+      </c>
+      <c r="S35" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T35" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U35" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V35" s="24" t="n"/>
+      <c r="W35" s="26" t="n"/>
+      <c r="X35" s="26" t="n"/>
+      <c r="Y35" s="25" t="n"/>
+      <c r="Z35" s="26" t="n"/>
+      <c r="AA35" s="28" t="n"/>
+      <c r="AB35" s="28" t="n"/>
+      <c r="AC35" s="30" t="n"/>
+      <c r="AD35" s="24" t="n"/>
+      <c r="AE35" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3800 (market_slug=aec-lol-doc-ae-2026-08-04).</t>
+        </is>
+      </c>
+      <c r="AF35" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG35" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH35" s="24" t="n"/>
+      <c r="AI35" s="31" t="n"/>
+      <c r="AJ35" s="31" t="n"/>
+      <c r="AK35" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL35" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM35" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN35" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO35" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP35" s="24" t="inlineStr">
+        <is>
+          <t>Anonymo Esports</t>
+        </is>
+      </c>
+      <c r="AQ35" s="24" t="inlineStr">
+        <is>
+          <t>Anonymo Esports</t>
+        </is>
+      </c>
+      <c r="AR35" s="24" t="inlineStr">
+        <is>
+          <t>Anonymo Esports</t>
+        </is>
+      </c>
+      <c r="AS35" s="24" t="inlineStr">
+        <is>
+          <t>DOCISK</t>
+        </is>
+      </c>
+      <c r="AT35" s="24" t="inlineStr">
+        <is>
+          <t>DOCISK</t>
+        </is>
+      </c>
+      <c r="AU35" s="24" t="inlineStr">
+        <is>
+          <t>DOCISK</t>
+        </is>
+      </c>
+      <c r="AV35" s="24" t="n"/>
+      <c r="AW35" s="24" t="n"/>
+      <c r="AX35" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY35" s="24" t="n"/>
+      <c r="AZ35" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA35" s="24" t="inlineStr">
+        <is>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+        </is>
+      </c>
+      <c r="BB35" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC35" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD35" s="24" t="inlineStr">
+        <is>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+        </is>
+      </c>
+      <c r="BE35" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF35" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG35" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH35" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:47.025076Z</t>
+        </is>
+      </c>
+      <c r="BI35" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ35" s="25" t="n"/>
+      <c r="BK35" s="26" t="n">
+        <v>163</v>
+      </c>
+      <c r="BL35" s="27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BM35" s="28" t="n">
+        <v>0.380228</v>
+      </c>
+      <c r="BN35" s="28" t="n"/>
+      <c r="BO35" s="28" t="n"/>
+      <c r="BP35" s="25" t="n"/>
+      <c r="BQ35" s="27" t="n"/>
+      <c r="BR35" s="28" t="n"/>
+      <c r="BS35" s="28" t="n"/>
+      <c r="BT35" s="28" t="n"/>
+      <c r="BU35" s="25" t="n"/>
+      <c r="BV35" s="29" t="n"/>
+      <c r="BW35" s="24" t="n"/>
+      <c r="BX35" s="30" t="n"/>
+      <c r="BY35" s="27" t="n"/>
+      <c r="BZ35" s="24" t="n"/>
+      <c r="CA35" s="31" t="n"/>
+      <c r="CB35" s="24" t="n"/>
+      <c r="CC35" s="24" t="n"/>
+      <c r="CD35" s="24" t="n"/>
+      <c r="CE35" s="24" t="n"/>
+      <c r="CF35" s="24" t="n"/>
+      <c r="CG35" s="24" t="n"/>
+      <c r="CH35" s="24" t="n"/>
+      <c r="CI35" s="24" t="n"/>
+      <c r="CJ35" s="24" t="n"/>
+      <c r="CK35" s="24" t="n"/>
+      <c r="CL35" s="24" t="n"/>
+      <c r="CM35" s="24" t="n"/>
+      <c r="CN35" s="24" t="n"/>
+      <c r="CO35" s="24" t="n"/>
+      <c r="CP35" s="24" t="n"/>
+      <c r="CQ35" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="36" customHeight="1">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>800cb61d26c84c57</t>
+        </is>
+      </c>
+      <c r="B36" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:56.302645Z</t>
+        </is>
+      </c>
+      <c r="C36" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D36" s="24" t="inlineStr">
+        <is>
+          <t>68691</t>
+        </is>
+      </c>
+      <c r="E36" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F36" s="24" t="inlineStr">
+        <is>
+          <t>ZennIT</t>
+        </is>
+      </c>
+      <c r="G36" s="24" t="inlineStr">
+        <is>
+          <t>Once Upon A Team</t>
+        </is>
+      </c>
+      <c r="H36" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I36" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J36" s="25" t="n"/>
+      <c r="K36" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L36" s="26" t="n">
+        <v>-203</v>
+      </c>
+      <c r="M36" s="27" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="N36" s="28" t="n">
+        <v>0.669967</v>
+      </c>
+      <c r="O36" s="28" t="n">
+        <v>0.549366</v>
+      </c>
+      <c r="P36" s="28" t="n"/>
+      <c r="Q36" s="28" t="n">
+        <v>-0.120601</v>
+      </c>
+      <c r="R36" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T36" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U36" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V36" s="24" t="n"/>
+      <c r="W36" s="26" t="n"/>
+      <c r="X36" s="26" t="n"/>
+      <c r="Y36" s="25" t="n"/>
+      <c r="Z36" s="26" t="n"/>
+      <c r="AA36" s="28" t="n"/>
+      <c r="AB36" s="28" t="n"/>
+      <c r="AC36" s="30" t="n"/>
+      <c r="AD36" s="24" t="n"/>
+      <c r="AE36" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-lol-ouat-znt-2026-08-04).</t>
+        </is>
+      </c>
+      <c r="AF36" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG36" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH36" s="24" t="n"/>
+      <c r="AI36" s="31" t="n"/>
+      <c r="AJ36" s="31" t="n"/>
+      <c r="AK36" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL36" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM36" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN36" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO36" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP36" s="24" t="inlineStr">
+        <is>
+          <t>ZennIT</t>
+        </is>
+      </c>
+      <c r="AQ36" s="24" t="inlineStr">
+        <is>
+          <t>ZennIT</t>
+        </is>
+      </c>
+      <c r="AR36" s="24" t="inlineStr">
+        <is>
+          <t>ZennIT</t>
+        </is>
+      </c>
+      <c r="AS36" s="24" t="inlineStr">
+        <is>
+          <t>Once Upon A Team</t>
+        </is>
+      </c>
+      <c r="AT36" s="24" t="inlineStr">
+        <is>
+          <t>Once Upon A Team</t>
+        </is>
+      </c>
+      <c r="AU36" s="24" t="inlineStr">
+        <is>
+          <t>Once Upon A Team</t>
+        </is>
+      </c>
+      <c r="AV36" s="24" t="n"/>
+      <c r="AW36" s="24" t="n"/>
+      <c r="AX36" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY36" s="24" t="n"/>
+      <c r="AZ36" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA36" s="24" t="inlineStr">
+        <is>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+        </is>
+      </c>
+      <c r="BB36" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC36" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD36" s="24" t="inlineStr">
+        <is>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+        </is>
+      </c>
+      <c r="BE36" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF36" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG36" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH36" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:48.018849Z</t>
+        </is>
+      </c>
+      <c r="BI36" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ36" s="25" t="n"/>
+      <c r="BK36" s="26" t="n">
+        <v>-203</v>
+      </c>
+      <c r="BL36" s="27" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="BM36" s="28" t="n">
+        <v>0.669967</v>
+      </c>
+      <c r="BN36" s="28" t="n"/>
+      <c r="BO36" s="28" t="n"/>
+      <c r="BP36" s="25" t="n"/>
+      <c r="BQ36" s="27" t="n"/>
+      <c r="BR36" s="28" t="n"/>
+      <c r="BS36" s="28" t="n"/>
+      <c r="BT36" s="28" t="n"/>
+      <c r="BU36" s="25" t="n"/>
+      <c r="BV36" s="29" t="n"/>
+      <c r="BW36" s="24" t="n"/>
+      <c r="BX36" s="30" t="n"/>
+      <c r="BY36" s="27" t="n"/>
+      <c r="BZ36" s="24" t="n"/>
+      <c r="CA36" s="31" t="n"/>
+      <c r="CB36" s="24" t="n"/>
+      <c r="CC36" s="24" t="n"/>
+      <c r="CD36" s="24" t="n"/>
+      <c r="CE36" s="24" t="n"/>
+      <c r="CF36" s="24" t="n"/>
+      <c r="CG36" s="24" t="n"/>
+      <c r="CH36" s="24" t="n"/>
+      <c r="CI36" s="24" t="n"/>
+      <c r="CJ36" s="24" t="n"/>
+      <c r="CK36" s="24" t="n"/>
+      <c r="CL36" s="24" t="n"/>
+      <c r="CM36" s="24" t="n"/>
+      <c r="CN36" s="24" t="n"/>
+      <c r="CO36" s="24" t="n"/>
+      <c r="CP36" s="24" t="n"/>
+      <c r="CQ36" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="36" customHeight="1">
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t>9dfd7a89789f4d73</t>
+        </is>
+      </c>
+      <c r="B37" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:56.302645Z</t>
+        </is>
+      </c>
+      <c r="C37" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D37" s="24" t="inlineStr">
+        <is>
+          <t>68689</t>
+        </is>
+      </c>
+      <c r="E37" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F37" s="24" t="inlineStr">
+        <is>
+          <t>Way Gaming Esports</t>
+        </is>
+      </c>
+      <c r="G37" s="24" t="inlineStr">
+        <is>
+          <t>Capybara Esports</t>
+        </is>
+      </c>
+      <c r="H37" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I37" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J37" s="25" t="n"/>
+      <c r="K37" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L37" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="M37" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="N37" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="O37" s="28" t="n">
+        <v>0.5739340000000001</v>
+      </c>
+      <c r="P37" s="28" t="n"/>
+      <c r="Q37" s="28" t="n">
+        <v>0.003119</v>
+      </c>
+      <c r="R37" s="26" t="n">
+        <v>22</v>
+      </c>
+      <c r="S37" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T37" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U37" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V37" s="24" t="n"/>
+      <c r="W37" s="26" t="n"/>
+      <c r="X37" s="26" t="n"/>
+      <c r="Y37" s="25" t="n"/>
+      <c r="Z37" s="26" t="n"/>
+      <c r="AA37" s="28" t="n"/>
+      <c r="AB37" s="28" t="n"/>
+      <c r="AC37" s="30" t="n"/>
+      <c r="AD37" s="24" t="n"/>
+      <c r="AE37" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-lol-capy-wge-2026-08-04).</t>
+        </is>
+      </c>
+      <c r="AF37" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG37" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH37" s="24" t="n"/>
+      <c r="AI37" s="31" t="n"/>
+      <c r="AJ37" s="31" t="n"/>
+      <c r="AK37" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL37" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM37" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN37" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO37" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP37" s="24" t="inlineStr">
+        <is>
+          <t>Way Gaming Esports</t>
+        </is>
+      </c>
+      <c r="AQ37" s="24" t="inlineStr">
+        <is>
+          <t>Way Gaming Esports</t>
+        </is>
+      </c>
+      <c r="AR37" s="24" t="inlineStr">
+        <is>
+          <t>Way Gaming Esports</t>
+        </is>
+      </c>
+      <c r="AS37" s="24" t="inlineStr">
+        <is>
+          <t>Capybara Esports</t>
+        </is>
+      </c>
+      <c r="AT37" s="24" t="inlineStr">
+        <is>
+          <t>Capybara Esports</t>
+        </is>
+      </c>
+      <c r="AU37" s="24" t="inlineStr">
+        <is>
+          <t>Capybara Esports</t>
+        </is>
+      </c>
+      <c r="AV37" s="24" t="n"/>
+      <c r="AW37" s="24" t="n"/>
+      <c r="AX37" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY37" s="24" t="n"/>
+      <c r="AZ37" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA37" s="24" t="inlineStr">
+        <is>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+        </is>
+      </c>
+      <c r="BB37" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC37" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD37" s="24" t="inlineStr">
+        <is>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+        </is>
+      </c>
+      <c r="BE37" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF37" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG37" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH37" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:48.567590Z</t>
+        </is>
+      </c>
+      <c r="BI37" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ37" s="25" t="n"/>
+      <c r="BK37" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="BL37" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="BM37" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="BN37" s="28" t="n"/>
+      <c r="BO37" s="28" t="n"/>
+      <c r="BP37" s="25" t="n"/>
+      <c r="BQ37" s="27" t="n"/>
+      <c r="BR37" s="28" t="n"/>
+      <c r="BS37" s="28" t="n"/>
+      <c r="BT37" s="28" t="n"/>
+      <c r="BU37" s="25" t="n"/>
+      <c r="BV37" s="29" t="n"/>
+      <c r="BW37" s="24" t="n"/>
+      <c r="BX37" s="30" t="n"/>
+      <c r="BY37" s="27" t="n"/>
+      <c r="BZ37" s="24" t="n"/>
+      <c r="CA37" s="31" t="n"/>
+      <c r="CB37" s="24" t="n"/>
+      <c r="CC37" s="24" t="n"/>
+      <c r="CD37" s="24" t="n"/>
+      <c r="CE37" s="24" t="n"/>
+      <c r="CF37" s="24" t="n"/>
+      <c r="CG37" s="24" t="n"/>
+      <c r="CH37" s="24" t="n"/>
+      <c r="CI37" s="24" t="n"/>
+      <c r="CJ37" s="24" t="n"/>
+      <c r="CK37" s="24" t="n"/>
+      <c r="CL37" s="24" t="n"/>
+      <c r="CM37" s="24" t="n"/>
+      <c r="CN37" s="24" t="n"/>
+      <c r="CO37" s="24" t="n"/>
+      <c r="CP37" s="24" t="n"/>
+      <c r="CQ37" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="36" customHeight="1">
+      <c r="A38" s="24" t="inlineStr">
+        <is>
+          <t>e048b6e77c6f407e</t>
+        </is>
+      </c>
+      <c r="B38" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:56.302645Z</t>
+        </is>
+      </c>
+      <c r="C38" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D38" s="24" t="inlineStr">
+        <is>
+          <t>68688</t>
+        </is>
+      </c>
+      <c r="E38" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F38" s="24" t="inlineStr">
+        <is>
+          <t>Joblife</t>
+        </is>
+      </c>
+      <c r="G38" s="24" t="inlineStr">
+        <is>
+          <t>ZYB Esport</t>
+        </is>
+      </c>
+      <c r="H38" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I38" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J38" s="25" t="n"/>
+      <c r="K38" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L38" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="M38" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="N38" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="O38" s="28" t="n">
+        <v>0.531003</v>
+      </c>
+      <c r="P38" s="28" t="n"/>
+      <c r="Q38" s="28" t="n">
+        <v>-0.018547</v>
+      </c>
+      <c r="R38" s="26" t="n">
+        <v>11</v>
+      </c>
+      <c r="S38" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T38" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U38" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V38" s="24" t="n"/>
+      <c r="W38" s="26" t="n"/>
+      <c r="X38" s="26" t="n"/>
+      <c r="Y38" s="25" t="n"/>
+      <c r="Z38" s="26" t="n"/>
+      <c r="AA38" s="28" t="n"/>
+      <c r="AB38" s="28" t="n"/>
+      <c r="AC38" s="30" t="n"/>
+      <c r="AD38" s="24" t="n"/>
+      <c r="AE38" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-lol-zyb-jl-2026-08-04).</t>
+        </is>
+      </c>
+      <c r="AF38" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG38" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH38" s="24" t="n"/>
+      <c r="AI38" s="31" t="n"/>
+      <c r="AJ38" s="31" t="n"/>
+      <c r="AK38" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL38" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM38" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN38" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO38" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP38" s="24" t="inlineStr">
+        <is>
+          <t>Joblife</t>
+        </is>
+      </c>
+      <c r="AQ38" s="24" t="inlineStr">
+        <is>
+          <t>Joblife</t>
+        </is>
+      </c>
+      <c r="AR38" s="24" t="inlineStr">
+        <is>
+          <t>Joblife</t>
+        </is>
+      </c>
+      <c r="AS38" s="24" t="inlineStr">
+        <is>
+          <t>ZYB Esport</t>
+        </is>
+      </c>
+      <c r="AT38" s="24" t="inlineStr">
+        <is>
+          <t>ZYB Esport</t>
+        </is>
+      </c>
+      <c r="AU38" s="24" t="inlineStr">
+        <is>
+          <t>ZYB Esport</t>
+        </is>
+      </c>
+      <c r="AV38" s="24" t="n"/>
+      <c r="AW38" s="24" t="n"/>
+      <c r="AX38" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY38" s="24" t="n"/>
+      <c r="AZ38" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA38" s="24" t="inlineStr">
+        <is>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+        </is>
+      </c>
+      <c r="BB38" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC38" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD38" s="24" t="inlineStr">
+        <is>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+        </is>
+      </c>
+      <c r="BE38" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF38" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG38" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH38" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:49.048776Z</t>
+        </is>
+      </c>
+      <c r="BI38" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ38" s="25" t="n"/>
+      <c r="BK38" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="BL38" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="BM38" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="BN38" s="28" t="n"/>
+      <c r="BO38" s="28" t="n"/>
+      <c r="BP38" s="25" t="n"/>
+      <c r="BQ38" s="27" t="n"/>
+      <c r="BR38" s="28" t="n"/>
+      <c r="BS38" s="28" t="n"/>
+      <c r="BT38" s="28" t="n"/>
+      <c r="BU38" s="25" t="n"/>
+      <c r="BV38" s="29" t="n"/>
+      <c r="BW38" s="24" t="n"/>
+      <c r="BX38" s="30" t="n"/>
+      <c r="BY38" s="27" t="n"/>
+      <c r="BZ38" s="24" t="n"/>
+      <c r="CA38" s="31" t="n"/>
+      <c r="CB38" s="24" t="n"/>
+      <c r="CC38" s="24" t="n"/>
+      <c r="CD38" s="24" t="n"/>
+      <c r="CE38" s="24" t="n"/>
+      <c r="CF38" s="24" t="n"/>
+      <c r="CG38" s="24" t="n"/>
+      <c r="CH38" s="24" t="n"/>
+      <c r="CI38" s="24" t="n"/>
+      <c r="CJ38" s="24" t="n"/>
+      <c r="CK38" s="24" t="n"/>
+      <c r="CL38" s="24" t="n"/>
+      <c r="CM38" s="24" t="n"/>
+      <c r="CN38" s="24" t="n"/>
+      <c r="CO38" s="24" t="n"/>
+      <c r="CP38" s="24" t="n"/>
+      <c r="CQ38" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="36" customHeight="1">
+      <c r="A39" s="24" t="inlineStr">
+        <is>
+          <t>cfb2d9fb5c744b21</t>
+        </is>
+      </c>
+      <c r="B39" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:56.302645Z</t>
+        </is>
+      </c>
+      <c r="C39" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D39" s="24" t="inlineStr">
+        <is>
+          <t>68690</t>
+        </is>
+      </c>
+      <c r="E39" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F39" s="24" t="inlineStr">
+        <is>
+          <t>Lupus Esports</t>
+        </is>
+      </c>
+      <c r="G39" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Croatian Flair x RLX </t>
+        </is>
+      </c>
+      <c r="H39" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I39" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J39" s="25" t="n"/>
+      <c r="K39" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L39" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="M39" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="N39" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="O39" s="28" t="n">
+        <v>0.55055</v>
+      </c>
+      <c r="P39" s="28" t="n"/>
+      <c r="Q39" s="28" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="R39" s="26" t="n">
+        <v>21</v>
+      </c>
+      <c r="S39" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T39" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U39" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V39" s="24" t="n"/>
+      <c r="W39" s="26" t="n"/>
+      <c r="X39" s="26" t="n"/>
+      <c r="Y39" s="25" t="n"/>
+      <c r="Z39" s="26" t="n"/>
+      <c r="AA39" s="28" t="n"/>
+      <c r="AB39" s="28" t="n"/>
+      <c r="AC39" s="30" t="n"/>
+      <c r="AD39" s="24" t="n"/>
+      <c r="AE39" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-lol-cfxr-lps-2026-08-04).</t>
+        </is>
+      </c>
+      <c r="AF39" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG39" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH39" s="24" t="n"/>
+      <c r="AI39" s="31" t="n"/>
+      <c r="AJ39" s="31" t="n"/>
+      <c r="AK39" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL39" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM39" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN39" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO39" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP39" s="24" t="inlineStr">
+        <is>
+          <t>Lupus Esports</t>
+        </is>
+      </c>
+      <c r="AQ39" s="24" t="inlineStr">
+        <is>
+          <t>Lupus Esports</t>
+        </is>
+      </c>
+      <c r="AR39" s="24" t="inlineStr">
+        <is>
+          <t>Lupus Esports</t>
+        </is>
+      </c>
+      <c r="AS39" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Croatian Flair x RLX </t>
+        </is>
+      </c>
+      <c r="AT39" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Croatian Flair x RLX </t>
+        </is>
+      </c>
+      <c r="AU39" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Croatian Flair x RLX </t>
+        </is>
+      </c>
+      <c r="AV39" s="24" t="n"/>
+      <c r="AW39" s="24" t="n"/>
+      <c r="AX39" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY39" s="24" t="n"/>
+      <c r="AZ39" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA39" s="24" t="inlineStr">
+        <is>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+        </is>
+      </c>
+      <c r="BB39" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC39" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD39" s="24" t="inlineStr">
+        <is>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+        </is>
+      </c>
+      <c r="BE39" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF39" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG39" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH39" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:49.613554Z</t>
+        </is>
+      </c>
+      <c r="BI39" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ39" s="25" t="n"/>
+      <c r="BK39" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="BL39" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="BM39" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="BN39" s="28" t="n"/>
+      <c r="BO39" s="28" t="n"/>
+      <c r="BP39" s="25" t="n"/>
+      <c r="BQ39" s="27" t="n"/>
+      <c r="BR39" s="28" t="n"/>
+      <c r="BS39" s="28" t="n"/>
+      <c r="BT39" s="28" t="n"/>
+      <c r="BU39" s="25" t="n"/>
+      <c r="BV39" s="29" t="n"/>
+      <c r="BW39" s="24" t="n"/>
+      <c r="BX39" s="30" t="n"/>
+      <c r="BY39" s="27" t="n"/>
+      <c r="BZ39" s="24" t="n"/>
+      <c r="CA39" s="31" t="n"/>
+      <c r="CB39" s="24" t="n"/>
+      <c r="CC39" s="24" t="n"/>
+      <c r="CD39" s="24" t="n"/>
+      <c r="CE39" s="24" t="n"/>
+      <c r="CF39" s="24" t="n"/>
+      <c r="CG39" s="24" t="n"/>
+      <c r="CH39" s="24" t="n"/>
+      <c r="CI39" s="24" t="n"/>
+      <c r="CJ39" s="24" t="n"/>
+      <c r="CK39" s="24" t="n"/>
+      <c r="CL39" s="24" t="n"/>
+      <c r="CM39" s="24" t="n"/>
+      <c r="CN39" s="24" t="n"/>
+      <c r="CO39" s="24" t="n"/>
+      <c r="CP39" s="24" t="n"/>
+      <c r="CQ39" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="36" customHeight="1">
+      <c r="A40" s="24" t="inlineStr">
+        <is>
+          <t>2c772ea2540843f1</t>
+        </is>
+      </c>
+      <c r="B40" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:56.302645Z</t>
+        </is>
+      </c>
+      <c r="C40" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="D40" s="24" t="inlineStr">
+        <is>
+          <t>69143</t>
+        </is>
+      </c>
+      <c r="E40" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F40" s="24" t="inlineStr">
+        <is>
+          <t>Malvinas Gaming</t>
+        </is>
+      </c>
+      <c r="G40" s="24" t="inlineStr">
+        <is>
+          <t>Maze Gaming</t>
+        </is>
+      </c>
+      <c r="H40" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I40" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J40" s="25" t="n"/>
+      <c r="K40" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L40" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="M40" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="N40" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="O40" s="28" t="n">
+        <v>0.624143</v>
+      </c>
+      <c r="P40" s="28" t="n"/>
+      <c r="Q40" s="28" t="n">
+        <v>0.004371</v>
+      </c>
+      <c r="R40" s="26" t="n">
+        <v>22</v>
+      </c>
+      <c r="S40" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T40" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U40" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V40" s="24" t="n"/>
+      <c r="W40" s="26" t="n"/>
+      <c r="X40" s="26" t="n"/>
+      <c r="Y40" s="25" t="n"/>
+      <c r="Z40" s="26" t="n"/>
+      <c r="AA40" s="28" t="n"/>
+      <c r="AB40" s="28" t="n"/>
+      <c r="AC40" s="30" t="n"/>
+      <c r="AD40" s="24" t="n"/>
+      <c r="AE40" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-lol-maz-mg-2026-08-04).</t>
+        </is>
+      </c>
+      <c r="AF40" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG40" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH40" s="24" t="n"/>
+      <c r="AI40" s="31" t="n"/>
+      <c r="AJ40" s="31" t="n"/>
+      <c r="AK40" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL40" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM40" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN40" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO40" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP40" s="24" t="inlineStr">
+        <is>
+          <t>Malvinas Gaming</t>
+        </is>
+      </c>
+      <c r="AQ40" s="24" t="inlineStr">
+        <is>
+          <t>Malvinas Gaming</t>
+        </is>
+      </c>
+      <c r="AR40" s="24" t="inlineStr">
+        <is>
+          <t>Malvinas Gaming</t>
+        </is>
+      </c>
+      <c r="AS40" s="24" t="inlineStr">
+        <is>
+          <t>Maze Gaming</t>
+        </is>
+      </c>
+      <c r="AT40" s="24" t="inlineStr">
+        <is>
+          <t>Maze Gaming</t>
+        </is>
+      </c>
+      <c r="AU40" s="24" t="inlineStr">
+        <is>
+          <t>Maze Gaming</t>
+        </is>
+      </c>
+      <c r="AV40" s="24" t="n"/>
+      <c r="AW40" s="24" t="n"/>
+      <c r="AX40" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY40" s="24" t="n"/>
+      <c r="AZ40" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA40" s="24" t="inlineStr">
+        <is>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+        </is>
+      </c>
+      <c r="BB40" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC40" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD40" s="24" t="inlineStr">
+        <is>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+        </is>
+      </c>
+      <c r="BE40" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF40" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG40" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH40" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:52.417381Z</t>
+        </is>
+      </c>
+      <c r="BI40" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ40" s="25" t="n"/>
+      <c r="BK40" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="BL40" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="BM40" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="BN40" s="28" t="n"/>
+      <c r="BO40" s="28" t="n"/>
+      <c r="BP40" s="25" t="n"/>
+      <c r="BQ40" s="27" t="n"/>
+      <c r="BR40" s="28" t="n"/>
+      <c r="BS40" s="28" t="n"/>
+      <c r="BT40" s="28" t="n"/>
+      <c r="BU40" s="25" t="n"/>
+      <c r="BV40" s="29" t="n"/>
+      <c r="BW40" s="24" t="n"/>
+      <c r="BX40" s="30" t="n"/>
+      <c r="BY40" s="27" t="n"/>
+      <c r="BZ40" s="24" t="n"/>
+      <c r="CA40" s="31" t="n"/>
+      <c r="CB40" s="24" t="n"/>
+      <c r="CC40" s="24" t="n"/>
+      <c r="CD40" s="24" t="n"/>
+      <c r="CE40" s="24" t="n"/>
+      <c r="CF40" s="24" t="n"/>
+      <c r="CG40" s="24" t="n"/>
+      <c r="CH40" s="24" t="n"/>
+      <c r="CI40" s="24" t="n"/>
+      <c r="CJ40" s="24" t="n"/>
+      <c r="CK40" s="24" t="n"/>
+      <c r="CL40" s="24" t="n"/>
+      <c r="CM40" s="24" t="n"/>
+      <c r="CN40" s="24" t="n"/>
+      <c r="CO40" s="24" t="n"/>
+      <c r="CP40" s="24" t="n"/>
+      <c r="CQ40" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="36" customHeight="1">
+      <c r="A41" s="24" t="inlineStr">
+        <is>
+          <t>442ac140fc9b4803</t>
+        </is>
+      </c>
+      <c r="B41" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:56.302645Z</t>
+        </is>
+      </c>
+      <c r="C41" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="D41" s="24" t="inlineStr">
+        <is>
+          <t>69144</t>
+        </is>
+      </c>
+      <c r="E41" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F41" s="24" t="inlineStr">
+        <is>
+          <t>INTZ e-Sports</t>
+        </is>
+      </c>
+      <c r="G41" s="24" t="inlineStr">
+        <is>
+          <t>Vivo Keyd Stars Academy</t>
+        </is>
+      </c>
+      <c r="H41" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I41" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J41" s="25" t="n"/>
+      <c r="K41" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L41" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="M41" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="N41" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="O41" s="28" t="n">
+        <v>0.591618</v>
+      </c>
+      <c r="P41" s="28" t="n"/>
+      <c r="Q41" s="28" t="n">
+        <v>0.032147</v>
+      </c>
+      <c r="R41" s="26" t="n">
+        <v>36</v>
+      </c>
+      <c r="S41" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T41" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U41" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V41" s="24" t="n"/>
+      <c r="W41" s="26" t="n"/>
+      <c r="X41" s="26" t="n"/>
+      <c r="Y41" s="25" t="n"/>
+      <c r="Z41" s="26" t="n"/>
+      <c r="AA41" s="28" t="n"/>
+      <c r="AB41" s="28" t="n"/>
+      <c r="AC41" s="30" t="n"/>
+      <c r="AD41" s="24" t="n"/>
+      <c r="AE41" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-lol-vksa-itz-2026-08-04).</t>
+        </is>
+      </c>
+      <c r="AF41" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG41" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH41" s="24" t="n"/>
+      <c r="AI41" s="31" t="n"/>
+      <c r="AJ41" s="31" t="n"/>
+      <c r="AK41" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL41" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM41" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN41" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO41" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP41" s="24" t="inlineStr">
+        <is>
+          <t>INTZ e-Sports</t>
+        </is>
+      </c>
+      <c r="AQ41" s="24" t="inlineStr">
+        <is>
+          <t>INTZ e-Sports</t>
+        </is>
+      </c>
+      <c r="AR41" s="24" t="inlineStr">
+        <is>
+          <t>INTZ e-Sports</t>
+        </is>
+      </c>
+      <c r="AS41" s="24" t="inlineStr">
+        <is>
+          <t>Vivo Keyd Stars Academy</t>
+        </is>
+      </c>
+      <c r="AT41" s="24" t="inlineStr">
+        <is>
+          <t>Vivo Keyd Stars Academy</t>
+        </is>
+      </c>
+      <c r="AU41" s="24" t="inlineStr">
+        <is>
+          <t>Vivo Keyd Stars Academy</t>
+        </is>
+      </c>
+      <c r="AV41" s="24" t="n"/>
+      <c r="AW41" s="24" t="n"/>
+      <c r="AX41" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY41" s="24" t="n"/>
+      <c r="AZ41" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA41" s="24" t="inlineStr">
+        <is>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+        </is>
+      </c>
+      <c r="BB41" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC41" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD41" s="24" t="inlineStr">
+        <is>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+        </is>
+      </c>
+      <c r="BE41" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF41" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG41" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH41" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:53.026230Z</t>
+        </is>
+      </c>
+      <c r="BI41" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ41" s="25" t="n"/>
+      <c r="BK41" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="BL41" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BM41" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="BN41" s="28" t="n"/>
+      <c r="BO41" s="28" t="n"/>
+      <c r="BP41" s="25" t="n"/>
+      <c r="BQ41" s="27" t="n"/>
+      <c r="BR41" s="28" t="n"/>
+      <c r="BS41" s="28" t="n"/>
+      <c r="BT41" s="28" t="n"/>
+      <c r="BU41" s="25" t="n"/>
+      <c r="BV41" s="29" t="n"/>
+      <c r="BW41" s="24" t="n"/>
+      <c r="BX41" s="30" t="n"/>
+      <c r="BY41" s="27" t="n"/>
+      <c r="BZ41" s="24" t="n"/>
+      <c r="CA41" s="31" t="n"/>
+      <c r="CB41" s="24" t="n"/>
+      <c r="CC41" s="24" t="n"/>
+      <c r="CD41" s="24" t="n"/>
+      <c r="CE41" s="24" t="n"/>
+      <c r="CF41" s="24" t="n"/>
+      <c r="CG41" s="24" t="n"/>
+      <c r="CH41" s="24" t="n"/>
+      <c r="CI41" s="24" t="n"/>
+      <c r="CJ41" s="24" t="n"/>
+      <c r="CK41" s="24" t="n"/>
+      <c r="CL41" s="24" t="n"/>
+      <c r="CM41" s="24" t="n"/>
+      <c r="CN41" s="24" t="n"/>
+      <c r="CO41" s="24" t="n"/>
+      <c r="CP41" s="24" t="n"/>
+      <c r="CQ41" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="36" customHeight="1">
+      <c r="A42" s="24" t="inlineStr">
+        <is>
+          <t>c041d27567494ec6</t>
+        </is>
+      </c>
+      <c r="B42" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:56.302645Z</t>
+        </is>
+      </c>
+      <c r="C42" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="D42" s="24" t="inlineStr">
+        <is>
+          <t>69141</t>
+        </is>
+      </c>
+      <c r="E42" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F42" s="24" t="inlineStr">
+        <is>
+          <t>Vitality.Bee</t>
+        </is>
+      </c>
+      <c r="G42" s="24" t="inlineStr">
+        <is>
+          <t>Karmine Corp Blue</t>
+        </is>
+      </c>
+      <c r="H42" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I42" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J42" s="25" t="n"/>
+      <c r="K42" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L42" s="26" t="n">
+        <v>-186</v>
+      </c>
+      <c r="M42" s="27" t="n">
+        <v>1.537634</v>
+      </c>
+      <c r="N42" s="28" t="n">
+        <v>0.65035</v>
+      </c>
+      <c r="O42" s="28" t="n">
+        <v>0.649994</v>
+      </c>
+      <c r="P42" s="28" t="n"/>
+      <c r="Q42" s="28" t="n">
+        <v>-0.000356</v>
+      </c>
+      <c r="R42" s="26" t="n">
+        <v>20</v>
+      </c>
+      <c r="S42" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T42" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U42" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V42" s="24" t="n"/>
+      <c r="W42" s="26" t="n"/>
+      <c r="X42" s="26" t="n"/>
+      <c r="Y42" s="25" t="n"/>
+      <c r="Z42" s="26" t="n"/>
+      <c r="AA42" s="28" t="n"/>
+      <c r="AB42" s="28" t="n"/>
+      <c r="AC42" s="30" t="n"/>
+      <c r="AD42" s="24" t="n"/>
+      <c r="AE42" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6500 (market_slug=aec-lol-kcb-vitb-2026-08-04).</t>
+        </is>
+      </c>
+      <c r="AF42" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG42" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH42" s="24" t="n"/>
+      <c r="AI42" s="31" t="n"/>
+      <c r="AJ42" s="31" t="n"/>
+      <c r="AK42" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL42" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM42" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN42" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO42" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP42" s="24" t="inlineStr">
+        <is>
+          <t>Vitality.Bee</t>
+        </is>
+      </c>
+      <c r="AQ42" s="24" t="inlineStr">
+        <is>
+          <t>Vitality.Bee</t>
+        </is>
+      </c>
+      <c r="AR42" s="24" t="inlineStr">
+        <is>
+          <t>Vitality.Bee</t>
+        </is>
+      </c>
+      <c r="AS42" s="24" t="inlineStr">
+        <is>
+          <t>Karmine Corp Blue</t>
+        </is>
+      </c>
+      <c r="AT42" s="24" t="inlineStr">
+        <is>
+          <t>Karmine Corp Blue</t>
+        </is>
+      </c>
+      <c r="AU42" s="24" t="inlineStr">
+        <is>
+          <t>Karmine Corp Blue</t>
+        </is>
+      </c>
+      <c r="AV42" s="24" t="n"/>
+      <c r="AW42" s="24" t="n"/>
+      <c r="AX42" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY42" s="24" t="n"/>
+      <c r="AZ42" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA42" s="24" t="inlineStr">
+        <is>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+        </is>
+      </c>
+      <c r="BB42" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC42" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD42" s="24" t="inlineStr">
+        <is>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+        </is>
+      </c>
+      <c r="BE42" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF42" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG42" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH42" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:53.530335Z</t>
+        </is>
+      </c>
+      <c r="BI42" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ42" s="25" t="n"/>
+      <c r="BK42" s="26" t="n">
+        <v>-186</v>
+      </c>
+      <c r="BL42" s="27" t="n">
+        <v>1.537634</v>
+      </c>
+      <c r="BM42" s="28" t="n">
+        <v>0.65035</v>
+      </c>
+      <c r="BN42" s="28" t="n"/>
+      <c r="BO42" s="28" t="n"/>
+      <c r="BP42" s="25" t="n"/>
+      <c r="BQ42" s="27" t="n"/>
+      <c r="BR42" s="28" t="n"/>
+      <c r="BS42" s="28" t="n"/>
+      <c r="BT42" s="28" t="n"/>
+      <c r="BU42" s="25" t="n"/>
+      <c r="BV42" s="29" t="n"/>
+      <c r="BW42" s="24" t="n"/>
+      <c r="BX42" s="30" t="n"/>
+      <c r="BY42" s="27" t="n"/>
+      <c r="BZ42" s="24" t="n"/>
+      <c r="CA42" s="31" t="n"/>
+      <c r="CB42" s="24" t="n"/>
+      <c r="CC42" s="24" t="n"/>
+      <c r="CD42" s="24" t="n"/>
+      <c r="CE42" s="24" t="n"/>
+      <c r="CF42" s="24" t="n"/>
+      <c r="CG42" s="24" t="n"/>
+      <c r="CH42" s="24" t="n"/>
+      <c r="CI42" s="24" t="n"/>
+      <c r="CJ42" s="24" t="n"/>
+      <c r="CK42" s="24" t="n"/>
+      <c r="CL42" s="24" t="n"/>
+      <c r="CM42" s="24" t="n"/>
+      <c r="CN42" s="24" t="n"/>
+      <c r="CO42" s="24" t="n"/>
+      <c r="CP42" s="24" t="n"/>
+      <c r="CQ42" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="36" customHeight="1">
+      <c r="A43" s="24" t="inlineStr">
+        <is>
+          <t>f6954aaa8b72488e</t>
+        </is>
+      </c>
+      <c r="B43" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:56.302645Z</t>
+        </is>
+      </c>
+      <c r="C43" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="D43" s="24" t="inlineStr">
+        <is>
+          <t>69234</t>
+        </is>
+      </c>
+      <c r="E43" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F43" s="24" t="inlineStr">
+        <is>
+          <t>Bubliki</t>
+        </is>
+      </c>
+      <c r="G43" s="24" t="inlineStr">
+        <is>
+          <t>Francesinhas</t>
+        </is>
+      </c>
+      <c r="H43" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I43" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J43" s="25" t="n"/>
+      <c r="K43" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L43" s="26" t="n">
+        <v>156</v>
+      </c>
+      <c r="M43" s="27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="N43" s="28" t="n">
+        <v>0.390625</v>
+      </c>
+      <c r="O43" s="28" t="n">
+        <v>0.51668</v>
+      </c>
+      <c r="P43" s="28" t="n"/>
+      <c r="Q43" s="28" t="n">
+        <v>0.126055</v>
+      </c>
+      <c r="R43" s="26" t="n">
+        <v>83</v>
+      </c>
+      <c r="S43" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T43" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U43" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V43" s="24" t="n"/>
+      <c r="W43" s="26" t="n"/>
+      <c r="X43" s="26" t="n"/>
+      <c r="Y43" s="25" t="n"/>
+      <c r="Z43" s="26" t="n"/>
+      <c r="AA43" s="28" t="n"/>
+      <c r="AB43" s="28" t="n"/>
+      <c r="AC43" s="30" t="n"/>
+      <c r="AD43" s="24" t="n"/>
+      <c r="AE43" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3900 (market_slug=aec-lol-fcn-bub-2026-08-04).</t>
+        </is>
+      </c>
+      <c r="AF43" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG43" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH43" s="24" t="n"/>
+      <c r="AI43" s="31" t="n"/>
+      <c r="AJ43" s="31" t="n"/>
+      <c r="AK43" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL43" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM43" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN43" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO43" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP43" s="24" t="inlineStr">
+        <is>
+          <t>Bubliki</t>
+        </is>
+      </c>
+      <c r="AQ43" s="24" t="inlineStr">
+        <is>
+          <t>Bubliki</t>
+        </is>
+      </c>
+      <c r="AR43" s="24" t="inlineStr">
+        <is>
+          <t>Bubliki</t>
+        </is>
+      </c>
+      <c r="AS43" s="24" t="inlineStr">
+        <is>
+          <t>Francesinhas</t>
+        </is>
+      </c>
+      <c r="AT43" s="24" t="inlineStr">
+        <is>
+          <t>Francesinhas</t>
+        </is>
+      </c>
+      <c r="AU43" s="24" t="inlineStr">
+        <is>
+          <t>Francesinhas</t>
+        </is>
+      </c>
+      <c r="AV43" s="24" t="n"/>
+      <c r="AW43" s="24" t="n"/>
+      <c r="AX43" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY43" s="24" t="n"/>
+      <c r="AZ43" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA43" s="24" t="inlineStr">
+        <is>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+        </is>
+      </c>
+      <c r="BB43" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC43" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD43" s="24" t="inlineStr">
+        <is>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+        </is>
+      </c>
+      <c r="BE43" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF43" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG43" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH43" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:54.079734Z</t>
+        </is>
+      </c>
+      <c r="BI43" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ43" s="25" t="n"/>
+      <c r="BK43" s="26" t="n">
+        <v>156</v>
+      </c>
+      <c r="BL43" s="27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BM43" s="28" t="n">
+        <v>0.390625</v>
+      </c>
+      <c r="BN43" s="28" t="n"/>
+      <c r="BO43" s="28" t="n"/>
+      <c r="BP43" s="25" t="n"/>
+      <c r="BQ43" s="27" t="n"/>
+      <c r="BR43" s="28" t="n"/>
+      <c r="BS43" s="28" t="n"/>
+      <c r="BT43" s="28" t="n"/>
+      <c r="BU43" s="25" t="n"/>
+      <c r="BV43" s="29" t="n"/>
+      <c r="BW43" s="24" t="n"/>
+      <c r="BX43" s="30" t="n"/>
+      <c r="BY43" s="27" t="n"/>
+      <c r="BZ43" s="24" t="n"/>
+      <c r="CA43" s="31" t="n"/>
+      <c r="CB43" s="24" t="n"/>
+      <c r="CC43" s="24" t="n"/>
+      <c r="CD43" s="24" t="n"/>
+      <c r="CE43" s="24" t="n"/>
+      <c r="CF43" s="24" t="n"/>
+      <c r="CG43" s="24" t="n"/>
+      <c r="CH43" s="24" t="n"/>
+      <c r="CI43" s="24" t="n"/>
+      <c r="CJ43" s="24" t="n"/>
+      <c r="CK43" s="24" t="n"/>
+      <c r="CL43" s="24" t="n"/>
+      <c r="CM43" s="24" t="n"/>
+      <c r="CN43" s="24" t="n"/>
+      <c r="CO43" s="24" t="n"/>
+      <c r="CP43" s="24" t="n"/>
+      <c r="CQ43" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="36" customHeight="1">
+      <c r="A44" s="24" t="inlineStr">
+        <is>
+          <t>408f74d7de044559</t>
+        </is>
+      </c>
+      <c r="B44" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:56.302645Z</t>
+        </is>
+      </c>
+      <c r="C44" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="D44" s="24" t="inlineStr">
+        <is>
+          <t>69273</t>
+        </is>
+      </c>
+      <c r="E44" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F44" s="24" t="inlineStr">
+        <is>
+          <t>RMD Gaming</t>
+        </is>
+      </c>
+      <c r="G44" s="24" t="inlineStr">
+        <is>
+          <t>7REX</t>
+        </is>
+      </c>
+      <c r="H44" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I44" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J44" s="25" t="n"/>
+      <c r="K44" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L44" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="M44" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="N44" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O44" s="28" t="n">
+        <v>0.604656</v>
+      </c>
+      <c r="P44" s="28" t="n"/>
+      <c r="Q44" s="28" t="n">
+        <v>0.004656</v>
+      </c>
+      <c r="R44" s="26" t="n">
+        <v>22</v>
+      </c>
+      <c r="S44" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T44" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U44" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V44" s="24" t="n"/>
+      <c r="W44" s="26" t="n"/>
+      <c r="X44" s="26" t="n"/>
+      <c r="Y44" s="25" t="n"/>
+      <c r="Z44" s="26" t="n"/>
+      <c r="AA44" s="28" t="n"/>
+      <c r="AB44" s="28" t="n"/>
+      <c r="AC44" s="30" t="n"/>
+      <c r="AD44" s="24" t="n"/>
+      <c r="AE44" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-lol-7rex-rmd-2026-08-04).</t>
+        </is>
+      </c>
+      <c r="AF44" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG44" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH44" s="24" t="n"/>
+      <c r="AI44" s="31" t="n"/>
+      <c r="AJ44" s="31" t="n"/>
+      <c r="AK44" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL44" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM44" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN44" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO44" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP44" s="24" t="inlineStr">
+        <is>
+          <t>RMD Gaming</t>
+        </is>
+      </c>
+      <c r="AQ44" s="24" t="inlineStr">
+        <is>
+          <t>RMD Gaming</t>
+        </is>
+      </c>
+      <c r="AR44" s="24" t="inlineStr">
+        <is>
+          <t>RMD Gaming</t>
+        </is>
+      </c>
+      <c r="AS44" s="24" t="inlineStr">
+        <is>
+          <t>7REX</t>
+        </is>
+      </c>
+      <c r="AT44" s="24" t="inlineStr">
+        <is>
+          <t>7REX</t>
+        </is>
+      </c>
+      <c r="AU44" s="24" t="inlineStr">
+        <is>
+          <t>7REX</t>
+        </is>
+      </c>
+      <c r="AV44" s="24" t="n"/>
+      <c r="AW44" s="24" t="n"/>
+      <c r="AX44" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY44" s="24" t="n"/>
+      <c r="AZ44" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA44" s="24" t="inlineStr">
+        <is>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+        </is>
+      </c>
+      <c r="BB44" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC44" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD44" s="24" t="inlineStr">
+        <is>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+        </is>
+      </c>
+      <c r="BE44" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF44" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG44" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH44" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:55.187744Z</t>
+        </is>
+      </c>
+      <c r="BI44" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ44" s="25" t="n"/>
+      <c r="BK44" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="BL44" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="BM44" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BN44" s="28" t="n"/>
+      <c r="BO44" s="28" t="n"/>
+      <c r="BP44" s="25" t="n"/>
+      <c r="BQ44" s="27" t="n"/>
+      <c r="BR44" s="28" t="n"/>
+      <c r="BS44" s="28" t="n"/>
+      <c r="BT44" s="28" t="n"/>
+      <c r="BU44" s="25" t="n"/>
+      <c r="BV44" s="29" t="n"/>
+      <c r="BW44" s="24" t="n"/>
+      <c r="BX44" s="30" t="n"/>
+      <c r="BY44" s="27" t="n"/>
+      <c r="BZ44" s="24" t="n"/>
+      <c r="CA44" s="31" t="n"/>
+      <c r="CB44" s="24" t="n"/>
+      <c r="CC44" s="24" t="n"/>
+      <c r="CD44" s="24" t="n"/>
+      <c r="CE44" s="24" t="n"/>
+      <c r="CF44" s="24" t="n"/>
+      <c r="CG44" s="24" t="n"/>
+      <c r="CH44" s="24" t="n"/>
+      <c r="CI44" s="24" t="n"/>
+      <c r="CJ44" s="24" t="n"/>
+      <c r="CK44" s="24" t="n"/>
+      <c r="CL44" s="24" t="n"/>
+      <c r="CM44" s="24" t="n"/>
+      <c r="CN44" s="24" t="n"/>
+      <c r="CO44" s="24" t="n"/>
+      <c r="CP44" s="24" t="n"/>
+      <c r="CQ44" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="36" customHeight="1">
+      <c r="A45" s="24" t="inlineStr">
+        <is>
+          <t>e34cd34cab424131</t>
+        </is>
+      </c>
+      <c r="B45" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:56.302645Z</t>
+        </is>
+      </c>
+      <c r="C45" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T23:00:00Z</t>
+        </is>
+      </c>
+      <c r="D45" s="24" t="inlineStr">
+        <is>
+          <t>69304</t>
+        </is>
+      </c>
+      <c r="E45" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F45" s="24" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="G45" s="24" t="inlineStr">
+        <is>
+          <t>KaBuM! Ilha das Lendas</t>
+        </is>
+      </c>
+      <c r="H45" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I45" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J45" s="25" t="n"/>
+      <c r="K45" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L45" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="M45" s="27" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="N45" s="28" t="n">
+        <v>0.509804</v>
+      </c>
+      <c r="O45" s="28" t="n">
+        <v>0.546359</v>
+      </c>
+      <c r="P45" s="28" t="n"/>
+      <c r="Q45" s="28" t="n">
+        <v>0.036555</v>
+      </c>
+      <c r="R45" s="26" t="n">
+        <v>38</v>
+      </c>
+      <c r="S45" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T45" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U45" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V45" s="24" t="n"/>
+      <c r="W45" s="26" t="n"/>
+      <c r="X45" s="26" t="n"/>
+      <c r="Y45" s="25" t="n"/>
+      <c r="Z45" s="26" t="n"/>
+      <c r="AA45" s="28" t="n"/>
+      <c r="AB45" s="28" t="n"/>
+      <c r="AC45" s="30" t="n"/>
+      <c r="AD45" s="24" t="n"/>
+      <c r="AE45" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-lol-kbm-pnga-2026-08-04).</t>
+        </is>
+      </c>
+      <c r="AF45" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG45" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH45" s="24" t="n"/>
+      <c r="AI45" s="31" t="n"/>
+      <c r="AJ45" s="31" t="n"/>
+      <c r="AK45" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL45" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM45" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN45" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO45" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP45" s="24" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="AQ45" s="24" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="AR45" s="24" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="AS45" s="24" t="inlineStr">
+        <is>
+          <t>KaBuM! Ilha das Lendas</t>
+        </is>
+      </c>
+      <c r="AT45" s="24" t="inlineStr">
+        <is>
+          <t>KaBuM! Ilha das Lendas</t>
+        </is>
+      </c>
+      <c r="AU45" s="24" t="inlineStr">
+        <is>
+          <t>KaBuM! Ilha das Lendas</t>
+        </is>
+      </c>
+      <c r="AV45" s="24" t="n"/>
+      <c r="AW45" s="24" t="n"/>
+      <c r="AX45" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY45" s="24" t="n"/>
+      <c r="AZ45" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA45" s="24" t="inlineStr">
+        <is>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+        </is>
+      </c>
+      <c r="BB45" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC45" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD45" s="24" t="inlineStr">
+        <is>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+        </is>
+      </c>
+      <c r="BE45" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF45" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG45" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH45" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:55.701889Z</t>
+        </is>
+      </c>
+      <c r="BI45" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ45" s="25" t="n"/>
+      <c r="BK45" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="BL45" s="27" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="BM45" s="28" t="n">
+        <v>0.509804</v>
+      </c>
+      <c r="BN45" s="28" t="n"/>
+      <c r="BO45" s="28" t="n"/>
+      <c r="BP45" s="25" t="n"/>
+      <c r="BQ45" s="27" t="n"/>
+      <c r="BR45" s="28" t="n"/>
+      <c r="BS45" s="28" t="n"/>
+      <c r="BT45" s="28" t="n"/>
+      <c r="BU45" s="25" t="n"/>
+      <c r="BV45" s="29" t="n"/>
+      <c r="BW45" s="24" t="n"/>
+      <c r="BX45" s="30" t="n"/>
+      <c r="BY45" s="27" t="n"/>
+      <c r="BZ45" s="24" t="n"/>
+      <c r="CA45" s="31" t="n"/>
+      <c r="CB45" s="24" t="n"/>
+      <c r="CC45" s="24" t="n"/>
+      <c r="CD45" s="24" t="n"/>
+      <c r="CE45" s="24" t="n"/>
+      <c r="CF45" s="24" t="n"/>
+      <c r="CG45" s="24" t="n"/>
+      <c r="CH45" s="24" t="n"/>
+      <c r="CI45" s="24" t="n"/>
+      <c r="CJ45" s="24" t="n"/>
+      <c r="CK45" s="24" t="n"/>
+      <c r="CL45" s="24" t="n"/>
+      <c r="CM45" s="24" t="n"/>
+      <c r="CN45" s="24" t="n"/>
+      <c r="CO45" s="24" t="n"/>
+      <c r="CP45" s="24" t="n"/>
+      <c r="CQ45" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="36" customHeight="1">
+      <c r="A46" s="24" t="inlineStr">
+        <is>
+          <t>bbe7069cec06486f</t>
+        </is>
+      </c>
+      <c r="B46" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:56.302645Z</t>
+        </is>
+      </c>
+      <c r="C46" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D46" s="24" t="inlineStr">
+        <is>
+          <t>69336</t>
+        </is>
+      </c>
+      <c r="E46" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F46" s="24" t="inlineStr">
+        <is>
+          <t>Ei Nerd Esports</t>
+        </is>
+      </c>
+      <c r="G46" s="24" t="inlineStr">
+        <is>
+          <t>Estral Esports</t>
+        </is>
+      </c>
+      <c r="H46" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I46" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J46" s="25" t="n"/>
+      <c r="K46" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L46" s="26" t="n">
+        <v>-203</v>
+      </c>
+      <c r="M46" s="27" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="N46" s="28" t="n">
+        <v>0.669967</v>
+      </c>
+      <c r="O46" s="28" t="n">
+        <v>0.74222</v>
+      </c>
+      <c r="P46" s="28" t="n"/>
+      <c r="Q46" s="28" t="n">
+        <v>0.072253</v>
+      </c>
+      <c r="R46" s="26" t="n">
+        <v>56</v>
+      </c>
+      <c r="S46" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T46" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U46" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V46" s="24" t="n"/>
+      <c r="W46" s="26" t="n"/>
+      <c r="X46" s="26" t="n"/>
+      <c r="Y46" s="25" t="n"/>
+      <c r="Z46" s="26" t="n"/>
+      <c r="AA46" s="28" t="n"/>
+      <c r="AB46" s="28" t="n"/>
+      <c r="AC46" s="30" t="n"/>
+      <c r="AD46" s="24" t="n"/>
+      <c r="AE46" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-lol-est-nerd-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF46" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG46" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH46" s="24" t="n"/>
+      <c r="AI46" s="31" t="n"/>
+      <c r="AJ46" s="31" t="n"/>
+      <c r="AK46" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL46" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM46" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN46" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO46" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP46" s="24" t="inlineStr">
+        <is>
+          <t>Ei Nerd Esports</t>
+        </is>
+      </c>
+      <c r="AQ46" s="24" t="inlineStr">
+        <is>
+          <t>Ei Nerd Esports</t>
+        </is>
+      </c>
+      <c r="AR46" s="24" t="inlineStr">
+        <is>
+          <t>Ei Nerd Esports</t>
+        </is>
+      </c>
+      <c r="AS46" s="24" t="inlineStr">
+        <is>
+          <t>Estral Esports</t>
+        </is>
+      </c>
+      <c r="AT46" s="24" t="inlineStr">
+        <is>
+          <t>Estral Esports</t>
+        </is>
+      </c>
+      <c r="AU46" s="24" t="inlineStr">
+        <is>
+          <t>Estral Esports</t>
+        </is>
+      </c>
+      <c r="AV46" s="24" t="n"/>
+      <c r="AW46" s="24" t="n"/>
+      <c r="AX46" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY46" s="24" t="n"/>
+      <c r="AZ46" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA46" s="24" t="inlineStr">
+        <is>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+        </is>
+      </c>
+      <c r="BB46" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC46" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD46" s="24" t="inlineStr">
+        <is>
+          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+        </is>
+      </c>
+      <c r="BE46" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF46" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG46" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH46" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:56.301588Z</t>
+        </is>
+      </c>
+      <c r="BI46" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ46" s="25" t="n"/>
+      <c r="BK46" s="26" t="n">
+        <v>-203</v>
+      </c>
+      <c r="BL46" s="27" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="BM46" s="28" t="n">
+        <v>0.669967</v>
+      </c>
+      <c r="BN46" s="28" t="n"/>
+      <c r="BO46" s="28" t="n"/>
+      <c r="BP46" s="25" t="n"/>
+      <c r="BQ46" s="27" t="n"/>
+      <c r="BR46" s="28" t="n"/>
+      <c r="BS46" s="28" t="n"/>
+      <c r="BT46" s="28" t="n"/>
+      <c r="BU46" s="25" t="n"/>
+      <c r="BV46" s="29" t="n"/>
+      <c r="BW46" s="24" t="n"/>
+      <c r="BX46" s="30" t="n"/>
+      <c r="BY46" s="27" t="n"/>
+      <c r="BZ46" s="24" t="n"/>
+      <c r="CA46" s="31" t="n"/>
+      <c r="CB46" s="24" t="n"/>
+      <c r="CC46" s="24" t="n"/>
+      <c r="CD46" s="24" t="n"/>
+      <c r="CE46" s="24" t="n"/>
+      <c r="CF46" s="24" t="n"/>
+      <c r="CG46" s="24" t="n"/>
+      <c r="CH46" s="24" t="n"/>
+      <c r="CI46" s="24" t="n"/>
+      <c r="CJ46" s="24" t="n"/>
+      <c r="CK46" s="24" t="n"/>
+      <c r="CL46" s="24" t="n"/>
+      <c r="CM46" s="24" t="n"/>
+      <c r="CN46" s="24" t="n"/>
+      <c r="CO46" s="24" t="n"/>
+      <c r="CP46" s="24" t="n"/>
+      <c r="CQ46" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
         </is>
       </c>
     </row>

--- a/data/research/lol.xlsx
+++ b/data/research/lol.xlsx
@@ -300,9 +300,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ46" headerRowCount="1">
-  <autoFilter ref="A1:CQ46"/>
-  <tableColumns count="95">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CR66" headerRowCount="1">
+  <autoFilter ref="A1:CR66"/>
+  <tableColumns count="96">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
     <tableColumn id="3" name="event_start_utc"/>
@@ -392,12 +392,13 @@
     <tableColumn id="87" name="unavailable_features"/>
     <tableColumn id="88" name="defensive_trend_gap"/>
     <tableColumn id="89" name="neutral_elo_rating_difference"/>
-    <tableColumn id="90" name="rest_disparity"/>
-    <tableColumn id="91" name="back_to_back_gap"/>
-    <tableColumn id="92" name="games_last_7_gap"/>
-    <tableColumn id="93" name="schedule_missingness"/>
-    <tableColumn id="94" name="market_residual_probability"/>
-    <tableColumn id="95" name="trade_candidate"/>
+    <tableColumn id="90" name="bullpen_weakness_gap"/>
+    <tableColumn id="91" name="rest_disparity"/>
+    <tableColumn id="92" name="back_to_back_gap"/>
+    <tableColumn id="93" name="games_last_7_gap"/>
+    <tableColumn id="94" name="schedule_missingness"/>
+    <tableColumn id="95" name="market_residual_probability"/>
+    <tableColumn id="96" name="trade_candidate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -754,19 +755,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$46)</f>
+        <f>COUNTA('Picks'!$A$2:$A$66)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$46,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$66,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$46,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$66,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$46,"settled",'Picks'!$V$2:$V$46,"win")+COUNTIFS('Picks'!$U$2:$U$46,"settled",'Picks'!$V$2:$V$46,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$66,"settled",'Picks'!$V$2:$V$66,"win")+COUNTIFS('Picks'!$U$2:$U$66,"settled",'Picks'!$V$2:$V$66,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +795,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$46,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$66,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$46,"&gt;0",'Picks'!$V$2:$V$46,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$46,"&gt;0",'Picks'!$V$2:$V$46,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$66,"&gt;0",'Picks'!$V$2:$V$66,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$66,"&gt;0",'Picks'!$V$2:$V$66,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$46,"&gt;0",'Picks'!$V$2:$V$46,"win")/(COUNTIFS('Picks'!$BX$2:$BX$46,"&gt;0",'Picks'!$V$2:$V$46,"win")+COUNTIFS('Picks'!$BX$2:$BX$46,"&gt;0",'Picks'!$V$2:$V$46,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$66,"&gt;0",'Picks'!$V$2:$V$66,"win")/(COUNTIFS('Picks'!$BX$2:$BX$66,"&gt;0",'Picks'!$V$2:$V$66,"win")+COUNTIFS('Picks'!$BX$2:$BX$66,"&gt;0",'Picks'!$V$2:$V$66,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$46)/SUM('Picks'!$BX$2:$BX$46),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$66)/SUM('Picks'!$BX$2:$BX$66),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +835,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$46)</f>
+        <f>SUM('Picks'!$BY$2:$BY$66)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$46,"&lt;&gt;",'Picks'!$AB$2:$AB$46),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$66,"&lt;&gt;",'Picks'!$AB$2:$AB$66),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$46,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$46,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$66,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$66,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$46,'Picks'!$AM$2:$AM$46,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$66,'Picks'!$AM$2:$AM$66,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +902,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$46,$A14,'Picks'!$U$2:$U$46,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$66,$A14,'Picks'!$U$2:$U$66,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$46,$A14,'Picks'!$U$2:$U$46,"settled",'Picks'!$V$2:$V$46,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$66,$A14,'Picks'!$U$2:$U$66,"settled",'Picks'!$V$2:$V$66,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$46,$A14,'Picks'!$U$2:$U$46,"settled",'Picks'!$V$2:$V$46,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$66,$A14,'Picks'!$U$2:$U$66,"settled",'Picks'!$V$2:$V$66,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +918,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$46,'Picks'!$H$2:$H$46,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$66,'Picks'!$H$2:$H$66,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$46,'Picks'!$H$2:$H$46,$A14,'Picks'!$U$2:$U$46,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$66,'Picks'!$H$2:$H$66,$A14,'Picks'!$U$2:$U$66,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +933,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$46,$A15,'Picks'!$U$2:$U$46,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$66,$A15,'Picks'!$U$2:$U$66,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$46,$A15,'Picks'!$U$2:$U$46,"settled",'Picks'!$V$2:$V$46,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$66,$A15,'Picks'!$U$2:$U$66,"settled",'Picks'!$V$2:$V$66,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$46,$A15,'Picks'!$U$2:$U$46,"settled",'Picks'!$V$2:$V$46,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$66,$A15,'Picks'!$U$2:$U$66,"settled",'Picks'!$V$2:$V$66,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +949,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$46,'Picks'!$H$2:$H$46,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$66,'Picks'!$H$2:$H$66,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$46,'Picks'!$H$2:$H$46,$A15,'Picks'!$U$2:$U$46,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$66,'Picks'!$H$2:$H$66,$A15,'Picks'!$U$2:$U$66,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +964,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$46,$A16,'Picks'!$U$2:$U$46,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$66,$A16,'Picks'!$U$2:$U$66,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$46,$A16,'Picks'!$U$2:$U$46,"settled",'Picks'!$V$2:$V$46,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$66,$A16,'Picks'!$U$2:$U$66,"settled",'Picks'!$V$2:$V$66,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$46,$A16,'Picks'!$U$2:$U$46,"settled",'Picks'!$V$2:$V$46,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$66,$A16,'Picks'!$U$2:$U$66,"settled",'Picks'!$V$2:$V$66,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +980,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$46,'Picks'!$H$2:$H$46,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$66,'Picks'!$H$2:$H$66,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$46,'Picks'!$H$2:$H$46,$A16,'Picks'!$U$2:$U$46,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$66,'Picks'!$H$2:$H$66,$A16,'Picks'!$U$2:$U$66,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ46"/>
+  <dimension ref="A1:CR66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1104,12 +1105,13 @@
     <col width="22" customWidth="1" min="87" max="87"/>
     <col width="21" customWidth="1" min="88" max="88"/>
     <col width="22" customWidth="1" min="89" max="89"/>
-    <col width="16" customWidth="1" min="90" max="90"/>
-    <col width="18" customWidth="1" min="91" max="91"/>
+    <col width="22" customWidth="1" min="90" max="90"/>
+    <col width="16" customWidth="1" min="91" max="91"/>
     <col width="18" customWidth="1" min="92" max="92"/>
-    <col width="22" customWidth="1" min="93" max="93"/>
+    <col width="18" customWidth="1" min="93" max="93"/>
     <col width="22" customWidth="1" min="94" max="94"/>
-    <col width="17" customWidth="1" min="95" max="95"/>
+    <col width="22" customWidth="1" min="95" max="95"/>
+    <col width="17" customWidth="1" min="96" max="96"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1560,30 +1562,35 @@
       </c>
       <c r="CL1" s="23" t="inlineStr">
         <is>
+          <t>bullpen_weakness_gap</t>
+        </is>
+      </c>
+      <c r="CM1" s="23" t="inlineStr">
+        <is>
           <t>rest_disparity</t>
         </is>
       </c>
-      <c r="CM1" s="23" t="inlineStr">
+      <c r="CN1" s="23" t="inlineStr">
         <is>
           <t>back_to_back_gap</t>
         </is>
       </c>
-      <c r="CN1" s="23" t="inlineStr">
+      <c r="CO1" s="23" t="inlineStr">
         <is>
           <t>games_last_7_gap</t>
         </is>
       </c>
-      <c r="CO1" s="23" t="inlineStr">
+      <c r="CP1" s="23" t="inlineStr">
         <is>
           <t>schedule_missingness</t>
         </is>
       </c>
-      <c r="CP1" s="23" t="inlineStr">
+      <c r="CQ1" s="23" t="inlineStr">
         <is>
           <t>market_residual_probability</t>
         </is>
       </c>
-      <c r="CQ1" s="23" t="inlineStr">
+      <c r="CR1" s="23" t="inlineStr">
         <is>
           <t>trade_candidate</t>
         </is>
@@ -1875,6 +1882,7 @@
       <c r="CO2" s="24" t="n"/>
       <c r="CP2" s="24" t="n"/>
       <c r="CQ2" s="24" t="n"/>
+      <c r="CR2" s="24" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
@@ -2162,6 +2170,7 @@
       <c r="CO3" s="24" t="n"/>
       <c r="CP3" s="24" t="n"/>
       <c r="CQ3" s="24" t="n"/>
+      <c r="CR3" s="24" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
@@ -2449,6 +2458,7 @@
       <c r="CO4" s="24" t="n"/>
       <c r="CP4" s="24" t="n"/>
       <c r="CQ4" s="24" t="n"/>
+      <c r="CR4" s="24" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
@@ -2736,6 +2746,7 @@
       <c r="CO5" s="24" t="n"/>
       <c r="CP5" s="24" t="n"/>
       <c r="CQ5" s="24" t="n"/>
+      <c r="CR5" s="24" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
@@ -3023,6 +3034,7 @@
       <c r="CO6" s="24" t="n"/>
       <c r="CP6" s="24" t="n"/>
       <c r="CQ6" s="24" t="n"/>
+      <c r="CR6" s="24" t="n"/>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
@@ -3310,6 +3322,7 @@
       <c r="CO7" s="24" t="n"/>
       <c r="CP7" s="24" t="n"/>
       <c r="CQ7" s="24" t="n"/>
+      <c r="CR7" s="24" t="n"/>
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
@@ -3597,6 +3610,7 @@
       <c r="CO8" s="24" t="n"/>
       <c r="CP8" s="24" t="n"/>
       <c r="CQ8" s="24" t="n"/>
+      <c r="CR8" s="24" t="n"/>
     </row>
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
@@ -3884,6 +3898,7 @@
       <c r="CO9" s="24" t="n"/>
       <c r="CP9" s="24" t="n"/>
       <c r="CQ9" s="24" t="n"/>
+      <c r="CR9" s="24" t="n"/>
     </row>
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
@@ -4171,6 +4186,7 @@
       <c r="CO10" s="24" t="n"/>
       <c r="CP10" s="24" t="n"/>
       <c r="CQ10" s="24" t="n"/>
+      <c r="CR10" s="24" t="n"/>
     </row>
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
@@ -4458,6 +4474,7 @@
       <c r="CO11" s="24" t="n"/>
       <c r="CP11" s="24" t="n"/>
       <c r="CQ11" s="24" t="n"/>
+      <c r="CR11" s="24" t="n"/>
     </row>
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
@@ -4745,6 +4762,7 @@
       <c r="CO12" s="24" t="n"/>
       <c r="CP12" s="24" t="n"/>
       <c r="CQ12" s="24" t="n"/>
+      <c r="CR12" s="24" t="n"/>
     </row>
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
@@ -5032,6 +5050,7 @@
       <c r="CO13" s="24" t="n"/>
       <c r="CP13" s="24" t="n"/>
       <c r="CQ13" s="24" t="n"/>
+      <c r="CR13" s="24" t="n"/>
     </row>
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="24" t="inlineStr">
@@ -5319,6 +5338,7 @@
       <c r="CO14" s="24" t="n"/>
       <c r="CP14" s="24" t="n"/>
       <c r="CQ14" s="24" t="n"/>
+      <c r="CR14" s="24" t="n"/>
     </row>
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="24" t="inlineStr">
@@ -5606,6 +5626,7 @@
       <c r="CO15" s="24" t="n"/>
       <c r="CP15" s="24" t="n"/>
       <c r="CQ15" s="24" t="n"/>
+      <c r="CR15" s="24" t="n"/>
     </row>
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="24" t="inlineStr">
@@ -5893,6 +5914,7 @@
       <c r="CO16" s="24" t="n"/>
       <c r="CP16" s="24" t="n"/>
       <c r="CQ16" s="24" t="n"/>
+      <c r="CR16" s="24" t="n"/>
     </row>
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="24" t="inlineStr">
@@ -6180,6 +6202,7 @@
       <c r="CO17" s="24" t="n"/>
       <c r="CP17" s="24" t="n"/>
       <c r="CQ17" s="24" t="n"/>
+      <c r="CR17" s="24" t="n"/>
     </row>
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="24" t="inlineStr">
@@ -6467,6 +6490,7 @@
       <c r="CO18" s="24" t="n"/>
       <c r="CP18" s="24" t="n"/>
       <c r="CQ18" s="24" t="n"/>
+      <c r="CR18" s="24" t="n"/>
     </row>
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="24" t="inlineStr">
@@ -6753,7 +6777,8 @@
       <c r="CN19" s="24" t="n"/>
       <c r="CO19" s="24" t="n"/>
       <c r="CP19" s="24" t="n"/>
-      <c r="CQ19" s="24" t="inlineStr">
+      <c r="CQ19" s="24" t="n"/>
+      <c r="CR19" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -7044,7 +7069,8 @@
       <c r="CN20" s="24" t="n"/>
       <c r="CO20" s="24" t="n"/>
       <c r="CP20" s="24" t="n"/>
-      <c r="CQ20" s="24" t="inlineStr">
+      <c r="CQ20" s="24" t="n"/>
+      <c r="CR20" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -7335,7 +7361,8 @@
       <c r="CN21" s="24" t="n"/>
       <c r="CO21" s="24" t="n"/>
       <c r="CP21" s="24" t="n"/>
-      <c r="CQ21" s="24" t="inlineStr">
+      <c r="CQ21" s="24" t="n"/>
+      <c r="CR21" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -7626,7 +7653,8 @@
       <c r="CN22" s="24" t="n"/>
       <c r="CO22" s="24" t="n"/>
       <c r="CP22" s="24" t="n"/>
-      <c r="CQ22" s="24" t="inlineStr">
+      <c r="CQ22" s="24" t="n"/>
+      <c r="CR22" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -7917,7 +7945,8 @@
       <c r="CN23" s="24" t="n"/>
       <c r="CO23" s="24" t="n"/>
       <c r="CP23" s="24" t="n"/>
-      <c r="CQ23" s="24" t="inlineStr">
+      <c r="CQ23" s="24" t="n"/>
+      <c r="CR23" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -8208,7 +8237,8 @@
       <c r="CN24" s="24" t="n"/>
       <c r="CO24" s="24" t="n"/>
       <c r="CP24" s="24" t="n"/>
-      <c r="CQ24" s="24" t="inlineStr">
+      <c r="CQ24" s="24" t="n"/>
+      <c r="CR24" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -8499,7 +8529,8 @@
       <c r="CN25" s="24" t="n"/>
       <c r="CO25" s="24" t="n"/>
       <c r="CP25" s="24" t="n"/>
-      <c r="CQ25" s="24" t="inlineStr">
+      <c r="CQ25" s="24" t="n"/>
+      <c r="CR25" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -8790,7 +8821,8 @@
       <c r="CN26" s="24" t="n"/>
       <c r="CO26" s="24" t="n"/>
       <c r="CP26" s="24" t="n"/>
-      <c r="CQ26" s="24" t="inlineStr">
+      <c r="CQ26" s="24" t="n"/>
+      <c r="CR26" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -9081,7 +9113,8 @@
       <c r="CN27" s="24" t="n"/>
       <c r="CO27" s="24" t="n"/>
       <c r="CP27" s="24" t="n"/>
-      <c r="CQ27" s="24" t="inlineStr">
+      <c r="CQ27" s="24" t="n"/>
+      <c r="CR27" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -9372,7 +9405,8 @@
       <c r="CN28" s="24" t="n"/>
       <c r="CO28" s="24" t="n"/>
       <c r="CP28" s="24" t="n"/>
-      <c r="CQ28" s="24" t="inlineStr">
+      <c r="CQ28" s="24" t="n"/>
+      <c r="CR28" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -9381,12 +9415,12 @@
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="24" t="inlineStr">
         <is>
-          <t>b2c01b5fde4a412c</t>
+          <t>e164be4d60ab48f6</t>
         </is>
       </c>
       <c r="B29" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:56.302645Z</t>
+          <t>2026-08-04T05:18:58.736816Z</t>
         </is>
       </c>
       <c r="C29" s="24" t="inlineStr">
@@ -9431,23 +9465,23 @@
         </is>
       </c>
       <c r="L29" s="26" t="n">
-        <v>-194</v>
+        <v>-117</v>
       </c>
       <c r="M29" s="27" t="n">
-        <v>1.515464</v>
+        <v>1.854701</v>
       </c>
       <c r="N29" s="28" t="n">
-        <v>0.659864</v>
+        <v>0.539171</v>
       </c>
       <c r="O29" s="28" t="n">
         <v>0.530268</v>
       </c>
       <c r="P29" s="28" t="n"/>
       <c r="Q29" s="28" t="n">
-        <v>-0.129596</v>
+        <v>-0.008902999999999999</v>
       </c>
       <c r="R29" s="26" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="S29" s="29" t="n">
         <v>1</v>
@@ -9473,7 +9507,7 @@
       <c r="AD29" s="24" t="n"/>
       <c r="AE29" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6600 (market_slug=aec-lol-t1-hle-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-lol-t1-hle-2026-08-04).</t>
         </is>
       </c>
       <c r="AF29" s="31" t="inlineStr">
@@ -9557,7 +9591,7 @@
       </c>
       <c r="BA29" s="24" t="inlineStr">
         <is>
-          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
         </is>
       </c>
       <c r="BB29" s="24" t="inlineStr">
@@ -9572,7 +9606,7 @@
       </c>
       <c r="BD29" s="24" t="inlineStr">
         <is>
-          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+          <t>3cad1698285ce067945fffa86d78b132eab6a11da046a54b1a9513fa3414e5e2</t>
         </is>
       </c>
       <c r="BE29" s="24" t="inlineStr">
@@ -9592,7 +9626,7 @@
       </c>
       <c r="BH29" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:40.152554Z</t>
+          <t>2026-08-04T05:18:18.693939Z</t>
         </is>
       </c>
       <c r="BI29" s="24" t="inlineStr">
@@ -9602,13 +9636,13 @@
       </c>
       <c r="BJ29" s="25" t="n"/>
       <c r="BK29" s="26" t="n">
-        <v>-194</v>
+        <v>-117</v>
       </c>
       <c r="BL29" s="27" t="n">
-        <v>1.515464</v>
+        <v>1.854701</v>
       </c>
       <c r="BM29" s="28" t="n">
-        <v>0.659864</v>
+        <v>0.539171</v>
       </c>
       <c r="BN29" s="28" t="n"/>
       <c r="BO29" s="28" t="n"/>
@@ -9639,7 +9673,8 @@
       <c r="CN29" s="24" t="n"/>
       <c r="CO29" s="24" t="n"/>
       <c r="CP29" s="24" t="n"/>
-      <c r="CQ29" s="24" t="inlineStr">
+      <c r="CQ29" s="24" t="n"/>
+      <c r="CR29" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -9648,12 +9683,12 @@
     <row r="30" ht="36" customHeight="1">
       <c r="A30" s="24" t="inlineStr">
         <is>
-          <t>3519cc599f834356</t>
+          <t>543dd0d72d1946a9</t>
         </is>
       </c>
       <c r="B30" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:56.302645Z</t>
+          <t>2026-08-04T08:56:56.469660Z</t>
         </is>
       </c>
       <c r="C30" s="24" t="inlineStr">
@@ -9698,20 +9733,20 @@
         </is>
       </c>
       <c r="L30" s="26" t="n">
-        <v>-213</v>
+        <v>-223</v>
       </c>
       <c r="M30" s="27" t="n">
-        <v>1.469484</v>
+        <v>1.44843</v>
       </c>
       <c r="N30" s="28" t="n">
-        <v>0.680511</v>
+        <v>0.690402</v>
       </c>
       <c r="O30" s="28" t="n">
         <v>0.613874</v>
       </c>
       <c r="P30" s="28" t="n"/>
       <c r="Q30" s="28" t="n">
-        <v>-0.066637</v>
+        <v>-0.076528</v>
       </c>
       <c r="R30" s="26" t="n">
         <v>0</v>
@@ -9740,7 +9775,7 @@
       <c r="AD30" s="24" t="n"/>
       <c r="AE30" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-lol-t1a-ktc-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-lol-t1a-ktc-2026-08-04).</t>
         </is>
       </c>
       <c r="AF30" s="31" t="inlineStr">
@@ -9824,7 +9859,7 @@
       </c>
       <c r="BA30" s="24" t="inlineStr">
         <is>
-          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
         </is>
       </c>
       <c r="BB30" s="24" t="inlineStr">
@@ -9839,7 +9874,7 @@
       </c>
       <c r="BD30" s="24" t="inlineStr">
         <is>
-          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
         </is>
       </c>
       <c r="BE30" s="24" t="inlineStr">
@@ -9859,7 +9894,7 @@
       </c>
       <c r="BH30" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:41.711967Z</t>
+          <t>2026-08-04T08:56:22.321845Z</t>
         </is>
       </c>
       <c r="BI30" s="24" t="inlineStr">
@@ -9869,13 +9904,13 @@
       </c>
       <c r="BJ30" s="25" t="n"/>
       <c r="BK30" s="26" t="n">
-        <v>-213</v>
+        <v>-223</v>
       </c>
       <c r="BL30" s="27" t="n">
-        <v>1.469484</v>
+        <v>1.44843</v>
       </c>
       <c r="BM30" s="28" t="n">
-        <v>0.680511</v>
+        <v>0.690402</v>
       </c>
       <c r="BN30" s="28" t="n"/>
       <c r="BO30" s="28" t="n"/>
@@ -9906,7 +9941,8 @@
       <c r="CN30" s="24" t="n"/>
       <c r="CO30" s="24" t="n"/>
       <c r="CP30" s="24" t="n"/>
-      <c r="CQ30" s="24" t="inlineStr">
+      <c r="CQ30" s="24" t="n"/>
+      <c r="CR30" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -9915,12 +9951,12 @@
     <row r="31" ht="36" customHeight="1">
       <c r="A31" s="24" t="inlineStr">
         <is>
-          <t>3fb0de25f8e046fa</t>
+          <t>d945818735054c3c</t>
         </is>
       </c>
       <c r="B31" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:56.302645Z</t>
+          <t>2026-08-04T08:56:56.469660Z</t>
         </is>
       </c>
       <c r="C31" s="24" t="inlineStr">
@@ -9965,23 +10001,23 @@
         </is>
       </c>
       <c r="L31" s="26" t="n">
-        <v>-150</v>
+        <v>-170</v>
       </c>
       <c r="M31" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.588235</v>
       </c>
       <c r="N31" s="28" t="n">
-        <v>0.6</v>
+        <v>0.62963</v>
       </c>
       <c r="O31" s="28" t="n">
         <v>0.578292</v>
       </c>
       <c r="P31" s="28" t="n"/>
       <c r="Q31" s="28" t="n">
-        <v>-0.021708</v>
+        <v>-0.051338</v>
       </c>
       <c r="R31" s="26" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="S31" s="29" t="n">
         <v>1.25</v>
@@ -10007,7 +10043,7 @@
       <c r="AD31" s="24" t="n"/>
       <c r="AE31" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-lol-bro-krx-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-lol-bro-krx-2026-08-04).</t>
         </is>
       </c>
       <c r="AF31" s="31" t="inlineStr">
@@ -10091,7 +10127,7 @@
       </c>
       <c r="BA31" s="24" t="inlineStr">
         <is>
-          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
         </is>
       </c>
       <c r="BB31" s="24" t="inlineStr">
@@ -10106,7 +10142,7 @@
       </c>
       <c r="BD31" s="24" t="inlineStr">
         <is>
-          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
         </is>
       </c>
       <c r="BE31" s="24" t="inlineStr">
@@ -10126,7 +10162,7 @@
       </c>
       <c r="BH31" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:42.207831Z</t>
+          <t>2026-08-04T08:56:22.857906Z</t>
         </is>
       </c>
       <c r="BI31" s="24" t="inlineStr">
@@ -10136,13 +10172,13 @@
       </c>
       <c r="BJ31" s="25" t="n"/>
       <c r="BK31" s="26" t="n">
-        <v>-150</v>
+        <v>-170</v>
       </c>
       <c r="BL31" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.588235</v>
       </c>
       <c r="BM31" s="28" t="n">
-        <v>0.6</v>
+        <v>0.62963</v>
       </c>
       <c r="BN31" s="28" t="n"/>
       <c r="BO31" s="28" t="n"/>
@@ -10173,7 +10209,8 @@
       <c r="CN31" s="24" t="n"/>
       <c r="CO31" s="24" t="n"/>
       <c r="CP31" s="24" t="n"/>
-      <c r="CQ31" s="24" t="inlineStr">
+      <c r="CQ31" s="24" t="n"/>
+      <c r="CR31" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -10182,22 +10219,22 @@
     <row r="32" ht="36" customHeight="1">
       <c r="A32" s="24" t="inlineStr">
         <is>
-          <t>966d0ee860cf46b4</t>
+          <t>e8f0590f77774c6c</t>
         </is>
       </c>
       <c r="B32" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:56.302645Z</t>
+          <t>2026-08-04T08:56:56.469660Z</t>
         </is>
       </c>
       <c r="C32" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T15:00:00Z</t>
+          <t>2026-08-04T16:00:00Z</t>
         </is>
       </c>
       <c r="D32" s="24" t="inlineStr">
         <is>
-          <t>70566</t>
+          <t>68510</t>
         </is>
       </c>
       <c r="E32" s="24" t="inlineStr">
@@ -10207,12 +10244,12 @@
       </c>
       <c r="F32" s="24" t="inlineStr">
         <is>
-          <t>Barcząca Esports</t>
+          <t>The Secret Club</t>
         </is>
       </c>
       <c r="G32" s="24" t="inlineStr">
         <is>
-          <t>Lodis</t>
+          <t>MAGAZA</t>
         </is>
       </c>
       <c r="H32" s="24" t="inlineStr">
@@ -10222,7 +10259,7 @@
       </c>
       <c r="I32" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J32" s="25" t="n"/>
@@ -10232,26 +10269,26 @@
         </is>
       </c>
       <c r="L32" s="26" t="n">
-        <v>223</v>
+        <v>144</v>
       </c>
       <c r="M32" s="27" t="n">
-        <v>3.23</v>
+        <v>2.44</v>
       </c>
       <c r="N32" s="28" t="n">
-        <v>0.309598</v>
+        <v>0.409836</v>
       </c>
       <c r="O32" s="28" t="n">
-        <v>0.69409</v>
+        <v>0.517061</v>
       </c>
       <c r="P32" s="28" t="n"/>
       <c r="Q32" s="28" t="n">
-        <v>0.384492</v>
+        <v>0.107225</v>
       </c>
       <c r="R32" s="26" t="n">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="S32" s="29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T32" s="24" t="inlineStr">
         <is>
@@ -10274,7 +10311,7 @@
       <c r="AD32" s="24" t="n"/>
       <c r="AE32" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3100 (market_slug=aec-lol-lds-bce-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.4100 (market_slug=aec-lol-mgz-tsc-2026-08-04).</t>
         </is>
       </c>
       <c r="AF32" s="31" t="inlineStr">
@@ -10292,7 +10329,7 @@
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL32" s="26" t="n">
@@ -10300,47 +10337,47 @@
       </c>
       <c r="AM32" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN32" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO32" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP32" s="24" t="inlineStr">
         <is>
-          <t>Barcząca Esports</t>
+          <t>The Secret Club</t>
         </is>
       </c>
       <c r="AQ32" s="24" t="inlineStr">
         <is>
-          <t>Barcząca Esports</t>
+          <t>The Secret Club</t>
         </is>
       </c>
       <c r="AR32" s="24" t="inlineStr">
         <is>
-          <t>Barcząca Esports</t>
+          <t>The Secret Club</t>
         </is>
       </c>
       <c r="AS32" s="24" t="inlineStr">
         <is>
-          <t>Lodis</t>
+          <t>MAGAZA</t>
         </is>
       </c>
       <c r="AT32" s="24" t="inlineStr">
         <is>
-          <t>Lodis</t>
+          <t>MAGAZA</t>
         </is>
       </c>
       <c r="AU32" s="24" t="inlineStr">
         <is>
-          <t>Lodis</t>
+          <t>MAGAZA</t>
         </is>
       </c>
       <c r="AV32" s="24" t="n"/>
@@ -10358,7 +10395,7 @@
       </c>
       <c r="BA32" s="24" t="inlineStr">
         <is>
-          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
         </is>
       </c>
       <c r="BB32" s="24" t="inlineStr">
@@ -10373,7 +10410,7 @@
       </c>
       <c r="BD32" s="24" t="inlineStr">
         <is>
-          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
         </is>
       </c>
       <c r="BE32" s="24" t="inlineStr">
@@ -10393,7 +10430,7 @@
       </c>
       <c r="BH32" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:43.286617Z</t>
+          <t>2026-08-04T08:56:24.555143Z</t>
         </is>
       </c>
       <c r="BI32" s="24" t="inlineStr">
@@ -10403,13 +10440,13 @@
       </c>
       <c r="BJ32" s="25" t="n"/>
       <c r="BK32" s="26" t="n">
-        <v>223</v>
+        <v>144</v>
       </c>
       <c r="BL32" s="27" t="n">
-        <v>3.23</v>
+        <v>2.44</v>
       </c>
       <c r="BM32" s="28" t="n">
-        <v>0.309598</v>
+        <v>0.409836</v>
       </c>
       <c r="BN32" s="28" t="n"/>
       <c r="BO32" s="28" t="n"/>
@@ -10440,7 +10477,8 @@
       <c r="CN32" s="24" t="n"/>
       <c r="CO32" s="24" t="n"/>
       <c r="CP32" s="24" t="n"/>
-      <c r="CQ32" s="24" t="inlineStr">
+      <c r="CQ32" s="24" t="n"/>
+      <c r="CR32" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -10449,12 +10487,12 @@
     <row r="33" ht="36" customHeight="1">
       <c r="A33" s="24" t="inlineStr">
         <is>
-          <t>87e0f926f2124592</t>
+          <t>0d452ec569fa4063</t>
         </is>
       </c>
       <c r="B33" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:56.302645Z</t>
+          <t>2026-08-04T08:56:56.469660Z</t>
         </is>
       </c>
       <c r="C33" s="24" t="inlineStr">
@@ -10499,23 +10537,23 @@
         </is>
       </c>
       <c r="L33" s="26" t="n">
-        <v>-104</v>
+        <v>-108</v>
       </c>
       <c r="M33" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.925926</v>
       </c>
       <c r="N33" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.519231</v>
       </c>
       <c r="O33" s="28" t="n">
         <v>0.631317</v>
       </c>
       <c r="P33" s="28" t="n"/>
       <c r="Q33" s="28" t="n">
-        <v>0.121513</v>
+        <v>0.112086</v>
       </c>
       <c r="R33" s="26" t="n">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="S33" s="29" t="n">
         <v>1.5</v>
@@ -10541,7 +10579,7 @@
       <c r="AD33" s="24" t="n"/>
       <c r="AE33" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-lol-ijc-sc-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.5200 (market_slug=aec-lol-ijc-sc-2026-08-04).</t>
         </is>
       </c>
       <c r="AF33" s="31" t="inlineStr">
@@ -10625,7 +10663,7 @@
       </c>
       <c r="BA33" s="24" t="inlineStr">
         <is>
-          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
         </is>
       </c>
       <c r="BB33" s="24" t="inlineStr">
@@ -10640,7 +10678,7 @@
       </c>
       <c r="BD33" s="24" t="inlineStr">
         <is>
-          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
         </is>
       </c>
       <c r="BE33" s="24" t="inlineStr">
@@ -10660,7 +10698,7 @@
       </c>
       <c r="BH33" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:44.932625Z</t>
+          <t>2026-08-04T08:56:25.701342Z</t>
         </is>
       </c>
       <c r="BI33" s="24" t="inlineStr">
@@ -10670,13 +10708,13 @@
       </c>
       <c r="BJ33" s="25" t="n"/>
       <c r="BK33" s="26" t="n">
-        <v>-104</v>
+        <v>-108</v>
       </c>
       <c r="BL33" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.925926</v>
       </c>
       <c r="BM33" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.519231</v>
       </c>
       <c r="BN33" s="28" t="n"/>
       <c r="BO33" s="28" t="n"/>
@@ -10707,7 +10745,8 @@
       <c r="CN33" s="24" t="n"/>
       <c r="CO33" s="24" t="n"/>
       <c r="CP33" s="24" t="n"/>
-      <c r="CQ33" s="24" t="inlineStr">
+      <c r="CQ33" s="24" t="n"/>
+      <c r="CR33" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -10716,12 +10755,12 @@
     <row r="34" ht="36" customHeight="1">
       <c r="A34" s="24" t="inlineStr">
         <is>
-          <t>6bdcf6660f9a4dde</t>
+          <t>d841c1d7a3e94d90</t>
         </is>
       </c>
       <c r="B34" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:56.302645Z</t>
+          <t>2026-08-04T08:56:56.469660Z</t>
         </is>
       </c>
       <c r="C34" s="24" t="inlineStr">
@@ -10731,7 +10770,7 @@
       </c>
       <c r="D34" s="24" t="inlineStr">
         <is>
-          <t>68585</t>
+          <t>70567</t>
         </is>
       </c>
       <c r="E34" s="24" t="inlineStr">
@@ -10741,12 +10780,12 @@
       </c>
       <c r="F34" s="24" t="inlineStr">
         <is>
-          <t>The Bandits</t>
+          <t>Anonymo Esports</t>
         </is>
       </c>
       <c r="G34" s="24" t="inlineStr">
         <is>
-          <t>mCon esports</t>
+          <t>DOCISK</t>
         </is>
       </c>
       <c r="H34" s="24" t="inlineStr">
@@ -10766,23 +10805,23 @@
         </is>
       </c>
       <c r="L34" s="26" t="n">
-        <v>212</v>
+        <v>163</v>
       </c>
       <c r="M34" s="27" t="n">
-        <v>3.12</v>
+        <v>2.63</v>
       </c>
       <c r="N34" s="28" t="n">
-        <v>0.320513</v>
+        <v>0.380228</v>
       </c>
       <c r="O34" s="28" t="n">
-        <v>0.509157</v>
+        <v>0.518338</v>
       </c>
       <c r="P34" s="28" t="n"/>
       <c r="Q34" s="28" t="n">
-        <v>0.188644</v>
+        <v>0.13811</v>
       </c>
       <c r="R34" s="26" t="n">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="S34" s="29" t="n">
         <v>1</v>
@@ -10808,7 +10847,7 @@
       <c r="AD34" s="24" t="n"/>
       <c r="AE34" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3200 (market_slug=aec-lol-mcn-ban-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.3800 (market_slug=aec-lol-doc-ae-2026-08-04).</t>
         </is>
       </c>
       <c r="AF34" s="31" t="inlineStr">
@@ -10849,32 +10888,32 @@
       </c>
       <c r="AP34" s="24" t="inlineStr">
         <is>
-          <t>The Bandits</t>
+          <t>Anonymo Esports</t>
         </is>
       </c>
       <c r="AQ34" s="24" t="inlineStr">
         <is>
-          <t>The Bandits</t>
+          <t>Anonymo Esports</t>
         </is>
       </c>
       <c r="AR34" s="24" t="inlineStr">
         <is>
-          <t>The Bandits</t>
+          <t>Anonymo Esports</t>
         </is>
       </c>
       <c r="AS34" s="24" t="inlineStr">
         <is>
-          <t>mCon esports</t>
+          <t>DOCISK</t>
         </is>
       </c>
       <c r="AT34" s="24" t="inlineStr">
         <is>
-          <t>mCon esports</t>
+          <t>DOCISK</t>
         </is>
       </c>
       <c r="AU34" s="24" t="inlineStr">
         <is>
-          <t>mCon esports</t>
+          <t>DOCISK</t>
         </is>
       </c>
       <c r="AV34" s="24" t="n"/>
@@ -10892,7 +10931,7 @@
       </c>
       <c r="BA34" s="24" t="inlineStr">
         <is>
-          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
         </is>
       </c>
       <c r="BB34" s="24" t="inlineStr">
@@ -10907,7 +10946,7 @@
       </c>
       <c r="BD34" s="24" t="inlineStr">
         <is>
-          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
         </is>
       </c>
       <c r="BE34" s="24" t="inlineStr">
@@ -10927,7 +10966,7 @@
       </c>
       <c r="BH34" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:46.530291Z</t>
+          <t>2026-08-04T08:56:26.316476Z</t>
         </is>
       </c>
       <c r="BI34" s="24" t="inlineStr">
@@ -10937,13 +10976,13 @@
       </c>
       <c r="BJ34" s="25" t="n"/>
       <c r="BK34" s="26" t="n">
-        <v>212</v>
+        <v>163</v>
       </c>
       <c r="BL34" s="27" t="n">
-        <v>3.12</v>
+        <v>2.63</v>
       </c>
       <c r="BM34" s="28" t="n">
-        <v>0.320513</v>
+        <v>0.380228</v>
       </c>
       <c r="BN34" s="28" t="n"/>
       <c r="BO34" s="28" t="n"/>
@@ -10974,7 +11013,8 @@
       <c r="CN34" s="24" t="n"/>
       <c r="CO34" s="24" t="n"/>
       <c r="CP34" s="24" t="n"/>
-      <c r="CQ34" s="24" t="inlineStr">
+      <c r="CQ34" s="24" t="n"/>
+      <c r="CR34" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -10983,22 +11023,22 @@
     <row r="35" ht="36" customHeight="1">
       <c r="A35" s="24" t="inlineStr">
         <is>
-          <t>c9c778eee56441ba</t>
+          <t>2290407cea2e4a40</t>
         </is>
       </c>
       <c r="B35" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:56.302645Z</t>
+          <t>2026-08-04T08:56:56.469660Z</t>
         </is>
       </c>
       <c r="C35" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T17:00:00Z</t>
+          <t>2026-08-04T18:00:00Z</t>
         </is>
       </c>
       <c r="D35" s="24" t="inlineStr">
         <is>
-          <t>70567</t>
+          <t>68691</t>
         </is>
       </c>
       <c r="E35" s="24" t="inlineStr">
@@ -11008,12 +11048,12 @@
       </c>
       <c r="F35" s="24" t="inlineStr">
         <is>
-          <t>Anonymo Esports</t>
+          <t>ZennIT</t>
         </is>
       </c>
       <c r="G35" s="24" t="inlineStr">
         <is>
-          <t>DOCISK</t>
+          <t>Once Upon A Team</t>
         </is>
       </c>
       <c r="H35" s="24" t="inlineStr">
@@ -11023,7 +11063,7 @@
       </c>
       <c r="I35" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J35" s="25" t="n"/>
@@ -11033,23 +11073,23 @@
         </is>
       </c>
       <c r="L35" s="26" t="n">
-        <v>163</v>
+        <v>-203</v>
       </c>
       <c r="M35" s="27" t="n">
-        <v>2.63</v>
+        <v>1.492611</v>
       </c>
       <c r="N35" s="28" t="n">
-        <v>0.380228</v>
+        <v>0.669967</v>
       </c>
       <c r="O35" s="28" t="n">
-        <v>0.518338</v>
+        <v>0.549366</v>
       </c>
       <c r="P35" s="28" t="n"/>
       <c r="Q35" s="28" t="n">
-        <v>0.13811</v>
+        <v>-0.120601</v>
       </c>
       <c r="R35" s="26" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="S35" s="29" t="n">
         <v>1</v>
@@ -11075,7 +11115,7 @@
       <c r="AD35" s="24" t="n"/>
       <c r="AE35" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3800 (market_slug=aec-lol-doc-ae-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-lol-ouat-znt-2026-08-04).</t>
         </is>
       </c>
       <c r="AF35" s="31" t="inlineStr">
@@ -11116,32 +11156,32 @@
       </c>
       <c r="AP35" s="24" t="inlineStr">
         <is>
-          <t>Anonymo Esports</t>
+          <t>ZennIT</t>
         </is>
       </c>
       <c r="AQ35" s="24" t="inlineStr">
         <is>
-          <t>Anonymo Esports</t>
+          <t>ZennIT</t>
         </is>
       </c>
       <c r="AR35" s="24" t="inlineStr">
         <is>
-          <t>Anonymo Esports</t>
+          <t>ZennIT</t>
         </is>
       </c>
       <c r="AS35" s="24" t="inlineStr">
         <is>
-          <t>DOCISK</t>
+          <t>Once Upon A Team</t>
         </is>
       </c>
       <c r="AT35" s="24" t="inlineStr">
         <is>
-          <t>DOCISK</t>
+          <t>Once Upon A Team</t>
         </is>
       </c>
       <c r="AU35" s="24" t="inlineStr">
         <is>
-          <t>DOCISK</t>
+          <t>Once Upon A Team</t>
         </is>
       </c>
       <c r="AV35" s="24" t="n"/>
@@ -11159,7 +11199,7 @@
       </c>
       <c r="BA35" s="24" t="inlineStr">
         <is>
-          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
         </is>
       </c>
       <c r="BB35" s="24" t="inlineStr">
@@ -11174,7 +11214,7 @@
       </c>
       <c r="BD35" s="24" t="inlineStr">
         <is>
-          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
         </is>
       </c>
       <c r="BE35" s="24" t="inlineStr">
@@ -11194,7 +11234,7 @@
       </c>
       <c r="BH35" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:47.025076Z</t>
+          <t>2026-08-04T08:56:29.255997Z</t>
         </is>
       </c>
       <c r="BI35" s="24" t="inlineStr">
@@ -11204,13 +11244,13 @@
       </c>
       <c r="BJ35" s="25" t="n"/>
       <c r="BK35" s="26" t="n">
-        <v>163</v>
+        <v>-203</v>
       </c>
       <c r="BL35" s="27" t="n">
-        <v>2.63</v>
+        <v>1.492611</v>
       </c>
       <c r="BM35" s="28" t="n">
-        <v>0.380228</v>
+        <v>0.669967</v>
       </c>
       <c r="BN35" s="28" t="n"/>
       <c r="BO35" s="28" t="n"/>
@@ -11241,21 +11281,22 @@
       <c r="CN35" s="24" t="n"/>
       <c r="CO35" s="24" t="n"/>
       <c r="CP35" s="24" t="n"/>
-      <c r="CQ35" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
+      <c r="CQ35" s="24" t="n"/>
+      <c r="CR35" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="36" ht="36" customHeight="1">
       <c r="A36" s="24" t="inlineStr">
         <is>
-          <t>800cb61d26c84c57</t>
+          <t>c267f2c13c334c73</t>
         </is>
       </c>
       <c r="B36" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:56.302645Z</t>
+          <t>2026-08-04T08:56:56.469660Z</t>
         </is>
       </c>
       <c r="C36" s="24" t="inlineStr">
@@ -11265,7 +11306,7 @@
       </c>
       <c r="D36" s="24" t="inlineStr">
         <is>
-          <t>68691</t>
+          <t>68690</t>
         </is>
       </c>
       <c r="E36" s="24" t="inlineStr">
@@ -11275,12 +11316,12 @@
       </c>
       <c r="F36" s="24" t="inlineStr">
         <is>
-          <t>ZennIT</t>
+          <t>Lupus Esports</t>
         </is>
       </c>
       <c r="G36" s="24" t="inlineStr">
         <is>
-          <t>Once Upon A Team</t>
+          <t xml:space="preserve">Croatian Flair x RLX </t>
         </is>
       </c>
       <c r="H36" s="24" t="inlineStr">
@@ -11290,7 +11331,7 @@
       </c>
       <c r="I36" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J36" s="25" t="n"/>
@@ -11300,23 +11341,23 @@
         </is>
       </c>
       <c r="L36" s="26" t="n">
-        <v>-203</v>
+        <v>-117</v>
       </c>
       <c r="M36" s="27" t="n">
-        <v>1.492611</v>
+        <v>1.854701</v>
       </c>
       <c r="N36" s="28" t="n">
-        <v>0.669967</v>
+        <v>0.539171</v>
       </c>
       <c r="O36" s="28" t="n">
-        <v>0.549366</v>
+        <v>0.55055</v>
       </c>
       <c r="P36" s="28" t="n"/>
       <c r="Q36" s="28" t="n">
-        <v>-0.120601</v>
+        <v>0.011379</v>
       </c>
       <c r="R36" s="26" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="S36" s="29" t="n">
         <v>1</v>
@@ -11342,7 +11383,7 @@
       <c r="AD36" s="24" t="n"/>
       <c r="AE36" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-lol-ouat-znt-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-lol-cfxr-lps-2026-08-04).</t>
         </is>
       </c>
       <c r="AF36" s="31" t="inlineStr">
@@ -11360,7 +11401,7 @@
       <c r="AJ36" s="31" t="n"/>
       <c r="AK36" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL36" s="26" t="n">
@@ -11368,47 +11409,47 @@
       </c>
       <c r="AM36" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN36" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO36" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP36" s="24" t="inlineStr">
         <is>
-          <t>ZennIT</t>
+          <t>Lupus Esports</t>
         </is>
       </c>
       <c r="AQ36" s="24" t="inlineStr">
         <is>
-          <t>ZennIT</t>
+          <t>Lupus Esports</t>
         </is>
       </c>
       <c r="AR36" s="24" t="inlineStr">
         <is>
-          <t>ZennIT</t>
+          <t>Lupus Esports</t>
         </is>
       </c>
       <c r="AS36" s="24" t="inlineStr">
         <is>
-          <t>Once Upon A Team</t>
+          <t xml:space="preserve">Croatian Flair x RLX </t>
         </is>
       </c>
       <c r="AT36" s="24" t="inlineStr">
         <is>
-          <t>Once Upon A Team</t>
+          <t xml:space="preserve">Croatian Flair x RLX </t>
         </is>
       </c>
       <c r="AU36" s="24" t="inlineStr">
         <is>
-          <t>Once Upon A Team</t>
+          <t xml:space="preserve">Croatian Flair x RLX </t>
         </is>
       </c>
       <c r="AV36" s="24" t="n"/>
@@ -11426,7 +11467,7 @@
       </c>
       <c r="BA36" s="24" t="inlineStr">
         <is>
-          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
         </is>
       </c>
       <c r="BB36" s="24" t="inlineStr">
@@ -11441,7 +11482,7 @@
       </c>
       <c r="BD36" s="24" t="inlineStr">
         <is>
-          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
         </is>
       </c>
       <c r="BE36" s="24" t="inlineStr">
@@ -11461,7 +11502,7 @@
       </c>
       <c r="BH36" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:48.018849Z</t>
+          <t>2026-08-04T08:56:29.939077Z</t>
         </is>
       </c>
       <c r="BI36" s="24" t="inlineStr">
@@ -11471,13 +11512,13 @@
       </c>
       <c r="BJ36" s="25" t="n"/>
       <c r="BK36" s="26" t="n">
-        <v>-203</v>
+        <v>-117</v>
       </c>
       <c r="BL36" s="27" t="n">
-        <v>1.492611</v>
+        <v>1.854701</v>
       </c>
       <c r="BM36" s="28" t="n">
-        <v>0.669967</v>
+        <v>0.539171</v>
       </c>
       <c r="BN36" s="28" t="n"/>
       <c r="BO36" s="28" t="n"/>
@@ -11508,21 +11549,22 @@
       <c r="CN36" s="24" t="n"/>
       <c r="CO36" s="24" t="n"/>
       <c r="CP36" s="24" t="n"/>
-      <c r="CQ36" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
+      <c r="CQ36" s="24" t="n"/>
+      <c r="CR36" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="37" ht="36" customHeight="1">
       <c r="A37" s="24" t="inlineStr">
         <is>
-          <t>9dfd7a89789f4d73</t>
+          <t>7c565f020050418f</t>
         </is>
       </c>
       <c r="B37" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:56.302645Z</t>
+          <t>2026-08-04T08:56:56.469660Z</t>
         </is>
       </c>
       <c r="C37" s="24" t="inlineStr">
@@ -11567,23 +11609,23 @@
         </is>
       </c>
       <c r="L37" s="26" t="n">
-        <v>-133</v>
+        <v>-150</v>
       </c>
       <c r="M37" s="27" t="n">
-        <v>1.75188</v>
+        <v>1.666667</v>
       </c>
       <c r="N37" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.6</v>
       </c>
       <c r="O37" s="28" t="n">
         <v>0.5739340000000001</v>
       </c>
       <c r="P37" s="28" t="n"/>
       <c r="Q37" s="28" t="n">
-        <v>0.003119</v>
+        <v>-0.026066</v>
       </c>
       <c r="R37" s="26" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="S37" s="29" t="n">
         <v>1.25</v>
@@ -11609,7 +11651,7 @@
       <c r="AD37" s="24" t="n"/>
       <c r="AE37" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-lol-capy-wge-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-lol-capy-wge-2026-08-04).</t>
         </is>
       </c>
       <c r="AF37" s="31" t="inlineStr">
@@ -11627,7 +11669,7 @@
       <c r="AJ37" s="31" t="n"/>
       <c r="AK37" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL37" s="26" t="n">
@@ -11635,17 +11677,17 @@
       </c>
       <c r="AM37" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN37" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO37" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP37" s="24" t="inlineStr">
@@ -11693,7 +11735,7 @@
       </c>
       <c r="BA37" s="24" t="inlineStr">
         <is>
-          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
         </is>
       </c>
       <c r="BB37" s="24" t="inlineStr">
@@ -11708,7 +11750,7 @@
       </c>
       <c r="BD37" s="24" t="inlineStr">
         <is>
-          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
         </is>
       </c>
       <c r="BE37" s="24" t="inlineStr">
@@ -11728,7 +11770,7 @@
       </c>
       <c r="BH37" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:48.567590Z</t>
+          <t>2026-08-04T08:56:30.477262Z</t>
         </is>
       </c>
       <c r="BI37" s="24" t="inlineStr">
@@ -11738,13 +11780,13 @@
       </c>
       <c r="BJ37" s="25" t="n"/>
       <c r="BK37" s="26" t="n">
-        <v>-133</v>
+        <v>-150</v>
       </c>
       <c r="BL37" s="27" t="n">
-        <v>1.75188</v>
+        <v>1.666667</v>
       </c>
       <c r="BM37" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.6</v>
       </c>
       <c r="BN37" s="28" t="n"/>
       <c r="BO37" s="28" t="n"/>
@@ -11775,21 +11817,22 @@
       <c r="CN37" s="24" t="n"/>
       <c r="CO37" s="24" t="n"/>
       <c r="CP37" s="24" t="n"/>
-      <c r="CQ37" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
+      <c r="CQ37" s="24" t="n"/>
+      <c r="CR37" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="38" ht="36" customHeight="1">
       <c r="A38" s="24" t="inlineStr">
         <is>
-          <t>e048b6e77c6f407e</t>
+          <t>ecc521fbceea451e</t>
         </is>
       </c>
       <c r="B38" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:56.302645Z</t>
+          <t>2026-08-04T08:56:56.469660Z</t>
         </is>
       </c>
       <c r="C38" s="24" t="inlineStr">
@@ -11960,7 +12003,7 @@
       </c>
       <c r="BA38" s="24" t="inlineStr">
         <is>
-          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
         </is>
       </c>
       <c r="BB38" s="24" t="inlineStr">
@@ -11975,7 +12018,7 @@
       </c>
       <c r="BD38" s="24" t="inlineStr">
         <is>
-          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
         </is>
       </c>
       <c r="BE38" s="24" t="inlineStr">
@@ -11995,7 +12038,7 @@
       </c>
       <c r="BH38" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:49.048776Z</t>
+          <t>2026-08-04T08:56:31.160482Z</t>
         </is>
       </c>
       <c r="BI38" s="24" t="inlineStr">
@@ -12042,7 +12085,8 @@
       <c r="CN38" s="24" t="n"/>
       <c r="CO38" s="24" t="n"/>
       <c r="CP38" s="24" t="n"/>
-      <c r="CQ38" s="24" t="inlineStr">
+      <c r="CQ38" s="24" t="n"/>
+      <c r="CR38" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -12051,22 +12095,22 @@
     <row r="39" ht="36" customHeight="1">
       <c r="A39" s="24" t="inlineStr">
         <is>
-          <t>cfb2d9fb5c744b21</t>
+          <t>a0f91ef42338491d</t>
         </is>
       </c>
       <c r="B39" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:56.302645Z</t>
+          <t>2026-08-04T08:56:56.469660Z</t>
         </is>
       </c>
       <c r="C39" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T18:00:00Z</t>
+          <t>2026-08-04T20:00:00Z</t>
         </is>
       </c>
       <c r="D39" s="24" t="inlineStr">
         <is>
-          <t>68690</t>
+          <t>69143</t>
         </is>
       </c>
       <c r="E39" s="24" t="inlineStr">
@@ -12076,12 +12120,12 @@
       </c>
       <c r="F39" s="24" t="inlineStr">
         <is>
-          <t>Lupus Esports</t>
+          <t>Malvinas Gaming</t>
         </is>
       </c>
       <c r="G39" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Croatian Flair x RLX </t>
+          <t>Maze Gaming</t>
         </is>
       </c>
       <c r="H39" s="24" t="inlineStr">
@@ -12101,26 +12145,26 @@
         </is>
       </c>
       <c r="L39" s="26" t="n">
-        <v>-122</v>
+        <v>-163</v>
       </c>
       <c r="M39" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.613497</v>
       </c>
       <c r="N39" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.619772</v>
       </c>
       <c r="O39" s="28" t="n">
-        <v>0.55055</v>
+        <v>0.624143</v>
       </c>
       <c r="P39" s="28" t="n"/>
       <c r="Q39" s="28" t="n">
-        <v>0.001</v>
+        <v>0.004371</v>
       </c>
       <c r="R39" s="26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S39" s="29" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="T39" s="24" t="inlineStr">
         <is>
@@ -12143,7 +12187,7 @@
       <c r="AD39" s="24" t="n"/>
       <c r="AE39" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-lol-cfxr-lps-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-lol-maz-mg-2026-08-04).</t>
         </is>
       </c>
       <c r="AF39" s="31" t="inlineStr">
@@ -12184,32 +12228,32 @@
       </c>
       <c r="AP39" s="24" t="inlineStr">
         <is>
-          <t>Lupus Esports</t>
+          <t>Malvinas Gaming</t>
         </is>
       </c>
       <c r="AQ39" s="24" t="inlineStr">
         <is>
-          <t>Lupus Esports</t>
+          <t>Malvinas Gaming</t>
         </is>
       </c>
       <c r="AR39" s="24" t="inlineStr">
         <is>
-          <t>Lupus Esports</t>
+          <t>Malvinas Gaming</t>
         </is>
       </c>
       <c r="AS39" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Croatian Flair x RLX </t>
+          <t>Maze Gaming</t>
         </is>
       </c>
       <c r="AT39" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Croatian Flair x RLX </t>
+          <t>Maze Gaming</t>
         </is>
       </c>
       <c r="AU39" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Croatian Flair x RLX </t>
+          <t>Maze Gaming</t>
         </is>
       </c>
       <c r="AV39" s="24" t="n"/>
@@ -12227,7 +12271,7 @@
       </c>
       <c r="BA39" s="24" t="inlineStr">
         <is>
-          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
         </is>
       </c>
       <c r="BB39" s="24" t="inlineStr">
@@ -12242,7 +12286,7 @@
       </c>
       <c r="BD39" s="24" t="inlineStr">
         <is>
-          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
         </is>
       </c>
       <c r="BE39" s="24" t="inlineStr">
@@ -12262,7 +12306,7 @@
       </c>
       <c r="BH39" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:49.613554Z</t>
+          <t>2026-08-04T08:56:34.284466Z</t>
         </is>
       </c>
       <c r="BI39" s="24" t="inlineStr">
@@ -12272,13 +12316,13 @@
       </c>
       <c r="BJ39" s="25" t="n"/>
       <c r="BK39" s="26" t="n">
-        <v>-122</v>
+        <v>-163</v>
       </c>
       <c r="BL39" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.613497</v>
       </c>
       <c r="BM39" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.619772</v>
       </c>
       <c r="BN39" s="28" t="n"/>
       <c r="BO39" s="28" t="n"/>
@@ -12309,7 +12353,8 @@
       <c r="CN39" s="24" t="n"/>
       <c r="CO39" s="24" t="n"/>
       <c r="CP39" s="24" t="n"/>
-      <c r="CQ39" s="24" t="inlineStr">
+      <c r="CQ39" s="24" t="n"/>
+      <c r="CR39" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -12318,12 +12363,12 @@
     <row r="40" ht="36" customHeight="1">
       <c r="A40" s="24" t="inlineStr">
         <is>
-          <t>2c772ea2540843f1</t>
+          <t>4605a6cd92a44696</t>
         </is>
       </c>
       <c r="B40" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:56.302645Z</t>
+          <t>2026-08-04T08:56:56.469660Z</t>
         </is>
       </c>
       <c r="C40" s="24" t="inlineStr">
@@ -12333,7 +12378,7 @@
       </c>
       <c r="D40" s="24" t="inlineStr">
         <is>
-          <t>69143</t>
+          <t>69144</t>
         </is>
       </c>
       <c r="E40" s="24" t="inlineStr">
@@ -12343,12 +12388,12 @@
       </c>
       <c r="F40" s="24" t="inlineStr">
         <is>
-          <t>Malvinas Gaming</t>
+          <t>INTZ e-Sports</t>
         </is>
       </c>
       <c r="G40" s="24" t="inlineStr">
         <is>
-          <t>Maze Gaming</t>
+          <t>Vivo Keyd Stars Academy</t>
         </is>
       </c>
       <c r="H40" s="24" t="inlineStr">
@@ -12368,26 +12413,26 @@
         </is>
       </c>
       <c r="L40" s="26" t="n">
-        <v>-163</v>
+        <v>104</v>
       </c>
       <c r="M40" s="27" t="n">
-        <v>1.613497</v>
+        <v>2.04</v>
       </c>
       <c r="N40" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.490196</v>
       </c>
       <c r="O40" s="28" t="n">
-        <v>0.624143</v>
+        <v>0.591618</v>
       </c>
       <c r="P40" s="28" t="n"/>
       <c r="Q40" s="28" t="n">
-        <v>0.004371</v>
+        <v>0.101422</v>
       </c>
       <c r="R40" s="26" t="n">
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="S40" s="29" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="T40" s="24" t="inlineStr">
         <is>
@@ -12410,7 +12455,7 @@
       <c r="AD40" s="24" t="n"/>
       <c r="AE40" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-lol-maz-mg-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.4900 (market_slug=aec-lol-vksa-itz-2026-08-04).</t>
         </is>
       </c>
       <c r="AF40" s="31" t="inlineStr">
@@ -12451,32 +12496,32 @@
       </c>
       <c r="AP40" s="24" t="inlineStr">
         <is>
-          <t>Malvinas Gaming</t>
+          <t>INTZ e-Sports</t>
         </is>
       </c>
       <c r="AQ40" s="24" t="inlineStr">
         <is>
-          <t>Malvinas Gaming</t>
+          <t>INTZ e-Sports</t>
         </is>
       </c>
       <c r="AR40" s="24" t="inlineStr">
         <is>
-          <t>Malvinas Gaming</t>
+          <t>INTZ e-Sports</t>
         </is>
       </c>
       <c r="AS40" s="24" t="inlineStr">
         <is>
-          <t>Maze Gaming</t>
+          <t>Vivo Keyd Stars Academy</t>
         </is>
       </c>
       <c r="AT40" s="24" t="inlineStr">
         <is>
-          <t>Maze Gaming</t>
+          <t>Vivo Keyd Stars Academy</t>
         </is>
       </c>
       <c r="AU40" s="24" t="inlineStr">
         <is>
-          <t>Maze Gaming</t>
+          <t>Vivo Keyd Stars Academy</t>
         </is>
       </c>
       <c r="AV40" s="24" t="n"/>
@@ -12494,7 +12539,7 @@
       </c>
       <c r="BA40" s="24" t="inlineStr">
         <is>
-          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
         </is>
       </c>
       <c r="BB40" s="24" t="inlineStr">
@@ -12509,7 +12554,7 @@
       </c>
       <c r="BD40" s="24" t="inlineStr">
         <is>
-          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
         </is>
       </c>
       <c r="BE40" s="24" t="inlineStr">
@@ -12529,7 +12574,7 @@
       </c>
       <c r="BH40" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:52.417381Z</t>
+          <t>2026-08-04T08:56:34.823771Z</t>
         </is>
       </c>
       <c r="BI40" s="24" t="inlineStr">
@@ -12539,13 +12584,13 @@
       </c>
       <c r="BJ40" s="25" t="n"/>
       <c r="BK40" s="26" t="n">
-        <v>-163</v>
+        <v>104</v>
       </c>
       <c r="BL40" s="27" t="n">
-        <v>1.613497</v>
+        <v>2.04</v>
       </c>
       <c r="BM40" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.490196</v>
       </c>
       <c r="BN40" s="28" t="n"/>
       <c r="BO40" s="28" t="n"/>
@@ -12576,7 +12621,8 @@
       <c r="CN40" s="24" t="n"/>
       <c r="CO40" s="24" t="n"/>
       <c r="CP40" s="24" t="n"/>
-      <c r="CQ40" s="24" t="inlineStr">
+      <c r="CQ40" s="24" t="n"/>
+      <c r="CR40" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -12585,12 +12631,12 @@
     <row r="41" ht="36" customHeight="1">
       <c r="A41" s="24" t="inlineStr">
         <is>
-          <t>442ac140fc9b4803</t>
+          <t>da93371c9e9d45ba</t>
         </is>
       </c>
       <c r="B41" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:56.302645Z</t>
+          <t>2026-08-04T08:56:56.469660Z</t>
         </is>
       </c>
       <c r="C41" s="24" t="inlineStr">
@@ -12600,7 +12646,7 @@
       </c>
       <c r="D41" s="24" t="inlineStr">
         <is>
-          <t>69144</t>
+          <t>69141</t>
         </is>
       </c>
       <c r="E41" s="24" t="inlineStr">
@@ -12610,12 +12656,12 @@
       </c>
       <c r="F41" s="24" t="inlineStr">
         <is>
-          <t>INTZ e-Sports</t>
+          <t>Vitality.Bee</t>
         </is>
       </c>
       <c r="G41" s="24" t="inlineStr">
         <is>
-          <t>Vivo Keyd Stars Academy</t>
+          <t>Karmine Corp Blue</t>
         </is>
       </c>
       <c r="H41" s="24" t="inlineStr">
@@ -12635,26 +12681,26 @@
         </is>
       </c>
       <c r="L41" s="26" t="n">
-        <v>-127</v>
+        <v>-186</v>
       </c>
       <c r="M41" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.537634</v>
       </c>
       <c r="N41" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.65035</v>
       </c>
       <c r="O41" s="28" t="n">
-        <v>0.591618</v>
+        <v>0.649994</v>
       </c>
       <c r="P41" s="28" t="n"/>
       <c r="Q41" s="28" t="n">
-        <v>0.032147</v>
+        <v>-0.000356</v>
       </c>
       <c r="R41" s="26" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="S41" s="29" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="T41" s="24" t="inlineStr">
         <is>
@@ -12677,7 +12723,7 @@
       <c r="AD41" s="24" t="n"/>
       <c r="AE41" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-lol-vksa-itz-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.6500 (market_slug=aec-lol-kcb-vitb-2026-08-04).</t>
         </is>
       </c>
       <c r="AF41" s="31" t="inlineStr">
@@ -12695,7 +12741,7 @@
       <c r="AJ41" s="31" t="n"/>
       <c r="AK41" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL41" s="26" t="n">
@@ -12703,47 +12749,47 @@
       </c>
       <c r="AM41" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN41" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO41" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP41" s="24" t="inlineStr">
         <is>
-          <t>INTZ e-Sports</t>
+          <t>Vitality.Bee</t>
         </is>
       </c>
       <c r="AQ41" s="24" t="inlineStr">
         <is>
-          <t>INTZ e-Sports</t>
+          <t>Vitality.Bee</t>
         </is>
       </c>
       <c r="AR41" s="24" t="inlineStr">
         <is>
-          <t>INTZ e-Sports</t>
+          <t>Vitality.Bee</t>
         </is>
       </c>
       <c r="AS41" s="24" t="inlineStr">
         <is>
-          <t>Vivo Keyd Stars Academy</t>
+          <t>Karmine Corp Blue</t>
         </is>
       </c>
       <c r="AT41" s="24" t="inlineStr">
         <is>
-          <t>Vivo Keyd Stars Academy</t>
+          <t>Karmine Corp Blue</t>
         </is>
       </c>
       <c r="AU41" s="24" t="inlineStr">
         <is>
-          <t>Vivo Keyd Stars Academy</t>
+          <t>Karmine Corp Blue</t>
         </is>
       </c>
       <c r="AV41" s="24" t="n"/>
@@ -12761,7 +12807,7 @@
       </c>
       <c r="BA41" s="24" t="inlineStr">
         <is>
-          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
         </is>
       </c>
       <c r="BB41" s="24" t="inlineStr">
@@ -12776,7 +12822,7 @@
       </c>
       <c r="BD41" s="24" t="inlineStr">
         <is>
-          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
         </is>
       </c>
       <c r="BE41" s="24" t="inlineStr">
@@ -12796,7 +12842,7 @@
       </c>
       <c r="BH41" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:53.026230Z</t>
+          <t>2026-08-04T08:56:35.473901Z</t>
         </is>
       </c>
       <c r="BI41" s="24" t="inlineStr">
@@ -12806,13 +12852,13 @@
       </c>
       <c r="BJ41" s="25" t="n"/>
       <c r="BK41" s="26" t="n">
-        <v>-127</v>
+        <v>-186</v>
       </c>
       <c r="BL41" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.537634</v>
       </c>
       <c r="BM41" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.65035</v>
       </c>
       <c r="BN41" s="28" t="n"/>
       <c r="BO41" s="28" t="n"/>
@@ -12843,31 +12889,32 @@
       <c r="CN41" s="24" t="n"/>
       <c r="CO41" s="24" t="n"/>
       <c r="CP41" s="24" t="n"/>
-      <c r="CQ41" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
+      <c r="CQ41" s="24" t="n"/>
+      <c r="CR41" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="42" ht="36" customHeight="1">
       <c r="A42" s="24" t="inlineStr">
         <is>
-          <t>c041d27567494ec6</t>
+          <t>1a9709a138004957</t>
         </is>
       </c>
       <c r="B42" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:56.302645Z</t>
+          <t>2026-08-04T08:56:56.469660Z</t>
         </is>
       </c>
       <c r="C42" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T20:00:00Z</t>
+          <t>2026-08-04T21:00:00Z</t>
         </is>
       </c>
       <c r="D42" s="24" t="inlineStr">
         <is>
-          <t>69141</t>
+          <t>69234</t>
         </is>
       </c>
       <c r="E42" s="24" t="inlineStr">
@@ -12877,12 +12924,12 @@
       </c>
       <c r="F42" s="24" t="inlineStr">
         <is>
-          <t>Vitality.Bee</t>
+          <t>Bubliki</t>
         </is>
       </c>
       <c r="G42" s="24" t="inlineStr">
         <is>
-          <t>Karmine Corp Blue</t>
+          <t>Francesinhas</t>
         </is>
       </c>
       <c r="H42" s="24" t="inlineStr">
@@ -12902,26 +12949,26 @@
         </is>
       </c>
       <c r="L42" s="26" t="n">
-        <v>-186</v>
+        <v>150</v>
       </c>
       <c r="M42" s="27" t="n">
-        <v>1.537634</v>
+        <v>2.5</v>
       </c>
       <c r="N42" s="28" t="n">
-        <v>0.65035</v>
+        <v>0.4</v>
       </c>
       <c r="O42" s="28" t="n">
-        <v>0.649994</v>
+        <v>0.51668</v>
       </c>
       <c r="P42" s="28" t="n"/>
       <c r="Q42" s="28" t="n">
-        <v>-0.000356</v>
+        <v>0.11668</v>
       </c>
       <c r="R42" s="26" t="n">
-        <v>20</v>
+        <v>78</v>
       </c>
       <c r="S42" s="29" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="T42" s="24" t="inlineStr">
         <is>
@@ -12944,7 +12991,7 @@
       <c r="AD42" s="24" t="n"/>
       <c r="AE42" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6500 (market_slug=aec-lol-kcb-vitb-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.4000 (market_slug=aec-lol-fcn-bub-2026-08-04).</t>
         </is>
       </c>
       <c r="AF42" s="31" t="inlineStr">
@@ -12985,32 +13032,32 @@
       </c>
       <c r="AP42" s="24" t="inlineStr">
         <is>
-          <t>Vitality.Bee</t>
+          <t>Bubliki</t>
         </is>
       </c>
       <c r="AQ42" s="24" t="inlineStr">
         <is>
-          <t>Vitality.Bee</t>
+          <t>Bubliki</t>
         </is>
       </c>
       <c r="AR42" s="24" t="inlineStr">
         <is>
-          <t>Vitality.Bee</t>
+          <t>Bubliki</t>
         </is>
       </c>
       <c r="AS42" s="24" t="inlineStr">
         <is>
-          <t>Karmine Corp Blue</t>
+          <t>Francesinhas</t>
         </is>
       </c>
       <c r="AT42" s="24" t="inlineStr">
         <is>
-          <t>Karmine Corp Blue</t>
+          <t>Francesinhas</t>
         </is>
       </c>
       <c r="AU42" s="24" t="inlineStr">
         <is>
-          <t>Karmine Corp Blue</t>
+          <t>Francesinhas</t>
         </is>
       </c>
       <c r="AV42" s="24" t="n"/>
@@ -13028,7 +13075,7 @@
       </c>
       <c r="BA42" s="24" t="inlineStr">
         <is>
-          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
         </is>
       </c>
       <c r="BB42" s="24" t="inlineStr">
@@ -13043,7 +13090,7 @@
       </c>
       <c r="BD42" s="24" t="inlineStr">
         <is>
-          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
         </is>
       </c>
       <c r="BE42" s="24" t="inlineStr">
@@ -13063,7 +13110,7 @@
       </c>
       <c r="BH42" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:53.530335Z</t>
+          <t>2026-08-04T08:56:35.928266Z</t>
         </is>
       </c>
       <c r="BI42" s="24" t="inlineStr">
@@ -13073,13 +13120,13 @@
       </c>
       <c r="BJ42" s="25" t="n"/>
       <c r="BK42" s="26" t="n">
-        <v>-186</v>
+        <v>150</v>
       </c>
       <c r="BL42" s="27" t="n">
-        <v>1.537634</v>
+        <v>2.5</v>
       </c>
       <c r="BM42" s="28" t="n">
-        <v>0.65035</v>
+        <v>0.4</v>
       </c>
       <c r="BN42" s="28" t="n"/>
       <c r="BO42" s="28" t="n"/>
@@ -13110,21 +13157,22 @@
       <c r="CN42" s="24" t="n"/>
       <c r="CO42" s="24" t="n"/>
       <c r="CP42" s="24" t="n"/>
-      <c r="CQ42" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
+      <c r="CQ42" s="24" t="n"/>
+      <c r="CR42" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="43" ht="36" customHeight="1">
       <c r="A43" s="24" t="inlineStr">
         <is>
-          <t>f6954aaa8b72488e</t>
+          <t>f3369b750e9a4754</t>
         </is>
       </c>
       <c r="B43" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:56.302645Z</t>
+          <t>2026-08-04T08:56:56.469660Z</t>
         </is>
       </c>
       <c r="C43" s="24" t="inlineStr">
@@ -13134,7 +13182,7 @@
       </c>
       <c r="D43" s="24" t="inlineStr">
         <is>
-          <t>69234</t>
+          <t>69233</t>
         </is>
       </c>
       <c r="E43" s="24" t="inlineStr">
@@ -13144,12 +13192,12 @@
       </c>
       <c r="F43" s="24" t="inlineStr">
         <is>
-          <t>Bubliki</t>
+          <t>Team Solid</t>
         </is>
       </c>
       <c r="G43" s="24" t="inlineStr">
         <is>
-          <t>Francesinhas</t>
+          <t>RED Academy</t>
         </is>
       </c>
       <c r="H43" s="24" t="inlineStr">
@@ -13169,26 +13217,26 @@
         </is>
       </c>
       <c r="L43" s="26" t="n">
-        <v>156</v>
+        <v>194</v>
       </c>
       <c r="M43" s="27" t="n">
-        <v>2.56</v>
+        <v>2.94</v>
       </c>
       <c r="N43" s="28" t="n">
-        <v>0.390625</v>
+        <v>0.340136</v>
       </c>
       <c r="O43" s="28" t="n">
-        <v>0.51668</v>
+        <v>0.5725</v>
       </c>
       <c r="P43" s="28" t="n"/>
       <c r="Q43" s="28" t="n">
-        <v>0.126055</v>
+        <v>0.232364</v>
       </c>
       <c r="R43" s="26" t="n">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="S43" s="29" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="T43" s="24" t="inlineStr">
         <is>
@@ -13211,7 +13259,7 @@
       <c r="AD43" s="24" t="n"/>
       <c r="AE43" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3900 (market_slug=aec-lol-fcn-bub-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.3400 (market_slug=aec-lol-reda-tse-2026-08-04).</t>
         </is>
       </c>
       <c r="AF43" s="31" t="inlineStr">
@@ -13229,7 +13277,7 @@
       <c r="AJ43" s="31" t="n"/>
       <c r="AK43" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL43" s="26" t="n">
@@ -13237,47 +13285,47 @@
       </c>
       <c r="AM43" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN43" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO43" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP43" s="24" t="inlineStr">
         <is>
-          <t>Bubliki</t>
+          <t>Team Solid</t>
         </is>
       </c>
       <c r="AQ43" s="24" t="inlineStr">
         <is>
-          <t>Bubliki</t>
+          <t>Team Solid</t>
         </is>
       </c>
       <c r="AR43" s="24" t="inlineStr">
         <is>
-          <t>Bubliki</t>
+          <t>Team Solid</t>
         </is>
       </c>
       <c r="AS43" s="24" t="inlineStr">
         <is>
-          <t>Francesinhas</t>
+          <t>RED Academy</t>
         </is>
       </c>
       <c r="AT43" s="24" t="inlineStr">
         <is>
-          <t>Francesinhas</t>
+          <t>RED Academy</t>
         </is>
       </c>
       <c r="AU43" s="24" t="inlineStr">
         <is>
-          <t>Francesinhas</t>
+          <t>RED Academy</t>
         </is>
       </c>
       <c r="AV43" s="24" t="n"/>
@@ -13295,7 +13343,7 @@
       </c>
       <c r="BA43" s="24" t="inlineStr">
         <is>
-          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
         </is>
       </c>
       <c r="BB43" s="24" t="inlineStr">
@@ -13310,7 +13358,7 @@
       </c>
       <c r="BD43" s="24" t="inlineStr">
         <is>
-          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
         </is>
       </c>
       <c r="BE43" s="24" t="inlineStr">
@@ -13330,7 +13378,7 @@
       </c>
       <c r="BH43" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:54.079734Z</t>
+          <t>2026-08-04T08:56:36.567095Z</t>
         </is>
       </c>
       <c r="BI43" s="24" t="inlineStr">
@@ -13340,13 +13388,13 @@
       </c>
       <c r="BJ43" s="25" t="n"/>
       <c r="BK43" s="26" t="n">
-        <v>156</v>
+        <v>194</v>
       </c>
       <c r="BL43" s="27" t="n">
-        <v>2.56</v>
+        <v>2.94</v>
       </c>
       <c r="BM43" s="28" t="n">
-        <v>0.390625</v>
+        <v>0.340136</v>
       </c>
       <c r="BN43" s="28" t="n"/>
       <c r="BO43" s="28" t="n"/>
@@ -13377,7 +13425,8 @@
       <c r="CN43" s="24" t="n"/>
       <c r="CO43" s="24" t="n"/>
       <c r="CP43" s="24" t="n"/>
-      <c r="CQ43" s="24" t="inlineStr">
+      <c r="CQ43" s="24" t="n"/>
+      <c r="CR43" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -13386,12 +13435,12 @@
     <row r="44" ht="36" customHeight="1">
       <c r="A44" s="24" t="inlineStr">
         <is>
-          <t>408f74d7de044559</t>
+          <t>93d9e90b7536488d</t>
         </is>
       </c>
       <c r="B44" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:56.302645Z</t>
+          <t>2026-08-04T08:56:56.469660Z</t>
         </is>
       </c>
       <c r="C44" s="24" t="inlineStr">
@@ -13436,23 +13485,23 @@
         </is>
       </c>
       <c r="L44" s="26" t="n">
-        <v>-150</v>
+        <v>-117</v>
       </c>
       <c r="M44" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.854701</v>
       </c>
       <c r="N44" s="28" t="n">
-        <v>0.6</v>
+        <v>0.539171</v>
       </c>
       <c r="O44" s="28" t="n">
         <v>0.604656</v>
       </c>
       <c r="P44" s="28" t="n"/>
       <c r="Q44" s="28" t="n">
-        <v>0.004656</v>
+        <v>0.065485</v>
       </c>
       <c r="R44" s="26" t="n">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="S44" s="29" t="n">
         <v>1.25</v>
@@ -13478,7 +13527,7 @@
       <c r="AD44" s="24" t="n"/>
       <c r="AE44" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-lol-7rex-rmd-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-lol-7rex-rmd-2026-08-04).</t>
         </is>
       </c>
       <c r="AF44" s="31" t="inlineStr">
@@ -13562,7 +13611,7 @@
       </c>
       <c r="BA44" s="24" t="inlineStr">
         <is>
-          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
         </is>
       </c>
       <c r="BB44" s="24" t="inlineStr">
@@ -13577,7 +13626,7 @@
       </c>
       <c r="BD44" s="24" t="inlineStr">
         <is>
-          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
         </is>
       </c>
       <c r="BE44" s="24" t="inlineStr">
@@ -13597,7 +13646,7 @@
       </c>
       <c r="BH44" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:55.187744Z</t>
+          <t>2026-08-04T08:56:37.194950Z</t>
         </is>
       </c>
       <c r="BI44" s="24" t="inlineStr">
@@ -13607,13 +13656,13 @@
       </c>
       <c r="BJ44" s="25" t="n"/>
       <c r="BK44" s="26" t="n">
-        <v>-150</v>
+        <v>-117</v>
       </c>
       <c r="BL44" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.854701</v>
       </c>
       <c r="BM44" s="28" t="n">
-        <v>0.6</v>
+        <v>0.539171</v>
       </c>
       <c r="BN44" s="28" t="n"/>
       <c r="BO44" s="28" t="n"/>
@@ -13644,7 +13693,8 @@
       <c r="CN44" s="24" t="n"/>
       <c r="CO44" s="24" t="n"/>
       <c r="CP44" s="24" t="n"/>
-      <c r="CQ44" s="24" t="inlineStr">
+      <c r="CQ44" s="24" t="n"/>
+      <c r="CR44" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -13653,12 +13703,12 @@
     <row r="45" ht="36" customHeight="1">
       <c r="A45" s="24" t="inlineStr">
         <is>
-          <t>e34cd34cab424131</t>
+          <t>b540df1859334978</t>
         </is>
       </c>
       <c r="B45" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:56.302645Z</t>
+          <t>2026-08-04T08:56:56.469660Z</t>
         </is>
       </c>
       <c r="C45" s="24" t="inlineStr">
@@ -13703,23 +13753,23 @@
         </is>
       </c>
       <c r="L45" s="26" t="n">
-        <v>-104</v>
+        <v>-127</v>
       </c>
       <c r="M45" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.787402</v>
       </c>
       <c r="N45" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="O45" s="28" t="n">
         <v>0.546359</v>
       </c>
       <c r="P45" s="28" t="n"/>
       <c r="Q45" s="28" t="n">
-        <v>0.036555</v>
+        <v>-0.013112</v>
       </c>
       <c r="R45" s="26" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="S45" s="29" t="n">
         <v>1</v>
@@ -13745,7 +13795,7 @@
       <c r="AD45" s="24" t="n"/>
       <c r="AE45" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-lol-kbm-pnga-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-lol-kbm-pnga-2026-08-04).</t>
         </is>
       </c>
       <c r="AF45" s="31" t="inlineStr">
@@ -13829,7 +13879,7 @@
       </c>
       <c r="BA45" s="24" t="inlineStr">
         <is>
-          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
         </is>
       </c>
       <c r="BB45" s="24" t="inlineStr">
@@ -13844,7 +13894,7 @@
       </c>
       <c r="BD45" s="24" t="inlineStr">
         <is>
-          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
         </is>
       </c>
       <c r="BE45" s="24" t="inlineStr">
@@ -13864,7 +13914,7 @@
       </c>
       <c r="BH45" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:55.701889Z</t>
+          <t>2026-08-04T08:56:37.736771Z</t>
         </is>
       </c>
       <c r="BI45" s="24" t="inlineStr">
@@ -13874,13 +13924,13 @@
       </c>
       <c r="BJ45" s="25" t="n"/>
       <c r="BK45" s="26" t="n">
-        <v>-104</v>
+        <v>-127</v>
       </c>
       <c r="BL45" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.787402</v>
       </c>
       <c r="BM45" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="BN45" s="28" t="n"/>
       <c r="BO45" s="28" t="n"/>
@@ -13911,31 +13961,32 @@
       <c r="CN45" s="24" t="n"/>
       <c r="CO45" s="24" t="n"/>
       <c r="CP45" s="24" t="n"/>
-      <c r="CQ45" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
+      <c r="CQ45" s="24" t="n"/>
+      <c r="CR45" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="46" ht="36" customHeight="1">
       <c r="A46" s="24" t="inlineStr">
         <is>
-          <t>bbe7069cec06486f</t>
+          <t>42b98355e0794604</t>
         </is>
       </c>
       <c r="B46" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:56.302645Z</t>
+          <t>2026-08-04T08:56:56.469660Z</t>
         </is>
       </c>
       <c r="C46" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T00:00:00Z</t>
+          <t>2026-08-05T05:00:00Z</t>
         </is>
       </c>
       <c r="D46" s="24" t="inlineStr">
         <is>
-          <t>69336</t>
+          <t>69507</t>
         </is>
       </c>
       <c r="E46" s="24" t="inlineStr">
@@ -13945,12 +13996,12 @@
       </c>
       <c r="F46" s="24" t="inlineStr">
         <is>
-          <t>Ei Nerd Esports</t>
+          <t>Nongshim Esports Academy</t>
         </is>
       </c>
       <c r="G46" s="24" t="inlineStr">
         <is>
-          <t>Estral Esports</t>
+          <t>Dplus KIA Challengers</t>
         </is>
       </c>
       <c r="H46" s="24" t="inlineStr">
@@ -13970,26 +14021,26 @@
         </is>
       </c>
       <c r="L46" s="26" t="n">
-        <v>-203</v>
+        <v>-138</v>
       </c>
       <c r="M46" s="27" t="n">
-        <v>1.492611</v>
+        <v>1.724638</v>
       </c>
       <c r="N46" s="28" t="n">
-        <v>0.669967</v>
+        <v>0.579832</v>
       </c>
       <c r="O46" s="28" t="n">
-        <v>0.74222</v>
+        <v>0.638913</v>
       </c>
       <c r="P46" s="28" t="n"/>
       <c r="Q46" s="28" t="n">
-        <v>0.072253</v>
+        <v>0.059081</v>
       </c>
       <c r="R46" s="26" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="S46" s="29" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="T46" s="24" t="inlineStr">
         <is>
@@ -14012,7 +14063,7 @@
       <c r="AD46" s="24" t="n"/>
       <c r="AE46" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-lol-est-nerd-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-lol-dkc-nsea-2026-08-05).</t>
         </is>
       </c>
       <c r="AF46" s="31" t="inlineStr">
@@ -14053,32 +14104,32 @@
       </c>
       <c r="AP46" s="24" t="inlineStr">
         <is>
-          <t>Ei Nerd Esports</t>
+          <t>Nongshim Esports Academy</t>
         </is>
       </c>
       <c r="AQ46" s="24" t="inlineStr">
         <is>
-          <t>Ei Nerd Esports</t>
+          <t>Nongshim Esports Academy</t>
         </is>
       </c>
       <c r="AR46" s="24" t="inlineStr">
         <is>
-          <t>Ei Nerd Esports</t>
+          <t>Nongshim Esports Academy</t>
         </is>
       </c>
       <c r="AS46" s="24" t="inlineStr">
         <is>
-          <t>Estral Esports</t>
+          <t>Dplus KIA Challengers</t>
         </is>
       </c>
       <c r="AT46" s="24" t="inlineStr">
         <is>
-          <t>Estral Esports</t>
+          <t>Dplus KIA Challengers</t>
         </is>
       </c>
       <c r="AU46" s="24" t="inlineStr">
         <is>
-          <t>Estral Esports</t>
+          <t>Dplus KIA Challengers</t>
         </is>
       </c>
       <c r="AV46" s="24" t="n"/>
@@ -14096,7 +14147,7 @@
       </c>
       <c r="BA46" s="24" t="inlineStr">
         <is>
-          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
         </is>
       </c>
       <c r="BB46" s="24" t="inlineStr">
@@ -14111,7 +14162,7 @@
       </c>
       <c r="BD46" s="24" t="inlineStr">
         <is>
-          <t>c0f2a708ccc94d5696faff9ca4ff9d58f719424636136d100ed9404e22178026</t>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
         </is>
       </c>
       <c r="BE46" s="24" t="inlineStr">
@@ -14131,7 +14182,7 @@
       </c>
       <c r="BH46" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:56.301588Z</t>
+          <t>2026-08-04T08:56:38.863908Z</t>
         </is>
       </c>
       <c r="BI46" s="24" t="inlineStr">
@@ -14141,13 +14192,13 @@
       </c>
       <c r="BJ46" s="25" t="n"/>
       <c r="BK46" s="26" t="n">
-        <v>-203</v>
+        <v>-138</v>
       </c>
       <c r="BL46" s="27" t="n">
-        <v>1.492611</v>
+        <v>1.724638</v>
       </c>
       <c r="BM46" s="28" t="n">
-        <v>0.669967</v>
+        <v>0.579832</v>
       </c>
       <c r="BN46" s="28" t="n"/>
       <c r="BO46" s="28" t="n"/>
@@ -14178,7 +14229,5368 @@
       <c r="CN46" s="24" t="n"/>
       <c r="CO46" s="24" t="n"/>
       <c r="CP46" s="24" t="n"/>
-      <c r="CQ46" s="24" t="inlineStr">
+      <c r="CQ46" s="24" t="n"/>
+      <c r="CR46" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="36" customHeight="1">
+      <c r="A47" s="24" t="inlineStr">
+        <is>
+          <t>2d74051d6d9e47d5</t>
+        </is>
+      </c>
+      <c r="B47" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:56.469660Z</t>
+        </is>
+      </c>
+      <c r="C47" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="D47" s="24" t="inlineStr">
+        <is>
+          <t>69506</t>
+        </is>
+      </c>
+      <c r="E47" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F47" s="24" t="inlineStr">
+        <is>
+          <t>Kiwoom DRX Challengers</t>
+        </is>
+      </c>
+      <c r="G47" s="24" t="inlineStr">
+        <is>
+          <t>BNK FearX Youth</t>
+        </is>
+      </c>
+      <c r="H47" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I47" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J47" s="25" t="n"/>
+      <c r="K47" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L47" s="26" t="n">
+        <v>144</v>
+      </c>
+      <c r="M47" s="27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="N47" s="28" t="n">
+        <v>0.409836</v>
+      </c>
+      <c r="O47" s="28" t="n">
+        <v>0.597302</v>
+      </c>
+      <c r="P47" s="28" t="n"/>
+      <c r="Q47" s="28" t="n">
+        <v>0.187466</v>
+      </c>
+      <c r="R47" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S47" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T47" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U47" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V47" s="24" t="n"/>
+      <c r="W47" s="26" t="n"/>
+      <c r="X47" s="26" t="n"/>
+      <c r="Y47" s="25" t="n"/>
+      <c r="Z47" s="26" t="n"/>
+      <c r="AA47" s="28" t="n"/>
+      <c r="AB47" s="28" t="n"/>
+      <c r="AC47" s="30" t="n"/>
+      <c r="AD47" s="24" t="n"/>
+      <c r="AE47" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4100 (market_slug=aec-lol-foxy-krxc-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF47" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG47" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH47" s="24" t="n"/>
+      <c r="AI47" s="31" t="n"/>
+      <c r="AJ47" s="31" t="n"/>
+      <c r="AK47" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL47" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM47" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN47" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO47" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP47" s="24" t="inlineStr">
+        <is>
+          <t>Kiwoom DRX Challengers</t>
+        </is>
+      </c>
+      <c r="AQ47" s="24" t="inlineStr">
+        <is>
+          <t>Kiwoom DRX Challengers</t>
+        </is>
+      </c>
+      <c r="AR47" s="24" t="inlineStr">
+        <is>
+          <t>Kiwoom DRX Challengers</t>
+        </is>
+      </c>
+      <c r="AS47" s="24" t="inlineStr">
+        <is>
+          <t>BNK FearX Youth</t>
+        </is>
+      </c>
+      <c r="AT47" s="24" t="inlineStr">
+        <is>
+          <t>BNK FearX Youth</t>
+        </is>
+      </c>
+      <c r="AU47" s="24" t="inlineStr">
+        <is>
+          <t>BNK FearX Youth</t>
+        </is>
+      </c>
+      <c r="AV47" s="24" t="n"/>
+      <c r="AW47" s="24" t="n"/>
+      <c r="AX47" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY47" s="24" t="n"/>
+      <c r="AZ47" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA47" s="24" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="BB47" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC47" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD47" s="24" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="BE47" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF47" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG47" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH47" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:39.338315Z</t>
+        </is>
+      </c>
+      <c r="BI47" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ47" s="25" t="n"/>
+      <c r="BK47" s="26" t="n">
+        <v>144</v>
+      </c>
+      <c r="BL47" s="27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BM47" s="28" t="n">
+        <v>0.409836</v>
+      </c>
+      <c r="BN47" s="28" t="n"/>
+      <c r="BO47" s="28" t="n"/>
+      <c r="BP47" s="25" t="n"/>
+      <c r="BQ47" s="27" t="n"/>
+      <c r="BR47" s="28" t="n"/>
+      <c r="BS47" s="28" t="n"/>
+      <c r="BT47" s="28" t="n"/>
+      <c r="BU47" s="25" t="n"/>
+      <c r="BV47" s="29" t="n"/>
+      <c r="BW47" s="24" t="n"/>
+      <c r="BX47" s="30" t="n"/>
+      <c r="BY47" s="27" t="n"/>
+      <c r="BZ47" s="24" t="n"/>
+      <c r="CA47" s="31" t="n"/>
+      <c r="CB47" s="24" t="n"/>
+      <c r="CC47" s="24" t="n"/>
+      <c r="CD47" s="24" t="n"/>
+      <c r="CE47" s="24" t="n"/>
+      <c r="CF47" s="24" t="n"/>
+      <c r="CG47" s="24" t="n"/>
+      <c r="CH47" s="24" t="n"/>
+      <c r="CI47" s="24" t="n"/>
+      <c r="CJ47" s="24" t="n"/>
+      <c r="CK47" s="24" t="n"/>
+      <c r="CL47" s="24" t="n"/>
+      <c r="CM47" s="24" t="n"/>
+      <c r="CN47" s="24" t="n"/>
+      <c r="CO47" s="24" t="n"/>
+      <c r="CP47" s="24" t="n"/>
+      <c r="CQ47" s="24" t="n"/>
+      <c r="CR47" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="36" customHeight="1">
+      <c r="A48" s="24" t="inlineStr">
+        <is>
+          <t>42cf1b2478204e12</t>
+        </is>
+      </c>
+      <c r="B48" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:56.469660Z</t>
+        </is>
+      </c>
+      <c r="C48" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="D48" s="24" t="inlineStr">
+        <is>
+          <t>69512</t>
+        </is>
+      </c>
+      <c r="E48" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F48" s="24" t="inlineStr">
+        <is>
+          <t>Nongshim Red Force</t>
+        </is>
+      </c>
+      <c r="G48" s="24" t="inlineStr">
+        <is>
+          <t>HANJIN BRION</t>
+        </is>
+      </c>
+      <c r="H48" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I48" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J48" s="25" t="n"/>
+      <c r="K48" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L48" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="M48" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="N48" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="O48" s="28" t="n">
+        <v>0.739915</v>
+      </c>
+      <c r="P48" s="28" t="n"/>
+      <c r="Q48" s="28" t="n">
+        <v>0.049513</v>
+      </c>
+      <c r="R48" s="26" t="n">
+        <v>45</v>
+      </c>
+      <c r="S48" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T48" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U48" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V48" s="24" t="n"/>
+      <c r="W48" s="26" t="n"/>
+      <c r="X48" s="26" t="n"/>
+      <c r="Y48" s="25" t="n"/>
+      <c r="Z48" s="26" t="n"/>
+      <c r="AA48" s="28" t="n"/>
+      <c r="AB48" s="28" t="n"/>
+      <c r="AC48" s="30" t="n"/>
+      <c r="AD48" s="24" t="n"/>
+      <c r="AE48" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-lol-bro-ns-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF48" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG48" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH48" s="24" t="n"/>
+      <c r="AI48" s="31" t="n"/>
+      <c r="AJ48" s="31" t="n"/>
+      <c r="AK48" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL48" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM48" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN48" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO48" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP48" s="24" t="inlineStr">
+        <is>
+          <t>Nongshim Red Force</t>
+        </is>
+      </c>
+      <c r="AQ48" s="24" t="inlineStr">
+        <is>
+          <t>Nongshim Red Force</t>
+        </is>
+      </c>
+      <c r="AR48" s="24" t="inlineStr">
+        <is>
+          <t>Nongshim Red Force</t>
+        </is>
+      </c>
+      <c r="AS48" s="24" t="inlineStr">
+        <is>
+          <t>HANJIN BRION</t>
+        </is>
+      </c>
+      <c r="AT48" s="24" t="inlineStr">
+        <is>
+          <t>HANJIN BRION</t>
+        </is>
+      </c>
+      <c r="AU48" s="24" t="inlineStr">
+        <is>
+          <t>HANJIN BRION</t>
+        </is>
+      </c>
+      <c r="AV48" s="24" t="n"/>
+      <c r="AW48" s="24" t="n"/>
+      <c r="AX48" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY48" s="24" t="n"/>
+      <c r="AZ48" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA48" s="24" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="BB48" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC48" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD48" s="24" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="BE48" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF48" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG48" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH48" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:39.828051Z</t>
+        </is>
+      </c>
+      <c r="BI48" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ48" s="25" t="n"/>
+      <c r="BK48" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="BL48" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="BM48" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="BN48" s="28" t="n"/>
+      <c r="BO48" s="28" t="n"/>
+      <c r="BP48" s="25" t="n"/>
+      <c r="BQ48" s="27" t="n"/>
+      <c r="BR48" s="28" t="n"/>
+      <c r="BS48" s="28" t="n"/>
+      <c r="BT48" s="28" t="n"/>
+      <c r="BU48" s="25" t="n"/>
+      <c r="BV48" s="29" t="n"/>
+      <c r="BW48" s="24" t="n"/>
+      <c r="BX48" s="30" t="n"/>
+      <c r="BY48" s="27" t="n"/>
+      <c r="BZ48" s="24" t="n"/>
+      <c r="CA48" s="31" t="n"/>
+      <c r="CB48" s="24" t="n"/>
+      <c r="CC48" s="24" t="n"/>
+      <c r="CD48" s="24" t="n"/>
+      <c r="CE48" s="24" t="n"/>
+      <c r="CF48" s="24" t="n"/>
+      <c r="CG48" s="24" t="n"/>
+      <c r="CH48" s="24" t="n"/>
+      <c r="CI48" s="24" t="n"/>
+      <c r="CJ48" s="24" t="n"/>
+      <c r="CK48" s="24" t="n"/>
+      <c r="CL48" s="24" t="n"/>
+      <c r="CM48" s="24" t="n"/>
+      <c r="CN48" s="24" t="n"/>
+      <c r="CO48" s="24" t="n"/>
+      <c r="CP48" s="24" t="n"/>
+      <c r="CQ48" s="24" t="n"/>
+      <c r="CR48" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="36" customHeight="1">
+      <c r="A49" s="24" t="inlineStr">
+        <is>
+          <t>0a7b6184cad24890</t>
+        </is>
+      </c>
+      <c r="B49" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:56.469660Z</t>
+        </is>
+      </c>
+      <c r="C49" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="D49" s="24" t="inlineStr">
+        <is>
+          <t>69511</t>
+        </is>
+      </c>
+      <c r="E49" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F49" s="24" t="inlineStr">
+        <is>
+          <t>New Meta</t>
+        </is>
+      </c>
+      <c r="G49" s="24" t="inlineStr">
+        <is>
+          <t>FENNEL</t>
+        </is>
+      </c>
+      <c r="H49" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I49" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J49" s="25" t="n"/>
+      <c r="K49" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L49" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="M49" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="N49" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="O49" s="28" t="n">
+        <v>0.699554</v>
+      </c>
+      <c r="P49" s="28" t="n"/>
+      <c r="Q49" s="28" t="n">
+        <v>0.090179</v>
+      </c>
+      <c r="R49" s="26" t="n">
+        <v>65</v>
+      </c>
+      <c r="S49" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T49" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U49" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V49" s="24" t="n"/>
+      <c r="W49" s="26" t="n"/>
+      <c r="X49" s="26" t="n"/>
+      <c r="Y49" s="25" t="n"/>
+      <c r="Z49" s="26" t="n"/>
+      <c r="AA49" s="28" t="n"/>
+      <c r="AB49" s="28" t="n"/>
+      <c r="AC49" s="30" t="n"/>
+      <c r="AD49" s="24" t="n"/>
+      <c r="AE49" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-lol-fnl-nme-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF49" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG49" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH49" s="24" t="n"/>
+      <c r="AI49" s="31" t="n"/>
+      <c r="AJ49" s="31" t="n"/>
+      <c r="AK49" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL49" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM49" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN49" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO49" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP49" s="24" t="inlineStr">
+        <is>
+          <t>New Meta</t>
+        </is>
+      </c>
+      <c r="AQ49" s="24" t="inlineStr">
+        <is>
+          <t>New Meta</t>
+        </is>
+      </c>
+      <c r="AR49" s="24" t="inlineStr">
+        <is>
+          <t>New Meta</t>
+        </is>
+      </c>
+      <c r="AS49" s="24" t="inlineStr">
+        <is>
+          <t>FENNEL</t>
+        </is>
+      </c>
+      <c r="AT49" s="24" t="inlineStr">
+        <is>
+          <t>FENNEL</t>
+        </is>
+      </c>
+      <c r="AU49" s="24" t="inlineStr">
+        <is>
+          <t>FENNEL</t>
+        </is>
+      </c>
+      <c r="AV49" s="24" t="n"/>
+      <c r="AW49" s="24" t="n"/>
+      <c r="AX49" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY49" s="24" t="n"/>
+      <c r="AZ49" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA49" s="24" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="BB49" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC49" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD49" s="24" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="BE49" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF49" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG49" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH49" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:40.294698Z</t>
+        </is>
+      </c>
+      <c r="BI49" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ49" s="25" t="n"/>
+      <c r="BK49" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="BL49" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="BM49" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="BN49" s="28" t="n"/>
+      <c r="BO49" s="28" t="n"/>
+      <c r="BP49" s="25" t="n"/>
+      <c r="BQ49" s="27" t="n"/>
+      <c r="BR49" s="28" t="n"/>
+      <c r="BS49" s="28" t="n"/>
+      <c r="BT49" s="28" t="n"/>
+      <c r="BU49" s="25" t="n"/>
+      <c r="BV49" s="29" t="n"/>
+      <c r="BW49" s="24" t="n"/>
+      <c r="BX49" s="30" t="n"/>
+      <c r="BY49" s="27" t="n"/>
+      <c r="BZ49" s="24" t="n"/>
+      <c r="CA49" s="31" t="n"/>
+      <c r="CB49" s="24" t="n"/>
+      <c r="CC49" s="24" t="n"/>
+      <c r="CD49" s="24" t="n"/>
+      <c r="CE49" s="24" t="n"/>
+      <c r="CF49" s="24" t="n"/>
+      <c r="CG49" s="24" t="n"/>
+      <c r="CH49" s="24" t="n"/>
+      <c r="CI49" s="24" t="n"/>
+      <c r="CJ49" s="24" t="n"/>
+      <c r="CK49" s="24" t="n"/>
+      <c r="CL49" s="24" t="n"/>
+      <c r="CM49" s="24" t="n"/>
+      <c r="CN49" s="24" t="n"/>
+      <c r="CO49" s="24" t="n"/>
+      <c r="CP49" s="24" t="n"/>
+      <c r="CQ49" s="24" t="n"/>
+      <c r="CR49" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="36" customHeight="1">
+      <c r="A50" s="24" t="inlineStr">
+        <is>
+          <t>c69371ca01dc4f85</t>
+        </is>
+      </c>
+      <c r="B50" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:56.469660Z</t>
+        </is>
+      </c>
+      <c r="C50" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="D50" s="24" t="inlineStr">
+        <is>
+          <t>69539</t>
+        </is>
+      </c>
+      <c r="E50" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F50" s="24" t="inlineStr">
+        <is>
+          <t>Gen.G</t>
+        </is>
+      </c>
+      <c r="G50" s="24" t="inlineStr">
+        <is>
+          <t>Hanwha Life Esports</t>
+        </is>
+      </c>
+      <c r="H50" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I50" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J50" s="25" t="n"/>
+      <c r="K50" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L50" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="M50" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="N50" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="O50" s="28" t="n">
+        <v>0.637225</v>
+      </c>
+      <c r="P50" s="28" t="n"/>
+      <c r="Q50" s="28" t="n">
+        <v>0.077754</v>
+      </c>
+      <c r="R50" s="26" t="n">
+        <v>59</v>
+      </c>
+      <c r="S50" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T50" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U50" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V50" s="24" t="n"/>
+      <c r="W50" s="26" t="n"/>
+      <c r="X50" s="26" t="n"/>
+      <c r="Y50" s="25" t="n"/>
+      <c r="Z50" s="26" t="n"/>
+      <c r="AA50" s="28" t="n"/>
+      <c r="AB50" s="28" t="n"/>
+      <c r="AC50" s="30" t="n"/>
+      <c r="AD50" s="24" t="n"/>
+      <c r="AE50" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-lol-hle-gen-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF50" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG50" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH50" s="24" t="n"/>
+      <c r="AI50" s="31" t="n"/>
+      <c r="AJ50" s="31" t="n"/>
+      <c r="AK50" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL50" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM50" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN50" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO50" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP50" s="24" t="inlineStr">
+        <is>
+          <t>Gen.G</t>
+        </is>
+      </c>
+      <c r="AQ50" s="24" t="inlineStr">
+        <is>
+          <t>Gen.G</t>
+        </is>
+      </c>
+      <c r="AR50" s="24" t="inlineStr">
+        <is>
+          <t>Gen.G</t>
+        </is>
+      </c>
+      <c r="AS50" s="24" t="inlineStr">
+        <is>
+          <t>Hanwha Life Esports</t>
+        </is>
+      </c>
+      <c r="AT50" s="24" t="inlineStr">
+        <is>
+          <t>Hanwha Life Esports</t>
+        </is>
+      </c>
+      <c r="AU50" s="24" t="inlineStr">
+        <is>
+          <t>Hanwha Life Esports</t>
+        </is>
+      </c>
+      <c r="AV50" s="24" t="n"/>
+      <c r="AW50" s="24" t="n"/>
+      <c r="AX50" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY50" s="24" t="n"/>
+      <c r="AZ50" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA50" s="24" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="BB50" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC50" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD50" s="24" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="BE50" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF50" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG50" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH50" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:41.252699Z</t>
+        </is>
+      </c>
+      <c r="BI50" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ50" s="25" t="n"/>
+      <c r="BK50" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="BL50" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BM50" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="BN50" s="28" t="n"/>
+      <c r="BO50" s="28" t="n"/>
+      <c r="BP50" s="25" t="n"/>
+      <c r="BQ50" s="27" t="n"/>
+      <c r="BR50" s="28" t="n"/>
+      <c r="BS50" s="28" t="n"/>
+      <c r="BT50" s="28" t="n"/>
+      <c r="BU50" s="25" t="n"/>
+      <c r="BV50" s="29" t="n"/>
+      <c r="BW50" s="24" t="n"/>
+      <c r="BX50" s="30" t="n"/>
+      <c r="BY50" s="27" t="n"/>
+      <c r="BZ50" s="24" t="n"/>
+      <c r="CA50" s="31" t="n"/>
+      <c r="CB50" s="24" t="n"/>
+      <c r="CC50" s="24" t="n"/>
+      <c r="CD50" s="24" t="n"/>
+      <c r="CE50" s="24" t="n"/>
+      <c r="CF50" s="24" t="n"/>
+      <c r="CG50" s="24" t="n"/>
+      <c r="CH50" s="24" t="n"/>
+      <c r="CI50" s="24" t="n"/>
+      <c r="CJ50" s="24" t="n"/>
+      <c r="CK50" s="24" t="n"/>
+      <c r="CL50" s="24" t="n"/>
+      <c r="CM50" s="24" t="n"/>
+      <c r="CN50" s="24" t="n"/>
+      <c r="CO50" s="24" t="n"/>
+      <c r="CP50" s="24" t="n"/>
+      <c r="CQ50" s="24" t="n"/>
+      <c r="CR50" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="36" customHeight="1">
+      <c r="A51" s="24" t="inlineStr">
+        <is>
+          <t>cd1900cb34ba475d</t>
+        </is>
+      </c>
+      <c r="B51" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:56.469660Z</t>
+        </is>
+      </c>
+      <c r="C51" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="D51" s="24" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="E51" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F51" s="24" t="inlineStr">
+        <is>
+          <t>Galions</t>
+        </is>
+      </c>
+      <c r="G51" s="24" t="inlineStr">
+        <is>
+          <t>TLN Pirates</t>
+        </is>
+      </c>
+      <c r="H51" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I51" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J51" s="25" t="n"/>
+      <c r="K51" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L51" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="M51" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="N51" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="O51" s="28" t="n">
+        <v>0.665588</v>
+      </c>
+      <c r="P51" s="28" t="n"/>
+      <c r="Q51" s="28" t="n">
+        <v>0.045816</v>
+      </c>
+      <c r="R51" s="26" t="n">
+        <v>43</v>
+      </c>
+      <c r="S51" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T51" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U51" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V51" s="24" t="n"/>
+      <c r="W51" s="26" t="n"/>
+      <c r="X51" s="26" t="n"/>
+      <c r="Y51" s="25" t="n"/>
+      <c r="Z51" s="26" t="n"/>
+      <c r="AA51" s="28" t="n"/>
+      <c r="AB51" s="28" t="n"/>
+      <c r="AC51" s="30" t="n"/>
+      <c r="AD51" s="24" t="n"/>
+      <c r="AE51" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-lol-tlnp-gal-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF51" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG51" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH51" s="24" t="n"/>
+      <c r="AI51" s="31" t="n"/>
+      <c r="AJ51" s="31" t="n"/>
+      <c r="AK51" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL51" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM51" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN51" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO51" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP51" s="24" t="inlineStr">
+        <is>
+          <t>Galions</t>
+        </is>
+      </c>
+      <c r="AQ51" s="24" t="inlineStr">
+        <is>
+          <t>Galions</t>
+        </is>
+      </c>
+      <c r="AR51" s="24" t="inlineStr">
+        <is>
+          <t>Galions</t>
+        </is>
+      </c>
+      <c r="AS51" s="24" t="inlineStr">
+        <is>
+          <t>TLN Pirates</t>
+        </is>
+      </c>
+      <c r="AT51" s="24" t="inlineStr">
+        <is>
+          <t>TLN Pirates</t>
+        </is>
+      </c>
+      <c r="AU51" s="24" t="inlineStr">
+        <is>
+          <t>TLN Pirates</t>
+        </is>
+      </c>
+      <c r="AV51" s="24" t="n"/>
+      <c r="AW51" s="24" t="n"/>
+      <c r="AX51" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY51" s="24" t="n"/>
+      <c r="AZ51" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA51" s="24" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="BB51" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC51" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD51" s="24" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="BE51" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF51" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG51" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH51" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:44.546269Z</t>
+        </is>
+      </c>
+      <c r="BI51" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ51" s="25" t="n"/>
+      <c r="BK51" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="BL51" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="BM51" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="BN51" s="28" t="n"/>
+      <c r="BO51" s="28" t="n"/>
+      <c r="BP51" s="25" t="n"/>
+      <c r="BQ51" s="27" t="n"/>
+      <c r="BR51" s="28" t="n"/>
+      <c r="BS51" s="28" t="n"/>
+      <c r="BT51" s="28" t="n"/>
+      <c r="BU51" s="25" t="n"/>
+      <c r="BV51" s="29" t="n"/>
+      <c r="BW51" s="24" t="n"/>
+      <c r="BX51" s="30" t="n"/>
+      <c r="BY51" s="27" t="n"/>
+      <c r="BZ51" s="24" t="n"/>
+      <c r="CA51" s="31" t="n"/>
+      <c r="CB51" s="24" t="n"/>
+      <c r="CC51" s="24" t="n"/>
+      <c r="CD51" s="24" t="n"/>
+      <c r="CE51" s="24" t="n"/>
+      <c r="CF51" s="24" t="n"/>
+      <c r="CG51" s="24" t="n"/>
+      <c r="CH51" s="24" t="n"/>
+      <c r="CI51" s="24" t="n"/>
+      <c r="CJ51" s="24" t="n"/>
+      <c r="CK51" s="24" t="n"/>
+      <c r="CL51" s="24" t="n"/>
+      <c r="CM51" s="24" t="n"/>
+      <c r="CN51" s="24" t="n"/>
+      <c r="CO51" s="24" t="n"/>
+      <c r="CP51" s="24" t="n"/>
+      <c r="CQ51" s="24" t="n"/>
+      <c r="CR51" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="36" customHeight="1">
+      <c r="A52" s="24" t="inlineStr">
+        <is>
+          <t>308b0ca16aa84142</t>
+        </is>
+      </c>
+      <c r="B52" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:56.469660Z</t>
+        </is>
+      </c>
+      <c r="C52" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="D52" s="24" t="inlineStr">
+        <is>
+          <t>69871</t>
+        </is>
+      </c>
+      <c r="E52" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F52" s="24" t="inlineStr">
+        <is>
+          <t>Kaufland Hangry Knights</t>
+        </is>
+      </c>
+      <c r="G52" s="24" t="inlineStr">
+        <is>
+          <t>TeamOrangeGaming</t>
+        </is>
+      </c>
+      <c r="H52" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I52" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J52" s="25" t="n"/>
+      <c r="K52" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L52" s="26" t="n">
+        <v>127</v>
+      </c>
+      <c r="M52" s="27" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="N52" s="28" t="n">
+        <v>0.440529</v>
+      </c>
+      <c r="O52" s="28" t="n">
+        <v>0.561203</v>
+      </c>
+      <c r="P52" s="28" t="n"/>
+      <c r="Q52" s="28" t="n">
+        <v>0.120674</v>
+      </c>
+      <c r="R52" s="26" t="n">
+        <v>80</v>
+      </c>
+      <c r="S52" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T52" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U52" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V52" s="24" t="n"/>
+      <c r="W52" s="26" t="n"/>
+      <c r="X52" s="26" t="n"/>
+      <c r="Y52" s="25" t="n"/>
+      <c r="Z52" s="26" t="n"/>
+      <c r="AA52" s="28" t="n"/>
+      <c r="AB52" s="28" t="n"/>
+      <c r="AC52" s="30" t="n"/>
+      <c r="AD52" s="24" t="n"/>
+      <c r="AE52" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-lol-tog-khk-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF52" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG52" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH52" s="24" t="n"/>
+      <c r="AI52" s="31" t="n"/>
+      <c r="AJ52" s="31" t="n"/>
+      <c r="AK52" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL52" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM52" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN52" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO52" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP52" s="24" t="inlineStr">
+        <is>
+          <t>Kaufland Hangry Knights</t>
+        </is>
+      </c>
+      <c r="AQ52" s="24" t="inlineStr">
+        <is>
+          <t>Kaufland Hangry Knights</t>
+        </is>
+      </c>
+      <c r="AR52" s="24" t="inlineStr">
+        <is>
+          <t>Kaufland Hangry Knights</t>
+        </is>
+      </c>
+      <c r="AS52" s="24" t="inlineStr">
+        <is>
+          <t>TeamOrangeGaming</t>
+        </is>
+      </c>
+      <c r="AT52" s="24" t="inlineStr">
+        <is>
+          <t>TeamOrangeGaming</t>
+        </is>
+      </c>
+      <c r="AU52" s="24" t="inlineStr">
+        <is>
+          <t>TeamOrangeGaming</t>
+        </is>
+      </c>
+      <c r="AV52" s="24" t="n"/>
+      <c r="AW52" s="24" t="n"/>
+      <c r="AX52" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY52" s="24" t="n"/>
+      <c r="AZ52" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA52" s="24" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="BB52" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC52" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD52" s="24" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="BE52" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF52" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG52" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH52" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:46.445811Z</t>
+        </is>
+      </c>
+      <c r="BI52" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ52" s="25" t="n"/>
+      <c r="BK52" s="26" t="n">
+        <v>127</v>
+      </c>
+      <c r="BL52" s="27" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BM52" s="28" t="n">
+        <v>0.440529</v>
+      </c>
+      <c r="BN52" s="28" t="n"/>
+      <c r="BO52" s="28" t="n"/>
+      <c r="BP52" s="25" t="n"/>
+      <c r="BQ52" s="27" t="n"/>
+      <c r="BR52" s="28" t="n"/>
+      <c r="BS52" s="28" t="n"/>
+      <c r="BT52" s="28" t="n"/>
+      <c r="BU52" s="25" t="n"/>
+      <c r="BV52" s="29" t="n"/>
+      <c r="BW52" s="24" t="n"/>
+      <c r="BX52" s="30" t="n"/>
+      <c r="BY52" s="27" t="n"/>
+      <c r="BZ52" s="24" t="n"/>
+      <c r="CA52" s="31" t="n"/>
+      <c r="CB52" s="24" t="n"/>
+      <c r="CC52" s="24" t="n"/>
+      <c r="CD52" s="24" t="n"/>
+      <c r="CE52" s="24" t="n"/>
+      <c r="CF52" s="24" t="n"/>
+      <c r="CG52" s="24" t="n"/>
+      <c r="CH52" s="24" t="n"/>
+      <c r="CI52" s="24" t="n"/>
+      <c r="CJ52" s="24" t="n"/>
+      <c r="CK52" s="24" t="n"/>
+      <c r="CL52" s="24" t="n"/>
+      <c r="CM52" s="24" t="n"/>
+      <c r="CN52" s="24" t="n"/>
+      <c r="CO52" s="24" t="n"/>
+      <c r="CP52" s="24" t="n"/>
+      <c r="CQ52" s="24" t="n"/>
+      <c r="CR52" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="36" customHeight="1">
+      <c r="A53" s="24" t="inlineStr">
+        <is>
+          <t>632f853d2bcc4ef8</t>
+        </is>
+      </c>
+      <c r="B53" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:56.469660Z</t>
+        </is>
+      </c>
+      <c r="C53" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="D53" s="24" t="inlineStr">
+        <is>
+          <t>70569</t>
+        </is>
+      </c>
+      <c r="E53" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F53" s="24" t="inlineStr">
+        <is>
+          <t>devils.one inStreamly</t>
+        </is>
+      </c>
+      <c r="G53" s="24" t="inlineStr">
+        <is>
+          <t>BOMBA Team</t>
+        </is>
+      </c>
+      <c r="H53" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I53" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J53" s="25" t="n"/>
+      <c r="K53" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L53" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="M53" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="N53" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="O53" s="28" t="n">
+        <v>0.832591</v>
+      </c>
+      <c r="P53" s="28" t="n"/>
+      <c r="Q53" s="28" t="n">
+        <v>0.242427</v>
+      </c>
+      <c r="R53" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S53" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T53" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U53" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V53" s="24" t="n"/>
+      <c r="W53" s="26" t="n"/>
+      <c r="X53" s="26" t="n"/>
+      <c r="Y53" s="25" t="n"/>
+      <c r="Z53" s="26" t="n"/>
+      <c r="AA53" s="28" t="n"/>
+      <c r="AB53" s="28" t="n"/>
+      <c r="AC53" s="30" t="n"/>
+      <c r="AD53" s="24" t="n"/>
+      <c r="AE53" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-lol-boom-dv1-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF53" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG53" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH53" s="24" t="n"/>
+      <c r="AI53" s="31" t="n"/>
+      <c r="AJ53" s="31" t="n"/>
+      <c r="AK53" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL53" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM53" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN53" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO53" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP53" s="24" t="inlineStr">
+        <is>
+          <t>devils.one inStreamly</t>
+        </is>
+      </c>
+      <c r="AQ53" s="24" t="inlineStr">
+        <is>
+          <t>devils.one inStreamly</t>
+        </is>
+      </c>
+      <c r="AR53" s="24" t="inlineStr">
+        <is>
+          <t>devils.one inStreamly</t>
+        </is>
+      </c>
+      <c r="AS53" s="24" t="inlineStr">
+        <is>
+          <t>BOMBA Team</t>
+        </is>
+      </c>
+      <c r="AT53" s="24" t="inlineStr">
+        <is>
+          <t>BOMBA Team</t>
+        </is>
+      </c>
+      <c r="AU53" s="24" t="inlineStr">
+        <is>
+          <t>BOMBA Team</t>
+        </is>
+      </c>
+      <c r="AV53" s="24" t="n"/>
+      <c r="AW53" s="24" t="n"/>
+      <c r="AX53" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY53" s="24" t="n"/>
+      <c r="AZ53" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA53" s="24" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="BB53" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC53" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD53" s="24" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="BE53" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF53" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG53" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH53" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:47.442405Z</t>
+        </is>
+      </c>
+      <c r="BI53" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ53" s="25" t="n"/>
+      <c r="BK53" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="BL53" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="BM53" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="BN53" s="28" t="n"/>
+      <c r="BO53" s="28" t="n"/>
+      <c r="BP53" s="25" t="n"/>
+      <c r="BQ53" s="27" t="n"/>
+      <c r="BR53" s="28" t="n"/>
+      <c r="BS53" s="28" t="n"/>
+      <c r="BT53" s="28" t="n"/>
+      <c r="BU53" s="25" t="n"/>
+      <c r="BV53" s="29" t="n"/>
+      <c r="BW53" s="24" t="n"/>
+      <c r="BX53" s="30" t="n"/>
+      <c r="BY53" s="27" t="n"/>
+      <c r="BZ53" s="24" t="n"/>
+      <c r="CA53" s="31" t="n"/>
+      <c r="CB53" s="24" t="n"/>
+      <c r="CC53" s="24" t="n"/>
+      <c r="CD53" s="24" t="n"/>
+      <c r="CE53" s="24" t="n"/>
+      <c r="CF53" s="24" t="n"/>
+      <c r="CG53" s="24" t="n"/>
+      <c r="CH53" s="24" t="n"/>
+      <c r="CI53" s="24" t="n"/>
+      <c r="CJ53" s="24" t="n"/>
+      <c r="CK53" s="24" t="n"/>
+      <c r="CL53" s="24" t="n"/>
+      <c r="CM53" s="24" t="n"/>
+      <c r="CN53" s="24" t="n"/>
+      <c r="CO53" s="24" t="n"/>
+      <c r="CP53" s="24" t="n"/>
+      <c r="CQ53" s="24" t="n"/>
+      <c r="CR53" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="36" customHeight="1">
+      <c r="A54" s="24" t="inlineStr">
+        <is>
+          <t>40ea7f5fa25e41c9</t>
+        </is>
+      </c>
+      <c r="B54" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:56.469660Z</t>
+        </is>
+      </c>
+      <c r="C54" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:30:00Z</t>
+        </is>
+      </c>
+      <c r="D54" s="24" t="inlineStr">
+        <is>
+          <t>69931</t>
+        </is>
+      </c>
+      <c r="E54" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F54" s="24" t="inlineStr">
+        <is>
+          <t>⁠Movistar KOI Fénix</t>
+        </is>
+      </c>
+      <c r="G54" s="24" t="inlineStr">
+        <is>
+          <t>UCAM Esports Club</t>
+        </is>
+      </c>
+      <c r="H54" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I54" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J54" s="25" t="n"/>
+      <c r="K54" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L54" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="M54" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="N54" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O54" s="28" t="n">
+        <v>0.577055</v>
+      </c>
+      <c r="P54" s="28" t="n"/>
+      <c r="Q54" s="28" t="n">
+        <v>0.077055</v>
+      </c>
+      <c r="R54" s="26" t="n">
+        <v>59</v>
+      </c>
+      <c r="S54" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T54" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U54" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V54" s="24" t="n"/>
+      <c r="W54" s="26" t="n"/>
+      <c r="X54" s="26" t="n"/>
+      <c r="Y54" s="25" t="n"/>
+      <c r="Z54" s="26" t="n"/>
+      <c r="AA54" s="28" t="n"/>
+      <c r="AB54" s="28" t="n"/>
+      <c r="AC54" s="30" t="n"/>
+      <c r="AD54" s="24" t="n"/>
+      <c r="AE54" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5000 (market_slug=aec-lol-ucam-mkf-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF54" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG54" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH54" s="24" t="n"/>
+      <c r="AI54" s="31" t="n"/>
+      <c r="AJ54" s="31" t="n"/>
+      <c r="AK54" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL54" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM54" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN54" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO54" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP54" s="24" t="inlineStr">
+        <is>
+          <t>⁠Movistar KOI Fénix</t>
+        </is>
+      </c>
+      <c r="AQ54" s="24" t="inlineStr">
+        <is>
+          <t>⁠Movistar KOI Fénix</t>
+        </is>
+      </c>
+      <c r="AR54" s="24" t="inlineStr">
+        <is>
+          <t>⁠Movistar KOI Fénix</t>
+        </is>
+      </c>
+      <c r="AS54" s="24" t="inlineStr">
+        <is>
+          <t>UCAM Esports Club</t>
+        </is>
+      </c>
+      <c r="AT54" s="24" t="inlineStr">
+        <is>
+          <t>UCAM Esports Club</t>
+        </is>
+      </c>
+      <c r="AU54" s="24" t="inlineStr">
+        <is>
+          <t>UCAM Esports Club</t>
+        </is>
+      </c>
+      <c r="AV54" s="24" t="n"/>
+      <c r="AW54" s="24" t="n"/>
+      <c r="AX54" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY54" s="24" t="n"/>
+      <c r="AZ54" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA54" s="24" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="BB54" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC54" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD54" s="24" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="BE54" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF54" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG54" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH54" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:47.949141Z</t>
+        </is>
+      </c>
+      <c r="BI54" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ54" s="25" t="n"/>
+      <c r="BK54" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="BL54" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM54" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BN54" s="28" t="n"/>
+      <c r="BO54" s="28" t="n"/>
+      <c r="BP54" s="25" t="n"/>
+      <c r="BQ54" s="27" t="n"/>
+      <c r="BR54" s="28" t="n"/>
+      <c r="BS54" s="28" t="n"/>
+      <c r="BT54" s="28" t="n"/>
+      <c r="BU54" s="25" t="n"/>
+      <c r="BV54" s="29" t="n"/>
+      <c r="BW54" s="24" t="n"/>
+      <c r="BX54" s="30" t="n"/>
+      <c r="BY54" s="27" t="n"/>
+      <c r="BZ54" s="24" t="n"/>
+      <c r="CA54" s="31" t="n"/>
+      <c r="CB54" s="24" t="n"/>
+      <c r="CC54" s="24" t="n"/>
+      <c r="CD54" s="24" t="n"/>
+      <c r="CE54" s="24" t="n"/>
+      <c r="CF54" s="24" t="n"/>
+      <c r="CG54" s="24" t="n"/>
+      <c r="CH54" s="24" t="n"/>
+      <c r="CI54" s="24" t="n"/>
+      <c r="CJ54" s="24" t="n"/>
+      <c r="CK54" s="24" t="n"/>
+      <c r="CL54" s="24" t="n"/>
+      <c r="CM54" s="24" t="n"/>
+      <c r="CN54" s="24" t="n"/>
+      <c r="CO54" s="24" t="n"/>
+      <c r="CP54" s="24" t="n"/>
+      <c r="CQ54" s="24" t="n"/>
+      <c r="CR54" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="36" customHeight="1">
+      <c r="A55" s="24" t="inlineStr">
+        <is>
+          <t>f439587bd2c842be</t>
+        </is>
+      </c>
+      <c r="B55" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:56.469660Z</t>
+        </is>
+      </c>
+      <c r="C55" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:30:00Z</t>
+        </is>
+      </c>
+      <c r="D55" s="24" t="inlineStr">
+        <is>
+          <t>69930</t>
+        </is>
+      </c>
+      <c r="E55" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F55" s="24" t="inlineStr">
+        <is>
+          <t>Bushido Wildcats</t>
+        </is>
+      </c>
+      <c r="G55" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PCIFIC </t>
+        </is>
+      </c>
+      <c r="H55" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I55" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J55" s="25" t="n"/>
+      <c r="K55" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L55" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="M55" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="N55" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="O55" s="28" t="n">
+        <v>0.536006</v>
+      </c>
+      <c r="P55" s="28" t="n"/>
+      <c r="Q55" s="28" t="n">
+        <v>0.08555599999999999</v>
+      </c>
+      <c r="R55" s="26" t="n">
+        <v>63</v>
+      </c>
+      <c r="S55" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T55" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U55" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V55" s="24" t="n"/>
+      <c r="W55" s="26" t="n"/>
+      <c r="X55" s="26" t="n"/>
+      <c r="Y55" s="25" t="n"/>
+      <c r="Z55" s="26" t="n"/>
+      <c r="AA55" s="28" t="n"/>
+      <c r="AB55" s="28" t="n"/>
+      <c r="AC55" s="30" t="n"/>
+      <c r="AD55" s="24" t="n"/>
+      <c r="AE55" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-lol-pcific-bw-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF55" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG55" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH55" s="24" t="n"/>
+      <c r="AI55" s="31" t="n"/>
+      <c r="AJ55" s="31" t="n"/>
+      <c r="AK55" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL55" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM55" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN55" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO55" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP55" s="24" t="inlineStr">
+        <is>
+          <t>Bushido Wildcats</t>
+        </is>
+      </c>
+      <c r="AQ55" s="24" t="inlineStr">
+        <is>
+          <t>Bushido Wildcats</t>
+        </is>
+      </c>
+      <c r="AR55" s="24" t="inlineStr">
+        <is>
+          <t>Bushido Wildcats</t>
+        </is>
+      </c>
+      <c r="AS55" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PCIFIC </t>
+        </is>
+      </c>
+      <c r="AT55" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PCIFIC </t>
+        </is>
+      </c>
+      <c r="AU55" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PCIFIC </t>
+        </is>
+      </c>
+      <c r="AV55" s="24" t="n"/>
+      <c r="AW55" s="24" t="n"/>
+      <c r="AX55" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY55" s="24" t="n"/>
+      <c r="AZ55" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA55" s="24" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="BB55" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC55" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD55" s="24" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="BE55" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF55" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG55" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH55" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:48.438562Z</t>
+        </is>
+      </c>
+      <c r="BI55" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ55" s="25" t="n"/>
+      <c r="BK55" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="BL55" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BM55" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="BN55" s="28" t="n"/>
+      <c r="BO55" s="28" t="n"/>
+      <c r="BP55" s="25" t="n"/>
+      <c r="BQ55" s="27" t="n"/>
+      <c r="BR55" s="28" t="n"/>
+      <c r="BS55" s="28" t="n"/>
+      <c r="BT55" s="28" t="n"/>
+      <c r="BU55" s="25" t="n"/>
+      <c r="BV55" s="29" t="n"/>
+      <c r="BW55" s="24" t="n"/>
+      <c r="BX55" s="30" t="n"/>
+      <c r="BY55" s="27" t="n"/>
+      <c r="BZ55" s="24" t="n"/>
+      <c r="CA55" s="31" t="n"/>
+      <c r="CB55" s="24" t="n"/>
+      <c r="CC55" s="24" t="n"/>
+      <c r="CD55" s="24" t="n"/>
+      <c r="CE55" s="24" t="n"/>
+      <c r="CF55" s="24" t="n"/>
+      <c r="CG55" s="24" t="n"/>
+      <c r="CH55" s="24" t="n"/>
+      <c r="CI55" s="24" t="n"/>
+      <c r="CJ55" s="24" t="n"/>
+      <c r="CK55" s="24" t="n"/>
+      <c r="CL55" s="24" t="n"/>
+      <c r="CM55" s="24" t="n"/>
+      <c r="CN55" s="24" t="n"/>
+      <c r="CO55" s="24" t="n"/>
+      <c r="CP55" s="24" t="n"/>
+      <c r="CQ55" s="24" t="n"/>
+      <c r="CR55" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="36" customHeight="1">
+      <c r="A56" s="24" t="inlineStr">
+        <is>
+          <t>7e44e2ed76904c7e</t>
+        </is>
+      </c>
+      <c r="B56" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:56.469660Z</t>
+        </is>
+      </c>
+      <c r="C56" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D56" s="24" t="inlineStr">
+        <is>
+          <t>69948</t>
+        </is>
+      </c>
+      <c r="E56" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F56" s="24" t="inlineStr">
+        <is>
+          <t>Solary</t>
+        </is>
+      </c>
+      <c r="G56" s="24" t="inlineStr">
+        <is>
+          <t>Karmine Corp Blue</t>
+        </is>
+      </c>
+      <c r="H56" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I56" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J56" s="25" t="n"/>
+      <c r="K56" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L56" s="26" t="n">
+        <v>-203</v>
+      </c>
+      <c r="M56" s="27" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="N56" s="28" t="n">
+        <v>0.669967</v>
+      </c>
+      <c r="O56" s="28" t="n">
+        <v>0.564089</v>
+      </c>
+      <c r="P56" s="28" t="n"/>
+      <c r="Q56" s="28" t="n">
+        <v>-0.105878</v>
+      </c>
+      <c r="R56" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T56" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U56" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V56" s="24" t="n"/>
+      <c r="W56" s="26" t="n"/>
+      <c r="X56" s="26" t="n"/>
+      <c r="Y56" s="25" t="n"/>
+      <c r="Z56" s="26" t="n"/>
+      <c r="AA56" s="28" t="n"/>
+      <c r="AB56" s="28" t="n"/>
+      <c r="AC56" s="30" t="n"/>
+      <c r="AD56" s="24" t="n"/>
+      <c r="AE56" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-lol-kcb-sly-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF56" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG56" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH56" s="24" t="n"/>
+      <c r="AI56" s="31" t="n"/>
+      <c r="AJ56" s="31" t="n"/>
+      <c r="AK56" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL56" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM56" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN56" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO56" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP56" s="24" t="inlineStr">
+        <is>
+          <t>Solary</t>
+        </is>
+      </c>
+      <c r="AQ56" s="24" t="inlineStr">
+        <is>
+          <t>Solary</t>
+        </is>
+      </c>
+      <c r="AR56" s="24" t="inlineStr">
+        <is>
+          <t>Solary</t>
+        </is>
+      </c>
+      <c r="AS56" s="24" t="inlineStr">
+        <is>
+          <t>Karmine Corp Blue</t>
+        </is>
+      </c>
+      <c r="AT56" s="24" t="inlineStr">
+        <is>
+          <t>Karmine Corp Blue</t>
+        </is>
+      </c>
+      <c r="AU56" s="24" t="inlineStr">
+        <is>
+          <t>Karmine Corp Blue</t>
+        </is>
+      </c>
+      <c r="AV56" s="24" t="n"/>
+      <c r="AW56" s="24" t="n"/>
+      <c r="AX56" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY56" s="24" t="n"/>
+      <c r="AZ56" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA56" s="24" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="BB56" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC56" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD56" s="24" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="BE56" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF56" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG56" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH56" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:49.352813Z</t>
+        </is>
+      </c>
+      <c r="BI56" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ56" s="25" t="n"/>
+      <c r="BK56" s="26" t="n">
+        <v>-203</v>
+      </c>
+      <c r="BL56" s="27" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="BM56" s="28" t="n">
+        <v>0.669967</v>
+      </c>
+      <c r="BN56" s="28" t="n"/>
+      <c r="BO56" s="28" t="n"/>
+      <c r="BP56" s="25" t="n"/>
+      <c r="BQ56" s="27" t="n"/>
+      <c r="BR56" s="28" t="n"/>
+      <c r="BS56" s="28" t="n"/>
+      <c r="BT56" s="28" t="n"/>
+      <c r="BU56" s="25" t="n"/>
+      <c r="BV56" s="29" t="n"/>
+      <c r="BW56" s="24" t="n"/>
+      <c r="BX56" s="30" t="n"/>
+      <c r="BY56" s="27" t="n"/>
+      <c r="BZ56" s="24" t="n"/>
+      <c r="CA56" s="31" t="n"/>
+      <c r="CB56" s="24" t="n"/>
+      <c r="CC56" s="24" t="n"/>
+      <c r="CD56" s="24" t="n"/>
+      <c r="CE56" s="24" t="n"/>
+      <c r="CF56" s="24" t="n"/>
+      <c r="CG56" s="24" t="n"/>
+      <c r="CH56" s="24" t="n"/>
+      <c r="CI56" s="24" t="n"/>
+      <c r="CJ56" s="24" t="n"/>
+      <c r="CK56" s="24" t="n"/>
+      <c r="CL56" s="24" t="n"/>
+      <c r="CM56" s="24" t="n"/>
+      <c r="CN56" s="24" t="n"/>
+      <c r="CO56" s="24" t="n"/>
+      <c r="CP56" s="24" t="n"/>
+      <c r="CQ56" s="24" t="n"/>
+      <c r="CR56" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="36" customHeight="1">
+      <c r="A57" s="24" t="inlineStr">
+        <is>
+          <t>ca87a9282d674c4d</t>
+        </is>
+      </c>
+      <c r="B57" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:56.469660Z</t>
+        </is>
+      </c>
+      <c r="C57" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D57" s="24" t="inlineStr">
+        <is>
+          <t>69949</t>
+        </is>
+      </c>
+      <c r="E57" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F57" s="24" t="inlineStr">
+        <is>
+          <t>Hyperion</t>
+        </is>
+      </c>
+      <c r="G57" s="24" t="inlineStr">
+        <is>
+          <t>Dominion Goblins</t>
+        </is>
+      </c>
+      <c r="H57" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I57" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J57" s="25" t="n"/>
+      <c r="K57" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L57" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="M57" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="N57" s="28" t="n">
+        <v>0.460829</v>
+      </c>
+      <c r="O57" s="28" t="n">
+        <v>0.530192</v>
+      </c>
+      <c r="P57" s="28" t="n"/>
+      <c r="Q57" s="28" t="n">
+        <v>0.06936299999999999</v>
+      </c>
+      <c r="R57" s="26" t="n">
+        <v>55</v>
+      </c>
+      <c r="S57" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T57" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U57" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V57" s="24" t="n"/>
+      <c r="W57" s="26" t="n"/>
+      <c r="X57" s="26" t="n"/>
+      <c r="Y57" s="25" t="n"/>
+      <c r="Z57" s="26" t="n"/>
+      <c r="AA57" s="28" t="n"/>
+      <c r="AB57" s="28" t="n"/>
+      <c r="AC57" s="30" t="n"/>
+      <c r="AD57" s="24" t="n"/>
+      <c r="AE57" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-lol-domi-hype-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF57" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG57" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH57" s="24" t="n"/>
+      <c r="AI57" s="31" t="n"/>
+      <c r="AJ57" s="31" t="n"/>
+      <c r="AK57" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL57" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM57" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN57" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO57" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP57" s="24" t="inlineStr">
+        <is>
+          <t>Hyperion</t>
+        </is>
+      </c>
+      <c r="AQ57" s="24" t="inlineStr">
+        <is>
+          <t>Hyperion</t>
+        </is>
+      </c>
+      <c r="AR57" s="24" t="inlineStr">
+        <is>
+          <t>Hyperion</t>
+        </is>
+      </c>
+      <c r="AS57" s="24" t="inlineStr">
+        <is>
+          <t>Dominion Goblins</t>
+        </is>
+      </c>
+      <c r="AT57" s="24" t="inlineStr">
+        <is>
+          <t>Dominion Goblins</t>
+        </is>
+      </c>
+      <c r="AU57" s="24" t="inlineStr">
+        <is>
+          <t>Dominion Goblins</t>
+        </is>
+      </c>
+      <c r="AV57" s="24" t="n"/>
+      <c r="AW57" s="24" t="n"/>
+      <c r="AX57" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY57" s="24" t="n"/>
+      <c r="AZ57" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA57" s="24" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="BB57" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC57" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD57" s="24" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="BE57" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF57" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG57" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH57" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:49.832690Z</t>
+        </is>
+      </c>
+      <c r="BI57" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ57" s="25" t="n"/>
+      <c r="BK57" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="BL57" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BM57" s="28" t="n">
+        <v>0.460829</v>
+      </c>
+      <c r="BN57" s="28" t="n"/>
+      <c r="BO57" s="28" t="n"/>
+      <c r="BP57" s="25" t="n"/>
+      <c r="BQ57" s="27" t="n"/>
+      <c r="BR57" s="28" t="n"/>
+      <c r="BS57" s="28" t="n"/>
+      <c r="BT57" s="28" t="n"/>
+      <c r="BU57" s="25" t="n"/>
+      <c r="BV57" s="29" t="n"/>
+      <c r="BW57" s="24" t="n"/>
+      <c r="BX57" s="30" t="n"/>
+      <c r="BY57" s="27" t="n"/>
+      <c r="BZ57" s="24" t="n"/>
+      <c r="CA57" s="31" t="n"/>
+      <c r="CB57" s="24" t="n"/>
+      <c r="CC57" s="24" t="n"/>
+      <c r="CD57" s="24" t="n"/>
+      <c r="CE57" s="24" t="n"/>
+      <c r="CF57" s="24" t="n"/>
+      <c r="CG57" s="24" t="n"/>
+      <c r="CH57" s="24" t="n"/>
+      <c r="CI57" s="24" t="n"/>
+      <c r="CJ57" s="24" t="n"/>
+      <c r="CK57" s="24" t="n"/>
+      <c r="CL57" s="24" t="n"/>
+      <c r="CM57" s="24" t="n"/>
+      <c r="CN57" s="24" t="n"/>
+      <c r="CO57" s="24" t="n"/>
+      <c r="CP57" s="24" t="n"/>
+      <c r="CQ57" s="24" t="n"/>
+      <c r="CR57" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="36" customHeight="1">
+      <c r="A58" s="24" t="inlineStr">
+        <is>
+          <t>cd4a0af1ff884108</t>
+        </is>
+      </c>
+      <c r="B58" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:56.469660Z</t>
+        </is>
+      </c>
+      <c r="C58" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D58" s="24" t="inlineStr">
+        <is>
+          <t>69950</t>
+        </is>
+      </c>
+      <c r="E58" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F58" s="24" t="inlineStr">
+        <is>
+          <t>Lupus Esports</t>
+        </is>
+      </c>
+      <c r="G58" s="24" t="inlineStr">
+        <is>
+          <t>SPIKE Syndicate</t>
+        </is>
+      </c>
+      <c r="H58" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I58" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J58" s="25" t="n"/>
+      <c r="K58" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L58" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="M58" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="N58" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="O58" s="28" t="n">
+        <v>0.534563</v>
+      </c>
+      <c r="P58" s="28" t="n"/>
+      <c r="Q58" s="28" t="n">
+        <v>-0.045269</v>
+      </c>
+      <c r="R58" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T58" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U58" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V58" s="24" t="n"/>
+      <c r="W58" s="26" t="n"/>
+      <c r="X58" s="26" t="n"/>
+      <c r="Y58" s="25" t="n"/>
+      <c r="Z58" s="26" t="n"/>
+      <c r="AA58" s="28" t="n"/>
+      <c r="AB58" s="28" t="n"/>
+      <c r="AC58" s="30" t="n"/>
+      <c r="AD58" s="24" t="n"/>
+      <c r="AE58" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-lol-spk-lps-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF58" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG58" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH58" s="24" t="n"/>
+      <c r="AI58" s="31" t="n"/>
+      <c r="AJ58" s="31" t="n"/>
+      <c r="AK58" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL58" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM58" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN58" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO58" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP58" s="24" t="inlineStr">
+        <is>
+          <t>Lupus Esports</t>
+        </is>
+      </c>
+      <c r="AQ58" s="24" t="inlineStr">
+        <is>
+          <t>Lupus Esports</t>
+        </is>
+      </c>
+      <c r="AR58" s="24" t="inlineStr">
+        <is>
+          <t>Lupus Esports</t>
+        </is>
+      </c>
+      <c r="AS58" s="24" t="inlineStr">
+        <is>
+          <t>SPIKE Syndicate</t>
+        </is>
+      </c>
+      <c r="AT58" s="24" t="inlineStr">
+        <is>
+          <t>SPIKE Syndicate</t>
+        </is>
+      </c>
+      <c r="AU58" s="24" t="inlineStr">
+        <is>
+          <t>SPIKE Syndicate</t>
+        </is>
+      </c>
+      <c r="AV58" s="24" t="n"/>
+      <c r="AW58" s="24" t="n"/>
+      <c r="AX58" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY58" s="24" t="n"/>
+      <c r="AZ58" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA58" s="24" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="BB58" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC58" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD58" s="24" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="BE58" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF58" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG58" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH58" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:50.326365Z</t>
+        </is>
+      </c>
+      <c r="BI58" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ58" s="25" t="n"/>
+      <c r="BK58" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="BL58" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="BM58" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="BN58" s="28" t="n"/>
+      <c r="BO58" s="28" t="n"/>
+      <c r="BP58" s="25" t="n"/>
+      <c r="BQ58" s="27" t="n"/>
+      <c r="BR58" s="28" t="n"/>
+      <c r="BS58" s="28" t="n"/>
+      <c r="BT58" s="28" t="n"/>
+      <c r="BU58" s="25" t="n"/>
+      <c r="BV58" s="29" t="n"/>
+      <c r="BW58" s="24" t="n"/>
+      <c r="BX58" s="30" t="n"/>
+      <c r="BY58" s="27" t="n"/>
+      <c r="BZ58" s="24" t="n"/>
+      <c r="CA58" s="31" t="n"/>
+      <c r="CB58" s="24" t="n"/>
+      <c r="CC58" s="24" t="n"/>
+      <c r="CD58" s="24" t="n"/>
+      <c r="CE58" s="24" t="n"/>
+      <c r="CF58" s="24" t="n"/>
+      <c r="CG58" s="24" t="n"/>
+      <c r="CH58" s="24" t="n"/>
+      <c r="CI58" s="24" t="n"/>
+      <c r="CJ58" s="24" t="n"/>
+      <c r="CK58" s="24" t="n"/>
+      <c r="CL58" s="24" t="n"/>
+      <c r="CM58" s="24" t="n"/>
+      <c r="CN58" s="24" t="n"/>
+      <c r="CO58" s="24" t="n"/>
+      <c r="CP58" s="24" t="n"/>
+      <c r="CQ58" s="24" t="n"/>
+      <c r="CR58" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="36" customHeight="1">
+      <c r="A59" s="24" t="inlineStr">
+        <is>
+          <t>1120235ad0b64397</t>
+        </is>
+      </c>
+      <c r="B59" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:56.469660Z</t>
+        </is>
+      </c>
+      <c r="C59" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D59" s="24" t="inlineStr">
+        <is>
+          <t>69951</t>
+        </is>
+      </c>
+      <c r="E59" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F59" s="24" t="inlineStr">
+        <is>
+          <t>Rich Gang</t>
+        </is>
+      </c>
+      <c r="G59" s="24" t="inlineStr">
+        <is>
+          <t>2 Massive</t>
+        </is>
+      </c>
+      <c r="H59" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I59" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J59" s="25" t="n"/>
+      <c r="K59" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L59" s="26" t="n">
+        <v>163</v>
+      </c>
+      <c r="M59" s="27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="N59" s="28" t="n">
+        <v>0.380228</v>
+      </c>
+      <c r="O59" s="28" t="n">
+        <v>0.5160709999999999</v>
+      </c>
+      <c r="P59" s="28" t="n"/>
+      <c r="Q59" s="28" t="n">
+        <v>0.135843</v>
+      </c>
+      <c r="R59" s="26" t="n">
+        <v>88</v>
+      </c>
+      <c r="S59" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T59" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U59" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V59" s="24" t="n"/>
+      <c r="W59" s="26" t="n"/>
+      <c r="X59" s="26" t="n"/>
+      <c r="Y59" s="25" t="n"/>
+      <c r="Z59" s="26" t="n"/>
+      <c r="AA59" s="28" t="n"/>
+      <c r="AB59" s="28" t="n"/>
+      <c r="AC59" s="30" t="n"/>
+      <c r="AD59" s="24" t="n"/>
+      <c r="AE59" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3800 (market_slug=aec-lol-mas-rgi-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF59" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG59" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH59" s="24" t="n"/>
+      <c r="AI59" s="31" t="n"/>
+      <c r="AJ59" s="31" t="n"/>
+      <c r="AK59" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL59" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM59" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN59" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO59" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP59" s="24" t="inlineStr">
+        <is>
+          <t>Rich Gang</t>
+        </is>
+      </c>
+      <c r="AQ59" s="24" t="inlineStr">
+        <is>
+          <t>Rich Gang</t>
+        </is>
+      </c>
+      <c r="AR59" s="24" t="inlineStr">
+        <is>
+          <t>Rich Gang</t>
+        </is>
+      </c>
+      <c r="AS59" s="24" t="inlineStr">
+        <is>
+          <t>2 Massive</t>
+        </is>
+      </c>
+      <c r="AT59" s="24" t="inlineStr">
+        <is>
+          <t>2 Massive</t>
+        </is>
+      </c>
+      <c r="AU59" s="24" t="inlineStr">
+        <is>
+          <t>2 Massive</t>
+        </is>
+      </c>
+      <c r="AV59" s="24" t="n"/>
+      <c r="AW59" s="24" t="n"/>
+      <c r="AX59" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY59" s="24" t="n"/>
+      <c r="AZ59" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA59" s="24" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="BB59" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC59" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD59" s="24" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="BE59" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF59" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG59" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH59" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:50.827783Z</t>
+        </is>
+      </c>
+      <c r="BI59" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ59" s="25" t="n"/>
+      <c r="BK59" s="26" t="n">
+        <v>163</v>
+      </c>
+      <c r="BL59" s="27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BM59" s="28" t="n">
+        <v>0.380228</v>
+      </c>
+      <c r="BN59" s="28" t="n"/>
+      <c r="BO59" s="28" t="n"/>
+      <c r="BP59" s="25" t="n"/>
+      <c r="BQ59" s="27" t="n"/>
+      <c r="BR59" s="28" t="n"/>
+      <c r="BS59" s="28" t="n"/>
+      <c r="BT59" s="28" t="n"/>
+      <c r="BU59" s="25" t="n"/>
+      <c r="BV59" s="29" t="n"/>
+      <c r="BW59" s="24" t="n"/>
+      <c r="BX59" s="30" t="n"/>
+      <c r="BY59" s="27" t="n"/>
+      <c r="BZ59" s="24" t="n"/>
+      <c r="CA59" s="31" t="n"/>
+      <c r="CB59" s="24" t="n"/>
+      <c r="CC59" s="24" t="n"/>
+      <c r="CD59" s="24" t="n"/>
+      <c r="CE59" s="24" t="n"/>
+      <c r="CF59" s="24" t="n"/>
+      <c r="CG59" s="24" t="n"/>
+      <c r="CH59" s="24" t="n"/>
+      <c r="CI59" s="24" t="n"/>
+      <c r="CJ59" s="24" t="n"/>
+      <c r="CK59" s="24" t="n"/>
+      <c r="CL59" s="24" t="n"/>
+      <c r="CM59" s="24" t="n"/>
+      <c r="CN59" s="24" t="n"/>
+      <c r="CO59" s="24" t="n"/>
+      <c r="CP59" s="24" t="n"/>
+      <c r="CQ59" s="24" t="n"/>
+      <c r="CR59" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="36" customHeight="1">
+      <c r="A60" s="24" t="inlineStr">
+        <is>
+          <t>9ed618ade4c3475f</t>
+        </is>
+      </c>
+      <c r="B60" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:56.469660Z</t>
+        </is>
+      </c>
+      <c r="C60" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="D60" s="24" t="inlineStr">
+        <is>
+          <t>70045</t>
+        </is>
+      </c>
+      <c r="E60" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F60" s="24" t="inlineStr">
+        <is>
+          <t>Ici Japon Corp. Esport</t>
+        </is>
+      </c>
+      <c r="G60" s="24" t="inlineStr">
+        <is>
+          <t>ZYB Esport</t>
+        </is>
+      </c>
+      <c r="H60" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I60" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J60" s="25" t="n"/>
+      <c r="K60" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L60" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="M60" s="27" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="N60" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="O60" s="28" t="n">
+        <v>0.607498</v>
+      </c>
+      <c r="P60" s="28" t="n"/>
+      <c r="Q60" s="28" t="n">
+        <v>0.088267</v>
+      </c>
+      <c r="R60" s="26" t="n">
+        <v>64</v>
+      </c>
+      <c r="S60" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T60" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U60" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V60" s="24" t="n"/>
+      <c r="W60" s="26" t="n"/>
+      <c r="X60" s="26" t="n"/>
+      <c r="Y60" s="25" t="n"/>
+      <c r="Z60" s="26" t="n"/>
+      <c r="AA60" s="28" t="n"/>
+      <c r="AB60" s="28" t="n"/>
+      <c r="AC60" s="30" t="n"/>
+      <c r="AD60" s="24" t="n"/>
+      <c r="AE60" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5200 (market_slug=aec-lol-zyb-ijc-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF60" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG60" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH60" s="24" t="n"/>
+      <c r="AI60" s="31" t="n"/>
+      <c r="AJ60" s="31" t="n"/>
+      <c r="AK60" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL60" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM60" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN60" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO60" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP60" s="24" t="inlineStr">
+        <is>
+          <t>Ici Japon Corp. Esport</t>
+        </is>
+      </c>
+      <c r="AQ60" s="24" t="inlineStr">
+        <is>
+          <t>Ici Japon Corp. Esport</t>
+        </is>
+      </c>
+      <c r="AR60" s="24" t="inlineStr">
+        <is>
+          <t>Ici Japon Corp. Esport</t>
+        </is>
+      </c>
+      <c r="AS60" s="24" t="inlineStr">
+        <is>
+          <t>ZYB Esport</t>
+        </is>
+      </c>
+      <c r="AT60" s="24" t="inlineStr">
+        <is>
+          <t>ZYB Esport</t>
+        </is>
+      </c>
+      <c r="AU60" s="24" t="inlineStr">
+        <is>
+          <t>ZYB Esport</t>
+        </is>
+      </c>
+      <c r="AV60" s="24" t="n"/>
+      <c r="AW60" s="24" t="n"/>
+      <c r="AX60" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY60" s="24" t="n"/>
+      <c r="AZ60" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA60" s="24" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="BB60" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC60" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD60" s="24" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="BE60" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF60" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG60" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH60" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:51.809850Z</t>
+        </is>
+      </c>
+      <c r="BI60" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ60" s="25" t="n"/>
+      <c r="BK60" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="BL60" s="27" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="BM60" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="BN60" s="28" t="n"/>
+      <c r="BO60" s="28" t="n"/>
+      <c r="BP60" s="25" t="n"/>
+      <c r="BQ60" s="27" t="n"/>
+      <c r="BR60" s="28" t="n"/>
+      <c r="BS60" s="28" t="n"/>
+      <c r="BT60" s="28" t="n"/>
+      <c r="BU60" s="25" t="n"/>
+      <c r="BV60" s="29" t="n"/>
+      <c r="BW60" s="24" t="n"/>
+      <c r="BX60" s="30" t="n"/>
+      <c r="BY60" s="27" t="n"/>
+      <c r="BZ60" s="24" t="n"/>
+      <c r="CA60" s="31" t="n"/>
+      <c r="CB60" s="24" t="n"/>
+      <c r="CC60" s="24" t="n"/>
+      <c r="CD60" s="24" t="n"/>
+      <c r="CE60" s="24" t="n"/>
+      <c r="CF60" s="24" t="n"/>
+      <c r="CG60" s="24" t="n"/>
+      <c r="CH60" s="24" t="n"/>
+      <c r="CI60" s="24" t="n"/>
+      <c r="CJ60" s="24" t="n"/>
+      <c r="CK60" s="24" t="n"/>
+      <c r="CL60" s="24" t="n"/>
+      <c r="CM60" s="24" t="n"/>
+      <c r="CN60" s="24" t="n"/>
+      <c r="CO60" s="24" t="n"/>
+      <c r="CP60" s="24" t="n"/>
+      <c r="CQ60" s="24" t="n"/>
+      <c r="CR60" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="36" customHeight="1">
+      <c r="A61" s="24" t="inlineStr">
+        <is>
+          <t>8ae2b418e6064ae0</t>
+        </is>
+      </c>
+      <c r="B61" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:56.469660Z</t>
+        </is>
+      </c>
+      <c r="C61" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="D61" s="24" t="inlineStr">
+        <is>
+          <t>70302</t>
+        </is>
+      </c>
+      <c r="E61" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F61" s="24" t="inlineStr">
+        <is>
+          <t>7REX</t>
+        </is>
+      </c>
+      <c r="G61" s="24" t="inlineStr">
+        <is>
+          <t>Team Solid</t>
+        </is>
+      </c>
+      <c r="H61" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I61" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J61" s="25" t="n"/>
+      <c r="K61" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L61" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="M61" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="N61" s="28" t="n">
+        <v>0.539171</v>
+      </c>
+      <c r="O61" s="28" t="n">
+        <v>0.535928</v>
+      </c>
+      <c r="P61" s="28" t="n"/>
+      <c r="Q61" s="28" t="n">
+        <v>-0.003243</v>
+      </c>
+      <c r="R61" s="26" t="n">
+        <v>18</v>
+      </c>
+      <c r="S61" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T61" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U61" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V61" s="24" t="n"/>
+      <c r="W61" s="26" t="n"/>
+      <c r="X61" s="26" t="n"/>
+      <c r="Y61" s="25" t="n"/>
+      <c r="Z61" s="26" t="n"/>
+      <c r="AA61" s="28" t="n"/>
+      <c r="AB61" s="28" t="n"/>
+      <c r="AC61" s="30" t="n"/>
+      <c r="AD61" s="24" t="n"/>
+      <c r="AE61" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-lol-tse-7rex-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF61" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG61" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH61" s="24" t="n"/>
+      <c r="AI61" s="31" t="n"/>
+      <c r="AJ61" s="31" t="n"/>
+      <c r="AK61" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL61" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM61" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN61" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO61" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP61" s="24" t="inlineStr">
+        <is>
+          <t>7REX</t>
+        </is>
+      </c>
+      <c r="AQ61" s="24" t="inlineStr">
+        <is>
+          <t>7REX</t>
+        </is>
+      </c>
+      <c r="AR61" s="24" t="inlineStr">
+        <is>
+          <t>7REX</t>
+        </is>
+      </c>
+      <c r="AS61" s="24" t="inlineStr">
+        <is>
+          <t>Team Solid</t>
+        </is>
+      </c>
+      <c r="AT61" s="24" t="inlineStr">
+        <is>
+          <t>Team Solid</t>
+        </is>
+      </c>
+      <c r="AU61" s="24" t="inlineStr">
+        <is>
+          <t>Team Solid</t>
+        </is>
+      </c>
+      <c r="AV61" s="24" t="n"/>
+      <c r="AW61" s="24" t="n"/>
+      <c r="AX61" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY61" s="24" t="n"/>
+      <c r="AZ61" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA61" s="24" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="BB61" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC61" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD61" s="24" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="BE61" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF61" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG61" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH61" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:52.802307Z</t>
+        </is>
+      </c>
+      <c r="BI61" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ61" s="25" t="n"/>
+      <c r="BK61" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="BL61" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="BM61" s="28" t="n">
+        <v>0.539171</v>
+      </c>
+      <c r="BN61" s="28" t="n"/>
+      <c r="BO61" s="28" t="n"/>
+      <c r="BP61" s="25" t="n"/>
+      <c r="BQ61" s="27" t="n"/>
+      <c r="BR61" s="28" t="n"/>
+      <c r="BS61" s="28" t="n"/>
+      <c r="BT61" s="28" t="n"/>
+      <c r="BU61" s="25" t="n"/>
+      <c r="BV61" s="29" t="n"/>
+      <c r="BW61" s="24" t="n"/>
+      <c r="BX61" s="30" t="n"/>
+      <c r="BY61" s="27" t="n"/>
+      <c r="BZ61" s="24" t="n"/>
+      <c r="CA61" s="31" t="n"/>
+      <c r="CB61" s="24" t="n"/>
+      <c r="CC61" s="24" t="n"/>
+      <c r="CD61" s="24" t="n"/>
+      <c r="CE61" s="24" t="n"/>
+      <c r="CF61" s="24" t="n"/>
+      <c r="CG61" s="24" t="n"/>
+      <c r="CH61" s="24" t="n"/>
+      <c r="CI61" s="24" t="n"/>
+      <c r="CJ61" s="24" t="n"/>
+      <c r="CK61" s="24" t="n"/>
+      <c r="CL61" s="24" t="n"/>
+      <c r="CM61" s="24" t="n"/>
+      <c r="CN61" s="24" t="n"/>
+      <c r="CO61" s="24" t="n"/>
+      <c r="CP61" s="24" t="n"/>
+      <c r="CQ61" s="24" t="n"/>
+      <c r="CR61" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="36" customHeight="1">
+      <c r="A62" s="24" t="inlineStr">
+        <is>
+          <t>bcd2f952b94e48ae</t>
+        </is>
+      </c>
+      <c r="B62" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:56.469660Z</t>
+        </is>
+      </c>
+      <c r="C62" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="D62" s="24" t="inlineStr">
+        <is>
+          <t>70349</t>
+        </is>
+      </c>
+      <c r="E62" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F62" s="24" t="inlineStr">
+        <is>
+          <t>Winthrop University</t>
+        </is>
+      </c>
+      <c r="G62" s="24" t="inlineStr">
+        <is>
+          <t>Blue Otter</t>
+        </is>
+      </c>
+      <c r="H62" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I62" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J62" s="25" t="n"/>
+      <c r="K62" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L62" s="26" t="n">
+        <v>-213</v>
+      </c>
+      <c r="M62" s="27" t="n">
+        <v>1.469484</v>
+      </c>
+      <c r="N62" s="28" t="n">
+        <v>0.680511</v>
+      </c>
+      <c r="O62" s="28" t="n">
+        <v>0.649617</v>
+      </c>
+      <c r="P62" s="28" t="n"/>
+      <c r="Q62" s="28" t="n">
+        <v>-0.030894</v>
+      </c>
+      <c r="R62" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="S62" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T62" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U62" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V62" s="24" t="n"/>
+      <c r="W62" s="26" t="n"/>
+      <c r="X62" s="26" t="n"/>
+      <c r="Y62" s="25" t="n"/>
+      <c r="Z62" s="26" t="n"/>
+      <c r="AA62" s="28" t="n"/>
+      <c r="AB62" s="28" t="n"/>
+      <c r="AC62" s="30" t="n"/>
+      <c r="AD62" s="24" t="n"/>
+      <c r="AE62" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-lol-blue-wu-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF62" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG62" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH62" s="24" t="n"/>
+      <c r="AI62" s="31" t="n"/>
+      <c r="AJ62" s="31" t="n"/>
+      <c r="AK62" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL62" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM62" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN62" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO62" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP62" s="24" t="inlineStr">
+        <is>
+          <t>Winthrop University</t>
+        </is>
+      </c>
+      <c r="AQ62" s="24" t="inlineStr">
+        <is>
+          <t>Winthrop University</t>
+        </is>
+      </c>
+      <c r="AR62" s="24" t="inlineStr">
+        <is>
+          <t>Winthrop University</t>
+        </is>
+      </c>
+      <c r="AS62" s="24" t="inlineStr">
+        <is>
+          <t>Blue Otter</t>
+        </is>
+      </c>
+      <c r="AT62" s="24" t="inlineStr">
+        <is>
+          <t>Blue Otter</t>
+        </is>
+      </c>
+      <c r="AU62" s="24" t="inlineStr">
+        <is>
+          <t>Blue Otter</t>
+        </is>
+      </c>
+      <c r="AV62" s="24" t="n"/>
+      <c r="AW62" s="24" t="n"/>
+      <c r="AX62" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY62" s="24" t="n"/>
+      <c r="AZ62" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA62" s="24" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="BB62" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC62" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD62" s="24" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="BE62" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF62" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG62" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH62" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:53.928842Z</t>
+        </is>
+      </c>
+      <c r="BI62" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ62" s="25" t="n"/>
+      <c r="BK62" s="26" t="n">
+        <v>-213</v>
+      </c>
+      <c r="BL62" s="27" t="n">
+        <v>1.469484</v>
+      </c>
+      <c r="BM62" s="28" t="n">
+        <v>0.680511</v>
+      </c>
+      <c r="BN62" s="28" t="n"/>
+      <c r="BO62" s="28" t="n"/>
+      <c r="BP62" s="25" t="n"/>
+      <c r="BQ62" s="27" t="n"/>
+      <c r="BR62" s="28" t="n"/>
+      <c r="BS62" s="28" t="n"/>
+      <c r="BT62" s="28" t="n"/>
+      <c r="BU62" s="25" t="n"/>
+      <c r="BV62" s="29" t="n"/>
+      <c r="BW62" s="24" t="n"/>
+      <c r="BX62" s="30" t="n"/>
+      <c r="BY62" s="27" t="n"/>
+      <c r="BZ62" s="24" t="n"/>
+      <c r="CA62" s="31" t="n"/>
+      <c r="CB62" s="24" t="n"/>
+      <c r="CC62" s="24" t="n"/>
+      <c r="CD62" s="24" t="n"/>
+      <c r="CE62" s="24" t="n"/>
+      <c r="CF62" s="24" t="n"/>
+      <c r="CG62" s="24" t="n"/>
+      <c r="CH62" s="24" t="n"/>
+      <c r="CI62" s="24" t="n"/>
+      <c r="CJ62" s="24" t="n"/>
+      <c r="CK62" s="24" t="n"/>
+      <c r="CL62" s="24" t="n"/>
+      <c r="CM62" s="24" t="n"/>
+      <c r="CN62" s="24" t="n"/>
+      <c r="CO62" s="24" t="n"/>
+      <c r="CP62" s="24" t="n"/>
+      <c r="CQ62" s="24" t="n"/>
+      <c r="CR62" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="36" customHeight="1">
+      <c r="A63" s="24" t="inlineStr">
+        <is>
+          <t>835b0d32870c497c</t>
+        </is>
+      </c>
+      <c r="B63" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:56.469660Z</t>
+        </is>
+      </c>
+      <c r="C63" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="D63" s="24" t="inlineStr">
+        <is>
+          <t>70348</t>
+        </is>
+      </c>
+      <c r="E63" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F63" s="24" t="inlineStr">
+        <is>
+          <t>White Dragons</t>
+        </is>
+      </c>
+      <c r="G63" s="24" t="inlineStr">
+        <is>
+          <t>NORTHERNGRADE ESPORTS</t>
+        </is>
+      </c>
+      <c r="H63" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I63" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J63" s="25" t="n"/>
+      <c r="K63" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L63" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="M63" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="N63" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="O63" s="28" t="n">
+        <v>0.500208</v>
+      </c>
+      <c r="P63" s="28" t="n"/>
+      <c r="Q63" s="28" t="n">
+        <v>-0.119564</v>
+      </c>
+      <c r="R63" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T63" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U63" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V63" s="24" t="n"/>
+      <c r="W63" s="26" t="n"/>
+      <c r="X63" s="26" t="n"/>
+      <c r="Y63" s="25" t="n"/>
+      <c r="Z63" s="26" t="n"/>
+      <c r="AA63" s="28" t="n"/>
+      <c r="AB63" s="28" t="n"/>
+      <c r="AC63" s="30" t="n"/>
+      <c r="AD63" s="24" t="n"/>
+      <c r="AE63" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-lol-nort-wd-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF63" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG63" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH63" s="24" t="n"/>
+      <c r="AI63" s="31" t="n"/>
+      <c r="AJ63" s="31" t="n"/>
+      <c r="AK63" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL63" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM63" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN63" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO63" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP63" s="24" t="inlineStr">
+        <is>
+          <t>White Dragons</t>
+        </is>
+      </c>
+      <c r="AQ63" s="24" t="inlineStr">
+        <is>
+          <t>White Dragons</t>
+        </is>
+      </c>
+      <c r="AR63" s="24" t="inlineStr">
+        <is>
+          <t>White Dragons</t>
+        </is>
+      </c>
+      <c r="AS63" s="24" t="inlineStr">
+        <is>
+          <t>NORTHERNGRADE ESPORTS</t>
+        </is>
+      </c>
+      <c r="AT63" s="24" t="inlineStr">
+        <is>
+          <t>NORTHERNGRADE ESPORTS</t>
+        </is>
+      </c>
+      <c r="AU63" s="24" t="inlineStr">
+        <is>
+          <t>NORTHERNGRADE ESPORTS</t>
+        </is>
+      </c>
+      <c r="AV63" s="24" t="n"/>
+      <c r="AW63" s="24" t="n"/>
+      <c r="AX63" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY63" s="24" t="n"/>
+      <c r="AZ63" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA63" s="24" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="BB63" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC63" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD63" s="24" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="BE63" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF63" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG63" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH63" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:54.377453Z</t>
+        </is>
+      </c>
+      <c r="BI63" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ63" s="25" t="n"/>
+      <c r="BK63" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="BL63" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="BM63" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="BN63" s="28" t="n"/>
+      <c r="BO63" s="28" t="n"/>
+      <c r="BP63" s="25" t="n"/>
+      <c r="BQ63" s="27" t="n"/>
+      <c r="BR63" s="28" t="n"/>
+      <c r="BS63" s="28" t="n"/>
+      <c r="BT63" s="28" t="n"/>
+      <c r="BU63" s="25" t="n"/>
+      <c r="BV63" s="29" t="n"/>
+      <c r="BW63" s="24" t="n"/>
+      <c r="BX63" s="30" t="n"/>
+      <c r="BY63" s="27" t="n"/>
+      <c r="BZ63" s="24" t="n"/>
+      <c r="CA63" s="31" t="n"/>
+      <c r="CB63" s="24" t="n"/>
+      <c r="CC63" s="24" t="n"/>
+      <c r="CD63" s="24" t="n"/>
+      <c r="CE63" s="24" t="n"/>
+      <c r="CF63" s="24" t="n"/>
+      <c r="CG63" s="24" t="n"/>
+      <c r="CH63" s="24" t="n"/>
+      <c r="CI63" s="24" t="n"/>
+      <c r="CJ63" s="24" t="n"/>
+      <c r="CK63" s="24" t="n"/>
+      <c r="CL63" s="24" t="n"/>
+      <c r="CM63" s="24" t="n"/>
+      <c r="CN63" s="24" t="n"/>
+      <c r="CO63" s="24" t="n"/>
+      <c r="CP63" s="24" t="n"/>
+      <c r="CQ63" s="24" t="n"/>
+      <c r="CR63" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="36" customHeight="1">
+      <c r="A64" s="24" t="inlineStr">
+        <is>
+          <t>5244e146f1fe46d5</t>
+        </is>
+      </c>
+      <c r="B64" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:56.469660Z</t>
+        </is>
+      </c>
+      <c r="C64" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="D64" s="24" t="inlineStr">
+        <is>
+          <t>70379</t>
+        </is>
+      </c>
+      <c r="E64" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F64" s="24" t="inlineStr">
+        <is>
+          <t>KaBuM! Ilha das Lendas</t>
+        </is>
+      </c>
+      <c r="G64" s="24" t="inlineStr">
+        <is>
+          <t>Ei Nerd Esports</t>
+        </is>
+      </c>
+      <c r="H64" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I64" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J64" s="25" t="n"/>
+      <c r="K64" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L64" s="26" t="n">
+        <v>133</v>
+      </c>
+      <c r="M64" s="27" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="N64" s="28" t="n">
+        <v>0.429185</v>
+      </c>
+      <c r="O64" s="28" t="n">
+        <v>0.5668840000000001</v>
+      </c>
+      <c r="P64" s="28" t="n"/>
+      <c r="Q64" s="28" t="n">
+        <v>0.137699</v>
+      </c>
+      <c r="R64" s="26" t="n">
+        <v>89</v>
+      </c>
+      <c r="S64" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T64" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U64" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V64" s="24" t="n"/>
+      <c r="W64" s="26" t="n"/>
+      <c r="X64" s="26" t="n"/>
+      <c r="Y64" s="25" t="n"/>
+      <c r="Z64" s="26" t="n"/>
+      <c r="AA64" s="28" t="n"/>
+      <c r="AB64" s="28" t="n"/>
+      <c r="AC64" s="30" t="n"/>
+      <c r="AD64" s="24" t="n"/>
+      <c r="AE64" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4300 (market_slug=aec-lol-nerd-kbm-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF64" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG64" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH64" s="24" t="n"/>
+      <c r="AI64" s="31" t="n"/>
+      <c r="AJ64" s="31" t="n"/>
+      <c r="AK64" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL64" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM64" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN64" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO64" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP64" s="24" t="inlineStr">
+        <is>
+          <t>KaBuM! Ilha das Lendas</t>
+        </is>
+      </c>
+      <c r="AQ64" s="24" t="inlineStr">
+        <is>
+          <t>KaBuM! Ilha das Lendas</t>
+        </is>
+      </c>
+      <c r="AR64" s="24" t="inlineStr">
+        <is>
+          <t>KaBuM! Ilha das Lendas</t>
+        </is>
+      </c>
+      <c r="AS64" s="24" t="inlineStr">
+        <is>
+          <t>Ei Nerd Esports</t>
+        </is>
+      </c>
+      <c r="AT64" s="24" t="inlineStr">
+        <is>
+          <t>Ei Nerd Esports</t>
+        </is>
+      </c>
+      <c r="AU64" s="24" t="inlineStr">
+        <is>
+          <t>Ei Nerd Esports</t>
+        </is>
+      </c>
+      <c r="AV64" s="24" t="n"/>
+      <c r="AW64" s="24" t="n"/>
+      <c r="AX64" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY64" s="24" t="n"/>
+      <c r="AZ64" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA64" s="24" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="BB64" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC64" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD64" s="24" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="BE64" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF64" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG64" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH64" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:54.874184Z</t>
+        </is>
+      </c>
+      <c r="BI64" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ64" s="25" t="n"/>
+      <c r="BK64" s="26" t="n">
+        <v>133</v>
+      </c>
+      <c r="BL64" s="27" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BM64" s="28" t="n">
+        <v>0.429185</v>
+      </c>
+      <c r="BN64" s="28" t="n"/>
+      <c r="BO64" s="28" t="n"/>
+      <c r="BP64" s="25" t="n"/>
+      <c r="BQ64" s="27" t="n"/>
+      <c r="BR64" s="28" t="n"/>
+      <c r="BS64" s="28" t="n"/>
+      <c r="BT64" s="28" t="n"/>
+      <c r="BU64" s="25" t="n"/>
+      <c r="BV64" s="29" t="n"/>
+      <c r="BW64" s="24" t="n"/>
+      <c r="BX64" s="30" t="n"/>
+      <c r="BY64" s="27" t="n"/>
+      <c r="BZ64" s="24" t="n"/>
+      <c r="CA64" s="31" t="n"/>
+      <c r="CB64" s="24" t="n"/>
+      <c r="CC64" s="24" t="n"/>
+      <c r="CD64" s="24" t="n"/>
+      <c r="CE64" s="24" t="n"/>
+      <c r="CF64" s="24" t="n"/>
+      <c r="CG64" s="24" t="n"/>
+      <c r="CH64" s="24" t="n"/>
+      <c r="CI64" s="24" t="n"/>
+      <c r="CJ64" s="24" t="n"/>
+      <c r="CK64" s="24" t="n"/>
+      <c r="CL64" s="24" t="n"/>
+      <c r="CM64" s="24" t="n"/>
+      <c r="CN64" s="24" t="n"/>
+      <c r="CO64" s="24" t="n"/>
+      <c r="CP64" s="24" t="n"/>
+      <c r="CQ64" s="24" t="n"/>
+      <c r="CR64" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="36" customHeight="1">
+      <c r="A65" s="24" t="inlineStr">
+        <is>
+          <t>3dae42edf8664905</t>
+        </is>
+      </c>
+      <c r="B65" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:56.469660Z</t>
+        </is>
+      </c>
+      <c r="C65" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D65" s="24" t="inlineStr">
+        <is>
+          <t>70454</t>
+        </is>
+      </c>
+      <c r="E65" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F65" s="24" t="inlineStr">
+        <is>
+          <t>Cupid Esports</t>
+        </is>
+      </c>
+      <c r="G65" s="24" t="inlineStr">
+        <is>
+          <t>NRG Esports</t>
+        </is>
+      </c>
+      <c r="H65" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I65" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J65" s="25" t="n"/>
+      <c r="K65" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L65" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="M65" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="N65" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="O65" s="28" t="n">
+        <v>0.515927</v>
+      </c>
+      <c r="P65" s="28" t="n"/>
+      <c r="Q65" s="28" t="n">
+        <v>-0.103845</v>
+      </c>
+      <c r="R65" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T65" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U65" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V65" s="24" t="n"/>
+      <c r="W65" s="26" t="n"/>
+      <c r="X65" s="26" t="n"/>
+      <c r="Y65" s="25" t="n"/>
+      <c r="Z65" s="26" t="n"/>
+      <c r="AA65" s="28" t="n"/>
+      <c r="AB65" s="28" t="n"/>
+      <c r="AC65" s="30" t="n"/>
+      <c r="AD65" s="24" t="n"/>
+      <c r="AE65" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-lol-nrg-cpd-2026-08-06).</t>
+        </is>
+      </c>
+      <c r="AF65" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG65" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH65" s="24" t="n"/>
+      <c r="AI65" s="31" t="n"/>
+      <c r="AJ65" s="31" t="n"/>
+      <c r="AK65" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL65" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM65" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN65" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO65" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP65" s="24" t="inlineStr">
+        <is>
+          <t>Cupid Esports</t>
+        </is>
+      </c>
+      <c r="AQ65" s="24" t="inlineStr">
+        <is>
+          <t>Cupid Esports</t>
+        </is>
+      </c>
+      <c r="AR65" s="24" t="inlineStr">
+        <is>
+          <t>Cupid Esports</t>
+        </is>
+      </c>
+      <c r="AS65" s="24" t="inlineStr">
+        <is>
+          <t>NRG Esports</t>
+        </is>
+      </c>
+      <c r="AT65" s="24" t="inlineStr">
+        <is>
+          <t>NRG Esports</t>
+        </is>
+      </c>
+      <c r="AU65" s="24" t="inlineStr">
+        <is>
+          <t>NRG Esports</t>
+        </is>
+      </c>
+      <c r="AV65" s="24" t="n"/>
+      <c r="AW65" s="24" t="n"/>
+      <c r="AX65" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY65" s="24" t="n"/>
+      <c r="AZ65" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA65" s="24" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="BB65" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC65" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD65" s="24" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="BE65" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF65" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG65" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH65" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:55.920586Z</t>
+        </is>
+      </c>
+      <c r="BI65" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ65" s="25" t="n"/>
+      <c r="BK65" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="BL65" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="BM65" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="BN65" s="28" t="n"/>
+      <c r="BO65" s="28" t="n"/>
+      <c r="BP65" s="25" t="n"/>
+      <c r="BQ65" s="27" t="n"/>
+      <c r="BR65" s="28" t="n"/>
+      <c r="BS65" s="28" t="n"/>
+      <c r="BT65" s="28" t="n"/>
+      <c r="BU65" s="25" t="n"/>
+      <c r="BV65" s="29" t="n"/>
+      <c r="BW65" s="24" t="n"/>
+      <c r="BX65" s="30" t="n"/>
+      <c r="BY65" s="27" t="n"/>
+      <c r="BZ65" s="24" t="n"/>
+      <c r="CA65" s="31" t="n"/>
+      <c r="CB65" s="24" t="n"/>
+      <c r="CC65" s="24" t="n"/>
+      <c r="CD65" s="24" t="n"/>
+      <c r="CE65" s="24" t="n"/>
+      <c r="CF65" s="24" t="n"/>
+      <c r="CG65" s="24" t="n"/>
+      <c r="CH65" s="24" t="n"/>
+      <c r="CI65" s="24" t="n"/>
+      <c r="CJ65" s="24" t="n"/>
+      <c r="CK65" s="24" t="n"/>
+      <c r="CL65" s="24" t="n"/>
+      <c r="CM65" s="24" t="n"/>
+      <c r="CN65" s="24" t="n"/>
+      <c r="CO65" s="24" t="n"/>
+      <c r="CP65" s="24" t="n"/>
+      <c r="CQ65" s="24" t="n"/>
+      <c r="CR65" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="36" customHeight="1">
+      <c r="A66" s="24" t="inlineStr">
+        <is>
+          <t>c88d2da337744db9</t>
+        </is>
+      </c>
+      <c r="B66" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:56.469660Z</t>
+        </is>
+      </c>
+      <c r="C66" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D66" s="24" t="inlineStr">
+        <is>
+          <t>70453</t>
+        </is>
+      </c>
+      <c r="E66" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F66" s="24" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="G66" s="24" t="inlineStr">
+        <is>
+          <t>INTZ e-Sports</t>
+        </is>
+      </c>
+      <c r="H66" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I66" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J66" s="25" t="n"/>
+      <c r="K66" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L66" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="M66" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="N66" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="O66" s="28" t="n">
+        <v>0.590765</v>
+      </c>
+      <c r="P66" s="28" t="n"/>
+      <c r="Q66" s="28" t="n">
+        <v>0.01995</v>
+      </c>
+      <c r="R66" s="26" t="n">
+        <v>30</v>
+      </c>
+      <c r="S66" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T66" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U66" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V66" s="24" t="n"/>
+      <c r="W66" s="26" t="n"/>
+      <c r="X66" s="26" t="n"/>
+      <c r="Y66" s="25" t="n"/>
+      <c r="Z66" s="26" t="n"/>
+      <c r="AA66" s="28" t="n"/>
+      <c r="AB66" s="28" t="n"/>
+      <c r="AC66" s="30" t="n"/>
+      <c r="AD66" s="24" t="n"/>
+      <c r="AE66" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-lol-itz-pnga-2026-08-06).</t>
+        </is>
+      </c>
+      <c r="AF66" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG66" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH66" s="24" t="n"/>
+      <c r="AI66" s="31" t="n"/>
+      <c r="AJ66" s="31" t="n"/>
+      <c r="AK66" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL66" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM66" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN66" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO66" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP66" s="24" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="AQ66" s="24" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="AR66" s="24" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="AS66" s="24" t="inlineStr">
+        <is>
+          <t>INTZ e-Sports</t>
+        </is>
+      </c>
+      <c r="AT66" s="24" t="inlineStr">
+        <is>
+          <t>INTZ e-Sports</t>
+        </is>
+      </c>
+      <c r="AU66" s="24" t="inlineStr">
+        <is>
+          <t>INTZ e-Sports</t>
+        </is>
+      </c>
+      <c r="AV66" s="24" t="n"/>
+      <c r="AW66" s="24" t="n"/>
+      <c r="AX66" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY66" s="24" t="n"/>
+      <c r="AZ66" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA66" s="24" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="BB66" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC66" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD66" s="24" t="inlineStr">
+        <is>
+          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+        </is>
+      </c>
+      <c r="BE66" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF66" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG66" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH66" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:56.469425Z</t>
+        </is>
+      </c>
+      <c r="BI66" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ66" s="25" t="n"/>
+      <c r="BK66" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="BL66" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="BM66" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="BN66" s="28" t="n"/>
+      <c r="BO66" s="28" t="n"/>
+      <c r="BP66" s="25" t="n"/>
+      <c r="BQ66" s="27" t="n"/>
+      <c r="BR66" s="28" t="n"/>
+      <c r="BS66" s="28" t="n"/>
+      <c r="BT66" s="28" t="n"/>
+      <c r="BU66" s="25" t="n"/>
+      <c r="BV66" s="29" t="n"/>
+      <c r="BW66" s="24" t="n"/>
+      <c r="BX66" s="30" t="n"/>
+      <c r="BY66" s="27" t="n"/>
+      <c r="BZ66" s="24" t="n"/>
+      <c r="CA66" s="31" t="n"/>
+      <c r="CB66" s="24" t="n"/>
+      <c r="CC66" s="24" t="n"/>
+      <c r="CD66" s="24" t="n"/>
+      <c r="CE66" s="24" t="n"/>
+      <c r="CF66" s="24" t="n"/>
+      <c r="CG66" s="24" t="n"/>
+      <c r="CH66" s="24" t="n"/>
+      <c r="CI66" s="24" t="n"/>
+      <c r="CJ66" s="24" t="n"/>
+      <c r="CK66" s="24" t="n"/>
+      <c r="CL66" s="24" t="n"/>
+      <c r="CM66" s="24" t="n"/>
+      <c r="CN66" s="24" t="n"/>
+      <c r="CO66" s="24" t="n"/>
+      <c r="CP66" s="24" t="n"/>
+      <c r="CQ66" s="24" t="n"/>
+      <c r="CR66" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>

--- a/data/research/lol.xlsx
+++ b/data/research/lol.xlsx
@@ -300,9 +300,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CR66" headerRowCount="1">
-  <autoFilter ref="A1:CR66"/>
-  <tableColumns count="96">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS67" headerRowCount="1">
+  <autoFilter ref="A1:CS67"/>
+  <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
     <tableColumn id="3" name="event_start_utc"/>
@@ -393,12 +393,13 @@
     <tableColumn id="88" name="defensive_trend_gap"/>
     <tableColumn id="89" name="neutral_elo_rating_difference"/>
     <tableColumn id="90" name="bullpen_weakness_gap"/>
-    <tableColumn id="91" name="rest_disparity"/>
-    <tableColumn id="92" name="back_to_back_gap"/>
-    <tableColumn id="93" name="games_last_7_gap"/>
-    <tableColumn id="94" name="schedule_missingness"/>
-    <tableColumn id="95" name="market_residual_probability"/>
-    <tableColumn id="96" name="trade_candidate"/>
+    <tableColumn id="91" name="starter_era_gap"/>
+    <tableColumn id="92" name="rest_disparity"/>
+    <tableColumn id="93" name="back_to_back_gap"/>
+    <tableColumn id="94" name="games_last_7_gap"/>
+    <tableColumn id="95" name="schedule_missingness"/>
+    <tableColumn id="96" name="market_residual_probability"/>
+    <tableColumn id="97" name="trade_candidate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -755,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$66)</f>
+        <f>COUNTA('Picks'!$A$2:$A$67)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$66,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$67,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$66,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$67,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$66,"settled",'Picks'!$V$2:$V$66,"win")+COUNTIFS('Picks'!$U$2:$U$66,"settled",'Picks'!$V$2:$V$66,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$67,"settled",'Picks'!$V$2:$V$67,"win")+COUNTIFS('Picks'!$U$2:$U$67,"settled",'Picks'!$V$2:$V$67,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -795,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$66,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$67,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$66,"&gt;0",'Picks'!$V$2:$V$66,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$66,"&gt;0",'Picks'!$V$2:$V$66,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$67,"&gt;0",'Picks'!$V$2:$V$67,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$67,"&gt;0",'Picks'!$V$2:$V$67,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$66,"&gt;0",'Picks'!$V$2:$V$66,"win")/(COUNTIFS('Picks'!$BX$2:$BX$66,"&gt;0",'Picks'!$V$2:$V$66,"win")+COUNTIFS('Picks'!$BX$2:$BX$66,"&gt;0",'Picks'!$V$2:$V$66,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$67,"&gt;0",'Picks'!$V$2:$V$67,"win")/(COUNTIFS('Picks'!$BX$2:$BX$67,"&gt;0",'Picks'!$V$2:$V$67,"win")+COUNTIFS('Picks'!$BX$2:$BX$67,"&gt;0",'Picks'!$V$2:$V$67,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$66)/SUM('Picks'!$BX$2:$BX$66),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$67)/SUM('Picks'!$BX$2:$BX$67),0)</f>
         <v/>
       </c>
     </row>
@@ -835,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$66)</f>
+        <f>SUM('Picks'!$BY$2:$BY$67)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$66,"&lt;&gt;",'Picks'!$AB$2:$AB$66),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$67,"&lt;&gt;",'Picks'!$AB$2:$AB$67),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$66,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$66,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$67,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$67,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$66,'Picks'!$AM$2:$AM$66,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$67,'Picks'!$AM$2:$AM$67,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -902,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$66,$A14,'Picks'!$U$2:$U$66,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$67,$A14,'Picks'!$U$2:$U$67,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$66,$A14,'Picks'!$U$2:$U$66,"settled",'Picks'!$V$2:$V$66,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$67,$A14,'Picks'!$U$2:$U$67,"settled",'Picks'!$V$2:$V$67,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$66,$A14,'Picks'!$U$2:$U$66,"settled",'Picks'!$V$2:$V$66,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$67,$A14,'Picks'!$U$2:$U$67,"settled",'Picks'!$V$2:$V$67,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -918,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$66,'Picks'!$H$2:$H$66,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$67,'Picks'!$H$2:$H$67,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$66,'Picks'!$H$2:$H$66,$A14,'Picks'!$U$2:$U$66,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$67,'Picks'!$H$2:$H$67,$A14,'Picks'!$U$2:$U$67,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -933,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$66,$A15,'Picks'!$U$2:$U$66,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$67,$A15,'Picks'!$U$2:$U$67,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$66,$A15,'Picks'!$U$2:$U$66,"settled",'Picks'!$V$2:$V$66,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$67,$A15,'Picks'!$U$2:$U$67,"settled",'Picks'!$V$2:$V$67,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$66,$A15,'Picks'!$U$2:$U$66,"settled",'Picks'!$V$2:$V$66,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$67,$A15,'Picks'!$U$2:$U$67,"settled",'Picks'!$V$2:$V$67,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -949,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$66,'Picks'!$H$2:$H$66,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$67,'Picks'!$H$2:$H$67,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$66,'Picks'!$H$2:$H$66,$A15,'Picks'!$U$2:$U$66,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$67,'Picks'!$H$2:$H$67,$A15,'Picks'!$U$2:$U$67,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -964,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$66,$A16,'Picks'!$U$2:$U$66,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$67,$A16,'Picks'!$U$2:$U$67,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$66,$A16,'Picks'!$U$2:$U$66,"settled",'Picks'!$V$2:$V$66,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$67,$A16,'Picks'!$U$2:$U$67,"settled",'Picks'!$V$2:$V$67,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$66,$A16,'Picks'!$U$2:$U$66,"settled",'Picks'!$V$2:$V$66,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$67,$A16,'Picks'!$U$2:$U$67,"settled",'Picks'!$V$2:$V$67,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -980,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$66,'Picks'!$H$2:$H$66,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$67,'Picks'!$H$2:$H$67,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$66,'Picks'!$H$2:$H$66,$A16,'Picks'!$U$2:$U$66,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$67,'Picks'!$H$2:$H$67,$A16,'Picks'!$U$2:$U$67,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1013,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CR66"/>
+  <dimension ref="A1:CS67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1106,12 +1107,13 @@
     <col width="21" customWidth="1" min="88" max="88"/>
     <col width="22" customWidth="1" min="89" max="89"/>
     <col width="22" customWidth="1" min="90" max="90"/>
-    <col width="16" customWidth="1" min="91" max="91"/>
-    <col width="18" customWidth="1" min="92" max="92"/>
+    <col width="17" customWidth="1" min="91" max="91"/>
+    <col width="16" customWidth="1" min="92" max="92"/>
     <col width="18" customWidth="1" min="93" max="93"/>
-    <col width="22" customWidth="1" min="94" max="94"/>
+    <col width="18" customWidth="1" min="94" max="94"/>
     <col width="22" customWidth="1" min="95" max="95"/>
-    <col width="17" customWidth="1" min="96" max="96"/>
+    <col width="22" customWidth="1" min="96" max="96"/>
+    <col width="17" customWidth="1" min="97" max="97"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1567,30 +1569,35 @@
       </c>
       <c r="CM1" s="23" t="inlineStr">
         <is>
+          <t>starter_era_gap</t>
+        </is>
+      </c>
+      <c r="CN1" s="23" t="inlineStr">
+        <is>
           <t>rest_disparity</t>
         </is>
       </c>
-      <c r="CN1" s="23" t="inlineStr">
+      <c r="CO1" s="23" t="inlineStr">
         <is>
           <t>back_to_back_gap</t>
         </is>
       </c>
-      <c r="CO1" s="23" t="inlineStr">
+      <c r="CP1" s="23" t="inlineStr">
         <is>
           <t>games_last_7_gap</t>
         </is>
       </c>
-      <c r="CP1" s="23" t="inlineStr">
+      <c r="CQ1" s="23" t="inlineStr">
         <is>
           <t>schedule_missingness</t>
         </is>
       </c>
-      <c r="CQ1" s="23" t="inlineStr">
+      <c r="CR1" s="23" t="inlineStr">
         <is>
           <t>market_residual_probability</t>
         </is>
       </c>
-      <c r="CR1" s="23" t="inlineStr">
+      <c r="CS1" s="23" t="inlineStr">
         <is>
           <t>trade_candidate</t>
         </is>
@@ -1883,6 +1890,7 @@
       <c r="CP2" s="24" t="n"/>
       <c r="CQ2" s="24" t="n"/>
       <c r="CR2" s="24" t="n"/>
+      <c r="CS2" s="24" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
@@ -2171,6 +2179,7 @@
       <c r="CP3" s="24" t="n"/>
       <c r="CQ3" s="24" t="n"/>
       <c r="CR3" s="24" t="n"/>
+      <c r="CS3" s="24" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
@@ -2459,6 +2468,7 @@
       <c r="CP4" s="24" t="n"/>
       <c r="CQ4" s="24" t="n"/>
       <c r="CR4" s="24" t="n"/>
+      <c r="CS4" s="24" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
@@ -2747,6 +2757,7 @@
       <c r="CP5" s="24" t="n"/>
       <c r="CQ5" s="24" t="n"/>
       <c r="CR5" s="24" t="n"/>
+      <c r="CS5" s="24" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
@@ -3035,6 +3046,7 @@
       <c r="CP6" s="24" t="n"/>
       <c r="CQ6" s="24" t="n"/>
       <c r="CR6" s="24" t="n"/>
+      <c r="CS6" s="24" t="n"/>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
@@ -3323,6 +3335,7 @@
       <c r="CP7" s="24" t="n"/>
       <c r="CQ7" s="24" t="n"/>
       <c r="CR7" s="24" t="n"/>
+      <c r="CS7" s="24" t="n"/>
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
@@ -3611,6 +3624,7 @@
       <c r="CP8" s="24" t="n"/>
       <c r="CQ8" s="24" t="n"/>
       <c r="CR8" s="24" t="n"/>
+      <c r="CS8" s="24" t="n"/>
     </row>
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
@@ -3899,6 +3913,7 @@
       <c r="CP9" s="24" t="n"/>
       <c r="CQ9" s="24" t="n"/>
       <c r="CR9" s="24" t="n"/>
+      <c r="CS9" s="24" t="n"/>
     </row>
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
@@ -4187,6 +4202,7 @@
       <c r="CP10" s="24" t="n"/>
       <c r="CQ10" s="24" t="n"/>
       <c r="CR10" s="24" t="n"/>
+      <c r="CS10" s="24" t="n"/>
     </row>
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
@@ -4475,6 +4491,7 @@
       <c r="CP11" s="24" t="n"/>
       <c r="CQ11" s="24" t="n"/>
       <c r="CR11" s="24" t="n"/>
+      <c r="CS11" s="24" t="n"/>
     </row>
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
@@ -4763,6 +4780,7 @@
       <c r="CP12" s="24" t="n"/>
       <c r="CQ12" s="24" t="n"/>
       <c r="CR12" s="24" t="n"/>
+      <c r="CS12" s="24" t="n"/>
     </row>
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
@@ -5051,6 +5069,7 @@
       <c r="CP13" s="24" t="n"/>
       <c r="CQ13" s="24" t="n"/>
       <c r="CR13" s="24" t="n"/>
+      <c r="CS13" s="24" t="n"/>
     </row>
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="24" t="inlineStr">
@@ -5339,6 +5358,7 @@
       <c r="CP14" s="24" t="n"/>
       <c r="CQ14" s="24" t="n"/>
       <c r="CR14" s="24" t="n"/>
+      <c r="CS14" s="24" t="n"/>
     </row>
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="24" t="inlineStr">
@@ -5627,6 +5647,7 @@
       <c r="CP15" s="24" t="n"/>
       <c r="CQ15" s="24" t="n"/>
       <c r="CR15" s="24" t="n"/>
+      <c r="CS15" s="24" t="n"/>
     </row>
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="24" t="inlineStr">
@@ -5915,6 +5936,7 @@
       <c r="CP16" s="24" t="n"/>
       <c r="CQ16" s="24" t="n"/>
       <c r="CR16" s="24" t="n"/>
+      <c r="CS16" s="24" t="n"/>
     </row>
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="24" t="inlineStr">
@@ -6203,6 +6225,7 @@
       <c r="CP17" s="24" t="n"/>
       <c r="CQ17" s="24" t="n"/>
       <c r="CR17" s="24" t="n"/>
+      <c r="CS17" s="24" t="n"/>
     </row>
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="24" t="inlineStr">
@@ -6491,6 +6514,7 @@
       <c r="CP18" s="24" t="n"/>
       <c r="CQ18" s="24" t="n"/>
       <c r="CR18" s="24" t="n"/>
+      <c r="CS18" s="24" t="n"/>
     </row>
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="24" t="inlineStr">
@@ -6778,7 +6802,8 @@
       <c r="CO19" s="24" t="n"/>
       <c r="CP19" s="24" t="n"/>
       <c r="CQ19" s="24" t="n"/>
-      <c r="CR19" s="24" t="inlineStr">
+      <c r="CR19" s="24" t="n"/>
+      <c r="CS19" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -7070,7 +7095,8 @@
       <c r="CO20" s="24" t="n"/>
       <c r="CP20" s="24" t="n"/>
       <c r="CQ20" s="24" t="n"/>
-      <c r="CR20" s="24" t="inlineStr">
+      <c r="CR20" s="24" t="n"/>
+      <c r="CS20" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -7362,7 +7388,8 @@
       <c r="CO21" s="24" t="n"/>
       <c r="CP21" s="24" t="n"/>
       <c r="CQ21" s="24" t="n"/>
-      <c r="CR21" s="24" t="inlineStr">
+      <c r="CR21" s="24" t="n"/>
+      <c r="CS21" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -7654,7 +7681,8 @@
       <c r="CO22" s="24" t="n"/>
       <c r="CP22" s="24" t="n"/>
       <c r="CQ22" s="24" t="n"/>
-      <c r="CR22" s="24" t="inlineStr">
+      <c r="CR22" s="24" t="n"/>
+      <c r="CS22" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -7946,7 +7974,8 @@
       <c r="CO23" s="24" t="n"/>
       <c r="CP23" s="24" t="n"/>
       <c r="CQ23" s="24" t="n"/>
-      <c r="CR23" s="24" t="inlineStr">
+      <c r="CR23" s="24" t="n"/>
+      <c r="CS23" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -8238,7 +8267,8 @@
       <c r="CO24" s="24" t="n"/>
       <c r="CP24" s="24" t="n"/>
       <c r="CQ24" s="24" t="n"/>
-      <c r="CR24" s="24" t="inlineStr">
+      <c r="CR24" s="24" t="n"/>
+      <c r="CS24" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -8530,7 +8560,8 @@
       <c r="CO25" s="24" t="n"/>
       <c r="CP25" s="24" t="n"/>
       <c r="CQ25" s="24" t="n"/>
-      <c r="CR25" s="24" t="inlineStr">
+      <c r="CR25" s="24" t="n"/>
+      <c r="CS25" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -8822,7 +8853,8 @@
       <c r="CO26" s="24" t="n"/>
       <c r="CP26" s="24" t="n"/>
       <c r="CQ26" s="24" t="n"/>
-      <c r="CR26" s="24" t="inlineStr">
+      <c r="CR26" s="24" t="n"/>
+      <c r="CS26" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -9114,7 +9146,8 @@
       <c r="CO27" s="24" t="n"/>
       <c r="CP27" s="24" t="n"/>
       <c r="CQ27" s="24" t="n"/>
-      <c r="CR27" s="24" t="inlineStr">
+      <c r="CR27" s="24" t="n"/>
+      <c r="CS27" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -9406,7 +9439,8 @@
       <c r="CO28" s="24" t="n"/>
       <c r="CP28" s="24" t="n"/>
       <c r="CQ28" s="24" t="n"/>
-      <c r="CR28" s="24" t="inlineStr">
+      <c r="CR28" s="24" t="n"/>
+      <c r="CS28" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -9493,18 +9527,38 @@
       </c>
       <c r="U29" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V29" s="24" t="n"/>
-      <c r="W29" s="26" t="n"/>
-      <c r="X29" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V29" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W29" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y29" s="25" t="n"/>
-      <c r="Z29" s="26" t="n"/>
-      <c r="AA29" s="28" t="n"/>
-      <c r="AB29" s="28" t="n"/>
-      <c r="AC29" s="30" t="n"/>
-      <c r="AD29" s="24" t="n"/>
+      <c r="Z29" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="AA29" s="28" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AB29" s="28" t="n">
+        <v>0.000829</v>
+      </c>
+      <c r="AC29" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD29" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:58:03.728171Z</t>
+        </is>
+      </c>
       <c r="AE29" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-lol-t1-hle-2026-08-04).</t>
@@ -9517,7 +9571,7 @@
       </c>
       <c r="AG29" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH29" s="24" t="n"/>
@@ -9647,8 +9701,12 @@
       <c r="BN29" s="28" t="n"/>
       <c r="BO29" s="28" t="n"/>
       <c r="BP29" s="25" t="n"/>
-      <c r="BQ29" s="27" t="n"/>
-      <c r="BR29" s="28" t="n"/>
+      <c r="BQ29" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="BR29" s="28" t="n">
+        <v>0.54</v>
+      </c>
       <c r="BS29" s="28" t="n"/>
       <c r="BT29" s="28" t="n"/>
       <c r="BU29" s="25" t="n"/>
@@ -9674,7 +9732,8 @@
       <c r="CO29" s="24" t="n"/>
       <c r="CP29" s="24" t="n"/>
       <c r="CQ29" s="24" t="n"/>
-      <c r="CR29" s="24" t="inlineStr">
+      <c r="CR29" s="24" t="n"/>
+      <c r="CS29" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -9761,18 +9820,38 @@
       </c>
       <c r="U30" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V30" s="24" t="n"/>
-      <c r="W30" s="26" t="n"/>
-      <c r="X30" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V30" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W30" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y30" s="25" t="n"/>
-      <c r="Z30" s="26" t="n"/>
-      <c r="AA30" s="28" t="n"/>
-      <c r="AB30" s="28" t="n"/>
-      <c r="AC30" s="30" t="n"/>
-      <c r="AD30" s="24" t="n"/>
+      <c r="Z30" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="AA30" s="28" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AB30" s="28" t="n">
+        <v>-0.000402</v>
+      </c>
+      <c r="AC30" s="30" t="n">
+        <v>0.6726</v>
+      </c>
+      <c r="AD30" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:03:37.106120Z</t>
+        </is>
+      </c>
       <c r="AE30" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-lol-t1a-ktc-2026-08-04).</t>
@@ -9915,8 +9994,12 @@
       <c r="BN30" s="28" t="n"/>
       <c r="BO30" s="28" t="n"/>
       <c r="BP30" s="25" t="n"/>
-      <c r="BQ30" s="27" t="n"/>
-      <c r="BR30" s="28" t="n"/>
+      <c r="BQ30" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="BR30" s="28" t="n">
+        <v>0.6899999999999999</v>
+      </c>
       <c r="BS30" s="28" t="n"/>
       <c r="BT30" s="28" t="n"/>
       <c r="BU30" s="25" t="n"/>
@@ -9942,7 +10025,8 @@
       <c r="CO30" s="24" t="n"/>
       <c r="CP30" s="24" t="n"/>
       <c r="CQ30" s="24" t="n"/>
-      <c r="CR30" s="24" t="inlineStr">
+      <c r="CR30" s="24" t="n"/>
+      <c r="CS30" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -10029,18 +10113,38 @@
       </c>
       <c r="U31" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V31" s="24" t="n"/>
-      <c r="W31" s="26" t="n"/>
-      <c r="X31" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V31" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W31" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X31" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y31" s="25" t="n"/>
-      <c r="Z31" s="26" t="n"/>
-      <c r="AA31" s="28" t="n"/>
-      <c r="AB31" s="28" t="n"/>
-      <c r="AC31" s="30" t="n"/>
-      <c r="AD31" s="24" t="n"/>
+      <c r="Z31" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="AA31" s="28" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AB31" s="28" t="n">
+        <v>0.00037</v>
+      </c>
+      <c r="AC31" s="30" t="n">
+        <v>0.7353</v>
+      </c>
+      <c r="AD31" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:03:38.702339Z</t>
+        </is>
+      </c>
       <c r="AE31" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-lol-bro-krx-2026-08-04).</t>
@@ -10183,8 +10287,12 @@
       <c r="BN31" s="28" t="n"/>
       <c r="BO31" s="28" t="n"/>
       <c r="BP31" s="25" t="n"/>
-      <c r="BQ31" s="27" t="n"/>
-      <c r="BR31" s="28" t="n"/>
+      <c r="BQ31" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="BR31" s="28" t="n">
+        <v>0.63</v>
+      </c>
       <c r="BS31" s="28" t="n"/>
       <c r="BT31" s="28" t="n"/>
       <c r="BU31" s="25" t="n"/>
@@ -10210,7 +10318,8 @@
       <c r="CO31" s="24" t="n"/>
       <c r="CP31" s="24" t="n"/>
       <c r="CQ31" s="24" t="n"/>
-      <c r="CR31" s="24" t="inlineStr">
+      <c r="CR31" s="24" t="n"/>
+      <c r="CS31" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -10219,12 +10328,12 @@
     <row r="32" ht="36" customHeight="1">
       <c r="A32" s="24" t="inlineStr">
         <is>
-          <t>e8f0590f77774c6c</t>
+          <t>fb6bd2135f56449e</t>
         </is>
       </c>
       <c r="B32" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:56.469660Z</t>
+          <t>2026-08-04T14:27:16.244146Z</t>
         </is>
       </c>
       <c r="C32" s="24" t="inlineStr">
@@ -10234,7 +10343,7 @@
       </c>
       <c r="D32" s="24" t="inlineStr">
         <is>
-          <t>68510</t>
+          <t>68509</t>
         </is>
       </c>
       <c r="E32" s="24" t="inlineStr">
@@ -10244,12 +10353,12 @@
       </c>
       <c r="F32" s="24" t="inlineStr">
         <is>
-          <t>The Secret Club</t>
+          <t>Skillcamp Esport</t>
         </is>
       </c>
       <c r="G32" s="24" t="inlineStr">
         <is>
-          <t>MAGAZA</t>
+          <t>Ici Japon Corp. Esport</t>
         </is>
       </c>
       <c r="H32" s="24" t="inlineStr">
@@ -10269,26 +10378,26 @@
         </is>
       </c>
       <c r="L32" s="26" t="n">
-        <v>144</v>
+        <v>-138</v>
       </c>
       <c r="M32" s="27" t="n">
-        <v>2.44</v>
+        <v>1.724638</v>
       </c>
       <c r="N32" s="28" t="n">
-        <v>0.409836</v>
+        <v>0.579832</v>
       </c>
       <c r="O32" s="28" t="n">
-        <v>0.517061</v>
+        <v>0.631258</v>
       </c>
       <c r="P32" s="28" t="n"/>
       <c r="Q32" s="28" t="n">
-        <v>0.107225</v>
+        <v>0.051426</v>
       </c>
       <c r="R32" s="26" t="n">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="S32" s="29" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="T32" s="24" t="inlineStr">
         <is>
@@ -10311,7 +10420,7 @@
       <c r="AD32" s="24" t="n"/>
       <c r="AE32" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4100 (market_slug=aec-lol-mgz-tsc-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-lol-ijc-sc-2026-08-04).</t>
         </is>
       </c>
       <c r="AF32" s="31" t="inlineStr">
@@ -10329,7 +10438,7 @@
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL32" s="26" t="n">
@@ -10337,47 +10446,47 @@
       </c>
       <c r="AM32" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN32" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO32" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP32" s="24" t="inlineStr">
         <is>
-          <t>The Secret Club</t>
+          <t>Skillcamp Esport</t>
         </is>
       </c>
       <c r="AQ32" s="24" t="inlineStr">
         <is>
-          <t>The Secret Club</t>
+          <t>Skillcamp Esport</t>
         </is>
       </c>
       <c r="AR32" s="24" t="inlineStr">
         <is>
-          <t>The Secret Club</t>
+          <t>Skillcamp Esport</t>
         </is>
       </c>
       <c r="AS32" s="24" t="inlineStr">
         <is>
-          <t>MAGAZA</t>
+          <t>Ici Japon Corp. Esport</t>
         </is>
       </c>
       <c r="AT32" s="24" t="inlineStr">
         <is>
-          <t>MAGAZA</t>
+          <t>Ici Japon Corp. Esport</t>
         </is>
       </c>
       <c r="AU32" s="24" t="inlineStr">
         <is>
-          <t>MAGAZA</t>
+          <t>Ici Japon Corp. Esport</t>
         </is>
       </c>
       <c r="AV32" s="24" t="n"/>
@@ -10395,7 +10504,7 @@
       </c>
       <c r="BA32" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BB32" s="24" t="inlineStr">
@@ -10410,7 +10519,7 @@
       </c>
       <c r="BD32" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BE32" s="24" t="inlineStr">
@@ -10430,7 +10539,7 @@
       </c>
       <c r="BH32" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:24.555143Z</t>
+          <t>2026-08-04T14:26:42.602034Z</t>
         </is>
       </c>
       <c r="BI32" s="24" t="inlineStr">
@@ -10440,13 +10549,13 @@
       </c>
       <c r="BJ32" s="25" t="n"/>
       <c r="BK32" s="26" t="n">
-        <v>144</v>
+        <v>-138</v>
       </c>
       <c r="BL32" s="27" t="n">
-        <v>2.44</v>
+        <v>1.724638</v>
       </c>
       <c r="BM32" s="28" t="n">
-        <v>0.409836</v>
+        <v>0.579832</v>
       </c>
       <c r="BN32" s="28" t="n"/>
       <c r="BO32" s="28" t="n"/>
@@ -10478,7 +10587,8 @@
       <c r="CO32" s="24" t="n"/>
       <c r="CP32" s="24" t="n"/>
       <c r="CQ32" s="24" t="n"/>
-      <c r="CR32" s="24" t="inlineStr">
+      <c r="CR32" s="24" t="n"/>
+      <c r="CS32" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -10487,22 +10597,22 @@
     <row r="33" ht="36" customHeight="1">
       <c r="A33" s="24" t="inlineStr">
         <is>
-          <t>0d452ec569fa4063</t>
+          <t>ba634685d7f54308</t>
         </is>
       </c>
       <c r="B33" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:56.469660Z</t>
+          <t>2026-08-04T14:27:16.244146Z</t>
         </is>
       </c>
       <c r="C33" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T16:00:00Z</t>
+          <t>2026-08-04T17:00:00Z</t>
         </is>
       </c>
       <c r="D33" s="24" t="inlineStr">
         <is>
-          <t>68509</t>
+          <t>70567</t>
         </is>
       </c>
       <c r="E33" s="24" t="inlineStr">
@@ -10512,12 +10622,12 @@
       </c>
       <c r="F33" s="24" t="inlineStr">
         <is>
-          <t>Skillcamp Esport</t>
+          <t>Anonymo Esports</t>
         </is>
       </c>
       <c r="G33" s="24" t="inlineStr">
         <is>
-          <t>Ici Japon Corp. Esport</t>
+          <t>DOCISK</t>
         </is>
       </c>
       <c r="H33" s="24" t="inlineStr">
@@ -10537,26 +10647,26 @@
         </is>
       </c>
       <c r="L33" s="26" t="n">
-        <v>-108</v>
+        <v>163</v>
       </c>
       <c r="M33" s="27" t="n">
-        <v>1.925926</v>
+        <v>2.63</v>
       </c>
       <c r="N33" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.380228</v>
       </c>
       <c r="O33" s="28" t="n">
-        <v>0.631317</v>
+        <v>0.518929</v>
       </c>
       <c r="P33" s="28" t="n"/>
       <c r="Q33" s="28" t="n">
-        <v>0.112086</v>
+        <v>0.138701</v>
       </c>
       <c r="R33" s="26" t="n">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="S33" s="29" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="T33" s="24" t="inlineStr">
         <is>
@@ -10579,7 +10689,7 @@
       <c r="AD33" s="24" t="n"/>
       <c r="AE33" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5200 (market_slug=aec-lol-ijc-sc-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.3800 (market_slug=aec-lol-doc-ae-2026-08-04).</t>
         </is>
       </c>
       <c r="AF33" s="31" t="inlineStr">
@@ -10597,7 +10707,7 @@
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL33" s="26" t="n">
@@ -10605,47 +10715,47 @@
       </c>
       <c r="AM33" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN33" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO33" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP33" s="24" t="inlineStr">
         <is>
-          <t>Skillcamp Esport</t>
+          <t>Anonymo Esports</t>
         </is>
       </c>
       <c r="AQ33" s="24" t="inlineStr">
         <is>
-          <t>Skillcamp Esport</t>
+          <t>Anonymo Esports</t>
         </is>
       </c>
       <c r="AR33" s="24" t="inlineStr">
         <is>
-          <t>Skillcamp Esport</t>
+          <t>Anonymo Esports</t>
         </is>
       </c>
       <c r="AS33" s="24" t="inlineStr">
         <is>
-          <t>Ici Japon Corp. Esport</t>
+          <t>DOCISK</t>
         </is>
       </c>
       <c r="AT33" s="24" t="inlineStr">
         <is>
-          <t>Ici Japon Corp. Esport</t>
+          <t>DOCISK</t>
         </is>
       </c>
       <c r="AU33" s="24" t="inlineStr">
         <is>
-          <t>Ici Japon Corp. Esport</t>
+          <t>DOCISK</t>
         </is>
       </c>
       <c r="AV33" s="24" t="n"/>
@@ -10663,7 +10773,7 @@
       </c>
       <c r="BA33" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BB33" s="24" t="inlineStr">
@@ -10678,7 +10788,7 @@
       </c>
       <c r="BD33" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BE33" s="24" t="inlineStr">
@@ -10698,7 +10808,7 @@
       </c>
       <c r="BH33" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:25.701342Z</t>
+          <t>2026-08-04T14:26:43.221842Z</t>
         </is>
       </c>
       <c r="BI33" s="24" t="inlineStr">
@@ -10708,13 +10818,13 @@
       </c>
       <c r="BJ33" s="25" t="n"/>
       <c r="BK33" s="26" t="n">
-        <v>-108</v>
+        <v>163</v>
       </c>
       <c r="BL33" s="27" t="n">
-        <v>1.925926</v>
+        <v>2.63</v>
       </c>
       <c r="BM33" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.380228</v>
       </c>
       <c r="BN33" s="28" t="n"/>
       <c r="BO33" s="28" t="n"/>
@@ -10746,7 +10856,8 @@
       <c r="CO33" s="24" t="n"/>
       <c r="CP33" s="24" t="n"/>
       <c r="CQ33" s="24" t="n"/>
-      <c r="CR33" s="24" t="inlineStr">
+      <c r="CR33" s="24" t="n"/>
+      <c r="CS33" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -10755,22 +10866,22 @@
     <row r="34" ht="36" customHeight="1">
       <c r="A34" s="24" t="inlineStr">
         <is>
-          <t>d841c1d7a3e94d90</t>
+          <t>ba6f42c2b0594545</t>
         </is>
       </c>
       <c r="B34" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:56.469660Z</t>
+          <t>2026-08-04T14:27:16.244146Z</t>
         </is>
       </c>
       <c r="C34" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T17:00:00Z</t>
+          <t>2026-08-04T18:00:00Z</t>
         </is>
       </c>
       <c r="D34" s="24" t="inlineStr">
         <is>
-          <t>70567</t>
+          <t>68690</t>
         </is>
       </c>
       <c r="E34" s="24" t="inlineStr">
@@ -10780,12 +10891,12 @@
       </c>
       <c r="F34" s="24" t="inlineStr">
         <is>
-          <t>Anonymo Esports</t>
+          <t>Lupus Esports</t>
         </is>
       </c>
       <c r="G34" s="24" t="inlineStr">
         <is>
-          <t>DOCISK</t>
+          <t xml:space="preserve">Croatian Flair x RLX </t>
         </is>
       </c>
       <c r="H34" s="24" t="inlineStr">
@@ -10805,23 +10916,23 @@
         </is>
       </c>
       <c r="L34" s="26" t="n">
-        <v>163</v>
+        <v>-117</v>
       </c>
       <c r="M34" s="27" t="n">
-        <v>2.63</v>
+        <v>1.854701</v>
       </c>
       <c r="N34" s="28" t="n">
-        <v>0.380228</v>
+        <v>0.539171</v>
       </c>
       <c r="O34" s="28" t="n">
-        <v>0.518338</v>
+        <v>0.5509500000000001</v>
       </c>
       <c r="P34" s="28" t="n"/>
       <c r="Q34" s="28" t="n">
-        <v>0.13811</v>
+        <v>0.011779</v>
       </c>
       <c r="R34" s="26" t="n">
-        <v>89</v>
+        <v>26</v>
       </c>
       <c r="S34" s="29" t="n">
         <v>1</v>
@@ -10847,7 +10958,7 @@
       <c r="AD34" s="24" t="n"/>
       <c r="AE34" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3800 (market_slug=aec-lol-doc-ae-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-lol-cfxr-lps-2026-08-04).</t>
         </is>
       </c>
       <c r="AF34" s="31" t="inlineStr">
@@ -10865,7 +10976,7 @@
       <c r="AJ34" s="31" t="n"/>
       <c r="AK34" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL34" s="26" t="n">
@@ -10873,47 +10984,47 @@
       </c>
       <c r="AM34" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN34" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO34" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP34" s="24" t="inlineStr">
         <is>
-          <t>Anonymo Esports</t>
+          <t>Lupus Esports</t>
         </is>
       </c>
       <c r="AQ34" s="24" t="inlineStr">
         <is>
-          <t>Anonymo Esports</t>
+          <t>Lupus Esports</t>
         </is>
       </c>
       <c r="AR34" s="24" t="inlineStr">
         <is>
-          <t>Anonymo Esports</t>
+          <t>Lupus Esports</t>
         </is>
       </c>
       <c r="AS34" s="24" t="inlineStr">
         <is>
-          <t>DOCISK</t>
+          <t xml:space="preserve">Croatian Flair x RLX </t>
         </is>
       </c>
       <c r="AT34" s="24" t="inlineStr">
         <is>
-          <t>DOCISK</t>
+          <t xml:space="preserve">Croatian Flair x RLX </t>
         </is>
       </c>
       <c r="AU34" s="24" t="inlineStr">
         <is>
-          <t>DOCISK</t>
+          <t xml:space="preserve">Croatian Flair x RLX </t>
         </is>
       </c>
       <c r="AV34" s="24" t="n"/>
@@ -10931,7 +11042,7 @@
       </c>
       <c r="BA34" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BB34" s="24" t="inlineStr">
@@ -10946,7 +11057,7 @@
       </c>
       <c r="BD34" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BE34" s="24" t="inlineStr">
@@ -10966,7 +11077,7 @@
       </c>
       <c r="BH34" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:26.316476Z</t>
+          <t>2026-08-04T14:26:46.197810Z</t>
         </is>
       </c>
       <c r="BI34" s="24" t="inlineStr">
@@ -10976,13 +11087,13 @@
       </c>
       <c r="BJ34" s="25" t="n"/>
       <c r="BK34" s="26" t="n">
-        <v>163</v>
+        <v>-117</v>
       </c>
       <c r="BL34" s="27" t="n">
-        <v>2.63</v>
+        <v>1.854701</v>
       </c>
       <c r="BM34" s="28" t="n">
-        <v>0.380228</v>
+        <v>0.539171</v>
       </c>
       <c r="BN34" s="28" t="n"/>
       <c r="BO34" s="28" t="n"/>
@@ -11014,7 +11125,8 @@
       <c r="CO34" s="24" t="n"/>
       <c r="CP34" s="24" t="n"/>
       <c r="CQ34" s="24" t="n"/>
-      <c r="CR34" s="24" t="inlineStr">
+      <c r="CR34" s="24" t="n"/>
+      <c r="CS34" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -11023,12 +11135,12 @@
     <row r="35" ht="36" customHeight="1">
       <c r="A35" s="24" t="inlineStr">
         <is>
-          <t>2290407cea2e4a40</t>
+          <t>6e19a704e2354ee7</t>
         </is>
       </c>
       <c r="B35" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:56.469660Z</t>
+          <t>2026-08-04T14:27:16.244146Z</t>
         </is>
       </c>
       <c r="C35" s="24" t="inlineStr">
@@ -11082,11 +11194,11 @@
         <v>0.669967</v>
       </c>
       <c r="O35" s="28" t="n">
-        <v>0.549366</v>
+        <v>0.548411</v>
       </c>
       <c r="P35" s="28" t="n"/>
       <c r="Q35" s="28" t="n">
-        <v>-0.120601</v>
+        <v>-0.121556</v>
       </c>
       <c r="R35" s="26" t="n">
         <v>0</v>
@@ -11199,7 +11311,7 @@
       </c>
       <c r="BA35" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BB35" s="24" t="inlineStr">
@@ -11214,7 +11326,7 @@
       </c>
       <c r="BD35" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BE35" s="24" t="inlineStr">
@@ -11234,7 +11346,7 @@
       </c>
       <c r="BH35" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:29.255997Z</t>
+          <t>2026-08-04T14:26:46.778646Z</t>
         </is>
       </c>
       <c r="BI35" s="24" t="inlineStr">
@@ -11282,7 +11394,8 @@
       <c r="CO35" s="24" t="n"/>
       <c r="CP35" s="24" t="n"/>
       <c r="CQ35" s="24" t="n"/>
-      <c r="CR35" s="24" t="inlineStr">
+      <c r="CR35" s="24" t="n"/>
+      <c r="CS35" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -11291,12 +11404,12 @@
     <row r="36" ht="36" customHeight="1">
       <c r="A36" s="24" t="inlineStr">
         <is>
-          <t>c267f2c13c334c73</t>
+          <t>d2f73455072e477f</t>
         </is>
       </c>
       <c r="B36" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:56.469660Z</t>
+          <t>2026-08-04T14:27:16.244146Z</t>
         </is>
       </c>
       <c r="C36" s="24" t="inlineStr">
@@ -11306,7 +11419,7 @@
       </c>
       <c r="D36" s="24" t="inlineStr">
         <is>
-          <t>68690</t>
+          <t>68689</t>
         </is>
       </c>
       <c r="E36" s="24" t="inlineStr">
@@ -11316,12 +11429,12 @@
       </c>
       <c r="F36" s="24" t="inlineStr">
         <is>
-          <t>Lupus Esports</t>
+          <t>Way Gaming Esports</t>
         </is>
       </c>
       <c r="G36" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Croatian Flair x RLX </t>
+          <t>Capybara Esports</t>
         </is>
       </c>
       <c r="H36" s="24" t="inlineStr">
@@ -11341,26 +11454,26 @@
         </is>
       </c>
       <c r="L36" s="26" t="n">
-        <v>-117</v>
+        <v>-194</v>
       </c>
       <c r="M36" s="27" t="n">
-        <v>1.854701</v>
+        <v>1.515464</v>
       </c>
       <c r="N36" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.659864</v>
       </c>
       <c r="O36" s="28" t="n">
-        <v>0.55055</v>
+        <v>0.574199</v>
       </c>
       <c r="P36" s="28" t="n"/>
       <c r="Q36" s="28" t="n">
-        <v>0.011379</v>
+        <v>-0.08566500000000001</v>
       </c>
       <c r="R36" s="26" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="S36" s="29" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="T36" s="24" t="inlineStr">
         <is>
@@ -11383,7 +11496,7 @@
       <c r="AD36" s="24" t="n"/>
       <c r="AE36" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-lol-cfxr-lps-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.6600 (market_slug=aec-lol-capy-wge-2026-08-04).</t>
         </is>
       </c>
       <c r="AF36" s="31" t="inlineStr">
@@ -11401,7 +11514,7 @@
       <c r="AJ36" s="31" t="n"/>
       <c r="AK36" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL36" s="26" t="n">
@@ -11409,47 +11522,47 @@
       </c>
       <c r="AM36" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN36" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO36" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP36" s="24" t="inlineStr">
         <is>
-          <t>Lupus Esports</t>
+          <t>Way Gaming Esports</t>
         </is>
       </c>
       <c r="AQ36" s="24" t="inlineStr">
         <is>
-          <t>Lupus Esports</t>
+          <t>Way Gaming Esports</t>
         </is>
       </c>
       <c r="AR36" s="24" t="inlineStr">
         <is>
-          <t>Lupus Esports</t>
+          <t>Way Gaming Esports</t>
         </is>
       </c>
       <c r="AS36" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Croatian Flair x RLX </t>
+          <t>Capybara Esports</t>
         </is>
       </c>
       <c r="AT36" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Croatian Flair x RLX </t>
+          <t>Capybara Esports</t>
         </is>
       </c>
       <c r="AU36" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Croatian Flair x RLX </t>
+          <t>Capybara Esports</t>
         </is>
       </c>
       <c r="AV36" s="24" t="n"/>
@@ -11467,7 +11580,7 @@
       </c>
       <c r="BA36" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BB36" s="24" t="inlineStr">
@@ -11482,7 +11595,7 @@
       </c>
       <c r="BD36" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BE36" s="24" t="inlineStr">
@@ -11502,7 +11615,7 @@
       </c>
       <c r="BH36" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:29.939077Z</t>
+          <t>2026-08-04T14:26:47.518880Z</t>
         </is>
       </c>
       <c r="BI36" s="24" t="inlineStr">
@@ -11512,13 +11625,13 @@
       </c>
       <c r="BJ36" s="25" t="n"/>
       <c r="BK36" s="26" t="n">
-        <v>-117</v>
+        <v>-194</v>
       </c>
       <c r="BL36" s="27" t="n">
-        <v>1.854701</v>
+        <v>1.515464</v>
       </c>
       <c r="BM36" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.659864</v>
       </c>
       <c r="BN36" s="28" t="n"/>
       <c r="BO36" s="28" t="n"/>
@@ -11550,21 +11663,22 @@
       <c r="CO36" s="24" t="n"/>
       <c r="CP36" s="24" t="n"/>
       <c r="CQ36" s="24" t="n"/>
-      <c r="CR36" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
+      <c r="CR36" s="24" t="n"/>
+      <c r="CS36" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="37" ht="36" customHeight="1">
       <c r="A37" s="24" t="inlineStr">
         <is>
-          <t>7c565f020050418f</t>
+          <t>c960e25408ee47e1</t>
         </is>
       </c>
       <c r="B37" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:56.469660Z</t>
+          <t>2026-08-04T14:27:16.244146Z</t>
         </is>
       </c>
       <c r="C37" s="24" t="inlineStr">
@@ -11574,7 +11688,7 @@
       </c>
       <c r="D37" s="24" t="inlineStr">
         <is>
-          <t>68689</t>
+          <t>68688</t>
         </is>
       </c>
       <c r="E37" s="24" t="inlineStr">
@@ -11584,12 +11698,12 @@
       </c>
       <c r="F37" s="24" t="inlineStr">
         <is>
-          <t>Way Gaming Esports</t>
+          <t>Joblife</t>
         </is>
       </c>
       <c r="G37" s="24" t="inlineStr">
         <is>
-          <t>Capybara Esports</t>
+          <t>ZYB Esport</t>
         </is>
       </c>
       <c r="H37" s="24" t="inlineStr">
@@ -11599,7 +11713,7 @@
       </c>
       <c r="I37" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J37" s="25" t="n"/>
@@ -11609,26 +11723,26 @@
         </is>
       </c>
       <c r="L37" s="26" t="n">
-        <v>-150</v>
+        <v>-117</v>
       </c>
       <c r="M37" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.854701</v>
       </c>
       <c r="N37" s="28" t="n">
-        <v>0.6</v>
+        <v>0.539171</v>
       </c>
       <c r="O37" s="28" t="n">
-        <v>0.5739340000000001</v>
+        <v>0.5301439999999999</v>
       </c>
       <c r="P37" s="28" t="n"/>
       <c r="Q37" s="28" t="n">
-        <v>-0.026066</v>
+        <v>-0.009027</v>
       </c>
       <c r="R37" s="26" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="S37" s="29" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="T37" s="24" t="inlineStr">
         <is>
@@ -11651,7 +11765,7 @@
       <c r="AD37" s="24" t="n"/>
       <c r="AE37" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-lol-capy-wge-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-lol-zyb-jl-2026-08-04).</t>
         </is>
       </c>
       <c r="AF37" s="31" t="inlineStr">
@@ -11692,32 +11806,32 @@
       </c>
       <c r="AP37" s="24" t="inlineStr">
         <is>
-          <t>Way Gaming Esports</t>
+          <t>Joblife</t>
         </is>
       </c>
       <c r="AQ37" s="24" t="inlineStr">
         <is>
-          <t>Way Gaming Esports</t>
+          <t>Joblife</t>
         </is>
       </c>
       <c r="AR37" s="24" t="inlineStr">
         <is>
-          <t>Way Gaming Esports</t>
+          <t>Joblife</t>
         </is>
       </c>
       <c r="AS37" s="24" t="inlineStr">
         <is>
-          <t>Capybara Esports</t>
+          <t>ZYB Esport</t>
         </is>
       </c>
       <c r="AT37" s="24" t="inlineStr">
         <is>
-          <t>Capybara Esports</t>
+          <t>ZYB Esport</t>
         </is>
       </c>
       <c r="AU37" s="24" t="inlineStr">
         <is>
-          <t>Capybara Esports</t>
+          <t>ZYB Esport</t>
         </is>
       </c>
       <c r="AV37" s="24" t="n"/>
@@ -11735,7 +11849,7 @@
       </c>
       <c r="BA37" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BB37" s="24" t="inlineStr">
@@ -11750,7 +11864,7 @@
       </c>
       <c r="BD37" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BE37" s="24" t="inlineStr">
@@ -11770,7 +11884,7 @@
       </c>
       <c r="BH37" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:30.477262Z</t>
+          <t>2026-08-04T14:26:48.052918Z</t>
         </is>
       </c>
       <c r="BI37" s="24" t="inlineStr">
@@ -11780,13 +11894,13 @@
       </c>
       <c r="BJ37" s="25" t="n"/>
       <c r="BK37" s="26" t="n">
-        <v>-150</v>
+        <v>-117</v>
       </c>
       <c r="BL37" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.854701</v>
       </c>
       <c r="BM37" s="28" t="n">
-        <v>0.6</v>
+        <v>0.539171</v>
       </c>
       <c r="BN37" s="28" t="n"/>
       <c r="BO37" s="28" t="n"/>
@@ -11818,7 +11932,8 @@
       <c r="CO37" s="24" t="n"/>
       <c r="CP37" s="24" t="n"/>
       <c r="CQ37" s="24" t="n"/>
-      <c r="CR37" s="24" t="inlineStr">
+      <c r="CR37" s="24" t="n"/>
+      <c r="CS37" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -11827,22 +11942,22 @@
     <row r="38" ht="36" customHeight="1">
       <c r="A38" s="24" t="inlineStr">
         <is>
-          <t>ecc521fbceea451e</t>
+          <t>0bf756b7a98a4d63</t>
         </is>
       </c>
       <c r="B38" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:56.469660Z</t>
+          <t>2026-08-04T14:27:16.244146Z</t>
         </is>
       </c>
       <c r="C38" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T18:00:00Z</t>
+          <t>2026-08-04T20:00:00Z</t>
         </is>
       </c>
       <c r="D38" s="24" t="inlineStr">
         <is>
-          <t>68688</t>
+          <t>69143</t>
         </is>
       </c>
       <c r="E38" s="24" t="inlineStr">
@@ -11852,12 +11967,12 @@
       </c>
       <c r="F38" s="24" t="inlineStr">
         <is>
-          <t>Joblife</t>
+          <t>Malvinas Gaming</t>
         </is>
       </c>
       <c r="G38" s="24" t="inlineStr">
         <is>
-          <t>ZYB Esport</t>
+          <t>Maze Gaming</t>
         </is>
       </c>
       <c r="H38" s="24" t="inlineStr">
@@ -11867,7 +11982,7 @@
       </c>
       <c r="I38" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J38" s="25" t="n"/>
@@ -11877,26 +11992,26 @@
         </is>
       </c>
       <c r="L38" s="26" t="n">
-        <v>-122</v>
+        <v>-163</v>
       </c>
       <c r="M38" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.613497</v>
       </c>
       <c r="N38" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.619772</v>
       </c>
       <c r="O38" s="28" t="n">
-        <v>0.531003</v>
+        <v>0.624122</v>
       </c>
       <c r="P38" s="28" t="n"/>
       <c r="Q38" s="28" t="n">
-        <v>-0.018547</v>
+        <v>0.00435</v>
       </c>
       <c r="R38" s="26" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="S38" s="29" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="T38" s="24" t="inlineStr">
         <is>
@@ -11919,7 +12034,7 @@
       <c r="AD38" s="24" t="n"/>
       <c r="AE38" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-lol-zyb-jl-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-lol-maz-mg-2026-08-04).</t>
         </is>
       </c>
       <c r="AF38" s="31" t="inlineStr">
@@ -11937,7 +12052,7 @@
       <c r="AJ38" s="31" t="n"/>
       <c r="AK38" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL38" s="26" t="n">
@@ -11945,47 +12060,47 @@
       </c>
       <c r="AM38" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN38" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO38" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP38" s="24" t="inlineStr">
         <is>
-          <t>Joblife</t>
+          <t>Malvinas Gaming</t>
         </is>
       </c>
       <c r="AQ38" s="24" t="inlineStr">
         <is>
-          <t>Joblife</t>
+          <t>Malvinas Gaming</t>
         </is>
       </c>
       <c r="AR38" s="24" t="inlineStr">
         <is>
-          <t>Joblife</t>
+          <t>Malvinas Gaming</t>
         </is>
       </c>
       <c r="AS38" s="24" t="inlineStr">
         <is>
-          <t>ZYB Esport</t>
+          <t>Maze Gaming</t>
         </is>
       </c>
       <c r="AT38" s="24" t="inlineStr">
         <is>
-          <t>ZYB Esport</t>
+          <t>Maze Gaming</t>
         </is>
       </c>
       <c r="AU38" s="24" t="inlineStr">
         <is>
-          <t>ZYB Esport</t>
+          <t>Maze Gaming</t>
         </is>
       </c>
       <c r="AV38" s="24" t="n"/>
@@ -12003,7 +12118,7 @@
       </c>
       <c r="BA38" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BB38" s="24" t="inlineStr">
@@ -12018,7 +12133,7 @@
       </c>
       <c r="BD38" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BE38" s="24" t="inlineStr">
@@ -12038,7 +12153,7 @@
       </c>
       <c r="BH38" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:31.160482Z</t>
+          <t>2026-08-04T14:26:50.250119Z</t>
         </is>
       </c>
       <c r="BI38" s="24" t="inlineStr">
@@ -12048,13 +12163,13 @@
       </c>
       <c r="BJ38" s="25" t="n"/>
       <c r="BK38" s="26" t="n">
-        <v>-122</v>
+        <v>-163</v>
       </c>
       <c r="BL38" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.613497</v>
       </c>
       <c r="BM38" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.619772</v>
       </c>
       <c r="BN38" s="28" t="n"/>
       <c r="BO38" s="28" t="n"/>
@@ -12086,21 +12201,22 @@
       <c r="CO38" s="24" t="n"/>
       <c r="CP38" s="24" t="n"/>
       <c r="CQ38" s="24" t="n"/>
-      <c r="CR38" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
+      <c r="CR38" s="24" t="n"/>
+      <c r="CS38" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="39" ht="36" customHeight="1">
       <c r="A39" s="24" t="inlineStr">
         <is>
-          <t>a0f91ef42338491d</t>
+          <t>165d28ee04c74574</t>
         </is>
       </c>
       <c r="B39" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:56.469660Z</t>
+          <t>2026-08-04T14:27:16.244146Z</t>
         </is>
       </c>
       <c r="C39" s="24" t="inlineStr">
@@ -12110,7 +12226,7 @@
       </c>
       <c r="D39" s="24" t="inlineStr">
         <is>
-          <t>69143</t>
+          <t>69144</t>
         </is>
       </c>
       <c r="E39" s="24" t="inlineStr">
@@ -12120,12 +12236,12 @@
       </c>
       <c r="F39" s="24" t="inlineStr">
         <is>
-          <t>Malvinas Gaming</t>
+          <t>INTZ e-Sports</t>
         </is>
       </c>
       <c r="G39" s="24" t="inlineStr">
         <is>
-          <t>Maze Gaming</t>
+          <t>Vivo Keyd Stars Academy</t>
         </is>
       </c>
       <c r="H39" s="24" t="inlineStr">
@@ -12145,26 +12261,26 @@
         </is>
       </c>
       <c r="L39" s="26" t="n">
-        <v>-163</v>
+        <v>117</v>
       </c>
       <c r="M39" s="27" t="n">
-        <v>1.613497</v>
+        <v>2.17</v>
       </c>
       <c r="N39" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.460829</v>
       </c>
       <c r="O39" s="28" t="n">
-        <v>0.624143</v>
+        <v>0.5918</v>
       </c>
       <c r="P39" s="28" t="n"/>
       <c r="Q39" s="28" t="n">
-        <v>0.004371</v>
+        <v>0.130971</v>
       </c>
       <c r="R39" s="26" t="n">
-        <v>22</v>
+        <v>85</v>
       </c>
       <c r="S39" s="29" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="T39" s="24" t="inlineStr">
         <is>
@@ -12187,7 +12303,7 @@
       <c r="AD39" s="24" t="n"/>
       <c r="AE39" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-lol-maz-mg-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-lol-vksa-itz-2026-08-04).</t>
         </is>
       </c>
       <c r="AF39" s="31" t="inlineStr">
@@ -12228,32 +12344,32 @@
       </c>
       <c r="AP39" s="24" t="inlineStr">
         <is>
-          <t>Malvinas Gaming</t>
+          <t>INTZ e-Sports</t>
         </is>
       </c>
       <c r="AQ39" s="24" t="inlineStr">
         <is>
-          <t>Malvinas Gaming</t>
+          <t>INTZ e-Sports</t>
         </is>
       </c>
       <c r="AR39" s="24" t="inlineStr">
         <is>
-          <t>Malvinas Gaming</t>
+          <t>INTZ e-Sports</t>
         </is>
       </c>
       <c r="AS39" s="24" t="inlineStr">
         <is>
-          <t>Maze Gaming</t>
+          <t>Vivo Keyd Stars Academy</t>
         </is>
       </c>
       <c r="AT39" s="24" t="inlineStr">
         <is>
-          <t>Maze Gaming</t>
+          <t>Vivo Keyd Stars Academy</t>
         </is>
       </c>
       <c r="AU39" s="24" t="inlineStr">
         <is>
-          <t>Maze Gaming</t>
+          <t>Vivo Keyd Stars Academy</t>
         </is>
       </c>
       <c r="AV39" s="24" t="n"/>
@@ -12271,7 +12387,7 @@
       </c>
       <c r="BA39" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BB39" s="24" t="inlineStr">
@@ -12286,7 +12402,7 @@
       </c>
       <c r="BD39" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BE39" s="24" t="inlineStr">
@@ -12306,7 +12422,7 @@
       </c>
       <c r="BH39" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:34.284466Z</t>
+          <t>2026-08-04T14:26:50.876512Z</t>
         </is>
       </c>
       <c r="BI39" s="24" t="inlineStr">
@@ -12316,13 +12432,13 @@
       </c>
       <c r="BJ39" s="25" t="n"/>
       <c r="BK39" s="26" t="n">
-        <v>-163</v>
+        <v>117</v>
       </c>
       <c r="BL39" s="27" t="n">
-        <v>1.613497</v>
+        <v>2.17</v>
       </c>
       <c r="BM39" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.460829</v>
       </c>
       <c r="BN39" s="28" t="n"/>
       <c r="BO39" s="28" t="n"/>
@@ -12354,7 +12470,8 @@
       <c r="CO39" s="24" t="n"/>
       <c r="CP39" s="24" t="n"/>
       <c r="CQ39" s="24" t="n"/>
-      <c r="CR39" s="24" t="inlineStr">
+      <c r="CR39" s="24" t="n"/>
+      <c r="CS39" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -12363,12 +12480,12 @@
     <row r="40" ht="36" customHeight="1">
       <c r="A40" s="24" t="inlineStr">
         <is>
-          <t>4605a6cd92a44696</t>
+          <t>a25b632b46ff4a82</t>
         </is>
       </c>
       <c r="B40" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:56.469660Z</t>
+          <t>2026-08-04T14:27:16.244146Z</t>
         </is>
       </c>
       <c r="C40" s="24" t="inlineStr">
@@ -12378,7 +12495,7 @@
       </c>
       <c r="D40" s="24" t="inlineStr">
         <is>
-          <t>69144</t>
+          <t>69141</t>
         </is>
       </c>
       <c r="E40" s="24" t="inlineStr">
@@ -12388,12 +12505,12 @@
       </c>
       <c r="F40" s="24" t="inlineStr">
         <is>
-          <t>INTZ e-Sports</t>
+          <t>Vitality.Bee</t>
         </is>
       </c>
       <c r="G40" s="24" t="inlineStr">
         <is>
-          <t>Vivo Keyd Stars Academy</t>
+          <t>Karmine Corp Blue</t>
         </is>
       </c>
       <c r="H40" s="24" t="inlineStr">
@@ -12413,26 +12530,26 @@
         </is>
       </c>
       <c r="L40" s="26" t="n">
-        <v>104</v>
+        <v>-194</v>
       </c>
       <c r="M40" s="27" t="n">
-        <v>2.04</v>
+        <v>1.515464</v>
       </c>
       <c r="N40" s="28" t="n">
-        <v>0.490196</v>
+        <v>0.659864</v>
       </c>
       <c r="O40" s="28" t="n">
-        <v>0.591618</v>
+        <v>0.649827</v>
       </c>
       <c r="P40" s="28" t="n"/>
       <c r="Q40" s="28" t="n">
-        <v>0.101422</v>
+        <v>-0.010037</v>
       </c>
       <c r="R40" s="26" t="n">
-        <v>71</v>
+        <v>15</v>
       </c>
       <c r="S40" s="29" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="T40" s="24" t="inlineStr">
         <is>
@@ -12455,7 +12572,7 @@
       <c r="AD40" s="24" t="n"/>
       <c r="AE40" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4900 (market_slug=aec-lol-vksa-itz-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.6600 (market_slug=aec-lol-kcb-vitb-2026-08-04).</t>
         </is>
       </c>
       <c r="AF40" s="31" t="inlineStr">
@@ -12473,7 +12590,7 @@
       <c r="AJ40" s="31" t="n"/>
       <c r="AK40" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL40" s="26" t="n">
@@ -12481,47 +12598,47 @@
       </c>
       <c r="AM40" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN40" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO40" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP40" s="24" t="inlineStr">
         <is>
-          <t>INTZ e-Sports</t>
+          <t>Vitality.Bee</t>
         </is>
       </c>
       <c r="AQ40" s="24" t="inlineStr">
         <is>
-          <t>INTZ e-Sports</t>
+          <t>Vitality.Bee</t>
         </is>
       </c>
       <c r="AR40" s="24" t="inlineStr">
         <is>
-          <t>INTZ e-Sports</t>
+          <t>Vitality.Bee</t>
         </is>
       </c>
       <c r="AS40" s="24" t="inlineStr">
         <is>
-          <t>Vivo Keyd Stars Academy</t>
+          <t>Karmine Corp Blue</t>
         </is>
       </c>
       <c r="AT40" s="24" t="inlineStr">
         <is>
-          <t>Vivo Keyd Stars Academy</t>
+          <t>Karmine Corp Blue</t>
         </is>
       </c>
       <c r="AU40" s="24" t="inlineStr">
         <is>
-          <t>Vivo Keyd Stars Academy</t>
+          <t>Karmine Corp Blue</t>
         </is>
       </c>
       <c r="AV40" s="24" t="n"/>
@@ -12539,7 +12656,7 @@
       </c>
       <c r="BA40" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BB40" s="24" t="inlineStr">
@@ -12554,7 +12671,7 @@
       </c>
       <c r="BD40" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BE40" s="24" t="inlineStr">
@@ -12574,7 +12691,7 @@
       </c>
       <c r="BH40" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:34.823771Z</t>
+          <t>2026-08-04T14:26:51.498406Z</t>
         </is>
       </c>
       <c r="BI40" s="24" t="inlineStr">
@@ -12584,13 +12701,13 @@
       </c>
       <c r="BJ40" s="25" t="n"/>
       <c r="BK40" s="26" t="n">
-        <v>104</v>
+        <v>-194</v>
       </c>
       <c r="BL40" s="27" t="n">
-        <v>2.04</v>
+        <v>1.515464</v>
       </c>
       <c r="BM40" s="28" t="n">
-        <v>0.490196</v>
+        <v>0.659864</v>
       </c>
       <c r="BN40" s="28" t="n"/>
       <c r="BO40" s="28" t="n"/>
@@ -12622,31 +12739,32 @@
       <c r="CO40" s="24" t="n"/>
       <c r="CP40" s="24" t="n"/>
       <c r="CQ40" s="24" t="n"/>
-      <c r="CR40" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
+      <c r="CR40" s="24" t="n"/>
+      <c r="CS40" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="41" ht="36" customHeight="1">
       <c r="A41" s="24" t="inlineStr">
         <is>
-          <t>da93371c9e9d45ba</t>
+          <t>331c0f28b0074553</t>
         </is>
       </c>
       <c r="B41" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:56.469660Z</t>
+          <t>2026-08-04T14:27:16.244146Z</t>
         </is>
       </c>
       <c r="C41" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T20:00:00Z</t>
+          <t>2026-08-04T21:00:00Z</t>
         </is>
       </c>
       <c r="D41" s="24" t="inlineStr">
         <is>
-          <t>69141</t>
+          <t>69233</t>
         </is>
       </c>
       <c r="E41" s="24" t="inlineStr">
@@ -12656,12 +12774,12 @@
       </c>
       <c r="F41" s="24" t="inlineStr">
         <is>
-          <t>Vitality.Bee</t>
+          <t>Team Solid</t>
         </is>
       </c>
       <c r="G41" s="24" t="inlineStr">
         <is>
-          <t>Karmine Corp Blue</t>
+          <t>RED Academy</t>
         </is>
       </c>
       <c r="H41" s="24" t="inlineStr">
@@ -12681,26 +12799,26 @@
         </is>
       </c>
       <c r="L41" s="26" t="n">
-        <v>-186</v>
+        <v>203</v>
       </c>
       <c r="M41" s="27" t="n">
-        <v>1.537634</v>
+        <v>3.03</v>
       </c>
       <c r="N41" s="28" t="n">
-        <v>0.65035</v>
+        <v>0.330033</v>
       </c>
       <c r="O41" s="28" t="n">
-        <v>0.649994</v>
+        <v>0.572751</v>
       </c>
       <c r="P41" s="28" t="n"/>
       <c r="Q41" s="28" t="n">
-        <v>-0.000356</v>
+        <v>0.242718</v>
       </c>
       <c r="R41" s="26" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="S41" s="29" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="T41" s="24" t="inlineStr">
         <is>
@@ -12723,7 +12841,7 @@
       <c r="AD41" s="24" t="n"/>
       <c r="AE41" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6500 (market_slug=aec-lol-kcb-vitb-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.3300 (market_slug=aec-lol-reda-tse-2026-08-04).</t>
         </is>
       </c>
       <c r="AF41" s="31" t="inlineStr">
@@ -12741,7 +12859,7 @@
       <c r="AJ41" s="31" t="n"/>
       <c r="AK41" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL41" s="26" t="n">
@@ -12749,47 +12867,47 @@
       </c>
       <c r="AM41" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN41" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO41" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP41" s="24" t="inlineStr">
         <is>
-          <t>Vitality.Bee</t>
+          <t>Team Solid</t>
         </is>
       </c>
       <c r="AQ41" s="24" t="inlineStr">
         <is>
-          <t>Vitality.Bee</t>
+          <t>Team Solid</t>
         </is>
       </c>
       <c r="AR41" s="24" t="inlineStr">
         <is>
-          <t>Vitality.Bee</t>
+          <t>Team Solid</t>
         </is>
       </c>
       <c r="AS41" s="24" t="inlineStr">
         <is>
-          <t>Karmine Corp Blue</t>
+          <t>RED Academy</t>
         </is>
       </c>
       <c r="AT41" s="24" t="inlineStr">
         <is>
-          <t>Karmine Corp Blue</t>
+          <t>RED Academy</t>
         </is>
       </c>
       <c r="AU41" s="24" t="inlineStr">
         <is>
-          <t>Karmine Corp Blue</t>
+          <t>RED Academy</t>
         </is>
       </c>
       <c r="AV41" s="24" t="n"/>
@@ -12807,7 +12925,7 @@
       </c>
       <c r="BA41" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BB41" s="24" t="inlineStr">
@@ -12822,7 +12940,7 @@
       </c>
       <c r="BD41" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BE41" s="24" t="inlineStr">
@@ -12842,7 +12960,7 @@
       </c>
       <c r="BH41" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:35.473901Z</t>
+          <t>2026-08-04T14:26:52.692865Z</t>
         </is>
       </c>
       <c r="BI41" s="24" t="inlineStr">
@@ -12852,13 +12970,13 @@
       </c>
       <c r="BJ41" s="25" t="n"/>
       <c r="BK41" s="26" t="n">
-        <v>-186</v>
+        <v>203</v>
       </c>
       <c r="BL41" s="27" t="n">
-        <v>1.537634</v>
+        <v>3.03</v>
       </c>
       <c r="BM41" s="28" t="n">
-        <v>0.65035</v>
+        <v>0.330033</v>
       </c>
       <c r="BN41" s="28" t="n"/>
       <c r="BO41" s="28" t="n"/>
@@ -12890,21 +13008,22 @@
       <c r="CO41" s="24" t="n"/>
       <c r="CP41" s="24" t="n"/>
       <c r="CQ41" s="24" t="n"/>
-      <c r="CR41" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
+      <c r="CR41" s="24" t="n"/>
+      <c r="CS41" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="42" ht="36" customHeight="1">
       <c r="A42" s="24" t="inlineStr">
         <is>
-          <t>1a9709a138004957</t>
+          <t>3392246d50974c96</t>
         </is>
       </c>
       <c r="B42" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:56.469660Z</t>
+          <t>2026-08-04T14:27:16.244146Z</t>
         </is>
       </c>
       <c r="C42" s="24" t="inlineStr">
@@ -12949,23 +13068,23 @@
         </is>
       </c>
       <c r="L42" s="26" t="n">
-        <v>150</v>
+        <v>127</v>
       </c>
       <c r="M42" s="27" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="N42" s="28" t="n">
-        <v>0.4</v>
+        <v>0.440529</v>
       </c>
       <c r="O42" s="28" t="n">
-        <v>0.51668</v>
+        <v>0.517271</v>
       </c>
       <c r="P42" s="28" t="n"/>
       <c r="Q42" s="28" t="n">
-        <v>0.11668</v>
+        <v>0.076742</v>
       </c>
       <c r="R42" s="26" t="n">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="S42" s="29" t="n">
         <v>1</v>
@@ -12991,7 +13110,7 @@
       <c r="AD42" s="24" t="n"/>
       <c r="AE42" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4000 (market_slug=aec-lol-fcn-bub-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-lol-fcn-bub-2026-08-04).</t>
         </is>
       </c>
       <c r="AF42" s="31" t="inlineStr">
@@ -13075,7 +13194,7 @@
       </c>
       <c r="BA42" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BB42" s="24" t="inlineStr">
@@ -13090,7 +13209,7 @@
       </c>
       <c r="BD42" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BE42" s="24" t="inlineStr">
@@ -13110,7 +13229,7 @@
       </c>
       <c r="BH42" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:35.928266Z</t>
+          <t>2026-08-04T14:26:53.332419Z</t>
         </is>
       </c>
       <c r="BI42" s="24" t="inlineStr">
@@ -13120,13 +13239,13 @@
       </c>
       <c r="BJ42" s="25" t="n"/>
       <c r="BK42" s="26" t="n">
-        <v>150</v>
+        <v>127</v>
       </c>
       <c r="BL42" s="27" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="BM42" s="28" t="n">
-        <v>0.4</v>
+        <v>0.440529</v>
       </c>
       <c r="BN42" s="28" t="n"/>
       <c r="BO42" s="28" t="n"/>
@@ -13158,7 +13277,8 @@
       <c r="CO42" s="24" t="n"/>
       <c r="CP42" s="24" t="n"/>
       <c r="CQ42" s="24" t="n"/>
-      <c r="CR42" s="24" t="inlineStr">
+      <c r="CR42" s="24" t="n"/>
+      <c r="CS42" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -13167,22 +13287,22 @@
     <row r="43" ht="36" customHeight="1">
       <c r="A43" s="24" t="inlineStr">
         <is>
-          <t>f3369b750e9a4754</t>
+          <t>972a21631e214bdd</t>
         </is>
       </c>
       <c r="B43" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:56.469660Z</t>
+          <t>2026-08-04T14:27:16.244146Z</t>
         </is>
       </c>
       <c r="C43" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T21:00:00Z</t>
+          <t>2026-08-04T22:00:00Z</t>
         </is>
       </c>
       <c r="D43" s="24" t="inlineStr">
         <is>
-          <t>69233</t>
+          <t>69273</t>
         </is>
       </c>
       <c r="E43" s="24" t="inlineStr">
@@ -13192,12 +13312,12 @@
       </c>
       <c r="F43" s="24" t="inlineStr">
         <is>
-          <t>Team Solid</t>
+          <t>RMD Gaming</t>
         </is>
       </c>
       <c r="G43" s="24" t="inlineStr">
         <is>
-          <t>RED Academy</t>
+          <t>7REX</t>
         </is>
       </c>
       <c r="H43" s="24" t="inlineStr">
@@ -13217,23 +13337,23 @@
         </is>
       </c>
       <c r="L43" s="26" t="n">
-        <v>194</v>
+        <v>-113</v>
       </c>
       <c r="M43" s="27" t="n">
-        <v>2.94</v>
+        <v>1.884956</v>
       </c>
       <c r="N43" s="28" t="n">
-        <v>0.340136</v>
+        <v>0.530516</v>
       </c>
       <c r="O43" s="28" t="n">
-        <v>0.5725</v>
+        <v>0.604693</v>
       </c>
       <c r="P43" s="28" t="n"/>
       <c r="Q43" s="28" t="n">
-        <v>0.232364</v>
+        <v>0.07417700000000001</v>
       </c>
       <c r="R43" s="26" t="n">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="S43" s="29" t="n">
         <v>1.25</v>
@@ -13259,7 +13379,7 @@
       <c r="AD43" s="24" t="n"/>
       <c r="AE43" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3400 (market_slug=aec-lol-reda-tse-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.5300 (market_slug=aec-lol-7rex-rmd-2026-08-04).</t>
         </is>
       </c>
       <c r="AF43" s="31" t="inlineStr">
@@ -13300,32 +13420,32 @@
       </c>
       <c r="AP43" s="24" t="inlineStr">
         <is>
-          <t>Team Solid</t>
+          <t>RMD Gaming</t>
         </is>
       </c>
       <c r="AQ43" s="24" t="inlineStr">
         <is>
-          <t>Team Solid</t>
+          <t>RMD Gaming</t>
         </is>
       </c>
       <c r="AR43" s="24" t="inlineStr">
         <is>
-          <t>Team Solid</t>
+          <t>RMD Gaming</t>
         </is>
       </c>
       <c r="AS43" s="24" t="inlineStr">
         <is>
-          <t>RED Academy</t>
+          <t>7REX</t>
         </is>
       </c>
       <c r="AT43" s="24" t="inlineStr">
         <is>
-          <t>RED Academy</t>
+          <t>7REX</t>
         </is>
       </c>
       <c r="AU43" s="24" t="inlineStr">
         <is>
-          <t>RED Academy</t>
+          <t>7REX</t>
         </is>
       </c>
       <c r="AV43" s="24" t="n"/>
@@ -13343,7 +13463,7 @@
       </c>
       <c r="BA43" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BB43" s="24" t="inlineStr">
@@ -13358,7 +13478,7 @@
       </c>
       <c r="BD43" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BE43" s="24" t="inlineStr">
@@ -13378,7 +13498,7 @@
       </c>
       <c r="BH43" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:36.567095Z</t>
+          <t>2026-08-04T14:26:53.902256Z</t>
         </is>
       </c>
       <c r="BI43" s="24" t="inlineStr">
@@ -13388,13 +13508,13 @@
       </c>
       <c r="BJ43" s="25" t="n"/>
       <c r="BK43" s="26" t="n">
-        <v>194</v>
+        <v>-113</v>
       </c>
       <c r="BL43" s="27" t="n">
-        <v>2.94</v>
+        <v>1.884956</v>
       </c>
       <c r="BM43" s="28" t="n">
-        <v>0.340136</v>
+        <v>0.530516</v>
       </c>
       <c r="BN43" s="28" t="n"/>
       <c r="BO43" s="28" t="n"/>
@@ -13426,7 +13546,8 @@
       <c r="CO43" s="24" t="n"/>
       <c r="CP43" s="24" t="n"/>
       <c r="CQ43" s="24" t="n"/>
-      <c r="CR43" s="24" t="inlineStr">
+      <c r="CR43" s="24" t="n"/>
+      <c r="CS43" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -13435,22 +13556,22 @@
     <row r="44" ht="36" customHeight="1">
       <c r="A44" s="24" t="inlineStr">
         <is>
-          <t>93d9e90b7536488d</t>
+          <t>5fad01cc0e6442f9</t>
         </is>
       </c>
       <c r="B44" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:56.469660Z</t>
+          <t>2026-08-04T14:27:16.244146Z</t>
         </is>
       </c>
       <c r="C44" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T22:00:00Z</t>
+          <t>2026-08-04T23:00:00Z</t>
         </is>
       </c>
       <c r="D44" s="24" t="inlineStr">
         <is>
-          <t>69273</t>
+          <t>69304</t>
         </is>
       </c>
       <c r="E44" s="24" t="inlineStr">
@@ -13460,12 +13581,12 @@
       </c>
       <c r="F44" s="24" t="inlineStr">
         <is>
-          <t>RMD Gaming</t>
+          <t>paiN Gaming Academy</t>
         </is>
       </c>
       <c r="G44" s="24" t="inlineStr">
         <is>
-          <t>7REX</t>
+          <t>KaBuM! Ilha das Lendas</t>
         </is>
       </c>
       <c r="H44" s="24" t="inlineStr">
@@ -13475,7 +13596,7 @@
       </c>
       <c r="I44" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J44" s="25" t="n"/>
@@ -13485,26 +13606,26 @@
         </is>
       </c>
       <c r="L44" s="26" t="n">
-        <v>-117</v>
+        <v>-133</v>
       </c>
       <c r="M44" s="27" t="n">
-        <v>1.854701</v>
+        <v>1.75188</v>
       </c>
       <c r="N44" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.570815</v>
       </c>
       <c r="O44" s="28" t="n">
-        <v>0.604656</v>
+        <v>0.545463</v>
       </c>
       <c r="P44" s="28" t="n"/>
       <c r="Q44" s="28" t="n">
-        <v>0.065485</v>
+        <v>-0.025352</v>
       </c>
       <c r="R44" s="26" t="n">
-        <v>53</v>
+        <v>7</v>
       </c>
       <c r="S44" s="29" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="T44" s="24" t="inlineStr">
         <is>
@@ -13527,7 +13648,7 @@
       <c r="AD44" s="24" t="n"/>
       <c r="AE44" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-lol-7rex-rmd-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-lol-kbm-pnga-2026-08-04).</t>
         </is>
       </c>
       <c r="AF44" s="31" t="inlineStr">
@@ -13545,7 +13666,7 @@
       <c r="AJ44" s="31" t="n"/>
       <c r="AK44" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL44" s="26" t="n">
@@ -13553,47 +13674,47 @@
       </c>
       <c r="AM44" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN44" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO44" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP44" s="24" t="inlineStr">
         <is>
-          <t>RMD Gaming</t>
+          <t>paiN Gaming Academy</t>
         </is>
       </c>
       <c r="AQ44" s="24" t="inlineStr">
         <is>
-          <t>RMD Gaming</t>
+          <t>paiN Gaming Academy</t>
         </is>
       </c>
       <c r="AR44" s="24" t="inlineStr">
         <is>
-          <t>RMD Gaming</t>
+          <t>paiN Gaming Academy</t>
         </is>
       </c>
       <c r="AS44" s="24" t="inlineStr">
         <is>
-          <t>7REX</t>
+          <t>KaBuM! Ilha das Lendas</t>
         </is>
       </c>
       <c r="AT44" s="24" t="inlineStr">
         <is>
-          <t>7REX</t>
+          <t>KaBuM! Ilha das Lendas</t>
         </is>
       </c>
       <c r="AU44" s="24" t="inlineStr">
         <is>
-          <t>7REX</t>
+          <t>KaBuM! Ilha das Lendas</t>
         </is>
       </c>
       <c r="AV44" s="24" t="n"/>
@@ -13611,7 +13732,7 @@
       </c>
       <c r="BA44" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BB44" s="24" t="inlineStr">
@@ -13626,7 +13747,7 @@
       </c>
       <c r="BD44" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BE44" s="24" t="inlineStr">
@@ -13646,7 +13767,7 @@
       </c>
       <c r="BH44" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:37.194950Z</t>
+          <t>2026-08-04T14:26:54.517243Z</t>
         </is>
       </c>
       <c r="BI44" s="24" t="inlineStr">
@@ -13656,13 +13777,13 @@
       </c>
       <c r="BJ44" s="25" t="n"/>
       <c r="BK44" s="26" t="n">
-        <v>-117</v>
+        <v>-133</v>
       </c>
       <c r="BL44" s="27" t="n">
-        <v>1.854701</v>
+        <v>1.75188</v>
       </c>
       <c r="BM44" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.570815</v>
       </c>
       <c r="BN44" s="28" t="n"/>
       <c r="BO44" s="28" t="n"/>
@@ -13694,31 +13815,32 @@
       <c r="CO44" s="24" t="n"/>
       <c r="CP44" s="24" t="n"/>
       <c r="CQ44" s="24" t="n"/>
-      <c r="CR44" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
+      <c r="CR44" s="24" t="n"/>
+      <c r="CS44" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="45" ht="36" customHeight="1">
       <c r="A45" s="24" t="inlineStr">
         <is>
-          <t>b540df1859334978</t>
+          <t>cb383beca24b4a26</t>
         </is>
       </c>
       <c r="B45" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:56.469660Z</t>
+          <t>2026-08-04T14:27:16.244146Z</t>
         </is>
       </c>
       <c r="C45" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T23:00:00Z</t>
+          <t>2026-08-05T05:00:00Z</t>
         </is>
       </c>
       <c r="D45" s="24" t="inlineStr">
         <is>
-          <t>69304</t>
+          <t>69506</t>
         </is>
       </c>
       <c r="E45" s="24" t="inlineStr">
@@ -13728,12 +13850,12 @@
       </c>
       <c r="F45" s="24" t="inlineStr">
         <is>
-          <t>paiN Gaming Academy</t>
+          <t>Kiwoom DRX Challengers</t>
         </is>
       </c>
       <c r="G45" s="24" t="inlineStr">
         <is>
-          <t>KaBuM! Ilha das Lendas</t>
+          <t>BNK FearX Youth</t>
         </is>
       </c>
       <c r="H45" s="24" t="inlineStr">
@@ -13743,7 +13865,7 @@
       </c>
       <c r="I45" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J45" s="25" t="n"/>
@@ -13753,26 +13875,26 @@
         </is>
       </c>
       <c r="L45" s="26" t="n">
-        <v>-127</v>
+        <v>144</v>
       </c>
       <c r="M45" s="27" t="n">
-        <v>1.787402</v>
+        <v>2.44</v>
       </c>
       <c r="N45" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.409836</v>
       </c>
       <c r="O45" s="28" t="n">
-        <v>0.546359</v>
+        <v>0.59741</v>
       </c>
       <c r="P45" s="28" t="n"/>
       <c r="Q45" s="28" t="n">
-        <v>-0.013112</v>
+        <v>0.187574</v>
       </c>
       <c r="R45" s="26" t="n">
-        <v>13</v>
+        <v>100</v>
       </c>
       <c r="S45" s="29" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="T45" s="24" t="inlineStr">
         <is>
@@ -13795,7 +13917,7 @@
       <c r="AD45" s="24" t="n"/>
       <c r="AE45" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-lol-kbm-pnga-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.4100 (market_slug=aec-lol-foxy-krxc-2026-08-05).</t>
         </is>
       </c>
       <c r="AF45" s="31" t="inlineStr">
@@ -13831,37 +13953,37 @@
       </c>
       <c r="AO45" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
         </is>
       </c>
       <c r="AP45" s="24" t="inlineStr">
         <is>
-          <t>paiN Gaming Academy</t>
+          <t>Kiwoom DRX Challengers</t>
         </is>
       </c>
       <c r="AQ45" s="24" t="inlineStr">
         <is>
-          <t>paiN Gaming Academy</t>
+          <t>Kiwoom DRX Challengers</t>
         </is>
       </c>
       <c r="AR45" s="24" t="inlineStr">
         <is>
-          <t>paiN Gaming Academy</t>
+          <t>Kiwoom DRX Challengers</t>
         </is>
       </c>
       <c r="AS45" s="24" t="inlineStr">
         <is>
-          <t>KaBuM! Ilha das Lendas</t>
+          <t>BNK FearX Youth</t>
         </is>
       </c>
       <c r="AT45" s="24" t="inlineStr">
         <is>
-          <t>KaBuM! Ilha das Lendas</t>
+          <t>BNK FearX Youth</t>
         </is>
       </c>
       <c r="AU45" s="24" t="inlineStr">
         <is>
-          <t>KaBuM! Ilha das Lendas</t>
+          <t>BNK FearX Youth</t>
         </is>
       </c>
       <c r="AV45" s="24" t="n"/>
@@ -13879,7 +14001,7 @@
       </c>
       <c r="BA45" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BB45" s="24" t="inlineStr">
@@ -13894,7 +14016,7 @@
       </c>
       <c r="BD45" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BE45" s="24" t="inlineStr">
@@ -13914,7 +14036,7 @@
       </c>
       <c r="BH45" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:37.736771Z</t>
+          <t>2026-08-04T14:26:55.708967Z</t>
         </is>
       </c>
       <c r="BI45" s="24" t="inlineStr">
@@ -13924,13 +14046,13 @@
       </c>
       <c r="BJ45" s="25" t="n"/>
       <c r="BK45" s="26" t="n">
-        <v>-127</v>
+        <v>144</v>
       </c>
       <c r="BL45" s="27" t="n">
-        <v>1.787402</v>
+        <v>2.44</v>
       </c>
       <c r="BM45" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.409836</v>
       </c>
       <c r="BN45" s="28" t="n"/>
       <c r="BO45" s="28" t="n"/>
@@ -13962,21 +14084,22 @@
       <c r="CO45" s="24" t="n"/>
       <c r="CP45" s="24" t="n"/>
       <c r="CQ45" s="24" t="n"/>
-      <c r="CR45" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
+      <c r="CR45" s="24" t="n"/>
+      <c r="CS45" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="46" ht="36" customHeight="1">
       <c r="A46" s="24" t="inlineStr">
         <is>
-          <t>42b98355e0794604</t>
+          <t>19491ce09cd24459</t>
         </is>
       </c>
       <c r="B46" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:56.469660Z</t>
+          <t>2026-08-04T14:27:16.244146Z</t>
         </is>
       </c>
       <c r="C46" s="24" t="inlineStr">
@@ -14030,14 +14153,14 @@
         <v>0.579832</v>
       </c>
       <c r="O46" s="28" t="n">
-        <v>0.638913</v>
+        <v>0.638652</v>
       </c>
       <c r="P46" s="28" t="n"/>
       <c r="Q46" s="28" t="n">
-        <v>0.059081</v>
+        <v>0.05882</v>
       </c>
       <c r="R46" s="26" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S46" s="29" t="n">
         <v>1.5</v>
@@ -14147,7 +14270,7 @@
       </c>
       <c r="BA46" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BB46" s="24" t="inlineStr">
@@ -14162,7 +14285,7 @@
       </c>
       <c r="BD46" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BE46" s="24" t="inlineStr">
@@ -14182,7 +14305,7 @@
       </c>
       <c r="BH46" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:38.863908Z</t>
+          <t>2026-08-04T14:26:56.319431Z</t>
         </is>
       </c>
       <c r="BI46" s="24" t="inlineStr">
@@ -14230,7 +14353,8 @@
       <c r="CO46" s="24" t="n"/>
       <c r="CP46" s="24" t="n"/>
       <c r="CQ46" s="24" t="n"/>
-      <c r="CR46" s="24" t="inlineStr">
+      <c r="CR46" s="24" t="n"/>
+      <c r="CS46" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -14239,22 +14363,22 @@
     <row r="47" ht="36" customHeight="1">
       <c r="A47" s="24" t="inlineStr">
         <is>
-          <t>2d74051d6d9e47d5</t>
+          <t>ec7874b89c604099</t>
         </is>
       </c>
       <c r="B47" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:56.469660Z</t>
+          <t>2026-08-04T14:27:16.244146Z</t>
         </is>
       </c>
       <c r="C47" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T05:00:00Z</t>
+          <t>2026-08-05T08:00:00Z</t>
         </is>
       </c>
       <c r="D47" s="24" t="inlineStr">
         <is>
-          <t>69506</t>
+          <t>69511</t>
         </is>
       </c>
       <c r="E47" s="24" t="inlineStr">
@@ -14264,12 +14388,12 @@
       </c>
       <c r="F47" s="24" t="inlineStr">
         <is>
-          <t>Kiwoom DRX Challengers</t>
+          <t>New Meta</t>
         </is>
       </c>
       <c r="G47" s="24" t="inlineStr">
         <is>
-          <t>BNK FearX Youth</t>
+          <t>FENNEL</t>
         </is>
       </c>
       <c r="H47" s="24" t="inlineStr">
@@ -14289,26 +14413,26 @@
         </is>
       </c>
       <c r="L47" s="26" t="n">
-        <v>144</v>
+        <v>-186</v>
       </c>
       <c r="M47" s="27" t="n">
-        <v>2.44</v>
+        <v>1.537634</v>
       </c>
       <c r="N47" s="28" t="n">
-        <v>0.409836</v>
+        <v>0.65035</v>
       </c>
       <c r="O47" s="28" t="n">
-        <v>0.597302</v>
+        <v>0.699121</v>
       </c>
       <c r="P47" s="28" t="n"/>
       <c r="Q47" s="28" t="n">
-        <v>0.187466</v>
+        <v>0.048771</v>
       </c>
       <c r="R47" s="26" t="n">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="S47" s="29" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="T47" s="24" t="inlineStr">
         <is>
@@ -14331,7 +14455,7 @@
       <c r="AD47" s="24" t="n"/>
       <c r="AE47" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4100 (market_slug=aec-lol-foxy-krxc-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.6500 (market_slug=aec-lol-fnl-nme-2026-08-05).</t>
         </is>
       </c>
       <c r="AF47" s="31" t="inlineStr">
@@ -14349,7 +14473,7 @@
       <c r="AJ47" s="31" t="n"/>
       <c r="AK47" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL47" s="26" t="n">
@@ -14357,47 +14481,47 @@
       </c>
       <c r="AM47" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN47" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO47" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP47" s="24" t="inlineStr">
         <is>
-          <t>Kiwoom DRX Challengers</t>
+          <t>New Meta</t>
         </is>
       </c>
       <c r="AQ47" s="24" t="inlineStr">
         <is>
-          <t>Kiwoom DRX Challengers</t>
+          <t>New Meta</t>
         </is>
       </c>
       <c r="AR47" s="24" t="inlineStr">
         <is>
-          <t>Kiwoom DRX Challengers</t>
+          <t>New Meta</t>
         </is>
       </c>
       <c r="AS47" s="24" t="inlineStr">
         <is>
-          <t>BNK FearX Youth</t>
+          <t>FENNEL</t>
         </is>
       </c>
       <c r="AT47" s="24" t="inlineStr">
         <is>
-          <t>BNK FearX Youth</t>
+          <t>FENNEL</t>
         </is>
       </c>
       <c r="AU47" s="24" t="inlineStr">
         <is>
-          <t>BNK FearX Youth</t>
+          <t>FENNEL</t>
         </is>
       </c>
       <c r="AV47" s="24" t="n"/>
@@ -14415,7 +14539,7 @@
       </c>
       <c r="BA47" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BB47" s="24" t="inlineStr">
@@ -14430,7 +14554,7 @@
       </c>
       <c r="BD47" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BE47" s="24" t="inlineStr">
@@ -14450,7 +14574,7 @@
       </c>
       <c r="BH47" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:39.338315Z</t>
+          <t>2026-08-04T14:26:56.857793Z</t>
         </is>
       </c>
       <c r="BI47" s="24" t="inlineStr">
@@ -14460,13 +14584,13 @@
       </c>
       <c r="BJ47" s="25" t="n"/>
       <c r="BK47" s="26" t="n">
-        <v>144</v>
+        <v>-186</v>
       </c>
       <c r="BL47" s="27" t="n">
-        <v>2.44</v>
+        <v>1.537634</v>
       </c>
       <c r="BM47" s="28" t="n">
-        <v>0.409836</v>
+        <v>0.65035</v>
       </c>
       <c r="BN47" s="28" t="n"/>
       <c r="BO47" s="28" t="n"/>
@@ -14498,7 +14622,8 @@
       <c r="CO47" s="24" t="n"/>
       <c r="CP47" s="24" t="n"/>
       <c r="CQ47" s="24" t="n"/>
-      <c r="CR47" s="24" t="inlineStr">
+      <c r="CR47" s="24" t="n"/>
+      <c r="CS47" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -14507,12 +14632,12 @@
     <row r="48" ht="36" customHeight="1">
       <c r="A48" s="24" t="inlineStr">
         <is>
-          <t>42cf1b2478204e12</t>
+          <t>9154b6d69f654e4d</t>
         </is>
       </c>
       <c r="B48" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:56.469660Z</t>
+          <t>2026-08-04T14:27:16.244146Z</t>
         </is>
       </c>
       <c r="C48" s="24" t="inlineStr">
@@ -14566,14 +14691,14 @@
         <v>0.690402</v>
       </c>
       <c r="O48" s="28" t="n">
-        <v>0.739915</v>
+        <v>0.752668</v>
       </c>
       <c r="P48" s="28" t="n"/>
       <c r="Q48" s="28" t="n">
-        <v>0.049513</v>
+        <v>0.062266</v>
       </c>
       <c r="R48" s="26" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="S48" s="29" t="n">
         <v>2</v>
@@ -14683,7 +14808,7 @@
       </c>
       <c r="BA48" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BB48" s="24" t="inlineStr">
@@ -14698,7 +14823,7 @@
       </c>
       <c r="BD48" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BE48" s="24" t="inlineStr">
@@ -14718,7 +14843,7 @@
       </c>
       <c r="BH48" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:39.828051Z</t>
+          <t>2026-08-04T14:26:57.357254Z</t>
         </is>
       </c>
       <c r="BI48" s="24" t="inlineStr">
@@ -14766,7 +14891,8 @@
       <c r="CO48" s="24" t="n"/>
       <c r="CP48" s="24" t="n"/>
       <c r="CQ48" s="24" t="n"/>
-      <c r="CR48" s="24" t="inlineStr">
+      <c r="CR48" s="24" t="n"/>
+      <c r="CS48" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -14775,22 +14901,22 @@
     <row r="49" ht="36" customHeight="1">
       <c r="A49" s="24" t="inlineStr">
         <is>
-          <t>0a7b6184cad24890</t>
+          <t>030c031f62b24e3a</t>
         </is>
       </c>
       <c r="B49" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:56.469660Z</t>
+          <t>2026-08-04T14:27:16.244146Z</t>
         </is>
       </c>
       <c r="C49" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T08:00:00Z</t>
+          <t>2026-08-05T10:00:00Z</t>
         </is>
       </c>
       <c r="D49" s="24" t="inlineStr">
         <is>
-          <t>69511</t>
+          <t>69539</t>
         </is>
       </c>
       <c r="E49" s="24" t="inlineStr">
@@ -14800,12 +14926,12 @@
       </c>
       <c r="F49" s="24" t="inlineStr">
         <is>
-          <t>New Meta</t>
+          <t>Gen.G</t>
         </is>
       </c>
       <c r="G49" s="24" t="inlineStr">
         <is>
-          <t>FENNEL</t>
+          <t>Hanwha Life Esports</t>
         </is>
       </c>
       <c r="H49" s="24" t="inlineStr">
@@ -14825,26 +14951,26 @@
         </is>
       </c>
       <c r="L49" s="26" t="n">
-        <v>-156</v>
+        <v>-122</v>
       </c>
       <c r="M49" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.819672</v>
       </c>
       <c r="N49" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.54955</v>
       </c>
       <c r="O49" s="28" t="n">
-        <v>0.699554</v>
+        <v>0.6034</v>
       </c>
       <c r="P49" s="28" t="n"/>
       <c r="Q49" s="28" t="n">
-        <v>0.090179</v>
+        <v>0.05385</v>
       </c>
       <c r="R49" s="26" t="n">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="S49" s="29" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="T49" s="24" t="inlineStr">
         <is>
@@ -14867,7 +14993,7 @@
       <c r="AD49" s="24" t="n"/>
       <c r="AE49" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-lol-fnl-nme-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-lol-hle-gen-2026-08-05).</t>
         </is>
       </c>
       <c r="AF49" s="31" t="inlineStr">
@@ -14908,32 +15034,32 @@
       </c>
       <c r="AP49" s="24" t="inlineStr">
         <is>
-          <t>New Meta</t>
+          <t>Gen.G</t>
         </is>
       </c>
       <c r="AQ49" s="24" t="inlineStr">
         <is>
-          <t>New Meta</t>
+          <t>Gen.G</t>
         </is>
       </c>
       <c r="AR49" s="24" t="inlineStr">
         <is>
-          <t>New Meta</t>
+          <t>Gen.G</t>
         </is>
       </c>
       <c r="AS49" s="24" t="inlineStr">
         <is>
-          <t>FENNEL</t>
+          <t>Hanwha Life Esports</t>
         </is>
       </c>
       <c r="AT49" s="24" t="inlineStr">
         <is>
-          <t>FENNEL</t>
+          <t>Hanwha Life Esports</t>
         </is>
       </c>
       <c r="AU49" s="24" t="inlineStr">
         <is>
-          <t>FENNEL</t>
+          <t>Hanwha Life Esports</t>
         </is>
       </c>
       <c r="AV49" s="24" t="n"/>
@@ -14951,7 +15077,7 @@
       </c>
       <c r="BA49" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BB49" s="24" t="inlineStr">
@@ -14966,7 +15092,7 @@
       </c>
       <c r="BD49" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BE49" s="24" t="inlineStr">
@@ -14986,7 +15112,7 @@
       </c>
       <c r="BH49" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:40.294698Z</t>
+          <t>2026-08-04T14:26:58.482445Z</t>
         </is>
       </c>
       <c r="BI49" s="24" t="inlineStr">
@@ -14996,13 +15122,13 @@
       </c>
       <c r="BJ49" s="25" t="n"/>
       <c r="BK49" s="26" t="n">
-        <v>-156</v>
+        <v>-122</v>
       </c>
       <c r="BL49" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.819672</v>
       </c>
       <c r="BM49" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.54955</v>
       </c>
       <c r="BN49" s="28" t="n"/>
       <c r="BO49" s="28" t="n"/>
@@ -15034,7 +15160,8 @@
       <c r="CO49" s="24" t="n"/>
       <c r="CP49" s="24" t="n"/>
       <c r="CQ49" s="24" t="n"/>
-      <c r="CR49" s="24" t="inlineStr">
+      <c r="CR49" s="24" t="n"/>
+      <c r="CS49" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -15043,22 +15170,22 @@
     <row r="50" ht="36" customHeight="1">
       <c r="A50" s="24" t="inlineStr">
         <is>
-          <t>c69371ca01dc4f85</t>
+          <t>59c732f143d748c0</t>
         </is>
       </c>
       <c r="B50" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:56.469660Z</t>
+          <t>2026-08-04T14:27:16.244146Z</t>
         </is>
       </c>
       <c r="C50" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T10:00:00Z</t>
+          <t>2026-08-05T16:00:00Z</t>
         </is>
       </c>
       <c r="D50" s="24" t="inlineStr">
         <is>
-          <t>69539</t>
+          <t>69817</t>
         </is>
       </c>
       <c r="E50" s="24" t="inlineStr">
@@ -15068,12 +15195,12 @@
       </c>
       <c r="F50" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>The Secret Club</t>
         </is>
       </c>
       <c r="G50" s="24" t="inlineStr">
         <is>
-          <t>Hanwha Life Esports</t>
+          <t>⁠Hooligans</t>
         </is>
       </c>
       <c r="H50" s="24" t="inlineStr">
@@ -15083,7 +15210,7 @@
       </c>
       <c r="I50" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J50" s="25" t="n"/>
@@ -15093,26 +15220,26 @@
         </is>
       </c>
       <c r="L50" s="26" t="n">
-        <v>-127</v>
+        <v>-170</v>
       </c>
       <c r="M50" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.588235</v>
       </c>
       <c r="N50" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.62963</v>
       </c>
       <c r="O50" s="28" t="n">
-        <v>0.637225</v>
+        <v>0.5593129999999999</v>
       </c>
       <c r="P50" s="28" t="n"/>
       <c r="Q50" s="28" t="n">
-        <v>0.077754</v>
+        <v>-0.070317</v>
       </c>
       <c r="R50" s="26" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="S50" s="29" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="T50" s="24" t="inlineStr">
         <is>
@@ -15135,7 +15262,7 @@
       <c r="AD50" s="24" t="n"/>
       <c r="AE50" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-lol-hle-gen-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-lol-hool-tsc-2026-08-05).</t>
         </is>
       </c>
       <c r="AF50" s="31" t="inlineStr">
@@ -15153,7 +15280,7 @@
       <c r="AJ50" s="31" t="n"/>
       <c r="AK50" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL50" s="26" t="n">
@@ -15161,47 +15288,47 @@
       </c>
       <c r="AM50" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN50" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO50" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP50" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>The Secret Club</t>
         </is>
       </c>
       <c r="AQ50" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>The Secret Club</t>
         </is>
       </c>
       <c r="AR50" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>The Secret Club</t>
         </is>
       </c>
       <c r="AS50" s="24" t="inlineStr">
         <is>
-          <t>Hanwha Life Esports</t>
+          <t>⁠Hooligans</t>
         </is>
       </c>
       <c r="AT50" s="24" t="inlineStr">
         <is>
-          <t>Hanwha Life Esports</t>
+          <t>⁠Hooligans</t>
         </is>
       </c>
       <c r="AU50" s="24" t="inlineStr">
         <is>
-          <t>Hanwha Life Esports</t>
+          <t>⁠Hooligans</t>
         </is>
       </c>
       <c r="AV50" s="24" t="n"/>
@@ -15219,7 +15346,7 @@
       </c>
       <c r="BA50" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BB50" s="24" t="inlineStr">
@@ -15234,7 +15361,7 @@
       </c>
       <c r="BD50" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BE50" s="24" t="inlineStr">
@@ -15254,7 +15381,7 @@
       </c>
       <c r="BH50" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:41.252699Z</t>
+          <t>2026-08-04T14:27:03.117755Z</t>
         </is>
       </c>
       <c r="BI50" s="24" t="inlineStr">
@@ -15264,13 +15391,13 @@
       </c>
       <c r="BJ50" s="25" t="n"/>
       <c r="BK50" s="26" t="n">
-        <v>-127</v>
+        <v>-170</v>
       </c>
       <c r="BL50" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.588235</v>
       </c>
       <c r="BM50" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.62963</v>
       </c>
       <c r="BN50" s="28" t="n"/>
       <c r="BO50" s="28" t="n"/>
@@ -15302,21 +15429,22 @@
       <c r="CO50" s="24" t="n"/>
       <c r="CP50" s="24" t="n"/>
       <c r="CQ50" s="24" t="n"/>
-      <c r="CR50" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
+      <c r="CR50" s="24" t="n"/>
+      <c r="CS50" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="51" ht="36" customHeight="1">
       <c r="A51" s="24" t="inlineStr">
         <is>
-          <t>cd1900cb34ba475d</t>
+          <t>38379ff25f4a4f6a</t>
         </is>
       </c>
       <c r="B51" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:56.469660Z</t>
+          <t>2026-08-04T14:27:16.244146Z</t>
         </is>
       </c>
       <c r="C51" s="24" t="inlineStr">
@@ -15326,7 +15454,7 @@
       </c>
       <c r="D51" s="24" t="inlineStr">
         <is>
-          <t>69816</t>
+          <t>69818</t>
         </is>
       </c>
       <c r="E51" s="24" t="inlineStr">
@@ -15336,12 +15464,12 @@
       </c>
       <c r="F51" s="24" t="inlineStr">
         <is>
-          <t>Galions</t>
+          <t>Pyramid IV Esports</t>
         </is>
       </c>
       <c r="G51" s="24" t="inlineStr">
         <is>
-          <t>TLN Pirates</t>
+          <t>JSK Esports</t>
         </is>
       </c>
       <c r="H51" s="24" t="inlineStr">
@@ -15361,26 +15489,26 @@
         </is>
       </c>
       <c r="L51" s="26" t="n">
-        <v>-163</v>
+        <v>144</v>
       </c>
       <c r="M51" s="27" t="n">
-        <v>1.613497</v>
+        <v>2.44</v>
       </c>
       <c r="N51" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.409836</v>
       </c>
       <c r="O51" s="28" t="n">
-        <v>0.665588</v>
+        <v>0.529223</v>
       </c>
       <c r="P51" s="28" t="n"/>
       <c r="Q51" s="28" t="n">
-        <v>0.045816</v>
+        <v>0.119387</v>
       </c>
       <c r="R51" s="26" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="S51" s="29" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="T51" s="24" t="inlineStr">
         <is>
@@ -15403,7 +15531,7 @@
       <c r="AD51" s="24" t="n"/>
       <c r="AE51" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-lol-tlnp-gal-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.4100 (market_slug=aec-lol-jsk-piv-2026-08-05).</t>
         </is>
       </c>
       <c r="AF51" s="31" t="inlineStr">
@@ -15421,7 +15549,7 @@
       <c r="AJ51" s="31" t="n"/>
       <c r="AK51" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL51" s="26" t="n">
@@ -15429,47 +15557,47 @@
       </c>
       <c r="AM51" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN51" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO51" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP51" s="24" t="inlineStr">
         <is>
-          <t>Galions</t>
+          <t>Pyramid IV Esports</t>
         </is>
       </c>
       <c r="AQ51" s="24" t="inlineStr">
         <is>
-          <t>Galions</t>
+          <t>Pyramid IV Esports</t>
         </is>
       </c>
       <c r="AR51" s="24" t="inlineStr">
         <is>
-          <t>Galions</t>
+          <t>Pyramid IV Esports</t>
         </is>
       </c>
       <c r="AS51" s="24" t="inlineStr">
         <is>
-          <t>TLN Pirates</t>
+          <t>JSK Esports</t>
         </is>
       </c>
       <c r="AT51" s="24" t="inlineStr">
         <is>
-          <t>TLN Pirates</t>
+          <t>JSK Esports</t>
         </is>
       </c>
       <c r="AU51" s="24" t="inlineStr">
         <is>
-          <t>TLN Pirates</t>
+          <t>JSK Esports</t>
         </is>
       </c>
       <c r="AV51" s="24" t="n"/>
@@ -15487,7 +15615,7 @@
       </c>
       <c r="BA51" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BB51" s="24" t="inlineStr">
@@ -15502,7 +15630,7 @@
       </c>
       <c r="BD51" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BE51" s="24" t="inlineStr">
@@ -15522,7 +15650,7 @@
       </c>
       <c r="BH51" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:44.546269Z</t>
+          <t>2026-08-04T14:27:04.287471Z</t>
         </is>
       </c>
       <c r="BI51" s="24" t="inlineStr">
@@ -15532,13 +15660,13 @@
       </c>
       <c r="BJ51" s="25" t="n"/>
       <c r="BK51" s="26" t="n">
-        <v>-163</v>
+        <v>144</v>
       </c>
       <c r="BL51" s="27" t="n">
-        <v>1.613497</v>
+        <v>2.44</v>
       </c>
       <c r="BM51" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.409836</v>
       </c>
       <c r="BN51" s="28" t="n"/>
       <c r="BO51" s="28" t="n"/>
@@ -15570,7 +15698,8 @@
       <c r="CO51" s="24" t="n"/>
       <c r="CP51" s="24" t="n"/>
       <c r="CQ51" s="24" t="n"/>
-      <c r="CR51" s="24" t="inlineStr">
+      <c r="CR51" s="24" t="n"/>
+      <c r="CS51" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -15579,12 +15708,12 @@
     <row r="52" ht="36" customHeight="1">
       <c r="A52" s="24" t="inlineStr">
         <is>
-          <t>308b0ca16aa84142</t>
+          <t>5289309a3bff402c</t>
         </is>
       </c>
       <c r="B52" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:56.469660Z</t>
+          <t>2026-08-04T14:27:16.244146Z</t>
         </is>
       </c>
       <c r="C52" s="24" t="inlineStr">
@@ -15594,7 +15723,7 @@
       </c>
       <c r="D52" s="24" t="inlineStr">
         <is>
-          <t>69871</t>
+          <t>70569</t>
         </is>
       </c>
       <c r="E52" s="24" t="inlineStr">
@@ -15604,12 +15733,12 @@
       </c>
       <c r="F52" s="24" t="inlineStr">
         <is>
-          <t>Kaufland Hangry Knights</t>
+          <t>devils.one inStreamly</t>
         </is>
       </c>
       <c r="G52" s="24" t="inlineStr">
         <is>
-          <t>TeamOrangeGaming</t>
+          <t>BOMBA Team</t>
         </is>
       </c>
       <c r="H52" s="24" t="inlineStr">
@@ -15629,26 +15758,26 @@
         </is>
       </c>
       <c r="L52" s="26" t="n">
-        <v>127</v>
+        <v>-144</v>
       </c>
       <c r="M52" s="27" t="n">
-        <v>2.27</v>
+        <v>1.694444</v>
       </c>
       <c r="N52" s="28" t="n">
-        <v>0.440529</v>
+        <v>0.590164</v>
       </c>
       <c r="O52" s="28" t="n">
-        <v>0.561203</v>
+        <v>0.831719</v>
       </c>
       <c r="P52" s="28" t="n"/>
       <c r="Q52" s="28" t="n">
-        <v>0.120674</v>
+        <v>0.241555</v>
       </c>
       <c r="R52" s="26" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="S52" s="29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T52" s="24" t="inlineStr">
         <is>
@@ -15671,7 +15800,7 @@
       <c r="AD52" s="24" t="n"/>
       <c r="AE52" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-lol-tog-khk-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-lol-boom-dv1-2026-08-05).</t>
         </is>
       </c>
       <c r="AF52" s="31" t="inlineStr">
@@ -15712,32 +15841,32 @@
       </c>
       <c r="AP52" s="24" t="inlineStr">
         <is>
-          <t>Kaufland Hangry Knights</t>
+          <t>devils.one inStreamly</t>
         </is>
       </c>
       <c r="AQ52" s="24" t="inlineStr">
         <is>
-          <t>Kaufland Hangry Knights</t>
+          <t>devils.one inStreamly</t>
         </is>
       </c>
       <c r="AR52" s="24" t="inlineStr">
         <is>
-          <t>Kaufland Hangry Knights</t>
+          <t>devils.one inStreamly</t>
         </is>
       </c>
       <c r="AS52" s="24" t="inlineStr">
         <is>
-          <t>TeamOrangeGaming</t>
+          <t>BOMBA Team</t>
         </is>
       </c>
       <c r="AT52" s="24" t="inlineStr">
         <is>
-          <t>TeamOrangeGaming</t>
+          <t>BOMBA Team</t>
         </is>
       </c>
       <c r="AU52" s="24" t="inlineStr">
         <is>
-          <t>TeamOrangeGaming</t>
+          <t>BOMBA Team</t>
         </is>
       </c>
       <c r="AV52" s="24" t="n"/>
@@ -15755,7 +15884,7 @@
       </c>
       <c r="BA52" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BB52" s="24" t="inlineStr">
@@ -15770,7 +15899,7 @@
       </c>
       <c r="BD52" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BE52" s="24" t="inlineStr">
@@ -15790,7 +15919,7 @@
       </c>
       <c r="BH52" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:46.445811Z</t>
+          <t>2026-08-04T14:27:04.870108Z</t>
         </is>
       </c>
       <c r="BI52" s="24" t="inlineStr">
@@ -15800,13 +15929,13 @@
       </c>
       <c r="BJ52" s="25" t="n"/>
       <c r="BK52" s="26" t="n">
-        <v>127</v>
+        <v>-144</v>
       </c>
       <c r="BL52" s="27" t="n">
-        <v>2.27</v>
+        <v>1.694444</v>
       </c>
       <c r="BM52" s="28" t="n">
-        <v>0.440529</v>
+        <v>0.590164</v>
       </c>
       <c r="BN52" s="28" t="n"/>
       <c r="BO52" s="28" t="n"/>
@@ -15838,7 +15967,8 @@
       <c r="CO52" s="24" t="n"/>
       <c r="CP52" s="24" t="n"/>
       <c r="CQ52" s="24" t="n"/>
-      <c r="CR52" s="24" t="inlineStr">
+      <c r="CR52" s="24" t="n"/>
+      <c r="CS52" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -15847,12 +15977,12 @@
     <row r="53" ht="36" customHeight="1">
       <c r="A53" s="24" t="inlineStr">
         <is>
-          <t>632f853d2bcc4ef8</t>
+          <t>d6c51801509f4171</t>
         </is>
       </c>
       <c r="B53" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:56.469660Z</t>
+          <t>2026-08-04T14:27:16.244146Z</t>
         </is>
       </c>
       <c r="C53" s="24" t="inlineStr">
@@ -15862,7 +15992,7 @@
       </c>
       <c r="D53" s="24" t="inlineStr">
         <is>
-          <t>70569</t>
+          <t>69871</t>
         </is>
       </c>
       <c r="E53" s="24" t="inlineStr">
@@ -15872,12 +16002,12 @@
       </c>
       <c r="F53" s="24" t="inlineStr">
         <is>
-          <t>devils.one inStreamly</t>
+          <t>Kaufland Hangry Knights</t>
         </is>
       </c>
       <c r="G53" s="24" t="inlineStr">
         <is>
-          <t>BOMBA Team</t>
+          <t>TeamOrangeGaming</t>
         </is>
       </c>
       <c r="H53" s="24" t="inlineStr">
@@ -15897,26 +16027,26 @@
         </is>
       </c>
       <c r="L53" s="26" t="n">
-        <v>-144</v>
+        <v>127</v>
       </c>
       <c r="M53" s="27" t="n">
-        <v>1.694444</v>
+        <v>2.27</v>
       </c>
       <c r="N53" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.440529</v>
       </c>
       <c r="O53" s="28" t="n">
-        <v>0.832591</v>
+        <v>0.56154</v>
       </c>
       <c r="P53" s="28" t="n"/>
       <c r="Q53" s="28" t="n">
-        <v>0.242427</v>
+        <v>0.121011</v>
       </c>
       <c r="R53" s="26" t="n">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="S53" s="29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T53" s="24" t="inlineStr">
         <is>
@@ -15939,7 +16069,7 @@
       <c r="AD53" s="24" t="n"/>
       <c r="AE53" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-lol-boom-dv1-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-lol-tog-khk-2026-08-05).</t>
         </is>
       </c>
       <c r="AF53" s="31" t="inlineStr">
@@ -15980,32 +16110,32 @@
       </c>
       <c r="AP53" s="24" t="inlineStr">
         <is>
-          <t>devils.one inStreamly</t>
+          <t>Kaufland Hangry Knights</t>
         </is>
       </c>
       <c r="AQ53" s="24" t="inlineStr">
         <is>
-          <t>devils.one inStreamly</t>
+          <t>Kaufland Hangry Knights</t>
         </is>
       </c>
       <c r="AR53" s="24" t="inlineStr">
         <is>
-          <t>devils.one inStreamly</t>
+          <t>Kaufland Hangry Knights</t>
         </is>
       </c>
       <c r="AS53" s="24" t="inlineStr">
         <is>
-          <t>BOMBA Team</t>
+          <t>TeamOrangeGaming</t>
         </is>
       </c>
       <c r="AT53" s="24" t="inlineStr">
         <is>
-          <t>BOMBA Team</t>
+          <t>TeamOrangeGaming</t>
         </is>
       </c>
       <c r="AU53" s="24" t="inlineStr">
         <is>
-          <t>BOMBA Team</t>
+          <t>TeamOrangeGaming</t>
         </is>
       </c>
       <c r="AV53" s="24" t="n"/>
@@ -16023,7 +16153,7 @@
       </c>
       <c r="BA53" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BB53" s="24" t="inlineStr">
@@ -16038,7 +16168,7 @@
       </c>
       <c r="BD53" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BE53" s="24" t="inlineStr">
@@ -16058,7 +16188,7 @@
       </c>
       <c r="BH53" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:47.442405Z</t>
+          <t>2026-08-04T14:27:05.368556Z</t>
         </is>
       </c>
       <c r="BI53" s="24" t="inlineStr">
@@ -16068,13 +16198,13 @@
       </c>
       <c r="BJ53" s="25" t="n"/>
       <c r="BK53" s="26" t="n">
-        <v>-144</v>
+        <v>127</v>
       </c>
       <c r="BL53" s="27" t="n">
-        <v>1.694444</v>
+        <v>2.27</v>
       </c>
       <c r="BM53" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.440529</v>
       </c>
       <c r="BN53" s="28" t="n"/>
       <c r="BO53" s="28" t="n"/>
@@ -16106,7 +16236,8 @@
       <c r="CO53" s="24" t="n"/>
       <c r="CP53" s="24" t="n"/>
       <c r="CQ53" s="24" t="n"/>
-      <c r="CR53" s="24" t="inlineStr">
+      <c r="CR53" s="24" t="n"/>
+      <c r="CS53" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -16115,12 +16246,12 @@
     <row r="54" ht="36" customHeight="1">
       <c r="A54" s="24" t="inlineStr">
         <is>
-          <t>40ea7f5fa25e41c9</t>
+          <t>6929757a226b4160</t>
         </is>
       </c>
       <c r="B54" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:56.469660Z</t>
+          <t>2026-08-04T14:27:16.244146Z</t>
         </is>
       </c>
       <c r="C54" s="24" t="inlineStr">
@@ -16174,11 +16305,11 @@
         <v>0.5</v>
       </c>
       <c r="O54" s="28" t="n">
-        <v>0.577055</v>
+        <v>0.577308</v>
       </c>
       <c r="P54" s="28" t="n"/>
       <c r="Q54" s="28" t="n">
-        <v>0.077055</v>
+        <v>0.077308</v>
       </c>
       <c r="R54" s="26" t="n">
         <v>59</v>
@@ -16291,7 +16422,7 @@
       </c>
       <c r="BA54" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BB54" s="24" t="inlineStr">
@@ -16306,7 +16437,7 @@
       </c>
       <c r="BD54" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BE54" s="24" t="inlineStr">
@@ -16326,7 +16457,7 @@
       </c>
       <c r="BH54" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:47.949141Z</t>
+          <t>2026-08-04T14:27:06.503337Z</t>
         </is>
       </c>
       <c r="BI54" s="24" t="inlineStr">
@@ -16374,7 +16505,8 @@
       <c r="CO54" s="24" t="n"/>
       <c r="CP54" s="24" t="n"/>
       <c r="CQ54" s="24" t="n"/>
-      <c r="CR54" s="24" t="inlineStr">
+      <c r="CR54" s="24" t="n"/>
+      <c r="CS54" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -16383,12 +16515,12 @@
     <row r="55" ht="36" customHeight="1">
       <c r="A55" s="24" t="inlineStr">
         <is>
-          <t>f439587bd2c842be</t>
+          <t>50dcaea0ae0a4b9a</t>
         </is>
       </c>
       <c r="B55" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:56.469660Z</t>
+          <t>2026-08-04T14:27:16.244146Z</t>
         </is>
       </c>
       <c r="C55" s="24" t="inlineStr">
@@ -16442,11 +16574,11 @@
         <v>0.45045</v>
       </c>
       <c r="O55" s="28" t="n">
-        <v>0.536006</v>
+        <v>0.536488</v>
       </c>
       <c r="P55" s="28" t="n"/>
       <c r="Q55" s="28" t="n">
-        <v>0.08555599999999999</v>
+        <v>0.086038</v>
       </c>
       <c r="R55" s="26" t="n">
         <v>63</v>
@@ -16559,7 +16691,7 @@
       </c>
       <c r="BA55" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BB55" s="24" t="inlineStr">
@@ -16574,7 +16706,7 @@
       </c>
       <c r="BD55" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BE55" s="24" t="inlineStr">
@@ -16594,7 +16726,7 @@
       </c>
       <c r="BH55" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:48.438562Z</t>
+          <t>2026-08-04T14:27:07.051647Z</t>
         </is>
       </c>
       <c r="BI55" s="24" t="inlineStr">
@@ -16642,7 +16774,8 @@
       <c r="CO55" s="24" t="n"/>
       <c r="CP55" s="24" t="n"/>
       <c r="CQ55" s="24" t="n"/>
-      <c r="CR55" s="24" t="inlineStr">
+      <c r="CR55" s="24" t="n"/>
+      <c r="CS55" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -16651,12 +16784,12 @@
     <row r="56" ht="36" customHeight="1">
       <c r="A56" s="24" t="inlineStr">
         <is>
-          <t>7e44e2ed76904c7e</t>
+          <t>5b259f4e79094584</t>
         </is>
       </c>
       <c r="B56" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:56.469660Z</t>
+          <t>2026-08-04T14:27:16.244146Z</t>
         </is>
       </c>
       <c r="C56" s="24" t="inlineStr">
@@ -16666,7 +16799,7 @@
       </c>
       <c r="D56" s="24" t="inlineStr">
         <is>
-          <t>69948</t>
+          <t>69952</t>
         </is>
       </c>
       <c r="E56" s="24" t="inlineStr">
@@ -16676,12 +16809,12 @@
       </c>
       <c r="F56" s="24" t="inlineStr">
         <is>
-          <t>Solary</t>
+          <t>Absolved</t>
         </is>
       </c>
       <c r="G56" s="24" t="inlineStr">
         <is>
-          <t>Karmine Corp Blue</t>
+          <t>Sørby eSport</t>
         </is>
       </c>
       <c r="H56" s="24" t="inlineStr">
@@ -16691,7 +16824,7 @@
       </c>
       <c r="I56" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J56" s="25" t="n"/>
@@ -16701,20 +16834,20 @@
         </is>
       </c>
       <c r="L56" s="26" t="n">
-        <v>-203</v>
+        <v>-144</v>
       </c>
       <c r="M56" s="27" t="n">
-        <v>1.492611</v>
+        <v>1.694444</v>
       </c>
       <c r="N56" s="28" t="n">
-        <v>0.669967</v>
+        <v>0.590164</v>
       </c>
       <c r="O56" s="28" t="n">
-        <v>0.564089</v>
+        <v>0.525829</v>
       </c>
       <c r="P56" s="28" t="n"/>
       <c r="Q56" s="28" t="n">
-        <v>-0.105878</v>
+        <v>-0.064335</v>
       </c>
       <c r="R56" s="26" t="n">
         <v>0</v>
@@ -16743,7 +16876,7 @@
       <c r="AD56" s="24" t="n"/>
       <c r="AE56" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-lol-kcb-sly-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-lol-sre-abs-2026-08-05).</t>
         </is>
       </c>
       <c r="AF56" s="31" t="inlineStr">
@@ -16784,32 +16917,32 @@
       </c>
       <c r="AP56" s="24" t="inlineStr">
         <is>
-          <t>Solary</t>
+          <t>Absolved</t>
         </is>
       </c>
       <c r="AQ56" s="24" t="inlineStr">
         <is>
-          <t>Solary</t>
+          <t>Absolved</t>
         </is>
       </c>
       <c r="AR56" s="24" t="inlineStr">
         <is>
-          <t>Solary</t>
+          <t>Absolved</t>
         </is>
       </c>
       <c r="AS56" s="24" t="inlineStr">
         <is>
-          <t>Karmine Corp Blue</t>
+          <t>Sørby eSport</t>
         </is>
       </c>
       <c r="AT56" s="24" t="inlineStr">
         <is>
-          <t>Karmine Corp Blue</t>
+          <t>Sørby eSport</t>
         </is>
       </c>
       <c r="AU56" s="24" t="inlineStr">
         <is>
-          <t>Karmine Corp Blue</t>
+          <t>Sørby eSport</t>
         </is>
       </c>
       <c r="AV56" s="24" t="n"/>
@@ -16827,7 +16960,7 @@
       </c>
       <c r="BA56" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BB56" s="24" t="inlineStr">
@@ -16842,7 +16975,7 @@
       </c>
       <c r="BD56" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BE56" s="24" t="inlineStr">
@@ -16862,7 +16995,7 @@
       </c>
       <c r="BH56" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:49.352813Z</t>
+          <t>2026-08-04T14:27:07.640962Z</t>
         </is>
       </c>
       <c r="BI56" s="24" t="inlineStr">
@@ -16872,13 +17005,13 @@
       </c>
       <c r="BJ56" s="25" t="n"/>
       <c r="BK56" s="26" t="n">
-        <v>-203</v>
+        <v>-144</v>
       </c>
       <c r="BL56" s="27" t="n">
-        <v>1.492611</v>
+        <v>1.694444</v>
       </c>
       <c r="BM56" s="28" t="n">
-        <v>0.669967</v>
+        <v>0.590164</v>
       </c>
       <c r="BN56" s="28" t="n"/>
       <c r="BO56" s="28" t="n"/>
@@ -16910,7 +17043,8 @@
       <c r="CO56" s="24" t="n"/>
       <c r="CP56" s="24" t="n"/>
       <c r="CQ56" s="24" t="n"/>
-      <c r="CR56" s="24" t="inlineStr">
+      <c r="CR56" s="24" t="n"/>
+      <c r="CS56" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -16919,12 +17053,12 @@
     <row r="57" ht="36" customHeight="1">
       <c r="A57" s="24" t="inlineStr">
         <is>
-          <t>ca87a9282d674c4d</t>
+          <t>55e460d13614462c</t>
         </is>
       </c>
       <c r="B57" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:56.469660Z</t>
+          <t>2026-08-04T14:27:16.244146Z</t>
         </is>
       </c>
       <c r="C57" s="24" t="inlineStr">
@@ -16934,7 +17068,7 @@
       </c>
       <c r="D57" s="24" t="inlineStr">
         <is>
-          <t>69949</t>
+          <t>69950</t>
         </is>
       </c>
       <c r="E57" s="24" t="inlineStr">
@@ -16944,12 +17078,12 @@
       </c>
       <c r="F57" s="24" t="inlineStr">
         <is>
-          <t>Hyperion</t>
+          <t>Lupus Esports</t>
         </is>
       </c>
       <c r="G57" s="24" t="inlineStr">
         <is>
-          <t>Dominion Goblins</t>
+          <t>SPIKE Syndicate</t>
         </is>
       </c>
       <c r="H57" s="24" t="inlineStr">
@@ -16969,23 +17103,23 @@
         </is>
       </c>
       <c r="L57" s="26" t="n">
-        <v>117</v>
+        <v>-144</v>
       </c>
       <c r="M57" s="27" t="n">
-        <v>2.17</v>
+        <v>1.694444</v>
       </c>
       <c r="N57" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.590164</v>
       </c>
       <c r="O57" s="28" t="n">
-        <v>0.530192</v>
+        <v>0.535054</v>
       </c>
       <c r="P57" s="28" t="n"/>
       <c r="Q57" s="28" t="n">
-        <v>0.06936299999999999</v>
+        <v>-0.05511</v>
       </c>
       <c r="R57" s="26" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="S57" s="29" t="n">
         <v>1</v>
@@ -17011,7 +17145,7 @@
       <c r="AD57" s="24" t="n"/>
       <c r="AE57" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-lol-domi-hype-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-lol-spk-lps-2026-08-05).</t>
         </is>
       </c>
       <c r="AF57" s="31" t="inlineStr">
@@ -17052,32 +17186,32 @@
       </c>
       <c r="AP57" s="24" t="inlineStr">
         <is>
-          <t>Hyperion</t>
+          <t>Lupus Esports</t>
         </is>
       </c>
       <c r="AQ57" s="24" t="inlineStr">
         <is>
-          <t>Hyperion</t>
+          <t>Lupus Esports</t>
         </is>
       </c>
       <c r="AR57" s="24" t="inlineStr">
         <is>
-          <t>Hyperion</t>
+          <t>Lupus Esports</t>
         </is>
       </c>
       <c r="AS57" s="24" t="inlineStr">
         <is>
-          <t>Dominion Goblins</t>
+          <t>SPIKE Syndicate</t>
         </is>
       </c>
       <c r="AT57" s="24" t="inlineStr">
         <is>
-          <t>Dominion Goblins</t>
+          <t>SPIKE Syndicate</t>
         </is>
       </c>
       <c r="AU57" s="24" t="inlineStr">
         <is>
-          <t>Dominion Goblins</t>
+          <t>SPIKE Syndicate</t>
         </is>
       </c>
       <c r="AV57" s="24" t="n"/>
@@ -17095,7 +17229,7 @@
       </c>
       <c r="BA57" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BB57" s="24" t="inlineStr">
@@ -17110,7 +17244,7 @@
       </c>
       <c r="BD57" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BE57" s="24" t="inlineStr">
@@ -17130,7 +17264,7 @@
       </c>
       <c r="BH57" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:49.832690Z</t>
+          <t>2026-08-04T14:27:08.193209Z</t>
         </is>
       </c>
       <c r="BI57" s="24" t="inlineStr">
@@ -17140,13 +17274,13 @@
       </c>
       <c r="BJ57" s="25" t="n"/>
       <c r="BK57" s="26" t="n">
-        <v>117</v>
+        <v>-144</v>
       </c>
       <c r="BL57" s="27" t="n">
-        <v>2.17</v>
+        <v>1.694444</v>
       </c>
       <c r="BM57" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.590164</v>
       </c>
       <c r="BN57" s="28" t="n"/>
       <c r="BO57" s="28" t="n"/>
@@ -17178,21 +17312,22 @@
       <c r="CO57" s="24" t="n"/>
       <c r="CP57" s="24" t="n"/>
       <c r="CQ57" s="24" t="n"/>
-      <c r="CR57" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
+      <c r="CR57" s="24" t="n"/>
+      <c r="CS57" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="58" ht="36" customHeight="1">
       <c r="A58" s="24" t="inlineStr">
         <is>
-          <t>cd4a0af1ff884108</t>
+          <t>26cf4ed475f2456e</t>
         </is>
       </c>
       <c r="B58" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:56.469660Z</t>
+          <t>2026-08-04T14:27:16.244146Z</t>
         </is>
       </c>
       <c r="C58" s="24" t="inlineStr">
@@ -17202,7 +17337,7 @@
       </c>
       <c r="D58" s="24" t="inlineStr">
         <is>
-          <t>69950</t>
+          <t>69949</t>
         </is>
       </c>
       <c r="E58" s="24" t="inlineStr">
@@ -17212,12 +17347,12 @@
       </c>
       <c r="F58" s="24" t="inlineStr">
         <is>
-          <t>Lupus Esports</t>
+          <t>Hyperion</t>
         </is>
       </c>
       <c r="G58" s="24" t="inlineStr">
         <is>
-          <t>SPIKE Syndicate</t>
+          <t>Dominion Goblins</t>
         </is>
       </c>
       <c r="H58" s="24" t="inlineStr">
@@ -17237,23 +17372,23 @@
         </is>
       </c>
       <c r="L58" s="26" t="n">
-        <v>-138</v>
+        <v>-113</v>
       </c>
       <c r="M58" s="27" t="n">
-        <v>1.724638</v>
+        <v>1.884956</v>
       </c>
       <c r="N58" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.530516</v>
       </c>
       <c r="O58" s="28" t="n">
-        <v>0.534563</v>
+        <v>0.530709</v>
       </c>
       <c r="P58" s="28" t="n"/>
       <c r="Q58" s="28" t="n">
-        <v>-0.045269</v>
+        <v>0.000193</v>
       </c>
       <c r="R58" s="26" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="S58" s="29" t="n">
         <v>1</v>
@@ -17279,7 +17414,7 @@
       <c r="AD58" s="24" t="n"/>
       <c r="AE58" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-lol-spk-lps-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.5300 (market_slug=aec-lol-domi-hype-2026-08-05).</t>
         </is>
       </c>
       <c r="AF58" s="31" t="inlineStr">
@@ -17320,32 +17455,32 @@
       </c>
       <c r="AP58" s="24" t="inlineStr">
         <is>
-          <t>Lupus Esports</t>
+          <t>Hyperion</t>
         </is>
       </c>
       <c r="AQ58" s="24" t="inlineStr">
         <is>
-          <t>Lupus Esports</t>
+          <t>Hyperion</t>
         </is>
       </c>
       <c r="AR58" s="24" t="inlineStr">
         <is>
-          <t>Lupus Esports</t>
+          <t>Hyperion</t>
         </is>
       </c>
       <c r="AS58" s="24" t="inlineStr">
         <is>
-          <t>SPIKE Syndicate</t>
+          <t>Dominion Goblins</t>
         </is>
       </c>
       <c r="AT58" s="24" t="inlineStr">
         <is>
-          <t>SPIKE Syndicate</t>
+          <t>Dominion Goblins</t>
         </is>
       </c>
       <c r="AU58" s="24" t="inlineStr">
         <is>
-          <t>SPIKE Syndicate</t>
+          <t>Dominion Goblins</t>
         </is>
       </c>
       <c r="AV58" s="24" t="n"/>
@@ -17363,7 +17498,7 @@
       </c>
       <c r="BA58" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BB58" s="24" t="inlineStr">
@@ -17378,7 +17513,7 @@
       </c>
       <c r="BD58" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BE58" s="24" t="inlineStr">
@@ -17398,7 +17533,7 @@
       </c>
       <c r="BH58" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:50.326365Z</t>
+          <t>2026-08-04T14:27:08.816447Z</t>
         </is>
       </c>
       <c r="BI58" s="24" t="inlineStr">
@@ -17408,13 +17543,13 @@
       </c>
       <c r="BJ58" s="25" t="n"/>
       <c r="BK58" s="26" t="n">
-        <v>-138</v>
+        <v>-113</v>
       </c>
       <c r="BL58" s="27" t="n">
-        <v>1.724638</v>
+        <v>1.884956</v>
       </c>
       <c r="BM58" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.530516</v>
       </c>
       <c r="BN58" s="28" t="n"/>
       <c r="BO58" s="28" t="n"/>
@@ -17446,21 +17581,22 @@
       <c r="CO58" s="24" t="n"/>
       <c r="CP58" s="24" t="n"/>
       <c r="CQ58" s="24" t="n"/>
-      <c r="CR58" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
+      <c r="CR58" s="24" t="n"/>
+      <c r="CS58" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="59" ht="36" customHeight="1">
       <c r="A59" s="24" t="inlineStr">
         <is>
-          <t>1120235ad0b64397</t>
+          <t>93e43e6dc0474c66</t>
         </is>
       </c>
       <c r="B59" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:56.469660Z</t>
+          <t>2026-08-04T14:27:16.244146Z</t>
         </is>
       </c>
       <c r="C59" s="24" t="inlineStr">
@@ -17470,7 +17606,7 @@
       </c>
       <c r="D59" s="24" t="inlineStr">
         <is>
-          <t>69951</t>
+          <t>69948</t>
         </is>
       </c>
       <c r="E59" s="24" t="inlineStr">
@@ -17480,12 +17616,12 @@
       </c>
       <c r="F59" s="24" t="inlineStr">
         <is>
-          <t>Rich Gang</t>
+          <t>Solary</t>
         </is>
       </c>
       <c r="G59" s="24" t="inlineStr">
         <is>
-          <t>2 Massive</t>
+          <t>Karmine Corp Blue</t>
         </is>
       </c>
       <c r="H59" s="24" t="inlineStr">
@@ -17505,23 +17641,23 @@
         </is>
       </c>
       <c r="L59" s="26" t="n">
-        <v>163</v>
+        <v>-213</v>
       </c>
       <c r="M59" s="27" t="n">
-        <v>2.63</v>
+        <v>1.469484</v>
       </c>
       <c r="N59" s="28" t="n">
-        <v>0.380228</v>
+        <v>0.680511</v>
       </c>
       <c r="O59" s="28" t="n">
-        <v>0.5160709999999999</v>
+        <v>0.563059</v>
       </c>
       <c r="P59" s="28" t="n"/>
       <c r="Q59" s="28" t="n">
-        <v>0.135843</v>
+        <v>-0.117452</v>
       </c>
       <c r="R59" s="26" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="S59" s="29" t="n">
         <v>1</v>
@@ -17547,7 +17683,7 @@
       <c r="AD59" s="24" t="n"/>
       <c r="AE59" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3800 (market_slug=aec-lol-mas-rgi-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-lol-kcb-sly-2026-08-05).</t>
         </is>
       </c>
       <c r="AF59" s="31" t="inlineStr">
@@ -17588,32 +17724,32 @@
       </c>
       <c r="AP59" s="24" t="inlineStr">
         <is>
-          <t>Rich Gang</t>
+          <t>Solary</t>
         </is>
       </c>
       <c r="AQ59" s="24" t="inlineStr">
         <is>
-          <t>Rich Gang</t>
+          <t>Solary</t>
         </is>
       </c>
       <c r="AR59" s="24" t="inlineStr">
         <is>
-          <t>Rich Gang</t>
+          <t>Solary</t>
         </is>
       </c>
       <c r="AS59" s="24" t="inlineStr">
         <is>
-          <t>2 Massive</t>
+          <t>Karmine Corp Blue</t>
         </is>
       </c>
       <c r="AT59" s="24" t="inlineStr">
         <is>
-          <t>2 Massive</t>
+          <t>Karmine Corp Blue</t>
         </is>
       </c>
       <c r="AU59" s="24" t="inlineStr">
         <is>
-          <t>2 Massive</t>
+          <t>Karmine Corp Blue</t>
         </is>
       </c>
       <c r="AV59" s="24" t="n"/>
@@ -17631,7 +17767,7 @@
       </c>
       <c r="BA59" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BB59" s="24" t="inlineStr">
@@ -17646,7 +17782,7 @@
       </c>
       <c r="BD59" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BE59" s="24" t="inlineStr">
@@ -17666,7 +17802,7 @@
       </c>
       <c r="BH59" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:50.827783Z</t>
+          <t>2026-08-04T14:27:09.396495Z</t>
         </is>
       </c>
       <c r="BI59" s="24" t="inlineStr">
@@ -17676,13 +17812,13 @@
       </c>
       <c r="BJ59" s="25" t="n"/>
       <c r="BK59" s="26" t="n">
-        <v>163</v>
+        <v>-213</v>
       </c>
       <c r="BL59" s="27" t="n">
-        <v>2.63</v>
+        <v>1.469484</v>
       </c>
       <c r="BM59" s="28" t="n">
-        <v>0.380228</v>
+        <v>0.680511</v>
       </c>
       <c r="BN59" s="28" t="n"/>
       <c r="BO59" s="28" t="n"/>
@@ -17714,31 +17850,32 @@
       <c r="CO59" s="24" t="n"/>
       <c r="CP59" s="24" t="n"/>
       <c r="CQ59" s="24" t="n"/>
-      <c r="CR59" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
+      <c r="CR59" s="24" t="n"/>
+      <c r="CS59" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="60" ht="36" customHeight="1">
       <c r="A60" s="24" t="inlineStr">
         <is>
-          <t>9ed618ade4c3475f</t>
+          <t>bd2d3c71b4b844c1</t>
         </is>
       </c>
       <c r="B60" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:56.469660Z</t>
+          <t>2026-08-04T14:27:16.244146Z</t>
         </is>
       </c>
       <c r="C60" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T19:00:00Z</t>
+          <t>2026-08-05T18:00:00Z</t>
         </is>
       </c>
       <c r="D60" s="24" t="inlineStr">
         <is>
-          <t>70045</t>
+          <t>69951</t>
         </is>
       </c>
       <c r="E60" s="24" t="inlineStr">
@@ -17748,12 +17885,12 @@
       </c>
       <c r="F60" s="24" t="inlineStr">
         <is>
-          <t>Ici Japon Corp. Esport</t>
+          <t>Rich Gang</t>
         </is>
       </c>
       <c r="G60" s="24" t="inlineStr">
         <is>
-          <t>ZYB Esport</t>
+          <t>2 Massive</t>
         </is>
       </c>
       <c r="H60" s="24" t="inlineStr">
@@ -17773,26 +17910,26 @@
         </is>
       </c>
       <c r="L60" s="26" t="n">
-        <v>-108</v>
+        <v>163</v>
       </c>
       <c r="M60" s="27" t="n">
-        <v>1.925926</v>
+        <v>2.63</v>
       </c>
       <c r="N60" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.380228</v>
       </c>
       <c r="O60" s="28" t="n">
-        <v>0.607498</v>
+        <v>0.515294</v>
       </c>
       <c r="P60" s="28" t="n"/>
       <c r="Q60" s="28" t="n">
-        <v>0.088267</v>
+        <v>0.135066</v>
       </c>
       <c r="R60" s="26" t="n">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="S60" s="29" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="T60" s="24" t="inlineStr">
         <is>
@@ -17815,7 +17952,7 @@
       <c r="AD60" s="24" t="n"/>
       <c r="AE60" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5200 (market_slug=aec-lol-zyb-ijc-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.3800 (market_slug=aec-lol-mas-rgi-2026-08-05).</t>
         </is>
       </c>
       <c r="AF60" s="31" t="inlineStr">
@@ -17833,7 +17970,7 @@
       <c r="AJ60" s="31" t="n"/>
       <c r="AK60" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL60" s="26" t="n">
@@ -17841,47 +17978,47 @@
       </c>
       <c r="AM60" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN60" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO60" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP60" s="24" t="inlineStr">
         <is>
-          <t>Ici Japon Corp. Esport</t>
+          <t>Rich Gang</t>
         </is>
       </c>
       <c r="AQ60" s="24" t="inlineStr">
         <is>
-          <t>Ici Japon Corp. Esport</t>
+          <t>Rich Gang</t>
         </is>
       </c>
       <c r="AR60" s="24" t="inlineStr">
         <is>
-          <t>Ici Japon Corp. Esport</t>
+          <t>Rich Gang</t>
         </is>
       </c>
       <c r="AS60" s="24" t="inlineStr">
         <is>
-          <t>ZYB Esport</t>
+          <t>2 Massive</t>
         </is>
       </c>
       <c r="AT60" s="24" t="inlineStr">
         <is>
-          <t>ZYB Esport</t>
+          <t>2 Massive</t>
         </is>
       </c>
       <c r="AU60" s="24" t="inlineStr">
         <is>
-          <t>ZYB Esport</t>
+          <t>2 Massive</t>
         </is>
       </c>
       <c r="AV60" s="24" t="n"/>
@@ -17899,7 +18036,7 @@
       </c>
       <c r="BA60" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BB60" s="24" t="inlineStr">
@@ -17914,7 +18051,7 @@
       </c>
       <c r="BD60" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BE60" s="24" t="inlineStr">
@@ -17934,7 +18071,7 @@
       </c>
       <c r="BH60" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:51.809850Z</t>
+          <t>2026-08-04T14:27:09.929255Z</t>
         </is>
       </c>
       <c r="BI60" s="24" t="inlineStr">
@@ -17944,13 +18081,13 @@
       </c>
       <c r="BJ60" s="25" t="n"/>
       <c r="BK60" s="26" t="n">
-        <v>-108</v>
+        <v>163</v>
       </c>
       <c r="BL60" s="27" t="n">
-        <v>1.925926</v>
+        <v>2.63</v>
       </c>
       <c r="BM60" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.380228</v>
       </c>
       <c r="BN60" s="28" t="n"/>
       <c r="BO60" s="28" t="n"/>
@@ -17982,7 +18119,8 @@
       <c r="CO60" s="24" t="n"/>
       <c r="CP60" s="24" t="n"/>
       <c r="CQ60" s="24" t="n"/>
-      <c r="CR60" s="24" t="inlineStr">
+      <c r="CR60" s="24" t="n"/>
+      <c r="CS60" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -17991,22 +18129,22 @@
     <row r="61" ht="36" customHeight="1">
       <c r="A61" s="24" t="inlineStr">
         <is>
-          <t>8ae2b418e6064ae0</t>
+          <t>686cc91cc43548ab</t>
         </is>
       </c>
       <c r="B61" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:56.469660Z</t>
+          <t>2026-08-04T14:27:16.244146Z</t>
         </is>
       </c>
       <c r="C61" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T20:00:00Z</t>
+          <t>2026-08-05T19:00:00Z</t>
         </is>
       </c>
       <c r="D61" s="24" t="inlineStr">
         <is>
-          <t>70302</t>
+          <t>70045</t>
         </is>
       </c>
       <c r="E61" s="24" t="inlineStr">
@@ -18016,12 +18154,12 @@
       </c>
       <c r="F61" s="24" t="inlineStr">
         <is>
-          <t>7REX</t>
+          <t>Ici Japon Corp. Esport</t>
         </is>
       </c>
       <c r="G61" s="24" t="inlineStr">
         <is>
-          <t>Team Solid</t>
+          <t>ZYB Esport</t>
         </is>
       </c>
       <c r="H61" s="24" t="inlineStr">
@@ -18041,26 +18179,26 @@
         </is>
       </c>
       <c r="L61" s="26" t="n">
-        <v>-117</v>
+        <v>-127</v>
       </c>
       <c r="M61" s="27" t="n">
-        <v>1.854701</v>
+        <v>1.787402</v>
       </c>
       <c r="N61" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="O61" s="28" t="n">
-        <v>0.535928</v>
+        <v>0.606257</v>
       </c>
       <c r="P61" s="28" t="n"/>
       <c r="Q61" s="28" t="n">
-        <v>-0.003243</v>
+        <v>0.046786</v>
       </c>
       <c r="R61" s="26" t="n">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="S61" s="29" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="T61" s="24" t="inlineStr">
         <is>
@@ -18083,7 +18221,7 @@
       <c r="AD61" s="24" t="n"/>
       <c r="AE61" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-lol-tse-7rex-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-lol-zyb-ijc-2026-08-05).</t>
         </is>
       </c>
       <c r="AF61" s="31" t="inlineStr">
@@ -18101,7 +18239,7 @@
       <c r="AJ61" s="31" t="n"/>
       <c r="AK61" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL61" s="26" t="n">
@@ -18109,47 +18247,47 @@
       </c>
       <c r="AM61" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN61" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO61" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP61" s="24" t="inlineStr">
         <is>
-          <t>7REX</t>
+          <t>Ici Japon Corp. Esport</t>
         </is>
       </c>
       <c r="AQ61" s="24" t="inlineStr">
         <is>
-          <t>7REX</t>
+          <t>Ici Japon Corp. Esport</t>
         </is>
       </c>
       <c r="AR61" s="24" t="inlineStr">
         <is>
-          <t>7REX</t>
+          <t>Ici Japon Corp. Esport</t>
         </is>
       </c>
       <c r="AS61" s="24" t="inlineStr">
         <is>
-          <t>Team Solid</t>
+          <t>ZYB Esport</t>
         </is>
       </c>
       <c r="AT61" s="24" t="inlineStr">
         <is>
-          <t>Team Solid</t>
+          <t>ZYB Esport</t>
         </is>
       </c>
       <c r="AU61" s="24" t="inlineStr">
         <is>
-          <t>Team Solid</t>
+          <t>ZYB Esport</t>
         </is>
       </c>
       <c r="AV61" s="24" t="n"/>
@@ -18167,7 +18305,7 @@
       </c>
       <c r="BA61" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BB61" s="24" t="inlineStr">
@@ -18182,7 +18320,7 @@
       </c>
       <c r="BD61" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BE61" s="24" t="inlineStr">
@@ -18202,7 +18340,7 @@
       </c>
       <c r="BH61" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:52.802307Z</t>
+          <t>2026-08-04T14:27:11.034551Z</t>
         </is>
       </c>
       <c r="BI61" s="24" t="inlineStr">
@@ -18212,13 +18350,13 @@
       </c>
       <c r="BJ61" s="25" t="n"/>
       <c r="BK61" s="26" t="n">
-        <v>-117</v>
+        <v>-127</v>
       </c>
       <c r="BL61" s="27" t="n">
-        <v>1.854701</v>
+        <v>1.787402</v>
       </c>
       <c r="BM61" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="BN61" s="28" t="n"/>
       <c r="BO61" s="28" t="n"/>
@@ -18250,31 +18388,32 @@
       <c r="CO61" s="24" t="n"/>
       <c r="CP61" s="24" t="n"/>
       <c r="CQ61" s="24" t="n"/>
-      <c r="CR61" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
+      <c r="CR61" s="24" t="n"/>
+      <c r="CS61" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="62" ht="36" customHeight="1">
       <c r="A62" s="24" t="inlineStr">
         <is>
-          <t>bcd2f952b94e48ae</t>
+          <t>eaf5af9d716e4f2e</t>
         </is>
       </c>
       <c r="B62" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:56.469660Z</t>
+          <t>2026-08-04T14:27:16.244146Z</t>
         </is>
       </c>
       <c r="C62" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T21:00:00Z</t>
+          <t>2026-08-05T20:00:00Z</t>
         </is>
       </c>
       <c r="D62" s="24" t="inlineStr">
         <is>
-          <t>70349</t>
+          <t>70301</t>
         </is>
       </c>
       <c r="E62" s="24" t="inlineStr">
@@ -18284,12 +18423,12 @@
       </c>
       <c r="F62" s="24" t="inlineStr">
         <is>
-          <t>Winthrop University</t>
+          <t>Skillcamp Esport</t>
         </is>
       </c>
       <c r="G62" s="24" t="inlineStr">
         <is>
-          <t>Blue Otter</t>
+          <t>Vitality.Bee</t>
         </is>
       </c>
       <c r="H62" s="24" t="inlineStr">
@@ -18299,7 +18438,7 @@
       </c>
       <c r="I62" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J62" s="25" t="n"/>
@@ -18309,23 +18448,23 @@
         </is>
       </c>
       <c r="L62" s="26" t="n">
-        <v>-213</v>
+        <v>100</v>
       </c>
       <c r="M62" s="27" t="n">
-        <v>1.469484</v>
+        <v>2</v>
       </c>
       <c r="N62" s="28" t="n">
-        <v>0.680511</v>
+        <v>0.5</v>
       </c>
       <c r="O62" s="28" t="n">
-        <v>0.649617</v>
+        <v>0.658341</v>
       </c>
       <c r="P62" s="28" t="n"/>
       <c r="Q62" s="28" t="n">
-        <v>-0.030894</v>
+        <v>0.158341</v>
       </c>
       <c r="R62" s="26" t="n">
-        <v>5</v>
+        <v>99</v>
       </c>
       <c r="S62" s="29" t="n">
         <v>1.75</v>
@@ -18351,7 +18490,7 @@
       <c r="AD62" s="24" t="n"/>
       <c r="AE62" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-lol-blue-wu-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.5000 (market_slug=aec-lol-vitb-sc-2026-08-05).</t>
         </is>
       </c>
       <c r="AF62" s="31" t="inlineStr">
@@ -18369,7 +18508,7 @@
       <c r="AJ62" s="31" t="n"/>
       <c r="AK62" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL62" s="26" t="n">
@@ -18377,47 +18516,47 @@
       </c>
       <c r="AM62" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN62" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO62" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP62" s="24" t="inlineStr">
         <is>
-          <t>Winthrop University</t>
+          <t>Skillcamp Esport</t>
         </is>
       </c>
       <c r="AQ62" s="24" t="inlineStr">
         <is>
-          <t>Winthrop University</t>
+          <t>Skillcamp Esport</t>
         </is>
       </c>
       <c r="AR62" s="24" t="inlineStr">
         <is>
-          <t>Winthrop University</t>
+          <t>Skillcamp Esport</t>
         </is>
       </c>
       <c r="AS62" s="24" t="inlineStr">
         <is>
-          <t>Blue Otter</t>
+          <t>Vitality.Bee</t>
         </is>
       </c>
       <c r="AT62" s="24" t="inlineStr">
         <is>
-          <t>Blue Otter</t>
+          <t>Vitality.Bee</t>
         </is>
       </c>
       <c r="AU62" s="24" t="inlineStr">
         <is>
-          <t>Blue Otter</t>
+          <t>Vitality.Bee</t>
         </is>
       </c>
       <c r="AV62" s="24" t="n"/>
@@ -18435,7 +18574,7 @@
       </c>
       <c r="BA62" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BB62" s="24" t="inlineStr">
@@ -18450,7 +18589,7 @@
       </c>
       <c r="BD62" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BE62" s="24" t="inlineStr">
@@ -18470,7 +18609,7 @@
       </c>
       <c r="BH62" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:53.928842Z</t>
+          <t>2026-08-04T14:27:11.579319Z</t>
         </is>
       </c>
       <c r="BI62" s="24" t="inlineStr">
@@ -18480,13 +18619,13 @@
       </c>
       <c r="BJ62" s="25" t="n"/>
       <c r="BK62" s="26" t="n">
-        <v>-213</v>
+        <v>100</v>
       </c>
       <c r="BL62" s="27" t="n">
-        <v>1.469484</v>
+        <v>2</v>
       </c>
       <c r="BM62" s="28" t="n">
-        <v>0.680511</v>
+        <v>0.5</v>
       </c>
       <c r="BN62" s="28" t="n"/>
       <c r="BO62" s="28" t="n"/>
@@ -18518,31 +18657,32 @@
       <c r="CO62" s="24" t="n"/>
       <c r="CP62" s="24" t="n"/>
       <c r="CQ62" s="24" t="n"/>
-      <c r="CR62" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
+      <c r="CR62" s="24" t="n"/>
+      <c r="CS62" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="63" ht="36" customHeight="1">
       <c r="A63" s="24" t="inlineStr">
         <is>
-          <t>835b0d32870c497c</t>
+          <t>13ee15c8a2674c57</t>
         </is>
       </c>
       <c r="B63" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:56.469660Z</t>
+          <t>2026-08-04T14:27:16.244146Z</t>
         </is>
       </c>
       <c r="C63" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T21:00:00Z</t>
+          <t>2026-08-05T20:00:00Z</t>
         </is>
       </c>
       <c r="D63" s="24" t="inlineStr">
         <is>
-          <t>70348</t>
+          <t>70302</t>
         </is>
       </c>
       <c r="E63" s="24" t="inlineStr">
@@ -18552,12 +18692,12 @@
       </c>
       <c r="F63" s="24" t="inlineStr">
         <is>
-          <t>White Dragons</t>
+          <t>7REX</t>
         </is>
       </c>
       <c r="G63" s="24" t="inlineStr">
         <is>
-          <t>NORTHERNGRADE ESPORTS</t>
+          <t>Team Solid</t>
         </is>
       </c>
       <c r="H63" s="24" t="inlineStr">
@@ -18567,7 +18707,7 @@
       </c>
       <c r="I63" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J63" s="25" t="n"/>
@@ -18577,23 +18717,23 @@
         </is>
       </c>
       <c r="L63" s="26" t="n">
-        <v>-163</v>
+        <v>-113</v>
       </c>
       <c r="M63" s="27" t="n">
-        <v>1.613497</v>
+        <v>1.884956</v>
       </c>
       <c r="N63" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.530516</v>
       </c>
       <c r="O63" s="28" t="n">
-        <v>0.500208</v>
+        <v>0.535018</v>
       </c>
       <c r="P63" s="28" t="n"/>
       <c r="Q63" s="28" t="n">
-        <v>-0.119564</v>
+        <v>0.004502</v>
       </c>
       <c r="R63" s="26" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="S63" s="29" t="n">
         <v>1</v>
@@ -18619,7 +18759,7 @@
       <c r="AD63" s="24" t="n"/>
       <c r="AE63" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-lol-nort-wd-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.5300 (market_slug=aec-lol-tse-7rex-2026-08-05).</t>
         </is>
       </c>
       <c r="AF63" s="31" t="inlineStr">
@@ -18660,32 +18800,32 @@
       </c>
       <c r="AP63" s="24" t="inlineStr">
         <is>
-          <t>White Dragons</t>
+          <t>7REX</t>
         </is>
       </c>
       <c r="AQ63" s="24" t="inlineStr">
         <is>
-          <t>White Dragons</t>
+          <t>7REX</t>
         </is>
       </c>
       <c r="AR63" s="24" t="inlineStr">
         <is>
-          <t>White Dragons</t>
+          <t>7REX</t>
         </is>
       </c>
       <c r="AS63" s="24" t="inlineStr">
         <is>
-          <t>NORTHERNGRADE ESPORTS</t>
+          <t>Team Solid</t>
         </is>
       </c>
       <c r="AT63" s="24" t="inlineStr">
         <is>
-          <t>NORTHERNGRADE ESPORTS</t>
+          <t>Team Solid</t>
         </is>
       </c>
       <c r="AU63" s="24" t="inlineStr">
         <is>
-          <t>NORTHERNGRADE ESPORTS</t>
+          <t>Team Solid</t>
         </is>
       </c>
       <c r="AV63" s="24" t="n"/>
@@ -18703,7 +18843,7 @@
       </c>
       <c r="BA63" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BB63" s="24" t="inlineStr">
@@ -18718,7 +18858,7 @@
       </c>
       <c r="BD63" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BE63" s="24" t="inlineStr">
@@ -18738,7 +18878,7 @@
       </c>
       <c r="BH63" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:54.377453Z</t>
+          <t>2026-08-04T14:27:12.222292Z</t>
         </is>
       </c>
       <c r="BI63" s="24" t="inlineStr">
@@ -18748,13 +18888,13 @@
       </c>
       <c r="BJ63" s="25" t="n"/>
       <c r="BK63" s="26" t="n">
-        <v>-163</v>
+        <v>-113</v>
       </c>
       <c r="BL63" s="27" t="n">
-        <v>1.613497</v>
+        <v>1.884956</v>
       </c>
       <c r="BM63" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.530516</v>
       </c>
       <c r="BN63" s="28" t="n"/>
       <c r="BO63" s="28" t="n"/>
@@ -18786,31 +18926,32 @@
       <c r="CO63" s="24" t="n"/>
       <c r="CP63" s="24" t="n"/>
       <c r="CQ63" s="24" t="n"/>
-      <c r="CR63" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
+      <c r="CR63" s="24" t="n"/>
+      <c r="CS63" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="64" ht="36" customHeight="1">
       <c r="A64" s="24" t="inlineStr">
         <is>
-          <t>5244e146f1fe46d5</t>
+          <t>4099198ffad042d7</t>
         </is>
       </c>
       <c r="B64" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:56.469660Z</t>
+          <t>2026-08-04T14:27:16.244146Z</t>
         </is>
       </c>
       <c r="C64" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T22:00:00Z</t>
+          <t>2026-08-05T21:00:00Z</t>
         </is>
       </c>
       <c r="D64" s="24" t="inlineStr">
         <is>
-          <t>70379</t>
+          <t>70349</t>
         </is>
       </c>
       <c r="E64" s="24" t="inlineStr">
@@ -18820,12 +18961,12 @@
       </c>
       <c r="F64" s="24" t="inlineStr">
         <is>
-          <t>KaBuM! Ilha das Lendas</t>
+          <t>Winthrop University</t>
         </is>
       </c>
       <c r="G64" s="24" t="inlineStr">
         <is>
-          <t>Ei Nerd Esports</t>
+          <t>Blue Otter</t>
         </is>
       </c>
       <c r="H64" s="24" t="inlineStr">
@@ -18845,26 +18986,26 @@
         </is>
       </c>
       <c r="L64" s="26" t="n">
-        <v>133</v>
+        <v>-213</v>
       </c>
       <c r="M64" s="27" t="n">
-        <v>2.33</v>
+        <v>1.469484</v>
       </c>
       <c r="N64" s="28" t="n">
-        <v>0.429185</v>
+        <v>0.680511</v>
       </c>
       <c r="O64" s="28" t="n">
-        <v>0.5668840000000001</v>
+        <v>0.648163</v>
       </c>
       <c r="P64" s="28" t="n"/>
       <c r="Q64" s="28" t="n">
-        <v>0.137699</v>
+        <v>-0.032348</v>
       </c>
       <c r="R64" s="26" t="n">
-        <v>89</v>
+        <v>4</v>
       </c>
       <c r="S64" s="29" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="T64" s="24" t="inlineStr">
         <is>
@@ -18887,7 +19028,7 @@
       <c r="AD64" s="24" t="n"/>
       <c r="AE64" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4300 (market_slug=aec-lol-nerd-kbm-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-lol-blue-wu-2026-08-05).</t>
         </is>
       </c>
       <c r="AF64" s="31" t="inlineStr">
@@ -18905,7 +19046,7 @@
       <c r="AJ64" s="31" t="n"/>
       <c r="AK64" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL64" s="26" t="n">
@@ -18913,47 +19054,47 @@
       </c>
       <c r="AM64" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN64" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO64" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP64" s="24" t="inlineStr">
         <is>
-          <t>KaBuM! Ilha das Lendas</t>
+          <t>Winthrop University</t>
         </is>
       </c>
       <c r="AQ64" s="24" t="inlineStr">
         <is>
-          <t>KaBuM! Ilha das Lendas</t>
+          <t>Winthrop University</t>
         </is>
       </c>
       <c r="AR64" s="24" t="inlineStr">
         <is>
-          <t>KaBuM! Ilha das Lendas</t>
+          <t>Winthrop University</t>
         </is>
       </c>
       <c r="AS64" s="24" t="inlineStr">
         <is>
-          <t>Ei Nerd Esports</t>
+          <t>Blue Otter</t>
         </is>
       </c>
       <c r="AT64" s="24" t="inlineStr">
         <is>
-          <t>Ei Nerd Esports</t>
+          <t>Blue Otter</t>
         </is>
       </c>
       <c r="AU64" s="24" t="inlineStr">
         <is>
-          <t>Ei Nerd Esports</t>
+          <t>Blue Otter</t>
         </is>
       </c>
       <c r="AV64" s="24" t="n"/>
@@ -18971,7 +19112,7 @@
       </c>
       <c r="BA64" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BB64" s="24" t="inlineStr">
@@ -18986,7 +19127,7 @@
       </c>
       <c r="BD64" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BE64" s="24" t="inlineStr">
@@ -19006,7 +19147,7 @@
       </c>
       <c r="BH64" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:54.874184Z</t>
+          <t>2026-08-04T14:27:12.884488Z</t>
         </is>
       </c>
       <c r="BI64" s="24" t="inlineStr">
@@ -19016,13 +19157,13 @@
       </c>
       <c r="BJ64" s="25" t="n"/>
       <c r="BK64" s="26" t="n">
-        <v>133</v>
+        <v>-213</v>
       </c>
       <c r="BL64" s="27" t="n">
-        <v>2.33</v>
+        <v>1.469484</v>
       </c>
       <c r="BM64" s="28" t="n">
-        <v>0.429185</v>
+        <v>0.680511</v>
       </c>
       <c r="BN64" s="28" t="n"/>
       <c r="BO64" s="28" t="n"/>
@@ -19054,31 +19195,32 @@
       <c r="CO64" s="24" t="n"/>
       <c r="CP64" s="24" t="n"/>
       <c r="CQ64" s="24" t="n"/>
-      <c r="CR64" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
+      <c r="CR64" s="24" t="n"/>
+      <c r="CS64" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="65" ht="36" customHeight="1">
       <c r="A65" s="24" t="inlineStr">
         <is>
-          <t>3dae42edf8664905</t>
+          <t>6d414b8a9cd74546</t>
         </is>
       </c>
       <c r="B65" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:56.469660Z</t>
+          <t>2026-08-04T14:27:16.244146Z</t>
         </is>
       </c>
       <c r="C65" s="24" t="inlineStr">
         <is>
-          <t>2026-08-06T00:00:00Z</t>
+          <t>2026-08-05T22:00:00Z</t>
         </is>
       </c>
       <c r="D65" s="24" t="inlineStr">
         <is>
-          <t>70454</t>
+          <t>70379</t>
         </is>
       </c>
       <c r="E65" s="24" t="inlineStr">
@@ -19088,12 +19230,12 @@
       </c>
       <c r="F65" s="24" t="inlineStr">
         <is>
-          <t>Cupid Esports</t>
+          <t>KaBuM! Ilha das Lendas</t>
         </is>
       </c>
       <c r="G65" s="24" t="inlineStr">
         <is>
-          <t>NRG Esports</t>
+          <t>Ei Nerd Esports</t>
         </is>
       </c>
       <c r="H65" s="24" t="inlineStr">
@@ -19103,7 +19245,7 @@
       </c>
       <c r="I65" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J65" s="25" t="n"/>
@@ -19113,23 +19255,23 @@
         </is>
       </c>
       <c r="L65" s="26" t="n">
-        <v>-163</v>
+        <v>122</v>
       </c>
       <c r="M65" s="27" t="n">
-        <v>1.613497</v>
+        <v>2.22</v>
       </c>
       <c r="N65" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.45045</v>
       </c>
       <c r="O65" s="28" t="n">
-        <v>0.515927</v>
+        <v>0.565806</v>
       </c>
       <c r="P65" s="28" t="n"/>
       <c r="Q65" s="28" t="n">
-        <v>-0.103845</v>
+        <v>0.115356</v>
       </c>
       <c r="R65" s="26" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="S65" s="29" t="n">
         <v>1</v>
@@ -19155,7 +19297,7 @@
       <c r="AD65" s="24" t="n"/>
       <c r="AE65" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-lol-nrg-cpd-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-lol-nerd-kbm-2026-08-05).</t>
         </is>
       </c>
       <c r="AF65" s="31" t="inlineStr">
@@ -19173,7 +19315,7 @@
       <c r="AJ65" s="31" t="n"/>
       <c r="AK65" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL65" s="26" t="n">
@@ -19181,47 +19323,47 @@
       </c>
       <c r="AM65" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN65" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO65" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP65" s="24" t="inlineStr">
         <is>
-          <t>Cupid Esports</t>
+          <t>KaBuM! Ilha das Lendas</t>
         </is>
       </c>
       <c r="AQ65" s="24" t="inlineStr">
         <is>
-          <t>Cupid Esports</t>
+          <t>KaBuM! Ilha das Lendas</t>
         </is>
       </c>
       <c r="AR65" s="24" t="inlineStr">
         <is>
-          <t>Cupid Esports</t>
+          <t>KaBuM! Ilha das Lendas</t>
         </is>
       </c>
       <c r="AS65" s="24" t="inlineStr">
         <is>
-          <t>NRG Esports</t>
+          <t>Ei Nerd Esports</t>
         </is>
       </c>
       <c r="AT65" s="24" t="inlineStr">
         <is>
-          <t>NRG Esports</t>
+          <t>Ei Nerd Esports</t>
         </is>
       </c>
       <c r="AU65" s="24" t="inlineStr">
         <is>
-          <t>NRG Esports</t>
+          <t>Ei Nerd Esports</t>
         </is>
       </c>
       <c r="AV65" s="24" t="n"/>
@@ -19239,7 +19381,7 @@
       </c>
       <c r="BA65" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BB65" s="24" t="inlineStr">
@@ -19254,7 +19396,7 @@
       </c>
       <c r="BD65" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BE65" s="24" t="inlineStr">
@@ -19274,7 +19416,7 @@
       </c>
       <c r="BH65" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:55.920586Z</t>
+          <t>2026-08-04T14:27:14.606628Z</t>
         </is>
       </c>
       <c r="BI65" s="24" t="inlineStr">
@@ -19284,13 +19426,13 @@
       </c>
       <c r="BJ65" s="25" t="n"/>
       <c r="BK65" s="26" t="n">
-        <v>-163</v>
+        <v>122</v>
       </c>
       <c r="BL65" s="27" t="n">
-        <v>1.613497</v>
+        <v>2.22</v>
       </c>
       <c r="BM65" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.45045</v>
       </c>
       <c r="BN65" s="28" t="n"/>
       <c r="BO65" s="28" t="n"/>
@@ -19322,21 +19464,22 @@
       <c r="CO65" s="24" t="n"/>
       <c r="CP65" s="24" t="n"/>
       <c r="CQ65" s="24" t="n"/>
-      <c r="CR65" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
+      <c r="CR65" s="24" t="n"/>
+      <c r="CS65" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="66" ht="36" customHeight="1">
       <c r="A66" s="24" t="inlineStr">
         <is>
-          <t>c88d2da337744db9</t>
+          <t>f40884a86e874074</t>
         </is>
       </c>
       <c r="B66" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:56.469660Z</t>
+          <t>2026-08-04T14:27:16.244146Z</t>
         </is>
       </c>
       <c r="C66" s="24" t="inlineStr">
@@ -19346,7 +19489,7 @@
       </c>
       <c r="D66" s="24" t="inlineStr">
         <is>
-          <t>70453</t>
+          <t>70454</t>
         </is>
       </c>
       <c r="E66" s="24" t="inlineStr">
@@ -19356,12 +19499,12 @@
       </c>
       <c r="F66" s="24" t="inlineStr">
         <is>
-          <t>paiN Gaming Academy</t>
+          <t>Cupid Esports</t>
         </is>
       </c>
       <c r="G66" s="24" t="inlineStr">
         <is>
-          <t>INTZ e-Sports</t>
+          <t>NRG Esports</t>
         </is>
       </c>
       <c r="H66" s="24" t="inlineStr">
@@ -19371,7 +19514,7 @@
       </c>
       <c r="I66" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J66" s="25" t="n"/>
@@ -19381,26 +19524,26 @@
         </is>
       </c>
       <c r="L66" s="26" t="n">
-        <v>-133</v>
+        <v>-163</v>
       </c>
       <c r="M66" s="27" t="n">
-        <v>1.75188</v>
+        <v>1.613497</v>
       </c>
       <c r="N66" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.619772</v>
       </c>
       <c r="O66" s="28" t="n">
-        <v>0.590765</v>
+        <v>0.51652</v>
       </c>
       <c r="P66" s="28" t="n"/>
       <c r="Q66" s="28" t="n">
-        <v>0.01995</v>
+        <v>-0.103252</v>
       </c>
       <c r="R66" s="26" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="S66" s="29" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="T66" s="24" t="inlineStr">
         <is>
@@ -19423,7 +19566,7 @@
       <c r="AD66" s="24" t="n"/>
       <c r="AE66" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-lol-itz-pnga-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-lol-nrg-cpd-2026-08-06).</t>
         </is>
       </c>
       <c r="AF66" s="31" t="inlineStr">
@@ -19441,7 +19584,7 @@
       <c r="AJ66" s="31" t="n"/>
       <c r="AK66" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL66" s="26" t="n">
@@ -19449,47 +19592,47 @@
       </c>
       <c r="AM66" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN66" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO66" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP66" s="24" t="inlineStr">
         <is>
-          <t>paiN Gaming Academy</t>
+          <t>Cupid Esports</t>
         </is>
       </c>
       <c r="AQ66" s="24" t="inlineStr">
         <is>
-          <t>paiN Gaming Academy</t>
+          <t>Cupid Esports</t>
         </is>
       </c>
       <c r="AR66" s="24" t="inlineStr">
         <is>
-          <t>paiN Gaming Academy</t>
+          <t>Cupid Esports</t>
         </is>
       </c>
       <c r="AS66" s="24" t="inlineStr">
         <is>
-          <t>INTZ e-Sports</t>
+          <t>NRG Esports</t>
         </is>
       </c>
       <c r="AT66" s="24" t="inlineStr">
         <is>
-          <t>INTZ e-Sports</t>
+          <t>NRG Esports</t>
         </is>
       </c>
       <c r="AU66" s="24" t="inlineStr">
         <is>
-          <t>INTZ e-Sports</t>
+          <t>NRG Esports</t>
         </is>
       </c>
       <c r="AV66" s="24" t="n"/>
@@ -19507,7 +19650,7 @@
       </c>
       <c r="BA66" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BB66" s="24" t="inlineStr">
@@ -19522,7 +19665,7 @@
       </c>
       <c r="BD66" s="24" t="inlineStr">
         <is>
-          <t>2aef9ef293099f7e3d21d8b6a25daad858c9b2bc1905102110b3b5d06e41ccd8</t>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
         </is>
       </c>
       <c r="BE66" s="24" t="inlineStr">
@@ -19542,7 +19685,7 @@
       </c>
       <c r="BH66" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:56.469425Z</t>
+          <t>2026-08-04T14:27:15.697177Z</t>
         </is>
       </c>
       <c r="BI66" s="24" t="inlineStr">
@@ -19552,13 +19695,13 @@
       </c>
       <c r="BJ66" s="25" t="n"/>
       <c r="BK66" s="26" t="n">
-        <v>-133</v>
+        <v>-163</v>
       </c>
       <c r="BL66" s="27" t="n">
-        <v>1.75188</v>
+        <v>1.613497</v>
       </c>
       <c r="BM66" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.619772</v>
       </c>
       <c r="BN66" s="28" t="n"/>
       <c r="BO66" s="28" t="n"/>
@@ -19590,7 +19733,277 @@
       <c r="CO66" s="24" t="n"/>
       <c r="CP66" s="24" t="n"/>
       <c r="CQ66" s="24" t="n"/>
-      <c r="CR66" s="24" t="inlineStr">
+      <c r="CR66" s="24" t="n"/>
+      <c r="CS66" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="36" customHeight="1">
+      <c r="A67" s="24" t="inlineStr">
+        <is>
+          <t>e597e0228d814ec0</t>
+        </is>
+      </c>
+      <c r="B67" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:27:16.244146Z</t>
+        </is>
+      </c>
+      <c r="C67" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D67" s="24" t="inlineStr">
+        <is>
+          <t>70453</t>
+        </is>
+      </c>
+      <c r="E67" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F67" s="24" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="G67" s="24" t="inlineStr">
+        <is>
+          <t>INTZ e-Sports</t>
+        </is>
+      </c>
+      <c r="H67" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I67" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J67" s="25" t="n"/>
+      <c r="K67" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L67" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="M67" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="N67" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="O67" s="28" t="n">
+        <v>0.589642</v>
+      </c>
+      <c r="P67" s="28" t="n"/>
+      <c r="Q67" s="28" t="n">
+        <v>0.018827</v>
+      </c>
+      <c r="R67" s="26" t="n">
+        <v>29</v>
+      </c>
+      <c r="S67" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T67" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U67" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V67" s="24" t="n"/>
+      <c r="W67" s="26" t="n"/>
+      <c r="X67" s="26" t="n"/>
+      <c r="Y67" s="25" t="n"/>
+      <c r="Z67" s="26" t="n"/>
+      <c r="AA67" s="28" t="n"/>
+      <c r="AB67" s="28" t="n"/>
+      <c r="AC67" s="30" t="n"/>
+      <c r="AD67" s="24" t="n"/>
+      <c r="AE67" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-lol-itz-pnga-2026-08-06).</t>
+        </is>
+      </c>
+      <c r="AF67" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG67" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH67" s="24" t="n"/>
+      <c r="AI67" s="31" t="n"/>
+      <c r="AJ67" s="31" t="n"/>
+      <c r="AK67" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL67" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM67" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN67" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO67" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP67" s="24" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="AQ67" s="24" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="AR67" s="24" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="AS67" s="24" t="inlineStr">
+        <is>
+          <t>INTZ e-Sports</t>
+        </is>
+      </c>
+      <c r="AT67" s="24" t="inlineStr">
+        <is>
+          <t>INTZ e-Sports</t>
+        </is>
+      </c>
+      <c r="AU67" s="24" t="inlineStr">
+        <is>
+          <t>INTZ e-Sports</t>
+        </is>
+      </c>
+      <c r="AV67" s="24" t="n"/>
+      <c r="AW67" s="24" t="n"/>
+      <c r="AX67" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY67" s="24" t="n"/>
+      <c r="AZ67" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA67" s="24" t="inlineStr">
+        <is>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
+        </is>
+      </c>
+      <c r="BB67" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC67" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD67" s="24" t="inlineStr">
+        <is>
+          <t>dc7b77701ce4867ddb9f1c332c65fa1da3998834e1696c65cab5baeb3fdce959</t>
+        </is>
+      </c>
+      <c r="BE67" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF67" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG67" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH67" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:27:16.243697Z</t>
+        </is>
+      </c>
+      <c r="BI67" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ67" s="25" t="n"/>
+      <c r="BK67" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="BL67" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="BM67" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="BN67" s="28" t="n"/>
+      <c r="BO67" s="28" t="n"/>
+      <c r="BP67" s="25" t="n"/>
+      <c r="BQ67" s="27" t="n"/>
+      <c r="BR67" s="28" t="n"/>
+      <c r="BS67" s="28" t="n"/>
+      <c r="BT67" s="28" t="n"/>
+      <c r="BU67" s="25" t="n"/>
+      <c r="BV67" s="29" t="n"/>
+      <c r="BW67" s="24" t="n"/>
+      <c r="BX67" s="30" t="n"/>
+      <c r="BY67" s="27" t="n"/>
+      <c r="BZ67" s="24" t="n"/>
+      <c r="CA67" s="31" t="n"/>
+      <c r="CB67" s="24" t="n"/>
+      <c r="CC67" s="24" t="n"/>
+      <c r="CD67" s="24" t="n"/>
+      <c r="CE67" s="24" t="n"/>
+      <c r="CF67" s="24" t="n"/>
+      <c r="CG67" s="24" t="n"/>
+      <c r="CH67" s="24" t="n"/>
+      <c r="CI67" s="24" t="n"/>
+      <c r="CJ67" s="24" t="n"/>
+      <c r="CK67" s="24" t="n"/>
+      <c r="CL67" s="24" t="n"/>
+      <c r="CM67" s="24" t="n"/>
+      <c r="CN67" s="24" t="n"/>
+      <c r="CO67" s="24" t="n"/>
+      <c r="CP67" s="24" t="n"/>
+      <c r="CQ67" s="24" t="n"/>
+      <c r="CR67" s="24" t="n"/>
+      <c r="CS67" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>

--- a/data/research/lol.xlsx
+++ b/data/research/lol.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Picks" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Picks" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Summary'!$A$1:$L$19</definedName>
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS88" headerRowCount="1">
-  <autoFilter ref="A1:CS88"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS86" headerRowCount="1">
+  <autoFilter ref="A1:CS86"/>
   <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -756,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$88)</f>
+        <f>COUNTA('Picks'!$A$2:$A$86)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$88,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$86,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$88,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$86,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$88,"settled",'Picks'!$V$2:$V$88,"win")+COUNTIFS('Picks'!$U$2:$U$88,"settled",'Picks'!$V$2:$V$88,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$86,"settled",'Picks'!$V$2:$V$86,"win")+COUNTIFS('Picks'!$U$2:$U$86,"settled",'Picks'!$V$2:$V$86,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -796,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$88,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$86,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$88,"&gt;0",'Picks'!$V$2:$V$88,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$88,"&gt;0",'Picks'!$V$2:$V$88,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$86,"&gt;0",'Picks'!$V$2:$V$86,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$86,"&gt;0",'Picks'!$V$2:$V$86,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$88,"&gt;0",'Picks'!$V$2:$V$88,"win")/(COUNTIFS('Picks'!$BX$2:$BX$88,"&gt;0",'Picks'!$V$2:$V$88,"win")+COUNTIFS('Picks'!$BX$2:$BX$88,"&gt;0",'Picks'!$V$2:$V$88,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$86,"&gt;0",'Picks'!$V$2:$V$86,"win")/(COUNTIFS('Picks'!$BX$2:$BX$86,"&gt;0",'Picks'!$V$2:$V$86,"win")+COUNTIFS('Picks'!$BX$2:$BX$86,"&gt;0",'Picks'!$V$2:$V$86,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$88)/SUM('Picks'!$BX$2:$BX$88),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$86)/SUM('Picks'!$BX$2:$BX$86),0)</f>
         <v/>
       </c>
     </row>
@@ -836,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$88)</f>
+        <f>SUM('Picks'!$BY$2:$BY$86)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$88,"&lt;&gt;",'Picks'!$AB$2:$AB$88),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$86,"&lt;&gt;",'Picks'!$AB$2:$AB$86),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$88,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$88,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$86,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$86,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$88,'Picks'!$AM$2:$AM$88,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$86,'Picks'!$AM$2:$AM$86,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -903,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$88,$A14,'Picks'!$U$2:$U$88,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$86,$A14,'Picks'!$U$2:$U$86,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$88,$A14,'Picks'!$U$2:$U$88,"settled",'Picks'!$V$2:$V$88,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$86,$A14,'Picks'!$U$2:$U$86,"settled",'Picks'!$V$2:$V$86,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$88,$A14,'Picks'!$U$2:$U$88,"settled",'Picks'!$V$2:$V$88,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$86,$A14,'Picks'!$U$2:$U$86,"settled",'Picks'!$V$2:$V$86,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -919,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$88,'Picks'!$H$2:$H$88,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$86,'Picks'!$H$2:$H$86,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$88,'Picks'!$H$2:$H$88,$A14,'Picks'!$U$2:$U$88,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$86,'Picks'!$H$2:$H$86,$A14,'Picks'!$U$2:$U$86,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -934,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$88,$A15,'Picks'!$U$2:$U$88,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$86,$A15,'Picks'!$U$2:$U$86,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$88,$A15,'Picks'!$U$2:$U$88,"settled",'Picks'!$V$2:$V$88,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$86,$A15,'Picks'!$U$2:$U$86,"settled",'Picks'!$V$2:$V$86,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$88,$A15,'Picks'!$U$2:$U$88,"settled",'Picks'!$V$2:$V$88,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$86,$A15,'Picks'!$U$2:$U$86,"settled",'Picks'!$V$2:$V$86,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -950,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$88,'Picks'!$H$2:$H$88,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$86,'Picks'!$H$2:$H$86,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$88,'Picks'!$H$2:$H$88,$A15,'Picks'!$U$2:$U$88,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$86,'Picks'!$H$2:$H$86,$A15,'Picks'!$U$2:$U$86,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -965,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$88,$A16,'Picks'!$U$2:$U$88,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$86,$A16,'Picks'!$U$2:$U$86,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$88,$A16,'Picks'!$U$2:$U$88,"settled",'Picks'!$V$2:$V$88,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$86,$A16,'Picks'!$U$2:$U$86,"settled",'Picks'!$V$2:$V$86,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$88,$A16,'Picks'!$U$2:$U$88,"settled",'Picks'!$V$2:$V$88,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$86,$A16,'Picks'!$U$2:$U$86,"settled",'Picks'!$V$2:$V$86,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -981,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$88,'Picks'!$H$2:$H$88,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$86,'Picks'!$H$2:$H$86,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$88,'Picks'!$H$2:$H$88,$A16,'Picks'!$U$2:$U$88,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$86,'Picks'!$H$2:$H$86,$A16,'Picks'!$U$2:$U$86,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS88"/>
+  <dimension ref="A1:CS86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -14215,18 +14215,38 @@
       </c>
       <c r="U45" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V45" s="24" t="n"/>
-      <c r="W45" s="26" t="n"/>
-      <c r="X45" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V45" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W45" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X45" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y45" s="25" t="n"/>
-      <c r="Z45" s="26" t="n"/>
-      <c r="AA45" s="28" t="n"/>
-      <c r="AB45" s="28" t="n"/>
-      <c r="AC45" s="30" t="n"/>
-      <c r="AD45" s="24" t="n"/>
+      <c r="Z45" s="26" t="n">
+        <v>144</v>
+      </c>
+      <c r="AA45" s="28" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AB45" s="28" t="n">
+        <v>-0.010168</v>
+      </c>
+      <c r="AC45" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD45" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:17:46.347305Z</t>
+        </is>
+      </c>
       <c r="AE45" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-lol-foxy-krxc-2026-08-05).</t>
@@ -14239,7 +14259,7 @@
       </c>
       <c r="AG45" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH45" s="24" t="n"/>
@@ -14369,8 +14389,12 @@
       <c r="BN45" s="28" t="n"/>
       <c r="BO45" s="28" t="n"/>
       <c r="BP45" s="25" t="n"/>
-      <c r="BQ45" s="27" t="n"/>
-      <c r="BR45" s="28" t="n"/>
+      <c r="BQ45" s="27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BR45" s="28" t="n">
+        <v>0.41</v>
+      </c>
       <c r="BS45" s="28" t="n"/>
       <c r="BT45" s="28" t="n"/>
       <c r="BU45" s="25" t="n"/>
@@ -14484,18 +14508,38 @@
       </c>
       <c r="U46" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V46" s="24" t="n"/>
-      <c r="W46" s="26" t="n"/>
-      <c r="X46" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V46" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W46" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y46" s="25" t="n"/>
-      <c r="Z46" s="26" t="n"/>
-      <c r="AA46" s="28" t="n"/>
-      <c r="AB46" s="28" t="n"/>
-      <c r="AC46" s="30" t="n"/>
-      <c r="AD46" s="24" t="n"/>
+      <c r="Z46" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="AA46" s="28" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AB46" s="28" t="n">
+        <v>0.000196</v>
+      </c>
+      <c r="AC46" s="30" t="n">
+        <v>1.6827</v>
+      </c>
+      <c r="AD46" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:17:48.746724Z</t>
+        </is>
+      </c>
       <c r="AE46" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-lol-dkc-nsea-2026-08-05).</t>
@@ -14638,8 +14682,12 @@
       <c r="BN46" s="28" t="n"/>
       <c r="BO46" s="28" t="n"/>
       <c r="BP46" s="25" t="n"/>
-      <c r="BQ46" s="27" t="n"/>
-      <c r="BR46" s="28" t="n"/>
+      <c r="BQ46" s="27" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="BR46" s="28" t="n">
+        <v>0.51</v>
+      </c>
       <c r="BS46" s="28" t="n"/>
       <c r="BT46" s="28" t="n"/>
       <c r="BU46" s="25" t="n"/>
@@ -14753,18 +14801,38 @@
       </c>
       <c r="U47" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V47" s="24" t="n"/>
-      <c r="W47" s="26" t="n"/>
-      <c r="X47" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V47" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W47" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y47" s="25" t="n"/>
-      <c r="Z47" s="26" t="n"/>
-      <c r="AA47" s="28" t="n"/>
-      <c r="AB47" s="28" t="n"/>
-      <c r="AC47" s="30" t="n"/>
-      <c r="AD47" s="24" t="n"/>
+      <c r="Z47" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="AA47" s="28" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AB47" s="28" t="n">
+        <v>-0.000402</v>
+      </c>
+      <c r="AC47" s="30" t="n">
+        <v>0.8969</v>
+      </c>
+      <c r="AD47" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:41:19.592577Z</t>
+        </is>
+      </c>
       <c r="AE47" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-lol-fnl-nme-2026-08-05).</t>
@@ -14907,8 +14975,12 @@
       <c r="BN47" s="28" t="n"/>
       <c r="BO47" s="28" t="n"/>
       <c r="BP47" s="25" t="n"/>
-      <c r="BQ47" s="27" t="n"/>
-      <c r="BR47" s="28" t="n"/>
+      <c r="BQ47" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="BR47" s="28" t="n">
+        <v>0.6899999999999999</v>
+      </c>
       <c r="BS47" s="28" t="n"/>
       <c r="BT47" s="28" t="n"/>
       <c r="BU47" s="25" t="n"/>
@@ -15022,18 +15094,38 @@
       </c>
       <c r="U48" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V48" s="24" t="n"/>
-      <c r="W48" s="26" t="n"/>
-      <c r="X48" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V48" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W48" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y48" s="25" t="n"/>
-      <c r="Z48" s="26" t="n"/>
-      <c r="AA48" s="28" t="n"/>
-      <c r="AB48" s="28" t="n"/>
-      <c r="AC48" s="30" t="n"/>
-      <c r="AD48" s="24" t="n"/>
+      <c r="Z48" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="AA48" s="28" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AB48" s="28" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="AC48" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD48" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:41:21.920279Z</t>
+        </is>
+      </c>
       <c r="AE48" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-lol-bro-ns-2026-08-05).</t>
@@ -15046,7 +15138,7 @@
       </c>
       <c r="AG48" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH48" s="24" t="n"/>
@@ -15176,8 +15268,12 @@
       <c r="BN48" s="28" t="n"/>
       <c r="BO48" s="28" t="n"/>
       <c r="BP48" s="25" t="n"/>
-      <c r="BQ48" s="27" t="n"/>
-      <c r="BR48" s="28" t="n"/>
+      <c r="BQ48" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="BR48" s="28" t="n">
+        <v>0.7</v>
+      </c>
       <c r="BS48" s="28" t="n"/>
       <c r="BT48" s="28" t="n"/>
       <c r="BU48" s="25" t="n"/>
@@ -15482,12 +15578,12 @@
     <row r="50" ht="36" customHeight="1">
       <c r="A50" s="24" t="inlineStr">
         <is>
-          <t>2e8376312ae34efa</t>
+          <t>244e97086bfd444f</t>
         </is>
       </c>
       <c r="B50" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:12.089327Z</t>
+          <t>2026-08-05T13:56:43.896254Z</t>
         </is>
       </c>
       <c r="C50" s="24" t="inlineStr">
@@ -15497,7 +15593,7 @@
       </c>
       <c r="D50" s="24" t="inlineStr">
         <is>
-          <t>69817</t>
+          <t>69818</t>
         </is>
       </c>
       <c r="E50" s="24" t="inlineStr">
@@ -15507,12 +15603,12 @@
       </c>
       <c r="F50" s="24" t="inlineStr">
         <is>
-          <t>The Secret Club</t>
+          <t>Pyramid IV Esports</t>
         </is>
       </c>
       <c r="G50" s="24" t="inlineStr">
         <is>
-          <t>⁠Hooligans</t>
+          <t>JSK Esports</t>
         </is>
       </c>
       <c r="H50" s="24" t="inlineStr">
@@ -15532,23 +15628,23 @@
         </is>
       </c>
       <c r="L50" s="26" t="n">
-        <v>-203</v>
+        <v>138</v>
       </c>
       <c r="M50" s="27" t="n">
-        <v>1.492611</v>
+        <v>2.38</v>
       </c>
       <c r="N50" s="28" t="n">
-        <v>0.669967</v>
+        <v>0.420168</v>
       </c>
       <c r="O50" s="28" t="n">
-        <v>0.528935</v>
+        <v>0.513767</v>
       </c>
       <c r="P50" s="28" t="n"/>
       <c r="Q50" s="28" t="n">
-        <v>-0.141032</v>
+        <v>0.093599</v>
       </c>
       <c r="R50" s="26" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="S50" s="29" t="n">
         <v>1</v>
@@ -15574,7 +15670,7 @@
       <c r="AD50" s="24" t="n"/>
       <c r="AE50" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-lol-hool-tsc-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-lol-jsk-piv-2026-08-05).</t>
         </is>
       </c>
       <c r="AF50" s="31" t="inlineStr">
@@ -15615,32 +15711,32 @@
       </c>
       <c r="AP50" s="24" t="inlineStr">
         <is>
-          <t>The Secret Club</t>
+          <t>Pyramid IV Esports</t>
         </is>
       </c>
       <c r="AQ50" s="24" t="inlineStr">
         <is>
-          <t>The Secret Club</t>
+          <t>Pyramid IV Esports</t>
         </is>
       </c>
       <c r="AR50" s="24" t="inlineStr">
         <is>
-          <t>The Secret Club</t>
+          <t>Pyramid IV Esports</t>
         </is>
       </c>
       <c r="AS50" s="24" t="inlineStr">
         <is>
-          <t>⁠Hooligans</t>
+          <t>JSK Esports</t>
         </is>
       </c>
       <c r="AT50" s="24" t="inlineStr">
         <is>
-          <t>⁠Hooligans</t>
+          <t>JSK Esports</t>
         </is>
       </c>
       <c r="AU50" s="24" t="inlineStr">
         <is>
-          <t>⁠Hooligans</t>
+          <t>JSK Esports</t>
         </is>
       </c>
       <c r="AV50" s="24" t="n"/>
@@ -15658,7 +15754,7 @@
       </c>
       <c r="BA50" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BB50" s="24" t="inlineStr">
@@ -15673,7 +15769,7 @@
       </c>
       <c r="BD50" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BE50" s="24" t="inlineStr">
@@ -15693,7 +15789,7 @@
       </c>
       <c r="BH50" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:20.048549Z</t>
+          <t>2026-08-05T13:56:11.509518Z</t>
         </is>
       </c>
       <c r="BI50" s="24" t="inlineStr">
@@ -15703,13 +15799,13 @@
       </c>
       <c r="BJ50" s="25" t="n"/>
       <c r="BK50" s="26" t="n">
-        <v>-203</v>
+        <v>138</v>
       </c>
       <c r="BL50" s="27" t="n">
-        <v>1.492611</v>
+        <v>2.38</v>
       </c>
       <c r="BM50" s="28" t="n">
-        <v>0.669967</v>
+        <v>0.420168</v>
       </c>
       <c r="BN50" s="28" t="n"/>
       <c r="BO50" s="28" t="n"/>
@@ -15744,19 +15840,19 @@
       <c r="CR50" s="24" t="n"/>
       <c r="CS50" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="51" ht="36" customHeight="1">
       <c r="A51" s="24" t="inlineStr">
         <is>
-          <t>b07d18621bd54510</t>
+          <t>00dd5007324144cb</t>
         </is>
       </c>
       <c r="B51" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:12.089327Z</t>
+          <t>2026-08-05T13:56:43.896254Z</t>
         </is>
       </c>
       <c r="C51" s="24" t="inlineStr">
@@ -15766,7 +15862,7 @@
       </c>
       <c r="D51" s="24" t="inlineStr">
         <is>
-          <t>69818</t>
+          <t>69819</t>
         </is>
       </c>
       <c r="E51" s="24" t="inlineStr">
@@ -15776,12 +15872,12 @@
       </c>
       <c r="F51" s="24" t="inlineStr">
         <is>
-          <t>Pyramid IV Esports</t>
+          <t>Epic Avalanche</t>
         </is>
       </c>
       <c r="G51" s="24" t="inlineStr">
         <is>
-          <t>JSK Esports</t>
+          <t>Brod n Friends</t>
         </is>
       </c>
       <c r="H51" s="24" t="inlineStr">
@@ -15791,7 +15887,7 @@
       </c>
       <c r="I51" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J51" s="25" t="n"/>
@@ -15801,23 +15897,23 @@
         </is>
       </c>
       <c r="L51" s="26" t="n">
-        <v>133</v>
+        <v>-178</v>
       </c>
       <c r="M51" s="27" t="n">
-        <v>2.33</v>
+        <v>1.561798</v>
       </c>
       <c r="N51" s="28" t="n">
-        <v>0.429185</v>
+        <v>0.640288</v>
       </c>
       <c r="O51" s="28" t="n">
-        <v>0.5136770000000001</v>
+        <v>0.530813</v>
       </c>
       <c r="P51" s="28" t="n"/>
       <c r="Q51" s="28" t="n">
-        <v>0.084492</v>
+        <v>-0.109475</v>
       </c>
       <c r="R51" s="26" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="S51" s="29" t="n">
         <v>1</v>
@@ -15843,7 +15939,7 @@
       <c r="AD51" s="24" t="n"/>
       <c r="AE51" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4300 (market_slug=aec-lol-jsk-piv-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-lol-bnf-ea-2026-08-05).</t>
         </is>
       </c>
       <c r="AF51" s="31" t="inlineStr">
@@ -15884,32 +15980,32 @@
       </c>
       <c r="AP51" s="24" t="inlineStr">
         <is>
-          <t>Pyramid IV Esports</t>
+          <t>Epic Avalanche</t>
         </is>
       </c>
       <c r="AQ51" s="24" t="inlineStr">
         <is>
-          <t>Pyramid IV Esports</t>
+          <t>Epic Avalanche</t>
         </is>
       </c>
       <c r="AR51" s="24" t="inlineStr">
         <is>
-          <t>Pyramid IV Esports</t>
+          <t>Epic Avalanche</t>
         </is>
       </c>
       <c r="AS51" s="24" t="inlineStr">
         <is>
-          <t>JSK Esports</t>
+          <t>Brod n Friends</t>
         </is>
       </c>
       <c r="AT51" s="24" t="inlineStr">
         <is>
-          <t>JSK Esports</t>
+          <t>Brod n Friends</t>
         </is>
       </c>
       <c r="AU51" s="24" t="inlineStr">
         <is>
-          <t>JSK Esports</t>
+          <t>Brod n Friends</t>
         </is>
       </c>
       <c r="AV51" s="24" t="n"/>
@@ -15927,7 +16023,7 @@
       </c>
       <c r="BA51" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BB51" s="24" t="inlineStr">
@@ -15942,7 +16038,7 @@
       </c>
       <c r="BD51" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BE51" s="24" t="inlineStr">
@@ -15962,7 +16058,7 @@
       </c>
       <c r="BH51" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:20.872989Z</t>
+          <t>2026-08-05T13:56:12.050160Z</t>
         </is>
       </c>
       <c r="BI51" s="24" t="inlineStr">
@@ -15972,13 +16068,13 @@
       </c>
       <c r="BJ51" s="25" t="n"/>
       <c r="BK51" s="26" t="n">
-        <v>133</v>
+        <v>-178</v>
       </c>
       <c r="BL51" s="27" t="n">
-        <v>2.33</v>
+        <v>1.561798</v>
       </c>
       <c r="BM51" s="28" t="n">
-        <v>0.429185</v>
+        <v>0.640288</v>
       </c>
       <c r="BN51" s="28" t="n"/>
       <c r="BO51" s="28" t="n"/>
@@ -16013,29 +16109,29 @@
       <c r="CR51" s="24" t="n"/>
       <c r="CS51" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="52" ht="36" customHeight="1">
       <c r="A52" s="24" t="inlineStr">
         <is>
-          <t>146c2cfc849d449d</t>
+          <t>e600d12fed3b4a7c</t>
         </is>
       </c>
       <c r="B52" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:12.089327Z</t>
+          <t>2026-08-05T13:56:43.896254Z</t>
         </is>
       </c>
       <c r="C52" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T16:00:00Z</t>
+          <t>2026-08-05T17:00:00Z</t>
         </is>
       </c>
       <c r="D52" s="24" t="inlineStr">
         <is>
-          <t>69819</t>
+          <t>69871</t>
         </is>
       </c>
       <c r="E52" s="24" t="inlineStr">
@@ -16045,12 +16141,12 @@
       </c>
       <c r="F52" s="24" t="inlineStr">
         <is>
-          <t>Epic Avalanche</t>
+          <t>Kaufland Hangry Knights</t>
         </is>
       </c>
       <c r="G52" s="24" t="inlineStr">
         <is>
-          <t>Brod n Friends</t>
+          <t>TeamOrangeGaming</t>
         </is>
       </c>
       <c r="H52" s="24" t="inlineStr">
@@ -16070,23 +16166,23 @@
         </is>
       </c>
       <c r="L52" s="26" t="n">
-        <v>-223</v>
+        <v>104</v>
       </c>
       <c r="M52" s="27" t="n">
-        <v>1.44843</v>
+        <v>2.04</v>
       </c>
       <c r="N52" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.490196</v>
       </c>
       <c r="O52" s="28" t="n">
-        <v>0.5310589999999999</v>
+        <v>0.54899</v>
       </c>
       <c r="P52" s="28" t="n"/>
       <c r="Q52" s="28" t="n">
-        <v>-0.159343</v>
+        <v>0.058794</v>
       </c>
       <c r="R52" s="26" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="S52" s="29" t="n">
         <v>1</v>
@@ -16112,7 +16208,7 @@
       <c r="AD52" s="24" t="n"/>
       <c r="AE52" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-lol-bnf-ea-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.4900 (market_slug=aec-lol-tog-khk-2026-08-05).</t>
         </is>
       </c>
       <c r="AF52" s="31" t="inlineStr">
@@ -16130,7 +16226,7 @@
       <c r="AJ52" s="31" t="n"/>
       <c r="AK52" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL52" s="26" t="n">
@@ -16138,47 +16234,47 @@
       </c>
       <c r="AM52" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN52" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO52" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP52" s="24" t="inlineStr">
         <is>
-          <t>Epic Avalanche</t>
+          <t>Kaufland Hangry Knights</t>
         </is>
       </c>
       <c r="AQ52" s="24" t="inlineStr">
         <is>
-          <t>Epic Avalanche</t>
+          <t>Kaufland Hangry Knights</t>
         </is>
       </c>
       <c r="AR52" s="24" t="inlineStr">
         <is>
-          <t>Epic Avalanche</t>
+          <t>Kaufland Hangry Knights</t>
         </is>
       </c>
       <c r="AS52" s="24" t="inlineStr">
         <is>
-          <t>Brod n Friends</t>
+          <t>TeamOrangeGaming</t>
         </is>
       </c>
       <c r="AT52" s="24" t="inlineStr">
         <is>
-          <t>Brod n Friends</t>
+          <t>TeamOrangeGaming</t>
         </is>
       </c>
       <c r="AU52" s="24" t="inlineStr">
         <is>
-          <t>Brod n Friends</t>
+          <t>TeamOrangeGaming</t>
         </is>
       </c>
       <c r="AV52" s="24" t="n"/>
@@ -16196,7 +16292,7 @@
       </c>
       <c r="BA52" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BB52" s="24" t="inlineStr">
@@ -16211,7 +16307,7 @@
       </c>
       <c r="BD52" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BE52" s="24" t="inlineStr">
@@ -16231,7 +16327,7 @@
       </c>
       <c r="BH52" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:21.723881Z</t>
+          <t>2026-08-05T13:56:13.554249Z</t>
         </is>
       </c>
       <c r="BI52" s="24" t="inlineStr">
@@ -16241,13 +16337,13 @@
       </c>
       <c r="BJ52" s="25" t="n"/>
       <c r="BK52" s="26" t="n">
-        <v>-223</v>
+        <v>104</v>
       </c>
       <c r="BL52" s="27" t="n">
-        <v>1.44843</v>
+        <v>2.04</v>
       </c>
       <c r="BM52" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.490196</v>
       </c>
       <c r="BN52" s="28" t="n"/>
       <c r="BO52" s="28" t="n"/>
@@ -16282,19 +16378,19 @@
       <c r="CR52" s="24" t="n"/>
       <c r="CS52" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="53" ht="36" customHeight="1">
       <c r="A53" s="24" t="inlineStr">
         <is>
-          <t>5d599dbac43a45f7</t>
+          <t>d64b7da574c04576</t>
         </is>
       </c>
       <c r="B53" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:12.089327Z</t>
+          <t>2026-08-05T13:56:43.896254Z</t>
         </is>
       </c>
       <c r="C53" s="24" t="inlineStr">
@@ -16304,7 +16400,7 @@
       </c>
       <c r="D53" s="24" t="inlineStr">
         <is>
-          <t>69871</t>
+          <t>70569</t>
         </is>
       </c>
       <c r="E53" s="24" t="inlineStr">
@@ -16314,12 +16410,12 @@
       </c>
       <c r="F53" s="24" t="inlineStr">
         <is>
-          <t>Kaufland Hangry Knights</t>
+          <t>devils.one inStreamly</t>
         </is>
       </c>
       <c r="G53" s="24" t="inlineStr">
         <is>
-          <t>TeamOrangeGaming</t>
+          <t>BOMBA Team</t>
         </is>
       </c>
       <c r="H53" s="24" t="inlineStr">
@@ -16339,26 +16435,26 @@
         </is>
       </c>
       <c r="L53" s="26" t="n">
-        <v>108</v>
+        <v>-113</v>
       </c>
       <c r="M53" s="27" t="n">
-        <v>2.08</v>
+        <v>1.884956</v>
       </c>
       <c r="N53" s="28" t="n">
-        <v>0.480769</v>
+        <v>0.530516</v>
       </c>
       <c r="O53" s="28" t="n">
-        <v>0.549408</v>
+        <v>0.761043</v>
       </c>
       <c r="P53" s="28" t="n"/>
       <c r="Q53" s="28" t="n">
-        <v>0.06863900000000001</v>
+        <v>0.230527</v>
       </c>
       <c r="R53" s="26" t="n">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="S53" s="29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T53" s="24" t="inlineStr">
         <is>
@@ -16381,7 +16477,7 @@
       <c r="AD53" s="24" t="n"/>
       <c r="AE53" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4800 (market_slug=aec-lol-tog-khk-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.5300 (market_slug=aec-lol-boom-dv1-2026-08-05).</t>
         </is>
       </c>
       <c r="AF53" s="31" t="inlineStr">
@@ -16422,32 +16518,32 @@
       </c>
       <c r="AP53" s="24" t="inlineStr">
         <is>
-          <t>Kaufland Hangry Knights</t>
+          <t>devils.one inStreamly</t>
         </is>
       </c>
       <c r="AQ53" s="24" t="inlineStr">
         <is>
-          <t>Kaufland Hangry Knights</t>
+          <t>devils.one inStreamly</t>
         </is>
       </c>
       <c r="AR53" s="24" t="inlineStr">
         <is>
-          <t>Kaufland Hangry Knights</t>
+          <t>devils.one inStreamly</t>
         </is>
       </c>
       <c r="AS53" s="24" t="inlineStr">
         <is>
-          <t>TeamOrangeGaming</t>
+          <t>BOMBA Team</t>
         </is>
       </c>
       <c r="AT53" s="24" t="inlineStr">
         <is>
-          <t>TeamOrangeGaming</t>
+          <t>BOMBA Team</t>
         </is>
       </c>
       <c r="AU53" s="24" t="inlineStr">
         <is>
-          <t>TeamOrangeGaming</t>
+          <t>BOMBA Team</t>
         </is>
       </c>
       <c r="AV53" s="24" t="n"/>
@@ -16465,7 +16561,7 @@
       </c>
       <c r="BA53" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BB53" s="24" t="inlineStr">
@@ -16480,7 +16576,7 @@
       </c>
       <c r="BD53" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BE53" s="24" t="inlineStr">
@@ -16500,7 +16596,7 @@
       </c>
       <c r="BH53" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:24.231605Z</t>
+          <t>2026-08-05T13:56:15.101150Z</t>
         </is>
       </c>
       <c r="BI53" s="24" t="inlineStr">
@@ -16510,13 +16606,13 @@
       </c>
       <c r="BJ53" s="25" t="n"/>
       <c r="BK53" s="26" t="n">
-        <v>108</v>
+        <v>-113</v>
       </c>
       <c r="BL53" s="27" t="n">
-        <v>2.08</v>
+        <v>1.884956</v>
       </c>
       <c r="BM53" s="28" t="n">
-        <v>0.480769</v>
+        <v>0.530516</v>
       </c>
       <c r="BN53" s="28" t="n"/>
       <c r="BO53" s="28" t="n"/>
@@ -16558,22 +16654,22 @@
     <row r="54" ht="36" customHeight="1">
       <c r="A54" s="24" t="inlineStr">
         <is>
-          <t>35074d162348431b</t>
+          <t>ea1a9cb1deda4861</t>
         </is>
       </c>
       <c r="B54" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:12.089327Z</t>
+          <t>2026-08-05T13:56:43.896254Z</t>
         </is>
       </c>
       <c r="C54" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T17:00:00Z</t>
+          <t>2026-08-05T17:30:00Z</t>
         </is>
       </c>
       <c r="D54" s="24" t="inlineStr">
         <is>
-          <t>70569</t>
+          <t>69930</t>
         </is>
       </c>
       <c r="E54" s="24" t="inlineStr">
@@ -16583,12 +16679,12 @@
       </c>
       <c r="F54" s="24" t="inlineStr">
         <is>
-          <t>devils.one inStreamly</t>
+          <t>Bushido Wildcats</t>
         </is>
       </c>
       <c r="G54" s="24" t="inlineStr">
         <is>
-          <t>BOMBA Team</t>
+          <t xml:space="preserve">PCIFIC </t>
         </is>
       </c>
       <c r="H54" s="24" t="inlineStr">
@@ -16608,26 +16704,26 @@
         </is>
       </c>
       <c r="L54" s="26" t="n">
-        <v>-113</v>
+        <v>133</v>
       </c>
       <c r="M54" s="27" t="n">
-        <v>1.884956</v>
+        <v>2.33</v>
       </c>
       <c r="N54" s="28" t="n">
-        <v>0.530516</v>
+        <v>0.429185</v>
       </c>
       <c r="O54" s="28" t="n">
-        <v>0.761888</v>
+        <v>0.559679</v>
       </c>
       <c r="P54" s="28" t="n"/>
       <c r="Q54" s="28" t="n">
-        <v>0.231372</v>
+        <v>0.130494</v>
       </c>
       <c r="R54" s="26" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="S54" s="29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T54" s="24" t="inlineStr">
         <is>
@@ -16650,7 +16746,7 @@
       <c r="AD54" s="24" t="n"/>
       <c r="AE54" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5300 (market_slug=aec-lol-boom-dv1-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.4300 (market_slug=aec-lol-pcific-bw-2026-08-05).</t>
         </is>
       </c>
       <c r="AF54" s="31" t="inlineStr">
@@ -16691,32 +16787,32 @@
       </c>
       <c r="AP54" s="24" t="inlineStr">
         <is>
-          <t>devils.one inStreamly</t>
+          <t>Bushido Wildcats</t>
         </is>
       </c>
       <c r="AQ54" s="24" t="inlineStr">
         <is>
-          <t>devils.one inStreamly</t>
+          <t>Bushido Wildcats</t>
         </is>
       </c>
       <c r="AR54" s="24" t="inlineStr">
         <is>
-          <t>devils.one inStreamly</t>
+          <t>Bushido Wildcats</t>
         </is>
       </c>
       <c r="AS54" s="24" t="inlineStr">
         <is>
-          <t>BOMBA Team</t>
+          <t xml:space="preserve">PCIFIC </t>
         </is>
       </c>
       <c r="AT54" s="24" t="inlineStr">
         <is>
-          <t>BOMBA Team</t>
+          <t xml:space="preserve">PCIFIC </t>
         </is>
       </c>
       <c r="AU54" s="24" t="inlineStr">
         <is>
-          <t>BOMBA Team</t>
+          <t xml:space="preserve">PCIFIC </t>
         </is>
       </c>
       <c r="AV54" s="24" t="n"/>
@@ -16734,7 +16830,7 @@
       </c>
       <c r="BA54" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BB54" s="24" t="inlineStr">
@@ -16749,7 +16845,7 @@
       </c>
       <c r="BD54" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BE54" s="24" t="inlineStr">
@@ -16769,7 +16865,7 @@
       </c>
       <c r="BH54" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:25.035543Z</t>
+          <t>2026-08-05T13:56:15.697510Z</t>
         </is>
       </c>
       <c r="BI54" s="24" t="inlineStr">
@@ -16779,13 +16875,13 @@
       </c>
       <c r="BJ54" s="25" t="n"/>
       <c r="BK54" s="26" t="n">
-        <v>-113</v>
+        <v>133</v>
       </c>
       <c r="BL54" s="27" t="n">
-        <v>1.884956</v>
+        <v>2.33</v>
       </c>
       <c r="BM54" s="28" t="n">
-        <v>0.530516</v>
+        <v>0.429185</v>
       </c>
       <c r="BN54" s="28" t="n"/>
       <c r="BO54" s="28" t="n"/>
@@ -16827,12 +16923,12 @@
     <row r="55" ht="36" customHeight="1">
       <c r="A55" s="24" t="inlineStr">
         <is>
-          <t>5007a67175a74862</t>
+          <t>334ee7fa77d041d8</t>
         </is>
       </c>
       <c r="B55" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:12.089327Z</t>
+          <t>2026-08-05T13:56:43.896254Z</t>
         </is>
       </c>
       <c r="C55" s="24" t="inlineStr">
@@ -16842,7 +16938,7 @@
       </c>
       <c r="D55" s="24" t="inlineStr">
         <is>
-          <t>69930</t>
+          <t>69931</t>
         </is>
       </c>
       <c r="E55" s="24" t="inlineStr">
@@ -16852,12 +16948,12 @@
       </c>
       <c r="F55" s="24" t="inlineStr">
         <is>
-          <t>Bushido Wildcats</t>
+          <t>⁠Movistar KOI Fénix</t>
         </is>
       </c>
       <c r="G55" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">PCIFIC </t>
+          <t>UCAM Esports Club</t>
         </is>
       </c>
       <c r="H55" s="24" t="inlineStr">
@@ -16877,26 +16973,26 @@
         </is>
       </c>
       <c r="L55" s="26" t="n">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="M55" s="27" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="N55" s="28" t="n">
-        <v>0.440529</v>
+        <v>0.480769</v>
       </c>
       <c r="O55" s="28" t="n">
-        <v>0.560145</v>
+        <v>0.598983</v>
       </c>
       <c r="P55" s="28" t="n"/>
       <c r="Q55" s="28" t="n">
-        <v>0.119616</v>
+        <v>0.118214</v>
       </c>
       <c r="R55" s="26" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S55" s="29" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="T55" s="24" t="inlineStr">
         <is>
@@ -16919,7 +17015,7 @@
       <c r="AD55" s="24" t="n"/>
       <c r="AE55" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-lol-pcific-bw-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.4800 (market_slug=aec-lol-ucam-mkf-2026-08-05).</t>
         </is>
       </c>
       <c r="AF55" s="31" t="inlineStr">
@@ -16960,32 +17056,32 @@
       </c>
       <c r="AP55" s="24" t="inlineStr">
         <is>
-          <t>Bushido Wildcats</t>
+          <t>⁠Movistar KOI Fénix</t>
         </is>
       </c>
       <c r="AQ55" s="24" t="inlineStr">
         <is>
-          <t>Bushido Wildcats</t>
+          <t>⁠Movistar KOI Fénix</t>
         </is>
       </c>
       <c r="AR55" s="24" t="inlineStr">
         <is>
-          <t>Bushido Wildcats</t>
+          <t>⁠Movistar KOI Fénix</t>
         </is>
       </c>
       <c r="AS55" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">PCIFIC </t>
+          <t>UCAM Esports Club</t>
         </is>
       </c>
       <c r="AT55" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">PCIFIC </t>
+          <t>UCAM Esports Club</t>
         </is>
       </c>
       <c r="AU55" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">PCIFIC </t>
+          <t>UCAM Esports Club</t>
         </is>
       </c>
       <c r="AV55" s="24" t="n"/>
@@ -17003,7 +17099,7 @@
       </c>
       <c r="BA55" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BB55" s="24" t="inlineStr">
@@ -17018,7 +17114,7 @@
       </c>
       <c r="BD55" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BE55" s="24" t="inlineStr">
@@ -17038,7 +17134,7 @@
       </c>
       <c r="BH55" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:26.738098Z</t>
+          <t>2026-08-05T13:56:16.191719Z</t>
         </is>
       </c>
       <c r="BI55" s="24" t="inlineStr">
@@ -17048,13 +17144,13 @@
       </c>
       <c r="BJ55" s="25" t="n"/>
       <c r="BK55" s="26" t="n">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="BL55" s="27" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="BM55" s="28" t="n">
-        <v>0.440529</v>
+        <v>0.480769</v>
       </c>
       <c r="BN55" s="28" t="n"/>
       <c r="BO55" s="28" t="n"/>
@@ -17096,22 +17192,22 @@
     <row r="56" ht="36" customHeight="1">
       <c r="A56" s="24" t="inlineStr">
         <is>
-          <t>52d558f29a2b46b5</t>
+          <t>02854e5b0ccf499c</t>
         </is>
       </c>
       <c r="B56" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:12.089327Z</t>
+          <t>2026-08-05T13:56:43.896254Z</t>
         </is>
       </c>
       <c r="C56" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T17:30:00Z</t>
+          <t>2026-08-05T18:00:00Z</t>
         </is>
       </c>
       <c r="D56" s="24" t="inlineStr">
         <is>
-          <t>69931</t>
+          <t>69950</t>
         </is>
       </c>
       <c r="E56" s="24" t="inlineStr">
@@ -17121,12 +17217,12 @@
       </c>
       <c r="F56" s="24" t="inlineStr">
         <is>
-          <t>⁠Movistar KOI Fénix</t>
+          <t>Lupus Esports</t>
         </is>
       </c>
       <c r="G56" s="24" t="inlineStr">
         <is>
-          <t>UCAM Esports Club</t>
+          <t>SPIKE Syndicate</t>
         </is>
       </c>
       <c r="H56" s="24" t="inlineStr">
@@ -17146,26 +17242,26 @@
         </is>
       </c>
       <c r="L56" s="26" t="n">
-        <v>113</v>
+        <v>-133</v>
       </c>
       <c r="M56" s="27" t="n">
-        <v>2.13</v>
+        <v>1.75188</v>
       </c>
       <c r="N56" s="28" t="n">
-        <v>0.469484</v>
+        <v>0.570815</v>
       </c>
       <c r="O56" s="28" t="n">
-        <v>0.599621</v>
+        <v>0.554999</v>
       </c>
       <c r="P56" s="28" t="n"/>
       <c r="Q56" s="28" t="n">
-        <v>0.130137</v>
+        <v>-0.015816</v>
       </c>
       <c r="R56" s="26" t="n">
-        <v>85</v>
+        <v>12</v>
       </c>
       <c r="S56" s="29" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="T56" s="24" t="inlineStr">
         <is>
@@ -17188,7 +17284,7 @@
       <c r="AD56" s="24" t="n"/>
       <c r="AE56" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4700 (market_slug=aec-lol-ucam-mkf-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-lol-spk-lps-2026-08-05).</t>
         </is>
       </c>
       <c r="AF56" s="31" t="inlineStr">
@@ -17206,7 +17302,7 @@
       <c r="AJ56" s="31" t="n"/>
       <c r="AK56" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL56" s="26" t="n">
@@ -17214,47 +17310,47 @@
       </c>
       <c r="AM56" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN56" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO56" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP56" s="24" t="inlineStr">
         <is>
-          <t>⁠Movistar KOI Fénix</t>
+          <t>Lupus Esports</t>
         </is>
       </c>
       <c r="AQ56" s="24" t="inlineStr">
         <is>
-          <t>⁠Movistar KOI Fénix</t>
+          <t>Lupus Esports</t>
         </is>
       </c>
       <c r="AR56" s="24" t="inlineStr">
         <is>
-          <t>⁠Movistar KOI Fénix</t>
+          <t>Lupus Esports</t>
         </is>
       </c>
       <c r="AS56" s="24" t="inlineStr">
         <is>
-          <t>UCAM Esports Club</t>
+          <t>SPIKE Syndicate</t>
         </is>
       </c>
       <c r="AT56" s="24" t="inlineStr">
         <is>
-          <t>UCAM Esports Club</t>
+          <t>SPIKE Syndicate</t>
         </is>
       </c>
       <c r="AU56" s="24" t="inlineStr">
         <is>
-          <t>UCAM Esports Club</t>
+          <t>SPIKE Syndicate</t>
         </is>
       </c>
       <c r="AV56" s="24" t="n"/>
@@ -17272,7 +17368,7 @@
       </c>
       <c r="BA56" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BB56" s="24" t="inlineStr">
@@ -17287,7 +17383,7 @@
       </c>
       <c r="BD56" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BE56" s="24" t="inlineStr">
@@ -17307,7 +17403,7 @@
       </c>
       <c r="BH56" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:27.650106Z</t>
+          <t>2026-08-05T13:56:16.816487Z</t>
         </is>
       </c>
       <c r="BI56" s="24" t="inlineStr">
@@ -17317,13 +17413,13 @@
       </c>
       <c r="BJ56" s="25" t="n"/>
       <c r="BK56" s="26" t="n">
-        <v>113</v>
+        <v>-133</v>
       </c>
       <c r="BL56" s="27" t="n">
-        <v>2.13</v>
+        <v>1.75188</v>
       </c>
       <c r="BM56" s="28" t="n">
-        <v>0.469484</v>
+        <v>0.570815</v>
       </c>
       <c r="BN56" s="28" t="n"/>
       <c r="BO56" s="28" t="n"/>
@@ -17358,19 +17454,19 @@
       <c r="CR56" s="24" t="n"/>
       <c r="CS56" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="57" ht="36" customHeight="1">
       <c r="A57" s="24" t="inlineStr">
         <is>
-          <t>543bfe4d4cb24946</t>
+          <t>0b80d9a6fb9c47e7</t>
         </is>
       </c>
       <c r="B57" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:12.089327Z</t>
+          <t>2026-08-05T13:56:43.896254Z</t>
         </is>
       </c>
       <c r="C57" s="24" t="inlineStr">
@@ -17380,7 +17476,7 @@
       </c>
       <c r="D57" s="24" t="inlineStr">
         <is>
-          <t>69949</t>
+          <t>69951</t>
         </is>
       </c>
       <c r="E57" s="24" t="inlineStr">
@@ -17390,12 +17486,12 @@
       </c>
       <c r="F57" s="24" t="inlineStr">
         <is>
-          <t>Hyperion</t>
+          <t>Rich Gang</t>
         </is>
       </c>
       <c r="G57" s="24" t="inlineStr">
         <is>
-          <t>Dominion Goblins</t>
+          <t>2 Massive</t>
         </is>
       </c>
       <c r="H57" s="24" t="inlineStr">
@@ -17405,7 +17501,7 @@
       </c>
       <c r="I57" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J57" s="25" t="n"/>
@@ -17415,23 +17511,23 @@
         </is>
       </c>
       <c r="L57" s="26" t="n">
-        <v>-122</v>
+        <v>-127</v>
       </c>
       <c r="M57" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.787402</v>
       </c>
       <c r="N57" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="O57" s="28" t="n">
-        <v>0.5197349999999999</v>
+        <v>0.511164</v>
       </c>
       <c r="P57" s="28" t="n"/>
       <c r="Q57" s="28" t="n">
-        <v>-0.029815</v>
+        <v>-0.048307</v>
       </c>
       <c r="R57" s="26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S57" s="29" t="n">
         <v>1</v>
@@ -17457,7 +17553,7 @@
       <c r="AD57" s="24" t="n"/>
       <c r="AE57" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-lol-domi-hype-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-lol-mas-rgi-2026-08-05).</t>
         </is>
       </c>
       <c r="AF57" s="31" t="inlineStr">
@@ -17498,32 +17594,32 @@
       </c>
       <c r="AP57" s="24" t="inlineStr">
         <is>
-          <t>Hyperion</t>
+          <t>Rich Gang</t>
         </is>
       </c>
       <c r="AQ57" s="24" t="inlineStr">
         <is>
-          <t>Hyperion</t>
+          <t>Rich Gang</t>
         </is>
       </c>
       <c r="AR57" s="24" t="inlineStr">
         <is>
-          <t>Hyperion</t>
+          <t>Rich Gang</t>
         </is>
       </c>
       <c r="AS57" s="24" t="inlineStr">
         <is>
-          <t>Dominion Goblins</t>
+          <t>2 Massive</t>
         </is>
       </c>
       <c r="AT57" s="24" t="inlineStr">
         <is>
-          <t>Dominion Goblins</t>
+          <t>2 Massive</t>
         </is>
       </c>
       <c r="AU57" s="24" t="inlineStr">
         <is>
-          <t>Dominion Goblins</t>
+          <t>2 Massive</t>
         </is>
       </c>
       <c r="AV57" s="24" t="n"/>
@@ -17541,7 +17637,7 @@
       </c>
       <c r="BA57" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BB57" s="24" t="inlineStr">
@@ -17556,7 +17652,7 @@
       </c>
       <c r="BD57" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BE57" s="24" t="inlineStr">
@@ -17576,7 +17672,7 @@
       </c>
       <c r="BH57" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:28.672608Z</t>
+          <t>2026-08-05T13:56:17.349853Z</t>
         </is>
       </c>
       <c r="BI57" s="24" t="inlineStr">
@@ -17586,13 +17682,13 @@
       </c>
       <c r="BJ57" s="25" t="n"/>
       <c r="BK57" s="26" t="n">
-        <v>-122</v>
+        <v>-127</v>
       </c>
       <c r="BL57" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.787402</v>
       </c>
       <c r="BM57" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="BN57" s="28" t="n"/>
       <c r="BO57" s="28" t="n"/>
@@ -17634,12 +17730,12 @@
     <row r="58" ht="36" customHeight="1">
       <c r="A58" s="24" t="inlineStr">
         <is>
-          <t>ddb8481f6adc4a6e</t>
+          <t>1221baeedb01499c</t>
         </is>
       </c>
       <c r="B58" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:12.089327Z</t>
+          <t>2026-08-05T13:56:43.896254Z</t>
         </is>
       </c>
       <c r="C58" s="24" t="inlineStr">
@@ -17684,20 +17780,20 @@
         </is>
       </c>
       <c r="L58" s="26" t="n">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="M58" s="27" t="n">
-        <v>2.94</v>
+        <v>3.03</v>
       </c>
       <c r="N58" s="28" t="n">
-        <v>0.340136</v>
+        <v>0.330033</v>
       </c>
       <c r="O58" s="28" t="n">
-        <v>0.506919</v>
+        <v>0.506691</v>
       </c>
       <c r="P58" s="28" t="n"/>
       <c r="Q58" s="28" t="n">
-        <v>0.166783</v>
+        <v>0.176658</v>
       </c>
       <c r="R58" s="26" t="n">
         <v>100</v>
@@ -17726,7 +17822,7 @@
       <c r="AD58" s="24" t="n"/>
       <c r="AE58" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3400 (market_slug=aec-lol-kcb-sly-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.3300 (market_slug=aec-lol-kcb-sly-2026-08-05).</t>
         </is>
       </c>
       <c r="AF58" s="31" t="inlineStr">
@@ -17810,7 +17906,7 @@
       </c>
       <c r="BA58" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BB58" s="24" t="inlineStr">
@@ -17825,7 +17921,7 @@
       </c>
       <c r="BD58" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BE58" s="24" t="inlineStr">
@@ -17845,7 +17941,7 @@
       </c>
       <c r="BH58" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:29.541094Z</t>
+          <t>2026-08-05T13:56:17.916988Z</t>
         </is>
       </c>
       <c r="BI58" s="24" t="inlineStr">
@@ -17855,13 +17951,13 @@
       </c>
       <c r="BJ58" s="25" t="n"/>
       <c r="BK58" s="26" t="n">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="BL58" s="27" t="n">
-        <v>2.94</v>
+        <v>3.03</v>
       </c>
       <c r="BM58" s="28" t="n">
-        <v>0.340136</v>
+        <v>0.330033</v>
       </c>
       <c r="BN58" s="28" t="n"/>
       <c r="BO58" s="28" t="n"/>
@@ -17903,12 +17999,12 @@
     <row r="59" ht="36" customHeight="1">
       <c r="A59" s="24" t="inlineStr">
         <is>
-          <t>c72b05071f1c4a2c</t>
+          <t>a46007789896424d</t>
         </is>
       </c>
       <c r="B59" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:12.089327Z</t>
+          <t>2026-08-05T13:56:43.896254Z</t>
         </is>
       </c>
       <c r="C59" s="24" t="inlineStr">
@@ -17918,7 +18014,7 @@
       </c>
       <c r="D59" s="24" t="inlineStr">
         <is>
-          <t>69950</t>
+          <t>69952</t>
         </is>
       </c>
       <c r="E59" s="24" t="inlineStr">
@@ -17928,12 +18024,12 @@
       </c>
       <c r="F59" s="24" t="inlineStr">
         <is>
-          <t>Lupus Esports</t>
+          <t>Absolved</t>
         </is>
       </c>
       <c r="G59" s="24" t="inlineStr">
         <is>
-          <t>SPIKE Syndicate</t>
+          <t>Sørby eSport</t>
         </is>
       </c>
       <c r="H59" s="24" t="inlineStr">
@@ -17953,23 +18049,23 @@
         </is>
       </c>
       <c r="L59" s="26" t="n">
-        <v>-133</v>
+        <v>-108</v>
       </c>
       <c r="M59" s="27" t="n">
-        <v>1.75188</v>
+        <v>1.925926</v>
       </c>
       <c r="N59" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.519231</v>
       </c>
       <c r="O59" s="28" t="n">
-        <v>0.555457</v>
+        <v>0.515608</v>
       </c>
       <c r="P59" s="28" t="n"/>
       <c r="Q59" s="28" t="n">
-        <v>-0.015358</v>
+        <v>-0.003623</v>
       </c>
       <c r="R59" s="26" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="S59" s="29" t="n">
         <v>1</v>
@@ -17995,7 +18091,7 @@
       <c r="AD59" s="24" t="n"/>
       <c r="AE59" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-lol-spk-lps-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.5200 (market_slug=aec-lol-sre-abs-2026-08-05).</t>
         </is>
       </c>
       <c r="AF59" s="31" t="inlineStr">
@@ -18036,32 +18132,32 @@
       </c>
       <c r="AP59" s="24" t="inlineStr">
         <is>
-          <t>Lupus Esports</t>
+          <t>Absolved</t>
         </is>
       </c>
       <c r="AQ59" s="24" t="inlineStr">
         <is>
-          <t>Lupus Esports</t>
+          <t>Absolved</t>
         </is>
       </c>
       <c r="AR59" s="24" t="inlineStr">
         <is>
-          <t>Lupus Esports</t>
+          <t>Absolved</t>
         </is>
       </c>
       <c r="AS59" s="24" t="inlineStr">
         <is>
-          <t>SPIKE Syndicate</t>
+          <t>Sørby eSport</t>
         </is>
       </c>
       <c r="AT59" s="24" t="inlineStr">
         <is>
-          <t>SPIKE Syndicate</t>
+          <t>Sørby eSport</t>
         </is>
       </c>
       <c r="AU59" s="24" t="inlineStr">
         <is>
-          <t>SPIKE Syndicate</t>
+          <t>Sørby eSport</t>
         </is>
       </c>
       <c r="AV59" s="24" t="n"/>
@@ -18079,7 +18175,7 @@
       </c>
       <c r="BA59" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BB59" s="24" t="inlineStr">
@@ -18094,7 +18190,7 @@
       </c>
       <c r="BD59" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BE59" s="24" t="inlineStr">
@@ -18114,7 +18210,7 @@
       </c>
       <c r="BH59" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:30.436829Z</t>
+          <t>2026-08-05T13:56:18.398327Z</t>
         </is>
       </c>
       <c r="BI59" s="24" t="inlineStr">
@@ -18124,13 +18220,13 @@
       </c>
       <c r="BJ59" s="25" t="n"/>
       <c r="BK59" s="26" t="n">
-        <v>-133</v>
+        <v>-108</v>
       </c>
       <c r="BL59" s="27" t="n">
-        <v>1.75188</v>
+        <v>1.925926</v>
       </c>
       <c r="BM59" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.519231</v>
       </c>
       <c r="BN59" s="28" t="n"/>
       <c r="BO59" s="28" t="n"/>
@@ -18172,12 +18268,12 @@
     <row r="60" ht="36" customHeight="1">
       <c r="A60" s="24" t="inlineStr">
         <is>
-          <t>dbc75fa9e04a4eca</t>
+          <t>cc7b564f763a4aa8</t>
         </is>
       </c>
       <c r="B60" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:12.089327Z</t>
+          <t>2026-08-05T13:56:43.896254Z</t>
         </is>
       </c>
       <c r="C60" s="24" t="inlineStr">
@@ -18187,7 +18283,7 @@
       </c>
       <c r="D60" s="24" t="inlineStr">
         <is>
-          <t>69951</t>
+          <t>69949</t>
         </is>
       </c>
       <c r="E60" s="24" t="inlineStr">
@@ -18197,12 +18293,12 @@
       </c>
       <c r="F60" s="24" t="inlineStr">
         <is>
-          <t>Rich Gang</t>
+          <t>Hyperion</t>
         </is>
       </c>
       <c r="G60" s="24" t="inlineStr">
         <is>
-          <t>2 Massive</t>
+          <t>Dominion Goblins</t>
         </is>
       </c>
       <c r="H60" s="24" t="inlineStr">
@@ -18212,7 +18308,7 @@
       </c>
       <c r="I60" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J60" s="25" t="n"/>
@@ -18222,23 +18318,23 @@
         </is>
       </c>
       <c r="L60" s="26" t="n">
-        <v>127</v>
+        <v>-108</v>
       </c>
       <c r="M60" s="27" t="n">
-        <v>2.27</v>
+        <v>1.925926</v>
       </c>
       <c r="N60" s="28" t="n">
-        <v>0.440529</v>
+        <v>0.519231</v>
       </c>
       <c r="O60" s="28" t="n">
-        <v>0.511094</v>
+        <v>0.519527</v>
       </c>
       <c r="P60" s="28" t="n"/>
       <c r="Q60" s="28" t="n">
-        <v>0.070565</v>
+        <v>0.000296</v>
       </c>
       <c r="R60" s="26" t="n">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="S60" s="29" t="n">
         <v>1</v>
@@ -18264,7 +18360,7 @@
       <c r="AD60" s="24" t="n"/>
       <c r="AE60" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-lol-mas-rgi-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.5200 (market_slug=aec-lol-domi-hype-2026-08-05).</t>
         </is>
       </c>
       <c r="AF60" s="31" t="inlineStr">
@@ -18305,32 +18401,32 @@
       </c>
       <c r="AP60" s="24" t="inlineStr">
         <is>
-          <t>Rich Gang</t>
+          <t>Hyperion</t>
         </is>
       </c>
       <c r="AQ60" s="24" t="inlineStr">
         <is>
-          <t>Rich Gang</t>
+          <t>Hyperion</t>
         </is>
       </c>
       <c r="AR60" s="24" t="inlineStr">
         <is>
-          <t>Rich Gang</t>
+          <t>Hyperion</t>
         </is>
       </c>
       <c r="AS60" s="24" t="inlineStr">
         <is>
-          <t>2 Massive</t>
+          <t>Dominion Goblins</t>
         </is>
       </c>
       <c r="AT60" s="24" t="inlineStr">
         <is>
-          <t>2 Massive</t>
+          <t>Dominion Goblins</t>
         </is>
       </c>
       <c r="AU60" s="24" t="inlineStr">
         <is>
-          <t>2 Massive</t>
+          <t>Dominion Goblins</t>
         </is>
       </c>
       <c r="AV60" s="24" t="n"/>
@@ -18348,7 +18444,7 @@
       </c>
       <c r="BA60" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BB60" s="24" t="inlineStr">
@@ -18363,7 +18459,7 @@
       </c>
       <c r="BD60" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BE60" s="24" t="inlineStr">
@@ -18383,7 +18479,7 @@
       </c>
       <c r="BH60" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:31.329768Z</t>
+          <t>2026-08-05T13:56:19.086046Z</t>
         </is>
       </c>
       <c r="BI60" s="24" t="inlineStr">
@@ -18393,13 +18489,13 @@
       </c>
       <c r="BJ60" s="25" t="n"/>
       <c r="BK60" s="26" t="n">
-        <v>127</v>
+        <v>-108</v>
       </c>
       <c r="BL60" s="27" t="n">
-        <v>2.27</v>
+        <v>1.925926</v>
       </c>
       <c r="BM60" s="28" t="n">
-        <v>0.440529</v>
+        <v>0.519231</v>
       </c>
       <c r="BN60" s="28" t="n"/>
       <c r="BO60" s="28" t="n"/>
@@ -18441,22 +18537,22 @@
     <row r="61" ht="36" customHeight="1">
       <c r="A61" s="24" t="inlineStr">
         <is>
-          <t>6006de28afec4ab6</t>
+          <t>0ea73003b4944980</t>
         </is>
       </c>
       <c r="B61" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:12.089327Z</t>
+          <t>2026-08-05T13:56:43.896254Z</t>
         </is>
       </c>
       <c r="C61" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T18:00:00Z</t>
+          <t>2026-08-05T19:00:00Z</t>
         </is>
       </c>
       <c r="D61" s="24" t="inlineStr">
         <is>
-          <t>69952</t>
+          <t>70045</t>
         </is>
       </c>
       <c r="E61" s="24" t="inlineStr">
@@ -18466,12 +18562,12 @@
       </c>
       <c r="F61" s="24" t="inlineStr">
         <is>
-          <t>Absolved</t>
+          <t>Ici Japon Corp. Esport</t>
         </is>
       </c>
       <c r="G61" s="24" t="inlineStr">
         <is>
-          <t>Sørby eSport</t>
+          <t>ZYB Esport</t>
         </is>
       </c>
       <c r="H61" s="24" t="inlineStr">
@@ -18481,7 +18577,7 @@
       </c>
       <c r="I61" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J61" s="25" t="n"/>
@@ -18491,26 +18587,26 @@
         </is>
       </c>
       <c r="L61" s="26" t="n">
-        <v>-113</v>
+        <v>122</v>
       </c>
       <c r="M61" s="27" t="n">
-        <v>1.884956</v>
+        <v>2.22</v>
       </c>
       <c r="N61" s="28" t="n">
-        <v>0.530516</v>
+        <v>0.45045</v>
       </c>
       <c r="O61" s="28" t="n">
-        <v>0.515799</v>
+        <v>0.598175</v>
       </c>
       <c r="P61" s="28" t="n"/>
       <c r="Q61" s="28" t="n">
-        <v>-0.014717</v>
+        <v>0.147725</v>
       </c>
       <c r="R61" s="26" t="n">
-        <v>13</v>
+        <v>94</v>
       </c>
       <c r="S61" s="29" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="T61" s="24" t="inlineStr">
         <is>
@@ -18533,7 +18629,7 @@
       <c r="AD61" s="24" t="n"/>
       <c r="AE61" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5300 (market_slug=aec-lol-sre-abs-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-lol-zyb-ijc-2026-08-05).</t>
         </is>
       </c>
       <c r="AF61" s="31" t="inlineStr">
@@ -18551,7 +18647,7 @@
       <c r="AJ61" s="31" t="n"/>
       <c r="AK61" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL61" s="26" t="n">
@@ -18559,47 +18655,47 @@
       </c>
       <c r="AM61" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN61" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO61" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP61" s="24" t="inlineStr">
         <is>
-          <t>Absolved</t>
+          <t>Ici Japon Corp. Esport</t>
         </is>
       </c>
       <c r="AQ61" s="24" t="inlineStr">
         <is>
-          <t>Absolved</t>
+          <t>Ici Japon Corp. Esport</t>
         </is>
       </c>
       <c r="AR61" s="24" t="inlineStr">
         <is>
-          <t>Absolved</t>
+          <t>Ici Japon Corp. Esport</t>
         </is>
       </c>
       <c r="AS61" s="24" t="inlineStr">
         <is>
-          <t>Sørby eSport</t>
+          <t>ZYB Esport</t>
         </is>
       </c>
       <c r="AT61" s="24" t="inlineStr">
         <is>
-          <t>Sørby eSport</t>
+          <t>ZYB Esport</t>
         </is>
       </c>
       <c r="AU61" s="24" t="inlineStr">
         <is>
-          <t>Sørby eSport</t>
+          <t>ZYB Esport</t>
         </is>
       </c>
       <c r="AV61" s="24" t="n"/>
@@ -18617,7 +18713,7 @@
       </c>
       <c r="BA61" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BB61" s="24" t="inlineStr">
@@ -18632,7 +18728,7 @@
       </c>
       <c r="BD61" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BE61" s="24" t="inlineStr">
@@ -18652,7 +18748,7 @@
       </c>
       <c r="BH61" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:32.125686Z</t>
+          <t>2026-08-05T13:56:20.348944Z</t>
         </is>
       </c>
       <c r="BI61" s="24" t="inlineStr">
@@ -18662,13 +18758,13 @@
       </c>
       <c r="BJ61" s="25" t="n"/>
       <c r="BK61" s="26" t="n">
-        <v>-113</v>
+        <v>122</v>
       </c>
       <c r="BL61" s="27" t="n">
-        <v>1.884956</v>
+        <v>2.22</v>
       </c>
       <c r="BM61" s="28" t="n">
-        <v>0.530516</v>
+        <v>0.45045</v>
       </c>
       <c r="BN61" s="28" t="n"/>
       <c r="BO61" s="28" t="n"/>
@@ -18703,29 +18799,29 @@
       <c r="CR61" s="24" t="n"/>
       <c r="CS61" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="62" ht="36" customHeight="1">
       <c r="A62" s="24" t="inlineStr">
         <is>
-          <t>16dc8330ea144aef</t>
+          <t>79aa5a9d72d94085</t>
         </is>
       </c>
       <c r="B62" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:12.089327Z</t>
+          <t>2026-08-05T13:56:43.896254Z</t>
         </is>
       </c>
       <c r="C62" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T19:00:00Z</t>
+          <t>2026-08-05T20:00:00Z</t>
         </is>
       </c>
       <c r="D62" s="24" t="inlineStr">
         <is>
-          <t>70045</t>
+          <t>70301</t>
         </is>
       </c>
       <c r="E62" s="24" t="inlineStr">
@@ -18735,12 +18831,12 @@
       </c>
       <c r="F62" s="24" t="inlineStr">
         <is>
-          <t>Ici Japon Corp. Esport</t>
+          <t>Skillcamp Esport</t>
         </is>
       </c>
       <c r="G62" s="24" t="inlineStr">
         <is>
-          <t>ZYB Esport</t>
+          <t>Vitality.Bee</t>
         </is>
       </c>
       <c r="H62" s="24" t="inlineStr">
@@ -18750,7 +18846,7 @@
       </c>
       <c r="I62" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J62" s="25" t="n"/>
@@ -18760,23 +18856,23 @@
         </is>
       </c>
       <c r="L62" s="26" t="n">
-        <v>144</v>
+        <v>-104</v>
       </c>
       <c r="M62" s="27" t="n">
-        <v>2.44</v>
+        <v>1.961538</v>
       </c>
       <c r="N62" s="28" t="n">
-        <v>0.409836</v>
+        <v>0.509804</v>
       </c>
       <c r="O62" s="28" t="n">
-        <v>0.598431</v>
+        <v>0.584761</v>
       </c>
       <c r="P62" s="28" t="n"/>
       <c r="Q62" s="28" t="n">
-        <v>0.188595</v>
+        <v>0.074957</v>
       </c>
       <c r="R62" s="26" t="n">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="S62" s="29" t="n">
         <v>1.25</v>
@@ -18802,7 +18898,7 @@
       <c r="AD62" s="24" t="n"/>
       <c r="AE62" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4100 (market_slug=aec-lol-zyb-ijc-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-lol-vitb-sc-2026-08-05).</t>
         </is>
       </c>
       <c r="AF62" s="31" t="inlineStr">
@@ -18843,32 +18939,32 @@
       </c>
       <c r="AP62" s="24" t="inlineStr">
         <is>
-          <t>Ici Japon Corp. Esport</t>
+          <t>Skillcamp Esport</t>
         </is>
       </c>
       <c r="AQ62" s="24" t="inlineStr">
         <is>
-          <t>Ici Japon Corp. Esport</t>
+          <t>Skillcamp Esport</t>
         </is>
       </c>
       <c r="AR62" s="24" t="inlineStr">
         <is>
-          <t>Ici Japon Corp. Esport</t>
+          <t>Skillcamp Esport</t>
         </is>
       </c>
       <c r="AS62" s="24" t="inlineStr">
         <is>
-          <t>ZYB Esport</t>
+          <t>Vitality.Bee</t>
         </is>
       </c>
       <c r="AT62" s="24" t="inlineStr">
         <is>
-          <t>ZYB Esport</t>
+          <t>Vitality.Bee</t>
         </is>
       </c>
       <c r="AU62" s="24" t="inlineStr">
         <is>
-          <t>ZYB Esport</t>
+          <t>Vitality.Bee</t>
         </is>
       </c>
       <c r="AV62" s="24" t="n"/>
@@ -18886,7 +18982,7 @@
       </c>
       <c r="BA62" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BB62" s="24" t="inlineStr">
@@ -18901,7 +18997,7 @@
       </c>
       <c r="BD62" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BE62" s="24" t="inlineStr">
@@ -18921,7 +19017,7 @@
       </c>
       <c r="BH62" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:33.888149Z</t>
+          <t>2026-08-05T13:56:20.853410Z</t>
         </is>
       </c>
       <c r="BI62" s="24" t="inlineStr">
@@ -18931,13 +19027,13 @@
       </c>
       <c r="BJ62" s="25" t="n"/>
       <c r="BK62" s="26" t="n">
-        <v>144</v>
+        <v>-104</v>
       </c>
       <c r="BL62" s="27" t="n">
-        <v>2.44</v>
+        <v>1.961538</v>
       </c>
       <c r="BM62" s="28" t="n">
-        <v>0.409836</v>
+        <v>0.509804</v>
       </c>
       <c r="BN62" s="28" t="n"/>
       <c r="BO62" s="28" t="n"/>
@@ -18979,12 +19075,12 @@
     <row r="63" ht="36" customHeight="1">
       <c r="A63" s="24" t="inlineStr">
         <is>
-          <t>251306a4eb4548a5</t>
+          <t>524a71f595cf4a80</t>
         </is>
       </c>
       <c r="B63" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:12.089327Z</t>
+          <t>2026-08-05T13:56:43.896254Z</t>
         </is>
       </c>
       <c r="C63" s="24" t="inlineStr">
@@ -18994,7 +19090,7 @@
       </c>
       <c r="D63" s="24" t="inlineStr">
         <is>
-          <t>70301</t>
+          <t>70302</t>
         </is>
       </c>
       <c r="E63" s="24" t="inlineStr">
@@ -19004,12 +19100,12 @@
       </c>
       <c r="F63" s="24" t="inlineStr">
         <is>
-          <t>Skillcamp Esport</t>
+          <t>7REX</t>
         </is>
       </c>
       <c r="G63" s="24" t="inlineStr">
         <is>
-          <t>Vitality.Bee</t>
+          <t>Team Solid</t>
         </is>
       </c>
       <c r="H63" s="24" t="inlineStr">
@@ -19019,7 +19115,7 @@
       </c>
       <c r="I63" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J63" s="25" t="n"/>
@@ -19029,26 +19125,26 @@
         </is>
       </c>
       <c r="L63" s="26" t="n">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="M63" s="27" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="N63" s="28" t="n">
-        <v>0.5</v>
+        <v>0.469484</v>
       </c>
       <c r="O63" s="28" t="n">
-        <v>0.5853390000000001</v>
+        <v>0.52275</v>
       </c>
       <c r="P63" s="28" t="n"/>
       <c r="Q63" s="28" t="n">
-        <v>0.085339</v>
+        <v>0.053266</v>
       </c>
       <c r="R63" s="26" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="S63" s="29" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="T63" s="24" t="inlineStr">
         <is>
@@ -19071,7 +19167,7 @@
       <c r="AD63" s="24" t="n"/>
       <c r="AE63" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5000 (market_slug=aec-lol-vitb-sc-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.4700 (market_slug=aec-lol-tse-7rex-2026-08-05).</t>
         </is>
       </c>
       <c r="AF63" s="31" t="inlineStr">
@@ -19089,7 +19185,7 @@
       <c r="AJ63" s="31" t="n"/>
       <c r="AK63" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL63" s="26" t="n">
@@ -19097,47 +19193,47 @@
       </c>
       <c r="AM63" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN63" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO63" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP63" s="24" t="inlineStr">
         <is>
-          <t>Skillcamp Esport</t>
+          <t>7REX</t>
         </is>
       </c>
       <c r="AQ63" s="24" t="inlineStr">
         <is>
-          <t>Skillcamp Esport</t>
+          <t>7REX</t>
         </is>
       </c>
       <c r="AR63" s="24" t="inlineStr">
         <is>
-          <t>Skillcamp Esport</t>
+          <t>7REX</t>
         </is>
       </c>
       <c r="AS63" s="24" t="inlineStr">
         <is>
-          <t>Vitality.Bee</t>
+          <t>Team Solid</t>
         </is>
       </c>
       <c r="AT63" s="24" t="inlineStr">
         <is>
-          <t>Vitality.Bee</t>
+          <t>Team Solid</t>
         </is>
       </c>
       <c r="AU63" s="24" t="inlineStr">
         <is>
-          <t>Vitality.Bee</t>
+          <t>Team Solid</t>
         </is>
       </c>
       <c r="AV63" s="24" t="n"/>
@@ -19155,7 +19251,7 @@
       </c>
       <c r="BA63" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BB63" s="24" t="inlineStr">
@@ -19170,7 +19266,7 @@
       </c>
       <c r="BD63" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BE63" s="24" t="inlineStr">
@@ -19190,7 +19286,7 @@
       </c>
       <c r="BH63" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:34.793544Z</t>
+          <t>2026-08-05T13:56:21.335184Z</t>
         </is>
       </c>
       <c r="BI63" s="24" t="inlineStr">
@@ -19200,13 +19296,13 @@
       </c>
       <c r="BJ63" s="25" t="n"/>
       <c r="BK63" s="26" t="n">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="BL63" s="27" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="BM63" s="28" t="n">
-        <v>0.5</v>
+        <v>0.469484</v>
       </c>
       <c r="BN63" s="28" t="n"/>
       <c r="BO63" s="28" t="n"/>
@@ -19248,22 +19344,22 @@
     <row r="64" ht="36" customHeight="1">
       <c r="A64" s="24" t="inlineStr">
         <is>
-          <t>79fdd1c270ef4413</t>
+          <t>f8aeec43779a4395</t>
         </is>
       </c>
       <c r="B64" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:12.089327Z</t>
+          <t>2026-08-05T13:56:43.896254Z</t>
         </is>
       </c>
       <c r="C64" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T20:00:00Z</t>
+          <t>2026-08-05T21:00:00Z</t>
         </is>
       </c>
       <c r="D64" s="24" t="inlineStr">
         <is>
-          <t>70302</t>
+          <t>70349</t>
         </is>
       </c>
       <c r="E64" s="24" t="inlineStr">
@@ -19273,12 +19369,12 @@
       </c>
       <c r="F64" s="24" t="inlineStr">
         <is>
-          <t>7REX</t>
+          <t>Winthrop University</t>
         </is>
       </c>
       <c r="G64" s="24" t="inlineStr">
         <is>
-          <t>Team Solid</t>
+          <t>Blue Otter</t>
         </is>
       </c>
       <c r="H64" s="24" t="inlineStr">
@@ -19298,26 +19394,26 @@
         </is>
       </c>
       <c r="L64" s="26" t="n">
-        <v>-113</v>
+        <v>-170</v>
       </c>
       <c r="M64" s="27" t="n">
-        <v>1.884956</v>
+        <v>1.588235</v>
       </c>
       <c r="N64" s="28" t="n">
-        <v>0.530516</v>
+        <v>0.62963</v>
       </c>
       <c r="O64" s="28" t="n">
-        <v>0.522659</v>
+        <v>0.670593</v>
       </c>
       <c r="P64" s="28" t="n"/>
       <c r="Q64" s="28" t="n">
-        <v>-0.007856999999999999</v>
+        <v>0.040963</v>
       </c>
       <c r="R64" s="26" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="S64" s="29" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="T64" s="24" t="inlineStr">
         <is>
@@ -19340,7 +19436,7 @@
       <c r="AD64" s="24" t="n"/>
       <c r="AE64" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5300 (market_slug=aec-lol-tse-7rex-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-lol-blue-wu-2026-08-05).</t>
         </is>
       </c>
       <c r="AF64" s="31" t="inlineStr">
@@ -19358,7 +19454,7 @@
       <c r="AJ64" s="31" t="n"/>
       <c r="AK64" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL64" s="26" t="n">
@@ -19366,47 +19462,47 @@
       </c>
       <c r="AM64" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN64" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO64" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP64" s="24" t="inlineStr">
         <is>
-          <t>7REX</t>
+          <t>Winthrop University</t>
         </is>
       </c>
       <c r="AQ64" s="24" t="inlineStr">
         <is>
-          <t>7REX</t>
+          <t>Winthrop University</t>
         </is>
       </c>
       <c r="AR64" s="24" t="inlineStr">
         <is>
-          <t>7REX</t>
+          <t>Winthrop University</t>
         </is>
       </c>
       <c r="AS64" s="24" t="inlineStr">
         <is>
-          <t>Team Solid</t>
+          <t>Blue Otter</t>
         </is>
       </c>
       <c r="AT64" s="24" t="inlineStr">
         <is>
-          <t>Team Solid</t>
+          <t>Blue Otter</t>
         </is>
       </c>
       <c r="AU64" s="24" t="inlineStr">
         <is>
-          <t>Team Solid</t>
+          <t>Blue Otter</t>
         </is>
       </c>
       <c r="AV64" s="24" t="n"/>
@@ -19424,7 +19520,7 @@
       </c>
       <c r="BA64" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BB64" s="24" t="inlineStr">
@@ -19439,7 +19535,7 @@
       </c>
       <c r="BD64" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BE64" s="24" t="inlineStr">
@@ -19459,7 +19555,7 @@
       </c>
       <c r="BH64" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:35.687295Z</t>
+          <t>2026-08-05T13:56:22.599351Z</t>
         </is>
       </c>
       <c r="BI64" s="24" t="inlineStr">
@@ -19469,13 +19565,13 @@
       </c>
       <c r="BJ64" s="25" t="n"/>
       <c r="BK64" s="26" t="n">
-        <v>-113</v>
+        <v>-170</v>
       </c>
       <c r="BL64" s="27" t="n">
-        <v>1.884956</v>
+        <v>1.588235</v>
       </c>
       <c r="BM64" s="28" t="n">
-        <v>0.530516</v>
+        <v>0.62963</v>
       </c>
       <c r="BN64" s="28" t="n"/>
       <c r="BO64" s="28" t="n"/>
@@ -19510,19 +19606,19 @@
       <c r="CR64" s="24" t="n"/>
       <c r="CS64" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="65" ht="36" customHeight="1">
       <c r="A65" s="24" t="inlineStr">
         <is>
-          <t>17a573c2907948cb</t>
+          <t>30f259327ee24786</t>
         </is>
       </c>
       <c r="B65" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:12.089327Z</t>
+          <t>2026-08-05T13:56:43.896254Z</t>
         </is>
       </c>
       <c r="C65" s="24" t="inlineStr">
@@ -19576,11 +19672,11 @@
         <v>0.490196</v>
       </c>
       <c r="O65" s="28" t="n">
-        <v>0.503336</v>
+        <v>0.503441</v>
       </c>
       <c r="P65" s="28" t="n"/>
       <c r="Q65" s="28" t="n">
-        <v>0.01314</v>
+        <v>0.013245</v>
       </c>
       <c r="R65" s="26" t="n">
         <v>27</v>
@@ -19693,7 +19789,7 @@
       </c>
       <c r="BA65" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BB65" s="24" t="inlineStr">
@@ -19708,7 +19804,7 @@
       </c>
       <c r="BD65" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BE65" s="24" t="inlineStr">
@@ -19728,7 +19824,7 @@
       </c>
       <c r="BH65" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:37.390862Z</t>
+          <t>2026-08-05T13:56:23.085592Z</t>
         </is>
       </c>
       <c r="BI65" s="24" t="inlineStr">
@@ -19786,22 +19882,22 @@
     <row r="66" ht="36" customHeight="1">
       <c r="A66" s="24" t="inlineStr">
         <is>
-          <t>ee467f46de1645b6</t>
+          <t>10dd5479febd4f3b</t>
         </is>
       </c>
       <c r="B66" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:12.089327Z</t>
+          <t>2026-08-05T13:56:43.896254Z</t>
         </is>
       </c>
       <c r="C66" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T21:00:00Z</t>
+          <t>2026-08-05T22:00:00Z</t>
         </is>
       </c>
       <c r="D66" s="24" t="inlineStr">
         <is>
-          <t>70349</t>
+          <t>70379</t>
         </is>
       </c>
       <c r="E66" s="24" t="inlineStr">
@@ -19811,12 +19907,12 @@
       </c>
       <c r="F66" s="24" t="inlineStr">
         <is>
-          <t>Winthrop University</t>
+          <t>KaBuM! Ilha das Lendas</t>
         </is>
       </c>
       <c r="G66" s="24" t="inlineStr">
         <is>
-          <t>Blue Otter</t>
+          <t>Ei Nerd Esports</t>
         </is>
       </c>
       <c r="H66" s="24" t="inlineStr">
@@ -19836,26 +19932,26 @@
         </is>
       </c>
       <c r="L66" s="26" t="n">
-        <v>-213</v>
+        <v>127</v>
       </c>
       <c r="M66" s="27" t="n">
-        <v>1.469484</v>
+        <v>2.27</v>
       </c>
       <c r="N66" s="28" t="n">
-        <v>0.680511</v>
+        <v>0.440529</v>
       </c>
       <c r="O66" s="28" t="n">
-        <v>0.671149</v>
+        <v>0.616429</v>
       </c>
       <c r="P66" s="28" t="n"/>
       <c r="Q66" s="28" t="n">
-        <v>-0.009362000000000001</v>
+        <v>0.1759</v>
       </c>
       <c r="R66" s="26" t="n">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="S66" s="29" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="T66" s="24" t="inlineStr">
         <is>
@@ -19878,7 +19974,7 @@
       <c r="AD66" s="24" t="n"/>
       <c r="AE66" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-lol-blue-wu-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-lol-nerd-kbm-2026-08-05).</t>
         </is>
       </c>
       <c r="AF66" s="31" t="inlineStr">
@@ -19896,7 +19992,7 @@
       <c r="AJ66" s="31" t="n"/>
       <c r="AK66" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL66" s="26" t="n">
@@ -19904,47 +20000,47 @@
       </c>
       <c r="AM66" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN66" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO66" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP66" s="24" t="inlineStr">
         <is>
-          <t>Winthrop University</t>
+          <t>KaBuM! Ilha das Lendas</t>
         </is>
       </c>
       <c r="AQ66" s="24" t="inlineStr">
         <is>
-          <t>Winthrop University</t>
+          <t>KaBuM! Ilha das Lendas</t>
         </is>
       </c>
       <c r="AR66" s="24" t="inlineStr">
         <is>
-          <t>Winthrop University</t>
+          <t>KaBuM! Ilha das Lendas</t>
         </is>
       </c>
       <c r="AS66" s="24" t="inlineStr">
         <is>
-          <t>Blue Otter</t>
+          <t>Ei Nerd Esports</t>
         </is>
       </c>
       <c r="AT66" s="24" t="inlineStr">
         <is>
-          <t>Blue Otter</t>
+          <t>Ei Nerd Esports</t>
         </is>
       </c>
       <c r="AU66" s="24" t="inlineStr">
         <is>
-          <t>Blue Otter</t>
+          <t>Ei Nerd Esports</t>
         </is>
       </c>
       <c r="AV66" s="24" t="n"/>
@@ -19962,7 +20058,7 @@
       </c>
       <c r="BA66" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BB66" s="24" t="inlineStr">
@@ -19977,7 +20073,7 @@
       </c>
       <c r="BD66" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BE66" s="24" t="inlineStr">
@@ -19997,7 +20093,7 @@
       </c>
       <c r="BH66" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:38.183438Z</t>
+          <t>2026-08-05T13:56:23.555880Z</t>
         </is>
       </c>
       <c r="BI66" s="24" t="inlineStr">
@@ -20007,13 +20103,13 @@
       </c>
       <c r="BJ66" s="25" t="n"/>
       <c r="BK66" s="26" t="n">
-        <v>-213</v>
+        <v>127</v>
       </c>
       <c r="BL66" s="27" t="n">
-        <v>1.469484</v>
+        <v>2.27</v>
       </c>
       <c r="BM66" s="28" t="n">
-        <v>0.680511</v>
+        <v>0.440529</v>
       </c>
       <c r="BN66" s="28" t="n"/>
       <c r="BO66" s="28" t="n"/>
@@ -20048,29 +20144,29 @@
       <c r="CR66" s="24" t="n"/>
       <c r="CS66" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="67" ht="36" customHeight="1">
       <c r="A67" s="24" t="inlineStr">
         <is>
-          <t>4ab457da250542be</t>
+          <t>3a7524f6209d4fe1</t>
         </is>
       </c>
       <c r="B67" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:12.089327Z</t>
+          <t>2026-08-05T13:56:43.896254Z</t>
         </is>
       </c>
       <c r="C67" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T22:00:00Z</t>
+          <t>2026-08-06T00:00:00Z</t>
         </is>
       </c>
       <c r="D67" s="24" t="inlineStr">
         <is>
-          <t>70379</t>
+          <t>70453</t>
         </is>
       </c>
       <c r="E67" s="24" t="inlineStr">
@@ -20080,12 +20176,12 @@
       </c>
       <c r="F67" s="24" t="inlineStr">
         <is>
-          <t>KaBuM! Ilha das Lendas</t>
+          <t>paiN Gaming Academy</t>
         </is>
       </c>
       <c r="G67" s="24" t="inlineStr">
         <is>
-          <t>Ei Nerd Esports</t>
+          <t>INTZ e-Sports</t>
         </is>
       </c>
       <c r="H67" s="24" t="inlineStr">
@@ -20095,7 +20191,7 @@
       </c>
       <c r="I67" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J67" s="25" t="n"/>
@@ -20105,26 +20201,26 @@
         </is>
       </c>
       <c r="L67" s="26" t="n">
-        <v>127</v>
+        <v>-108</v>
       </c>
       <c r="M67" s="27" t="n">
-        <v>2.27</v>
+        <v>1.925926</v>
       </c>
       <c r="N67" s="28" t="n">
-        <v>0.440529</v>
+        <v>0.519231</v>
       </c>
       <c r="O67" s="28" t="n">
-        <v>0.616766</v>
+        <v>0.501166</v>
       </c>
       <c r="P67" s="28" t="n"/>
       <c r="Q67" s="28" t="n">
-        <v>0.176237</v>
+        <v>-0.018065</v>
       </c>
       <c r="R67" s="26" t="n">
-        <v>100</v>
+        <v>11</v>
       </c>
       <c r="S67" s="29" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="T67" s="24" t="inlineStr">
         <is>
@@ -20147,7 +20243,7 @@
       <c r="AD67" s="24" t="n"/>
       <c r="AE67" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-lol-nerd-kbm-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.5200 (market_slug=aec-lol-itz-pnga-2026-08-06).</t>
         </is>
       </c>
       <c r="AF67" s="31" t="inlineStr">
@@ -20165,7 +20261,7 @@
       <c r="AJ67" s="31" t="n"/>
       <c r="AK67" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL67" s="26" t="n">
@@ -20173,47 +20269,47 @@
       </c>
       <c r="AM67" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN67" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO67" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP67" s="24" t="inlineStr">
         <is>
-          <t>KaBuM! Ilha das Lendas</t>
+          <t>paiN Gaming Academy</t>
         </is>
       </c>
       <c r="AQ67" s="24" t="inlineStr">
         <is>
-          <t>KaBuM! Ilha das Lendas</t>
+          <t>paiN Gaming Academy</t>
         </is>
       </c>
       <c r="AR67" s="24" t="inlineStr">
         <is>
-          <t>KaBuM! Ilha das Lendas</t>
+          <t>paiN Gaming Academy</t>
         </is>
       </c>
       <c r="AS67" s="24" t="inlineStr">
         <is>
-          <t>Ei Nerd Esports</t>
+          <t>INTZ e-Sports</t>
         </is>
       </c>
       <c r="AT67" s="24" t="inlineStr">
         <is>
-          <t>Ei Nerd Esports</t>
+          <t>INTZ e-Sports</t>
         </is>
       </c>
       <c r="AU67" s="24" t="inlineStr">
         <is>
-          <t>Ei Nerd Esports</t>
+          <t>INTZ e-Sports</t>
         </is>
       </c>
       <c r="AV67" s="24" t="n"/>
@@ -20231,7 +20327,7 @@
       </c>
       <c r="BA67" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BB67" s="24" t="inlineStr">
@@ -20246,7 +20342,7 @@
       </c>
       <c r="BD67" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BE67" s="24" t="inlineStr">
@@ -20266,7 +20362,7 @@
       </c>
       <c r="BH67" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:38.992546Z</t>
+          <t>2026-08-05T13:56:24.877539Z</t>
         </is>
       </c>
       <c r="BI67" s="24" t="inlineStr">
@@ -20276,13 +20372,13 @@
       </c>
       <c r="BJ67" s="25" t="n"/>
       <c r="BK67" s="26" t="n">
-        <v>127</v>
+        <v>-108</v>
       </c>
       <c r="BL67" s="27" t="n">
-        <v>2.27</v>
+        <v>1.925926</v>
       </c>
       <c r="BM67" s="28" t="n">
-        <v>0.440529</v>
+        <v>0.519231</v>
       </c>
       <c r="BN67" s="28" t="n"/>
       <c r="BO67" s="28" t="n"/>
@@ -20317,19 +20413,19 @@
       <c r="CR67" s="24" t="n"/>
       <c r="CS67" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="68" ht="36" customHeight="1">
       <c r="A68" s="24" t="inlineStr">
         <is>
-          <t>15338739290a44e9</t>
+          <t>3d411f35637542e8</t>
         </is>
       </c>
       <c r="B68" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:12.089327Z</t>
+          <t>2026-08-05T13:56:43.896254Z</t>
         </is>
       </c>
       <c r="C68" s="24" t="inlineStr">
@@ -20374,23 +20470,23 @@
         </is>
       </c>
       <c r="L68" s="26" t="n">
-        <v>-156</v>
+        <v>-117</v>
       </c>
       <c r="M68" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.854701</v>
       </c>
       <c r="N68" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.539171</v>
       </c>
       <c r="O68" s="28" t="n">
-        <v>0.51791</v>
+        <v>0.517701</v>
       </c>
       <c r="P68" s="28" t="n"/>
       <c r="Q68" s="28" t="n">
-        <v>-0.091465</v>
+        <v>-0.02147</v>
       </c>
       <c r="R68" s="26" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="S68" s="29" t="n">
         <v>1</v>
@@ -20416,7 +20512,7 @@
       <c r="AD68" s="24" t="n"/>
       <c r="AE68" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-lol-nrg-cpd-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-lol-nrg-cpd-2026-08-06).</t>
         </is>
       </c>
       <c r="AF68" s="31" t="inlineStr">
@@ -20500,7 +20596,7 @@
       </c>
       <c r="BA68" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BB68" s="24" t="inlineStr">
@@ -20515,7 +20611,7 @@
       </c>
       <c r="BD68" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BE68" s="24" t="inlineStr">
@@ -20535,7 +20631,7 @@
       </c>
       <c r="BH68" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:40.686831Z</t>
+          <t>2026-08-05T13:56:25.480320Z</t>
         </is>
       </c>
       <c r="BI68" s="24" t="inlineStr">
@@ -20545,13 +20641,13 @@
       </c>
       <c r="BJ68" s="25" t="n"/>
       <c r="BK68" s="26" t="n">
-        <v>-156</v>
+        <v>-117</v>
       </c>
       <c r="BL68" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.854701</v>
       </c>
       <c r="BM68" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.539171</v>
       </c>
       <c r="BN68" s="28" t="n"/>
       <c r="BO68" s="28" t="n"/>
@@ -20593,22 +20689,22 @@
     <row r="69" ht="36" customHeight="1">
       <c r="A69" s="24" t="inlineStr">
         <is>
-          <t>23414061ae934e10</t>
+          <t>dc3869dd1c354276</t>
         </is>
       </c>
       <c r="B69" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:12.089327Z</t>
+          <t>2026-08-05T13:56:43.896254Z</t>
         </is>
       </c>
       <c r="C69" s="24" t="inlineStr">
         <is>
-          <t>2026-08-06T00:00:00Z</t>
+          <t>2026-08-06T07:00:00Z</t>
         </is>
       </c>
       <c r="D69" s="24" t="inlineStr">
         <is>
-          <t>70453</t>
+          <t>70560</t>
         </is>
       </c>
       <c r="E69" s="24" t="inlineStr">
@@ -20618,12 +20714,12 @@
       </c>
       <c r="F69" s="24" t="inlineStr">
         <is>
-          <t>paiN Gaming Academy</t>
+          <t>ThunderTalk Gaming</t>
         </is>
       </c>
       <c r="G69" s="24" t="inlineStr">
         <is>
-          <t>INTZ e-Sports</t>
+          <t>LGD Gaming</t>
         </is>
       </c>
       <c r="H69" s="24" t="inlineStr">
@@ -20643,26 +20739,26 @@
         </is>
       </c>
       <c r="L69" s="26" t="n">
-        <v>122</v>
+        <v>-104</v>
       </c>
       <c r="M69" s="27" t="n">
-        <v>2.22</v>
+        <v>1.961538</v>
       </c>
       <c r="N69" s="28" t="n">
-        <v>0.45045</v>
+        <v>0.509804</v>
       </c>
       <c r="O69" s="28" t="n">
-        <v>0.501368</v>
+        <v>0.6021260000000001</v>
       </c>
       <c r="P69" s="28" t="n"/>
       <c r="Q69" s="28" t="n">
-        <v>0.050918</v>
+        <v>0.092322</v>
       </c>
       <c r="R69" s="26" t="n">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="S69" s="29" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="T69" s="24" t="inlineStr">
         <is>
@@ -20685,7 +20781,7 @@
       <c r="AD69" s="24" t="n"/>
       <c r="AE69" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-lol-itz-pnga-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-lol-lgd-tt-2026-08-06).</t>
         </is>
       </c>
       <c r="AF69" s="31" t="inlineStr">
@@ -20703,7 +20799,7 @@
       <c r="AJ69" s="31" t="n"/>
       <c r="AK69" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL69" s="26" t="n">
@@ -20711,47 +20807,47 @@
       </c>
       <c r="AM69" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN69" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO69" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP69" s="24" t="inlineStr">
         <is>
-          <t>paiN Gaming Academy</t>
+          <t>ThunderTalk Gaming</t>
         </is>
       </c>
       <c r="AQ69" s="24" t="inlineStr">
         <is>
-          <t>paiN Gaming Academy</t>
+          <t>ThunderTalk Gaming</t>
         </is>
       </c>
       <c r="AR69" s="24" t="inlineStr">
         <is>
-          <t>paiN Gaming Academy</t>
+          <t>ThunderTalk Gaming</t>
         </is>
       </c>
       <c r="AS69" s="24" t="inlineStr">
         <is>
-          <t>INTZ e-Sports</t>
+          <t>LGD Gaming</t>
         </is>
       </c>
       <c r="AT69" s="24" t="inlineStr">
         <is>
-          <t>INTZ e-Sports</t>
+          <t>LGD Gaming</t>
         </is>
       </c>
       <c r="AU69" s="24" t="inlineStr">
         <is>
-          <t>INTZ e-Sports</t>
+          <t>LGD Gaming</t>
         </is>
       </c>
       <c r="AV69" s="24" t="n"/>
@@ -20769,7 +20865,7 @@
       </c>
       <c r="BA69" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BB69" s="24" t="inlineStr">
@@ -20784,7 +20880,7 @@
       </c>
       <c r="BD69" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BE69" s="24" t="inlineStr">
@@ -20804,7 +20900,7 @@
       </c>
       <c r="BH69" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:41.503876Z</t>
+          <t>2026-08-05T13:56:26.928954Z</t>
         </is>
       </c>
       <c r="BI69" s="24" t="inlineStr">
@@ -20814,13 +20910,13 @@
       </c>
       <c r="BJ69" s="25" t="n"/>
       <c r="BK69" s="26" t="n">
-        <v>122</v>
+        <v>-104</v>
       </c>
       <c r="BL69" s="27" t="n">
-        <v>2.22</v>
+        <v>1.961538</v>
       </c>
       <c r="BM69" s="28" t="n">
-        <v>0.45045</v>
+        <v>0.509804</v>
       </c>
       <c r="BN69" s="28" t="n"/>
       <c r="BO69" s="28" t="n"/>
@@ -20862,22 +20958,22 @@
     <row r="70" ht="36" customHeight="1">
       <c r="A70" s="24" t="inlineStr">
         <is>
-          <t>e66f74da81df4930</t>
+          <t>453181e81f714d23</t>
         </is>
       </c>
       <c r="B70" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:12.089327Z</t>
+          <t>2026-08-05T13:56:43.896254Z</t>
         </is>
       </c>
       <c r="C70" s="24" t="inlineStr">
         <is>
-          <t>2026-08-06T07:00:00Z</t>
+          <t>2026-08-06T08:00:00Z</t>
         </is>
       </c>
       <c r="D70" s="24" t="inlineStr">
         <is>
-          <t>70560</t>
+          <t>70563</t>
         </is>
       </c>
       <c r="E70" s="24" t="inlineStr">
@@ -20887,12 +20983,12 @@
       </c>
       <c r="F70" s="24" t="inlineStr">
         <is>
-          <t>ThunderTalk Gaming</t>
+          <t>DN SOOPers</t>
         </is>
       </c>
       <c r="G70" s="24" t="inlineStr">
         <is>
-          <t>LGD Gaming</t>
+          <t>Kiwoom DRX</t>
         </is>
       </c>
       <c r="H70" s="24" t="inlineStr">
@@ -20912,23 +21008,23 @@
         </is>
       </c>
       <c r="L70" s="26" t="n">
-        <v>122</v>
+        <v>-213</v>
       </c>
       <c r="M70" s="27" t="n">
-        <v>2.22</v>
+        <v>1.469484</v>
       </c>
       <c r="N70" s="28" t="n">
-        <v>0.45045</v>
+        <v>0.680511</v>
       </c>
       <c r="O70" s="28" t="n">
-        <v>0.620532</v>
+        <v>0.630332</v>
       </c>
       <c r="P70" s="28" t="n"/>
       <c r="Q70" s="28" t="n">
-        <v>0.170082</v>
+        <v>-0.050179</v>
       </c>
       <c r="R70" s="26" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S70" s="29" t="n">
         <v>1.5</v>
@@ -20954,7 +21050,7 @@
       <c r="AD70" s="24" t="n"/>
       <c r="AE70" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-lol-lgd-tt-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-lol-krx-dns-2026-08-06).</t>
         </is>
       </c>
       <c r="AF70" s="31" t="inlineStr">
@@ -20972,7 +21068,7 @@
       <c r="AJ70" s="31" t="n"/>
       <c r="AK70" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL70" s="26" t="n">
@@ -20980,47 +21076,47 @@
       </c>
       <c r="AM70" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN70" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO70" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP70" s="24" t="inlineStr">
         <is>
-          <t>ThunderTalk Gaming</t>
+          <t>DN SOOPers</t>
         </is>
       </c>
       <c r="AQ70" s="24" t="inlineStr">
         <is>
-          <t>ThunderTalk Gaming</t>
+          <t>DN SOOPers</t>
         </is>
       </c>
       <c r="AR70" s="24" t="inlineStr">
         <is>
-          <t>ThunderTalk Gaming</t>
+          <t>DN SOOPers</t>
         </is>
       </c>
       <c r="AS70" s="24" t="inlineStr">
         <is>
-          <t>LGD Gaming</t>
+          <t>Kiwoom DRX</t>
         </is>
       </c>
       <c r="AT70" s="24" t="inlineStr">
         <is>
-          <t>LGD Gaming</t>
+          <t>Kiwoom DRX</t>
         </is>
       </c>
       <c r="AU70" s="24" t="inlineStr">
         <is>
-          <t>LGD Gaming</t>
+          <t>Kiwoom DRX</t>
         </is>
       </c>
       <c r="AV70" s="24" t="n"/>
@@ -21038,7 +21134,7 @@
       </c>
       <c r="BA70" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BB70" s="24" t="inlineStr">
@@ -21053,7 +21149,7 @@
       </c>
       <c r="BD70" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BE70" s="24" t="inlineStr">
@@ -21073,7 +21169,7 @@
       </c>
       <c r="BH70" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:44.488114Z</t>
+          <t>2026-08-05T13:56:27.626295Z</t>
         </is>
       </c>
       <c r="BI70" s="24" t="inlineStr">
@@ -21083,13 +21179,13 @@
       </c>
       <c r="BJ70" s="25" t="n"/>
       <c r="BK70" s="26" t="n">
-        <v>122</v>
+        <v>-213</v>
       </c>
       <c r="BL70" s="27" t="n">
-        <v>2.22</v>
+        <v>1.469484</v>
       </c>
       <c r="BM70" s="28" t="n">
-        <v>0.45045</v>
+        <v>0.680511</v>
       </c>
       <c r="BN70" s="28" t="n"/>
       <c r="BO70" s="28" t="n"/>
@@ -21124,29 +21220,29 @@
       <c r="CR70" s="24" t="n"/>
       <c r="CS70" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="71" ht="36" customHeight="1">
       <c r="A71" s="24" t="inlineStr">
         <is>
-          <t>6498236f7bd14e55</t>
+          <t>2c2dc68a422045ed</t>
         </is>
       </c>
       <c r="B71" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:12.089327Z</t>
+          <t>2026-08-05T13:56:43.896254Z</t>
         </is>
       </c>
       <c r="C71" s="24" t="inlineStr">
         <is>
-          <t>2026-08-06T08:00:00Z</t>
+          <t>2026-08-06T09:00:00Z</t>
         </is>
       </c>
       <c r="D71" s="24" t="inlineStr">
         <is>
-          <t>70563</t>
+          <t>70573</t>
         </is>
       </c>
       <c r="E71" s="24" t="inlineStr">
@@ -21156,12 +21252,12 @@
       </c>
       <c r="F71" s="24" t="inlineStr">
         <is>
-          <t>DN SOOPers</t>
+          <t>Ground Zero Gaming</t>
         </is>
       </c>
       <c r="G71" s="24" t="inlineStr">
         <is>
-          <t>Kiwoom DRX</t>
+          <t>Fukuoka SoftBank Hawks Gaming</t>
         </is>
       </c>
       <c r="H71" s="24" t="inlineStr">
@@ -21181,26 +21277,26 @@
         </is>
       </c>
       <c r="L71" s="26" t="n">
-        <v>-213</v>
+        <v>144</v>
       </c>
       <c r="M71" s="27" t="n">
-        <v>1.469484</v>
+        <v>2.44</v>
       </c>
       <c r="N71" s="28" t="n">
-        <v>0.680511</v>
+        <v>0.409836</v>
       </c>
       <c r="O71" s="28" t="n">
-        <v>0.631121</v>
+        <v>0.678118</v>
       </c>
       <c r="P71" s="28" t="n"/>
       <c r="Q71" s="28" t="n">
-        <v>-0.04939</v>
+        <v>0.268282</v>
       </c>
       <c r="R71" s="26" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S71" s="29" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="T71" s="24" t="inlineStr">
         <is>
@@ -21223,7 +21319,7 @@
       <c r="AD71" s="24" t="n"/>
       <c r="AE71" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-lol-krx-dns-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.4100 (market_slug=aec-lol-shg-gz-2026-08-06).</t>
         </is>
       </c>
       <c r="AF71" s="31" t="inlineStr">
@@ -21241,7 +21337,7 @@
       <c r="AJ71" s="31" t="n"/>
       <c r="AK71" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL71" s="26" t="n">
@@ -21249,47 +21345,47 @@
       </c>
       <c r="AM71" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN71" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO71" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP71" s="24" t="inlineStr">
         <is>
-          <t>DN SOOPers</t>
+          <t>Ground Zero Gaming</t>
         </is>
       </c>
       <c r="AQ71" s="24" t="inlineStr">
         <is>
-          <t>DN SOOPers</t>
+          <t>Ground Zero Gaming</t>
         </is>
       </c>
       <c r="AR71" s="24" t="inlineStr">
         <is>
-          <t>DN SOOPers</t>
+          <t>Ground Zero Gaming</t>
         </is>
       </c>
       <c r="AS71" s="24" t="inlineStr">
         <is>
-          <t>Kiwoom DRX</t>
+          <t>Fukuoka SoftBank Hawks Gaming</t>
         </is>
       </c>
       <c r="AT71" s="24" t="inlineStr">
         <is>
-          <t>Kiwoom DRX</t>
+          <t>Fukuoka SoftBank Hawks Gaming</t>
         </is>
       </c>
       <c r="AU71" s="24" t="inlineStr">
         <is>
-          <t>Kiwoom DRX</t>
+          <t>Fukuoka SoftBank Hawks Gaming</t>
         </is>
       </c>
       <c r="AV71" s="24" t="n"/>
@@ -21307,7 +21403,7 @@
       </c>
       <c r="BA71" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BB71" s="24" t="inlineStr">
@@ -21322,7 +21418,7 @@
       </c>
       <c r="BD71" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BE71" s="24" t="inlineStr">
@@ -21342,7 +21438,7 @@
       </c>
       <c r="BH71" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:45.295580Z</t>
+          <t>2026-08-05T13:56:28.210290Z</t>
         </is>
       </c>
       <c r="BI71" s="24" t="inlineStr">
@@ -21352,13 +21448,13 @@
       </c>
       <c r="BJ71" s="25" t="n"/>
       <c r="BK71" s="26" t="n">
-        <v>-213</v>
+        <v>144</v>
       </c>
       <c r="BL71" s="27" t="n">
-        <v>1.469484</v>
+        <v>2.44</v>
       </c>
       <c r="BM71" s="28" t="n">
-        <v>0.680511</v>
+        <v>0.409836</v>
       </c>
       <c r="BN71" s="28" t="n"/>
       <c r="BO71" s="28" t="n"/>
@@ -21393,19 +21489,19 @@
       <c r="CR71" s="24" t="n"/>
       <c r="CS71" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="72" ht="36" customHeight="1">
       <c r="A72" s="24" t="inlineStr">
         <is>
-          <t>ee012e1686e84296</t>
+          <t>73bd27b85249459b</t>
         </is>
       </c>
       <c r="B72" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:12.089327Z</t>
+          <t>2026-08-05T13:56:43.896254Z</t>
         </is>
       </c>
       <c r="C72" s="24" t="inlineStr">
@@ -21415,7 +21511,7 @@
       </c>
       <c r="D72" s="24" t="inlineStr">
         <is>
-          <t>70573</t>
+          <t>70574</t>
         </is>
       </c>
       <c r="E72" s="24" t="inlineStr">
@@ -21425,12 +21521,12 @@
       </c>
       <c r="F72" s="24" t="inlineStr">
         <is>
-          <t>Ground Zero Gaming</t>
+          <t>Ninjas in Pyjamas</t>
         </is>
       </c>
       <c r="G72" s="24" t="inlineStr">
         <is>
-          <t>Fukuoka SoftBank Hawks Gaming</t>
+          <t>Invictus Gaming</t>
         </is>
       </c>
       <c r="H72" s="24" t="inlineStr">
@@ -21440,7 +21536,7 @@
       </c>
       <c r="I72" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J72" s="25" t="n"/>
@@ -21450,26 +21546,26 @@
         </is>
       </c>
       <c r="L72" s="26" t="n">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="M72" s="27" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="N72" s="28" t="n">
-        <v>0.409836</v>
+        <v>0.4</v>
       </c>
       <c r="O72" s="28" t="n">
-        <v>0.678987</v>
+        <v>0.509796</v>
       </c>
       <c r="P72" s="28" t="n"/>
       <c r="Q72" s="28" t="n">
-        <v>0.269151</v>
+        <v>0.109796</v>
       </c>
       <c r="R72" s="26" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="S72" s="29" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="T72" s="24" t="inlineStr">
         <is>
@@ -21492,7 +21588,7 @@
       <c r="AD72" s="24" t="n"/>
       <c r="AE72" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4100 (market_slug=aec-lol-shg-gz-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.4000 (market_slug=aec-lol-ig-nip-2026-08-06).</t>
         </is>
       </c>
       <c r="AF72" s="31" t="inlineStr">
@@ -21510,7 +21606,7 @@
       <c r="AJ72" s="31" t="n"/>
       <c r="AK72" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL72" s="26" t="n">
@@ -21518,47 +21614,47 @@
       </c>
       <c r="AM72" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN72" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO72" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP72" s="24" t="inlineStr">
         <is>
-          <t>Ground Zero Gaming</t>
+          <t>Ninjas in Pyjamas</t>
         </is>
       </c>
       <c r="AQ72" s="24" t="inlineStr">
         <is>
-          <t>Ground Zero Gaming</t>
+          <t>Ninjas in Pyjamas</t>
         </is>
       </c>
       <c r="AR72" s="24" t="inlineStr">
         <is>
-          <t>Ground Zero Gaming</t>
+          <t>Ninjas in Pyjamas</t>
         </is>
       </c>
       <c r="AS72" s="24" t="inlineStr">
         <is>
-          <t>Fukuoka SoftBank Hawks Gaming</t>
+          <t>Invictus Gaming</t>
         </is>
       </c>
       <c r="AT72" s="24" t="inlineStr">
         <is>
-          <t>Fukuoka SoftBank Hawks Gaming</t>
+          <t>Invictus Gaming</t>
         </is>
       </c>
       <c r="AU72" s="24" t="inlineStr">
         <is>
-          <t>Fukuoka SoftBank Hawks Gaming</t>
+          <t>Invictus Gaming</t>
         </is>
       </c>
       <c r="AV72" s="24" t="n"/>
@@ -21576,7 +21672,7 @@
       </c>
       <c r="BA72" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BB72" s="24" t="inlineStr">
@@ -21591,7 +21687,7 @@
       </c>
       <c r="BD72" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BE72" s="24" t="inlineStr">
@@ -21611,7 +21707,7 @@
       </c>
       <c r="BH72" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:46.091265Z</t>
+          <t>2026-08-05T13:56:28.798597Z</t>
         </is>
       </c>
       <c r="BI72" s="24" t="inlineStr">
@@ -21621,13 +21717,13 @@
       </c>
       <c r="BJ72" s="25" t="n"/>
       <c r="BK72" s="26" t="n">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="BL72" s="27" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="BM72" s="28" t="n">
-        <v>0.409836</v>
+        <v>0.4</v>
       </c>
       <c r="BN72" s="28" t="n"/>
       <c r="BO72" s="28" t="n"/>
@@ -21669,22 +21765,22 @@
     <row r="73" ht="36" customHeight="1">
       <c r="A73" s="24" t="inlineStr">
         <is>
-          <t>e072fbb5057042dc</t>
+          <t>a04f986f516f4ccd</t>
         </is>
       </c>
       <c r="B73" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:12.089327Z</t>
+          <t>2026-08-05T13:56:43.896254Z</t>
         </is>
       </c>
       <c r="C73" s="24" t="inlineStr">
         <is>
-          <t>2026-08-06T09:00:00Z</t>
+          <t>2026-08-06T10:00:00Z</t>
         </is>
       </c>
       <c r="D73" s="24" t="inlineStr">
         <is>
-          <t>70574</t>
+          <t>70594</t>
         </is>
       </c>
       <c r="E73" s="24" t="inlineStr">
@@ -21694,12 +21790,12 @@
       </c>
       <c r="F73" s="24" t="inlineStr">
         <is>
-          <t>Ninjas in Pyjamas</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="G73" s="24" t="inlineStr">
         <is>
-          <t>Invictus Gaming</t>
+          <t>Dplus KIA</t>
         </is>
       </c>
       <c r="H73" s="24" t="inlineStr">
@@ -21719,23 +21815,23 @@
         </is>
       </c>
       <c r="L73" s="26" t="n">
-        <v>150</v>
+        <v>-108</v>
       </c>
       <c r="M73" s="27" t="n">
-        <v>2.5</v>
+        <v>1.925926</v>
       </c>
       <c r="N73" s="28" t="n">
-        <v>0.4</v>
+        <v>0.519231</v>
       </c>
       <c r="O73" s="28" t="n">
-        <v>0.509616</v>
+        <v>0.553149</v>
       </c>
       <c r="P73" s="28" t="n"/>
       <c r="Q73" s="28" t="n">
-        <v>0.109616</v>
+        <v>0.033918</v>
       </c>
       <c r="R73" s="26" t="n">
-        <v>75</v>
+        <v>37</v>
       </c>
       <c r="S73" s="29" t="n">
         <v>1</v>
@@ -21761,7 +21857,7 @@
       <c r="AD73" s="24" t="n"/>
       <c r="AE73" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4000 (market_slug=aec-lol-ig-nip-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.5200 (market_slug=aec-lol-dk-t1-2026-08-06).</t>
         </is>
       </c>
       <c r="AF73" s="31" t="inlineStr">
@@ -21779,7 +21875,7 @@
       <c r="AJ73" s="31" t="n"/>
       <c r="AK73" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL73" s="26" t="n">
@@ -21787,47 +21883,47 @@
       </c>
       <c r="AM73" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN73" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO73" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP73" s="24" t="inlineStr">
         <is>
-          <t>Ninjas in Pyjamas</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="AQ73" s="24" t="inlineStr">
         <is>
-          <t>Ninjas in Pyjamas</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="AR73" s="24" t="inlineStr">
         <is>
-          <t>Ninjas in Pyjamas</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="AS73" s="24" t="inlineStr">
         <is>
-          <t>Invictus Gaming</t>
+          <t>Dplus KIA</t>
         </is>
       </c>
       <c r="AT73" s="24" t="inlineStr">
         <is>
-          <t>Invictus Gaming</t>
+          <t>Dplus KIA</t>
         </is>
       </c>
       <c r="AU73" s="24" t="inlineStr">
         <is>
-          <t>Invictus Gaming</t>
+          <t>Dplus KIA</t>
         </is>
       </c>
       <c r="AV73" s="24" t="n"/>
@@ -21845,7 +21941,7 @@
       </c>
       <c r="BA73" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BB73" s="24" t="inlineStr">
@@ -21860,7 +21956,7 @@
       </c>
       <c r="BD73" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BE73" s="24" t="inlineStr">
@@ -21880,7 +21976,7 @@
       </c>
       <c r="BH73" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:46.918233Z</t>
+          <t>2026-08-05T13:56:29.341663Z</t>
         </is>
       </c>
       <c r="BI73" s="24" t="inlineStr">
@@ -21890,13 +21986,13 @@
       </c>
       <c r="BJ73" s="25" t="n"/>
       <c r="BK73" s="26" t="n">
-        <v>150</v>
+        <v>-108</v>
       </c>
       <c r="BL73" s="27" t="n">
-        <v>2.5</v>
+        <v>1.925926</v>
       </c>
       <c r="BM73" s="28" t="n">
-        <v>0.4</v>
+        <v>0.519231</v>
       </c>
       <c r="BN73" s="28" t="n"/>
       <c r="BO73" s="28" t="n"/>
@@ -21938,22 +22034,22 @@
     <row r="74" ht="36" customHeight="1">
       <c r="A74" s="24" t="inlineStr">
         <is>
-          <t>f281aba817024dab</t>
+          <t>c8158b6023de4f94</t>
         </is>
       </c>
       <c r="B74" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:12.089327Z</t>
+          <t>2026-08-05T13:56:43.896254Z</t>
         </is>
       </c>
       <c r="C74" s="24" t="inlineStr">
         <is>
-          <t>2026-08-06T10:00:00Z</t>
+          <t>2026-08-06T16:00:00Z</t>
         </is>
       </c>
       <c r="D74" s="24" t="inlineStr">
         <is>
-          <t>70594</t>
+          <t>70788</t>
         </is>
       </c>
       <c r="E74" s="24" t="inlineStr">
@@ -21963,12 +22059,12 @@
       </c>
       <c r="F74" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Esprit Shōnen</t>
         </is>
       </c>
       <c r="G74" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA</t>
+          <t>Ici Japon Corp. Esport</t>
         </is>
       </c>
       <c r="H74" s="24" t="inlineStr">
@@ -21978,7 +22074,7 @@
       </c>
       <c r="I74" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J74" s="25" t="n"/>
@@ -21988,26 +22084,26 @@
         </is>
       </c>
       <c r="L74" s="26" t="n">
-        <v>-108</v>
+        <v>-213</v>
       </c>
       <c r="M74" s="27" t="n">
-        <v>1.925926</v>
+        <v>1.469484</v>
       </c>
       <c r="N74" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.680511</v>
       </c>
       <c r="O74" s="28" t="n">
-        <v>0.55358</v>
+        <v>0.692554</v>
       </c>
       <c r="P74" s="28" t="n"/>
       <c r="Q74" s="28" t="n">
-        <v>0.034349</v>
+        <v>0.012043</v>
       </c>
       <c r="R74" s="26" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="S74" s="29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T74" s="24" t="inlineStr">
         <is>
@@ -22030,7 +22126,7 @@
       <c r="AD74" s="24" t="n"/>
       <c r="AE74" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5200 (market_slug=aec-lol-dk-t1-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-lol-ijc-ess-2026-08-06).</t>
         </is>
       </c>
       <c r="AF74" s="31" t="inlineStr">
@@ -22071,32 +22167,32 @@
       </c>
       <c r="AP74" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Esprit Shōnen</t>
         </is>
       </c>
       <c r="AQ74" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Esprit Shōnen</t>
         </is>
       </c>
       <c r="AR74" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Esprit Shōnen</t>
         </is>
       </c>
       <c r="AS74" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA</t>
+          <t>Ici Japon Corp. Esport</t>
         </is>
       </c>
       <c r="AT74" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA</t>
+          <t>Ici Japon Corp. Esport</t>
         </is>
       </c>
       <c r="AU74" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA</t>
+          <t>Ici Japon Corp. Esport</t>
         </is>
       </c>
       <c r="AV74" s="24" t="n"/>
@@ -22114,7 +22210,7 @@
       </c>
       <c r="BA74" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BB74" s="24" t="inlineStr">
@@ -22129,7 +22225,7 @@
       </c>
       <c r="BD74" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BE74" s="24" t="inlineStr">
@@ -22149,7 +22245,7 @@
       </c>
       <c r="BH74" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:47.837724Z</t>
+          <t>2026-08-05T13:56:33.192924Z</t>
         </is>
       </c>
       <c r="BI74" s="24" t="inlineStr">
@@ -22159,13 +22255,13 @@
       </c>
       <c r="BJ74" s="25" t="n"/>
       <c r="BK74" s="26" t="n">
-        <v>-108</v>
+        <v>-213</v>
       </c>
       <c r="BL74" s="27" t="n">
-        <v>1.925926</v>
+        <v>1.469484</v>
       </c>
       <c r="BM74" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.680511</v>
       </c>
       <c r="BN74" s="28" t="n"/>
       <c r="BO74" s="28" t="n"/>
@@ -22207,12 +22303,12 @@
     <row r="75" ht="36" customHeight="1">
       <c r="A75" s="24" t="inlineStr">
         <is>
-          <t>3e87da4b79ef4a11</t>
+          <t>119fecc2562f44ea</t>
         </is>
       </c>
       <c r="B75" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:12.089327Z</t>
+          <t>2026-08-05T13:56:43.896254Z</t>
         </is>
       </c>
       <c r="C75" s="24" t="inlineStr">
@@ -22222,7 +22318,7 @@
       </c>
       <c r="D75" s="24" t="inlineStr">
         <is>
-          <t>70788</t>
+          <t>70790</t>
         </is>
       </c>
       <c r="E75" s="24" t="inlineStr">
@@ -22232,12 +22328,12 @@
       </c>
       <c r="F75" s="24" t="inlineStr">
         <is>
-          <t>Esprit Shōnen</t>
+          <t>Baam Esports</t>
         </is>
       </c>
       <c r="G75" s="24" t="inlineStr">
         <is>
-          <t>Ici Japon Corp. Esport</t>
+          <t>One More Esports</t>
         </is>
       </c>
       <c r="H75" s="24" t="inlineStr">
@@ -22247,7 +22343,7 @@
       </c>
       <c r="I75" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J75" s="25" t="n"/>
@@ -22257,23 +22353,23 @@
         </is>
       </c>
       <c r="L75" s="26" t="n">
-        <v>-213</v>
+        <v>-144</v>
       </c>
       <c r="M75" s="27" t="n">
-        <v>1.469484</v>
+        <v>1.694444</v>
       </c>
       <c r="N75" s="28" t="n">
-        <v>0.680511</v>
+        <v>0.590164</v>
       </c>
       <c r="O75" s="28" t="n">
-        <v>0.6935249999999999</v>
+        <v>0.764526</v>
       </c>
       <c r="P75" s="28" t="n"/>
       <c r="Q75" s="28" t="n">
-        <v>0.013014</v>
+        <v>0.174362</v>
       </c>
       <c r="R75" s="26" t="n">
-        <v>27</v>
+        <v>100</v>
       </c>
       <c r="S75" s="29" t="n">
         <v>2</v>
@@ -22299,7 +22395,7 @@
       <c r="AD75" s="24" t="n"/>
       <c r="AE75" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-lol-ijc-ess-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-lol-one-bam-2026-08-06).</t>
         </is>
       </c>
       <c r="AF75" s="31" t="inlineStr">
@@ -22340,32 +22436,32 @@
       </c>
       <c r="AP75" s="24" t="inlineStr">
         <is>
-          <t>Esprit Shōnen</t>
+          <t>Baam Esports</t>
         </is>
       </c>
       <c r="AQ75" s="24" t="inlineStr">
         <is>
-          <t>Esprit Shōnen</t>
+          <t>Baam Esports</t>
         </is>
       </c>
       <c r="AR75" s="24" t="inlineStr">
         <is>
-          <t>Esprit Shōnen</t>
+          <t>Baam Esports</t>
         </is>
       </c>
       <c r="AS75" s="24" t="inlineStr">
         <is>
-          <t>Ici Japon Corp. Esport</t>
+          <t>One More Esports</t>
         </is>
       </c>
       <c r="AT75" s="24" t="inlineStr">
         <is>
-          <t>Ici Japon Corp. Esport</t>
+          <t>One More Esports</t>
         </is>
       </c>
       <c r="AU75" s="24" t="inlineStr">
         <is>
-          <t>Ici Japon Corp. Esport</t>
+          <t>One More Esports</t>
         </is>
       </c>
       <c r="AV75" s="24" t="n"/>
@@ -22383,7 +22479,7 @@
       </c>
       <c r="BA75" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BB75" s="24" t="inlineStr">
@@ -22398,7 +22494,7 @@
       </c>
       <c r="BD75" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BE75" s="24" t="inlineStr">
@@ -22418,7 +22514,7 @@
       </c>
       <c r="BH75" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:53.039362Z</t>
+          <t>2026-08-05T13:56:34.263579Z</t>
         </is>
       </c>
       <c r="BI75" s="24" t="inlineStr">
@@ -22428,13 +22524,13 @@
       </c>
       <c r="BJ75" s="25" t="n"/>
       <c r="BK75" s="26" t="n">
-        <v>-213</v>
+        <v>-144</v>
       </c>
       <c r="BL75" s="27" t="n">
-        <v>1.469484</v>
+        <v>1.694444</v>
       </c>
       <c r="BM75" s="28" t="n">
-        <v>0.680511</v>
+        <v>0.590164</v>
       </c>
       <c r="BN75" s="28" t="n"/>
       <c r="BO75" s="28" t="n"/>
@@ -22476,22 +22572,22 @@
     <row r="76" ht="36" customHeight="1">
       <c r="A76" s="24" t="inlineStr">
         <is>
-          <t>dcc8068d831f49f6</t>
+          <t>a78e68f5bc634585</t>
         </is>
       </c>
       <c r="B76" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:12.089327Z</t>
+          <t>2026-08-05T13:56:43.896254Z</t>
         </is>
       </c>
       <c r="C76" s="24" t="inlineStr">
         <is>
-          <t>2026-08-06T16:00:00Z</t>
+          <t>2026-08-06T17:00:00Z</t>
         </is>
       </c>
       <c r="D76" s="24" t="inlineStr">
         <is>
-          <t>70789</t>
+          <t>70860</t>
         </is>
       </c>
       <c r="E76" s="24" t="inlineStr">
@@ -22501,12 +22597,12 @@
       </c>
       <c r="F76" s="24" t="inlineStr">
         <is>
-          <t>Lupus Esports</t>
+          <t>Skillcamp Esport</t>
         </is>
       </c>
       <c r="G76" s="24" t="inlineStr">
         <is>
-          <t>The Secret Club</t>
+          <t>Karmine Corp Blue</t>
         </is>
       </c>
       <c r="H76" s="24" t="inlineStr">
@@ -22526,26 +22622,26 @@
         </is>
       </c>
       <c r="L76" s="26" t="n">
-        <v>-223</v>
+        <v>-150</v>
       </c>
       <c r="M76" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.666667</v>
       </c>
       <c r="N76" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.6</v>
       </c>
       <c r="O76" s="28" t="n">
-        <v>0.639494</v>
+        <v>0.744077</v>
       </c>
       <c r="P76" s="28" t="n"/>
       <c r="Q76" s="28" t="n">
-        <v>-0.050908</v>
+        <v>0.144077</v>
       </c>
       <c r="R76" s="26" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="S76" s="29" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="T76" s="24" t="inlineStr">
         <is>
@@ -22568,7 +22664,7 @@
       <c r="AD76" s="24" t="n"/>
       <c r="AE76" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-lol-tsc-lps-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-lol-kcb-sc-2026-08-06).</t>
         </is>
       </c>
       <c r="AF76" s="31" t="inlineStr">
@@ -22586,7 +22682,7 @@
       <c r="AJ76" s="31" t="n"/>
       <c r="AK76" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL76" s="26" t="n">
@@ -22594,47 +22690,47 @@
       </c>
       <c r="AM76" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN76" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO76" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP76" s="24" t="inlineStr">
         <is>
-          <t>Lupus Esports</t>
+          <t>Skillcamp Esport</t>
         </is>
       </c>
       <c r="AQ76" s="24" t="inlineStr">
         <is>
-          <t>Lupus Esports</t>
+          <t>Skillcamp Esport</t>
         </is>
       </c>
       <c r="AR76" s="24" t="inlineStr">
         <is>
-          <t>Lupus Esports</t>
+          <t>Skillcamp Esport</t>
         </is>
       </c>
       <c r="AS76" s="24" t="inlineStr">
         <is>
-          <t>The Secret Club</t>
+          <t>Karmine Corp Blue</t>
         </is>
       </c>
       <c r="AT76" s="24" t="inlineStr">
         <is>
-          <t>The Secret Club</t>
+          <t>Karmine Corp Blue</t>
         </is>
       </c>
       <c r="AU76" s="24" t="inlineStr">
         <is>
-          <t>The Secret Club</t>
+          <t>Karmine Corp Blue</t>
         </is>
       </c>
       <c r="AV76" s="24" t="n"/>
@@ -22652,7 +22748,7 @@
       </c>
       <c r="BA76" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BB76" s="24" t="inlineStr">
@@ -22667,7 +22763,7 @@
       </c>
       <c r="BD76" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BE76" s="24" t="inlineStr">
@@ -22687,7 +22783,7 @@
       </c>
       <c r="BH76" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:54.131588Z</t>
+          <t>2026-08-05T13:56:34.906561Z</t>
         </is>
       </c>
       <c r="BI76" s="24" t="inlineStr">
@@ -22697,13 +22793,13 @@
       </c>
       <c r="BJ76" s="25" t="n"/>
       <c r="BK76" s="26" t="n">
-        <v>-223</v>
+        <v>-150</v>
       </c>
       <c r="BL76" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.666667</v>
       </c>
       <c r="BM76" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.6</v>
       </c>
       <c r="BN76" s="28" t="n"/>
       <c r="BO76" s="28" t="n"/>
@@ -22738,29 +22834,29 @@
       <c r="CR76" s="24" t="n"/>
       <c r="CS76" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="77" ht="36" customHeight="1">
       <c r="A77" s="24" t="inlineStr">
         <is>
-          <t>cf005b0f6c454992</t>
+          <t>b95bbd9bf4b04d4d</t>
         </is>
       </c>
       <c r="B77" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:12.089327Z</t>
+          <t>2026-08-05T13:56:43.896254Z</t>
         </is>
       </c>
       <c r="C77" s="24" t="inlineStr">
         <is>
-          <t>2026-08-06T16:00:00Z</t>
+          <t>2026-08-06T17:00:00Z</t>
         </is>
       </c>
       <c r="D77" s="24" t="inlineStr">
         <is>
-          <t>70790</t>
+          <t>70862</t>
         </is>
       </c>
       <c r="E77" s="24" t="inlineStr">
@@ -22770,12 +22866,12 @@
       </c>
       <c r="F77" s="24" t="inlineStr">
         <is>
-          <t>Baam Esports</t>
+          <t>EKO Esports</t>
         </is>
       </c>
       <c r="G77" s="24" t="inlineStr">
         <is>
-          <t>One More Esports</t>
+          <t>Colossal Gaming</t>
         </is>
       </c>
       <c r="H77" s="24" t="inlineStr">
@@ -22785,7 +22881,7 @@
       </c>
       <c r="I77" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J77" s="25" t="n"/>
@@ -22795,23 +22891,23 @@
         </is>
       </c>
       <c r="L77" s="26" t="n">
-        <v>-144</v>
+        <v>-186</v>
       </c>
       <c r="M77" s="27" t="n">
-        <v>1.694444</v>
+        <v>1.537634</v>
       </c>
       <c r="N77" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.65035</v>
       </c>
       <c r="O77" s="28" t="n">
-        <v>0.765346</v>
+        <v>0.697999</v>
       </c>
       <c r="P77" s="28" t="n"/>
       <c r="Q77" s="28" t="n">
-        <v>0.175182</v>
+        <v>0.047649</v>
       </c>
       <c r="R77" s="26" t="n">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="S77" s="29" t="n">
         <v>2</v>
@@ -22837,7 +22933,7 @@
       <c r="AD77" s="24" t="n"/>
       <c r="AE77" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-lol-one-bam-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.6500 (market_slug=aec-lol-cg-eko-2026-08-06).</t>
         </is>
       </c>
       <c r="AF77" s="31" t="inlineStr">
@@ -22878,32 +22974,32 @@
       </c>
       <c r="AP77" s="24" t="inlineStr">
         <is>
-          <t>Baam Esports</t>
+          <t>EKO Esports</t>
         </is>
       </c>
       <c r="AQ77" s="24" t="inlineStr">
         <is>
-          <t>Baam Esports</t>
+          <t>EKO Esports</t>
         </is>
       </c>
       <c r="AR77" s="24" t="inlineStr">
         <is>
-          <t>Baam Esports</t>
+          <t>EKO Esports</t>
         </is>
       </c>
       <c r="AS77" s="24" t="inlineStr">
         <is>
-          <t>One More Esports</t>
+          <t>Colossal Gaming</t>
         </is>
       </c>
       <c r="AT77" s="24" t="inlineStr">
         <is>
-          <t>One More Esports</t>
+          <t>Colossal Gaming</t>
         </is>
       </c>
       <c r="AU77" s="24" t="inlineStr">
         <is>
-          <t>One More Esports</t>
+          <t>Colossal Gaming</t>
         </is>
       </c>
       <c r="AV77" s="24" t="n"/>
@@ -22921,7 +23017,7 @@
       </c>
       <c r="BA77" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BB77" s="24" t="inlineStr">
@@ -22936,7 +23032,7 @@
       </c>
       <c r="BD77" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BE77" s="24" t="inlineStr">
@@ -22956,7 +23052,7 @@
       </c>
       <c r="BH77" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:55.077551Z</t>
+          <t>2026-08-05T13:56:35.496841Z</t>
         </is>
       </c>
       <c r="BI77" s="24" t="inlineStr">
@@ -22966,13 +23062,13 @@
       </c>
       <c r="BJ77" s="25" t="n"/>
       <c r="BK77" s="26" t="n">
-        <v>-144</v>
+        <v>-186</v>
       </c>
       <c r="BL77" s="27" t="n">
-        <v>1.694444</v>
+        <v>1.537634</v>
       </c>
       <c r="BM77" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.65035</v>
       </c>
       <c r="BN77" s="28" t="n"/>
       <c r="BO77" s="28" t="n"/>
@@ -23014,12 +23110,12 @@
     <row r="78" ht="36" customHeight="1">
       <c r="A78" s="24" t="inlineStr">
         <is>
-          <t>318477890f7a4058</t>
+          <t>a1f7eb6913514b48</t>
         </is>
       </c>
       <c r="B78" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:12.089327Z</t>
+          <t>2026-08-05T13:56:43.896254Z</t>
         </is>
       </c>
       <c r="C78" s="24" t="inlineStr">
@@ -23029,7 +23125,7 @@
       </c>
       <c r="D78" s="24" t="inlineStr">
         <is>
-          <t>70860</t>
+          <t>70863</t>
         </is>
       </c>
       <c r="E78" s="24" t="inlineStr">
@@ -23039,12 +23135,12 @@
       </c>
       <c r="F78" s="24" t="inlineStr">
         <is>
-          <t>Skillcamp Esport</t>
+          <t>Senshi Esports</t>
         </is>
       </c>
       <c r="G78" s="24" t="inlineStr">
         <is>
-          <t>Karmine Corp Blue</t>
+          <t>Myth Esports</t>
         </is>
       </c>
       <c r="H78" s="24" t="inlineStr">
@@ -23054,7 +23150,7 @@
       </c>
       <c r="I78" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J78" s="25" t="n"/>
@@ -23064,26 +23160,26 @@
         </is>
       </c>
       <c r="L78" s="26" t="n">
-        <v>-150</v>
+        <v>127</v>
       </c>
       <c r="M78" s="27" t="n">
-        <v>1.666667</v>
+        <v>2.27</v>
       </c>
       <c r="N78" s="28" t="n">
-        <v>0.6</v>
+        <v>0.440529</v>
       </c>
       <c r="O78" s="28" t="n">
-        <v>0.745171</v>
+        <v>0.514652</v>
       </c>
       <c r="P78" s="28" t="n"/>
       <c r="Q78" s="28" t="n">
-        <v>0.145171</v>
+        <v>0.07412299999999999</v>
       </c>
       <c r="R78" s="26" t="n">
-        <v>93</v>
+        <v>57</v>
       </c>
       <c r="S78" s="29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T78" s="24" t="inlineStr">
         <is>
@@ -23106,7 +23202,7 @@
       <c r="AD78" s="24" t="n"/>
       <c r="AE78" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-lol-kcb-sc-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-lol-myth-sec-2026-08-06).</t>
         </is>
       </c>
       <c r="AF78" s="31" t="inlineStr">
@@ -23124,7 +23220,7 @@
       <c r="AJ78" s="31" t="n"/>
       <c r="AK78" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL78" s="26" t="n">
@@ -23132,47 +23228,47 @@
       </c>
       <c r="AM78" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN78" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO78" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP78" s="24" t="inlineStr">
         <is>
-          <t>Skillcamp Esport</t>
+          <t>Senshi Esports</t>
         </is>
       </c>
       <c r="AQ78" s="24" t="inlineStr">
         <is>
-          <t>Skillcamp Esport</t>
+          <t>Senshi Esports</t>
         </is>
       </c>
       <c r="AR78" s="24" t="inlineStr">
         <is>
-          <t>Skillcamp Esport</t>
+          <t>Senshi Esports</t>
         </is>
       </c>
       <c r="AS78" s="24" t="inlineStr">
         <is>
-          <t>Karmine Corp Blue</t>
+          <t>Myth Esports</t>
         </is>
       </c>
       <c r="AT78" s="24" t="inlineStr">
         <is>
-          <t>Karmine Corp Blue</t>
+          <t>Myth Esports</t>
         </is>
       </c>
       <c r="AU78" s="24" t="inlineStr">
         <is>
-          <t>Karmine Corp Blue</t>
+          <t>Myth Esports</t>
         </is>
       </c>
       <c r="AV78" s="24" t="n"/>
@@ -23190,7 +23286,7 @@
       </c>
       <c r="BA78" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BB78" s="24" t="inlineStr">
@@ -23205,7 +23301,7 @@
       </c>
       <c r="BD78" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BE78" s="24" t="inlineStr">
@@ -23225,7 +23321,7 @@
       </c>
       <c r="BH78" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:56.857849Z</t>
+          <t>2026-08-05T13:56:36.074282Z</t>
         </is>
       </c>
       <c r="BI78" s="24" t="inlineStr">
@@ -23235,13 +23331,13 @@
       </c>
       <c r="BJ78" s="25" t="n"/>
       <c r="BK78" s="26" t="n">
-        <v>-150</v>
+        <v>127</v>
       </c>
       <c r="BL78" s="27" t="n">
-        <v>1.666667</v>
+        <v>2.27</v>
       </c>
       <c r="BM78" s="28" t="n">
-        <v>0.6</v>
+        <v>0.440529</v>
       </c>
       <c r="BN78" s="28" t="n"/>
       <c r="BO78" s="28" t="n"/>
@@ -23283,22 +23379,22 @@
     <row r="79" ht="36" customHeight="1">
       <c r="A79" s="24" t="inlineStr">
         <is>
-          <t>85de09c14bae47d5</t>
+          <t>9ff5f6581a014255</t>
         </is>
       </c>
       <c r="B79" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:12.089327Z</t>
+          <t>2026-08-05T13:56:43.896254Z</t>
         </is>
       </c>
       <c r="C79" s="24" t="inlineStr">
         <is>
-          <t>2026-08-06T17:00:00Z</t>
+          <t>2026-08-06T18:00:00Z</t>
         </is>
       </c>
       <c r="D79" s="24" t="inlineStr">
         <is>
-          <t>70862</t>
+          <t>70899</t>
         </is>
       </c>
       <c r="E79" s="24" t="inlineStr">
@@ -23308,12 +23404,12 @@
       </c>
       <c r="F79" s="24" t="inlineStr">
         <is>
-          <t>EKO Esports</t>
+          <t>Joblife</t>
         </is>
       </c>
       <c r="G79" s="24" t="inlineStr">
         <is>
-          <t>Colossal Gaming</t>
+          <t>TLN Pirates</t>
         </is>
       </c>
       <c r="H79" s="24" t="inlineStr">
@@ -23333,26 +23429,26 @@
         </is>
       </c>
       <c r="L79" s="26" t="n">
-        <v>-203</v>
+        <v>-133</v>
       </c>
       <c r="M79" s="27" t="n">
-        <v>1.492611</v>
+        <v>1.75188</v>
       </c>
       <c r="N79" s="28" t="n">
-        <v>0.669967</v>
+        <v>0.570815</v>
       </c>
       <c r="O79" s="28" t="n">
-        <v>0.698972</v>
+        <v>0.6554720000000001</v>
       </c>
       <c r="P79" s="28" t="n"/>
       <c r="Q79" s="28" t="n">
-        <v>0.029005</v>
+        <v>0.084657</v>
       </c>
       <c r="R79" s="26" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="S79" s="29" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="T79" s="24" t="inlineStr">
         <is>
@@ -23375,7 +23471,7 @@
       <c r="AD79" s="24" t="n"/>
       <c r="AE79" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-lol-cg-eko-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-lol-tlnp-jl-2026-08-06).</t>
         </is>
       </c>
       <c r="AF79" s="31" t="inlineStr">
@@ -23416,32 +23512,32 @@
       </c>
       <c r="AP79" s="24" t="inlineStr">
         <is>
-          <t>EKO Esports</t>
+          <t>Joblife</t>
         </is>
       </c>
       <c r="AQ79" s="24" t="inlineStr">
         <is>
-          <t>EKO Esports</t>
+          <t>Joblife</t>
         </is>
       </c>
       <c r="AR79" s="24" t="inlineStr">
         <is>
-          <t>EKO Esports</t>
+          <t>Joblife</t>
         </is>
       </c>
       <c r="AS79" s="24" t="inlineStr">
         <is>
-          <t>Colossal Gaming</t>
+          <t>TLN Pirates</t>
         </is>
       </c>
       <c r="AT79" s="24" t="inlineStr">
         <is>
-          <t>Colossal Gaming</t>
+          <t>TLN Pirates</t>
         </is>
       </c>
       <c r="AU79" s="24" t="inlineStr">
         <is>
-          <t>Colossal Gaming</t>
+          <t>TLN Pirates</t>
         </is>
       </c>
       <c r="AV79" s="24" t="n"/>
@@ -23459,7 +23555,7 @@
       </c>
       <c r="BA79" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BB79" s="24" t="inlineStr">
@@ -23474,7 +23570,7 @@
       </c>
       <c r="BD79" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BE79" s="24" t="inlineStr">
@@ -23494,7 +23590,7 @@
       </c>
       <c r="BH79" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:57.734148Z</t>
+          <t>2026-08-05T13:56:37.925941Z</t>
         </is>
       </c>
       <c r="BI79" s="24" t="inlineStr">
@@ -23504,13 +23600,13 @@
       </c>
       <c r="BJ79" s="25" t="n"/>
       <c r="BK79" s="26" t="n">
-        <v>-203</v>
+        <v>-133</v>
       </c>
       <c r="BL79" s="27" t="n">
-        <v>1.492611</v>
+        <v>1.75188</v>
       </c>
       <c r="BM79" s="28" t="n">
-        <v>0.669967</v>
+        <v>0.570815</v>
       </c>
       <c r="BN79" s="28" t="n"/>
       <c r="BO79" s="28" t="n"/>
@@ -23552,12 +23648,12 @@
     <row r="80" ht="36" customHeight="1">
       <c r="A80" s="24" t="inlineStr">
         <is>
-          <t>1f313f038d7442f7</t>
+          <t>5044fda3950d4746</t>
         </is>
       </c>
       <c r="B80" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:12.089327Z</t>
+          <t>2026-08-05T13:56:43.896254Z</t>
         </is>
       </c>
       <c r="C80" s="24" t="inlineStr">
@@ -23567,7 +23663,7 @@
       </c>
       <c r="D80" s="24" t="inlineStr">
         <is>
-          <t>70899</t>
+          <t>70903</t>
         </is>
       </c>
       <c r="E80" s="24" t="inlineStr">
@@ -23577,12 +23673,12 @@
       </c>
       <c r="F80" s="24" t="inlineStr">
         <is>
-          <t>Joblife</t>
+          <t>Zena Esports</t>
         </is>
       </c>
       <c r="G80" s="24" t="inlineStr">
         <is>
-          <t>TLN Pirates</t>
+          <t>GMBLERS ESPORTS</t>
         </is>
       </c>
       <c r="H80" s="24" t="inlineStr">
@@ -23602,26 +23698,26 @@
         </is>
       </c>
       <c r="L80" s="26" t="n">
-        <v>-233</v>
+        <v>-108</v>
       </c>
       <c r="M80" s="27" t="n">
-        <v>1.429185</v>
+        <v>1.925926</v>
       </c>
       <c r="N80" s="28" t="n">
-        <v>0.6997</v>
+        <v>0.519231</v>
       </c>
       <c r="O80" s="28" t="n">
-        <v>0.656326</v>
+        <v>0.631922</v>
       </c>
       <c r="P80" s="28" t="n"/>
       <c r="Q80" s="28" t="n">
-        <v>-0.043374</v>
+        <v>0.112691</v>
       </c>
       <c r="R80" s="26" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="S80" s="29" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="T80" s="24" t="inlineStr">
         <is>
@@ -23644,7 +23740,7 @@
       <c r="AD80" s="24" t="n"/>
       <c r="AE80" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-lol-tlnp-jl-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.5200 (market_slug=aec-lol-gmb-zena-2026-08-06).</t>
         </is>
       </c>
       <c r="AF80" s="31" t="inlineStr">
@@ -23662,7 +23758,7 @@
       <c r="AJ80" s="31" t="n"/>
       <c r="AK80" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL80" s="26" t="n">
@@ -23670,47 +23766,47 @@
       </c>
       <c r="AM80" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN80" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO80" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP80" s="24" t="inlineStr">
         <is>
-          <t>Joblife</t>
+          <t>Zena Esports</t>
         </is>
       </c>
       <c r="AQ80" s="24" t="inlineStr">
         <is>
-          <t>Joblife</t>
+          <t>Zena Esports</t>
         </is>
       </c>
       <c r="AR80" s="24" t="inlineStr">
         <is>
-          <t>Joblife</t>
+          <t>Zena Esports</t>
         </is>
       </c>
       <c r="AS80" s="24" t="inlineStr">
         <is>
-          <t>TLN Pirates</t>
+          <t>GMBLERS ESPORTS</t>
         </is>
       </c>
       <c r="AT80" s="24" t="inlineStr">
         <is>
-          <t>TLN Pirates</t>
+          <t>GMBLERS ESPORTS</t>
         </is>
       </c>
       <c r="AU80" s="24" t="inlineStr">
         <is>
-          <t>TLN Pirates</t>
+          <t>GMBLERS ESPORTS</t>
         </is>
       </c>
       <c r="AV80" s="24" t="n"/>
@@ -23728,7 +23824,7 @@
       </c>
       <c r="BA80" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BB80" s="24" t="inlineStr">
@@ -23743,7 +23839,7 @@
       </c>
       <c r="BD80" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BE80" s="24" t="inlineStr">
@@ -23763,7 +23859,7 @@
       </c>
       <c r="BH80" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:02.718244Z</t>
+          <t>2026-08-05T13:56:39.588429Z</t>
         </is>
       </c>
       <c r="BI80" s="24" t="inlineStr">
@@ -23773,13 +23869,13 @@
       </c>
       <c r="BJ80" s="25" t="n"/>
       <c r="BK80" s="26" t="n">
-        <v>-233</v>
+        <v>-108</v>
       </c>
       <c r="BL80" s="27" t="n">
-        <v>1.429185</v>
+        <v>1.925926</v>
       </c>
       <c r="BM80" s="28" t="n">
-        <v>0.6997</v>
+        <v>0.519231</v>
       </c>
       <c r="BN80" s="28" t="n"/>
       <c r="BO80" s="28" t="n"/>
@@ -23814,29 +23910,29 @@
       <c r="CR80" s="24" t="n"/>
       <c r="CS80" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="81" ht="36" customHeight="1">
       <c r="A81" s="24" t="inlineStr">
         <is>
-          <t>b5ae145033d940fd</t>
+          <t>b05ee965656b45c2</t>
         </is>
       </c>
       <c r="B81" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:12.089327Z</t>
+          <t>2026-08-05T13:56:43.896254Z</t>
         </is>
       </c>
       <c r="C81" s="24" t="inlineStr">
         <is>
-          <t>2026-08-06T18:00:00Z</t>
+          <t>2026-08-06T18:30:00Z</t>
         </is>
       </c>
       <c r="D81" s="24" t="inlineStr">
         <is>
-          <t>70902</t>
+          <t>70944</t>
         </is>
       </c>
       <c r="E81" s="24" t="inlineStr">
@@ -23846,12 +23942,12 @@
       </c>
       <c r="F81" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Croatian Flair x RLX </t>
+          <t>GnG Amazigh</t>
         </is>
       </c>
       <c r="G81" s="24" t="inlineStr">
         <is>
-          <t>SPIKE Syndicate</t>
+          <t>3BL Esports</t>
         </is>
       </c>
       <c r="H81" s="24" t="inlineStr">
@@ -23861,7 +23957,7 @@
       </c>
       <c r="I81" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J81" s="25" t="n"/>
@@ -23871,23 +23967,23 @@
         </is>
       </c>
       <c r="L81" s="26" t="n">
-        <v>133</v>
+        <v>100</v>
       </c>
       <c r="M81" s="27" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="N81" s="28" t="n">
-        <v>0.429185</v>
+        <v>0.5</v>
       </c>
       <c r="O81" s="28" t="n">
-        <v>0.509947</v>
+        <v>0.503829</v>
       </c>
       <c r="P81" s="28" t="n"/>
       <c r="Q81" s="28" t="n">
-        <v>0.080762</v>
+        <v>0.003829</v>
       </c>
       <c r="R81" s="26" t="n">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="S81" s="29" t="n">
         <v>1</v>
@@ -23913,7 +24009,7 @@
       <c r="AD81" s="24" t="n"/>
       <c r="AE81" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4300 (market_slug=aec-lol-spk-cfxr-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.5000 (market_slug=aec-lol-3bl-gng-2026-08-06).</t>
         </is>
       </c>
       <c r="AF81" s="31" t="inlineStr">
@@ -23954,32 +24050,32 @@
       </c>
       <c r="AP81" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Croatian Flair x RLX </t>
+          <t>GnG Amazigh</t>
         </is>
       </c>
       <c r="AQ81" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Croatian Flair x RLX </t>
+          <t>GnG Amazigh</t>
         </is>
       </c>
       <c r="AR81" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Croatian Flair x RLX </t>
+          <t>GnG Amazigh</t>
         </is>
       </c>
       <c r="AS81" s="24" t="inlineStr">
         <is>
-          <t>SPIKE Syndicate</t>
+          <t>3BL Esports</t>
         </is>
       </c>
       <c r="AT81" s="24" t="inlineStr">
         <is>
-          <t>SPIKE Syndicate</t>
+          <t>3BL Esports</t>
         </is>
       </c>
       <c r="AU81" s="24" t="inlineStr">
         <is>
-          <t>SPIKE Syndicate</t>
+          <t>3BL Esports</t>
         </is>
       </c>
       <c r="AV81" s="24" t="n"/>
@@ -23997,7 +24093,7 @@
       </c>
       <c r="BA81" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BB81" s="24" t="inlineStr">
@@ -24012,7 +24108,7 @@
       </c>
       <c r="BD81" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BE81" s="24" t="inlineStr">
@@ -24032,7 +24128,7 @@
       </c>
       <c r="BH81" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:04.589090Z</t>
+          <t>2026-08-05T13:56:40.648836Z</t>
         </is>
       </c>
       <c r="BI81" s="24" t="inlineStr">
@@ -24042,13 +24138,13 @@
       </c>
       <c r="BJ81" s="25" t="n"/>
       <c r="BK81" s="26" t="n">
-        <v>133</v>
+        <v>100</v>
       </c>
       <c r="BL81" s="27" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="BM81" s="28" t="n">
-        <v>0.429185</v>
+        <v>0.5</v>
       </c>
       <c r="BN81" s="28" t="n"/>
       <c r="BO81" s="28" t="n"/>
@@ -24090,22 +24186,22 @@
     <row r="82" ht="36" customHeight="1">
       <c r="A82" s="24" t="inlineStr">
         <is>
-          <t>caba8c05b0ae47cd</t>
+          <t>78bb5d658f3e43ec</t>
         </is>
       </c>
       <c r="B82" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:12.089327Z</t>
+          <t>2026-08-05T13:56:43.896254Z</t>
         </is>
       </c>
       <c r="C82" s="24" t="inlineStr">
         <is>
-          <t>2026-08-06T18:00:00Z</t>
+          <t>2026-08-06T19:00:00Z</t>
         </is>
       </c>
       <c r="D82" s="24" t="inlineStr">
         <is>
-          <t>70903</t>
+          <t>71181</t>
         </is>
       </c>
       <c r="E82" s="24" t="inlineStr">
@@ -24115,12 +24211,12 @@
       </c>
       <c r="F82" s="24" t="inlineStr">
         <is>
-          <t>Zena Esports</t>
+          <t>Galions</t>
         </is>
       </c>
       <c r="G82" s="24" t="inlineStr">
         <is>
-          <t>GMBLERS ESPORTS</t>
+          <t>Solary</t>
         </is>
       </c>
       <c r="H82" s="24" t="inlineStr">
@@ -24130,7 +24226,7 @@
       </c>
       <c r="I82" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J82" s="25" t="n"/>
@@ -24140,26 +24236,26 @@
         </is>
       </c>
       <c r="L82" s="26" t="n">
-        <v>-150</v>
+        <v>-127</v>
       </c>
       <c r="M82" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.787402</v>
       </c>
       <c r="N82" s="28" t="n">
-        <v>0.6</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="O82" s="28" t="n">
-        <v>0.632681</v>
+        <v>0.513031</v>
       </c>
       <c r="P82" s="28" t="n"/>
       <c r="Q82" s="28" t="n">
-        <v>0.032681</v>
+        <v>-0.04644</v>
       </c>
       <c r="R82" s="26" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="S82" s="29" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="T82" s="24" t="inlineStr">
         <is>
@@ -24182,7 +24278,7 @@
       <c r="AD82" s="24" t="n"/>
       <c r="AE82" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-lol-gmb-zena-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-lol-sly-gal-2026-08-06).</t>
         </is>
       </c>
       <c r="AF82" s="31" t="inlineStr">
@@ -24200,7 +24296,7 @@
       <c r="AJ82" s="31" t="n"/>
       <c r="AK82" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL82" s="26" t="n">
@@ -24208,47 +24304,47 @@
       </c>
       <c r="AM82" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN82" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO82" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP82" s="24" t="inlineStr">
         <is>
-          <t>Zena Esports</t>
+          <t>Galions</t>
         </is>
       </c>
       <c r="AQ82" s="24" t="inlineStr">
         <is>
-          <t>Zena Esports</t>
+          <t>Galions</t>
         </is>
       </c>
       <c r="AR82" s="24" t="inlineStr">
         <is>
-          <t>Zena Esports</t>
+          <t>Galions</t>
         </is>
       </c>
       <c r="AS82" s="24" t="inlineStr">
         <is>
-          <t>GMBLERS ESPORTS</t>
+          <t>Solary</t>
         </is>
       </c>
       <c r="AT82" s="24" t="inlineStr">
         <is>
-          <t>GMBLERS ESPORTS</t>
+          <t>Solary</t>
         </is>
       </c>
       <c r="AU82" s="24" t="inlineStr">
         <is>
-          <t>GMBLERS ESPORTS</t>
+          <t>Solary</t>
         </is>
       </c>
       <c r="AV82" s="24" t="n"/>
@@ -24266,7 +24362,7 @@
       </c>
       <c r="BA82" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BB82" s="24" t="inlineStr">
@@ -24281,7 +24377,7 @@
       </c>
       <c r="BD82" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BE82" s="24" t="inlineStr">
@@ -24301,7 +24397,7 @@
       </c>
       <c r="BH82" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:05.384864Z</t>
+          <t>2026-08-05T13:56:41.196285Z</t>
         </is>
       </c>
       <c r="BI82" s="24" t="inlineStr">
@@ -24311,13 +24407,13 @@
       </c>
       <c r="BJ82" s="25" t="n"/>
       <c r="BK82" s="26" t="n">
-        <v>-150</v>
+        <v>-127</v>
       </c>
       <c r="BL82" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.787402</v>
       </c>
       <c r="BM82" s="28" t="n">
-        <v>0.6</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="BN82" s="28" t="n"/>
       <c r="BO82" s="28" t="n"/>
@@ -24352,29 +24448,29 @@
       <c r="CR82" s="24" t="n"/>
       <c r="CS82" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="83" ht="36" customHeight="1">
       <c r="A83" s="24" t="inlineStr">
         <is>
-          <t>8356d78133244efd</t>
+          <t>3c4d4088ba1f4c0d</t>
         </is>
       </c>
       <c r="B83" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:12.089327Z</t>
+          <t>2026-08-05T13:56:43.896254Z</t>
         </is>
       </c>
       <c r="C83" s="24" t="inlineStr">
         <is>
-          <t>2026-08-06T18:30:00Z</t>
+          <t>2026-08-06T20:00:00Z</t>
         </is>
       </c>
       <c r="D83" s="24" t="inlineStr">
         <is>
-          <t>70944</t>
+          <t>71214</t>
         </is>
       </c>
       <c r="E83" s="24" t="inlineStr">
@@ -24384,12 +24480,12 @@
       </c>
       <c r="F83" s="24" t="inlineStr">
         <is>
-          <t>GnG Amazigh</t>
+          <t>Vitality.Bee</t>
         </is>
       </c>
       <c r="G83" s="24" t="inlineStr">
         <is>
-          <t>3BL Esports</t>
+          <t>ZYB Esport</t>
         </is>
       </c>
       <c r="H83" s="24" t="inlineStr">
@@ -24399,7 +24495,7 @@
       </c>
       <c r="I83" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J83" s="25" t="n"/>
@@ -24409,26 +24505,26 @@
         </is>
       </c>
       <c r="L83" s="26" t="n">
-        <v>108</v>
+        <v>-127</v>
       </c>
       <c r="M83" s="27" t="n">
-        <v>2.08</v>
+        <v>1.787402</v>
       </c>
       <c r="N83" s="28" t="n">
-        <v>0.480769</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="O83" s="28" t="n">
-        <v>0.5040289999999999</v>
+        <v>0.638828</v>
       </c>
       <c r="P83" s="28" t="n"/>
       <c r="Q83" s="28" t="n">
-        <v>0.02326</v>
+        <v>0.079357</v>
       </c>
       <c r="R83" s="26" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="S83" s="29" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="T83" s="24" t="inlineStr">
         <is>
@@ -24451,7 +24547,7 @@
       <c r="AD83" s="24" t="n"/>
       <c r="AE83" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4800 (market_slug=aec-lol-3bl-gng-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-lol-zyb-vitb-2026-08-06).</t>
         </is>
       </c>
       <c r="AF83" s="31" t="inlineStr">
@@ -24469,7 +24565,7 @@
       <c r="AJ83" s="31" t="n"/>
       <c r="AK83" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL83" s="26" t="n">
@@ -24477,47 +24573,47 @@
       </c>
       <c r="AM83" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN83" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO83" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP83" s="24" t="inlineStr">
         <is>
-          <t>GnG Amazigh</t>
+          <t>Vitality.Bee</t>
         </is>
       </c>
       <c r="AQ83" s="24" t="inlineStr">
         <is>
-          <t>GnG Amazigh</t>
+          <t>Vitality.Bee</t>
         </is>
       </c>
       <c r="AR83" s="24" t="inlineStr">
         <is>
-          <t>GnG Amazigh</t>
+          <t>Vitality.Bee</t>
         </is>
       </c>
       <c r="AS83" s="24" t="inlineStr">
         <is>
-          <t>3BL Esports</t>
+          <t>ZYB Esport</t>
         </is>
       </c>
       <c r="AT83" s="24" t="inlineStr">
         <is>
-          <t>3BL Esports</t>
+          <t>ZYB Esport</t>
         </is>
       </c>
       <c r="AU83" s="24" t="inlineStr">
         <is>
-          <t>3BL Esports</t>
+          <t>ZYB Esport</t>
         </is>
       </c>
       <c r="AV83" s="24" t="n"/>
@@ -24535,7 +24631,7 @@
       </c>
       <c r="BA83" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BB83" s="24" t="inlineStr">
@@ -24550,7 +24646,7 @@
       </c>
       <c r="BD83" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BE83" s="24" t="inlineStr">
@@ -24570,7 +24666,7 @@
       </c>
       <c r="BH83" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:06.971695Z</t>
+          <t>2026-08-05T13:56:42.235304Z</t>
         </is>
       </c>
       <c r="BI83" s="24" t="inlineStr">
@@ -24580,13 +24676,13 @@
       </c>
       <c r="BJ83" s="25" t="n"/>
       <c r="BK83" s="26" t="n">
-        <v>108</v>
+        <v>-127</v>
       </c>
       <c r="BL83" s="27" t="n">
-        <v>2.08</v>
+        <v>1.787402</v>
       </c>
       <c r="BM83" s="28" t="n">
-        <v>0.480769</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="BN83" s="28" t="n"/>
       <c r="BO83" s="28" t="n"/>
@@ -24628,22 +24724,22 @@
     <row r="84" ht="36" customHeight="1">
       <c r="A84" s="24" t="inlineStr">
         <is>
-          <t>96bb77843eb44c7b</t>
+          <t>0dea460519894e1a</t>
         </is>
       </c>
       <c r="B84" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:12.089327Z</t>
+          <t>2026-08-05T13:56:43.896254Z</t>
         </is>
       </c>
       <c r="C84" s="24" t="inlineStr">
         <is>
-          <t>2026-08-06T19:00:00Z</t>
+          <t>2026-08-06T21:00:00Z</t>
         </is>
       </c>
       <c r="D84" s="24" t="inlineStr">
         <is>
-          <t>71181</t>
+          <t>71313</t>
         </is>
       </c>
       <c r="E84" s="24" t="inlineStr">
@@ -24653,12 +24749,12 @@
       </c>
       <c r="F84" s="24" t="inlineStr">
         <is>
-          <t>Galions</t>
+          <t>Panelão LHC</t>
         </is>
       </c>
       <c r="G84" s="24" t="inlineStr">
         <is>
-          <t>Solary</t>
+          <t>Tung Tung Bogi</t>
         </is>
       </c>
       <c r="H84" s="24" t="inlineStr">
@@ -24668,7 +24764,7 @@
       </c>
       <c r="I84" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J84" s="25" t="n"/>
@@ -24678,20 +24774,20 @@
         </is>
       </c>
       <c r="L84" s="26" t="n">
-        <v>-127</v>
+        <v>-156</v>
       </c>
       <c r="M84" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.641026</v>
       </c>
       <c r="N84" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.609375</v>
       </c>
       <c r="O84" s="28" t="n">
-        <v>0.512894</v>
+        <v>0.502932</v>
       </c>
       <c r="P84" s="28" t="n"/>
       <c r="Q84" s="28" t="n">
-        <v>-0.046577</v>
+        <v>-0.106443</v>
       </c>
       <c r="R84" s="26" t="n">
         <v>0</v>
@@ -24720,7 +24816,7 @@
       <c r="AD84" s="24" t="n"/>
       <c r="AE84" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-lol-sly-gal-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-lol-tung-pane-2026-08-06).</t>
         </is>
       </c>
       <c r="AF84" s="31" t="inlineStr">
@@ -24761,32 +24857,32 @@
       </c>
       <c r="AP84" s="24" t="inlineStr">
         <is>
-          <t>Galions</t>
+          <t>Panelão LHC</t>
         </is>
       </c>
       <c r="AQ84" s="24" t="inlineStr">
         <is>
-          <t>Galions</t>
+          <t>Panelão LHC</t>
         </is>
       </c>
       <c r="AR84" s="24" t="inlineStr">
         <is>
-          <t>Galions</t>
+          <t>Panelão LHC</t>
         </is>
       </c>
       <c r="AS84" s="24" t="inlineStr">
         <is>
-          <t>Solary</t>
+          <t>Tung Tung Bogi</t>
         </is>
       </c>
       <c r="AT84" s="24" t="inlineStr">
         <is>
-          <t>Solary</t>
+          <t>Tung Tung Bogi</t>
         </is>
       </c>
       <c r="AU84" s="24" t="inlineStr">
         <is>
-          <t>Solary</t>
+          <t>Tung Tung Bogi</t>
         </is>
       </c>
       <c r="AV84" s="24" t="n"/>
@@ -24804,7 +24900,7 @@
       </c>
       <c r="BA84" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BB84" s="24" t="inlineStr">
@@ -24819,7 +24915,7 @@
       </c>
       <c r="BD84" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BE84" s="24" t="inlineStr">
@@ -24839,7 +24935,7 @@
       </c>
       <c r="BH84" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:07.828700Z</t>
+          <t>2026-08-05T13:56:42.849817Z</t>
         </is>
       </c>
       <c r="BI84" s="24" t="inlineStr">
@@ -24849,13 +24945,13 @@
       </c>
       <c r="BJ84" s="25" t="n"/>
       <c r="BK84" s="26" t="n">
-        <v>-127</v>
+        <v>-156</v>
       </c>
       <c r="BL84" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.641026</v>
       </c>
       <c r="BM84" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.609375</v>
       </c>
       <c r="BN84" s="28" t="n"/>
       <c r="BO84" s="28" t="n"/>
@@ -24897,22 +24993,22 @@
     <row r="85" ht="36" customHeight="1">
       <c r="A85" s="24" t="inlineStr">
         <is>
-          <t>b772564a2f00435f</t>
+          <t>1e8fd46f19714faa</t>
         </is>
       </c>
       <c r="B85" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:12.089327Z</t>
+          <t>2026-08-05T13:56:43.896254Z</t>
         </is>
       </c>
       <c r="C85" s="24" t="inlineStr">
         <is>
-          <t>2026-08-06T20:00:00Z</t>
+          <t>2026-08-06T21:00:00Z</t>
         </is>
       </c>
       <c r="D85" s="24" t="inlineStr">
         <is>
-          <t>71214</t>
+          <t>71314</t>
         </is>
       </c>
       <c r="E85" s="24" t="inlineStr">
@@ -24922,12 +25018,12 @@
       </c>
       <c r="F85" s="24" t="inlineStr">
         <is>
-          <t>Vitality.Bee</t>
+          <t>CCG Esports</t>
         </is>
       </c>
       <c r="G85" s="24" t="inlineStr">
         <is>
-          <t>ZYB Esport</t>
+          <t>Maryville University</t>
         </is>
       </c>
       <c r="H85" s="24" t="inlineStr">
@@ -24937,7 +25033,7 @@
       </c>
       <c r="I85" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J85" s="25" t="n"/>
@@ -24947,26 +25043,26 @@
         </is>
       </c>
       <c r="L85" s="26" t="n">
-        <v>-127</v>
+        <v>-133</v>
       </c>
       <c r="M85" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.75188</v>
       </c>
       <c r="N85" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.570815</v>
       </c>
       <c r="O85" s="28" t="n">
-        <v>0.639259</v>
+        <v>0.558487</v>
       </c>
       <c r="P85" s="28" t="n"/>
       <c r="Q85" s="28" t="n">
-        <v>0.079788</v>
+        <v>-0.012328</v>
       </c>
       <c r="R85" s="26" t="n">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="S85" s="29" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="T85" s="24" t="inlineStr">
         <is>
@@ -24989,7 +25085,7 @@
       <c r="AD85" s="24" t="n"/>
       <c r="AE85" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-lol-zyb-vitb-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-lol-mvu-ccg-2026-08-06).</t>
         </is>
       </c>
       <c r="AF85" s="31" t="inlineStr">
@@ -25007,7 +25103,7 @@
       <c r="AJ85" s="31" t="n"/>
       <c r="AK85" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL85" s="26" t="n">
@@ -25015,47 +25111,47 @@
       </c>
       <c r="AM85" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN85" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO85" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP85" s="24" t="inlineStr">
         <is>
-          <t>Vitality.Bee</t>
+          <t>CCG Esports</t>
         </is>
       </c>
       <c r="AQ85" s="24" t="inlineStr">
         <is>
-          <t>Vitality.Bee</t>
+          <t>CCG Esports</t>
         </is>
       </c>
       <c r="AR85" s="24" t="inlineStr">
         <is>
-          <t>Vitality.Bee</t>
+          <t>CCG Esports</t>
         </is>
       </c>
       <c r="AS85" s="24" t="inlineStr">
         <is>
-          <t>ZYB Esport</t>
+          <t>Maryville University</t>
         </is>
       </c>
       <c r="AT85" s="24" t="inlineStr">
         <is>
-          <t>ZYB Esport</t>
+          <t>Maryville University</t>
         </is>
       </c>
       <c r="AU85" s="24" t="inlineStr">
         <is>
-          <t>ZYB Esport</t>
+          <t>Maryville University</t>
         </is>
       </c>
       <c r="AV85" s="24" t="n"/>
@@ -25073,7 +25169,7 @@
       </c>
       <c r="BA85" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BB85" s="24" t="inlineStr">
@@ -25088,7 +25184,7 @@
       </c>
       <c r="BD85" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BE85" s="24" t="inlineStr">
@@ -25108,7 +25204,7 @@
       </c>
       <c r="BH85" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:09.483653Z</t>
+          <t>2026-08-05T13:56:43.373932Z</t>
         </is>
       </c>
       <c r="BI85" s="24" t="inlineStr">
@@ -25118,13 +25214,13 @@
       </c>
       <c r="BJ85" s="25" t="n"/>
       <c r="BK85" s="26" t="n">
-        <v>-127</v>
+        <v>-133</v>
       </c>
       <c r="BL85" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.75188</v>
       </c>
       <c r="BM85" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.570815</v>
       </c>
       <c r="BN85" s="28" t="n"/>
       <c r="BO85" s="28" t="n"/>
@@ -25159,29 +25255,29 @@
       <c r="CR85" s="24" t="n"/>
       <c r="CS85" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="86" ht="36" customHeight="1">
       <c r="A86" s="24" t="inlineStr">
         <is>
-          <t>f22c033d55f24c2b</t>
+          <t>10b0058b288e4618</t>
         </is>
       </c>
       <c r="B86" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:12.089327Z</t>
+          <t>2026-08-05T13:56:43.896254Z</t>
         </is>
       </c>
       <c r="C86" s="24" t="inlineStr">
         <is>
-          <t>2026-08-06T21:00:00Z</t>
+          <t>2026-08-07T00:00:00Z</t>
         </is>
       </c>
       <c r="D86" s="24" t="inlineStr">
         <is>
-          <t>71313</t>
+          <t>71538</t>
         </is>
       </c>
       <c r="E86" s="24" t="inlineStr">
@@ -25191,12 +25287,12 @@
       </c>
       <c r="F86" s="24" t="inlineStr">
         <is>
-          <t>Panelão LHC</t>
+          <t>Contingent Esports</t>
         </is>
       </c>
       <c r="G86" s="24" t="inlineStr">
         <is>
-          <t>Tung Tung Bogi</t>
+          <t>Conviction</t>
         </is>
       </c>
       <c r="H86" s="24" t="inlineStr">
@@ -25216,20 +25312,20 @@
         </is>
       </c>
       <c r="L86" s="26" t="n">
-        <v>-194</v>
+        <v>-213</v>
       </c>
       <c r="M86" s="27" t="n">
-        <v>1.515464</v>
+        <v>1.469484</v>
       </c>
       <c r="N86" s="28" t="n">
-        <v>0.659864</v>
+        <v>0.680511</v>
       </c>
       <c r="O86" s="28" t="n">
-        <v>0.5030559999999999</v>
+        <v>0.513663</v>
       </c>
       <c r="P86" s="28" t="n"/>
       <c r="Q86" s="28" t="n">
-        <v>-0.156808</v>
+        <v>-0.166848</v>
       </c>
       <c r="R86" s="26" t="n">
         <v>0</v>
@@ -25258,7 +25354,7 @@
       <c r="AD86" s="24" t="n"/>
       <c r="AE86" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6600 (market_slug=aec-lol-tung-pane-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-lol-cnv-cont-2026-08-07).</t>
         </is>
       </c>
       <c r="AF86" s="31" t="inlineStr">
@@ -25299,32 +25395,32 @@
       </c>
       <c r="AP86" s="24" t="inlineStr">
         <is>
-          <t>Panelão LHC</t>
+          <t>Contingent Esports</t>
         </is>
       </c>
       <c r="AQ86" s="24" t="inlineStr">
         <is>
-          <t>Panelão LHC</t>
+          <t>Contingent Esports</t>
         </is>
       </c>
       <c r="AR86" s="24" t="inlineStr">
         <is>
-          <t>Panelão LHC</t>
+          <t>Contingent Esports</t>
         </is>
       </c>
       <c r="AS86" s="24" t="inlineStr">
         <is>
-          <t>Tung Tung Bogi</t>
+          <t>Conviction</t>
         </is>
       </c>
       <c r="AT86" s="24" t="inlineStr">
         <is>
-          <t>Tung Tung Bogi</t>
+          <t>Conviction</t>
         </is>
       </c>
       <c r="AU86" s="24" t="inlineStr">
         <is>
-          <t>Tung Tung Bogi</t>
+          <t>Conviction</t>
         </is>
       </c>
       <c r="AV86" s="24" t="n"/>
@@ -25342,7 +25438,7 @@
       </c>
       <c r="BA86" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BB86" s="24" t="inlineStr">
@@ -25357,7 +25453,7 @@
       </c>
       <c r="BD86" s="24" t="inlineStr">
         <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
+          <t>3b2b7fa569f62411a6dc2753c695e98717a67f225e8074aac963d117b250c28b</t>
         </is>
       </c>
       <c r="BE86" s="24" t="inlineStr">
@@ -25377,7 +25473,7 @@
       </c>
       <c r="BH86" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:10.277618Z</t>
+          <t>2026-08-05T13:56:43.895788Z</t>
         </is>
       </c>
       <c r="BI86" s="24" t="inlineStr">
@@ -25387,13 +25483,13 @@
       </c>
       <c r="BJ86" s="25" t="n"/>
       <c r="BK86" s="26" t="n">
-        <v>-194</v>
+        <v>-213</v>
       </c>
       <c r="BL86" s="27" t="n">
-        <v>1.515464</v>
+        <v>1.469484</v>
       </c>
       <c r="BM86" s="28" t="n">
-        <v>0.659864</v>
+        <v>0.680511</v>
       </c>
       <c r="BN86" s="28" t="n"/>
       <c r="BO86" s="28" t="n"/>
@@ -25432,544 +25528,6 @@
         </is>
       </c>
     </row>
-    <row r="87" ht="36" customHeight="1">
-      <c r="A87" s="24" t="inlineStr">
-        <is>
-          <t>c6d5891f5b9148fd</t>
-        </is>
-      </c>
-      <c r="B87" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T04:39:12.089327Z</t>
-        </is>
-      </c>
-      <c r="C87" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-06T21:00:00Z</t>
-        </is>
-      </c>
-      <c r="D87" s="24" t="inlineStr">
-        <is>
-          <t>71314</t>
-        </is>
-      </c>
-      <c r="E87" s="24" t="inlineStr">
-        <is>
-          <t>LOL</t>
-        </is>
-      </c>
-      <c r="F87" s="24" t="inlineStr">
-        <is>
-          <t>CCG Esports</t>
-        </is>
-      </c>
-      <c r="G87" s="24" t="inlineStr">
-        <is>
-          <t>Maryville University</t>
-        </is>
-      </c>
-      <c r="H87" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I87" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J87" s="25" t="n"/>
-      <c r="K87" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L87" s="26" t="n">
-        <v>-133</v>
-      </c>
-      <c r="M87" s="27" t="n">
-        <v>1.75188</v>
-      </c>
-      <c r="N87" s="28" t="n">
-        <v>0.570815</v>
-      </c>
-      <c r="O87" s="28" t="n">
-        <v>0.558957</v>
-      </c>
-      <c r="P87" s="28" t="n"/>
-      <c r="Q87" s="28" t="n">
-        <v>-0.011858</v>
-      </c>
-      <c r="R87" s="26" t="n">
-        <v>14</v>
-      </c>
-      <c r="S87" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T87" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v6</t>
-        </is>
-      </c>
-      <c r="U87" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V87" s="24" t="n"/>
-      <c r="W87" s="26" t="n"/>
-      <c r="X87" s="26" t="n"/>
-      <c r="Y87" s="25" t="n"/>
-      <c r="Z87" s="26" t="n"/>
-      <c r="AA87" s="28" t="n"/>
-      <c r="AB87" s="28" t="n"/>
-      <c r="AC87" s="30" t="n"/>
-      <c r="AD87" s="24" t="n"/>
-      <c r="AE87" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-lol-mvu-ccg-2026-08-06).</t>
-        </is>
-      </c>
-      <c r="AF87" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG87" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH87" s="24" t="n"/>
-      <c r="AI87" s="31" t="n"/>
-      <c r="AJ87" s="31" t="n"/>
-      <c r="AK87" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL87" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM87" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN87" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO87" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP87" s="24" t="inlineStr">
-        <is>
-          <t>CCG Esports</t>
-        </is>
-      </c>
-      <c r="AQ87" s="24" t="inlineStr">
-        <is>
-          <t>CCG Esports</t>
-        </is>
-      </c>
-      <c r="AR87" s="24" t="inlineStr">
-        <is>
-          <t>CCG Esports</t>
-        </is>
-      </c>
-      <c r="AS87" s="24" t="inlineStr">
-        <is>
-          <t>Maryville University</t>
-        </is>
-      </c>
-      <c r="AT87" s="24" t="inlineStr">
-        <is>
-          <t>Maryville University</t>
-        </is>
-      </c>
-      <c r="AU87" s="24" t="inlineStr">
-        <is>
-          <t>Maryville University</t>
-        </is>
-      </c>
-      <c r="AV87" s="24" t="n"/>
-      <c r="AW87" s="24" t="n"/>
-      <c r="AX87" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY87" s="24" t="n"/>
-      <c r="AZ87" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA87" s="24" t="inlineStr">
-        <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
-        </is>
-      </c>
-      <c r="BB87" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC87" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v6</t>
-        </is>
-      </c>
-      <c r="BD87" s="24" t="inlineStr">
-        <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
-        </is>
-      </c>
-      <c r="BE87" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF87" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG87" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v6</t>
-        </is>
-      </c>
-      <c r="BH87" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T04:39:11.278172Z</t>
-        </is>
-      </c>
-      <c r="BI87" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ87" s="25" t="n"/>
-      <c r="BK87" s="26" t="n">
-        <v>-133</v>
-      </c>
-      <c r="BL87" s="27" t="n">
-        <v>1.75188</v>
-      </c>
-      <c r="BM87" s="28" t="n">
-        <v>0.570815</v>
-      </c>
-      <c r="BN87" s="28" t="n"/>
-      <c r="BO87" s="28" t="n"/>
-      <c r="BP87" s="25" t="n"/>
-      <c r="BQ87" s="27" t="n"/>
-      <c r="BR87" s="28" t="n"/>
-      <c r="BS87" s="28" t="n"/>
-      <c r="BT87" s="28" t="n"/>
-      <c r="BU87" s="25" t="n"/>
-      <c r="BV87" s="29" t="n"/>
-      <c r="BW87" s="24" t="n"/>
-      <c r="BX87" s="30" t="n"/>
-      <c r="BY87" s="27" t="n"/>
-      <c r="BZ87" s="24" t="n"/>
-      <c r="CA87" s="31" t="n"/>
-      <c r="CB87" s="24" t="n"/>
-      <c r="CC87" s="24" t="n"/>
-      <c r="CD87" s="24" t="n"/>
-      <c r="CE87" s="24" t="n"/>
-      <c r="CF87" s="24" t="n"/>
-      <c r="CG87" s="24" t="n"/>
-      <c r="CH87" s="24" t="n"/>
-      <c r="CI87" s="24" t="n"/>
-      <c r="CJ87" s="24" t="n"/>
-      <c r="CK87" s="24" t="n"/>
-      <c r="CL87" s="24" t="n"/>
-      <c r="CM87" s="24" t="n"/>
-      <c r="CN87" s="24" t="n"/>
-      <c r="CO87" s="24" t="n"/>
-      <c r="CP87" s="24" t="n"/>
-      <c r="CQ87" s="24" t="n"/>
-      <c r="CR87" s="24" t="n"/>
-      <c r="CS87" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="36" customHeight="1">
-      <c r="A88" s="24" t="inlineStr">
-        <is>
-          <t>eb29512ccac842bf</t>
-        </is>
-      </c>
-      <c r="B88" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T04:39:12.089327Z</t>
-        </is>
-      </c>
-      <c r="C88" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-07T00:00:00Z</t>
-        </is>
-      </c>
-      <c r="D88" s="24" t="inlineStr">
-        <is>
-          <t>71538</t>
-        </is>
-      </c>
-      <c r="E88" s="24" t="inlineStr">
-        <is>
-          <t>LOL</t>
-        </is>
-      </c>
-      <c r="F88" s="24" t="inlineStr">
-        <is>
-          <t>Contingent Esports</t>
-        </is>
-      </c>
-      <c r="G88" s="24" t="inlineStr">
-        <is>
-          <t>Conviction</t>
-        </is>
-      </c>
-      <c r="H88" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I88" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J88" s="25" t="n"/>
-      <c r="K88" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L88" s="26" t="n">
-        <v>-223</v>
-      </c>
-      <c r="M88" s="27" t="n">
-        <v>1.44843</v>
-      </c>
-      <c r="N88" s="28" t="n">
-        <v>0.690402</v>
-      </c>
-      <c r="O88" s="28" t="n">
-        <v>0.513826</v>
-      </c>
-      <c r="P88" s="28" t="n"/>
-      <c r="Q88" s="28" t="n">
-        <v>-0.176576</v>
-      </c>
-      <c r="R88" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S88" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T88" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v6</t>
-        </is>
-      </c>
-      <c r="U88" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V88" s="24" t="n"/>
-      <c r="W88" s="26" t="n"/>
-      <c r="X88" s="26" t="n"/>
-      <c r="Y88" s="25" t="n"/>
-      <c r="Z88" s="26" t="n"/>
-      <c r="AA88" s="28" t="n"/>
-      <c r="AB88" s="28" t="n"/>
-      <c r="AC88" s="30" t="n"/>
-      <c r="AD88" s="24" t="n"/>
-      <c r="AE88" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-lol-cnv-cont-2026-08-07).</t>
-        </is>
-      </c>
-      <c r="AF88" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG88" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH88" s="24" t="n"/>
-      <c r="AI88" s="31" t="n"/>
-      <c r="AJ88" s="31" t="n"/>
-      <c r="AK88" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL88" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM88" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN88" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO88" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP88" s="24" t="inlineStr">
-        <is>
-          <t>Contingent Esports</t>
-        </is>
-      </c>
-      <c r="AQ88" s="24" t="inlineStr">
-        <is>
-          <t>Contingent Esports</t>
-        </is>
-      </c>
-      <c r="AR88" s="24" t="inlineStr">
-        <is>
-          <t>Contingent Esports</t>
-        </is>
-      </c>
-      <c r="AS88" s="24" t="inlineStr">
-        <is>
-          <t>Conviction</t>
-        </is>
-      </c>
-      <c r="AT88" s="24" t="inlineStr">
-        <is>
-          <t>Conviction</t>
-        </is>
-      </c>
-      <c r="AU88" s="24" t="inlineStr">
-        <is>
-          <t>Conviction</t>
-        </is>
-      </c>
-      <c r="AV88" s="24" t="n"/>
-      <c r="AW88" s="24" t="n"/>
-      <c r="AX88" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY88" s="24" t="n"/>
-      <c r="AZ88" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA88" s="24" t="inlineStr">
-        <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
-        </is>
-      </c>
-      <c r="BB88" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC88" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v6</t>
-        </is>
-      </c>
-      <c r="BD88" s="24" t="inlineStr">
-        <is>
-          <t>9a8d5ad7f045de5eb1cb17aea82bbcf9812b40ca30a6256eba6436fea9a94482</t>
-        </is>
-      </c>
-      <c r="BE88" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF88" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG88" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v6</t>
-        </is>
-      </c>
-      <c r="BH88" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T04:39:12.088967Z</t>
-        </is>
-      </c>
-      <c r="BI88" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ88" s="25" t="n"/>
-      <c r="BK88" s="26" t="n">
-        <v>-223</v>
-      </c>
-      <c r="BL88" s="27" t="n">
-        <v>1.44843</v>
-      </c>
-      <c r="BM88" s="28" t="n">
-        <v>0.690402</v>
-      </c>
-      <c r="BN88" s="28" t="n"/>
-      <c r="BO88" s="28" t="n"/>
-      <c r="BP88" s="25" t="n"/>
-      <c r="BQ88" s="27" t="n"/>
-      <c r="BR88" s="28" t="n"/>
-      <c r="BS88" s="28" t="n"/>
-      <c r="BT88" s="28" t="n"/>
-      <c r="BU88" s="25" t="n"/>
-      <c r="BV88" s="29" t="n"/>
-      <c r="BW88" s="24" t="n"/>
-      <c r="BX88" s="30" t="n"/>
-      <c r="BY88" s="27" t="n"/>
-      <c r="BZ88" s="24" t="n"/>
-      <c r="CA88" s="31" t="n"/>
-      <c r="CB88" s="24" t="n"/>
-      <c r="CC88" s="24" t="n"/>
-      <c r="CD88" s="24" t="n"/>
-      <c r="CE88" s="24" t="n"/>
-      <c r="CF88" s="24" t="n"/>
-      <c r="CG88" s="24" t="n"/>
-      <c r="CH88" s="24" t="n"/>
-      <c r="CI88" s="24" t="n"/>
-      <c r="CJ88" s="24" t="n"/>
-      <c r="CK88" s="24" t="n"/>
-      <c r="CL88" s="24" t="n"/>
-      <c r="CM88" s="24" t="n"/>
-      <c r="CN88" s="24" t="n"/>
-      <c r="CO88" s="24" t="n"/>
-      <c r="CP88" s="24" t="n"/>
-      <c r="CQ88" s="24" t="n"/>
-      <c r="CR88" s="24" t="n"/>
-      <c r="CS88" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research/lol.xlsx
+++ b/data/research/lol.xlsx
@@ -27475,18 +27475,38 @@
       </c>
       <c r="U91" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V91" s="24" t="n"/>
-      <c r="W91" s="26" t="n"/>
-      <c r="X91" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V91" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W91" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X91" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y91" s="25" t="n"/>
-      <c r="Z91" s="26" t="n"/>
-      <c r="AA91" s="28" t="n"/>
-      <c r="AB91" s="28" t="n"/>
-      <c r="AC91" s="30" t="n"/>
-      <c r="AD91" s="24" t="n"/>
+      <c r="Z91" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="AA91" s="28" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AB91" s="28" t="n">
+        <v>0.00037</v>
+      </c>
+      <c r="AC91" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:27:13.780824Z</t>
+        </is>
+      </c>
       <c r="AE91" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-lol-shft-gx-2026-08-07).</t>
@@ -27629,8 +27649,12 @@
       <c r="BN91" s="28" t="n"/>
       <c r="BO91" s="28" t="n"/>
       <c r="BP91" s="25" t="n"/>
-      <c r="BQ91" s="27" t="n"/>
-      <c r="BR91" s="28" t="n"/>
+      <c r="BQ91" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="BR91" s="28" t="n">
+        <v>0.63</v>
+      </c>
       <c r="BS91" s="28" t="n"/>
       <c r="BT91" s="28" t="n"/>
       <c r="BU91" s="25" t="n"/>
@@ -27744,18 +27768,38 @@
       </c>
       <c r="U92" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V92" s="24" t="n"/>
-      <c r="W92" s="26" t="n"/>
-      <c r="X92" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V92" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W92" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X92" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y92" s="25" t="n"/>
-      <c r="Z92" s="26" t="n"/>
-      <c r="AA92" s="28" t="n"/>
-      <c r="AB92" s="28" t="n"/>
-      <c r="AC92" s="30" t="n"/>
-      <c r="AD92" s="24" t="n"/>
+      <c r="Z92" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="AA92" s="28" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AB92" s="28" t="n">
+        <v>0.000829</v>
+      </c>
+      <c r="AC92" s="30" t="n">
+        <v>1.2821</v>
+      </c>
+      <c r="AD92" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:27:16.469279Z</t>
+        </is>
+      </c>
       <c r="AE92" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-lol-aee-tts-2026-08-07).</t>
@@ -27898,8 +27942,12 @@
       <c r="BN92" s="28" t="n"/>
       <c r="BO92" s="28" t="n"/>
       <c r="BP92" s="25" t="n"/>
-      <c r="BQ92" s="27" t="n"/>
-      <c r="BR92" s="28" t="n"/>
+      <c r="BQ92" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="BR92" s="28" t="n">
+        <v>0.54</v>
+      </c>
       <c r="BS92" s="28" t="n"/>
       <c r="BT92" s="28" t="n"/>
       <c r="BU92" s="25" t="n"/>
@@ -27935,12 +27983,12 @@
     <row r="93" ht="36" customHeight="1">
       <c r="A93" s="24" t="inlineStr">
         <is>
-          <t>57b58f2735fc4d4c</t>
+          <t>861721ef7a3c4975</t>
         </is>
       </c>
       <c r="B93" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:24:10.407714Z</t>
+          <t>2026-08-07T18:31:20.691239Z</t>
         </is>
       </c>
       <c r="C93" s="24" t="inlineStr">
@@ -27994,11 +28042,11 @@
         <v>0.460829</v>
       </c>
       <c r="O93" s="28" t="n">
-        <v>0.576745</v>
+        <v>0.576862</v>
       </c>
       <c r="P93" s="28" t="n"/>
       <c r="Q93" s="28" t="n">
-        <v>0.115916</v>
+        <v>0.116033</v>
       </c>
       <c r="R93" s="26" t="n">
         <v>78</v>
@@ -28111,7 +28159,7 @@
       </c>
       <c r="BA93" s="24" t="inlineStr">
         <is>
-          <t>326a42c58f2a208dee1dc4f634e9901156f475883f7f16a3237a5e1b513fa5f9</t>
+          <t>d3791916ff32605dd2265e280637577dccc694ea8768ae90edb98370e9029821</t>
         </is>
       </c>
       <c r="BB93" s="24" t="inlineStr">
@@ -28126,7 +28174,7 @@
       </c>
       <c r="BD93" s="24" t="inlineStr">
         <is>
-          <t>326a42c58f2a208dee1dc4f634e9901156f475883f7f16a3237a5e1b513fa5f9</t>
+          <t>d3791916ff32605dd2265e280637577dccc694ea8768ae90edb98370e9029821</t>
         </is>
       </c>
       <c r="BE93" s="24" t="inlineStr">
@@ -28146,7 +28194,7 @@
       </c>
       <c r="BH93" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:23:56.287371Z</t>
+          <t>2026-08-07T18:31:07.695348Z</t>
         </is>
       </c>
       <c r="BI93" s="24" t="inlineStr">
@@ -28204,12 +28252,12 @@
     <row r="94" ht="36" customHeight="1">
       <c r="A94" s="24" t="inlineStr">
         <is>
-          <t>abb93a58f76046cb</t>
+          <t>caf03d09757343f2</t>
         </is>
       </c>
       <c r="B94" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:24:10.407714Z</t>
+          <t>2026-08-07T18:31:20.691239Z</t>
         </is>
       </c>
       <c r="C94" s="24" t="inlineStr">
@@ -28263,11 +28311,11 @@
         <v>0.480769</v>
       </c>
       <c r="O94" s="28" t="n">
-        <v>0.6956059999999999</v>
+        <v>0.695648</v>
       </c>
       <c r="P94" s="28" t="n"/>
       <c r="Q94" s="28" t="n">
-        <v>0.214837</v>
+        <v>0.214879</v>
       </c>
       <c r="R94" s="26" t="n">
         <v>100</v>
@@ -28380,7 +28428,7 @@
       </c>
       <c r="BA94" s="24" t="inlineStr">
         <is>
-          <t>326a42c58f2a208dee1dc4f634e9901156f475883f7f16a3237a5e1b513fa5f9</t>
+          <t>d3791916ff32605dd2265e280637577dccc694ea8768ae90edb98370e9029821</t>
         </is>
       </c>
       <c r="BB94" s="24" t="inlineStr">
@@ -28395,7 +28443,7 @@
       </c>
       <c r="BD94" s="24" t="inlineStr">
         <is>
-          <t>326a42c58f2a208dee1dc4f634e9901156f475883f7f16a3237a5e1b513fa5f9</t>
+          <t>d3791916ff32605dd2265e280637577dccc694ea8768ae90edb98370e9029821</t>
         </is>
       </c>
       <c r="BE94" s="24" t="inlineStr">
@@ -28415,7 +28463,7 @@
       </c>
       <c r="BH94" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:23:56.826662Z</t>
+          <t>2026-08-07T18:31:08.212012Z</t>
         </is>
       </c>
       <c r="BI94" s="24" t="inlineStr">
@@ -28473,12 +28521,12 @@
     <row r="95" ht="36" customHeight="1">
       <c r="A95" s="24" t="inlineStr">
         <is>
-          <t>ead4dfd717d04d85</t>
+          <t>a594ede30371457f</t>
         </is>
       </c>
       <c r="B95" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:24:10.407714Z</t>
+          <t>2026-08-07T18:31:20.691239Z</t>
         </is>
       </c>
       <c r="C95" s="24" t="inlineStr">
@@ -28532,11 +28580,11 @@
         <v>0.480769</v>
       </c>
       <c r="O95" s="28" t="n">
-        <v>0.627435</v>
+        <v>0.627171</v>
       </c>
       <c r="P95" s="28" t="n"/>
       <c r="Q95" s="28" t="n">
-        <v>0.146666</v>
+        <v>0.146402</v>
       </c>
       <c r="R95" s="26" t="n">
         <v>93</v>
@@ -28649,7 +28697,7 @@
       </c>
       <c r="BA95" s="24" t="inlineStr">
         <is>
-          <t>326a42c58f2a208dee1dc4f634e9901156f475883f7f16a3237a5e1b513fa5f9</t>
+          <t>d3791916ff32605dd2265e280637577dccc694ea8768ae90edb98370e9029821</t>
         </is>
       </c>
       <c r="BB95" s="24" t="inlineStr">
@@ -28664,7 +28712,7 @@
       </c>
       <c r="BD95" s="24" t="inlineStr">
         <is>
-          <t>326a42c58f2a208dee1dc4f634e9901156f475883f7f16a3237a5e1b513fa5f9</t>
+          <t>d3791916ff32605dd2265e280637577dccc694ea8768ae90edb98370e9029821</t>
         </is>
       </c>
       <c r="BE95" s="24" t="inlineStr">
@@ -28684,7 +28732,7 @@
       </c>
       <c r="BH95" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:23:57.410433Z</t>
+          <t>2026-08-07T18:31:08.974236Z</t>
         </is>
       </c>
       <c r="BI95" s="24" t="inlineStr">
@@ -28742,12 +28790,12 @@
     <row r="96" ht="36" customHeight="1">
       <c r="A96" s="24" t="inlineStr">
         <is>
-          <t>f59174839ac648e6</t>
+          <t>17f0547a70a14a3d</t>
         </is>
       </c>
       <c r="B96" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:24:10.407714Z</t>
+          <t>2026-08-07T18:31:20.691239Z</t>
         </is>
       </c>
       <c r="C96" s="24" t="inlineStr">
@@ -28801,11 +28849,11 @@
         <v>0.579832</v>
       </c>
       <c r="O96" s="28" t="n">
-        <v>0.588198</v>
+        <v>0.588376</v>
       </c>
       <c r="P96" s="28" t="n"/>
       <c r="Q96" s="28" t="n">
-        <v>0.008366</v>
+        <v>0.008544</v>
       </c>
       <c r="R96" s="26" t="n">
         <v>24</v>
@@ -28918,7 +28966,7 @@
       </c>
       <c r="BA96" s="24" t="inlineStr">
         <is>
-          <t>326a42c58f2a208dee1dc4f634e9901156f475883f7f16a3237a5e1b513fa5f9</t>
+          <t>d3791916ff32605dd2265e280637577dccc694ea8768ae90edb98370e9029821</t>
         </is>
       </c>
       <c r="BB96" s="24" t="inlineStr">
@@ -28933,7 +28981,7 @@
       </c>
       <c r="BD96" s="24" t="inlineStr">
         <is>
-          <t>326a42c58f2a208dee1dc4f634e9901156f475883f7f16a3237a5e1b513fa5f9</t>
+          <t>d3791916ff32605dd2265e280637577dccc694ea8768ae90edb98370e9029821</t>
         </is>
       </c>
       <c r="BE96" s="24" t="inlineStr">
@@ -28953,7 +29001,7 @@
       </c>
       <c r="BH96" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:23:57.916632Z</t>
+          <t>2026-08-07T18:31:09.548140Z</t>
         </is>
       </c>
       <c r="BI96" s="24" t="inlineStr">
@@ -29011,12 +29059,12 @@
     <row r="97" ht="36" customHeight="1">
       <c r="A97" s="24" t="inlineStr">
         <is>
-          <t>21740095129f409b</t>
+          <t>d58565aa96cd4a8c</t>
         </is>
       </c>
       <c r="B97" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:24:10.407714Z</t>
+          <t>2026-08-07T18:31:20.691239Z</t>
         </is>
       </c>
       <c r="C97" s="24" t="inlineStr">
@@ -29070,11 +29118,11 @@
         <v>0.690402</v>
       </c>
       <c r="O97" s="28" t="n">
-        <v>0.650821</v>
+        <v>0.650938</v>
       </c>
       <c r="P97" s="28" t="n"/>
       <c r="Q97" s="28" t="n">
-        <v>-0.039581</v>
+        <v>-0.039464</v>
       </c>
       <c r="R97" s="26" t="n">
         <v>0</v>
@@ -29187,7 +29235,7 @@
       </c>
       <c r="BA97" s="24" t="inlineStr">
         <is>
-          <t>326a42c58f2a208dee1dc4f634e9901156f475883f7f16a3237a5e1b513fa5f9</t>
+          <t>d3791916ff32605dd2265e280637577dccc694ea8768ae90edb98370e9029821</t>
         </is>
       </c>
       <c r="BB97" s="24" t="inlineStr">
@@ -29202,7 +29250,7 @@
       </c>
       <c r="BD97" s="24" t="inlineStr">
         <is>
-          <t>326a42c58f2a208dee1dc4f634e9901156f475883f7f16a3237a5e1b513fa5f9</t>
+          <t>d3791916ff32605dd2265e280637577dccc694ea8768ae90edb98370e9029821</t>
         </is>
       </c>
       <c r="BE97" s="24" t="inlineStr">
@@ -29222,7 +29270,7 @@
       </c>
       <c r="BH97" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:23:59.012458Z</t>
+          <t>2026-08-07T18:31:10.581328Z</t>
         </is>
       </c>
       <c r="BI97" s="24" t="inlineStr">
@@ -29280,12 +29328,12 @@
     <row r="98" ht="36" customHeight="1">
       <c r="A98" s="24" t="inlineStr">
         <is>
-          <t>a0f09920539e48a8</t>
+          <t>54e2eb768a9e49e9</t>
         </is>
       </c>
       <c r="B98" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:24:10.407714Z</t>
+          <t>2026-08-07T18:31:20.691239Z</t>
         </is>
       </c>
       <c r="C98" s="24" t="inlineStr">
@@ -29330,23 +29378,23 @@
         </is>
       </c>
       <c r="L98" s="26" t="n">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="M98" s="27" t="n">
-        <v>2.13</v>
+        <v>2.04</v>
       </c>
       <c r="N98" s="28" t="n">
-        <v>0.469484</v>
+        <v>0.490196</v>
       </c>
       <c r="O98" s="28" t="n">
-        <v>0.605705</v>
+        <v>0.605845</v>
       </c>
       <c r="P98" s="28" t="n"/>
       <c r="Q98" s="28" t="n">
-        <v>0.136221</v>
+        <v>0.115649</v>
       </c>
       <c r="R98" s="26" t="n">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="S98" s="29" t="n">
         <v>1.25</v>
@@ -29372,7 +29420,7 @@
       <c r="AD98" s="24" t="n"/>
       <c r="AE98" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4700 (market_slug=aec-lol-t1-hle-2026-08-08).</t>
+          <t>Neutral Elo baseline; executable ask 0.4900 (market_slug=aec-lol-t1-hle-2026-08-08).</t>
         </is>
       </c>
       <c r="AF98" s="31" t="inlineStr">
@@ -29456,7 +29504,7 @@
       </c>
       <c r="BA98" s="24" t="inlineStr">
         <is>
-          <t>326a42c58f2a208dee1dc4f634e9901156f475883f7f16a3237a5e1b513fa5f9</t>
+          <t>d3791916ff32605dd2265e280637577dccc694ea8768ae90edb98370e9029821</t>
         </is>
       </c>
       <c r="BB98" s="24" t="inlineStr">
@@ -29471,7 +29519,7 @@
       </c>
       <c r="BD98" s="24" t="inlineStr">
         <is>
-          <t>326a42c58f2a208dee1dc4f634e9901156f475883f7f16a3237a5e1b513fa5f9</t>
+          <t>d3791916ff32605dd2265e280637577dccc694ea8768ae90edb98370e9029821</t>
         </is>
       </c>
       <c r="BE98" s="24" t="inlineStr">
@@ -29491,7 +29539,7 @@
       </c>
       <c r="BH98" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:23:59.567486Z</t>
+          <t>2026-08-07T18:31:11.080798Z</t>
         </is>
       </c>
       <c r="BI98" s="24" t="inlineStr">
@@ -29501,13 +29549,13 @@
       </c>
       <c r="BJ98" s="25" t="n"/>
       <c r="BK98" s="26" t="n">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="BL98" s="27" t="n">
-        <v>2.13</v>
+        <v>2.04</v>
       </c>
       <c r="BM98" s="28" t="n">
-        <v>0.469484</v>
+        <v>0.490196</v>
       </c>
       <c r="BN98" s="28" t="n"/>
       <c r="BO98" s="28" t="n"/>
@@ -29549,12 +29597,12 @@
     <row r="99" ht="36" customHeight="1">
       <c r="A99" s="24" t="inlineStr">
         <is>
-          <t>ce56f966fcba4867</t>
+          <t>ec7b84f1b105483f</t>
         </is>
       </c>
       <c r="B99" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:24:10.407714Z</t>
+          <t>2026-08-07T18:31:20.691239Z</t>
         </is>
       </c>
       <c r="C99" s="24" t="inlineStr">
@@ -29608,11 +29656,11 @@
         <v>0.6</v>
       </c>
       <c r="O99" s="28" t="n">
-        <v>0.540737</v>
+        <v>0.540926</v>
       </c>
       <c r="P99" s="28" t="n"/>
       <c r="Q99" s="28" t="n">
-        <v>-0.059263</v>
+        <v>-0.059074</v>
       </c>
       <c r="R99" s="26" t="n">
         <v>0</v>
@@ -29725,7 +29773,7 @@
       </c>
       <c r="BA99" s="24" t="inlineStr">
         <is>
-          <t>326a42c58f2a208dee1dc4f634e9901156f475883f7f16a3237a5e1b513fa5f9</t>
+          <t>d3791916ff32605dd2265e280637577dccc694ea8768ae90edb98370e9029821</t>
         </is>
       </c>
       <c r="BB99" s="24" t="inlineStr">
@@ -29740,7 +29788,7 @@
       </c>
       <c r="BD99" s="24" t="inlineStr">
         <is>
-          <t>326a42c58f2a208dee1dc4f634e9901156f475883f7f16a3237a5e1b513fa5f9</t>
+          <t>d3791916ff32605dd2265e280637577dccc694ea8768ae90edb98370e9029821</t>
         </is>
       </c>
       <c r="BE99" s="24" t="inlineStr">
@@ -29760,7 +29808,7 @@
       </c>
       <c r="BH99" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:24:00.091597Z</t>
+          <t>2026-08-07T18:31:11.745061Z</t>
         </is>
       </c>
       <c r="BI99" s="24" t="inlineStr">
@@ -29818,12 +29866,12 @@
     <row r="100" ht="36" customHeight="1">
       <c r="A100" s="24" t="inlineStr">
         <is>
-          <t>32eada431acd483a</t>
+          <t>cff7e6536d5345a7</t>
         </is>
       </c>
       <c r="B100" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:24:10.407714Z</t>
+          <t>2026-08-07T18:31:20.691239Z</t>
         </is>
       </c>
       <c r="C100" s="24" t="inlineStr">
@@ -29868,26 +29916,26 @@
         </is>
       </c>
       <c r="L100" s="26" t="n">
-        <v>-156</v>
+        <v>-138</v>
       </c>
       <c r="M100" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.724638</v>
       </c>
       <c r="N100" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.579832</v>
       </c>
       <c r="O100" s="28" t="n">
-        <v>0.675044</v>
+        <v>0.675074</v>
       </c>
       <c r="P100" s="28" t="n"/>
       <c r="Q100" s="28" t="n">
-        <v>0.06566900000000001</v>
+        <v>0.09524199999999999</v>
       </c>
       <c r="R100" s="26" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="S100" s="29" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="T100" s="24" t="inlineStr">
         <is>
@@ -29910,7 +29958,7 @@
       <c r="AD100" s="24" t="n"/>
       <c r="AE100" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-lol-gls-els-2026-08-08).</t>
+          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-lol-gls-els-2026-08-08).</t>
         </is>
       </c>
       <c r="AF100" s="31" t="inlineStr">
@@ -29928,7 +29976,7 @@
       <c r="AJ100" s="31" t="n"/>
       <c r="AK100" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL100" s="26" t="n">
@@ -29936,17 +29984,17 @@
       </c>
       <c r="AM100" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN100" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO100" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_WINNER_OVERVALUED</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP100" s="24" t="inlineStr">
@@ -29994,7 +30042,7 @@
       </c>
       <c r="BA100" s="24" t="inlineStr">
         <is>
-          <t>326a42c58f2a208dee1dc4f634e9901156f475883f7f16a3237a5e1b513fa5f9</t>
+          <t>d3791916ff32605dd2265e280637577dccc694ea8768ae90edb98370e9029821</t>
         </is>
       </c>
       <c r="BB100" s="24" t="inlineStr">
@@ -30009,7 +30057,7 @@
       </c>
       <c r="BD100" s="24" t="inlineStr">
         <is>
-          <t>326a42c58f2a208dee1dc4f634e9901156f475883f7f16a3237a5e1b513fa5f9</t>
+          <t>d3791916ff32605dd2265e280637577dccc694ea8768ae90edb98370e9029821</t>
         </is>
       </c>
       <c r="BE100" s="24" t="inlineStr">
@@ -30029,7 +30077,7 @@
       </c>
       <c r="BH100" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:24:02.682012Z</t>
+          <t>2026-08-07T18:31:14.111862Z</t>
         </is>
       </c>
       <c r="BI100" s="24" t="inlineStr">
@@ -30039,13 +30087,13 @@
       </c>
       <c r="BJ100" s="25" t="n"/>
       <c r="BK100" s="26" t="n">
-        <v>-156</v>
+        <v>-138</v>
       </c>
       <c r="BL100" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.724638</v>
       </c>
       <c r="BM100" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.579832</v>
       </c>
       <c r="BN100" s="28" t="n"/>
       <c r="BO100" s="28" t="n"/>
@@ -30087,12 +30135,12 @@
     <row r="101" ht="36" customHeight="1">
       <c r="A101" s="24" t="inlineStr">
         <is>
-          <t>5f24d514d8034eea</t>
+          <t>2a5f1289c7644293</t>
         </is>
       </c>
       <c r="B101" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:24:10.407714Z</t>
+          <t>2026-08-07T18:31:20.691239Z</t>
         </is>
       </c>
       <c r="C101" s="24" t="inlineStr">
@@ -30137,23 +30185,23 @@
         </is>
       </c>
       <c r="L101" s="26" t="n">
-        <v>-122</v>
+        <v>-127</v>
       </c>
       <c r="M101" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.787402</v>
       </c>
       <c r="N101" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="O101" s="28" t="n">
-        <v>0.517831</v>
+        <v>0.518025</v>
       </c>
       <c r="P101" s="28" t="n"/>
       <c r="Q101" s="28" t="n">
-        <v>-0.031719</v>
+        <v>-0.041446</v>
       </c>
       <c r="R101" s="26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S101" s="29" t="n">
         <v>0</v>
@@ -30179,7 +30227,7 @@
       <c r="AD101" s="24" t="n"/>
       <c r="AE101" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-lol-kcbs-pcs-2026-08-08).</t>
+          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-lol-kcbs-pcs-2026-08-08).</t>
         </is>
       </c>
       <c r="AF101" s="31" t="inlineStr">
@@ -30263,7 +30311,7 @@
       </c>
       <c r="BA101" s="24" t="inlineStr">
         <is>
-          <t>326a42c58f2a208dee1dc4f634e9901156f475883f7f16a3237a5e1b513fa5f9</t>
+          <t>d3791916ff32605dd2265e280637577dccc694ea8768ae90edb98370e9029821</t>
         </is>
       </c>
       <c r="BB101" s="24" t="inlineStr">
@@ -30278,7 +30326,7 @@
       </c>
       <c r="BD101" s="24" t="inlineStr">
         <is>
-          <t>326a42c58f2a208dee1dc4f634e9901156f475883f7f16a3237a5e1b513fa5f9</t>
+          <t>d3791916ff32605dd2265e280637577dccc694ea8768ae90edb98370e9029821</t>
         </is>
       </c>
       <c r="BE101" s="24" t="inlineStr">
@@ -30298,7 +30346,7 @@
       </c>
       <c r="BH101" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:24:04.554182Z</t>
+          <t>2026-08-07T18:31:15.520994Z</t>
         </is>
       </c>
       <c r="BI101" s="24" t="inlineStr">
@@ -30308,13 +30356,13 @@
       </c>
       <c r="BJ101" s="25" t="n"/>
       <c r="BK101" s="26" t="n">
-        <v>-122</v>
+        <v>-127</v>
       </c>
       <c r="BL101" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.787402</v>
       </c>
       <c r="BM101" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="BN101" s="28" t="n"/>
       <c r="BO101" s="28" t="n"/>
@@ -30356,12 +30404,12 @@
     <row r="102" ht="36" customHeight="1">
       <c r="A102" s="24" t="inlineStr">
         <is>
-          <t>6121701a5c0143c7</t>
+          <t>a78a6552bcc84faf</t>
         </is>
       </c>
       <c r="B102" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:24:10.407714Z</t>
+          <t>2026-08-07T18:31:20.691239Z</t>
         </is>
       </c>
       <c r="C102" s="24" t="inlineStr">
@@ -30415,11 +30463,11 @@
         <v>0.609375</v>
       </c>
       <c r="O102" s="28" t="n">
-        <v>0.638142</v>
+        <v>0.63815</v>
       </c>
       <c r="P102" s="28" t="n"/>
       <c r="Q102" s="28" t="n">
-        <v>0.028767</v>
+        <v>0.028775</v>
       </c>
       <c r="R102" s="26" t="n">
         <v>34</v>
@@ -30532,7 +30580,7 @@
       </c>
       <c r="BA102" s="24" t="inlineStr">
         <is>
-          <t>326a42c58f2a208dee1dc4f634e9901156f475883f7f16a3237a5e1b513fa5f9</t>
+          <t>d3791916ff32605dd2265e280637577dccc694ea8768ae90edb98370e9029821</t>
         </is>
       </c>
       <c r="BB102" s="24" t="inlineStr">
@@ -30547,7 +30595,7 @@
       </c>
       <c r="BD102" s="24" t="inlineStr">
         <is>
-          <t>326a42c58f2a208dee1dc4f634e9901156f475883f7f16a3237a5e1b513fa5f9</t>
+          <t>d3791916ff32605dd2265e280637577dccc694ea8768ae90edb98370e9029821</t>
         </is>
       </c>
       <c r="BE102" s="24" t="inlineStr">
@@ -30567,7 +30615,7 @@
       </c>
       <c r="BH102" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:24:05.084455Z</t>
+          <t>2026-08-07T18:31:16.025918Z</t>
         </is>
       </c>
       <c r="BI102" s="24" t="inlineStr">
@@ -30625,12 +30673,12 @@
     <row r="103" ht="36" customHeight="1">
       <c r="A103" s="24" t="inlineStr">
         <is>
-          <t>da8c8381138b4999</t>
+          <t>3ad7acaef68745a4</t>
         </is>
       </c>
       <c r="B103" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:24:10.407714Z</t>
+          <t>2026-08-07T18:31:20.691239Z</t>
         </is>
       </c>
       <c r="C103" s="24" t="inlineStr">
@@ -30684,11 +30732,11 @@
         <v>0.65035</v>
       </c>
       <c r="O103" s="28" t="n">
-        <v>0.676056</v>
+        <v>0.6757919999999999</v>
       </c>
       <c r="P103" s="28" t="n"/>
       <c r="Q103" s="28" t="n">
-        <v>0.025706</v>
+        <v>0.025442</v>
       </c>
       <c r="R103" s="26" t="n">
         <v>33</v>
@@ -30801,7 +30849,7 @@
       </c>
       <c r="BA103" s="24" t="inlineStr">
         <is>
-          <t>326a42c58f2a208dee1dc4f634e9901156f475883f7f16a3237a5e1b513fa5f9</t>
+          <t>d3791916ff32605dd2265e280637577dccc694ea8768ae90edb98370e9029821</t>
         </is>
       </c>
       <c r="BB103" s="24" t="inlineStr">
@@ -30816,7 +30864,7 @@
       </c>
       <c r="BD103" s="24" t="inlineStr">
         <is>
-          <t>326a42c58f2a208dee1dc4f634e9901156f475883f7f16a3237a5e1b513fa5f9</t>
+          <t>d3791916ff32605dd2265e280637577dccc694ea8768ae90edb98370e9029821</t>
         </is>
       </c>
       <c r="BE103" s="24" t="inlineStr">
@@ -30836,7 +30884,7 @@
       </c>
       <c r="BH103" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:24:07.403776Z</t>
+          <t>2026-08-07T18:31:17.358650Z</t>
         </is>
       </c>
       <c r="BI103" s="24" t="inlineStr">
@@ -30894,12 +30942,12 @@
     <row r="104" ht="36" customHeight="1">
       <c r="A104" s="24" t="inlineStr">
         <is>
-          <t>9ce26f2767184735</t>
+          <t>dc866fe058bf46cd</t>
         </is>
       </c>
       <c r="B104" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:24:10.407714Z</t>
+          <t>2026-08-07T18:31:20.691239Z</t>
         </is>
       </c>
       <c r="C104" s="24" t="inlineStr">
@@ -30953,11 +31001,11 @@
         <v>0.490196</v>
       </c>
       <c r="O104" s="28" t="n">
-        <v>0.692705</v>
+        <v>0.6928530000000001</v>
       </c>
       <c r="P104" s="28" t="n"/>
       <c r="Q104" s="28" t="n">
-        <v>0.202509</v>
+        <v>0.202657</v>
       </c>
       <c r="R104" s="26" t="n">
         <v>100</v>
@@ -31070,7 +31118,7 @@
       </c>
       <c r="BA104" s="24" t="inlineStr">
         <is>
-          <t>326a42c58f2a208dee1dc4f634e9901156f475883f7f16a3237a5e1b513fa5f9</t>
+          <t>d3791916ff32605dd2265e280637577dccc694ea8768ae90edb98370e9029821</t>
         </is>
       </c>
       <c r="BB104" s="24" t="inlineStr">
@@ -31085,7 +31133,7 @@
       </c>
       <c r="BD104" s="24" t="inlineStr">
         <is>
-          <t>326a42c58f2a208dee1dc4f634e9901156f475883f7f16a3237a5e1b513fa5f9</t>
+          <t>d3791916ff32605dd2265e280637577dccc694ea8768ae90edb98370e9029821</t>
         </is>
       </c>
       <c r="BE104" s="24" t="inlineStr">
@@ -31105,7 +31153,7 @@
       </c>
       <c r="BH104" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:24:07.921330Z</t>
+          <t>2026-08-07T18:31:18.039096Z</t>
         </is>
       </c>
       <c r="BI104" s="24" t="inlineStr">
@@ -31163,12 +31211,12 @@
     <row r="105" ht="36" customHeight="1">
       <c r="A105" s="24" t="inlineStr">
         <is>
-          <t>fb8053ca87aa4106</t>
+          <t>fb3f04cdc01d491c</t>
         </is>
       </c>
       <c r="B105" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:24:10.407714Z</t>
+          <t>2026-08-07T18:31:20.691239Z</t>
         </is>
       </c>
       <c r="C105" s="24" t="inlineStr">
@@ -31222,11 +31270,11 @@
         <v>0.690402</v>
       </c>
       <c r="O105" s="28" t="n">
-        <v>0.586349</v>
+        <v>0.564656</v>
       </c>
       <c r="P105" s="28" t="n"/>
       <c r="Q105" s="28" t="n">
-        <v>-0.104053</v>
+        <v>-0.125746</v>
       </c>
       <c r="R105" s="26" t="n">
         <v>0</v>
@@ -31339,7 +31387,7 @@
       </c>
       <c r="BA105" s="24" t="inlineStr">
         <is>
-          <t>326a42c58f2a208dee1dc4f634e9901156f475883f7f16a3237a5e1b513fa5f9</t>
+          <t>d3791916ff32605dd2265e280637577dccc694ea8768ae90edb98370e9029821</t>
         </is>
       </c>
       <c r="BB105" s="24" t="inlineStr">
@@ -31354,7 +31402,7 @@
       </c>
       <c r="BD105" s="24" t="inlineStr">
         <is>
-          <t>326a42c58f2a208dee1dc4f634e9901156f475883f7f16a3237a5e1b513fa5f9</t>
+          <t>d3791916ff32605dd2265e280637577dccc694ea8768ae90edb98370e9029821</t>
         </is>
       </c>
       <c r="BE105" s="24" t="inlineStr">
@@ -31374,7 +31422,7 @@
       </c>
       <c r="BH105" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:24:08.482800Z</t>
+          <t>2026-08-07T18:31:18.546666Z</t>
         </is>
       </c>
       <c r="BI105" s="24" t="inlineStr">
